--- a/historique_joueurs.xlsx
+++ b/historique_joueurs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H957"/>
+  <dimension ref="A1:H1066"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31806,6 +31806,3660 @@
         <v>0</v>
       </c>
     </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>Filipinho95</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>Filipe</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E958" t="n">
+        <v>1</v>
+      </c>
+      <c r="F958" t="n">
+        <v>410</v>
+      </c>
+      <c r="G958" t="n">
+        <v>4</v>
+      </c>
+      <c r="H958" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>MargauxCtln</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>Margaux</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E959" t="n">
+        <v>2</v>
+      </c>
+      <c r="F959" t="n">
+        <v>376</v>
+      </c>
+      <c r="G959" t="n">
+        <v>4</v>
+      </c>
+      <c r="H959" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>Mamad_Shelter</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>Mamadou</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E960" t="n">
+        <v>3</v>
+      </c>
+      <c r="F960" t="n">
+        <v>376</v>
+      </c>
+      <c r="G960" t="n">
+        <v>4</v>
+      </c>
+      <c r="H960" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>MagicMath</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>Mathieu</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E961" t="n">
+        <v>4</v>
+      </c>
+      <c r="F961" t="n">
+        <v>376</v>
+      </c>
+      <c r="G961" t="n">
+        <v>4</v>
+      </c>
+      <c r="H961" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>WalidSiuuuuu</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>Walid</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E962" t="n">
+        <v>5</v>
+      </c>
+      <c r="F962" t="n">
+        <v>356</v>
+      </c>
+      <c r="G962" t="n">
+        <v>4</v>
+      </c>
+      <c r="H962" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>DJOSWA</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oswaina </t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E963" t="n">
+        <v>6</v>
+      </c>
+      <c r="F963" t="n">
+        <v>356</v>
+      </c>
+      <c r="G963" t="n">
+        <v>4</v>
+      </c>
+      <c r="H963" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>SID-F-ANDRE</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>Denis</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E964" t="n">
+        <v>7</v>
+      </c>
+      <c r="F964" t="n">
+        <v>355</v>
+      </c>
+      <c r="G964" t="n">
+        <v>3</v>
+      </c>
+      <c r="H964" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>ChrisKr1Deg1</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>christophe</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E965" t="n">
+        <v>8</v>
+      </c>
+      <c r="F965" t="n">
+        <v>323</v>
+      </c>
+      <c r="G965" t="n">
+        <v>2</v>
+      </c>
+      <c r="H965" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>Coucoucassecou</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>Brayen</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E966" t="n">
+        <v>9</v>
+      </c>
+      <c r="F966" t="n">
+        <v>322</v>
+      </c>
+      <c r="G966" t="n">
+        <v>3</v>
+      </c>
+      <c r="H966" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>Paulasipi1998</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E967" t="n">
+        <v>10</v>
+      </c>
+      <c r="F967" t="n">
+        <v>322</v>
+      </c>
+      <c r="G967" t="n">
+        <v>3</v>
+      </c>
+      <c r="H967" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>Panaff</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>Panaf</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E968" t="n">
+        <v>11</v>
+      </c>
+      <c r="F968" t="n">
+        <v>315</v>
+      </c>
+      <c r="G968" t="n">
+        <v>3</v>
+      </c>
+      <c r="H968" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>Kaliced</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>Kalice</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E969" t="n">
+        <v>12</v>
+      </c>
+      <c r="F969" t="n">
+        <v>302</v>
+      </c>
+      <c r="G969" t="n">
+        <v>3</v>
+      </c>
+      <c r="H969" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>FRHTCTD10</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>Candice</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E970" t="n">
+        <v>13</v>
+      </c>
+      <c r="F970" t="n">
+        <v>282</v>
+      </c>
+      <c r="G970" t="n">
+        <v>3</v>
+      </c>
+      <c r="H970" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>Mr-Worldwide</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E971" t="n">
+        <v>14</v>
+      </c>
+      <c r="F971" t="n">
+        <v>280</v>
+      </c>
+      <c r="G971" t="n">
+        <v>3</v>
+      </c>
+      <c r="H971" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>Fethinho</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>Fethi</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E972" t="n">
+        <v>15</v>
+      </c>
+      <c r="F972" t="n">
+        <v>280</v>
+      </c>
+      <c r="G972" t="n">
+        <v>3</v>
+      </c>
+      <c r="H972" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>Ouiouiausoleil</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>Ouissal</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E973" t="n">
+        <v>16</v>
+      </c>
+      <c r="F973" t="n">
+        <v>280</v>
+      </c>
+      <c r="G973" t="n">
+        <v>3</v>
+      </c>
+      <c r="H973" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>BOUGA#2JGXP</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>BOUGA</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E974" t="n">
+        <v>17</v>
+      </c>
+      <c r="F974" t="n">
+        <v>260</v>
+      </c>
+      <c r="G974" t="n">
+        <v>3</v>
+      </c>
+      <c r="H974" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>Anais757817</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>Anaïs</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E975" t="n">
+        <v>18</v>
+      </c>
+      <c r="F975" t="n">
+        <v>260</v>
+      </c>
+      <c r="G975" t="n">
+        <v>3</v>
+      </c>
+      <c r="H975" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>MatuRenard</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>Mathias</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr"/>
+      <c r="E976" t="n">
+        <v>19</v>
+      </c>
+      <c r="F976" t="n">
+        <v>259</v>
+      </c>
+      <c r="G976" t="n">
+        <v>3</v>
+      </c>
+      <c r="H976" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>Liliuus</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>Lilia</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E977" t="n">
+        <v>20</v>
+      </c>
+      <c r="F977" t="n">
+        <v>259</v>
+      </c>
+      <c r="G977" t="n">
+        <v>3</v>
+      </c>
+      <c r="H977" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>Ppo28</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>Prescylla</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr"/>
+      <c r="E978" t="n">
+        <v>21</v>
+      </c>
+      <c r="F978" t="n">
+        <v>259</v>
+      </c>
+      <c r="G978" t="n">
+        <v>3</v>
+      </c>
+      <c r="H978" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>Gronaldo_95</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>Gronaldo</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E979" t="n">
+        <v>22</v>
+      </c>
+      <c r="F979" t="n">
+        <v>239</v>
+      </c>
+      <c r="G979" t="n">
+        <v>3</v>
+      </c>
+      <c r="H979" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>Devilrock95</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E980" t="n">
+        <v>23</v>
+      </c>
+      <c r="F980" t="n">
+        <v>239</v>
+      </c>
+      <c r="G980" t="n">
+        <v>3</v>
+      </c>
+      <c r="H980" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>Ninaaaa</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>Nina</t>
+        </is>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E981" t="n">
+        <v>24</v>
+      </c>
+      <c r="F981" t="n">
+        <v>239</v>
+      </c>
+      <c r="G981" t="n">
+        <v>3</v>
+      </c>
+      <c r="H981" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>Cleem22</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>Clemence</t>
+        </is>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E982" t="n">
+        <v>25</v>
+      </c>
+      <c r="F982" t="n">
+        <v>239</v>
+      </c>
+      <c r="G982" t="n">
+        <v>3</v>
+      </c>
+      <c r="H982" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>catherine#5FRTD</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>catherine</t>
+        </is>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E983" t="n">
+        <v>26</v>
+      </c>
+      <c r="F983" t="n">
+        <v>239</v>
+      </c>
+      <c r="G983" t="n">
+        <v>3</v>
+      </c>
+      <c r="H983" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>Maruyama</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>Gabrielle</t>
+        </is>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E984" t="n">
+        <v>27</v>
+      </c>
+      <c r="F984" t="n">
+        <v>239</v>
+      </c>
+      <c r="G984" t="n">
+        <v>3</v>
+      </c>
+      <c r="H984" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>Leandrocp</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>Leandro</t>
+        </is>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E985" t="n">
+        <v>28</v>
+      </c>
+      <c r="F985" t="n">
+        <v>239</v>
+      </c>
+      <c r="G985" t="n">
+        <v>3</v>
+      </c>
+      <c r="H985" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>Marion1822</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>Marion</t>
+        </is>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E986" t="n">
+        <v>29</v>
+      </c>
+      <c r="F986" t="n">
+        <v>239</v>
+      </c>
+      <c r="G986" t="n">
+        <v>3</v>
+      </c>
+      <c r="H986" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>chaychaychay</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>Chaymaa</t>
+        </is>
+      </c>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E987" t="n">
+        <v>30</v>
+      </c>
+      <c r="F987" t="n">
+        <v>239</v>
+      </c>
+      <c r="G987" t="n">
+        <v>3</v>
+      </c>
+      <c r="H987" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>WIL1610</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>William</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E988" t="n">
+        <v>31</v>
+      </c>
+      <c r="F988" t="n">
+        <v>233</v>
+      </c>
+      <c r="G988" t="n">
+        <v>2</v>
+      </c>
+      <c r="H988" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>Erwan#4G91X</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>Erwan</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E989" t="n">
+        <v>32</v>
+      </c>
+      <c r="F989" t="n">
+        <v>219</v>
+      </c>
+      <c r="G989" t="n">
+        <v>3</v>
+      </c>
+      <c r="H989" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>GLR_PRIME</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>Gabriel</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E990" t="n">
+        <v>33</v>
+      </c>
+      <c r="F990" t="n">
+        <v>219</v>
+      </c>
+      <c r="G990" t="n">
+        <v>3</v>
+      </c>
+      <c r="H990" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>Exia95</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E991" t="n">
+        <v>34</v>
+      </c>
+      <c r="F991" t="n">
+        <v>212</v>
+      </c>
+      <c r="G991" t="n">
+        <v>2</v>
+      </c>
+      <c r="H991" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>Matt#4B4CU</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E992" t="n">
+        <v>35</v>
+      </c>
+      <c r="F992" t="n">
+        <v>211</v>
+      </c>
+      <c r="G992" t="n">
+        <v>2</v>
+      </c>
+      <c r="H992" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>dian-bgt</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>Diane</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E993" t="n">
+        <v>36</v>
+      </c>
+      <c r="F993" t="n">
+        <v>206</v>
+      </c>
+      <c r="G993" t="n">
+        <v>2</v>
+      </c>
+      <c r="H993" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>LilianeB</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liliane </t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E994" t="n">
+        <v>37</v>
+      </c>
+      <c r="F994" t="n">
+        <v>206</v>
+      </c>
+      <c r="G994" t="n">
+        <v>2</v>
+      </c>
+      <c r="H994" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>Julie</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr"/>
+      <c r="E995" t="n">
+        <v>38</v>
+      </c>
+      <c r="F995" t="n">
+        <v>206</v>
+      </c>
+      <c r="G995" t="n">
+        <v>2</v>
+      </c>
+      <c r="H995" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>Romain_JO</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>Romain J</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E996" t="n">
+        <v>39</v>
+      </c>
+      <c r="F996" t="n">
+        <v>191</v>
+      </c>
+      <c r="G996" t="n">
+        <v>2</v>
+      </c>
+      <c r="H996" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>JeremFZ</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>Jérémy</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E997" t="n">
+        <v>40</v>
+      </c>
+      <c r="F997" t="n">
+        <v>191</v>
+      </c>
+      <c r="G997" t="n">
+        <v>2</v>
+      </c>
+      <c r="H997" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>AudreyB225</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>Audrey</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E998" t="n">
+        <v>41</v>
+      </c>
+      <c r="F998" t="n">
+        <v>190</v>
+      </c>
+      <c r="G998" t="n">
+        <v>2</v>
+      </c>
+      <c r="H998" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>BadrLeo</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>Badr Leo</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E999" t="n">
+        <v>42</v>
+      </c>
+      <c r="F999" t="n">
+        <v>186</v>
+      </c>
+      <c r="G999" t="n">
+        <v>2</v>
+      </c>
+      <c r="H999" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>YassineZ95</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>Yassine Z</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E1000" t="n">
+        <v>43</v>
+      </c>
+      <c r="F1000" t="n">
+        <v>186</v>
+      </c>
+      <c r="G1000" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1000" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>Ilan_260_</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ilann </t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1001" t="n">
+        <v>44</v>
+      </c>
+      <c r="F1001" t="n">
+        <v>185</v>
+      </c>
+      <c r="G1001" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1001" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>abihuts</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>Antonio Moctezuma</t>
+        </is>
+      </c>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1002" t="n">
+        <v>45</v>
+      </c>
+      <c r="F1002" t="n">
+        <v>172</v>
+      </c>
+      <c r="G1002" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1002" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>Chadia__</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>Chadia</t>
+        </is>
+      </c>
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1003" t="n">
+        <v>46</v>
+      </c>
+      <c r="F1003" t="n">
+        <v>170</v>
+      </c>
+      <c r="G1003" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1003" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>Stephbreton</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>STEPHANE</t>
+        </is>
+      </c>
+      <c r="D1004" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1004" t="n">
+        <v>47</v>
+      </c>
+      <c r="F1004" t="n">
+        <v>166</v>
+      </c>
+      <c r="G1004" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1004" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>GOAT#UE2WM8M9</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>Marilena</t>
+        </is>
+      </c>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1005" t="n">
+        <v>48</v>
+      </c>
+      <c r="F1005" t="n">
+        <v>165</v>
+      </c>
+      <c r="G1005" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1005" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>Ceciledp</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>Cécile</t>
+        </is>
+      </c>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1006" t="n">
+        <v>49</v>
+      </c>
+      <c r="F1006" t="n">
+        <v>145</v>
+      </c>
+      <c r="G1006" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1006" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>Fuzo697</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1007" t="n">
+        <v>50</v>
+      </c>
+      <c r="F1007" t="n">
+        <v>145</v>
+      </c>
+      <c r="G1007" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1007" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>Yebri</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>Brieuc</t>
+        </is>
+      </c>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1008" t="n">
+        <v>51</v>
+      </c>
+      <c r="F1008" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1008" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1008" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>Leo_durable</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>Leo</t>
+        </is>
+      </c>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1009" t="n">
+        <v>52</v>
+      </c>
+      <c r="F1009" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1009" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1009" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>EmyEnzo</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>Emilie</t>
+        </is>
+      </c>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1010" t="n">
+        <v>53</v>
+      </c>
+      <c r="F1010" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1010" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1010" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>Priscilla#4LCAF</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>Priscilla</t>
+        </is>
+      </c>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1011" t="n">
+        <v>54</v>
+      </c>
+      <c r="F1011" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1011" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1011" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>Pipou931</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>Juliie</t>
+        </is>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1012" t="n">
+        <v>55</v>
+      </c>
+      <c r="F1012" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1012" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1012" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>Farah_One</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>Farah</t>
+        </is>
+      </c>
+      <c r="D1013" t="inlineStr"/>
+      <c r="E1013" t="n">
+        <v>56</v>
+      </c>
+      <c r="F1013" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1013" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1013" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>François</t>
+        </is>
+      </c>
+      <c r="D1014" t="inlineStr"/>
+      <c r="E1014" t="n">
+        <v>57</v>
+      </c>
+      <c r="F1014" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1014" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1014" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>Seesee</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>Selver</t>
+        </is>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1015" t="n">
+        <v>58</v>
+      </c>
+      <c r="F1015" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1015" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1015" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>lenaaik</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>Lénaïk</t>
+        </is>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1016" t="n">
+        <v>59</v>
+      </c>
+      <c r="F1016" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1016" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1016" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>C4M</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1017" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1017" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1017" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1017" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>Rosa_1009</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>Rosaline</t>
+        </is>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1018" t="n">
+        <v>61</v>
+      </c>
+      <c r="F1018" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1018" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1018" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>Elisewiss</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>Elise</t>
+        </is>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1019" t="n">
+        <v>62</v>
+      </c>
+      <c r="F1019" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1019" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1019" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>Soraya-Y</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>Soraya</t>
+        </is>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1020" t="n">
+        <v>63</v>
+      </c>
+      <c r="F1020" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1020" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1020" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>1993ahm</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>Ahmed</t>
+        </is>
+      </c>
+      <c r="D1021" t="inlineStr"/>
+      <c r="E1021" t="n">
+        <v>64</v>
+      </c>
+      <c r="F1021" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1021" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1021" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>MyriamAmr</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>Myriam</t>
+        </is>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1022" t="n">
+        <v>65</v>
+      </c>
+      <c r="F1022" t="n">
+        <v>137</v>
+      </c>
+      <c r="G1022" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1022" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>Timy</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1023" t="n">
+        <v>66</v>
+      </c>
+      <c r="F1023" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1023" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1023" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>JEVAISGAGNER10</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>Xavier</t>
+        </is>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1024" t="n">
+        <v>67</v>
+      </c>
+      <c r="F1024" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1024" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1024" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>HamzaG</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>Hamza</t>
+        </is>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1025" t="n">
+        <v>68</v>
+      </c>
+      <c r="F1025" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1025" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1025" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>LeaBrd</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>Léa</t>
+        </is>
+      </c>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1026" t="n">
+        <v>69</v>
+      </c>
+      <c r="F1026" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1026" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1026" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>davidd23</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D1027" t="inlineStr"/>
+      <c r="E1027" t="n">
+        <v>70</v>
+      </c>
+      <c r="F1027" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1027" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1027" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>Nonito20</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>Arnaud</t>
+        </is>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1028" t="n">
+        <v>71</v>
+      </c>
+      <c r="F1028" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1028" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1028" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1029" t="n">
+        <v>72</v>
+      </c>
+      <c r="F1029" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1029" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1029" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>Kolas</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1030" t="n">
+        <v>73</v>
+      </c>
+      <c r="F1030" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1030" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1030" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>Laetice2020</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>Laetitia</t>
+        </is>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1031" t="n">
+        <v>74</v>
+      </c>
+      <c r="F1031" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1031" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1031" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>Emilay</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>Émilie</t>
+        </is>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1032" t="n">
+        <v>75</v>
+      </c>
+      <c r="F1032" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1032" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1032" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>Lyzone</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>Lison</t>
+        </is>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1033" t="n">
+        <v>76</v>
+      </c>
+      <c r="F1033" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1033" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1033" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>Melissagzb</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>Melissa</t>
+        </is>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1034" t="n">
+        <v>77</v>
+      </c>
+      <c r="F1034" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1034" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1034" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>Marie__92</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>Marie</t>
+        </is>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1035" t="n">
+        <v>78</v>
+      </c>
+      <c r="F1035" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1035" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1035" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>K_Marp</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1036" t="n">
+        <v>79</v>
+      </c>
+      <c r="F1036" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1036" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1036" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>Cindie_JJA</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>Cindie</t>
+        </is>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1037" t="n">
+        <v>80</v>
+      </c>
+      <c r="F1037" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1037" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1037" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>JKInternational</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>Joachim</t>
+        </is>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1038" t="n">
+        <v>81</v>
+      </c>
+      <c r="F1038" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1038" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1038" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>GOAT#UE4U8KA6</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>Jean Baptiste</t>
+        </is>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1039" t="n">
+        <v>82</v>
+      </c>
+      <c r="F1039" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1039" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1039" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>goat#AD6GS</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>goat</t>
+        </is>
+      </c>
+      <c r="D1040" t="inlineStr"/>
+      <c r="E1040" t="n">
+        <v>83</v>
+      </c>
+      <c r="F1040" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1040" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1040" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>Camillewbl</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D1041" t="inlineStr"/>
+      <c r="E1041" t="n">
+        <v>84</v>
+      </c>
+      <c r="F1041" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1041" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1041" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>Emma_Noel</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>Emma</t>
+        </is>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1042" t="n">
+        <v>85</v>
+      </c>
+      <c r="F1042" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1042" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1042" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>RBTL</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>lea</t>
+        </is>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1043" t="n">
+        <v>86</v>
+      </c>
+      <c r="F1043" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1043" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1043" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>A-MOE</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>Françoise</t>
+        </is>
+      </c>
+      <c r="D1044" t="inlineStr"/>
+      <c r="E1044" t="n">
+        <v>87</v>
+      </c>
+      <c r="F1044" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1044" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1044" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>Davido#4BZ54</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>Davido</t>
+        </is>
+      </c>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1045" t="n">
+        <v>88</v>
+      </c>
+      <c r="F1045" t="n">
+        <v>96</v>
+      </c>
+      <c r="G1045" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1045" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>BrickXVI</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="D1046" t="inlineStr"/>
+      <c r="E1046" t="n">
+        <v>89</v>
+      </c>
+      <c r="F1046" t="n">
+        <v>74</v>
+      </c>
+      <c r="G1046" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1046" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>Taylor2901</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>ousmane</t>
+        </is>
+      </c>
+      <c r="D1047" t="inlineStr"/>
+      <c r="E1047" t="n">
+        <v>90</v>
+      </c>
+      <c r="F1047" t="n">
+        <v>74</v>
+      </c>
+      <c r="G1047" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1047" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>Ze_GOAT</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>Yasser</t>
+        </is>
+      </c>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1048" t="n">
+        <v>91</v>
+      </c>
+      <c r="F1048" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1048" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1048" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>Krol#4R8XC</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>Krol</t>
+        </is>
+      </c>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1049" t="n">
+        <v>92</v>
+      </c>
+      <c r="F1049" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1049" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1049" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>PacoSarra</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>Ibra</t>
+        </is>
+      </c>
+      <c r="D1050" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1050" t="n">
+        <v>93</v>
+      </c>
+      <c r="F1050" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1050" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1050" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>Droit_au_but7723</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>Calixthe</t>
+        </is>
+      </c>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1051" t="n">
+        <v>94</v>
+      </c>
+      <c r="F1051" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1051" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1051" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>Ambrepic</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>Ambre</t>
+        </is>
+      </c>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1052" t="n">
+        <v>95</v>
+      </c>
+      <c r="F1052" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1052" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1052" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>PavelMel</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>Mélissa</t>
+        </is>
+      </c>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1053" t="n">
+        <v>96</v>
+      </c>
+      <c r="F1053" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1053" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1053" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>Mylene-Jnt</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>Mylène</t>
+        </is>
+      </c>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1054" t="n">
+        <v>97</v>
+      </c>
+      <c r="F1054" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1054" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1054" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>Teddbear</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>Tedy</t>
+        </is>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E1055" t="n">
+        <v>98</v>
+      </c>
+      <c r="F1055" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1055" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1055" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>Camss</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1056" t="n">
+        <v>99</v>
+      </c>
+      <c r="F1056" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1056" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1056" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>SabC1</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1057" t="n">
+        <v>100</v>
+      </c>
+      <c r="F1057" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1057" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1057" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>KIKS999</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>Killian</t>
+        </is>
+      </c>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1058" t="n">
+        <v>101</v>
+      </c>
+      <c r="F1058" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1058" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1058" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>MxKnight</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1059" t="n">
+        <v>102</v>
+      </c>
+      <c r="F1059" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1059" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1059" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>RomainLect</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>romain</t>
+        </is>
+      </c>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E1060" t="n">
+        <v>103</v>
+      </c>
+      <c r="F1060" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1060" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1060" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>SamSamH8</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>Samia</t>
+        </is>
+      </c>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1061" t="n">
+        <v>104</v>
+      </c>
+      <c r="F1061" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1061" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1061" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>Daviddesco1</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1062" t="n">
+        <v>105</v>
+      </c>
+      <c r="F1062" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1062" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1062" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>Sab_M45</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1063" t="n">
+        <v>106</v>
+      </c>
+      <c r="F1063" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1063" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1063" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>Valentine___</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>Valentine</t>
+        </is>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1064" t="n">
+        <v>107</v>
+      </c>
+      <c r="F1064" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1064" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1064" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>PANENKANY</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>Damien</t>
+        </is>
+      </c>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1065" t="n">
+        <v>108</v>
+      </c>
+      <c r="F1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1065" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>MT35T</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>Mathilde</t>
+        </is>
+      </c>
+      <c r="D1066" t="inlineStr"/>
+      <c r="E1066" t="n">
+        <v>109</v>
+      </c>
+      <c r="F1066" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1066" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1066" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historique_joueurs.xlsx
+++ b/historique_joueurs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1066"/>
+  <dimension ref="A1:H1175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35460,6 +35460,3660 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>Filipinho95</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>Filipe</t>
+        </is>
+      </c>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E1067" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1067" t="n">
+        <v>410</v>
+      </c>
+      <c r="G1067" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1067" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>MargauxCtln</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>Margaux</t>
+        </is>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1068" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1068" t="n">
+        <v>376</v>
+      </c>
+      <c r="G1068" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1068" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>Mamad_Shelter</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>Mamadou</t>
+        </is>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1069" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1069" t="n">
+        <v>376</v>
+      </c>
+      <c r="G1069" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1069" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>MagicMath</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>Mathieu</t>
+        </is>
+      </c>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1070" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1070" t="n">
+        <v>376</v>
+      </c>
+      <c r="G1070" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1070" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>WalidSiuuuuu</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>Walid</t>
+        </is>
+      </c>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1071" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1071" t="n">
+        <v>356</v>
+      </c>
+      <c r="G1071" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1071" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>DJOSWA</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oswaina </t>
+        </is>
+      </c>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1072" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1072" t="n">
+        <v>356</v>
+      </c>
+      <c r="G1072" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1072" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>SID-F-ANDRE</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>Denis</t>
+        </is>
+      </c>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1073" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1073" t="n">
+        <v>355</v>
+      </c>
+      <c r="G1073" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1073" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>ChrisKr1Deg1</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>christophe</t>
+        </is>
+      </c>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1074" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1074" t="n">
+        <v>323</v>
+      </c>
+      <c r="G1074" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1074" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>Coucoucassecou</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>Brayen</t>
+        </is>
+      </c>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1075" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1075" t="n">
+        <v>322</v>
+      </c>
+      <c r="G1075" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1075" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>Paulasipi1998</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1076" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1076" t="n">
+        <v>322</v>
+      </c>
+      <c r="G1076" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1076" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>Panaff</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>Panaf</t>
+        </is>
+      </c>
+      <c r="D1077" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1077" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1077" t="n">
+        <v>315</v>
+      </c>
+      <c r="G1077" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1077" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>Kaliced</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>Kalice</t>
+        </is>
+      </c>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1078" t="n">
+        <v>12</v>
+      </c>
+      <c r="F1078" t="n">
+        <v>302</v>
+      </c>
+      <c r="G1078" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1078" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>FRHTCTD10</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>Candice</t>
+        </is>
+      </c>
+      <c r="D1079" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1079" t="n">
+        <v>13</v>
+      </c>
+      <c r="F1079" t="n">
+        <v>282</v>
+      </c>
+      <c r="G1079" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1079" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>Mr-Worldwide</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1080" t="n">
+        <v>14</v>
+      </c>
+      <c r="F1080" t="n">
+        <v>280</v>
+      </c>
+      <c r="G1080" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1080" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>Fethinho</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>Fethi</t>
+        </is>
+      </c>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E1081" t="n">
+        <v>15</v>
+      </c>
+      <c r="F1081" t="n">
+        <v>280</v>
+      </c>
+      <c r="G1081" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1081" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>Ouiouiausoleil</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>Ouissal</t>
+        </is>
+      </c>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1082" t="n">
+        <v>16</v>
+      </c>
+      <c r="F1082" t="n">
+        <v>280</v>
+      </c>
+      <c r="G1082" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1082" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>BOUGA#2JGXP</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>BOUGA</t>
+        </is>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1083" t="n">
+        <v>17</v>
+      </c>
+      <c r="F1083" t="n">
+        <v>260</v>
+      </c>
+      <c r="G1083" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1083" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>Anais757817</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>Anaïs</t>
+        </is>
+      </c>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1084" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1084" t="n">
+        <v>260</v>
+      </c>
+      <c r="G1084" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1084" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>MatuRenard</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>Mathias</t>
+        </is>
+      </c>
+      <c r="D1085" t="inlineStr"/>
+      <c r="E1085" t="n">
+        <v>19</v>
+      </c>
+      <c r="F1085" t="n">
+        <v>259</v>
+      </c>
+      <c r="G1085" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1085" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>Liliuus</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>Lilia</t>
+        </is>
+      </c>
+      <c r="D1086" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1086" t="n">
+        <v>20</v>
+      </c>
+      <c r="F1086" t="n">
+        <v>259</v>
+      </c>
+      <c r="G1086" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1086" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>Ppo28</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>Prescylla</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr"/>
+      <c r="E1087" t="n">
+        <v>21</v>
+      </c>
+      <c r="F1087" t="n">
+        <v>259</v>
+      </c>
+      <c r="G1087" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1087" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>Gronaldo_95</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>Gronaldo</t>
+        </is>
+      </c>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1088" t="n">
+        <v>22</v>
+      </c>
+      <c r="F1088" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1088" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1088" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>Devilrock95</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1089" t="n">
+        <v>23</v>
+      </c>
+      <c r="F1089" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1089" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1089" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>Ninaaaa</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>Nina</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1090" t="n">
+        <v>24</v>
+      </c>
+      <c r="F1090" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1090" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1090" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>Cleem22</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>Clemence</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1091" t="n">
+        <v>25</v>
+      </c>
+      <c r="F1091" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1091" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1091" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>catherine#5FRTD</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>catherine</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1092" t="n">
+        <v>26</v>
+      </c>
+      <c r="F1092" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1092" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1092" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>Maruyama</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>Gabrielle</t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1093" t="n">
+        <v>27</v>
+      </c>
+      <c r="F1093" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1093" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1093" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>Leandrocp</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>Leandro</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1094" t="n">
+        <v>28</v>
+      </c>
+      <c r="F1094" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1094" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1094" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>Marion1822</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>Marion</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1095" t="n">
+        <v>29</v>
+      </c>
+      <c r="F1095" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1095" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1095" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>chaychaychay</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>Chaymaa</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1096" t="n">
+        <v>30</v>
+      </c>
+      <c r="F1096" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1096" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1096" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>WIL1610</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>William</t>
+        </is>
+      </c>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1097" t="n">
+        <v>31</v>
+      </c>
+      <c r="F1097" t="n">
+        <v>233</v>
+      </c>
+      <c r="G1097" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1097" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>Erwan#4G91X</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>Erwan</t>
+        </is>
+      </c>
+      <c r="D1098" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1098" t="n">
+        <v>32</v>
+      </c>
+      <c r="F1098" t="n">
+        <v>219</v>
+      </c>
+      <c r="G1098" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1098" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>GLR_PRIME</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>Gabriel</t>
+        </is>
+      </c>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1099" t="n">
+        <v>33</v>
+      </c>
+      <c r="F1099" t="n">
+        <v>219</v>
+      </c>
+      <c r="G1099" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1099" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>Exia95</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1100" t="n">
+        <v>34</v>
+      </c>
+      <c r="F1100" t="n">
+        <v>212</v>
+      </c>
+      <c r="G1100" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1100" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>Matt#4B4CU</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="D1101" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1101" t="n">
+        <v>35</v>
+      </c>
+      <c r="F1101" t="n">
+        <v>211</v>
+      </c>
+      <c r="G1101" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1101" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>dian-bgt</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>Diane</t>
+        </is>
+      </c>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1102" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1102" t="n">
+        <v>206</v>
+      </c>
+      <c r="G1102" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1102" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>LilianeB</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liliane </t>
+        </is>
+      </c>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1103" t="n">
+        <v>37</v>
+      </c>
+      <c r="F1103" t="n">
+        <v>206</v>
+      </c>
+      <c r="G1103" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1103" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>Julie</t>
+        </is>
+      </c>
+      <c r="D1104" t="inlineStr"/>
+      <c r="E1104" t="n">
+        <v>38</v>
+      </c>
+      <c r="F1104" t="n">
+        <v>206</v>
+      </c>
+      <c r="G1104" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1104" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>Romain_JO</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>Romain J</t>
+        </is>
+      </c>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1105" t="n">
+        <v>39</v>
+      </c>
+      <c r="F1105" t="n">
+        <v>191</v>
+      </c>
+      <c r="G1105" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>JeremFZ</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>Jérémy</t>
+        </is>
+      </c>
+      <c r="D1106" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1106" t="n">
+        <v>40</v>
+      </c>
+      <c r="F1106" t="n">
+        <v>191</v>
+      </c>
+      <c r="G1106" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>AudreyB225</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>Audrey</t>
+        </is>
+      </c>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1107" t="n">
+        <v>41</v>
+      </c>
+      <c r="F1107" t="n">
+        <v>190</v>
+      </c>
+      <c r="G1107" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1107" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>BadrLeo</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>Badr Leo</t>
+        </is>
+      </c>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1108" t="n">
+        <v>42</v>
+      </c>
+      <c r="F1108" t="n">
+        <v>186</v>
+      </c>
+      <c r="G1108" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1108" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>YassineZ95</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>Yassine Z</t>
+        </is>
+      </c>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E1109" t="n">
+        <v>43</v>
+      </c>
+      <c r="F1109" t="n">
+        <v>186</v>
+      </c>
+      <c r="G1109" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1109" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>Ilan_260_</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ilann </t>
+        </is>
+      </c>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1110" t="n">
+        <v>44</v>
+      </c>
+      <c r="F1110" t="n">
+        <v>185</v>
+      </c>
+      <c r="G1110" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1110" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>abihuts</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>Antonio Moctezuma</t>
+        </is>
+      </c>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1111" t="n">
+        <v>45</v>
+      </c>
+      <c r="F1111" t="n">
+        <v>172</v>
+      </c>
+      <c r="G1111" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>Chadia__</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>Chadia</t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1112" t="n">
+        <v>46</v>
+      </c>
+      <c r="F1112" t="n">
+        <v>170</v>
+      </c>
+      <c r="G1112" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>Stephbreton</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>STEPHANE</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1113" t="n">
+        <v>47</v>
+      </c>
+      <c r="F1113" t="n">
+        <v>166</v>
+      </c>
+      <c r="G1113" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>GOAT#UE2WM8M9</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>Marilena</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1114" t="n">
+        <v>48</v>
+      </c>
+      <c r="F1114" t="n">
+        <v>165</v>
+      </c>
+      <c r="G1114" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1114" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>Ceciledp</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>Cécile</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1115" t="n">
+        <v>49</v>
+      </c>
+      <c r="F1115" t="n">
+        <v>145</v>
+      </c>
+      <c r="G1115" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>Fuzo697</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1116" t="n">
+        <v>50</v>
+      </c>
+      <c r="F1116" t="n">
+        <v>145</v>
+      </c>
+      <c r="G1116" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>Yebri</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>Brieuc</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1117" t="n">
+        <v>51</v>
+      </c>
+      <c r="F1117" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1117" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1117" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>Leo_durable</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>Leo</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1118" t="n">
+        <v>52</v>
+      </c>
+      <c r="F1118" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1118" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1118" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>EmyEnzo</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>Emilie</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1119" t="n">
+        <v>53</v>
+      </c>
+      <c r="F1119" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1119" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1119" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>Priscilla#4LCAF</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>Priscilla</t>
+        </is>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1120" t="n">
+        <v>54</v>
+      </c>
+      <c r="F1120" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1120" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1120" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>Pipou931</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>Juliie</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1121" t="n">
+        <v>55</v>
+      </c>
+      <c r="F1121" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1121" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1121" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>Farah_One</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>Farah</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr"/>
+      <c r="E1122" t="n">
+        <v>56</v>
+      </c>
+      <c r="F1122" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1122" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1122" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>François</t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr"/>
+      <c r="E1123" t="n">
+        <v>57</v>
+      </c>
+      <c r="F1123" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1123" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1123" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>Seesee</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>Selver</t>
+        </is>
+      </c>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1124" t="n">
+        <v>58</v>
+      </c>
+      <c r="F1124" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1124" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1124" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>lenaaik</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>Lénaïk</t>
+        </is>
+      </c>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1125" t="n">
+        <v>59</v>
+      </c>
+      <c r="F1125" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1125" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1125" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>C4M</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1126" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1126" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1126" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1126" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>Rosa_1009</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>Rosaline</t>
+        </is>
+      </c>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1127" t="n">
+        <v>61</v>
+      </c>
+      <c r="F1127" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1127" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1127" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>Elisewiss</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>Elise</t>
+        </is>
+      </c>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1128" t="n">
+        <v>62</v>
+      </c>
+      <c r="F1128" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1128" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1128" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>Soraya-Y</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>Soraya</t>
+        </is>
+      </c>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1129" t="n">
+        <v>63</v>
+      </c>
+      <c r="F1129" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1129" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1129" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>1993ahm</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>Ahmed</t>
+        </is>
+      </c>
+      <c r="D1130" t="inlineStr"/>
+      <c r="E1130" t="n">
+        <v>64</v>
+      </c>
+      <c r="F1130" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1130" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1130" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>MyriamAmr</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>Myriam</t>
+        </is>
+      </c>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1131" t="n">
+        <v>65</v>
+      </c>
+      <c r="F1131" t="n">
+        <v>137</v>
+      </c>
+      <c r="G1131" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1131" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>Timy</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1132" t="n">
+        <v>66</v>
+      </c>
+      <c r="F1132" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1132" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>JEVAISGAGNER10</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>Xavier</t>
+        </is>
+      </c>
+      <c r="D1133" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1133" t="n">
+        <v>67</v>
+      </c>
+      <c r="F1133" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1133" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>HamzaG</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>Hamza</t>
+        </is>
+      </c>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1134" t="n">
+        <v>68</v>
+      </c>
+      <c r="F1134" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1134" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>LeaBrd</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>Léa</t>
+        </is>
+      </c>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1135" t="n">
+        <v>69</v>
+      </c>
+      <c r="F1135" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1135" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>davidd23</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D1136" t="inlineStr"/>
+      <c r="E1136" t="n">
+        <v>70</v>
+      </c>
+      <c r="F1136" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1136" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>Nonito20</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>Arnaud</t>
+        </is>
+      </c>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1137" t="n">
+        <v>71</v>
+      </c>
+      <c r="F1137" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1137" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="D1138" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1138" t="n">
+        <v>72</v>
+      </c>
+      <c r="F1138" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1138" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>Kolas</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D1139" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1139" t="n">
+        <v>73</v>
+      </c>
+      <c r="F1139" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1139" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>Laetice2020</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>Laetitia</t>
+        </is>
+      </c>
+      <c r="D1140" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1140" t="n">
+        <v>74</v>
+      </c>
+      <c r="F1140" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1140" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>Emilay</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>Émilie</t>
+        </is>
+      </c>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1141" t="n">
+        <v>75</v>
+      </c>
+      <c r="F1141" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1141" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>Lyzone</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>Lison</t>
+        </is>
+      </c>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1142" t="n">
+        <v>76</v>
+      </c>
+      <c r="F1142" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1142" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>Melissagzb</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>Melissa</t>
+        </is>
+      </c>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1143" t="n">
+        <v>77</v>
+      </c>
+      <c r="F1143" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1143" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>Marie__92</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>Marie</t>
+        </is>
+      </c>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1144" t="n">
+        <v>78</v>
+      </c>
+      <c r="F1144" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1144" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>K_Marp</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1145" t="n">
+        <v>79</v>
+      </c>
+      <c r="F1145" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1145" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>Cindie_JJA</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>Cindie</t>
+        </is>
+      </c>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1146" t="n">
+        <v>80</v>
+      </c>
+      <c r="F1146" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1146" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>JKInternational</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>Joachim</t>
+        </is>
+      </c>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1147" t="n">
+        <v>81</v>
+      </c>
+      <c r="F1147" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1147" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>GOAT#UE4U8KA6</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>Jean Baptiste</t>
+        </is>
+      </c>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1148" t="n">
+        <v>82</v>
+      </c>
+      <c r="F1148" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1148" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>goat#AD6GS</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>goat</t>
+        </is>
+      </c>
+      <c r="D1149" t="inlineStr"/>
+      <c r="E1149" t="n">
+        <v>83</v>
+      </c>
+      <c r="F1149" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1149" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>Camillewbl</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D1150" t="inlineStr"/>
+      <c r="E1150" t="n">
+        <v>84</v>
+      </c>
+      <c r="F1150" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1150" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>Emma_Noel</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>Emma</t>
+        </is>
+      </c>
+      <c r="D1151" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1151" t="n">
+        <v>85</v>
+      </c>
+      <c r="F1151" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1151" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>RBTL</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>lea</t>
+        </is>
+      </c>
+      <c r="D1152" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1152" t="n">
+        <v>86</v>
+      </c>
+      <c r="F1152" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1152" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>A-MOE</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>Françoise</t>
+        </is>
+      </c>
+      <c r="D1153" t="inlineStr"/>
+      <c r="E1153" t="n">
+        <v>87</v>
+      </c>
+      <c r="F1153" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1153" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>Davido#4BZ54</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>Davido</t>
+        </is>
+      </c>
+      <c r="D1154" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1154" t="n">
+        <v>88</v>
+      </c>
+      <c r="F1154" t="n">
+        <v>96</v>
+      </c>
+      <c r="G1154" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>BrickXVI</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="D1155" t="inlineStr"/>
+      <c r="E1155" t="n">
+        <v>89</v>
+      </c>
+      <c r="F1155" t="n">
+        <v>74</v>
+      </c>
+      <c r="G1155" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>Taylor2901</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>ousmane</t>
+        </is>
+      </c>
+      <c r="D1156" t="inlineStr"/>
+      <c r="E1156" t="n">
+        <v>90</v>
+      </c>
+      <c r="F1156" t="n">
+        <v>74</v>
+      </c>
+      <c r="G1156" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>Ze_GOAT</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>Yasser</t>
+        </is>
+      </c>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1157" t="n">
+        <v>91</v>
+      </c>
+      <c r="F1157" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1157" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1157" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>Krol#4R8XC</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>Krol</t>
+        </is>
+      </c>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1158" t="n">
+        <v>92</v>
+      </c>
+      <c r="F1158" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1158" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1158" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>PacoSarra</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>Ibra</t>
+        </is>
+      </c>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1159" t="n">
+        <v>93</v>
+      </c>
+      <c r="F1159" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1159" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1159" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>Droit_au_but7723</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>Calixthe</t>
+        </is>
+      </c>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1160" t="n">
+        <v>94</v>
+      </c>
+      <c r="F1160" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1160" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1160" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>Ambrepic</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>Ambre</t>
+        </is>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1161" t="n">
+        <v>95</v>
+      </c>
+      <c r="F1161" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1161" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1161" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>PavelMel</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>Mélissa</t>
+        </is>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1162" t="n">
+        <v>96</v>
+      </c>
+      <c r="F1162" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1162" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>Mylene-Jnt</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>Mylène</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1163" t="n">
+        <v>97</v>
+      </c>
+      <c r="F1163" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1163" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>Teddbear</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>Tedy</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E1164" t="n">
+        <v>98</v>
+      </c>
+      <c r="F1164" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1164" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>Camss</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1165" t="n">
+        <v>99</v>
+      </c>
+      <c r="F1165" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1165" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>SabC1</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1166" t="n">
+        <v>100</v>
+      </c>
+      <c r="F1166" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1166" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>KIKS999</t>
+        </is>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>Killian</t>
+        </is>
+      </c>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1167" t="n">
+        <v>101</v>
+      </c>
+      <c r="F1167" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1167" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1167" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>MxKnight</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1168" t="n">
+        <v>102</v>
+      </c>
+      <c r="F1168" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1168" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>RomainLect</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>romain</t>
+        </is>
+      </c>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E1169" t="n">
+        <v>103</v>
+      </c>
+      <c r="F1169" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1169" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>SamSamH8</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>Samia</t>
+        </is>
+      </c>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1170" t="n">
+        <v>104</v>
+      </c>
+      <c r="F1170" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1170" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>Daviddesco1</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1171" t="n">
+        <v>105</v>
+      </c>
+      <c r="F1171" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1171" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>Sab_M45</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1172" t="n">
+        <v>106</v>
+      </c>
+      <c r="F1172" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1172" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>Valentine___</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>Valentine</t>
+        </is>
+      </c>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1173" t="n">
+        <v>107</v>
+      </c>
+      <c r="F1173" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1173" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>PANENKANY</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>Damien</t>
+        </is>
+      </c>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1174" t="n">
+        <v>108</v>
+      </c>
+      <c r="F1174" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1174" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>MT35T</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>Mathilde</t>
+        </is>
+      </c>
+      <c r="D1175" t="inlineStr"/>
+      <c r="E1175" t="n">
+        <v>109</v>
+      </c>
+      <c r="F1175" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1175" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1175" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historique_joueurs.xlsx
+++ b/historique_joueurs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1175"/>
+  <dimension ref="A1:H1284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39114,6 +39114,3660 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>Filipinho95</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>Filipe</t>
+        </is>
+      </c>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E1176" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1176" t="n">
+        <v>410</v>
+      </c>
+      <c r="G1176" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>MargauxCtln</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>Margaux</t>
+        </is>
+      </c>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1177" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1177" t="n">
+        <v>376</v>
+      </c>
+      <c r="G1177" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1177" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>Mamad_Shelter</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>Mamadou</t>
+        </is>
+      </c>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1178" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1178" t="n">
+        <v>376</v>
+      </c>
+      <c r="G1178" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1178" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>MagicMath</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>Mathieu</t>
+        </is>
+      </c>
+      <c r="D1179" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1179" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1179" t="n">
+        <v>376</v>
+      </c>
+      <c r="G1179" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1179" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>WalidSiuuuuu</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>Walid</t>
+        </is>
+      </c>
+      <c r="D1180" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1180" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1180" t="n">
+        <v>356</v>
+      </c>
+      <c r="G1180" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1180" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>DJOSWA</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oswaina </t>
+        </is>
+      </c>
+      <c r="D1181" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1181" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1181" t="n">
+        <v>356</v>
+      </c>
+      <c r="G1181" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1181" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>SID-F-ANDRE</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>Denis</t>
+        </is>
+      </c>
+      <c r="D1182" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1182" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1182" t="n">
+        <v>355</v>
+      </c>
+      <c r="G1182" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1182" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>ChrisKr1Deg1</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>christophe</t>
+        </is>
+      </c>
+      <c r="D1183" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1183" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1183" t="n">
+        <v>323</v>
+      </c>
+      <c r="G1183" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1183" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>Coucoucassecou</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>Brayen</t>
+        </is>
+      </c>
+      <c r="D1184" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1184" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1184" t="n">
+        <v>322</v>
+      </c>
+      <c r="G1184" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1184" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>Paulasipi1998</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="D1185" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1185" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1185" t="n">
+        <v>322</v>
+      </c>
+      <c r="G1185" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1185" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>Panaff</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>Panaf</t>
+        </is>
+      </c>
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1186" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1186" t="n">
+        <v>315</v>
+      </c>
+      <c r="G1186" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1186" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>Kaliced</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>Kalice</t>
+        </is>
+      </c>
+      <c r="D1187" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1187" t="n">
+        <v>12</v>
+      </c>
+      <c r="F1187" t="n">
+        <v>302</v>
+      </c>
+      <c r="G1187" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1187" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>FRHTCTD10</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>Candice</t>
+        </is>
+      </c>
+      <c r="D1188" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1188" t="n">
+        <v>13</v>
+      </c>
+      <c r="F1188" t="n">
+        <v>282</v>
+      </c>
+      <c r="G1188" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1188" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>Mr-Worldwide</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="D1189" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1189" t="n">
+        <v>14</v>
+      </c>
+      <c r="F1189" t="n">
+        <v>280</v>
+      </c>
+      <c r="G1189" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1189" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>Fethinho</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>Fethi</t>
+        </is>
+      </c>
+      <c r="D1190" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E1190" t="n">
+        <v>15</v>
+      </c>
+      <c r="F1190" t="n">
+        <v>280</v>
+      </c>
+      <c r="G1190" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1190" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>Ouiouiausoleil</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>Ouissal</t>
+        </is>
+      </c>
+      <c r="D1191" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1191" t="n">
+        <v>16</v>
+      </c>
+      <c r="F1191" t="n">
+        <v>280</v>
+      </c>
+      <c r="G1191" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1191" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>BOUGA#2JGXP</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>BOUGA</t>
+        </is>
+      </c>
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1192" t="n">
+        <v>17</v>
+      </c>
+      <c r="F1192" t="n">
+        <v>260</v>
+      </c>
+      <c r="G1192" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1192" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>Anais757817</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>Anaïs</t>
+        </is>
+      </c>
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1193" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1193" t="n">
+        <v>260</v>
+      </c>
+      <c r="G1193" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1193" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>MatuRenard</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>Mathias</t>
+        </is>
+      </c>
+      <c r="D1194" t="inlineStr"/>
+      <c r="E1194" t="n">
+        <v>19</v>
+      </c>
+      <c r="F1194" t="n">
+        <v>259</v>
+      </c>
+      <c r="G1194" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1194" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>Liliuus</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>Lilia</t>
+        </is>
+      </c>
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1195" t="n">
+        <v>20</v>
+      </c>
+      <c r="F1195" t="n">
+        <v>259</v>
+      </c>
+      <c r="G1195" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1195" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>Ppo28</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>Prescylla</t>
+        </is>
+      </c>
+      <c r="D1196" t="inlineStr"/>
+      <c r="E1196" t="n">
+        <v>21</v>
+      </c>
+      <c r="F1196" t="n">
+        <v>259</v>
+      </c>
+      <c r="G1196" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1196" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>Gronaldo_95</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>Gronaldo</t>
+        </is>
+      </c>
+      <c r="D1197" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1197" t="n">
+        <v>22</v>
+      </c>
+      <c r="F1197" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1197" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1197" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>Devilrock95</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="D1198" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1198" t="n">
+        <v>23</v>
+      </c>
+      <c r="F1198" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1198" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1198" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>Ninaaaa</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>Nina</t>
+        </is>
+      </c>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1199" t="n">
+        <v>24</v>
+      </c>
+      <c r="F1199" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1199" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1199" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>Cleem22</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>Clemence</t>
+        </is>
+      </c>
+      <c r="D1200" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1200" t="n">
+        <v>25</v>
+      </c>
+      <c r="F1200" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1200" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1200" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>catherine#5FRTD</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>catherine</t>
+        </is>
+      </c>
+      <c r="D1201" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1201" t="n">
+        <v>26</v>
+      </c>
+      <c r="F1201" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1201" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1201" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>Maruyama</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>Gabrielle</t>
+        </is>
+      </c>
+      <c r="D1202" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1202" t="n">
+        <v>27</v>
+      </c>
+      <c r="F1202" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1202" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1202" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>Leandrocp</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>Leandro</t>
+        </is>
+      </c>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1203" t="n">
+        <v>28</v>
+      </c>
+      <c r="F1203" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1203" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1203" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>Marion1822</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>Marion</t>
+        </is>
+      </c>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1204" t="n">
+        <v>29</v>
+      </c>
+      <c r="F1204" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1204" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1204" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>chaychaychay</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>Chaymaa</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1205" t="n">
+        <v>30</v>
+      </c>
+      <c r="F1205" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1205" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1205" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>WIL1610</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>William</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1206" t="n">
+        <v>31</v>
+      </c>
+      <c r="F1206" t="n">
+        <v>233</v>
+      </c>
+      <c r="G1206" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1206" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>Erwan#4G91X</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>Erwan</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1207" t="n">
+        <v>32</v>
+      </c>
+      <c r="F1207" t="n">
+        <v>219</v>
+      </c>
+      <c r="G1207" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1207" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>GLR_PRIME</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>Gabriel</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1208" t="n">
+        <v>33</v>
+      </c>
+      <c r="F1208" t="n">
+        <v>219</v>
+      </c>
+      <c r="G1208" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1208" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>Exia95</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1209" t="n">
+        <v>34</v>
+      </c>
+      <c r="F1209" t="n">
+        <v>212</v>
+      </c>
+      <c r="G1209" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1209" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>Matt#4B4CU</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1210" t="n">
+        <v>35</v>
+      </c>
+      <c r="F1210" t="n">
+        <v>211</v>
+      </c>
+      <c r="G1210" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1210" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>dian-bgt</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>Diane</t>
+        </is>
+      </c>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1211" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1211" t="n">
+        <v>206</v>
+      </c>
+      <c r="G1211" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1211" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>LilianeB</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liliane </t>
+        </is>
+      </c>
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1212" t="n">
+        <v>37</v>
+      </c>
+      <c r="F1212" t="n">
+        <v>206</v>
+      </c>
+      <c r="G1212" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1212" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>Julie</t>
+        </is>
+      </c>
+      <c r="D1213" t="inlineStr"/>
+      <c r="E1213" t="n">
+        <v>38</v>
+      </c>
+      <c r="F1213" t="n">
+        <v>206</v>
+      </c>
+      <c r="G1213" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1213" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>Romain_JO</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>Romain J</t>
+        </is>
+      </c>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1214" t="n">
+        <v>39</v>
+      </c>
+      <c r="F1214" t="n">
+        <v>191</v>
+      </c>
+      <c r="G1214" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1214" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>JeremFZ</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>Jérémy</t>
+        </is>
+      </c>
+      <c r="D1215" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1215" t="n">
+        <v>40</v>
+      </c>
+      <c r="F1215" t="n">
+        <v>191</v>
+      </c>
+      <c r="G1215" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1215" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>AudreyB225</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>Audrey</t>
+        </is>
+      </c>
+      <c r="D1216" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1216" t="n">
+        <v>41</v>
+      </c>
+      <c r="F1216" t="n">
+        <v>190</v>
+      </c>
+      <c r="G1216" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1216" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>BadrLeo</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>Badr Leo</t>
+        </is>
+      </c>
+      <c r="D1217" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1217" t="n">
+        <v>42</v>
+      </c>
+      <c r="F1217" t="n">
+        <v>186</v>
+      </c>
+      <c r="G1217" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1217" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>YassineZ95</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>Yassine Z</t>
+        </is>
+      </c>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E1218" t="n">
+        <v>43</v>
+      </c>
+      <c r="F1218" t="n">
+        <v>186</v>
+      </c>
+      <c r="G1218" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1218" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>Ilan_260_</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ilann </t>
+        </is>
+      </c>
+      <c r="D1219" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1219" t="n">
+        <v>44</v>
+      </c>
+      <c r="F1219" t="n">
+        <v>185</v>
+      </c>
+      <c r="G1219" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1219" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>abihuts</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>Antonio Moctezuma</t>
+        </is>
+      </c>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1220" t="n">
+        <v>45</v>
+      </c>
+      <c r="F1220" t="n">
+        <v>172</v>
+      </c>
+      <c r="G1220" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1220" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>Chadia__</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>Chadia</t>
+        </is>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1221" t="n">
+        <v>46</v>
+      </c>
+      <c r="F1221" t="n">
+        <v>170</v>
+      </c>
+      <c r="G1221" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1221" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>Stephbreton</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>STEPHANE</t>
+        </is>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1222" t="n">
+        <v>47</v>
+      </c>
+      <c r="F1222" t="n">
+        <v>166</v>
+      </c>
+      <c r="G1222" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1222" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>GOAT#UE2WM8M9</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>Marilena</t>
+        </is>
+      </c>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1223" t="n">
+        <v>48</v>
+      </c>
+      <c r="F1223" t="n">
+        <v>165</v>
+      </c>
+      <c r="G1223" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1223" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>Ceciledp</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>Cécile</t>
+        </is>
+      </c>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1224" t="n">
+        <v>49</v>
+      </c>
+      <c r="F1224" t="n">
+        <v>145</v>
+      </c>
+      <c r="G1224" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1224" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>Fuzo697</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D1225" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1225" t="n">
+        <v>50</v>
+      </c>
+      <c r="F1225" t="n">
+        <v>145</v>
+      </c>
+      <c r="G1225" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1225" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>Yebri</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>Brieuc</t>
+        </is>
+      </c>
+      <c r="D1226" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1226" t="n">
+        <v>51</v>
+      </c>
+      <c r="F1226" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1226" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1226" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>Leo_durable</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>Leo</t>
+        </is>
+      </c>
+      <c r="D1227" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1227" t="n">
+        <v>52</v>
+      </c>
+      <c r="F1227" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1227" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1227" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>EmyEnzo</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>Emilie</t>
+        </is>
+      </c>
+      <c r="D1228" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1228" t="n">
+        <v>53</v>
+      </c>
+      <c r="F1228" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1228" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1228" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>Priscilla#4LCAF</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>Priscilla</t>
+        </is>
+      </c>
+      <c r="D1229" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1229" t="n">
+        <v>54</v>
+      </c>
+      <c r="F1229" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1229" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1229" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>Pipou931</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>Juliie</t>
+        </is>
+      </c>
+      <c r="D1230" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1230" t="n">
+        <v>55</v>
+      </c>
+      <c r="F1230" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1230" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1230" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>Farah_One</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>Farah</t>
+        </is>
+      </c>
+      <c r="D1231" t="inlineStr"/>
+      <c r="E1231" t="n">
+        <v>56</v>
+      </c>
+      <c r="F1231" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1231" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1231" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>François</t>
+        </is>
+      </c>
+      <c r="D1232" t="inlineStr"/>
+      <c r="E1232" t="n">
+        <v>57</v>
+      </c>
+      <c r="F1232" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1232" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1232" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>Seesee</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>Selver</t>
+        </is>
+      </c>
+      <c r="D1233" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1233" t="n">
+        <v>58</v>
+      </c>
+      <c r="F1233" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1233" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1233" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>lenaaik</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>Lénaïk</t>
+        </is>
+      </c>
+      <c r="D1234" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1234" t="n">
+        <v>59</v>
+      </c>
+      <c r="F1234" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1234" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1234" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>C4M</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D1235" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1235" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1235" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1235" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1235" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>Rosa_1009</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>Rosaline</t>
+        </is>
+      </c>
+      <c r="D1236" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1236" t="n">
+        <v>61</v>
+      </c>
+      <c r="F1236" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1236" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1236" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>Elisewiss</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>Elise</t>
+        </is>
+      </c>
+      <c r="D1237" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1237" t="n">
+        <v>62</v>
+      </c>
+      <c r="F1237" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1237" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1237" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>Soraya-Y</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>Soraya</t>
+        </is>
+      </c>
+      <c r="D1238" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1238" t="n">
+        <v>63</v>
+      </c>
+      <c r="F1238" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1238" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1238" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>1993ahm</t>
+        </is>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>Ahmed</t>
+        </is>
+      </c>
+      <c r="D1239" t="inlineStr"/>
+      <c r="E1239" t="n">
+        <v>64</v>
+      </c>
+      <c r="F1239" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1239" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1239" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>MyriamAmr</t>
+        </is>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>Myriam</t>
+        </is>
+      </c>
+      <c r="D1240" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1240" t="n">
+        <v>65</v>
+      </c>
+      <c r="F1240" t="n">
+        <v>137</v>
+      </c>
+      <c r="G1240" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1240" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>Timy</t>
+        </is>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="D1241" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1241" t="n">
+        <v>66</v>
+      </c>
+      <c r="F1241" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1241" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1241" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>JEVAISGAGNER10</t>
+        </is>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>Xavier</t>
+        </is>
+      </c>
+      <c r="D1242" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1242" t="n">
+        <v>67</v>
+      </c>
+      <c r="F1242" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1242" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1242" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>HamzaG</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>Hamza</t>
+        </is>
+      </c>
+      <c r="D1243" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1243" t="n">
+        <v>68</v>
+      </c>
+      <c r="F1243" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1243" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1243" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>LeaBrd</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>Léa</t>
+        </is>
+      </c>
+      <c r="D1244" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1244" t="n">
+        <v>69</v>
+      </c>
+      <c r="F1244" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1244" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1244" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>davidd23</t>
+        </is>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D1245" t="inlineStr"/>
+      <c r="E1245" t="n">
+        <v>70</v>
+      </c>
+      <c r="F1245" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1245" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1245" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>Nonito20</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>Arnaud</t>
+        </is>
+      </c>
+      <c r="D1246" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1246" t="n">
+        <v>71</v>
+      </c>
+      <c r="F1246" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1246" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1246" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="D1247" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1247" t="n">
+        <v>72</v>
+      </c>
+      <c r="F1247" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1247" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1247" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>Kolas</t>
+        </is>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D1248" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1248" t="n">
+        <v>73</v>
+      </c>
+      <c r="F1248" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1248" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1248" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>Laetice2020</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>Laetitia</t>
+        </is>
+      </c>
+      <c r="D1249" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1249" t="n">
+        <v>74</v>
+      </c>
+      <c r="F1249" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1249" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1249" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>Emilay</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>Émilie</t>
+        </is>
+      </c>
+      <c r="D1250" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1250" t="n">
+        <v>75</v>
+      </c>
+      <c r="F1250" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1250" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1250" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>Lyzone</t>
+        </is>
+      </c>
+      <c r="C1251" t="inlineStr">
+        <is>
+          <t>Lison</t>
+        </is>
+      </c>
+      <c r="D1251" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1251" t="n">
+        <v>76</v>
+      </c>
+      <c r="F1251" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1251" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1251" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>Melissagzb</t>
+        </is>
+      </c>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>Melissa</t>
+        </is>
+      </c>
+      <c r="D1252" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1252" t="n">
+        <v>77</v>
+      </c>
+      <c r="F1252" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1252" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1252" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>Marie__92</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>Marie</t>
+        </is>
+      </c>
+      <c r="D1253" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1253" t="n">
+        <v>78</v>
+      </c>
+      <c r="F1253" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1253" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1253" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>K_Marp</t>
+        </is>
+      </c>
+      <c r="C1254" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
+      <c r="D1254" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1254" t="n">
+        <v>79</v>
+      </c>
+      <c r="F1254" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1254" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1254" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>Cindie_JJA</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>Cindie</t>
+        </is>
+      </c>
+      <c r="D1255" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1255" t="n">
+        <v>80</v>
+      </c>
+      <c r="F1255" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1255" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1255" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>JKInternational</t>
+        </is>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>Joachim</t>
+        </is>
+      </c>
+      <c r="D1256" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1256" t="n">
+        <v>81</v>
+      </c>
+      <c r="F1256" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1256" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1256" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>GOAT#UE4U8KA6</t>
+        </is>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>Jean Baptiste</t>
+        </is>
+      </c>
+      <c r="D1257" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1257" t="n">
+        <v>82</v>
+      </c>
+      <c r="F1257" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1257" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1257" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>goat#AD6GS</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>goat</t>
+        </is>
+      </c>
+      <c r="D1258" t="inlineStr"/>
+      <c r="E1258" t="n">
+        <v>83</v>
+      </c>
+      <c r="F1258" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1258" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1258" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>Camillewbl</t>
+        </is>
+      </c>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D1259" t="inlineStr"/>
+      <c r="E1259" t="n">
+        <v>84</v>
+      </c>
+      <c r="F1259" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1259" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1259" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>Emma_Noel</t>
+        </is>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>Emma</t>
+        </is>
+      </c>
+      <c r="D1260" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1260" t="n">
+        <v>85</v>
+      </c>
+      <c r="F1260" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1260" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1260" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>RBTL</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>lea</t>
+        </is>
+      </c>
+      <c r="D1261" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1261" t="n">
+        <v>86</v>
+      </c>
+      <c r="F1261" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1261" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1261" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>A-MOE</t>
+        </is>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>Françoise</t>
+        </is>
+      </c>
+      <c r="D1262" t="inlineStr"/>
+      <c r="E1262" t="n">
+        <v>87</v>
+      </c>
+      <c r="F1262" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1262" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1262" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>Davido#4BZ54</t>
+        </is>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>Davido</t>
+        </is>
+      </c>
+      <c r="D1263" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1263" t="n">
+        <v>88</v>
+      </c>
+      <c r="F1263" t="n">
+        <v>96</v>
+      </c>
+      <c r="G1263" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1263" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>BrickXVI</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="D1264" t="inlineStr"/>
+      <c r="E1264" t="n">
+        <v>89</v>
+      </c>
+      <c r="F1264" t="n">
+        <v>74</v>
+      </c>
+      <c r="G1264" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1264" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>Taylor2901</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>ousmane</t>
+        </is>
+      </c>
+      <c r="D1265" t="inlineStr"/>
+      <c r="E1265" t="n">
+        <v>90</v>
+      </c>
+      <c r="F1265" t="n">
+        <v>74</v>
+      </c>
+      <c r="G1265" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1265" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>Ze_GOAT</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>Yasser</t>
+        </is>
+      </c>
+      <c r="D1266" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1266" t="n">
+        <v>91</v>
+      </c>
+      <c r="F1266" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1266" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1266" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>Krol#4R8XC</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>Krol</t>
+        </is>
+      </c>
+      <c r="D1267" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1267" t="n">
+        <v>92</v>
+      </c>
+      <c r="F1267" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1267" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1267" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>PacoSarra</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>Ibra</t>
+        </is>
+      </c>
+      <c r="D1268" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1268" t="n">
+        <v>93</v>
+      </c>
+      <c r="F1268" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1268" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1268" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>Droit_au_but7723</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>Calixthe</t>
+        </is>
+      </c>
+      <c r="D1269" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1269" t="n">
+        <v>94</v>
+      </c>
+      <c r="F1269" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1269" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1269" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>Ambrepic</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>Ambre</t>
+        </is>
+      </c>
+      <c r="D1270" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1270" t="n">
+        <v>95</v>
+      </c>
+      <c r="F1270" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1270" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1270" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>PavelMel</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>Mélissa</t>
+        </is>
+      </c>
+      <c r="D1271" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1271" t="n">
+        <v>96</v>
+      </c>
+      <c r="F1271" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1271" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1271" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>Mylene-Jnt</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>Mylène</t>
+        </is>
+      </c>
+      <c r="D1272" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1272" t="n">
+        <v>97</v>
+      </c>
+      <c r="F1272" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1272" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1272" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>Teddbear</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>Tedy</t>
+        </is>
+      </c>
+      <c r="D1273" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E1273" t="n">
+        <v>98</v>
+      </c>
+      <c r="F1273" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1273" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1273" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>Camss</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D1274" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1274" t="n">
+        <v>99</v>
+      </c>
+      <c r="F1274" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1274" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1274" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>SabC1</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="D1275" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1275" t="n">
+        <v>100</v>
+      </c>
+      <c r="F1275" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1275" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1275" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>KIKS999</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>Killian</t>
+        </is>
+      </c>
+      <c r="D1276" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1276" t="n">
+        <v>101</v>
+      </c>
+      <c r="F1276" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1276" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1276" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>MxKnight</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D1277" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1277" t="n">
+        <v>102</v>
+      </c>
+      <c r="F1277" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1277" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1277" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>RomainLect</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>romain</t>
+        </is>
+      </c>
+      <c r="D1278" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E1278" t="n">
+        <v>103</v>
+      </c>
+      <c r="F1278" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1278" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1278" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>SamSamH8</t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>Samia</t>
+        </is>
+      </c>
+      <c r="D1279" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1279" t="n">
+        <v>104</v>
+      </c>
+      <c r="F1279" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1279" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1279" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>Daviddesco1</t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D1280" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1280" t="n">
+        <v>105</v>
+      </c>
+      <c r="F1280" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1280" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1280" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>Sab_M45</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="D1281" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1281" t="n">
+        <v>106</v>
+      </c>
+      <c r="F1281" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1281" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1281" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>Valentine___</t>
+        </is>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>Valentine</t>
+        </is>
+      </c>
+      <c r="D1282" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1282" t="n">
+        <v>107</v>
+      </c>
+      <c r="F1282" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1282" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1282" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>PANENKANY</t>
+        </is>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>Damien</t>
+        </is>
+      </c>
+      <c r="D1283" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1283" t="n">
+        <v>108</v>
+      </c>
+      <c r="F1283" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1283" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1283" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>MT35T</t>
+        </is>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>Mathilde</t>
+        </is>
+      </c>
+      <c r="D1284" t="inlineStr"/>
+      <c r="E1284" t="n">
+        <v>109</v>
+      </c>
+      <c r="F1284" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1284" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1284" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historique_joueurs.xlsx
+++ b/historique_joueurs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1284"/>
+  <dimension ref="A1:H1393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42768,6 +42768,3660 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>Filipinho95</t>
+        </is>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>Filipe</t>
+        </is>
+      </c>
+      <c r="D1285" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E1285" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1285" t="n">
+        <v>410</v>
+      </c>
+      <c r="G1285" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1285" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>MargauxCtln</t>
+        </is>
+      </c>
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t>Margaux</t>
+        </is>
+      </c>
+      <c r="D1286" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1286" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1286" t="n">
+        <v>376</v>
+      </c>
+      <c r="G1286" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1286" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>Mamad_Shelter</t>
+        </is>
+      </c>
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>Mamadou</t>
+        </is>
+      </c>
+      <c r="D1287" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1287" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1287" t="n">
+        <v>376</v>
+      </c>
+      <c r="G1287" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1287" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>MagicMath</t>
+        </is>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>Mathieu</t>
+        </is>
+      </c>
+      <c r="D1288" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1288" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1288" t="n">
+        <v>376</v>
+      </c>
+      <c r="G1288" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1288" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>WalidSiuuuuu</t>
+        </is>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>Walid</t>
+        </is>
+      </c>
+      <c r="D1289" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1289" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1289" t="n">
+        <v>356</v>
+      </c>
+      <c r="G1289" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1289" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>DJOSWA</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oswaina </t>
+        </is>
+      </c>
+      <c r="D1290" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1290" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1290" t="n">
+        <v>356</v>
+      </c>
+      <c r="G1290" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1290" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>SID-F-ANDRE</t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>Denis</t>
+        </is>
+      </c>
+      <c r="D1291" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1291" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1291" t="n">
+        <v>355</v>
+      </c>
+      <c r="G1291" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1291" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>ChrisKr1Deg1</t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>christophe</t>
+        </is>
+      </c>
+      <c r="D1292" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1292" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1292" t="n">
+        <v>323</v>
+      </c>
+      <c r="G1292" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1292" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>Coucoucassecou</t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>Brayen</t>
+        </is>
+      </c>
+      <c r="D1293" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1293" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1293" t="n">
+        <v>322</v>
+      </c>
+      <c r="G1293" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1293" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>Paulasipi1998</t>
+        </is>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="D1294" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1294" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1294" t="n">
+        <v>322</v>
+      </c>
+      <c r="G1294" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1294" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>Panaff</t>
+        </is>
+      </c>
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t>Panaf</t>
+        </is>
+      </c>
+      <c r="D1295" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1295" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1295" t="n">
+        <v>315</v>
+      </c>
+      <c r="G1295" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1295" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>Kaliced</t>
+        </is>
+      </c>
+      <c r="C1296" t="inlineStr">
+        <is>
+          <t>Kalice</t>
+        </is>
+      </c>
+      <c r="D1296" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1296" t="n">
+        <v>12</v>
+      </c>
+      <c r="F1296" t="n">
+        <v>302</v>
+      </c>
+      <c r="G1296" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1296" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>FRHTCTD10</t>
+        </is>
+      </c>
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t>Candice</t>
+        </is>
+      </c>
+      <c r="D1297" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1297" t="n">
+        <v>13</v>
+      </c>
+      <c r="F1297" t="n">
+        <v>282</v>
+      </c>
+      <c r="G1297" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1297" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>Mr-Worldwide</t>
+        </is>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="D1298" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1298" t="n">
+        <v>14</v>
+      </c>
+      <c r="F1298" t="n">
+        <v>280</v>
+      </c>
+      <c r="G1298" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1298" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>Fethinho</t>
+        </is>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>Fethi</t>
+        </is>
+      </c>
+      <c r="D1299" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E1299" t="n">
+        <v>15</v>
+      </c>
+      <c r="F1299" t="n">
+        <v>280</v>
+      </c>
+      <c r="G1299" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1299" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>Ouiouiausoleil</t>
+        </is>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>Ouissal</t>
+        </is>
+      </c>
+      <c r="D1300" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1300" t="n">
+        <v>16</v>
+      </c>
+      <c r="F1300" t="n">
+        <v>280</v>
+      </c>
+      <c r="G1300" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1300" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>BOUGA#2JGXP</t>
+        </is>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>BOUGA</t>
+        </is>
+      </c>
+      <c r="D1301" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1301" t="n">
+        <v>17</v>
+      </c>
+      <c r="F1301" t="n">
+        <v>260</v>
+      </c>
+      <c r="G1301" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1301" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>Anais757817</t>
+        </is>
+      </c>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>Anaïs</t>
+        </is>
+      </c>
+      <c r="D1302" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1302" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1302" t="n">
+        <v>260</v>
+      </c>
+      <c r="G1302" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1302" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>MatuRenard</t>
+        </is>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t>Mathias</t>
+        </is>
+      </c>
+      <c r="D1303" t="inlineStr"/>
+      <c r="E1303" t="n">
+        <v>19</v>
+      </c>
+      <c r="F1303" t="n">
+        <v>259</v>
+      </c>
+      <c r="G1303" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1303" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>Liliuus</t>
+        </is>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>Lilia</t>
+        </is>
+      </c>
+      <c r="D1304" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1304" t="n">
+        <v>20</v>
+      </c>
+      <c r="F1304" t="n">
+        <v>259</v>
+      </c>
+      <c r="G1304" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1304" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>Ppo28</t>
+        </is>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>Prescylla</t>
+        </is>
+      </c>
+      <c r="D1305" t="inlineStr"/>
+      <c r="E1305" t="n">
+        <v>21</v>
+      </c>
+      <c r="F1305" t="n">
+        <v>259</v>
+      </c>
+      <c r="G1305" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1305" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>Gronaldo_95</t>
+        </is>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t>Gronaldo</t>
+        </is>
+      </c>
+      <c r="D1306" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1306" t="n">
+        <v>22</v>
+      </c>
+      <c r="F1306" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1306" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1306" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>Devilrock95</t>
+        </is>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="D1307" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1307" t="n">
+        <v>23</v>
+      </c>
+      <c r="F1307" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1307" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1307" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>Ninaaaa</t>
+        </is>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>Nina</t>
+        </is>
+      </c>
+      <c r="D1308" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1308" t="n">
+        <v>24</v>
+      </c>
+      <c r="F1308" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1308" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1308" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>Cleem22</t>
+        </is>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>Clemence</t>
+        </is>
+      </c>
+      <c r="D1309" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1309" t="n">
+        <v>25</v>
+      </c>
+      <c r="F1309" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1309" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1309" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>catherine#5FRTD</t>
+        </is>
+      </c>
+      <c r="C1310" t="inlineStr">
+        <is>
+          <t>catherine</t>
+        </is>
+      </c>
+      <c r="D1310" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1310" t="n">
+        <v>26</v>
+      </c>
+      <c r="F1310" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1310" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1310" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>Maruyama</t>
+        </is>
+      </c>
+      <c r="C1311" t="inlineStr">
+        <is>
+          <t>Gabrielle</t>
+        </is>
+      </c>
+      <c r="D1311" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1311" t="n">
+        <v>27</v>
+      </c>
+      <c r="F1311" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1311" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1311" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>Leandrocp</t>
+        </is>
+      </c>
+      <c r="C1312" t="inlineStr">
+        <is>
+          <t>Leandro</t>
+        </is>
+      </c>
+      <c r="D1312" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1312" t="n">
+        <v>28</v>
+      </c>
+      <c r="F1312" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1312" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1312" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>Marion1822</t>
+        </is>
+      </c>
+      <c r="C1313" t="inlineStr">
+        <is>
+          <t>Marion</t>
+        </is>
+      </c>
+      <c r="D1313" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1313" t="n">
+        <v>29</v>
+      </c>
+      <c r="F1313" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1313" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1313" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>chaychaychay</t>
+        </is>
+      </c>
+      <c r="C1314" t="inlineStr">
+        <is>
+          <t>Chaymaa</t>
+        </is>
+      </c>
+      <c r="D1314" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1314" t="n">
+        <v>30</v>
+      </c>
+      <c r="F1314" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1314" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1314" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>WIL1610</t>
+        </is>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>William</t>
+        </is>
+      </c>
+      <c r="D1315" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1315" t="n">
+        <v>31</v>
+      </c>
+      <c r="F1315" t="n">
+        <v>233</v>
+      </c>
+      <c r="G1315" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1315" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>Erwan#4G91X</t>
+        </is>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>Erwan</t>
+        </is>
+      </c>
+      <c r="D1316" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1316" t="n">
+        <v>32</v>
+      </c>
+      <c r="F1316" t="n">
+        <v>219</v>
+      </c>
+      <c r="G1316" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1316" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>GLR_PRIME</t>
+        </is>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>Gabriel</t>
+        </is>
+      </c>
+      <c r="D1317" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1317" t="n">
+        <v>33</v>
+      </c>
+      <c r="F1317" t="n">
+        <v>219</v>
+      </c>
+      <c r="G1317" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1317" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>Exia95</t>
+        </is>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D1318" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1318" t="n">
+        <v>34</v>
+      </c>
+      <c r="F1318" t="n">
+        <v>212</v>
+      </c>
+      <c r="G1318" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1318" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>Matt#4B4CU</t>
+        </is>
+      </c>
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="D1319" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1319" t="n">
+        <v>35</v>
+      </c>
+      <c r="F1319" t="n">
+        <v>211</v>
+      </c>
+      <c r="G1319" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1319" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>dian-bgt</t>
+        </is>
+      </c>
+      <c r="C1320" t="inlineStr">
+        <is>
+          <t>Diane</t>
+        </is>
+      </c>
+      <c r="D1320" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1320" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1320" t="n">
+        <v>206</v>
+      </c>
+      <c r="G1320" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1320" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>LilianeB</t>
+        </is>
+      </c>
+      <c r="C1321" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liliane </t>
+        </is>
+      </c>
+      <c r="D1321" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1321" t="n">
+        <v>37</v>
+      </c>
+      <c r="F1321" t="n">
+        <v>206</v>
+      </c>
+      <c r="G1321" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1321" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="C1322" t="inlineStr">
+        <is>
+          <t>Julie</t>
+        </is>
+      </c>
+      <c r="D1322" t="inlineStr"/>
+      <c r="E1322" t="n">
+        <v>38</v>
+      </c>
+      <c r="F1322" t="n">
+        <v>206</v>
+      </c>
+      <c r="G1322" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1322" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>Romain_JO</t>
+        </is>
+      </c>
+      <c r="C1323" t="inlineStr">
+        <is>
+          <t>Romain J</t>
+        </is>
+      </c>
+      <c r="D1323" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1323" t="n">
+        <v>39</v>
+      </c>
+      <c r="F1323" t="n">
+        <v>191</v>
+      </c>
+      <c r="G1323" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1323" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>JeremFZ</t>
+        </is>
+      </c>
+      <c r="C1324" t="inlineStr">
+        <is>
+          <t>Jérémy</t>
+        </is>
+      </c>
+      <c r="D1324" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1324" t="n">
+        <v>40</v>
+      </c>
+      <c r="F1324" t="n">
+        <v>191</v>
+      </c>
+      <c r="G1324" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1324" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>AudreyB225</t>
+        </is>
+      </c>
+      <c r="C1325" t="inlineStr">
+        <is>
+          <t>Audrey</t>
+        </is>
+      </c>
+      <c r="D1325" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1325" t="n">
+        <v>41</v>
+      </c>
+      <c r="F1325" t="n">
+        <v>190</v>
+      </c>
+      <c r="G1325" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1325" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>BadrLeo</t>
+        </is>
+      </c>
+      <c r="C1326" t="inlineStr">
+        <is>
+          <t>Badr Leo</t>
+        </is>
+      </c>
+      <c r="D1326" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1326" t="n">
+        <v>42</v>
+      </c>
+      <c r="F1326" t="n">
+        <v>186</v>
+      </c>
+      <c r="G1326" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1326" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>YassineZ95</t>
+        </is>
+      </c>
+      <c r="C1327" t="inlineStr">
+        <is>
+          <t>Yassine Z</t>
+        </is>
+      </c>
+      <c r="D1327" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E1327" t="n">
+        <v>43</v>
+      </c>
+      <c r="F1327" t="n">
+        <v>186</v>
+      </c>
+      <c r="G1327" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1327" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>Ilan_260_</t>
+        </is>
+      </c>
+      <c r="C1328" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ilann </t>
+        </is>
+      </c>
+      <c r="D1328" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1328" t="n">
+        <v>44</v>
+      </c>
+      <c r="F1328" t="n">
+        <v>185</v>
+      </c>
+      <c r="G1328" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1328" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>abihuts</t>
+        </is>
+      </c>
+      <c r="C1329" t="inlineStr">
+        <is>
+          <t>Antonio Moctezuma</t>
+        </is>
+      </c>
+      <c r="D1329" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1329" t="n">
+        <v>45</v>
+      </c>
+      <c r="F1329" t="n">
+        <v>172</v>
+      </c>
+      <c r="G1329" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1329" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>Chadia__</t>
+        </is>
+      </c>
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>Chadia</t>
+        </is>
+      </c>
+      <c r="D1330" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1330" t="n">
+        <v>46</v>
+      </c>
+      <c r="F1330" t="n">
+        <v>170</v>
+      </c>
+      <c r="G1330" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1330" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>Stephbreton</t>
+        </is>
+      </c>
+      <c r="C1331" t="inlineStr">
+        <is>
+          <t>STEPHANE</t>
+        </is>
+      </c>
+      <c r="D1331" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1331" t="n">
+        <v>47</v>
+      </c>
+      <c r="F1331" t="n">
+        <v>166</v>
+      </c>
+      <c r="G1331" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1331" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>GOAT#UE2WM8M9</t>
+        </is>
+      </c>
+      <c r="C1332" t="inlineStr">
+        <is>
+          <t>Marilena</t>
+        </is>
+      </c>
+      <c r="D1332" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1332" t="n">
+        <v>48</v>
+      </c>
+      <c r="F1332" t="n">
+        <v>165</v>
+      </c>
+      <c r="G1332" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1332" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>Ceciledp</t>
+        </is>
+      </c>
+      <c r="C1333" t="inlineStr">
+        <is>
+          <t>Cécile</t>
+        </is>
+      </c>
+      <c r="D1333" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1333" t="n">
+        <v>49</v>
+      </c>
+      <c r="F1333" t="n">
+        <v>145</v>
+      </c>
+      <c r="G1333" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1333" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>Fuzo697</t>
+        </is>
+      </c>
+      <c r="C1334" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D1334" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1334" t="n">
+        <v>50</v>
+      </c>
+      <c r="F1334" t="n">
+        <v>145</v>
+      </c>
+      <c r="G1334" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1334" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>Yebri</t>
+        </is>
+      </c>
+      <c r="C1335" t="inlineStr">
+        <is>
+          <t>Brieuc</t>
+        </is>
+      </c>
+      <c r="D1335" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1335" t="n">
+        <v>51</v>
+      </c>
+      <c r="F1335" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1335" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1335" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>Leo_durable</t>
+        </is>
+      </c>
+      <c r="C1336" t="inlineStr">
+        <is>
+          <t>Leo</t>
+        </is>
+      </c>
+      <c r="D1336" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1336" t="n">
+        <v>52</v>
+      </c>
+      <c r="F1336" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1336" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1336" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>EmyEnzo</t>
+        </is>
+      </c>
+      <c r="C1337" t="inlineStr">
+        <is>
+          <t>Emilie</t>
+        </is>
+      </c>
+      <c r="D1337" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1337" t="n">
+        <v>53</v>
+      </c>
+      <c r="F1337" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1337" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1337" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>Priscilla#4LCAF</t>
+        </is>
+      </c>
+      <c r="C1338" t="inlineStr">
+        <is>
+          <t>Priscilla</t>
+        </is>
+      </c>
+      <c r="D1338" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1338" t="n">
+        <v>54</v>
+      </c>
+      <c r="F1338" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1338" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1338" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>Pipou931</t>
+        </is>
+      </c>
+      <c r="C1339" t="inlineStr">
+        <is>
+          <t>Juliie</t>
+        </is>
+      </c>
+      <c r="D1339" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1339" t="n">
+        <v>55</v>
+      </c>
+      <c r="F1339" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1339" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1339" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t>Farah_One</t>
+        </is>
+      </c>
+      <c r="C1340" t="inlineStr">
+        <is>
+          <t>Farah</t>
+        </is>
+      </c>
+      <c r="D1340" t="inlineStr"/>
+      <c r="E1340" t="n">
+        <v>56</v>
+      </c>
+      <c r="F1340" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1340" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1340" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="C1341" t="inlineStr">
+        <is>
+          <t>François</t>
+        </is>
+      </c>
+      <c r="D1341" t="inlineStr"/>
+      <c r="E1341" t="n">
+        <v>57</v>
+      </c>
+      <c r="F1341" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1341" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1341" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t>Seesee</t>
+        </is>
+      </c>
+      <c r="C1342" t="inlineStr">
+        <is>
+          <t>Selver</t>
+        </is>
+      </c>
+      <c r="D1342" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1342" t="n">
+        <v>58</v>
+      </c>
+      <c r="F1342" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1342" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1342" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>lenaaik</t>
+        </is>
+      </c>
+      <c r="C1343" t="inlineStr">
+        <is>
+          <t>Lénaïk</t>
+        </is>
+      </c>
+      <c r="D1343" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1343" t="n">
+        <v>59</v>
+      </c>
+      <c r="F1343" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1343" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1343" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t>C4M</t>
+        </is>
+      </c>
+      <c r="C1344" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D1344" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1344" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1344" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1344" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1344" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t>Rosa_1009</t>
+        </is>
+      </c>
+      <c r="C1345" t="inlineStr">
+        <is>
+          <t>Rosaline</t>
+        </is>
+      </c>
+      <c r="D1345" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1345" t="n">
+        <v>61</v>
+      </c>
+      <c r="F1345" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1345" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1345" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t>Elisewiss</t>
+        </is>
+      </c>
+      <c r="C1346" t="inlineStr">
+        <is>
+          <t>Elise</t>
+        </is>
+      </c>
+      <c r="D1346" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1346" t="n">
+        <v>62</v>
+      </c>
+      <c r="F1346" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1346" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1346" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1347" t="inlineStr">
+        <is>
+          <t>Soraya-Y</t>
+        </is>
+      </c>
+      <c r="C1347" t="inlineStr">
+        <is>
+          <t>Soraya</t>
+        </is>
+      </c>
+      <c r="D1347" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1347" t="n">
+        <v>63</v>
+      </c>
+      <c r="F1347" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1347" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1347" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t>1993ahm</t>
+        </is>
+      </c>
+      <c r="C1348" t="inlineStr">
+        <is>
+          <t>Ahmed</t>
+        </is>
+      </c>
+      <c r="D1348" t="inlineStr"/>
+      <c r="E1348" t="n">
+        <v>64</v>
+      </c>
+      <c r="F1348" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1348" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1348" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t>MyriamAmr</t>
+        </is>
+      </c>
+      <c r="C1349" t="inlineStr">
+        <is>
+          <t>Myriam</t>
+        </is>
+      </c>
+      <c r="D1349" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1349" t="n">
+        <v>65</v>
+      </c>
+      <c r="F1349" t="n">
+        <v>137</v>
+      </c>
+      <c r="G1349" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1349" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1350" t="inlineStr">
+        <is>
+          <t>Timy</t>
+        </is>
+      </c>
+      <c r="C1350" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="D1350" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1350" t="n">
+        <v>66</v>
+      </c>
+      <c r="F1350" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1350" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1350" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1351" t="inlineStr">
+        <is>
+          <t>JEVAISGAGNER10</t>
+        </is>
+      </c>
+      <c r="C1351" t="inlineStr">
+        <is>
+          <t>Xavier</t>
+        </is>
+      </c>
+      <c r="D1351" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1351" t="n">
+        <v>67</v>
+      </c>
+      <c r="F1351" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1351" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1351" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
+          <t>HamzaG</t>
+        </is>
+      </c>
+      <c r="C1352" t="inlineStr">
+        <is>
+          <t>Hamza</t>
+        </is>
+      </c>
+      <c r="D1352" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1352" t="n">
+        <v>68</v>
+      </c>
+      <c r="F1352" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1352" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1352" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t>LeaBrd</t>
+        </is>
+      </c>
+      <c r="C1353" t="inlineStr">
+        <is>
+          <t>Léa</t>
+        </is>
+      </c>
+      <c r="D1353" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1353" t="n">
+        <v>69</v>
+      </c>
+      <c r="F1353" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1353" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1353" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>davidd23</t>
+        </is>
+      </c>
+      <c r="C1354" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D1354" t="inlineStr"/>
+      <c r="E1354" t="n">
+        <v>70</v>
+      </c>
+      <c r="F1354" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1354" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1354" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>Nonito20</t>
+        </is>
+      </c>
+      <c r="C1355" t="inlineStr">
+        <is>
+          <t>Arnaud</t>
+        </is>
+      </c>
+      <c r="D1355" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1355" t="n">
+        <v>71</v>
+      </c>
+      <c r="F1355" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1355" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1355" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="C1356" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="D1356" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1356" t="n">
+        <v>72</v>
+      </c>
+      <c r="F1356" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1356" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1356" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t>Kolas</t>
+        </is>
+      </c>
+      <c r="C1357" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D1357" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1357" t="n">
+        <v>73</v>
+      </c>
+      <c r="F1357" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1357" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1357" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t>Laetice2020</t>
+        </is>
+      </c>
+      <c r="C1358" t="inlineStr">
+        <is>
+          <t>Laetitia</t>
+        </is>
+      </c>
+      <c r="D1358" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1358" t="n">
+        <v>74</v>
+      </c>
+      <c r="F1358" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1358" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1358" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>Emilay</t>
+        </is>
+      </c>
+      <c r="C1359" t="inlineStr">
+        <is>
+          <t>Émilie</t>
+        </is>
+      </c>
+      <c r="D1359" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1359" t="n">
+        <v>75</v>
+      </c>
+      <c r="F1359" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1359" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1359" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>Lyzone</t>
+        </is>
+      </c>
+      <c r="C1360" t="inlineStr">
+        <is>
+          <t>Lison</t>
+        </is>
+      </c>
+      <c r="D1360" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1360" t="n">
+        <v>76</v>
+      </c>
+      <c r="F1360" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1360" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1360" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>Melissagzb</t>
+        </is>
+      </c>
+      <c r="C1361" t="inlineStr">
+        <is>
+          <t>Melissa</t>
+        </is>
+      </c>
+      <c r="D1361" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1361" t="n">
+        <v>77</v>
+      </c>
+      <c r="F1361" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1361" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1361" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>Marie__92</t>
+        </is>
+      </c>
+      <c r="C1362" t="inlineStr">
+        <is>
+          <t>Marie</t>
+        </is>
+      </c>
+      <c r="D1362" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1362" t="n">
+        <v>78</v>
+      </c>
+      <c r="F1362" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1362" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1362" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>K_Marp</t>
+        </is>
+      </c>
+      <c r="C1363" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
+      <c r="D1363" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1363" t="n">
+        <v>79</v>
+      </c>
+      <c r="F1363" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1363" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1363" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>Cindie_JJA</t>
+        </is>
+      </c>
+      <c r="C1364" t="inlineStr">
+        <is>
+          <t>Cindie</t>
+        </is>
+      </c>
+      <c r="D1364" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1364" t="n">
+        <v>80</v>
+      </c>
+      <c r="F1364" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1364" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1364" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>JKInternational</t>
+        </is>
+      </c>
+      <c r="C1365" t="inlineStr">
+        <is>
+          <t>Joachim</t>
+        </is>
+      </c>
+      <c r="D1365" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1365" t="n">
+        <v>81</v>
+      </c>
+      <c r="F1365" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1365" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1365" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>GOAT#UE4U8KA6</t>
+        </is>
+      </c>
+      <c r="C1366" t="inlineStr">
+        <is>
+          <t>Jean Baptiste</t>
+        </is>
+      </c>
+      <c r="D1366" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1366" t="n">
+        <v>82</v>
+      </c>
+      <c r="F1366" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1366" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1366" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t>goat#AD6GS</t>
+        </is>
+      </c>
+      <c r="C1367" t="inlineStr">
+        <is>
+          <t>goat</t>
+        </is>
+      </c>
+      <c r="D1367" t="inlineStr"/>
+      <c r="E1367" t="n">
+        <v>83</v>
+      </c>
+      <c r="F1367" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1367" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1367" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1368" t="inlineStr">
+        <is>
+          <t>Camillewbl</t>
+        </is>
+      </c>
+      <c r="C1368" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D1368" t="inlineStr"/>
+      <c r="E1368" t="n">
+        <v>84</v>
+      </c>
+      <c r="F1368" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1368" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1368" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1369" t="inlineStr">
+        <is>
+          <t>Emma_Noel</t>
+        </is>
+      </c>
+      <c r="C1369" t="inlineStr">
+        <is>
+          <t>Emma</t>
+        </is>
+      </c>
+      <c r="D1369" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1369" t="n">
+        <v>85</v>
+      </c>
+      <c r="F1369" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1369" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1369" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1370" t="inlineStr">
+        <is>
+          <t>RBTL</t>
+        </is>
+      </c>
+      <c r="C1370" t="inlineStr">
+        <is>
+          <t>lea</t>
+        </is>
+      </c>
+      <c r="D1370" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1370" t="n">
+        <v>86</v>
+      </c>
+      <c r="F1370" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1370" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1370" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1371" t="inlineStr">
+        <is>
+          <t>A-MOE</t>
+        </is>
+      </c>
+      <c r="C1371" t="inlineStr">
+        <is>
+          <t>Françoise</t>
+        </is>
+      </c>
+      <c r="D1371" t="inlineStr"/>
+      <c r="E1371" t="n">
+        <v>87</v>
+      </c>
+      <c r="F1371" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1371" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1371" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1372" t="inlineStr">
+        <is>
+          <t>Davido#4BZ54</t>
+        </is>
+      </c>
+      <c r="C1372" t="inlineStr">
+        <is>
+          <t>Davido</t>
+        </is>
+      </c>
+      <c r="D1372" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1372" t="n">
+        <v>88</v>
+      </c>
+      <c r="F1372" t="n">
+        <v>96</v>
+      </c>
+      <c r="G1372" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1372" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1373" t="inlineStr">
+        <is>
+          <t>BrickXVI</t>
+        </is>
+      </c>
+      <c r="C1373" t="inlineStr">
+        <is>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="D1373" t="inlineStr"/>
+      <c r="E1373" t="n">
+        <v>89</v>
+      </c>
+      <c r="F1373" t="n">
+        <v>74</v>
+      </c>
+      <c r="G1373" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1373" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1374" t="inlineStr">
+        <is>
+          <t>Taylor2901</t>
+        </is>
+      </c>
+      <c r="C1374" t="inlineStr">
+        <is>
+          <t>ousmane</t>
+        </is>
+      </c>
+      <c r="D1374" t="inlineStr"/>
+      <c r="E1374" t="n">
+        <v>90</v>
+      </c>
+      <c r="F1374" t="n">
+        <v>74</v>
+      </c>
+      <c r="G1374" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1374" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1375" t="inlineStr">
+        <is>
+          <t>Ze_GOAT</t>
+        </is>
+      </c>
+      <c r="C1375" t="inlineStr">
+        <is>
+          <t>Yasser</t>
+        </is>
+      </c>
+      <c r="D1375" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1375" t="n">
+        <v>91</v>
+      </c>
+      <c r="F1375" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1375" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1375" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1376" t="inlineStr">
+        <is>
+          <t>Krol#4R8XC</t>
+        </is>
+      </c>
+      <c r="C1376" t="inlineStr">
+        <is>
+          <t>Krol</t>
+        </is>
+      </c>
+      <c r="D1376" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1376" t="n">
+        <v>92</v>
+      </c>
+      <c r="F1376" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1376" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1376" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1377" t="inlineStr">
+        <is>
+          <t>PacoSarra</t>
+        </is>
+      </c>
+      <c r="C1377" t="inlineStr">
+        <is>
+          <t>Ibra</t>
+        </is>
+      </c>
+      <c r="D1377" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1377" t="n">
+        <v>93</v>
+      </c>
+      <c r="F1377" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1377" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1377" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1378" t="inlineStr">
+        <is>
+          <t>Droit_au_but7723</t>
+        </is>
+      </c>
+      <c r="C1378" t="inlineStr">
+        <is>
+          <t>Calixthe</t>
+        </is>
+      </c>
+      <c r="D1378" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1378" t="n">
+        <v>94</v>
+      </c>
+      <c r="F1378" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1378" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1378" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1379" t="inlineStr">
+        <is>
+          <t>Ambrepic</t>
+        </is>
+      </c>
+      <c r="C1379" t="inlineStr">
+        <is>
+          <t>Ambre</t>
+        </is>
+      </c>
+      <c r="D1379" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1379" t="n">
+        <v>95</v>
+      </c>
+      <c r="F1379" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1379" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1379" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1380" t="inlineStr">
+        <is>
+          <t>PavelMel</t>
+        </is>
+      </c>
+      <c r="C1380" t="inlineStr">
+        <is>
+          <t>Mélissa</t>
+        </is>
+      </c>
+      <c r="D1380" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1380" t="n">
+        <v>96</v>
+      </c>
+      <c r="F1380" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1380" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1380" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1381" t="inlineStr">
+        <is>
+          <t>Mylene-Jnt</t>
+        </is>
+      </c>
+      <c r="C1381" t="inlineStr">
+        <is>
+          <t>Mylène</t>
+        </is>
+      </c>
+      <c r="D1381" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1381" t="n">
+        <v>97</v>
+      </c>
+      <c r="F1381" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1381" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1381" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1382" t="inlineStr">
+        <is>
+          <t>Teddbear</t>
+        </is>
+      </c>
+      <c r="C1382" t="inlineStr">
+        <is>
+          <t>Tedy</t>
+        </is>
+      </c>
+      <c r="D1382" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E1382" t="n">
+        <v>98</v>
+      </c>
+      <c r="F1382" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1382" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1382" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1383" t="inlineStr">
+        <is>
+          <t>Camss</t>
+        </is>
+      </c>
+      <c r="C1383" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D1383" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1383" t="n">
+        <v>99</v>
+      </c>
+      <c r="F1383" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1383" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1383" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1384" t="inlineStr">
+        <is>
+          <t>SabC1</t>
+        </is>
+      </c>
+      <c r="C1384" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="D1384" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1384" t="n">
+        <v>100</v>
+      </c>
+      <c r="F1384" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1384" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1384" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1385" t="inlineStr">
+        <is>
+          <t>KIKS999</t>
+        </is>
+      </c>
+      <c r="C1385" t="inlineStr">
+        <is>
+          <t>Killian</t>
+        </is>
+      </c>
+      <c r="D1385" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1385" t="n">
+        <v>101</v>
+      </c>
+      <c r="F1385" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1385" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1385" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1386" t="inlineStr">
+        <is>
+          <t>MxKnight</t>
+        </is>
+      </c>
+      <c r="C1386" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D1386" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1386" t="n">
+        <v>102</v>
+      </c>
+      <c r="F1386" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1386" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1386" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t>RomainLect</t>
+        </is>
+      </c>
+      <c r="C1387" t="inlineStr">
+        <is>
+          <t>romain</t>
+        </is>
+      </c>
+      <c r="D1387" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E1387" t="n">
+        <v>103</v>
+      </c>
+      <c r="F1387" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1387" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1387" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1388" t="inlineStr">
+        <is>
+          <t>SamSamH8</t>
+        </is>
+      </c>
+      <c r="C1388" t="inlineStr">
+        <is>
+          <t>Samia</t>
+        </is>
+      </c>
+      <c r="D1388" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1388" t="n">
+        <v>104</v>
+      </c>
+      <c r="F1388" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1388" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1388" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1389" t="inlineStr">
+        <is>
+          <t>Daviddesco1</t>
+        </is>
+      </c>
+      <c r="C1389" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D1389" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1389" t="n">
+        <v>105</v>
+      </c>
+      <c r="F1389" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1389" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1389" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t>Sab_M45</t>
+        </is>
+      </c>
+      <c r="C1390" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="D1390" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1390" t="n">
+        <v>106</v>
+      </c>
+      <c r="F1390" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1390" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1390" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1391" t="inlineStr">
+        <is>
+          <t>Valentine___</t>
+        </is>
+      </c>
+      <c r="C1391" t="inlineStr">
+        <is>
+          <t>Valentine</t>
+        </is>
+      </c>
+      <c r="D1391" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1391" t="n">
+        <v>107</v>
+      </c>
+      <c r="F1391" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1391" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1391" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1392" t="inlineStr">
+        <is>
+          <t>PANENKANY</t>
+        </is>
+      </c>
+      <c r="C1392" t="inlineStr">
+        <is>
+          <t>Damien</t>
+        </is>
+      </c>
+      <c r="D1392" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1392" t="n">
+        <v>108</v>
+      </c>
+      <c r="F1392" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1392" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1392" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1393" t="inlineStr">
+        <is>
+          <t>MT35T</t>
+        </is>
+      </c>
+      <c r="C1393" t="inlineStr">
+        <is>
+          <t>Mathilde</t>
+        </is>
+      </c>
+      <c r="D1393" t="inlineStr"/>
+      <c r="E1393" t="n">
+        <v>109</v>
+      </c>
+      <c r="F1393" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1393" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1393" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historique_joueurs.xlsx
+++ b/historique_joueurs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1393"/>
+  <dimension ref="A1:H1502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46422,6 +46422,3688 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1394">
+      <c r="A1394" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1394" t="inlineStr">
+        <is>
+          <t>Filipinho95</t>
+        </is>
+      </c>
+      <c r="C1394" t="inlineStr">
+        <is>
+          <t>Filipe</t>
+        </is>
+      </c>
+      <c r="D1394" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E1394" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1394" t="n">
+        <v>410</v>
+      </c>
+      <c r="G1394" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1394" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1395" t="inlineStr">
+        <is>
+          <t>MargauxCtln</t>
+        </is>
+      </c>
+      <c r="C1395" t="inlineStr">
+        <is>
+          <t>Margaux</t>
+        </is>
+      </c>
+      <c r="D1395" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1395" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1395" t="n">
+        <v>376</v>
+      </c>
+      <c r="G1395" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1395" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1396" t="inlineStr">
+        <is>
+          <t>Mamad_Shelter</t>
+        </is>
+      </c>
+      <c r="C1396" t="inlineStr">
+        <is>
+          <t>Mamadou</t>
+        </is>
+      </c>
+      <c r="D1396" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1396" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1396" t="n">
+        <v>376</v>
+      </c>
+      <c r="G1396" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1396" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t>MagicMath</t>
+        </is>
+      </c>
+      <c r="C1397" t="inlineStr">
+        <is>
+          <t>Mathieu</t>
+        </is>
+      </c>
+      <c r="D1397" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1397" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1397" t="n">
+        <v>376</v>
+      </c>
+      <c r="G1397" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1397" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1398" t="inlineStr">
+        <is>
+          <t>WalidSiuuuuu</t>
+        </is>
+      </c>
+      <c r="C1398" t="inlineStr">
+        <is>
+          <t>Walid</t>
+        </is>
+      </c>
+      <c r="D1398" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1398" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1398" t="n">
+        <v>356</v>
+      </c>
+      <c r="G1398" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1398" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1399" t="inlineStr">
+        <is>
+          <t>DJOSWA</t>
+        </is>
+      </c>
+      <c r="C1399" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oswaina </t>
+        </is>
+      </c>
+      <c r="D1399" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1399" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1399" t="n">
+        <v>356</v>
+      </c>
+      <c r="G1399" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1399" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1400" t="inlineStr">
+        <is>
+          <t>SID-F-ANDRE</t>
+        </is>
+      </c>
+      <c r="C1400" t="inlineStr">
+        <is>
+          <t>Denis</t>
+        </is>
+      </c>
+      <c r="D1400" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1400" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1400" t="n">
+        <v>355</v>
+      </c>
+      <c r="G1400" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1400" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1401" t="inlineStr">
+        <is>
+          <t>ChrisKr1Deg1</t>
+        </is>
+      </c>
+      <c r="C1401" t="inlineStr">
+        <is>
+          <t>christophe</t>
+        </is>
+      </c>
+      <c r="D1401" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1401" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1401" t="n">
+        <v>323</v>
+      </c>
+      <c r="G1401" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1401" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1402" t="inlineStr">
+        <is>
+          <t>Coucoucassecou</t>
+        </is>
+      </c>
+      <c r="C1402" t="inlineStr">
+        <is>
+          <t>Brayen</t>
+        </is>
+      </c>
+      <c r="D1402" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1402" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1402" t="n">
+        <v>322</v>
+      </c>
+      <c r="G1402" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1402" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1403" t="inlineStr">
+        <is>
+          <t>Paulasipi1998</t>
+        </is>
+      </c>
+      <c r="C1403" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="D1403" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1403" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1403" t="n">
+        <v>322</v>
+      </c>
+      <c r="G1403" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1403" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1404" t="inlineStr">
+        <is>
+          <t>Panaff</t>
+        </is>
+      </c>
+      <c r="C1404" t="inlineStr">
+        <is>
+          <t>Panaf</t>
+        </is>
+      </c>
+      <c r="D1404" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1404" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1404" t="n">
+        <v>315</v>
+      </c>
+      <c r="G1404" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1404" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1405" t="inlineStr">
+        <is>
+          <t>Kaliced</t>
+        </is>
+      </c>
+      <c r="C1405" t="inlineStr">
+        <is>
+          <t>Kalice</t>
+        </is>
+      </c>
+      <c r="D1405" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1405" t="n">
+        <v>12</v>
+      </c>
+      <c r="F1405" t="n">
+        <v>302</v>
+      </c>
+      <c r="G1405" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1405" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1406" t="inlineStr">
+        <is>
+          <t>FRHTCTD10</t>
+        </is>
+      </c>
+      <c r="C1406" t="inlineStr">
+        <is>
+          <t>Candice</t>
+        </is>
+      </c>
+      <c r="D1406" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1406" t="n">
+        <v>13</v>
+      </c>
+      <c r="F1406" t="n">
+        <v>282</v>
+      </c>
+      <c r="G1406" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1406" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1407" t="inlineStr">
+        <is>
+          <t>Mr-Worldwide</t>
+        </is>
+      </c>
+      <c r="C1407" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="D1407" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1407" t="n">
+        <v>14</v>
+      </c>
+      <c r="F1407" t="n">
+        <v>280</v>
+      </c>
+      <c r="G1407" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1407" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1408" t="inlineStr">
+        <is>
+          <t>Fethinho</t>
+        </is>
+      </c>
+      <c r="C1408" t="inlineStr">
+        <is>
+          <t>Fethi</t>
+        </is>
+      </c>
+      <c r="D1408" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E1408" t="n">
+        <v>15</v>
+      </c>
+      <c r="F1408" t="n">
+        <v>280</v>
+      </c>
+      <c r="G1408" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1408" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1409" t="inlineStr">
+        <is>
+          <t>Ouiouiausoleil</t>
+        </is>
+      </c>
+      <c r="C1409" t="inlineStr">
+        <is>
+          <t>Ouissal</t>
+        </is>
+      </c>
+      <c r="D1409" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1409" t="n">
+        <v>16</v>
+      </c>
+      <c r="F1409" t="n">
+        <v>280</v>
+      </c>
+      <c r="G1409" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1409" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1410" t="inlineStr">
+        <is>
+          <t>BOUGA#2JGXP</t>
+        </is>
+      </c>
+      <c r="C1410" t="inlineStr">
+        <is>
+          <t>BOUGA</t>
+        </is>
+      </c>
+      <c r="D1410" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1410" t="n">
+        <v>17</v>
+      </c>
+      <c r="F1410" t="n">
+        <v>260</v>
+      </c>
+      <c r="G1410" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1410" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1411" t="inlineStr">
+        <is>
+          <t>Anais757817</t>
+        </is>
+      </c>
+      <c r="C1411" t="inlineStr">
+        <is>
+          <t>Anaïs</t>
+        </is>
+      </c>
+      <c r="D1411" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1411" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1411" t="n">
+        <v>260</v>
+      </c>
+      <c r="G1411" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1411" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1412" t="inlineStr">
+        <is>
+          <t>MatuRenard</t>
+        </is>
+      </c>
+      <c r="C1412" t="inlineStr">
+        <is>
+          <t>Mathias</t>
+        </is>
+      </c>
+      <c r="D1412" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1412" t="n">
+        <v>19</v>
+      </c>
+      <c r="F1412" t="n">
+        <v>259</v>
+      </c>
+      <c r="G1412" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1412" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1413" t="inlineStr">
+        <is>
+          <t>Liliuus</t>
+        </is>
+      </c>
+      <c r="C1413" t="inlineStr">
+        <is>
+          <t>Lilia</t>
+        </is>
+      </c>
+      <c r="D1413" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1413" t="n">
+        <v>20</v>
+      </c>
+      <c r="F1413" t="n">
+        <v>259</v>
+      </c>
+      <c r="G1413" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1413" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1414" t="inlineStr">
+        <is>
+          <t>Ppo28</t>
+        </is>
+      </c>
+      <c r="C1414" t="inlineStr">
+        <is>
+          <t>Prescylla</t>
+        </is>
+      </c>
+      <c r="D1414" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E1414" t="n">
+        <v>21</v>
+      </c>
+      <c r="F1414" t="n">
+        <v>259</v>
+      </c>
+      <c r="G1414" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1414" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1415" t="inlineStr">
+        <is>
+          <t>Gronaldo_95</t>
+        </is>
+      </c>
+      <c r="C1415" t="inlineStr">
+        <is>
+          <t>Gronaldo</t>
+        </is>
+      </c>
+      <c r="D1415" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1415" t="n">
+        <v>22</v>
+      </c>
+      <c r="F1415" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1415" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1415" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1416" t="inlineStr">
+        <is>
+          <t>Devilrock95</t>
+        </is>
+      </c>
+      <c r="C1416" t="inlineStr">
+        <is>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="D1416" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1416" t="n">
+        <v>23</v>
+      </c>
+      <c r="F1416" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1416" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1416" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1417" t="inlineStr">
+        <is>
+          <t>Ninaaaa</t>
+        </is>
+      </c>
+      <c r="C1417" t="inlineStr">
+        <is>
+          <t>Nina</t>
+        </is>
+      </c>
+      <c r="D1417" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1417" t="n">
+        <v>24</v>
+      </c>
+      <c r="F1417" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1417" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1417" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1418" t="inlineStr">
+        <is>
+          <t>Cleem22</t>
+        </is>
+      </c>
+      <c r="C1418" t="inlineStr">
+        <is>
+          <t>Clemence</t>
+        </is>
+      </c>
+      <c r="D1418" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1418" t="n">
+        <v>25</v>
+      </c>
+      <c r="F1418" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1418" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1418" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1419" t="inlineStr">
+        <is>
+          <t>catherine#5FRTD</t>
+        </is>
+      </c>
+      <c r="C1419" t="inlineStr">
+        <is>
+          <t>catherine</t>
+        </is>
+      </c>
+      <c r="D1419" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1419" t="n">
+        <v>26</v>
+      </c>
+      <c r="F1419" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1419" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1419" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1420" t="inlineStr">
+        <is>
+          <t>Maruyama</t>
+        </is>
+      </c>
+      <c r="C1420" t="inlineStr">
+        <is>
+          <t>Gabrielle</t>
+        </is>
+      </c>
+      <c r="D1420" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1420" t="n">
+        <v>27</v>
+      </c>
+      <c r="F1420" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1420" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1420" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1421" t="inlineStr">
+        <is>
+          <t>Leandrocp</t>
+        </is>
+      </c>
+      <c r="C1421" t="inlineStr">
+        <is>
+          <t>Leandro</t>
+        </is>
+      </c>
+      <c r="D1421" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1421" t="n">
+        <v>28</v>
+      </c>
+      <c r="F1421" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1421" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1421" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1422" t="inlineStr">
+        <is>
+          <t>Marion1822</t>
+        </is>
+      </c>
+      <c r="C1422" t="inlineStr">
+        <is>
+          <t>Marion</t>
+        </is>
+      </c>
+      <c r="D1422" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1422" t="n">
+        <v>29</v>
+      </c>
+      <c r="F1422" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1422" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1422" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1423" t="inlineStr">
+        <is>
+          <t>chaychaychay</t>
+        </is>
+      </c>
+      <c r="C1423" t="inlineStr">
+        <is>
+          <t>Chaymaa</t>
+        </is>
+      </c>
+      <c r="D1423" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1423" t="n">
+        <v>30</v>
+      </c>
+      <c r="F1423" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1423" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1423" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1424" t="inlineStr">
+        <is>
+          <t>WIL1610</t>
+        </is>
+      </c>
+      <c r="C1424" t="inlineStr">
+        <is>
+          <t>William</t>
+        </is>
+      </c>
+      <c r="D1424" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1424" t="n">
+        <v>31</v>
+      </c>
+      <c r="F1424" t="n">
+        <v>233</v>
+      </c>
+      <c r="G1424" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1424" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1425" t="inlineStr">
+        <is>
+          <t>Erwan#4G91X</t>
+        </is>
+      </c>
+      <c r="C1425" t="inlineStr">
+        <is>
+          <t>Erwan</t>
+        </is>
+      </c>
+      <c r="D1425" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1425" t="n">
+        <v>32</v>
+      </c>
+      <c r="F1425" t="n">
+        <v>219</v>
+      </c>
+      <c r="G1425" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1425" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1426" t="inlineStr">
+        <is>
+          <t>GLR_PRIME</t>
+        </is>
+      </c>
+      <c r="C1426" t="inlineStr">
+        <is>
+          <t>Gabriel</t>
+        </is>
+      </c>
+      <c r="D1426" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1426" t="n">
+        <v>33</v>
+      </c>
+      <c r="F1426" t="n">
+        <v>219</v>
+      </c>
+      <c r="G1426" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1426" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1427" t="inlineStr">
+        <is>
+          <t>Exia95</t>
+        </is>
+      </c>
+      <c r="C1427" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D1427" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1427" t="n">
+        <v>34</v>
+      </c>
+      <c r="F1427" t="n">
+        <v>212</v>
+      </c>
+      <c r="G1427" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1427" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1428" t="inlineStr">
+        <is>
+          <t>Matt#4B4CU</t>
+        </is>
+      </c>
+      <c r="C1428" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="D1428" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1428" t="n">
+        <v>35</v>
+      </c>
+      <c r="F1428" t="n">
+        <v>211</v>
+      </c>
+      <c r="G1428" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1428" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1429" t="inlineStr">
+        <is>
+          <t>dian-bgt</t>
+        </is>
+      </c>
+      <c r="C1429" t="inlineStr">
+        <is>
+          <t>Diane</t>
+        </is>
+      </c>
+      <c r="D1429" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1429" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1429" t="n">
+        <v>206</v>
+      </c>
+      <c r="G1429" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1429" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1430" t="inlineStr">
+        <is>
+          <t>LilianeB</t>
+        </is>
+      </c>
+      <c r="C1430" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liliane </t>
+        </is>
+      </c>
+      <c r="D1430" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1430" t="n">
+        <v>37</v>
+      </c>
+      <c r="F1430" t="n">
+        <v>206</v>
+      </c>
+      <c r="G1430" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1430" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1431" t="inlineStr">
+        <is>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="C1431" t="inlineStr">
+        <is>
+          <t>Julie</t>
+        </is>
+      </c>
+      <c r="D1431" t="inlineStr"/>
+      <c r="E1431" t="n">
+        <v>38</v>
+      </c>
+      <c r="F1431" t="n">
+        <v>206</v>
+      </c>
+      <c r="G1431" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1431" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1432" t="inlineStr">
+        <is>
+          <t>Romain_JO</t>
+        </is>
+      </c>
+      <c r="C1432" t="inlineStr">
+        <is>
+          <t>Romain J</t>
+        </is>
+      </c>
+      <c r="D1432" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1432" t="n">
+        <v>39</v>
+      </c>
+      <c r="F1432" t="n">
+        <v>191</v>
+      </c>
+      <c r="G1432" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1432" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1433" t="inlineStr">
+        <is>
+          <t>JeremFZ</t>
+        </is>
+      </c>
+      <c r="C1433" t="inlineStr">
+        <is>
+          <t>Jérémy</t>
+        </is>
+      </c>
+      <c r="D1433" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1433" t="n">
+        <v>40</v>
+      </c>
+      <c r="F1433" t="n">
+        <v>191</v>
+      </c>
+      <c r="G1433" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1433" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1434" t="inlineStr">
+        <is>
+          <t>AudreyB225</t>
+        </is>
+      </c>
+      <c r="C1434" t="inlineStr">
+        <is>
+          <t>Audrey</t>
+        </is>
+      </c>
+      <c r="D1434" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1434" t="n">
+        <v>41</v>
+      </c>
+      <c r="F1434" t="n">
+        <v>190</v>
+      </c>
+      <c r="G1434" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1434" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1435" t="inlineStr">
+        <is>
+          <t>BadrLeo</t>
+        </is>
+      </c>
+      <c r="C1435" t="inlineStr">
+        <is>
+          <t>Badr Leo</t>
+        </is>
+      </c>
+      <c r="D1435" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1435" t="n">
+        <v>42</v>
+      </c>
+      <c r="F1435" t="n">
+        <v>186</v>
+      </c>
+      <c r="G1435" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1435" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1436" t="inlineStr">
+        <is>
+          <t>YassineZ95</t>
+        </is>
+      </c>
+      <c r="C1436" t="inlineStr">
+        <is>
+          <t>Yassine Z</t>
+        </is>
+      </c>
+      <c r="D1436" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E1436" t="n">
+        <v>43</v>
+      </c>
+      <c r="F1436" t="n">
+        <v>186</v>
+      </c>
+      <c r="G1436" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1436" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1437" t="inlineStr">
+        <is>
+          <t>Ilan_260_</t>
+        </is>
+      </c>
+      <c r="C1437" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ilann </t>
+        </is>
+      </c>
+      <c r="D1437" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1437" t="n">
+        <v>44</v>
+      </c>
+      <c r="F1437" t="n">
+        <v>185</v>
+      </c>
+      <c r="G1437" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1437" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1438" t="inlineStr">
+        <is>
+          <t>abihuts</t>
+        </is>
+      </c>
+      <c r="C1438" t="inlineStr">
+        <is>
+          <t>Antonio Moctezuma</t>
+        </is>
+      </c>
+      <c r="D1438" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1438" t="n">
+        <v>45</v>
+      </c>
+      <c r="F1438" t="n">
+        <v>172</v>
+      </c>
+      <c r="G1438" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1438" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1439" t="inlineStr">
+        <is>
+          <t>Chadia__</t>
+        </is>
+      </c>
+      <c r="C1439" t="inlineStr">
+        <is>
+          <t>Chadia</t>
+        </is>
+      </c>
+      <c r="D1439" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1439" t="n">
+        <v>46</v>
+      </c>
+      <c r="F1439" t="n">
+        <v>170</v>
+      </c>
+      <c r="G1439" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1439" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1440" t="inlineStr">
+        <is>
+          <t>Stephbreton</t>
+        </is>
+      </c>
+      <c r="C1440" t="inlineStr">
+        <is>
+          <t>STEPHANE</t>
+        </is>
+      </c>
+      <c r="D1440" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1440" t="n">
+        <v>47</v>
+      </c>
+      <c r="F1440" t="n">
+        <v>166</v>
+      </c>
+      <c r="G1440" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1440" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1441" t="inlineStr">
+        <is>
+          <t>GOAT#UE2WM8M9</t>
+        </is>
+      </c>
+      <c r="C1441" t="inlineStr">
+        <is>
+          <t>Marilena</t>
+        </is>
+      </c>
+      <c r="D1441" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1441" t="n">
+        <v>48</v>
+      </c>
+      <c r="F1441" t="n">
+        <v>165</v>
+      </c>
+      <c r="G1441" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1441" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1442" t="inlineStr">
+        <is>
+          <t>Ceciledp</t>
+        </is>
+      </c>
+      <c r="C1442" t="inlineStr">
+        <is>
+          <t>Cécile</t>
+        </is>
+      </c>
+      <c r="D1442" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1442" t="n">
+        <v>49</v>
+      </c>
+      <c r="F1442" t="n">
+        <v>145</v>
+      </c>
+      <c r="G1442" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1442" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1443" t="inlineStr">
+        <is>
+          <t>Fuzo697</t>
+        </is>
+      </c>
+      <c r="C1443" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D1443" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1443" t="n">
+        <v>50</v>
+      </c>
+      <c r="F1443" t="n">
+        <v>145</v>
+      </c>
+      <c r="G1443" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1443" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1444" t="inlineStr">
+        <is>
+          <t>Yebri</t>
+        </is>
+      </c>
+      <c r="C1444" t="inlineStr">
+        <is>
+          <t>Brieuc</t>
+        </is>
+      </c>
+      <c r="D1444" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1444" t="n">
+        <v>51</v>
+      </c>
+      <c r="F1444" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1444" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1444" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1445" t="inlineStr">
+        <is>
+          <t>Leo_durable</t>
+        </is>
+      </c>
+      <c r="C1445" t="inlineStr">
+        <is>
+          <t>Leo</t>
+        </is>
+      </c>
+      <c r="D1445" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1445" t="n">
+        <v>52</v>
+      </c>
+      <c r="F1445" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1445" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1445" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1446" t="inlineStr">
+        <is>
+          <t>EmyEnzo</t>
+        </is>
+      </c>
+      <c r="C1446" t="inlineStr">
+        <is>
+          <t>Emilie</t>
+        </is>
+      </c>
+      <c r="D1446" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1446" t="n">
+        <v>53</v>
+      </c>
+      <c r="F1446" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1446" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1446" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1447" t="inlineStr">
+        <is>
+          <t>Priscilla#4LCAF</t>
+        </is>
+      </c>
+      <c r="C1447" t="inlineStr">
+        <is>
+          <t>Priscilla</t>
+        </is>
+      </c>
+      <c r="D1447" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1447" t="n">
+        <v>54</v>
+      </c>
+      <c r="F1447" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1447" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1447" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1448" t="inlineStr">
+        <is>
+          <t>Pipou931</t>
+        </is>
+      </c>
+      <c r="C1448" t="inlineStr">
+        <is>
+          <t>Juliie</t>
+        </is>
+      </c>
+      <c r="D1448" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1448" t="n">
+        <v>55</v>
+      </c>
+      <c r="F1448" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1448" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1448" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1449" t="inlineStr">
+        <is>
+          <t>Farah_One</t>
+        </is>
+      </c>
+      <c r="C1449" t="inlineStr">
+        <is>
+          <t>Farah</t>
+        </is>
+      </c>
+      <c r="D1449" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1449" t="n">
+        <v>56</v>
+      </c>
+      <c r="F1449" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1449" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1449" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1450" t="inlineStr">
+        <is>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="C1450" t="inlineStr">
+        <is>
+          <t>François</t>
+        </is>
+      </c>
+      <c r="D1450" t="inlineStr"/>
+      <c r="E1450" t="n">
+        <v>57</v>
+      </c>
+      <c r="F1450" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1450" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1450" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1451" t="inlineStr">
+        <is>
+          <t>Seesee</t>
+        </is>
+      </c>
+      <c r="C1451" t="inlineStr">
+        <is>
+          <t>Selver</t>
+        </is>
+      </c>
+      <c r="D1451" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1451" t="n">
+        <v>58</v>
+      </c>
+      <c r="F1451" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1451" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1451" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1452" t="inlineStr">
+        <is>
+          <t>lenaaik</t>
+        </is>
+      </c>
+      <c r="C1452" t="inlineStr">
+        <is>
+          <t>Lénaïk</t>
+        </is>
+      </c>
+      <c r="D1452" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1452" t="n">
+        <v>59</v>
+      </c>
+      <c r="F1452" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1452" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1452" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1453" t="inlineStr">
+        <is>
+          <t>C4M</t>
+        </is>
+      </c>
+      <c r="C1453" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D1453" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1453" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1453" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1453" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1453" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1454" t="inlineStr">
+        <is>
+          <t>Rosa_1009</t>
+        </is>
+      </c>
+      <c r="C1454" t="inlineStr">
+        <is>
+          <t>Rosaline</t>
+        </is>
+      </c>
+      <c r="D1454" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1454" t="n">
+        <v>61</v>
+      </c>
+      <c r="F1454" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1454" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1454" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1455" t="inlineStr">
+        <is>
+          <t>Elisewiss</t>
+        </is>
+      </c>
+      <c r="C1455" t="inlineStr">
+        <is>
+          <t>Elise</t>
+        </is>
+      </c>
+      <c r="D1455" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1455" t="n">
+        <v>62</v>
+      </c>
+      <c r="F1455" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1455" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1455" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1456" t="inlineStr">
+        <is>
+          <t>Soraya-Y</t>
+        </is>
+      </c>
+      <c r="C1456" t="inlineStr">
+        <is>
+          <t>Soraya</t>
+        </is>
+      </c>
+      <c r="D1456" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1456" t="n">
+        <v>63</v>
+      </c>
+      <c r="F1456" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1456" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1456" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1457" t="inlineStr">
+        <is>
+          <t>1993ahm</t>
+        </is>
+      </c>
+      <c r="C1457" t="inlineStr">
+        <is>
+          <t>Ahmed</t>
+        </is>
+      </c>
+      <c r="D1457" t="inlineStr"/>
+      <c r="E1457" t="n">
+        <v>64</v>
+      </c>
+      <c r="F1457" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1457" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1457" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1458" t="inlineStr">
+        <is>
+          <t>MyriamAmr</t>
+        </is>
+      </c>
+      <c r="C1458" t="inlineStr">
+        <is>
+          <t>Myriam</t>
+        </is>
+      </c>
+      <c r="D1458" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1458" t="n">
+        <v>65</v>
+      </c>
+      <c r="F1458" t="n">
+        <v>137</v>
+      </c>
+      <c r="G1458" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1458" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1459" t="inlineStr">
+        <is>
+          <t>Timy</t>
+        </is>
+      </c>
+      <c r="C1459" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="D1459" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1459" t="n">
+        <v>66</v>
+      </c>
+      <c r="F1459" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1459" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1459" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1460" t="inlineStr">
+        <is>
+          <t>JEVAISGAGNER10</t>
+        </is>
+      </c>
+      <c r="C1460" t="inlineStr">
+        <is>
+          <t>Xavier</t>
+        </is>
+      </c>
+      <c r="D1460" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1460" t="n">
+        <v>67</v>
+      </c>
+      <c r="F1460" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1460" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1460" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1461" t="inlineStr">
+        <is>
+          <t>HamzaG</t>
+        </is>
+      </c>
+      <c r="C1461" t="inlineStr">
+        <is>
+          <t>Hamza</t>
+        </is>
+      </c>
+      <c r="D1461" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1461" t="n">
+        <v>68</v>
+      </c>
+      <c r="F1461" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1461" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1461" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1462" t="inlineStr">
+        <is>
+          <t>LeaBrd</t>
+        </is>
+      </c>
+      <c r="C1462" t="inlineStr">
+        <is>
+          <t>Léa</t>
+        </is>
+      </c>
+      <c r="D1462" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1462" t="n">
+        <v>69</v>
+      </c>
+      <c r="F1462" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1462" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1462" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1463" t="inlineStr">
+        <is>
+          <t>davidd23</t>
+        </is>
+      </c>
+      <c r="C1463" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D1463" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1463" t="n">
+        <v>70</v>
+      </c>
+      <c r="F1463" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1463" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1463" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1464" t="inlineStr">
+        <is>
+          <t>Nonito20</t>
+        </is>
+      </c>
+      <c r="C1464" t="inlineStr">
+        <is>
+          <t>Arnaud</t>
+        </is>
+      </c>
+      <c r="D1464" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1464" t="n">
+        <v>71</v>
+      </c>
+      <c r="F1464" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1464" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1464" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1465" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="C1465" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="D1465" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1465" t="n">
+        <v>72</v>
+      </c>
+      <c r="F1465" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1465" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1465" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1466" t="inlineStr">
+        <is>
+          <t>Kolas</t>
+        </is>
+      </c>
+      <c r="C1466" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D1466" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1466" t="n">
+        <v>73</v>
+      </c>
+      <c r="F1466" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1466" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1466" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1467" t="inlineStr">
+        <is>
+          <t>Laetice2020</t>
+        </is>
+      </c>
+      <c r="C1467" t="inlineStr">
+        <is>
+          <t>Laetitia</t>
+        </is>
+      </c>
+      <c r="D1467" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1467" t="n">
+        <v>74</v>
+      </c>
+      <c r="F1467" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1467" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1467" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1468" t="inlineStr">
+        <is>
+          <t>Emilay</t>
+        </is>
+      </c>
+      <c r="C1468" t="inlineStr">
+        <is>
+          <t>Émilie</t>
+        </is>
+      </c>
+      <c r="D1468" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1468" t="n">
+        <v>75</v>
+      </c>
+      <c r="F1468" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1468" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1468" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1469" t="inlineStr">
+        <is>
+          <t>Lyzone</t>
+        </is>
+      </c>
+      <c r="C1469" t="inlineStr">
+        <is>
+          <t>Lison</t>
+        </is>
+      </c>
+      <c r="D1469" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1469" t="n">
+        <v>76</v>
+      </c>
+      <c r="F1469" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1469" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1469" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1470" t="inlineStr">
+        <is>
+          <t>Melissagzb</t>
+        </is>
+      </c>
+      <c r="C1470" t="inlineStr">
+        <is>
+          <t>Melissa</t>
+        </is>
+      </c>
+      <c r="D1470" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1470" t="n">
+        <v>77</v>
+      </c>
+      <c r="F1470" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1470" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1470" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1471" t="inlineStr">
+        <is>
+          <t>Marie__92</t>
+        </is>
+      </c>
+      <c r="C1471" t="inlineStr">
+        <is>
+          <t>Marie</t>
+        </is>
+      </c>
+      <c r="D1471" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1471" t="n">
+        <v>78</v>
+      </c>
+      <c r="F1471" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1471" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1471" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1472" t="inlineStr">
+        <is>
+          <t>K_Marp</t>
+        </is>
+      </c>
+      <c r="C1472" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
+      <c r="D1472" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1472" t="n">
+        <v>79</v>
+      </c>
+      <c r="F1472" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1472" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1472" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1473" t="inlineStr">
+        <is>
+          <t>Cindie_JJA</t>
+        </is>
+      </c>
+      <c r="C1473" t="inlineStr">
+        <is>
+          <t>Cindie</t>
+        </is>
+      </c>
+      <c r="D1473" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1473" t="n">
+        <v>80</v>
+      </c>
+      <c r="F1473" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1473" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1473" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1474" t="inlineStr">
+        <is>
+          <t>JKInternational</t>
+        </is>
+      </c>
+      <c r="C1474" t="inlineStr">
+        <is>
+          <t>Joachim</t>
+        </is>
+      </c>
+      <c r="D1474" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1474" t="n">
+        <v>81</v>
+      </c>
+      <c r="F1474" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1474" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1474" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1475" t="inlineStr">
+        <is>
+          <t>GOAT#UE4U8KA6</t>
+        </is>
+      </c>
+      <c r="C1475" t="inlineStr">
+        <is>
+          <t>Jean Baptiste</t>
+        </is>
+      </c>
+      <c r="D1475" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1475" t="n">
+        <v>82</v>
+      </c>
+      <c r="F1475" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1475" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1475" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1476" t="inlineStr">
+        <is>
+          <t>goat#AD6GS</t>
+        </is>
+      </c>
+      <c r="C1476" t="inlineStr">
+        <is>
+          <t>goat</t>
+        </is>
+      </c>
+      <c r="D1476" t="inlineStr"/>
+      <c r="E1476" t="n">
+        <v>83</v>
+      </c>
+      <c r="F1476" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1476" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1476" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1477" t="inlineStr">
+        <is>
+          <t>Camillewbl</t>
+        </is>
+      </c>
+      <c r="C1477" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D1477" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1477" t="n">
+        <v>84</v>
+      </c>
+      <c r="F1477" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1477" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1477" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1478" t="inlineStr">
+        <is>
+          <t>Emma_Noel</t>
+        </is>
+      </c>
+      <c r="C1478" t="inlineStr">
+        <is>
+          <t>Emma</t>
+        </is>
+      </c>
+      <c r="D1478" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1478" t="n">
+        <v>85</v>
+      </c>
+      <c r="F1478" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1478" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1478" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1479" t="inlineStr">
+        <is>
+          <t>RBTL</t>
+        </is>
+      </c>
+      <c r="C1479" t="inlineStr">
+        <is>
+          <t>lea</t>
+        </is>
+      </c>
+      <c r="D1479" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1479" t="n">
+        <v>86</v>
+      </c>
+      <c r="F1479" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1479" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1479" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1480" t="inlineStr">
+        <is>
+          <t>A-MOE</t>
+        </is>
+      </c>
+      <c r="C1480" t="inlineStr">
+        <is>
+          <t>Françoise</t>
+        </is>
+      </c>
+      <c r="D1480" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1480" t="n">
+        <v>87</v>
+      </c>
+      <c r="F1480" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1480" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1480" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1481" t="inlineStr">
+        <is>
+          <t>Davido#4BZ54</t>
+        </is>
+      </c>
+      <c r="C1481" t="inlineStr">
+        <is>
+          <t>Davido</t>
+        </is>
+      </c>
+      <c r="D1481" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1481" t="n">
+        <v>88</v>
+      </c>
+      <c r="F1481" t="n">
+        <v>96</v>
+      </c>
+      <c r="G1481" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1481" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1482" t="inlineStr">
+        <is>
+          <t>BrickXVI</t>
+        </is>
+      </c>
+      <c r="C1482" t="inlineStr">
+        <is>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="D1482" t="inlineStr"/>
+      <c r="E1482" t="n">
+        <v>89</v>
+      </c>
+      <c r="F1482" t="n">
+        <v>74</v>
+      </c>
+      <c r="G1482" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1482" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1483" t="inlineStr">
+        <is>
+          <t>Taylor2901</t>
+        </is>
+      </c>
+      <c r="C1483" t="inlineStr">
+        <is>
+          <t>ousmane</t>
+        </is>
+      </c>
+      <c r="D1483" t="inlineStr"/>
+      <c r="E1483" t="n">
+        <v>90</v>
+      </c>
+      <c r="F1483" t="n">
+        <v>74</v>
+      </c>
+      <c r="G1483" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1483" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1484" t="inlineStr">
+        <is>
+          <t>Ze_GOAT</t>
+        </is>
+      </c>
+      <c r="C1484" t="inlineStr">
+        <is>
+          <t>Yasser</t>
+        </is>
+      </c>
+      <c r="D1484" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1484" t="n">
+        <v>91</v>
+      </c>
+      <c r="F1484" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1484" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1484" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1485" t="inlineStr">
+        <is>
+          <t>Krol#4R8XC</t>
+        </is>
+      </c>
+      <c r="C1485" t="inlineStr">
+        <is>
+          <t>Krol</t>
+        </is>
+      </c>
+      <c r="D1485" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1485" t="n">
+        <v>92</v>
+      </c>
+      <c r="F1485" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1485" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1485" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1486" t="inlineStr">
+        <is>
+          <t>PacoSarra</t>
+        </is>
+      </c>
+      <c r="C1486" t="inlineStr">
+        <is>
+          <t>Ibra</t>
+        </is>
+      </c>
+      <c r="D1486" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1486" t="n">
+        <v>93</v>
+      </c>
+      <c r="F1486" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1486" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1486" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1487" t="inlineStr">
+        <is>
+          <t>Droit_au_but7723</t>
+        </is>
+      </c>
+      <c r="C1487" t="inlineStr">
+        <is>
+          <t>Calixthe</t>
+        </is>
+      </c>
+      <c r="D1487" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1487" t="n">
+        <v>94</v>
+      </c>
+      <c r="F1487" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1487" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1487" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1488" t="inlineStr">
+        <is>
+          <t>Ambrepic</t>
+        </is>
+      </c>
+      <c r="C1488" t="inlineStr">
+        <is>
+          <t>Ambre</t>
+        </is>
+      </c>
+      <c r="D1488" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1488" t="n">
+        <v>95</v>
+      </c>
+      <c r="F1488" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1488" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1488" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1489" t="inlineStr">
+        <is>
+          <t>PavelMel</t>
+        </is>
+      </c>
+      <c r="C1489" t="inlineStr">
+        <is>
+          <t>Mélissa</t>
+        </is>
+      </c>
+      <c r="D1489" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1489" t="n">
+        <v>96</v>
+      </c>
+      <c r="F1489" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1489" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1489" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1490" t="inlineStr">
+        <is>
+          <t>Mylene-Jnt</t>
+        </is>
+      </c>
+      <c r="C1490" t="inlineStr">
+        <is>
+          <t>Mylène</t>
+        </is>
+      </c>
+      <c r="D1490" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1490" t="n">
+        <v>97</v>
+      </c>
+      <c r="F1490" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1490" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1490" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1491" t="inlineStr">
+        <is>
+          <t>Teddbear</t>
+        </is>
+      </c>
+      <c r="C1491" t="inlineStr">
+        <is>
+          <t>Tedy</t>
+        </is>
+      </c>
+      <c r="D1491" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E1491" t="n">
+        <v>98</v>
+      </c>
+      <c r="F1491" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1491" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1491" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1492" t="inlineStr">
+        <is>
+          <t>Camss</t>
+        </is>
+      </c>
+      <c r="C1492" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D1492" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1492" t="n">
+        <v>99</v>
+      </c>
+      <c r="F1492" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1492" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1492" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1493" t="inlineStr">
+        <is>
+          <t>SabC1</t>
+        </is>
+      </c>
+      <c r="C1493" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="D1493" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1493" t="n">
+        <v>100</v>
+      </c>
+      <c r="F1493" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1493" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1493" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1494" t="inlineStr">
+        <is>
+          <t>KIKS999</t>
+        </is>
+      </c>
+      <c r="C1494" t="inlineStr">
+        <is>
+          <t>Killian</t>
+        </is>
+      </c>
+      <c r="D1494" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1494" t="n">
+        <v>101</v>
+      </c>
+      <c r="F1494" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1494" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1494" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1495" t="inlineStr">
+        <is>
+          <t>MxKnight</t>
+        </is>
+      </c>
+      <c r="C1495" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D1495" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1495" t="n">
+        <v>102</v>
+      </c>
+      <c r="F1495" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1495" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1495" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1496" t="inlineStr">
+        <is>
+          <t>RomainLect</t>
+        </is>
+      </c>
+      <c r="C1496" t="inlineStr">
+        <is>
+          <t>romain</t>
+        </is>
+      </c>
+      <c r="D1496" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E1496" t="n">
+        <v>103</v>
+      </c>
+      <c r="F1496" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1496" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1496" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1497" t="inlineStr">
+        <is>
+          <t>SamSamH8</t>
+        </is>
+      </c>
+      <c r="C1497" t="inlineStr">
+        <is>
+          <t>Samia</t>
+        </is>
+      </c>
+      <c r="D1497" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1497" t="n">
+        <v>104</v>
+      </c>
+      <c r="F1497" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1497" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1497" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1498" t="inlineStr">
+        <is>
+          <t>Daviddesco1</t>
+        </is>
+      </c>
+      <c r="C1498" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D1498" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1498" t="n">
+        <v>105</v>
+      </c>
+      <c r="F1498" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1498" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1498" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1499" t="inlineStr">
+        <is>
+          <t>Sab_M45</t>
+        </is>
+      </c>
+      <c r="C1499" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="D1499" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1499" t="n">
+        <v>106</v>
+      </c>
+      <c r="F1499" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1499" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1499" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1500" t="inlineStr">
+        <is>
+          <t>Valentine___</t>
+        </is>
+      </c>
+      <c r="C1500" t="inlineStr">
+        <is>
+          <t>Valentine</t>
+        </is>
+      </c>
+      <c r="D1500" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1500" t="n">
+        <v>107</v>
+      </c>
+      <c r="F1500" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1500" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1500" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1501" t="inlineStr">
+        <is>
+          <t>PANENKANY</t>
+        </is>
+      </c>
+      <c r="C1501" t="inlineStr">
+        <is>
+          <t>Damien</t>
+        </is>
+      </c>
+      <c r="D1501" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1501" t="n">
+        <v>108</v>
+      </c>
+      <c r="F1501" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1501" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1501" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1502" t="inlineStr">
+        <is>
+          <t>MT35T</t>
+        </is>
+      </c>
+      <c r="C1502" t="inlineStr">
+        <is>
+          <t>Mathilde</t>
+        </is>
+      </c>
+      <c r="D1502" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1502" t="n">
+        <v>109</v>
+      </c>
+      <c r="F1502" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1502" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1502" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historique_joueurs.xlsx
+++ b/historique_joueurs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1502"/>
+  <dimension ref="A1:H1611"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50104,6 +50104,3688 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1503">
+      <c r="A1503" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1503" t="inlineStr">
+        <is>
+          <t>Filipinho95</t>
+        </is>
+      </c>
+      <c r="C1503" t="inlineStr">
+        <is>
+          <t>Filipe</t>
+        </is>
+      </c>
+      <c r="D1503" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E1503" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1503" t="n">
+        <v>410</v>
+      </c>
+      <c r="G1503" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1503" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1504" t="inlineStr">
+        <is>
+          <t>MargauxCtln</t>
+        </is>
+      </c>
+      <c r="C1504" t="inlineStr">
+        <is>
+          <t>Margaux</t>
+        </is>
+      </c>
+      <c r="D1504" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1504" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1504" t="n">
+        <v>376</v>
+      </c>
+      <c r="G1504" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1504" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1505" t="inlineStr">
+        <is>
+          <t>Mamad_Shelter</t>
+        </is>
+      </c>
+      <c r="C1505" t="inlineStr">
+        <is>
+          <t>Mamadou</t>
+        </is>
+      </c>
+      <c r="D1505" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1505" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1505" t="n">
+        <v>376</v>
+      </c>
+      <c r="G1505" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1505" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1506" t="inlineStr">
+        <is>
+          <t>MagicMath</t>
+        </is>
+      </c>
+      <c r="C1506" t="inlineStr">
+        <is>
+          <t>Mathieu</t>
+        </is>
+      </c>
+      <c r="D1506" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1506" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1506" t="n">
+        <v>376</v>
+      </c>
+      <c r="G1506" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1506" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1507" t="inlineStr">
+        <is>
+          <t>WalidSiuuuuu</t>
+        </is>
+      </c>
+      <c r="C1507" t="inlineStr">
+        <is>
+          <t>Walid</t>
+        </is>
+      </c>
+      <c r="D1507" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1507" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1507" t="n">
+        <v>356</v>
+      </c>
+      <c r="G1507" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1507" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1508" t="inlineStr">
+        <is>
+          <t>DJOSWA</t>
+        </is>
+      </c>
+      <c r="C1508" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oswaina </t>
+        </is>
+      </c>
+      <c r="D1508" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1508" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1508" t="n">
+        <v>356</v>
+      </c>
+      <c r="G1508" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1508" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1509" t="inlineStr">
+        <is>
+          <t>SID-F-ANDRE</t>
+        </is>
+      </c>
+      <c r="C1509" t="inlineStr">
+        <is>
+          <t>Denis</t>
+        </is>
+      </c>
+      <c r="D1509" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1509" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1509" t="n">
+        <v>355</v>
+      </c>
+      <c r="G1509" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1509" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1510" t="inlineStr">
+        <is>
+          <t>ChrisKr1Deg1</t>
+        </is>
+      </c>
+      <c r="C1510" t="inlineStr">
+        <is>
+          <t>christophe</t>
+        </is>
+      </c>
+      <c r="D1510" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1510" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1510" t="n">
+        <v>323</v>
+      </c>
+      <c r="G1510" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1510" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1511" t="inlineStr">
+        <is>
+          <t>Coucoucassecou</t>
+        </is>
+      </c>
+      <c r="C1511" t="inlineStr">
+        <is>
+          <t>Brayen</t>
+        </is>
+      </c>
+      <c r="D1511" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1511" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1511" t="n">
+        <v>322</v>
+      </c>
+      <c r="G1511" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1511" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1512" t="inlineStr">
+        <is>
+          <t>Paulasipi1998</t>
+        </is>
+      </c>
+      <c r="C1512" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="D1512" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1512" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1512" t="n">
+        <v>322</v>
+      </c>
+      <c r="G1512" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1512" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1513" t="inlineStr">
+        <is>
+          <t>Panaff</t>
+        </is>
+      </c>
+      <c r="C1513" t="inlineStr">
+        <is>
+          <t>Panaf</t>
+        </is>
+      </c>
+      <c r="D1513" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1513" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1513" t="n">
+        <v>315</v>
+      </c>
+      <c r="G1513" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1513" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1514" t="inlineStr">
+        <is>
+          <t>Kaliced</t>
+        </is>
+      </c>
+      <c r="C1514" t="inlineStr">
+        <is>
+          <t>Kalice</t>
+        </is>
+      </c>
+      <c r="D1514" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1514" t="n">
+        <v>12</v>
+      </c>
+      <c r="F1514" t="n">
+        <v>302</v>
+      </c>
+      <c r="G1514" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1514" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1515" t="inlineStr">
+        <is>
+          <t>FRHTCTD10</t>
+        </is>
+      </c>
+      <c r="C1515" t="inlineStr">
+        <is>
+          <t>Candice</t>
+        </is>
+      </c>
+      <c r="D1515" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1515" t="n">
+        <v>13</v>
+      </c>
+      <c r="F1515" t="n">
+        <v>282</v>
+      </c>
+      <c r="G1515" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1515" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1516" t="inlineStr">
+        <is>
+          <t>Mr-Worldwide</t>
+        </is>
+      </c>
+      <c r="C1516" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="D1516" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1516" t="n">
+        <v>14</v>
+      </c>
+      <c r="F1516" t="n">
+        <v>280</v>
+      </c>
+      <c r="G1516" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1516" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1517" t="inlineStr">
+        <is>
+          <t>Fethinho</t>
+        </is>
+      </c>
+      <c r="C1517" t="inlineStr">
+        <is>
+          <t>Fethi</t>
+        </is>
+      </c>
+      <c r="D1517" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E1517" t="n">
+        <v>15</v>
+      </c>
+      <c r="F1517" t="n">
+        <v>280</v>
+      </c>
+      <c r="G1517" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1517" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1518" t="inlineStr">
+        <is>
+          <t>Ouiouiausoleil</t>
+        </is>
+      </c>
+      <c r="C1518" t="inlineStr">
+        <is>
+          <t>Ouissal</t>
+        </is>
+      </c>
+      <c r="D1518" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1518" t="n">
+        <v>16</v>
+      </c>
+      <c r="F1518" t="n">
+        <v>280</v>
+      </c>
+      <c r="G1518" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1518" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1519" t="inlineStr">
+        <is>
+          <t>BOUGA#2JGXP</t>
+        </is>
+      </c>
+      <c r="C1519" t="inlineStr">
+        <is>
+          <t>BOUGA</t>
+        </is>
+      </c>
+      <c r="D1519" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1519" t="n">
+        <v>17</v>
+      </c>
+      <c r="F1519" t="n">
+        <v>260</v>
+      </c>
+      <c r="G1519" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1519" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1520" t="inlineStr">
+        <is>
+          <t>Anais757817</t>
+        </is>
+      </c>
+      <c r="C1520" t="inlineStr">
+        <is>
+          <t>Anaïs</t>
+        </is>
+      </c>
+      <c r="D1520" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1520" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1520" t="n">
+        <v>260</v>
+      </c>
+      <c r="G1520" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1520" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1521" t="inlineStr">
+        <is>
+          <t>MatuRenard</t>
+        </is>
+      </c>
+      <c r="C1521" t="inlineStr">
+        <is>
+          <t>Mathias</t>
+        </is>
+      </c>
+      <c r="D1521" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1521" t="n">
+        <v>19</v>
+      </c>
+      <c r="F1521" t="n">
+        <v>259</v>
+      </c>
+      <c r="G1521" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1521" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1522" t="inlineStr">
+        <is>
+          <t>Liliuus</t>
+        </is>
+      </c>
+      <c r="C1522" t="inlineStr">
+        <is>
+          <t>Lilia</t>
+        </is>
+      </c>
+      <c r="D1522" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1522" t="n">
+        <v>20</v>
+      </c>
+      <c r="F1522" t="n">
+        <v>259</v>
+      </c>
+      <c r="G1522" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1522" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1523" t="inlineStr">
+        <is>
+          <t>Ppo28</t>
+        </is>
+      </c>
+      <c r="C1523" t="inlineStr">
+        <is>
+          <t>Prescylla</t>
+        </is>
+      </c>
+      <c r="D1523" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E1523" t="n">
+        <v>21</v>
+      </c>
+      <c r="F1523" t="n">
+        <v>259</v>
+      </c>
+      <c r="G1523" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1523" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1524" t="inlineStr">
+        <is>
+          <t>Gronaldo_95</t>
+        </is>
+      </c>
+      <c r="C1524" t="inlineStr">
+        <is>
+          <t>Gronaldo</t>
+        </is>
+      </c>
+      <c r="D1524" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1524" t="n">
+        <v>22</v>
+      </c>
+      <c r="F1524" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1524" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1524" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1525" t="inlineStr">
+        <is>
+          <t>Devilrock95</t>
+        </is>
+      </c>
+      <c r="C1525" t="inlineStr">
+        <is>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="D1525" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1525" t="n">
+        <v>23</v>
+      </c>
+      <c r="F1525" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1525" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1525" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1526" t="inlineStr">
+        <is>
+          <t>Ninaaaa</t>
+        </is>
+      </c>
+      <c r="C1526" t="inlineStr">
+        <is>
+          <t>Nina</t>
+        </is>
+      </c>
+      <c r="D1526" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1526" t="n">
+        <v>24</v>
+      </c>
+      <c r="F1526" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1526" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1526" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1527" t="inlineStr">
+        <is>
+          <t>Cleem22</t>
+        </is>
+      </c>
+      <c r="C1527" t="inlineStr">
+        <is>
+          <t>Clemence</t>
+        </is>
+      </c>
+      <c r="D1527" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1527" t="n">
+        <v>25</v>
+      </c>
+      <c r="F1527" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1527" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1527" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1528" t="inlineStr">
+        <is>
+          <t>catherine#5FRTD</t>
+        </is>
+      </c>
+      <c r="C1528" t="inlineStr">
+        <is>
+          <t>catherine</t>
+        </is>
+      </c>
+      <c r="D1528" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1528" t="n">
+        <v>26</v>
+      </c>
+      <c r="F1528" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1528" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1528" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1529" t="inlineStr">
+        <is>
+          <t>Maruyama</t>
+        </is>
+      </c>
+      <c r="C1529" t="inlineStr">
+        <is>
+          <t>Gabrielle</t>
+        </is>
+      </c>
+      <c r="D1529" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1529" t="n">
+        <v>27</v>
+      </c>
+      <c r="F1529" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1529" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1529" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1530" t="inlineStr">
+        <is>
+          <t>Leandrocp</t>
+        </is>
+      </c>
+      <c r="C1530" t="inlineStr">
+        <is>
+          <t>Leandro</t>
+        </is>
+      </c>
+      <c r="D1530" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1530" t="n">
+        <v>28</v>
+      </c>
+      <c r="F1530" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1530" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1530" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1531" t="inlineStr">
+        <is>
+          <t>Marion1822</t>
+        </is>
+      </c>
+      <c r="C1531" t="inlineStr">
+        <is>
+          <t>Marion</t>
+        </is>
+      </c>
+      <c r="D1531" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1531" t="n">
+        <v>29</v>
+      </c>
+      <c r="F1531" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1531" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1531" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1532" t="inlineStr">
+        <is>
+          <t>chaychaychay</t>
+        </is>
+      </c>
+      <c r="C1532" t="inlineStr">
+        <is>
+          <t>Chaymaa</t>
+        </is>
+      </c>
+      <c r="D1532" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1532" t="n">
+        <v>30</v>
+      </c>
+      <c r="F1532" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1532" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1532" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1533" t="inlineStr">
+        <is>
+          <t>WIL1610</t>
+        </is>
+      </c>
+      <c r="C1533" t="inlineStr">
+        <is>
+          <t>William</t>
+        </is>
+      </c>
+      <c r="D1533" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1533" t="n">
+        <v>31</v>
+      </c>
+      <c r="F1533" t="n">
+        <v>233</v>
+      </c>
+      <c r="G1533" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1533" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="A1534" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1534" t="inlineStr">
+        <is>
+          <t>Erwan#4G91X</t>
+        </is>
+      </c>
+      <c r="C1534" t="inlineStr">
+        <is>
+          <t>Erwan</t>
+        </is>
+      </c>
+      <c r="D1534" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1534" t="n">
+        <v>32</v>
+      </c>
+      <c r="F1534" t="n">
+        <v>219</v>
+      </c>
+      <c r="G1534" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1534" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1535" t="inlineStr">
+        <is>
+          <t>GLR_PRIME</t>
+        </is>
+      </c>
+      <c r="C1535" t="inlineStr">
+        <is>
+          <t>Gabriel</t>
+        </is>
+      </c>
+      <c r="D1535" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1535" t="n">
+        <v>33</v>
+      </c>
+      <c r="F1535" t="n">
+        <v>219</v>
+      </c>
+      <c r="G1535" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1535" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1536" t="inlineStr">
+        <is>
+          <t>Exia95</t>
+        </is>
+      </c>
+      <c r="C1536" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D1536" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1536" t="n">
+        <v>34</v>
+      </c>
+      <c r="F1536" t="n">
+        <v>212</v>
+      </c>
+      <c r="G1536" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1536" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1537" t="inlineStr">
+        <is>
+          <t>Matt#4B4CU</t>
+        </is>
+      </c>
+      <c r="C1537" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="D1537" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1537" t="n">
+        <v>35</v>
+      </c>
+      <c r="F1537" t="n">
+        <v>211</v>
+      </c>
+      <c r="G1537" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1537" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1538" t="inlineStr">
+        <is>
+          <t>dian-bgt</t>
+        </is>
+      </c>
+      <c r="C1538" t="inlineStr">
+        <is>
+          <t>Diane</t>
+        </is>
+      </c>
+      <c r="D1538" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1538" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1538" t="n">
+        <v>206</v>
+      </c>
+      <c r="G1538" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1538" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1539" t="inlineStr">
+        <is>
+          <t>LilianeB</t>
+        </is>
+      </c>
+      <c r="C1539" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liliane </t>
+        </is>
+      </c>
+      <c r="D1539" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1539" t="n">
+        <v>37</v>
+      </c>
+      <c r="F1539" t="n">
+        <v>206</v>
+      </c>
+      <c r="G1539" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1539" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1540" t="inlineStr">
+        <is>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="C1540" t="inlineStr">
+        <is>
+          <t>Julie</t>
+        </is>
+      </c>
+      <c r="D1540" t="inlineStr"/>
+      <c r="E1540" t="n">
+        <v>38</v>
+      </c>
+      <c r="F1540" t="n">
+        <v>206</v>
+      </c>
+      <c r="G1540" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1540" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1541" t="inlineStr">
+        <is>
+          <t>Romain_JO</t>
+        </is>
+      </c>
+      <c r="C1541" t="inlineStr">
+        <is>
+          <t>Romain J</t>
+        </is>
+      </c>
+      <c r="D1541" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1541" t="n">
+        <v>39</v>
+      </c>
+      <c r="F1541" t="n">
+        <v>191</v>
+      </c>
+      <c r="G1541" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1541" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1542" t="inlineStr">
+        <is>
+          <t>JeremFZ</t>
+        </is>
+      </c>
+      <c r="C1542" t="inlineStr">
+        <is>
+          <t>Jérémy</t>
+        </is>
+      </c>
+      <c r="D1542" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1542" t="n">
+        <v>40</v>
+      </c>
+      <c r="F1542" t="n">
+        <v>191</v>
+      </c>
+      <c r="G1542" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1542" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1543" t="inlineStr">
+        <is>
+          <t>AudreyB225</t>
+        </is>
+      </c>
+      <c r="C1543" t="inlineStr">
+        <is>
+          <t>Audrey</t>
+        </is>
+      </c>
+      <c r="D1543" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1543" t="n">
+        <v>41</v>
+      </c>
+      <c r="F1543" t="n">
+        <v>190</v>
+      </c>
+      <c r="G1543" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1543" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1544" t="inlineStr">
+        <is>
+          <t>BadrLeo</t>
+        </is>
+      </c>
+      <c r="C1544" t="inlineStr">
+        <is>
+          <t>Badr Leo</t>
+        </is>
+      </c>
+      <c r="D1544" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1544" t="n">
+        <v>42</v>
+      </c>
+      <c r="F1544" t="n">
+        <v>186</v>
+      </c>
+      <c r="G1544" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1544" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1545" t="inlineStr">
+        <is>
+          <t>YassineZ95</t>
+        </is>
+      </c>
+      <c r="C1545" t="inlineStr">
+        <is>
+          <t>Yassine Z</t>
+        </is>
+      </c>
+      <c r="D1545" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E1545" t="n">
+        <v>43</v>
+      </c>
+      <c r="F1545" t="n">
+        <v>186</v>
+      </c>
+      <c r="G1545" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1545" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1546" t="inlineStr">
+        <is>
+          <t>Ilan_260_</t>
+        </is>
+      </c>
+      <c r="C1546" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ilann </t>
+        </is>
+      </c>
+      <c r="D1546" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1546" t="n">
+        <v>44</v>
+      </c>
+      <c r="F1546" t="n">
+        <v>185</v>
+      </c>
+      <c r="G1546" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1546" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1547" t="inlineStr">
+        <is>
+          <t>abihuts</t>
+        </is>
+      </c>
+      <c r="C1547" t="inlineStr">
+        <is>
+          <t>Antonio Moctezuma</t>
+        </is>
+      </c>
+      <c r="D1547" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1547" t="n">
+        <v>45</v>
+      </c>
+      <c r="F1547" t="n">
+        <v>172</v>
+      </c>
+      <c r="G1547" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1547" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1548" t="inlineStr">
+        <is>
+          <t>Chadia__</t>
+        </is>
+      </c>
+      <c r="C1548" t="inlineStr">
+        <is>
+          <t>Chadia</t>
+        </is>
+      </c>
+      <c r="D1548" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1548" t="n">
+        <v>46</v>
+      </c>
+      <c r="F1548" t="n">
+        <v>170</v>
+      </c>
+      <c r="G1548" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1548" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1549" t="inlineStr">
+        <is>
+          <t>Stephbreton</t>
+        </is>
+      </c>
+      <c r="C1549" t="inlineStr">
+        <is>
+          <t>STEPHANE</t>
+        </is>
+      </c>
+      <c r="D1549" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1549" t="n">
+        <v>47</v>
+      </c>
+      <c r="F1549" t="n">
+        <v>166</v>
+      </c>
+      <c r="G1549" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1549" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1550" t="inlineStr">
+        <is>
+          <t>GOAT#UE2WM8M9</t>
+        </is>
+      </c>
+      <c r="C1550" t="inlineStr">
+        <is>
+          <t>Marilena</t>
+        </is>
+      </c>
+      <c r="D1550" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1550" t="n">
+        <v>48</v>
+      </c>
+      <c r="F1550" t="n">
+        <v>165</v>
+      </c>
+      <c r="G1550" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1550" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1551" t="inlineStr">
+        <is>
+          <t>Ceciledp</t>
+        </is>
+      </c>
+      <c r="C1551" t="inlineStr">
+        <is>
+          <t>Cécile</t>
+        </is>
+      </c>
+      <c r="D1551" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1551" t="n">
+        <v>49</v>
+      </c>
+      <c r="F1551" t="n">
+        <v>145</v>
+      </c>
+      <c r="G1551" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1551" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1552" t="inlineStr">
+        <is>
+          <t>Fuzo697</t>
+        </is>
+      </c>
+      <c r="C1552" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D1552" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1552" t="n">
+        <v>50</v>
+      </c>
+      <c r="F1552" t="n">
+        <v>145</v>
+      </c>
+      <c r="G1552" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1552" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1553" t="inlineStr">
+        <is>
+          <t>Yebri</t>
+        </is>
+      </c>
+      <c r="C1553" t="inlineStr">
+        <is>
+          <t>Brieuc</t>
+        </is>
+      </c>
+      <c r="D1553" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1553" t="n">
+        <v>51</v>
+      </c>
+      <c r="F1553" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1553" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1553" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1554" t="inlineStr">
+        <is>
+          <t>Leo_durable</t>
+        </is>
+      </c>
+      <c r="C1554" t="inlineStr">
+        <is>
+          <t>Leo</t>
+        </is>
+      </c>
+      <c r="D1554" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1554" t="n">
+        <v>52</v>
+      </c>
+      <c r="F1554" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1554" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1554" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1555" t="inlineStr">
+        <is>
+          <t>EmyEnzo</t>
+        </is>
+      </c>
+      <c r="C1555" t="inlineStr">
+        <is>
+          <t>Emilie</t>
+        </is>
+      </c>
+      <c r="D1555" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1555" t="n">
+        <v>53</v>
+      </c>
+      <c r="F1555" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1555" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1555" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1556" t="inlineStr">
+        <is>
+          <t>Priscilla#4LCAF</t>
+        </is>
+      </c>
+      <c r="C1556" t="inlineStr">
+        <is>
+          <t>Priscilla</t>
+        </is>
+      </c>
+      <c r="D1556" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1556" t="n">
+        <v>54</v>
+      </c>
+      <c r="F1556" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1556" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1556" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1557" t="inlineStr">
+        <is>
+          <t>Pipou931</t>
+        </is>
+      </c>
+      <c r="C1557" t="inlineStr">
+        <is>
+          <t>Juliie</t>
+        </is>
+      </c>
+      <c r="D1557" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1557" t="n">
+        <v>55</v>
+      </c>
+      <c r="F1557" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1557" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1557" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1558" t="inlineStr">
+        <is>
+          <t>Farah_One</t>
+        </is>
+      </c>
+      <c r="C1558" t="inlineStr">
+        <is>
+          <t>Farah</t>
+        </is>
+      </c>
+      <c r="D1558" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1558" t="n">
+        <v>56</v>
+      </c>
+      <c r="F1558" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1558" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1558" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1559" t="inlineStr">
+        <is>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="C1559" t="inlineStr">
+        <is>
+          <t>François</t>
+        </is>
+      </c>
+      <c r="D1559" t="inlineStr"/>
+      <c r="E1559" t="n">
+        <v>57</v>
+      </c>
+      <c r="F1559" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1559" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1559" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1560" t="inlineStr">
+        <is>
+          <t>Seesee</t>
+        </is>
+      </c>
+      <c r="C1560" t="inlineStr">
+        <is>
+          <t>Selver</t>
+        </is>
+      </c>
+      <c r="D1560" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1560" t="n">
+        <v>58</v>
+      </c>
+      <c r="F1560" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1560" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1560" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1561" t="inlineStr">
+        <is>
+          <t>lenaaik</t>
+        </is>
+      </c>
+      <c r="C1561" t="inlineStr">
+        <is>
+          <t>Lénaïk</t>
+        </is>
+      </c>
+      <c r="D1561" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1561" t="n">
+        <v>59</v>
+      </c>
+      <c r="F1561" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1561" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1561" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1562" t="inlineStr">
+        <is>
+          <t>C4M</t>
+        </is>
+      </c>
+      <c r="C1562" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D1562" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1562" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1562" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1562" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1562" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1563" t="inlineStr">
+        <is>
+          <t>Rosa_1009</t>
+        </is>
+      </c>
+      <c r="C1563" t="inlineStr">
+        <is>
+          <t>Rosaline</t>
+        </is>
+      </c>
+      <c r="D1563" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1563" t="n">
+        <v>61</v>
+      </c>
+      <c r="F1563" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1563" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1563" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1564" t="inlineStr">
+        <is>
+          <t>Elisewiss</t>
+        </is>
+      </c>
+      <c r="C1564" t="inlineStr">
+        <is>
+          <t>Elise</t>
+        </is>
+      </c>
+      <c r="D1564" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1564" t="n">
+        <v>62</v>
+      </c>
+      <c r="F1564" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1564" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1564" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1565" t="inlineStr">
+        <is>
+          <t>Soraya-Y</t>
+        </is>
+      </c>
+      <c r="C1565" t="inlineStr">
+        <is>
+          <t>Soraya</t>
+        </is>
+      </c>
+      <c r="D1565" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1565" t="n">
+        <v>63</v>
+      </c>
+      <c r="F1565" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1565" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1565" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1566">
+      <c r="A1566" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1566" t="inlineStr">
+        <is>
+          <t>1993ahm</t>
+        </is>
+      </c>
+      <c r="C1566" t="inlineStr">
+        <is>
+          <t>Ahmed</t>
+        </is>
+      </c>
+      <c r="D1566" t="inlineStr"/>
+      <c r="E1566" t="n">
+        <v>64</v>
+      </c>
+      <c r="F1566" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1566" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1566" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="A1567" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1567" t="inlineStr">
+        <is>
+          <t>MyriamAmr</t>
+        </is>
+      </c>
+      <c r="C1567" t="inlineStr">
+        <is>
+          <t>Myriam</t>
+        </is>
+      </c>
+      <c r="D1567" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1567" t="n">
+        <v>65</v>
+      </c>
+      <c r="F1567" t="n">
+        <v>137</v>
+      </c>
+      <c r="G1567" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1567" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1568">
+      <c r="A1568" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1568" t="inlineStr">
+        <is>
+          <t>Timy</t>
+        </is>
+      </c>
+      <c r="C1568" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="D1568" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1568" t="n">
+        <v>66</v>
+      </c>
+      <c r="F1568" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1568" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1568" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="A1569" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1569" t="inlineStr">
+        <is>
+          <t>JEVAISGAGNER10</t>
+        </is>
+      </c>
+      <c r="C1569" t="inlineStr">
+        <is>
+          <t>Xavier</t>
+        </is>
+      </c>
+      <c r="D1569" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1569" t="n">
+        <v>67</v>
+      </c>
+      <c r="F1569" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1569" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1569" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="A1570" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1570" t="inlineStr">
+        <is>
+          <t>HamzaG</t>
+        </is>
+      </c>
+      <c r="C1570" t="inlineStr">
+        <is>
+          <t>Hamza</t>
+        </is>
+      </c>
+      <c r="D1570" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1570" t="n">
+        <v>68</v>
+      </c>
+      <c r="F1570" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1570" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1570" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1571" t="inlineStr">
+        <is>
+          <t>LeaBrd</t>
+        </is>
+      </c>
+      <c r="C1571" t="inlineStr">
+        <is>
+          <t>Léa</t>
+        </is>
+      </c>
+      <c r="D1571" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1571" t="n">
+        <v>69</v>
+      </c>
+      <c r="F1571" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1571" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1571" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1572" t="inlineStr">
+        <is>
+          <t>davidd23</t>
+        </is>
+      </c>
+      <c r="C1572" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D1572" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1572" t="n">
+        <v>70</v>
+      </c>
+      <c r="F1572" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1572" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1572" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1573" t="inlineStr">
+        <is>
+          <t>Nonito20</t>
+        </is>
+      </c>
+      <c r="C1573" t="inlineStr">
+        <is>
+          <t>Arnaud</t>
+        </is>
+      </c>
+      <c r="D1573" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1573" t="n">
+        <v>71</v>
+      </c>
+      <c r="F1573" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1573" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1573" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1574" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="C1574" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="D1574" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1574" t="n">
+        <v>72</v>
+      </c>
+      <c r="F1574" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1574" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1574" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1575" t="inlineStr">
+        <is>
+          <t>Kolas</t>
+        </is>
+      </c>
+      <c r="C1575" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D1575" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1575" t="n">
+        <v>73</v>
+      </c>
+      <c r="F1575" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1575" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1575" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1576" t="inlineStr">
+        <is>
+          <t>Laetice2020</t>
+        </is>
+      </c>
+      <c r="C1576" t="inlineStr">
+        <is>
+          <t>Laetitia</t>
+        </is>
+      </c>
+      <c r="D1576" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1576" t="n">
+        <v>74</v>
+      </c>
+      <c r="F1576" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1576" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1576" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1577" t="inlineStr">
+        <is>
+          <t>Emilay</t>
+        </is>
+      </c>
+      <c r="C1577" t="inlineStr">
+        <is>
+          <t>Émilie</t>
+        </is>
+      </c>
+      <c r="D1577" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1577" t="n">
+        <v>75</v>
+      </c>
+      <c r="F1577" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1577" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1577" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1578" t="inlineStr">
+        <is>
+          <t>Lyzone</t>
+        </is>
+      </c>
+      <c r="C1578" t="inlineStr">
+        <is>
+          <t>Lison</t>
+        </is>
+      </c>
+      <c r="D1578" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1578" t="n">
+        <v>76</v>
+      </c>
+      <c r="F1578" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1578" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1578" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1579" t="inlineStr">
+        <is>
+          <t>Melissagzb</t>
+        </is>
+      </c>
+      <c r="C1579" t="inlineStr">
+        <is>
+          <t>Melissa</t>
+        </is>
+      </c>
+      <c r="D1579" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1579" t="n">
+        <v>77</v>
+      </c>
+      <c r="F1579" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1579" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1579" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1580" t="inlineStr">
+        <is>
+          <t>Marie__92</t>
+        </is>
+      </c>
+      <c r="C1580" t="inlineStr">
+        <is>
+          <t>Marie</t>
+        </is>
+      </c>
+      <c r="D1580" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1580" t="n">
+        <v>78</v>
+      </c>
+      <c r="F1580" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1580" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1580" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1581" t="inlineStr">
+        <is>
+          <t>K_Marp</t>
+        </is>
+      </c>
+      <c r="C1581" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
+      <c r="D1581" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1581" t="n">
+        <v>79</v>
+      </c>
+      <c r="F1581" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1581" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1581" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1582" t="inlineStr">
+        <is>
+          <t>Cindie_JJA</t>
+        </is>
+      </c>
+      <c r="C1582" t="inlineStr">
+        <is>
+          <t>Cindie</t>
+        </is>
+      </c>
+      <c r="D1582" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1582" t="n">
+        <v>80</v>
+      </c>
+      <c r="F1582" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1582" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1582" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1583" t="inlineStr">
+        <is>
+          <t>JKInternational</t>
+        </is>
+      </c>
+      <c r="C1583" t="inlineStr">
+        <is>
+          <t>Joachim</t>
+        </is>
+      </c>
+      <c r="D1583" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1583" t="n">
+        <v>81</v>
+      </c>
+      <c r="F1583" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1583" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1583" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1584" t="inlineStr">
+        <is>
+          <t>GOAT#UE4U8KA6</t>
+        </is>
+      </c>
+      <c r="C1584" t="inlineStr">
+        <is>
+          <t>Jean Baptiste</t>
+        </is>
+      </c>
+      <c r="D1584" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1584" t="n">
+        <v>82</v>
+      </c>
+      <c r="F1584" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1584" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1584" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1585" t="inlineStr">
+        <is>
+          <t>goat#AD6GS</t>
+        </is>
+      </c>
+      <c r="C1585" t="inlineStr">
+        <is>
+          <t>goat</t>
+        </is>
+      </c>
+      <c r="D1585" t="inlineStr"/>
+      <c r="E1585" t="n">
+        <v>83</v>
+      </c>
+      <c r="F1585" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1585" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1585" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1586" t="inlineStr">
+        <is>
+          <t>Camillewbl</t>
+        </is>
+      </c>
+      <c r="C1586" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D1586" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1586" t="n">
+        <v>84</v>
+      </c>
+      <c r="F1586" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1586" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1586" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1587" t="inlineStr">
+        <is>
+          <t>Emma_Noel</t>
+        </is>
+      </c>
+      <c r="C1587" t="inlineStr">
+        <is>
+          <t>Emma</t>
+        </is>
+      </c>
+      <c r="D1587" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1587" t="n">
+        <v>85</v>
+      </c>
+      <c r="F1587" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1587" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1587" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1588" t="inlineStr">
+        <is>
+          <t>RBTL</t>
+        </is>
+      </c>
+      <c r="C1588" t="inlineStr">
+        <is>
+          <t>lea</t>
+        </is>
+      </c>
+      <c r="D1588" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1588" t="n">
+        <v>86</v>
+      </c>
+      <c r="F1588" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1588" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1588" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1589" t="inlineStr">
+        <is>
+          <t>A-MOE</t>
+        </is>
+      </c>
+      <c r="C1589" t="inlineStr">
+        <is>
+          <t>Françoise</t>
+        </is>
+      </c>
+      <c r="D1589" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1589" t="n">
+        <v>87</v>
+      </c>
+      <c r="F1589" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1589" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1589" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1590" t="inlineStr">
+        <is>
+          <t>Davido#4BZ54</t>
+        </is>
+      </c>
+      <c r="C1590" t="inlineStr">
+        <is>
+          <t>Davido</t>
+        </is>
+      </c>
+      <c r="D1590" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1590" t="n">
+        <v>88</v>
+      </c>
+      <c r="F1590" t="n">
+        <v>96</v>
+      </c>
+      <c r="G1590" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1590" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1591" t="inlineStr">
+        <is>
+          <t>BrickXVI</t>
+        </is>
+      </c>
+      <c r="C1591" t="inlineStr">
+        <is>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="D1591" t="inlineStr"/>
+      <c r="E1591" t="n">
+        <v>89</v>
+      </c>
+      <c r="F1591" t="n">
+        <v>74</v>
+      </c>
+      <c r="G1591" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1591" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1592" t="inlineStr">
+        <is>
+          <t>Taylor2901</t>
+        </is>
+      </c>
+      <c r="C1592" t="inlineStr">
+        <is>
+          <t>ousmane</t>
+        </is>
+      </c>
+      <c r="D1592" t="inlineStr"/>
+      <c r="E1592" t="n">
+        <v>90</v>
+      </c>
+      <c r="F1592" t="n">
+        <v>74</v>
+      </c>
+      <c r="G1592" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1592" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1593" t="inlineStr">
+        <is>
+          <t>Ze_GOAT</t>
+        </is>
+      </c>
+      <c r="C1593" t="inlineStr">
+        <is>
+          <t>Yasser</t>
+        </is>
+      </c>
+      <c r="D1593" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1593" t="n">
+        <v>91</v>
+      </c>
+      <c r="F1593" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1593" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1593" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1594" t="inlineStr">
+        <is>
+          <t>Krol#4R8XC</t>
+        </is>
+      </c>
+      <c r="C1594" t="inlineStr">
+        <is>
+          <t>Krol</t>
+        </is>
+      </c>
+      <c r="D1594" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1594" t="n">
+        <v>92</v>
+      </c>
+      <c r="F1594" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1594" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1594" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1595" t="inlineStr">
+        <is>
+          <t>PacoSarra</t>
+        </is>
+      </c>
+      <c r="C1595" t="inlineStr">
+        <is>
+          <t>Ibra</t>
+        </is>
+      </c>
+      <c r="D1595" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1595" t="n">
+        <v>93</v>
+      </c>
+      <c r="F1595" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1595" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1595" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1596" t="inlineStr">
+        <is>
+          <t>Droit_au_but7723</t>
+        </is>
+      </c>
+      <c r="C1596" t="inlineStr">
+        <is>
+          <t>Calixthe</t>
+        </is>
+      </c>
+      <c r="D1596" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1596" t="n">
+        <v>94</v>
+      </c>
+      <c r="F1596" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1596" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1596" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1597" t="inlineStr">
+        <is>
+          <t>Ambrepic</t>
+        </is>
+      </c>
+      <c r="C1597" t="inlineStr">
+        <is>
+          <t>Ambre</t>
+        </is>
+      </c>
+      <c r="D1597" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1597" t="n">
+        <v>95</v>
+      </c>
+      <c r="F1597" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1597" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1597" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1598" t="inlineStr">
+        <is>
+          <t>PavelMel</t>
+        </is>
+      </c>
+      <c r="C1598" t="inlineStr">
+        <is>
+          <t>Mélissa</t>
+        </is>
+      </c>
+      <c r="D1598" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1598" t="n">
+        <v>96</v>
+      </c>
+      <c r="F1598" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1598" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1598" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1599" t="inlineStr">
+        <is>
+          <t>Mylene-Jnt</t>
+        </is>
+      </c>
+      <c r="C1599" t="inlineStr">
+        <is>
+          <t>Mylène</t>
+        </is>
+      </c>
+      <c r="D1599" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1599" t="n">
+        <v>97</v>
+      </c>
+      <c r="F1599" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1599" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1599" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1600" t="inlineStr">
+        <is>
+          <t>Teddbear</t>
+        </is>
+      </c>
+      <c r="C1600" t="inlineStr">
+        <is>
+          <t>Tedy</t>
+        </is>
+      </c>
+      <c r="D1600" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E1600" t="n">
+        <v>98</v>
+      </c>
+      <c r="F1600" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1600" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1600" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1601" t="inlineStr">
+        <is>
+          <t>Camss</t>
+        </is>
+      </c>
+      <c r="C1601" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D1601" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1601" t="n">
+        <v>99</v>
+      </c>
+      <c r="F1601" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1601" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1601" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1602">
+      <c r="A1602" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1602" t="inlineStr">
+        <is>
+          <t>SabC1</t>
+        </is>
+      </c>
+      <c r="C1602" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="D1602" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1602" t="n">
+        <v>100</v>
+      </c>
+      <c r="F1602" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1602" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1602" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1603" t="inlineStr">
+        <is>
+          <t>KIKS999</t>
+        </is>
+      </c>
+      <c r="C1603" t="inlineStr">
+        <is>
+          <t>Killian</t>
+        </is>
+      </c>
+      <c r="D1603" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1603" t="n">
+        <v>101</v>
+      </c>
+      <c r="F1603" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1603" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1603" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1604" t="inlineStr">
+        <is>
+          <t>MxKnight</t>
+        </is>
+      </c>
+      <c r="C1604" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D1604" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1604" t="n">
+        <v>102</v>
+      </c>
+      <c r="F1604" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1604" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1604" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1605">
+      <c r="A1605" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1605" t="inlineStr">
+        <is>
+          <t>RomainLect</t>
+        </is>
+      </c>
+      <c r="C1605" t="inlineStr">
+        <is>
+          <t>romain</t>
+        </is>
+      </c>
+      <c r="D1605" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E1605" t="n">
+        <v>103</v>
+      </c>
+      <c r="F1605" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1605" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1605" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1606">
+      <c r="A1606" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1606" t="inlineStr">
+        <is>
+          <t>SamSamH8</t>
+        </is>
+      </c>
+      <c r="C1606" t="inlineStr">
+        <is>
+          <t>Samia</t>
+        </is>
+      </c>
+      <c r="D1606" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1606" t="n">
+        <v>104</v>
+      </c>
+      <c r="F1606" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1606" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1606" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="A1607" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1607" t="inlineStr">
+        <is>
+          <t>Daviddesco1</t>
+        </is>
+      </c>
+      <c r="C1607" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D1607" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1607" t="n">
+        <v>105</v>
+      </c>
+      <c r="F1607" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1607" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1607" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1608">
+      <c r="A1608" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1608" t="inlineStr">
+        <is>
+          <t>Sab_M45</t>
+        </is>
+      </c>
+      <c r="C1608" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="D1608" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1608" t="n">
+        <v>106</v>
+      </c>
+      <c r="F1608" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1608" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1608" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="A1609" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1609" t="inlineStr">
+        <is>
+          <t>Valentine___</t>
+        </is>
+      </c>
+      <c r="C1609" t="inlineStr">
+        <is>
+          <t>Valentine</t>
+        </is>
+      </c>
+      <c r="D1609" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1609" t="n">
+        <v>107</v>
+      </c>
+      <c r="F1609" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1609" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1609" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1610">
+      <c r="A1610" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1610" t="inlineStr">
+        <is>
+          <t>PANENKANY</t>
+        </is>
+      </c>
+      <c r="C1610" t="inlineStr">
+        <is>
+          <t>Damien</t>
+        </is>
+      </c>
+      <c r="D1610" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1610" t="n">
+        <v>108</v>
+      </c>
+      <c r="F1610" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1610" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1610" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1611" t="inlineStr">
+        <is>
+          <t>MT35T</t>
+        </is>
+      </c>
+      <c r="C1611" t="inlineStr">
+        <is>
+          <t>Mathilde</t>
+        </is>
+      </c>
+      <c r="D1611" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1611" t="n">
+        <v>109</v>
+      </c>
+      <c r="F1611" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1611" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1611" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historique_joueurs.xlsx
+++ b/historique_joueurs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1611"/>
+  <dimension ref="A1:H1720"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53786,6 +53786,3688 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1612">
+      <c r="A1612" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1612" t="inlineStr">
+        <is>
+          <t>Filipinho95</t>
+        </is>
+      </c>
+      <c r="C1612" t="inlineStr">
+        <is>
+          <t>Filipe</t>
+        </is>
+      </c>
+      <c r="D1612" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1612" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1612" t="n">
+        <v>443</v>
+      </c>
+      <c r="G1612" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1612" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1613">
+      <c r="A1613" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1613" t="inlineStr">
+        <is>
+          <t>MargauxCtln</t>
+        </is>
+      </c>
+      <c r="C1613" t="inlineStr">
+        <is>
+          <t>Margaux</t>
+        </is>
+      </c>
+      <c r="D1613" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1613" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1613" t="n">
+        <v>409</v>
+      </c>
+      <c r="G1613" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1613" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1614">
+      <c r="A1614" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1614" t="inlineStr">
+        <is>
+          <t>Mamad_Shelter</t>
+        </is>
+      </c>
+      <c r="C1614" t="inlineStr">
+        <is>
+          <t>Mamadou</t>
+        </is>
+      </c>
+      <c r="D1614" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1614" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1614" t="n">
+        <v>409</v>
+      </c>
+      <c r="G1614" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1614" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1615" t="inlineStr">
+        <is>
+          <t>MagicMath</t>
+        </is>
+      </c>
+      <c r="C1615" t="inlineStr">
+        <is>
+          <t>Mathieu</t>
+        </is>
+      </c>
+      <c r="D1615" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1615" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1615" t="n">
+        <v>409</v>
+      </c>
+      <c r="G1615" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1615" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1616" t="inlineStr">
+        <is>
+          <t>Coucoucassecou</t>
+        </is>
+      </c>
+      <c r="C1616" t="inlineStr">
+        <is>
+          <t>Brayen</t>
+        </is>
+      </c>
+      <c r="D1616" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1616" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1616" t="n">
+        <v>405</v>
+      </c>
+      <c r="G1616" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1616" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="A1617" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1617" t="inlineStr">
+        <is>
+          <t>DJOSWA</t>
+        </is>
+      </c>
+      <c r="C1617" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oswaina </t>
+        </is>
+      </c>
+      <c r="D1617" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1617" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1617" t="n">
+        <v>389</v>
+      </c>
+      <c r="G1617" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1617" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1618" t="inlineStr">
+        <is>
+          <t>SID-F-ANDRE</t>
+        </is>
+      </c>
+      <c r="C1618" t="inlineStr">
+        <is>
+          <t>Denis</t>
+        </is>
+      </c>
+      <c r="D1618" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1618" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1618" t="n">
+        <v>388</v>
+      </c>
+      <c r="G1618" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1618" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1619" t="inlineStr">
+        <is>
+          <t>FRHTCTD10</t>
+        </is>
+      </c>
+      <c r="C1619" t="inlineStr">
+        <is>
+          <t>Candice</t>
+        </is>
+      </c>
+      <c r="D1619" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1619" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1619" t="n">
+        <v>365</v>
+      </c>
+      <c r="G1619" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1619" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1620">
+      <c r="A1620" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1620" t="inlineStr">
+        <is>
+          <t>WalidSiuuuuu</t>
+        </is>
+      </c>
+      <c r="C1620" t="inlineStr">
+        <is>
+          <t>Walid</t>
+        </is>
+      </c>
+      <c r="D1620" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1620" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1620" t="n">
+        <v>356</v>
+      </c>
+      <c r="G1620" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1620" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1621" t="inlineStr">
+        <is>
+          <t>ChrisKr1Deg1</t>
+        </is>
+      </c>
+      <c r="C1621" t="inlineStr">
+        <is>
+          <t>christophe</t>
+        </is>
+      </c>
+      <c r="D1621" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1621" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1621" t="n">
+        <v>356</v>
+      </c>
+      <c r="G1621" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1621" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1622">
+      <c r="A1622" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1622" t="inlineStr">
+        <is>
+          <t>Paulasipi1998</t>
+        </is>
+      </c>
+      <c r="C1622" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="D1622" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1622" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1622" t="n">
+        <v>355</v>
+      </c>
+      <c r="G1622" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1622" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1623" t="inlineStr">
+        <is>
+          <t>Panaff</t>
+        </is>
+      </c>
+      <c r="C1623" t="inlineStr">
+        <is>
+          <t>Panaf</t>
+        </is>
+      </c>
+      <c r="D1623" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1623" t="n">
+        <v>12</v>
+      </c>
+      <c r="F1623" t="n">
+        <v>348</v>
+      </c>
+      <c r="G1623" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1623" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1624" t="inlineStr">
+        <is>
+          <t>Kaliced</t>
+        </is>
+      </c>
+      <c r="C1624" t="inlineStr">
+        <is>
+          <t>Kalice</t>
+        </is>
+      </c>
+      <c r="D1624" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1624" t="n">
+        <v>13</v>
+      </c>
+      <c r="F1624" t="n">
+        <v>335</v>
+      </c>
+      <c r="G1624" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1624" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1625" t="inlineStr">
+        <is>
+          <t>Mr-Worldwide</t>
+        </is>
+      </c>
+      <c r="C1625" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="D1625" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1625" t="n">
+        <v>14</v>
+      </c>
+      <c r="F1625" t="n">
+        <v>313</v>
+      </c>
+      <c r="G1625" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1625" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="A1626" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1626" t="inlineStr">
+        <is>
+          <t>Fethinho</t>
+        </is>
+      </c>
+      <c r="C1626" t="inlineStr">
+        <is>
+          <t>Fethi</t>
+        </is>
+      </c>
+      <c r="D1626" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1626" t="n">
+        <v>15</v>
+      </c>
+      <c r="F1626" t="n">
+        <v>313</v>
+      </c>
+      <c r="G1626" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1626" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="A1627" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1627" t="inlineStr">
+        <is>
+          <t>Ouiouiausoleil</t>
+        </is>
+      </c>
+      <c r="C1627" t="inlineStr">
+        <is>
+          <t>Ouissal</t>
+        </is>
+      </c>
+      <c r="D1627" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1627" t="n">
+        <v>16</v>
+      </c>
+      <c r="F1627" t="n">
+        <v>313</v>
+      </c>
+      <c r="G1627" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1627" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1628" t="inlineStr">
+        <is>
+          <t>BOUGA#2JGXP</t>
+        </is>
+      </c>
+      <c r="C1628" t="inlineStr">
+        <is>
+          <t>BOUGA</t>
+        </is>
+      </c>
+      <c r="D1628" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1628" t="n">
+        <v>17</v>
+      </c>
+      <c r="F1628" t="n">
+        <v>293</v>
+      </c>
+      <c r="G1628" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1628" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1629">
+      <c r="A1629" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1629" t="inlineStr">
+        <is>
+          <t>Anais757817</t>
+        </is>
+      </c>
+      <c r="C1629" t="inlineStr">
+        <is>
+          <t>Anaïs</t>
+        </is>
+      </c>
+      <c r="D1629" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1629" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1629" t="n">
+        <v>293</v>
+      </c>
+      <c r="G1629" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1629" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1630">
+      <c r="A1630" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1630" t="inlineStr">
+        <is>
+          <t>MatuRenard</t>
+        </is>
+      </c>
+      <c r="C1630" t="inlineStr">
+        <is>
+          <t>Mathias</t>
+        </is>
+      </c>
+      <c r="D1630" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1630" t="n">
+        <v>19</v>
+      </c>
+      <c r="F1630" t="n">
+        <v>292</v>
+      </c>
+      <c r="G1630" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1630" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="A1631" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1631" t="inlineStr">
+        <is>
+          <t>Liliuus</t>
+        </is>
+      </c>
+      <c r="C1631" t="inlineStr">
+        <is>
+          <t>Lilia</t>
+        </is>
+      </c>
+      <c r="D1631" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1631" t="n">
+        <v>20</v>
+      </c>
+      <c r="F1631" t="n">
+        <v>292</v>
+      </c>
+      <c r="G1631" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1631" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1632">
+      <c r="A1632" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1632" t="inlineStr">
+        <is>
+          <t>Ppo28</t>
+        </is>
+      </c>
+      <c r="C1632" t="inlineStr">
+        <is>
+          <t>Prescylla</t>
+        </is>
+      </c>
+      <c r="D1632" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1632" t="n">
+        <v>21</v>
+      </c>
+      <c r="F1632" t="n">
+        <v>292</v>
+      </c>
+      <c r="G1632" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1632" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1633">
+      <c r="A1633" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1633" t="inlineStr">
+        <is>
+          <t>Gronaldo_95</t>
+        </is>
+      </c>
+      <c r="C1633" t="inlineStr">
+        <is>
+          <t>Gronaldo</t>
+        </is>
+      </c>
+      <c r="D1633" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1633" t="n">
+        <v>22</v>
+      </c>
+      <c r="F1633" t="n">
+        <v>272</v>
+      </c>
+      <c r="G1633" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1633" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1634">
+      <c r="A1634" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1634" t="inlineStr">
+        <is>
+          <t>Devilrock95</t>
+        </is>
+      </c>
+      <c r="C1634" t="inlineStr">
+        <is>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="D1634" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1634" t="n">
+        <v>23</v>
+      </c>
+      <c r="F1634" t="n">
+        <v>272</v>
+      </c>
+      <c r="G1634" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1634" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1635">
+      <c r="A1635" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1635" t="inlineStr">
+        <is>
+          <t>Cleem22</t>
+        </is>
+      </c>
+      <c r="C1635" t="inlineStr">
+        <is>
+          <t>Clemence</t>
+        </is>
+      </c>
+      <c r="D1635" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1635" t="n">
+        <v>24</v>
+      </c>
+      <c r="F1635" t="n">
+        <v>272</v>
+      </c>
+      <c r="G1635" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1635" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1636" t="inlineStr">
+        <is>
+          <t>catherine#5FRTD</t>
+        </is>
+      </c>
+      <c r="C1636" t="inlineStr">
+        <is>
+          <t>catherine</t>
+        </is>
+      </c>
+      <c r="D1636" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1636" t="n">
+        <v>25</v>
+      </c>
+      <c r="F1636" t="n">
+        <v>272</v>
+      </c>
+      <c r="G1636" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1636" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1637" t="inlineStr">
+        <is>
+          <t>Maruyama</t>
+        </is>
+      </c>
+      <c r="C1637" t="inlineStr">
+        <is>
+          <t>Gabrielle</t>
+        </is>
+      </c>
+      <c r="D1637" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1637" t="n">
+        <v>26</v>
+      </c>
+      <c r="F1637" t="n">
+        <v>272</v>
+      </c>
+      <c r="G1637" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1637" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="A1638" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1638" t="inlineStr">
+        <is>
+          <t>Leandrocp</t>
+        </is>
+      </c>
+      <c r="C1638" t="inlineStr">
+        <is>
+          <t>Leandro</t>
+        </is>
+      </c>
+      <c r="D1638" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1638" t="n">
+        <v>27</v>
+      </c>
+      <c r="F1638" t="n">
+        <v>272</v>
+      </c>
+      <c r="G1638" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1638" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1639" t="inlineStr">
+        <is>
+          <t>Marion1822</t>
+        </is>
+      </c>
+      <c r="C1639" t="inlineStr">
+        <is>
+          <t>Marion</t>
+        </is>
+      </c>
+      <c r="D1639" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1639" t="n">
+        <v>28</v>
+      </c>
+      <c r="F1639" t="n">
+        <v>272</v>
+      </c>
+      <c r="G1639" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1639" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1640" t="inlineStr">
+        <is>
+          <t>chaychaychay</t>
+        </is>
+      </c>
+      <c r="C1640" t="inlineStr">
+        <is>
+          <t>Chaymaa</t>
+        </is>
+      </c>
+      <c r="D1640" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1640" t="n">
+        <v>29</v>
+      </c>
+      <c r="F1640" t="n">
+        <v>272</v>
+      </c>
+      <c r="G1640" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1640" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1641" t="inlineStr">
+        <is>
+          <t>WIL1610</t>
+        </is>
+      </c>
+      <c r="C1641" t="inlineStr">
+        <is>
+          <t>William</t>
+        </is>
+      </c>
+      <c r="D1641" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1641" t="n">
+        <v>30</v>
+      </c>
+      <c r="F1641" t="n">
+        <v>266</v>
+      </c>
+      <c r="G1641" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1641" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1642" t="inlineStr">
+        <is>
+          <t>Erwan#4G91X</t>
+        </is>
+      </c>
+      <c r="C1642" t="inlineStr">
+        <is>
+          <t>Erwan</t>
+        </is>
+      </c>
+      <c r="D1642" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1642" t="n">
+        <v>31</v>
+      </c>
+      <c r="F1642" t="n">
+        <v>252</v>
+      </c>
+      <c r="G1642" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1642" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1643" t="inlineStr">
+        <is>
+          <t>GLR_PRIME</t>
+        </is>
+      </c>
+      <c r="C1643" t="inlineStr">
+        <is>
+          <t>Gabriel</t>
+        </is>
+      </c>
+      <c r="D1643" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1643" t="n">
+        <v>32</v>
+      </c>
+      <c r="F1643" t="n">
+        <v>252</v>
+      </c>
+      <c r="G1643" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1643" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1644" t="inlineStr">
+        <is>
+          <t>Exia95</t>
+        </is>
+      </c>
+      <c r="C1644" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D1644" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1644" t="n">
+        <v>33</v>
+      </c>
+      <c r="F1644" t="n">
+        <v>245</v>
+      </c>
+      <c r="G1644" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1644" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1645" t="inlineStr">
+        <is>
+          <t>Matt#4B4CU</t>
+        </is>
+      </c>
+      <c r="C1645" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="D1645" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1645" t="n">
+        <v>34</v>
+      </c>
+      <c r="F1645" t="n">
+        <v>244</v>
+      </c>
+      <c r="G1645" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1645" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1646" t="inlineStr">
+        <is>
+          <t>dian-bgt</t>
+        </is>
+      </c>
+      <c r="C1646" t="inlineStr">
+        <is>
+          <t>Diane</t>
+        </is>
+      </c>
+      <c r="D1646" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1646" t="n">
+        <v>35</v>
+      </c>
+      <c r="F1646" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1646" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1646" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1647" t="inlineStr">
+        <is>
+          <t>LilianeB</t>
+        </is>
+      </c>
+      <c r="C1647" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liliane </t>
+        </is>
+      </c>
+      <c r="D1647" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1647" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1647" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1647" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1647" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1648" t="inlineStr">
+        <is>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="C1648" t="inlineStr">
+        <is>
+          <t>Julie</t>
+        </is>
+      </c>
+      <c r="D1648" t="inlineStr"/>
+      <c r="E1648" t="n">
+        <v>37</v>
+      </c>
+      <c r="F1648" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1648" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1648" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1649" t="inlineStr">
+        <is>
+          <t>Ninaaaa</t>
+        </is>
+      </c>
+      <c r="C1649" t="inlineStr">
+        <is>
+          <t>Nina</t>
+        </is>
+      </c>
+      <c r="D1649" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1649" t="n">
+        <v>38</v>
+      </c>
+      <c r="F1649" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1649" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1649" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1650" t="inlineStr">
+        <is>
+          <t>Romain_JO</t>
+        </is>
+      </c>
+      <c r="C1650" t="inlineStr">
+        <is>
+          <t>Romain J</t>
+        </is>
+      </c>
+      <c r="D1650" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1650" t="n">
+        <v>39</v>
+      </c>
+      <c r="F1650" t="n">
+        <v>224</v>
+      </c>
+      <c r="G1650" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1650" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1651" t="inlineStr">
+        <is>
+          <t>JeremFZ</t>
+        </is>
+      </c>
+      <c r="C1651" t="inlineStr">
+        <is>
+          <t>Jérémy</t>
+        </is>
+      </c>
+      <c r="D1651" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1651" t="n">
+        <v>40</v>
+      </c>
+      <c r="F1651" t="n">
+        <v>224</v>
+      </c>
+      <c r="G1651" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1651" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1652" t="inlineStr">
+        <is>
+          <t>AudreyB225</t>
+        </is>
+      </c>
+      <c r="C1652" t="inlineStr">
+        <is>
+          <t>Audrey</t>
+        </is>
+      </c>
+      <c r="D1652" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1652" t="n">
+        <v>41</v>
+      </c>
+      <c r="F1652" t="n">
+        <v>223</v>
+      </c>
+      <c r="G1652" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1652" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1653" t="inlineStr">
+        <is>
+          <t>BadrLeo</t>
+        </is>
+      </c>
+      <c r="C1653" t="inlineStr">
+        <is>
+          <t>Badr Leo</t>
+        </is>
+      </c>
+      <c r="D1653" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1653" t="n">
+        <v>42</v>
+      </c>
+      <c r="F1653" t="n">
+        <v>219</v>
+      </c>
+      <c r="G1653" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1653" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1654" t="inlineStr">
+        <is>
+          <t>Ilan_260_</t>
+        </is>
+      </c>
+      <c r="C1654" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ilann </t>
+        </is>
+      </c>
+      <c r="D1654" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1654" t="n">
+        <v>43</v>
+      </c>
+      <c r="F1654" t="n">
+        <v>218</v>
+      </c>
+      <c r="G1654" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1654" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1655" t="inlineStr">
+        <is>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="C1655" t="inlineStr">
+        <is>
+          <t>François</t>
+        </is>
+      </c>
+      <c r="D1655" t="inlineStr"/>
+      <c r="E1655" t="n">
+        <v>44</v>
+      </c>
+      <c r="F1655" t="n">
+        <v>209</v>
+      </c>
+      <c r="G1655" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1655" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1656" t="inlineStr">
+        <is>
+          <t>LeaBrd</t>
+        </is>
+      </c>
+      <c r="C1656" t="inlineStr">
+        <is>
+          <t>Léa</t>
+        </is>
+      </c>
+      <c r="D1656" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1656" t="n">
+        <v>45</v>
+      </c>
+      <c r="F1656" t="n">
+        <v>206</v>
+      </c>
+      <c r="G1656" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1656" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1657" t="inlineStr">
+        <is>
+          <t>Emilay</t>
+        </is>
+      </c>
+      <c r="C1657" t="inlineStr">
+        <is>
+          <t>Émilie</t>
+        </is>
+      </c>
+      <c r="D1657" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1657" t="n">
+        <v>46</v>
+      </c>
+      <c r="F1657" t="n">
+        <v>206</v>
+      </c>
+      <c r="G1657" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1657" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1658" t="inlineStr">
+        <is>
+          <t>Emma_Noel</t>
+        </is>
+      </c>
+      <c r="C1658" t="inlineStr">
+        <is>
+          <t>Emma</t>
+        </is>
+      </c>
+      <c r="D1658" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1658" t="n">
+        <v>47</v>
+      </c>
+      <c r="F1658" t="n">
+        <v>206</v>
+      </c>
+      <c r="G1658" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1658" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1659" t="inlineStr">
+        <is>
+          <t>A-MOE</t>
+        </is>
+      </c>
+      <c r="C1659" t="inlineStr">
+        <is>
+          <t>Françoise</t>
+        </is>
+      </c>
+      <c r="D1659" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1659" t="n">
+        <v>48</v>
+      </c>
+      <c r="F1659" t="n">
+        <v>206</v>
+      </c>
+      <c r="G1659" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1659" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1660" t="inlineStr">
+        <is>
+          <t>abihuts</t>
+        </is>
+      </c>
+      <c r="C1660" t="inlineStr">
+        <is>
+          <t>Antonio Moctezuma</t>
+        </is>
+      </c>
+      <c r="D1660" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1660" t="n">
+        <v>49</v>
+      </c>
+      <c r="F1660" t="n">
+        <v>205</v>
+      </c>
+      <c r="G1660" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1660" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1661" t="inlineStr">
+        <is>
+          <t>Chadia__</t>
+        </is>
+      </c>
+      <c r="C1661" t="inlineStr">
+        <is>
+          <t>Chadia</t>
+        </is>
+      </c>
+      <c r="D1661" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1661" t="n">
+        <v>50</v>
+      </c>
+      <c r="F1661" t="n">
+        <v>203</v>
+      </c>
+      <c r="G1661" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1661" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1662" t="inlineStr">
+        <is>
+          <t>GOAT#UE2WM8M9</t>
+        </is>
+      </c>
+      <c r="C1662" t="inlineStr">
+        <is>
+          <t>Marilena</t>
+        </is>
+      </c>
+      <c r="D1662" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1662" t="n">
+        <v>51</v>
+      </c>
+      <c r="F1662" t="n">
+        <v>198</v>
+      </c>
+      <c r="G1662" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1662" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="A1663" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1663" t="inlineStr">
+        <is>
+          <t>YassineZ95</t>
+        </is>
+      </c>
+      <c r="C1663" t="inlineStr">
+        <is>
+          <t>Yassine Z</t>
+        </is>
+      </c>
+      <c r="D1663" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1663" t="n">
+        <v>52</v>
+      </c>
+      <c r="F1663" t="n">
+        <v>186</v>
+      </c>
+      <c r="G1663" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1663" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1664" t="inlineStr">
+        <is>
+          <t>Fuzo697</t>
+        </is>
+      </c>
+      <c r="C1664" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D1664" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1664" t="n">
+        <v>53</v>
+      </c>
+      <c r="F1664" t="n">
+        <v>178</v>
+      </c>
+      <c r="G1664" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1664" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1665">
+      <c r="A1665" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1665" t="inlineStr">
+        <is>
+          <t>Yebri</t>
+        </is>
+      </c>
+      <c r="C1665" t="inlineStr">
+        <is>
+          <t>Brieuc</t>
+        </is>
+      </c>
+      <c r="D1665" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1665" t="n">
+        <v>54</v>
+      </c>
+      <c r="F1665" t="n">
+        <v>176</v>
+      </c>
+      <c r="G1665" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1665" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1666" t="inlineStr">
+        <is>
+          <t>Leo_durable</t>
+        </is>
+      </c>
+      <c r="C1666" t="inlineStr">
+        <is>
+          <t>Leo</t>
+        </is>
+      </c>
+      <c r="D1666" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1666" t="n">
+        <v>55</v>
+      </c>
+      <c r="F1666" t="n">
+        <v>176</v>
+      </c>
+      <c r="G1666" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1666" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1667" t="inlineStr">
+        <is>
+          <t>EmyEnzo</t>
+        </is>
+      </c>
+      <c r="C1667" t="inlineStr">
+        <is>
+          <t>Emilie</t>
+        </is>
+      </c>
+      <c r="D1667" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1667" t="n">
+        <v>56</v>
+      </c>
+      <c r="F1667" t="n">
+        <v>176</v>
+      </c>
+      <c r="G1667" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1667" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1668" t="inlineStr">
+        <is>
+          <t>Priscilla#4LCAF</t>
+        </is>
+      </c>
+      <c r="C1668" t="inlineStr">
+        <is>
+          <t>Priscilla</t>
+        </is>
+      </c>
+      <c r="D1668" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1668" t="n">
+        <v>57</v>
+      </c>
+      <c r="F1668" t="n">
+        <v>176</v>
+      </c>
+      <c r="G1668" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1668" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1669" t="inlineStr">
+        <is>
+          <t>Pipou931</t>
+        </is>
+      </c>
+      <c r="C1669" t="inlineStr">
+        <is>
+          <t>Juliie</t>
+        </is>
+      </c>
+      <c r="D1669" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1669" t="n">
+        <v>58</v>
+      </c>
+      <c r="F1669" t="n">
+        <v>176</v>
+      </c>
+      <c r="G1669" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1669" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1670" t="inlineStr">
+        <is>
+          <t>Farah_One</t>
+        </is>
+      </c>
+      <c r="C1670" t="inlineStr">
+        <is>
+          <t>Farah</t>
+        </is>
+      </c>
+      <c r="D1670" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1670" t="n">
+        <v>59</v>
+      </c>
+      <c r="F1670" t="n">
+        <v>176</v>
+      </c>
+      <c r="G1670" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1670" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1671" t="inlineStr">
+        <is>
+          <t>Seesee</t>
+        </is>
+      </c>
+      <c r="C1671" t="inlineStr">
+        <is>
+          <t>Selver</t>
+        </is>
+      </c>
+      <c r="D1671" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1671" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1671" t="n">
+        <v>176</v>
+      </c>
+      <c r="G1671" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1671" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1672" t="inlineStr">
+        <is>
+          <t>lenaaik</t>
+        </is>
+      </c>
+      <c r="C1672" t="inlineStr">
+        <is>
+          <t>Lénaïk</t>
+        </is>
+      </c>
+      <c r="D1672" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1672" t="n">
+        <v>61</v>
+      </c>
+      <c r="F1672" t="n">
+        <v>176</v>
+      </c>
+      <c r="G1672" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1672" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1673" t="inlineStr">
+        <is>
+          <t>C4M</t>
+        </is>
+      </c>
+      <c r="C1673" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D1673" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1673" t="n">
+        <v>62</v>
+      </c>
+      <c r="F1673" t="n">
+        <v>176</v>
+      </c>
+      <c r="G1673" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1673" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1674" t="inlineStr">
+        <is>
+          <t>Rosa_1009</t>
+        </is>
+      </c>
+      <c r="C1674" t="inlineStr">
+        <is>
+          <t>Rosaline</t>
+        </is>
+      </c>
+      <c r="D1674" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1674" t="n">
+        <v>63</v>
+      </c>
+      <c r="F1674" t="n">
+        <v>176</v>
+      </c>
+      <c r="G1674" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1674" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1675" t="inlineStr">
+        <is>
+          <t>Elisewiss</t>
+        </is>
+      </c>
+      <c r="C1675" t="inlineStr">
+        <is>
+          <t>Elise</t>
+        </is>
+      </c>
+      <c r="D1675" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1675" t="n">
+        <v>64</v>
+      </c>
+      <c r="F1675" t="n">
+        <v>176</v>
+      </c>
+      <c r="G1675" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1675" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1676" t="inlineStr">
+        <is>
+          <t>Soraya-Y</t>
+        </is>
+      </c>
+      <c r="C1676" t="inlineStr">
+        <is>
+          <t>Soraya</t>
+        </is>
+      </c>
+      <c r="D1676" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1676" t="n">
+        <v>65</v>
+      </c>
+      <c r="F1676" t="n">
+        <v>176</v>
+      </c>
+      <c r="G1676" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1676" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1677" t="inlineStr">
+        <is>
+          <t>1993ahm</t>
+        </is>
+      </c>
+      <c r="C1677" t="inlineStr">
+        <is>
+          <t>Ahmed</t>
+        </is>
+      </c>
+      <c r="D1677" t="inlineStr"/>
+      <c r="E1677" t="n">
+        <v>66</v>
+      </c>
+      <c r="F1677" t="n">
+        <v>176</v>
+      </c>
+      <c r="G1677" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1677" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1678" t="inlineStr">
+        <is>
+          <t>Stephbreton</t>
+        </is>
+      </c>
+      <c r="C1678" t="inlineStr">
+        <is>
+          <t>STEPHANE</t>
+        </is>
+      </c>
+      <c r="D1678" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1678" t="n">
+        <v>67</v>
+      </c>
+      <c r="F1678" t="n">
+        <v>166</v>
+      </c>
+      <c r="G1678" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1678" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1679" t="inlineStr">
+        <is>
+          <t>Davido#4BZ54</t>
+        </is>
+      </c>
+      <c r="C1679" t="inlineStr">
+        <is>
+          <t>Davido</t>
+        </is>
+      </c>
+      <c r="D1679" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1679" t="n">
+        <v>68</v>
+      </c>
+      <c r="F1679" t="n">
+        <v>162</v>
+      </c>
+      <c r="G1679" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1679" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1680" t="inlineStr">
+        <is>
+          <t>Timy</t>
+        </is>
+      </c>
+      <c r="C1680" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="D1680" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1680" t="n">
+        <v>69</v>
+      </c>
+      <c r="F1680" t="n">
+        <v>156</v>
+      </c>
+      <c r="G1680" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1680" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1681" t="inlineStr">
+        <is>
+          <t>JEVAISGAGNER10</t>
+        </is>
+      </c>
+      <c r="C1681" t="inlineStr">
+        <is>
+          <t>Xavier</t>
+        </is>
+      </c>
+      <c r="D1681" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1681" t="n">
+        <v>70</v>
+      </c>
+      <c r="F1681" t="n">
+        <v>156</v>
+      </c>
+      <c r="G1681" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1681" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1682" t="inlineStr">
+        <is>
+          <t>HamzaG</t>
+        </is>
+      </c>
+      <c r="C1682" t="inlineStr">
+        <is>
+          <t>Hamza</t>
+        </is>
+      </c>
+      <c r="D1682" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1682" t="n">
+        <v>71</v>
+      </c>
+      <c r="F1682" t="n">
+        <v>156</v>
+      </c>
+      <c r="G1682" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1682" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1683" t="inlineStr">
+        <is>
+          <t>davidd23</t>
+        </is>
+      </c>
+      <c r="C1683" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D1683" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1683" t="n">
+        <v>72</v>
+      </c>
+      <c r="F1683" t="n">
+        <v>156</v>
+      </c>
+      <c r="G1683" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1683" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1684" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="C1684" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="D1684" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1684" t="n">
+        <v>73</v>
+      </c>
+      <c r="F1684" t="n">
+        <v>156</v>
+      </c>
+      <c r="G1684" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1684" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1685" t="inlineStr">
+        <is>
+          <t>Kolas</t>
+        </is>
+      </c>
+      <c r="C1685" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D1685" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1685" t="n">
+        <v>74</v>
+      </c>
+      <c r="F1685" t="n">
+        <v>156</v>
+      </c>
+      <c r="G1685" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1685" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1686" t="inlineStr">
+        <is>
+          <t>Laetice2020</t>
+        </is>
+      </c>
+      <c r="C1686" t="inlineStr">
+        <is>
+          <t>Laetitia</t>
+        </is>
+      </c>
+      <c r="D1686" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1686" t="n">
+        <v>75</v>
+      </c>
+      <c r="F1686" t="n">
+        <v>156</v>
+      </c>
+      <c r="G1686" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1686" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1687" t="inlineStr">
+        <is>
+          <t>Lyzone</t>
+        </is>
+      </c>
+      <c r="C1687" t="inlineStr">
+        <is>
+          <t>Lison</t>
+        </is>
+      </c>
+      <c r="D1687" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1687" t="n">
+        <v>76</v>
+      </c>
+      <c r="F1687" t="n">
+        <v>156</v>
+      </c>
+      <c r="G1687" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1687" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1688" t="inlineStr">
+        <is>
+          <t>Melissagzb</t>
+        </is>
+      </c>
+      <c r="C1688" t="inlineStr">
+        <is>
+          <t>Melissa</t>
+        </is>
+      </c>
+      <c r="D1688" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1688" t="n">
+        <v>77</v>
+      </c>
+      <c r="F1688" t="n">
+        <v>156</v>
+      </c>
+      <c r="G1688" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1688" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1689" t="inlineStr">
+        <is>
+          <t>Marie__92</t>
+        </is>
+      </c>
+      <c r="C1689" t="inlineStr">
+        <is>
+          <t>Marie</t>
+        </is>
+      </c>
+      <c r="D1689" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1689" t="n">
+        <v>78</v>
+      </c>
+      <c r="F1689" t="n">
+        <v>156</v>
+      </c>
+      <c r="G1689" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1689" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="A1690" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1690" t="inlineStr">
+        <is>
+          <t>K_Marp</t>
+        </is>
+      </c>
+      <c r="C1690" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
+      <c r="D1690" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1690" t="n">
+        <v>79</v>
+      </c>
+      <c r="F1690" t="n">
+        <v>156</v>
+      </c>
+      <c r="G1690" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1690" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="A1691" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1691" t="inlineStr">
+        <is>
+          <t>Cindie_JJA</t>
+        </is>
+      </c>
+      <c r="C1691" t="inlineStr">
+        <is>
+          <t>Cindie</t>
+        </is>
+      </c>
+      <c r="D1691" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1691" t="n">
+        <v>80</v>
+      </c>
+      <c r="F1691" t="n">
+        <v>156</v>
+      </c>
+      <c r="G1691" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1691" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1692">
+      <c r="A1692" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1692" t="inlineStr">
+        <is>
+          <t>JKInternational</t>
+        </is>
+      </c>
+      <c r="C1692" t="inlineStr">
+        <is>
+          <t>Joachim</t>
+        </is>
+      </c>
+      <c r="D1692" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1692" t="n">
+        <v>81</v>
+      </c>
+      <c r="F1692" t="n">
+        <v>156</v>
+      </c>
+      <c r="G1692" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1692" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="A1693" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1693" t="inlineStr">
+        <is>
+          <t>GOAT#UE4U8KA6</t>
+        </is>
+      </c>
+      <c r="C1693" t="inlineStr">
+        <is>
+          <t>Jean Baptiste</t>
+        </is>
+      </c>
+      <c r="D1693" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1693" t="n">
+        <v>82</v>
+      </c>
+      <c r="F1693" t="n">
+        <v>156</v>
+      </c>
+      <c r="G1693" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1693" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="A1694" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1694" t="inlineStr">
+        <is>
+          <t>goat#AD6GS</t>
+        </is>
+      </c>
+      <c r="C1694" t="inlineStr">
+        <is>
+          <t>goat</t>
+        </is>
+      </c>
+      <c r="D1694" t="inlineStr"/>
+      <c r="E1694" t="n">
+        <v>83</v>
+      </c>
+      <c r="F1694" t="n">
+        <v>156</v>
+      </c>
+      <c r="G1694" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1694" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1695" t="inlineStr">
+        <is>
+          <t>Camillewbl</t>
+        </is>
+      </c>
+      <c r="C1695" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D1695" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1695" t="n">
+        <v>84</v>
+      </c>
+      <c r="F1695" t="n">
+        <v>156</v>
+      </c>
+      <c r="G1695" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1695" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1696" t="inlineStr">
+        <is>
+          <t>RBTL</t>
+        </is>
+      </c>
+      <c r="C1696" t="inlineStr">
+        <is>
+          <t>lea</t>
+        </is>
+      </c>
+      <c r="D1696" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1696" t="n">
+        <v>85</v>
+      </c>
+      <c r="F1696" t="n">
+        <v>156</v>
+      </c>
+      <c r="G1696" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1696" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1697" t="inlineStr">
+        <is>
+          <t>Ceciledp</t>
+        </is>
+      </c>
+      <c r="C1697" t="inlineStr">
+        <is>
+          <t>Cécile</t>
+        </is>
+      </c>
+      <c r="D1697" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1697" t="n">
+        <v>86</v>
+      </c>
+      <c r="F1697" t="n">
+        <v>145</v>
+      </c>
+      <c r="G1697" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1697" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1698" t="inlineStr">
+        <is>
+          <t>MyriamAmr</t>
+        </is>
+      </c>
+      <c r="C1698" t="inlineStr">
+        <is>
+          <t>Myriam</t>
+        </is>
+      </c>
+      <c r="D1698" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1698" t="n">
+        <v>87</v>
+      </c>
+      <c r="F1698" t="n">
+        <v>137</v>
+      </c>
+      <c r="G1698" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1698" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1699" t="inlineStr">
+        <is>
+          <t>Nonito20</t>
+        </is>
+      </c>
+      <c r="C1699" t="inlineStr">
+        <is>
+          <t>Arnaud</t>
+        </is>
+      </c>
+      <c r="D1699" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1699" t="n">
+        <v>88</v>
+      </c>
+      <c r="F1699" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1699" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1699" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1700" t="inlineStr">
+        <is>
+          <t>BrickXVI</t>
+        </is>
+      </c>
+      <c r="C1700" t="inlineStr">
+        <is>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="D1700" t="inlineStr"/>
+      <c r="E1700" t="n">
+        <v>89</v>
+      </c>
+      <c r="F1700" t="n">
+        <v>107</v>
+      </c>
+      <c r="G1700" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1700" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="A1701" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1701" t="inlineStr">
+        <is>
+          <t>Taylor2901</t>
+        </is>
+      </c>
+      <c r="C1701" t="inlineStr">
+        <is>
+          <t>ousmane</t>
+        </is>
+      </c>
+      <c r="D1701" t="inlineStr"/>
+      <c r="E1701" t="n">
+        <v>90</v>
+      </c>
+      <c r="F1701" t="n">
+        <v>107</v>
+      </c>
+      <c r="G1701" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1701" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1702">
+      <c r="A1702" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1702" t="inlineStr">
+        <is>
+          <t>Ze_GOAT</t>
+        </is>
+      </c>
+      <c r="C1702" t="inlineStr">
+        <is>
+          <t>Yasser</t>
+        </is>
+      </c>
+      <c r="D1702" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1702" t="n">
+        <v>91</v>
+      </c>
+      <c r="F1702" t="n">
+        <v>102</v>
+      </c>
+      <c r="G1702" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1702" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1703" t="inlineStr">
+        <is>
+          <t>Krol#4R8XC</t>
+        </is>
+      </c>
+      <c r="C1703" t="inlineStr">
+        <is>
+          <t>Krol</t>
+        </is>
+      </c>
+      <c r="D1703" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1703" t="n">
+        <v>92</v>
+      </c>
+      <c r="F1703" t="n">
+        <v>102</v>
+      </c>
+      <c r="G1703" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1703" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1704">
+      <c r="A1704" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1704" t="inlineStr">
+        <is>
+          <t>PacoSarra</t>
+        </is>
+      </c>
+      <c r="C1704" t="inlineStr">
+        <is>
+          <t>Ibra</t>
+        </is>
+      </c>
+      <c r="D1704" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1704" t="n">
+        <v>93</v>
+      </c>
+      <c r="F1704" t="n">
+        <v>102</v>
+      </c>
+      <c r="G1704" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1704" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="A1705" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1705" t="inlineStr">
+        <is>
+          <t>Droit_au_but7723</t>
+        </is>
+      </c>
+      <c r="C1705" t="inlineStr">
+        <is>
+          <t>Calixthe</t>
+        </is>
+      </c>
+      <c r="D1705" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1705" t="n">
+        <v>94</v>
+      </c>
+      <c r="F1705" t="n">
+        <v>102</v>
+      </c>
+      <c r="G1705" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1705" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1706" t="inlineStr">
+        <is>
+          <t>Mylene-Jnt</t>
+        </is>
+      </c>
+      <c r="C1706" t="inlineStr">
+        <is>
+          <t>Mylène</t>
+        </is>
+      </c>
+      <c r="D1706" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1706" t="n">
+        <v>95</v>
+      </c>
+      <c r="F1706" t="n">
+        <v>82</v>
+      </c>
+      <c r="G1706" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1706" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="A1707" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1707" t="inlineStr">
+        <is>
+          <t>Teddbear</t>
+        </is>
+      </c>
+      <c r="C1707" t="inlineStr">
+        <is>
+          <t>Tedy</t>
+        </is>
+      </c>
+      <c r="D1707" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1707" t="n">
+        <v>96</v>
+      </c>
+      <c r="F1707" t="n">
+        <v>82</v>
+      </c>
+      <c r="G1707" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1707" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="A1708" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1708" t="inlineStr">
+        <is>
+          <t>SabC1</t>
+        </is>
+      </c>
+      <c r="C1708" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="D1708" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1708" t="n">
+        <v>97</v>
+      </c>
+      <c r="F1708" t="n">
+        <v>82</v>
+      </c>
+      <c r="G1708" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1708" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1709">
+      <c r="A1709" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1709" t="inlineStr">
+        <is>
+          <t>KIKS999</t>
+        </is>
+      </c>
+      <c r="C1709" t="inlineStr">
+        <is>
+          <t>Killian</t>
+        </is>
+      </c>
+      <c r="D1709" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1709" t="n">
+        <v>98</v>
+      </c>
+      <c r="F1709" t="n">
+        <v>82</v>
+      </c>
+      <c r="G1709" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1709" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1710" t="inlineStr">
+        <is>
+          <t>MxKnight</t>
+        </is>
+      </c>
+      <c r="C1710" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D1710" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1710" t="n">
+        <v>99</v>
+      </c>
+      <c r="F1710" t="n">
+        <v>82</v>
+      </c>
+      <c r="G1710" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1710" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1711" t="inlineStr">
+        <is>
+          <t>RomainLect</t>
+        </is>
+      </c>
+      <c r="C1711" t="inlineStr">
+        <is>
+          <t>romain</t>
+        </is>
+      </c>
+      <c r="D1711" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1711" t="n">
+        <v>100</v>
+      </c>
+      <c r="F1711" t="n">
+        <v>82</v>
+      </c>
+      <c r="G1711" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1711" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1712">
+      <c r="A1712" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1712" t="inlineStr">
+        <is>
+          <t>SamSamH8</t>
+        </is>
+      </c>
+      <c r="C1712" t="inlineStr">
+        <is>
+          <t>Samia</t>
+        </is>
+      </c>
+      <c r="D1712" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1712" t="n">
+        <v>101</v>
+      </c>
+      <c r="F1712" t="n">
+        <v>82</v>
+      </c>
+      <c r="G1712" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1712" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1713" t="inlineStr">
+        <is>
+          <t>Daviddesco1</t>
+        </is>
+      </c>
+      <c r="C1713" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D1713" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1713" t="n">
+        <v>102</v>
+      </c>
+      <c r="F1713" t="n">
+        <v>82</v>
+      </c>
+      <c r="G1713" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1713" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1714" t="inlineStr">
+        <is>
+          <t>Sab_M45</t>
+        </is>
+      </c>
+      <c r="C1714" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="D1714" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1714" t="n">
+        <v>103</v>
+      </c>
+      <c r="F1714" t="n">
+        <v>82</v>
+      </c>
+      <c r="G1714" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1714" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="A1715" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1715" t="inlineStr">
+        <is>
+          <t>Valentine___</t>
+        </is>
+      </c>
+      <c r="C1715" t="inlineStr">
+        <is>
+          <t>Valentine</t>
+        </is>
+      </c>
+      <c r="D1715" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1715" t="n">
+        <v>104</v>
+      </c>
+      <c r="F1715" t="n">
+        <v>82</v>
+      </c>
+      <c r="G1715" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1715" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1716">
+      <c r="A1716" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1716" t="inlineStr">
+        <is>
+          <t>Ambrepic</t>
+        </is>
+      </c>
+      <c r="C1716" t="inlineStr">
+        <is>
+          <t>Ambre</t>
+        </is>
+      </c>
+      <c r="D1716" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1716" t="n">
+        <v>105</v>
+      </c>
+      <c r="F1716" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1716" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1716" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1717">
+      <c r="A1717" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1717" t="inlineStr">
+        <is>
+          <t>PavelMel</t>
+        </is>
+      </c>
+      <c r="C1717" t="inlineStr">
+        <is>
+          <t>Mélissa</t>
+        </is>
+      </c>
+      <c r="D1717" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1717" t="n">
+        <v>106</v>
+      </c>
+      <c r="F1717" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1717" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1717" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1718">
+      <c r="A1718" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1718" t="inlineStr">
+        <is>
+          <t>Camss</t>
+        </is>
+      </c>
+      <c r="C1718" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D1718" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1718" t="n">
+        <v>107</v>
+      </c>
+      <c r="F1718" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1718" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1718" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1719">
+      <c r="A1719" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1719" t="inlineStr">
+        <is>
+          <t>PANENKANY</t>
+        </is>
+      </c>
+      <c r="C1719" t="inlineStr">
+        <is>
+          <t>Damien</t>
+        </is>
+      </c>
+      <c r="D1719" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1719" t="n">
+        <v>108</v>
+      </c>
+      <c r="F1719" t="n">
+        <v>33</v>
+      </c>
+      <c r="G1719" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1719" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1720">
+      <c r="A1720" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1720" t="inlineStr">
+        <is>
+          <t>MT35T</t>
+        </is>
+      </c>
+      <c r="C1720" t="inlineStr">
+        <is>
+          <t>Mathilde</t>
+        </is>
+      </c>
+      <c r="D1720" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1720" t="n">
+        <v>109</v>
+      </c>
+      <c r="F1720" t="n">
+        <v>33</v>
+      </c>
+      <c r="G1720" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1720" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historique_joueurs.xlsx
+++ b/historique_joueurs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1720"/>
+  <dimension ref="A1:H1829"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57468,6 +57468,3688 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1721">
+      <c r="A1721" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1721" t="inlineStr">
+        <is>
+          <t>Filipinho95</t>
+        </is>
+      </c>
+      <c r="C1721" t="inlineStr">
+        <is>
+          <t>Filipe</t>
+        </is>
+      </c>
+      <c r="D1721" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1721" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1721" t="n">
+        <v>410</v>
+      </c>
+      <c r="G1721" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1721" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1722">
+      <c r="A1722" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1722" t="inlineStr">
+        <is>
+          <t>Ninaaaa</t>
+        </is>
+      </c>
+      <c r="C1722" t="inlineStr">
+        <is>
+          <t>Nina</t>
+        </is>
+      </c>
+      <c r="D1722" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1722" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1722" t="n">
+        <v>400</v>
+      </c>
+      <c r="G1722" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1722" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1723">
+      <c r="A1723" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1723" t="inlineStr">
+        <is>
+          <t>MargauxCtln</t>
+        </is>
+      </c>
+      <c r="C1723" t="inlineStr">
+        <is>
+          <t>Margaux</t>
+        </is>
+      </c>
+      <c r="D1723" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1723" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1723" t="n">
+        <v>376</v>
+      </c>
+      <c r="G1723" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1723" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1724">
+      <c r="A1724" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1724" t="inlineStr">
+        <is>
+          <t>Mamad_Shelter</t>
+        </is>
+      </c>
+      <c r="C1724" t="inlineStr">
+        <is>
+          <t>Mamadou</t>
+        </is>
+      </c>
+      <c r="D1724" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1724" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1724" t="n">
+        <v>376</v>
+      </c>
+      <c r="G1724" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1724" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1725">
+      <c r="A1725" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1725" t="inlineStr">
+        <is>
+          <t>MagicMath</t>
+        </is>
+      </c>
+      <c r="C1725" t="inlineStr">
+        <is>
+          <t>Mathieu</t>
+        </is>
+      </c>
+      <c r="D1725" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1725" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1725" t="n">
+        <v>376</v>
+      </c>
+      <c r="G1725" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1725" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1726">
+      <c r="A1726" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1726" t="inlineStr">
+        <is>
+          <t>WalidSiuuuuu</t>
+        </is>
+      </c>
+      <c r="C1726" t="inlineStr">
+        <is>
+          <t>Walid</t>
+        </is>
+      </c>
+      <c r="D1726" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1726" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1726" t="n">
+        <v>356</v>
+      </c>
+      <c r="G1726" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1726" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1727">
+      <c r="A1727" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1727" t="inlineStr">
+        <is>
+          <t>DJOSWA</t>
+        </is>
+      </c>
+      <c r="C1727" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oswaina </t>
+        </is>
+      </c>
+      <c r="D1727" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1727" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1727" t="n">
+        <v>356</v>
+      </c>
+      <c r="G1727" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1727" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1728">
+      <c r="A1728" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1728" t="inlineStr">
+        <is>
+          <t>SID-F-ANDRE</t>
+        </is>
+      </c>
+      <c r="C1728" t="inlineStr">
+        <is>
+          <t>Denis</t>
+        </is>
+      </c>
+      <c r="D1728" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1728" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1728" t="n">
+        <v>355</v>
+      </c>
+      <c r="G1728" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1728" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1729">
+      <c r="A1729" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1729" t="inlineStr">
+        <is>
+          <t>ChrisKr1Deg1</t>
+        </is>
+      </c>
+      <c r="C1729" t="inlineStr">
+        <is>
+          <t>christophe</t>
+        </is>
+      </c>
+      <c r="D1729" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1729" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1729" t="n">
+        <v>323</v>
+      </c>
+      <c r="G1729" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1729" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1730">
+      <c r="A1730" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1730" t="inlineStr">
+        <is>
+          <t>Coucoucassecou</t>
+        </is>
+      </c>
+      <c r="C1730" t="inlineStr">
+        <is>
+          <t>Brayen</t>
+        </is>
+      </c>
+      <c r="D1730" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1730" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1730" t="n">
+        <v>322</v>
+      </c>
+      <c r="G1730" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1730" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1731">
+      <c r="A1731" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1731" t="inlineStr">
+        <is>
+          <t>Paulasipi1998</t>
+        </is>
+      </c>
+      <c r="C1731" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="D1731" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1731" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1731" t="n">
+        <v>322</v>
+      </c>
+      <c r="G1731" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1731" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1732">
+      <c r="A1732" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1732" t="inlineStr">
+        <is>
+          <t>Panaff</t>
+        </is>
+      </c>
+      <c r="C1732" t="inlineStr">
+        <is>
+          <t>Panaf</t>
+        </is>
+      </c>
+      <c r="D1732" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1732" t="n">
+        <v>12</v>
+      </c>
+      <c r="F1732" t="n">
+        <v>315</v>
+      </c>
+      <c r="G1732" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1732" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1733">
+      <c r="A1733" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1733" t="inlineStr">
+        <is>
+          <t>Stephbreton</t>
+        </is>
+      </c>
+      <c r="C1733" t="inlineStr">
+        <is>
+          <t>STEPHANE</t>
+        </is>
+      </c>
+      <c r="D1733" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1733" t="n">
+        <v>13</v>
+      </c>
+      <c r="F1733" t="n">
+        <v>307</v>
+      </c>
+      <c r="G1733" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1733" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1734">
+      <c r="A1734" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1734" t="inlineStr">
+        <is>
+          <t>Kaliced</t>
+        </is>
+      </c>
+      <c r="C1734" t="inlineStr">
+        <is>
+          <t>Kalice</t>
+        </is>
+      </c>
+      <c r="D1734" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1734" t="n">
+        <v>14</v>
+      </c>
+      <c r="F1734" t="n">
+        <v>302</v>
+      </c>
+      <c r="G1734" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1734" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1735">
+      <c r="A1735" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1735" t="inlineStr">
+        <is>
+          <t>MyriamAmr</t>
+        </is>
+      </c>
+      <c r="C1735" t="inlineStr">
+        <is>
+          <t>Myriam</t>
+        </is>
+      </c>
+      <c r="D1735" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1735" t="n">
+        <v>15</v>
+      </c>
+      <c r="F1735" t="n">
+        <v>298</v>
+      </c>
+      <c r="G1735" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1735" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1736">
+      <c r="A1736" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1736" t="inlineStr">
+        <is>
+          <t>Nonito20</t>
+        </is>
+      </c>
+      <c r="C1736" t="inlineStr">
+        <is>
+          <t>Arnaud</t>
+        </is>
+      </c>
+      <c r="D1736" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1736" t="n">
+        <v>16</v>
+      </c>
+      <c r="F1736" t="n">
+        <v>284</v>
+      </c>
+      <c r="G1736" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1736" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1737">
+      <c r="A1737" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1737" t="inlineStr">
+        <is>
+          <t>FRHTCTD10</t>
+        </is>
+      </c>
+      <c r="C1737" t="inlineStr">
+        <is>
+          <t>Candice</t>
+        </is>
+      </c>
+      <c r="D1737" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1737" t="n">
+        <v>17</v>
+      </c>
+      <c r="F1737" t="n">
+        <v>282</v>
+      </c>
+      <c r="G1737" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1737" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1738">
+      <c r="A1738" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1738" t="inlineStr">
+        <is>
+          <t>Mr-Worldwide</t>
+        </is>
+      </c>
+      <c r="C1738" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="D1738" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1738" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1738" t="n">
+        <v>280</v>
+      </c>
+      <c r="G1738" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1738" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1739">
+      <c r="A1739" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1739" t="inlineStr">
+        <is>
+          <t>Fethinho</t>
+        </is>
+      </c>
+      <c r="C1739" t="inlineStr">
+        <is>
+          <t>Fethi</t>
+        </is>
+      </c>
+      <c r="D1739" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1739" t="n">
+        <v>19</v>
+      </c>
+      <c r="F1739" t="n">
+        <v>280</v>
+      </c>
+      <c r="G1739" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1739" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1740">
+      <c r="A1740" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1740" t="inlineStr">
+        <is>
+          <t>Ouiouiausoleil</t>
+        </is>
+      </c>
+      <c r="C1740" t="inlineStr">
+        <is>
+          <t>Ouissal</t>
+        </is>
+      </c>
+      <c r="D1740" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1740" t="n">
+        <v>20</v>
+      </c>
+      <c r="F1740" t="n">
+        <v>280</v>
+      </c>
+      <c r="G1740" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1740" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1741">
+      <c r="A1741" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1741" t="inlineStr">
+        <is>
+          <t>BOUGA#2JGXP</t>
+        </is>
+      </c>
+      <c r="C1741" t="inlineStr">
+        <is>
+          <t>BOUGA</t>
+        </is>
+      </c>
+      <c r="D1741" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1741" t="n">
+        <v>21</v>
+      </c>
+      <c r="F1741" t="n">
+        <v>260</v>
+      </c>
+      <c r="G1741" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1741" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1742">
+      <c r="A1742" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1742" t="inlineStr">
+        <is>
+          <t>Anais757817</t>
+        </is>
+      </c>
+      <c r="C1742" t="inlineStr">
+        <is>
+          <t>Anaïs</t>
+        </is>
+      </c>
+      <c r="D1742" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1742" t="n">
+        <v>22</v>
+      </c>
+      <c r="F1742" t="n">
+        <v>260</v>
+      </c>
+      <c r="G1742" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1742" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1743">
+      <c r="A1743" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1743" t="inlineStr">
+        <is>
+          <t>MatuRenard</t>
+        </is>
+      </c>
+      <c r="C1743" t="inlineStr">
+        <is>
+          <t>Mathias</t>
+        </is>
+      </c>
+      <c r="D1743" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1743" t="n">
+        <v>23</v>
+      </c>
+      <c r="F1743" t="n">
+        <v>259</v>
+      </c>
+      <c r="G1743" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1743" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1744">
+      <c r="A1744" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1744" t="inlineStr">
+        <is>
+          <t>Liliuus</t>
+        </is>
+      </c>
+      <c r="C1744" t="inlineStr">
+        <is>
+          <t>Lilia</t>
+        </is>
+      </c>
+      <c r="D1744" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1744" t="n">
+        <v>24</v>
+      </c>
+      <c r="F1744" t="n">
+        <v>259</v>
+      </c>
+      <c r="G1744" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1744" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1745">
+      <c r="A1745" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1745" t="inlineStr">
+        <is>
+          <t>Ppo28</t>
+        </is>
+      </c>
+      <c r="C1745" t="inlineStr">
+        <is>
+          <t>Prescylla</t>
+        </is>
+      </c>
+      <c r="D1745" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1745" t="n">
+        <v>25</v>
+      </c>
+      <c r="F1745" t="n">
+        <v>259</v>
+      </c>
+      <c r="G1745" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1745" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1746">
+      <c r="A1746" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1746" t="inlineStr">
+        <is>
+          <t>Gronaldo_95</t>
+        </is>
+      </c>
+      <c r="C1746" t="inlineStr">
+        <is>
+          <t>Gronaldo</t>
+        </is>
+      </c>
+      <c r="D1746" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1746" t="n">
+        <v>26</v>
+      </c>
+      <c r="F1746" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1746" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1746" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1747">
+      <c r="A1747" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1747" t="inlineStr">
+        <is>
+          <t>Devilrock95</t>
+        </is>
+      </c>
+      <c r="C1747" t="inlineStr">
+        <is>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="D1747" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1747" t="n">
+        <v>27</v>
+      </c>
+      <c r="F1747" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1747" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1747" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1748">
+      <c r="A1748" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1748" t="inlineStr">
+        <is>
+          <t>Cleem22</t>
+        </is>
+      </c>
+      <c r="C1748" t="inlineStr">
+        <is>
+          <t>Clemence</t>
+        </is>
+      </c>
+      <c r="D1748" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1748" t="n">
+        <v>28</v>
+      </c>
+      <c r="F1748" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1748" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1748" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1749">
+      <c r="A1749" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1749" t="inlineStr">
+        <is>
+          <t>catherine#5FRTD</t>
+        </is>
+      </c>
+      <c r="C1749" t="inlineStr">
+        <is>
+          <t>catherine</t>
+        </is>
+      </c>
+      <c r="D1749" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1749" t="n">
+        <v>29</v>
+      </c>
+      <c r="F1749" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1749" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1749" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1750">
+      <c r="A1750" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1750" t="inlineStr">
+        <is>
+          <t>Maruyama</t>
+        </is>
+      </c>
+      <c r="C1750" t="inlineStr">
+        <is>
+          <t>Gabrielle</t>
+        </is>
+      </c>
+      <c r="D1750" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1750" t="n">
+        <v>30</v>
+      </c>
+      <c r="F1750" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1750" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1750" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1751">
+      <c r="A1751" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1751" t="inlineStr">
+        <is>
+          <t>Leandrocp</t>
+        </is>
+      </c>
+      <c r="C1751" t="inlineStr">
+        <is>
+          <t>Leandro</t>
+        </is>
+      </c>
+      <c r="D1751" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1751" t="n">
+        <v>31</v>
+      </c>
+      <c r="F1751" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1751" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1751" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="A1752" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1752" t="inlineStr">
+        <is>
+          <t>Marion1822</t>
+        </is>
+      </c>
+      <c r="C1752" t="inlineStr">
+        <is>
+          <t>Marion</t>
+        </is>
+      </c>
+      <c r="D1752" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1752" t="n">
+        <v>32</v>
+      </c>
+      <c r="F1752" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1752" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1752" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1753">
+      <c r="A1753" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1753" t="inlineStr">
+        <is>
+          <t>chaychaychay</t>
+        </is>
+      </c>
+      <c r="C1753" t="inlineStr">
+        <is>
+          <t>Chaymaa</t>
+        </is>
+      </c>
+      <c r="D1753" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1753" t="n">
+        <v>33</v>
+      </c>
+      <c r="F1753" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1753" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1753" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1754">
+      <c r="A1754" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1754" t="inlineStr">
+        <is>
+          <t>WIL1610</t>
+        </is>
+      </c>
+      <c r="C1754" t="inlineStr">
+        <is>
+          <t>William</t>
+        </is>
+      </c>
+      <c r="D1754" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1754" t="n">
+        <v>34</v>
+      </c>
+      <c r="F1754" t="n">
+        <v>233</v>
+      </c>
+      <c r="G1754" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1754" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1755">
+      <c r="A1755" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1755" t="inlineStr">
+        <is>
+          <t>Erwan#4G91X</t>
+        </is>
+      </c>
+      <c r="C1755" t="inlineStr">
+        <is>
+          <t>Erwan</t>
+        </is>
+      </c>
+      <c r="D1755" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1755" t="n">
+        <v>35</v>
+      </c>
+      <c r="F1755" t="n">
+        <v>219</v>
+      </c>
+      <c r="G1755" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1755" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1756">
+      <c r="A1756" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1756" t="inlineStr">
+        <is>
+          <t>GLR_PRIME</t>
+        </is>
+      </c>
+      <c r="C1756" t="inlineStr">
+        <is>
+          <t>Gabriel</t>
+        </is>
+      </c>
+      <c r="D1756" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1756" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1756" t="n">
+        <v>219</v>
+      </c>
+      <c r="G1756" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1756" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1757">
+      <c r="A1757" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1757" t="inlineStr">
+        <is>
+          <t>Exia95</t>
+        </is>
+      </c>
+      <c r="C1757" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D1757" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1757" t="n">
+        <v>37</v>
+      </c>
+      <c r="F1757" t="n">
+        <v>212</v>
+      </c>
+      <c r="G1757" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1757" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1758">
+      <c r="A1758" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1758" t="inlineStr">
+        <is>
+          <t>Matt#4B4CU</t>
+        </is>
+      </c>
+      <c r="C1758" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="D1758" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1758" t="n">
+        <v>38</v>
+      </c>
+      <c r="F1758" t="n">
+        <v>211</v>
+      </c>
+      <c r="G1758" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1758" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1759">
+      <c r="A1759" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1759" t="inlineStr">
+        <is>
+          <t>dian-bgt</t>
+        </is>
+      </c>
+      <c r="C1759" t="inlineStr">
+        <is>
+          <t>Diane</t>
+        </is>
+      </c>
+      <c r="D1759" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1759" t="n">
+        <v>39</v>
+      </c>
+      <c r="F1759" t="n">
+        <v>206</v>
+      </c>
+      <c r="G1759" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1759" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1760">
+      <c r="A1760" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1760" t="inlineStr">
+        <is>
+          <t>LilianeB</t>
+        </is>
+      </c>
+      <c r="C1760" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liliane </t>
+        </is>
+      </c>
+      <c r="D1760" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1760" t="n">
+        <v>40</v>
+      </c>
+      <c r="F1760" t="n">
+        <v>206</v>
+      </c>
+      <c r="G1760" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1760" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1761">
+      <c r="A1761" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1761" t="inlineStr">
+        <is>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="C1761" t="inlineStr">
+        <is>
+          <t>Julie</t>
+        </is>
+      </c>
+      <c r="D1761" t="inlineStr"/>
+      <c r="E1761" t="n">
+        <v>41</v>
+      </c>
+      <c r="F1761" t="n">
+        <v>206</v>
+      </c>
+      <c r="G1761" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1761" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1762">
+      <c r="A1762" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1762" t="inlineStr">
+        <is>
+          <t>Romain_JO</t>
+        </is>
+      </c>
+      <c r="C1762" t="inlineStr">
+        <is>
+          <t>Romain J</t>
+        </is>
+      </c>
+      <c r="D1762" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1762" t="n">
+        <v>42</v>
+      </c>
+      <c r="F1762" t="n">
+        <v>191</v>
+      </c>
+      <c r="G1762" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1762" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1763">
+      <c r="A1763" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1763" t="inlineStr">
+        <is>
+          <t>JeremFZ</t>
+        </is>
+      </c>
+      <c r="C1763" t="inlineStr">
+        <is>
+          <t>Jérémy</t>
+        </is>
+      </c>
+      <c r="D1763" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1763" t="n">
+        <v>43</v>
+      </c>
+      <c r="F1763" t="n">
+        <v>191</v>
+      </c>
+      <c r="G1763" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1763" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1764">
+      <c r="A1764" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1764" t="inlineStr">
+        <is>
+          <t>AudreyB225</t>
+        </is>
+      </c>
+      <c r="C1764" t="inlineStr">
+        <is>
+          <t>Audrey</t>
+        </is>
+      </c>
+      <c r="D1764" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1764" t="n">
+        <v>44</v>
+      </c>
+      <c r="F1764" t="n">
+        <v>190</v>
+      </c>
+      <c r="G1764" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1764" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1765">
+      <c r="A1765" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1765" t="inlineStr">
+        <is>
+          <t>Camss</t>
+        </is>
+      </c>
+      <c r="C1765" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D1765" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1765" t="n">
+        <v>45</v>
+      </c>
+      <c r="F1765" t="n">
+        <v>190</v>
+      </c>
+      <c r="G1765" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1765" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1766">
+      <c r="A1766" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1766" t="inlineStr">
+        <is>
+          <t>BadrLeo</t>
+        </is>
+      </c>
+      <c r="C1766" t="inlineStr">
+        <is>
+          <t>Badr Leo</t>
+        </is>
+      </c>
+      <c r="D1766" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1766" t="n">
+        <v>46</v>
+      </c>
+      <c r="F1766" t="n">
+        <v>186</v>
+      </c>
+      <c r="G1766" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1766" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1767">
+      <c r="A1767" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1767" t="inlineStr">
+        <is>
+          <t>YassineZ95</t>
+        </is>
+      </c>
+      <c r="C1767" t="inlineStr">
+        <is>
+          <t>Yassine Z</t>
+        </is>
+      </c>
+      <c r="D1767" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1767" t="n">
+        <v>47</v>
+      </c>
+      <c r="F1767" t="n">
+        <v>186</v>
+      </c>
+      <c r="G1767" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1767" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1768">
+      <c r="A1768" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1768" t="inlineStr">
+        <is>
+          <t>Ilan_260_</t>
+        </is>
+      </c>
+      <c r="C1768" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ilann </t>
+        </is>
+      </c>
+      <c r="D1768" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1768" t="n">
+        <v>48</v>
+      </c>
+      <c r="F1768" t="n">
+        <v>185</v>
+      </c>
+      <c r="G1768" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1768" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1769">
+      <c r="A1769" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1769" t="inlineStr">
+        <is>
+          <t>abihuts</t>
+        </is>
+      </c>
+      <c r="C1769" t="inlineStr">
+        <is>
+          <t>Antonio Moctezuma</t>
+        </is>
+      </c>
+      <c r="D1769" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1769" t="n">
+        <v>49</v>
+      </c>
+      <c r="F1769" t="n">
+        <v>172</v>
+      </c>
+      <c r="G1769" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1769" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1770">
+      <c r="A1770" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1770" t="inlineStr">
+        <is>
+          <t>Chadia__</t>
+        </is>
+      </c>
+      <c r="C1770" t="inlineStr">
+        <is>
+          <t>Chadia</t>
+        </is>
+      </c>
+      <c r="D1770" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1770" t="n">
+        <v>50</v>
+      </c>
+      <c r="F1770" t="n">
+        <v>170</v>
+      </c>
+      <c r="G1770" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1770" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1771">
+      <c r="A1771" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1771" t="inlineStr">
+        <is>
+          <t>GOAT#UE2WM8M9</t>
+        </is>
+      </c>
+      <c r="C1771" t="inlineStr">
+        <is>
+          <t>Marilena</t>
+        </is>
+      </c>
+      <c r="D1771" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1771" t="n">
+        <v>51</v>
+      </c>
+      <c r="F1771" t="n">
+        <v>165</v>
+      </c>
+      <c r="G1771" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1771" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1772">
+      <c r="A1772" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1772" t="inlineStr">
+        <is>
+          <t>Ceciledp</t>
+        </is>
+      </c>
+      <c r="C1772" t="inlineStr">
+        <is>
+          <t>Cécile</t>
+        </is>
+      </c>
+      <c r="D1772" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1772" t="n">
+        <v>52</v>
+      </c>
+      <c r="F1772" t="n">
+        <v>145</v>
+      </c>
+      <c r="G1772" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1772" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1773">
+      <c r="A1773" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1773" t="inlineStr">
+        <is>
+          <t>Fuzo697</t>
+        </is>
+      </c>
+      <c r="C1773" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D1773" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1773" t="n">
+        <v>53</v>
+      </c>
+      <c r="F1773" t="n">
+        <v>145</v>
+      </c>
+      <c r="G1773" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1773" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1774">
+      <c r="A1774" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1774" t="inlineStr">
+        <is>
+          <t>Yebri</t>
+        </is>
+      </c>
+      <c r="C1774" t="inlineStr">
+        <is>
+          <t>Brieuc</t>
+        </is>
+      </c>
+      <c r="D1774" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1774" t="n">
+        <v>54</v>
+      </c>
+      <c r="F1774" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1774" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1774" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1775">
+      <c r="A1775" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1775" t="inlineStr">
+        <is>
+          <t>Leo_durable</t>
+        </is>
+      </c>
+      <c r="C1775" t="inlineStr">
+        <is>
+          <t>Leo</t>
+        </is>
+      </c>
+      <c r="D1775" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1775" t="n">
+        <v>55</v>
+      </c>
+      <c r="F1775" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1775" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1775" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1776">
+      <c r="A1776" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1776" t="inlineStr">
+        <is>
+          <t>EmyEnzo</t>
+        </is>
+      </c>
+      <c r="C1776" t="inlineStr">
+        <is>
+          <t>Emilie</t>
+        </is>
+      </c>
+      <c r="D1776" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1776" t="n">
+        <v>56</v>
+      </c>
+      <c r="F1776" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1776" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1776" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1777">
+      <c r="A1777" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1777" t="inlineStr">
+        <is>
+          <t>Priscilla#4LCAF</t>
+        </is>
+      </c>
+      <c r="C1777" t="inlineStr">
+        <is>
+          <t>Priscilla</t>
+        </is>
+      </c>
+      <c r="D1777" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1777" t="n">
+        <v>57</v>
+      </c>
+      <c r="F1777" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1777" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1777" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1778">
+      <c r="A1778" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1778" t="inlineStr">
+        <is>
+          <t>Pipou931</t>
+        </is>
+      </c>
+      <c r="C1778" t="inlineStr">
+        <is>
+          <t>Juliie</t>
+        </is>
+      </c>
+      <c r="D1778" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1778" t="n">
+        <v>58</v>
+      </c>
+      <c r="F1778" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1778" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1778" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1779">
+      <c r="A1779" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1779" t="inlineStr">
+        <is>
+          <t>Farah_One</t>
+        </is>
+      </c>
+      <c r="C1779" t="inlineStr">
+        <is>
+          <t>Farah</t>
+        </is>
+      </c>
+      <c r="D1779" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1779" t="n">
+        <v>59</v>
+      </c>
+      <c r="F1779" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1779" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1779" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1780">
+      <c r="A1780" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1780" t="inlineStr">
+        <is>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="C1780" t="inlineStr">
+        <is>
+          <t>François</t>
+        </is>
+      </c>
+      <c r="D1780" t="inlineStr"/>
+      <c r="E1780" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1780" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1780" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1780" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1781">
+      <c r="A1781" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1781" t="inlineStr">
+        <is>
+          <t>Seesee</t>
+        </is>
+      </c>
+      <c r="C1781" t="inlineStr">
+        <is>
+          <t>Selver</t>
+        </is>
+      </c>
+      <c r="D1781" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1781" t="n">
+        <v>61</v>
+      </c>
+      <c r="F1781" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1781" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1781" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1782">
+      <c r="A1782" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1782" t="inlineStr">
+        <is>
+          <t>lenaaik</t>
+        </is>
+      </c>
+      <c r="C1782" t="inlineStr">
+        <is>
+          <t>Lénaïk</t>
+        </is>
+      </c>
+      <c r="D1782" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1782" t="n">
+        <v>62</v>
+      </c>
+      <c r="F1782" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1782" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1782" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1783">
+      <c r="A1783" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1783" t="inlineStr">
+        <is>
+          <t>C4M</t>
+        </is>
+      </c>
+      <c r="C1783" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D1783" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1783" t="n">
+        <v>63</v>
+      </c>
+      <c r="F1783" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1783" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1783" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1784">
+      <c r="A1784" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1784" t="inlineStr">
+        <is>
+          <t>Rosa_1009</t>
+        </is>
+      </c>
+      <c r="C1784" t="inlineStr">
+        <is>
+          <t>Rosaline</t>
+        </is>
+      </c>
+      <c r="D1784" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1784" t="n">
+        <v>64</v>
+      </c>
+      <c r="F1784" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1784" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1784" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1785">
+      <c r="A1785" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1785" t="inlineStr">
+        <is>
+          <t>Elisewiss</t>
+        </is>
+      </c>
+      <c r="C1785" t="inlineStr">
+        <is>
+          <t>Elise</t>
+        </is>
+      </c>
+      <c r="D1785" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1785" t="n">
+        <v>65</v>
+      </c>
+      <c r="F1785" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1785" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1785" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1786">
+      <c r="A1786" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1786" t="inlineStr">
+        <is>
+          <t>Soraya-Y</t>
+        </is>
+      </c>
+      <c r="C1786" t="inlineStr">
+        <is>
+          <t>Soraya</t>
+        </is>
+      </c>
+      <c r="D1786" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1786" t="n">
+        <v>66</v>
+      </c>
+      <c r="F1786" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1786" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1786" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1787">
+      <c r="A1787" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1787" t="inlineStr">
+        <is>
+          <t>1993ahm</t>
+        </is>
+      </c>
+      <c r="C1787" t="inlineStr">
+        <is>
+          <t>Ahmed</t>
+        </is>
+      </c>
+      <c r="D1787" t="inlineStr"/>
+      <c r="E1787" t="n">
+        <v>67</v>
+      </c>
+      <c r="F1787" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1787" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1787" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1788">
+      <c r="A1788" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1788" t="inlineStr">
+        <is>
+          <t>Timy</t>
+        </is>
+      </c>
+      <c r="C1788" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="D1788" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1788" t="n">
+        <v>68</v>
+      </c>
+      <c r="F1788" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1788" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1788" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1789">
+      <c r="A1789" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1789" t="inlineStr">
+        <is>
+          <t>JEVAISGAGNER10</t>
+        </is>
+      </c>
+      <c r="C1789" t="inlineStr">
+        <is>
+          <t>Xavier</t>
+        </is>
+      </c>
+      <c r="D1789" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1789" t="n">
+        <v>69</v>
+      </c>
+      <c r="F1789" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1789" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1789" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1790">
+      <c r="A1790" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1790" t="inlineStr">
+        <is>
+          <t>HamzaG</t>
+        </is>
+      </c>
+      <c r="C1790" t="inlineStr">
+        <is>
+          <t>Hamza</t>
+        </is>
+      </c>
+      <c r="D1790" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1790" t="n">
+        <v>70</v>
+      </c>
+      <c r="F1790" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1790" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1790" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1791">
+      <c r="A1791" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1791" t="inlineStr">
+        <is>
+          <t>LeaBrd</t>
+        </is>
+      </c>
+      <c r="C1791" t="inlineStr">
+        <is>
+          <t>Léa</t>
+        </is>
+      </c>
+      <c r="D1791" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1791" t="n">
+        <v>71</v>
+      </c>
+      <c r="F1791" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1791" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1791" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1792">
+      <c r="A1792" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1792" t="inlineStr">
+        <is>
+          <t>davidd23</t>
+        </is>
+      </c>
+      <c r="C1792" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D1792" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1792" t="n">
+        <v>72</v>
+      </c>
+      <c r="F1792" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1792" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1792" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1793">
+      <c r="A1793" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1793" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="C1793" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="D1793" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1793" t="n">
+        <v>73</v>
+      </c>
+      <c r="F1793" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1793" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1793" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1794">
+      <c r="A1794" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1794" t="inlineStr">
+        <is>
+          <t>Kolas</t>
+        </is>
+      </c>
+      <c r="C1794" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D1794" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1794" t="n">
+        <v>74</v>
+      </c>
+      <c r="F1794" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1794" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1794" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1795">
+      <c r="A1795" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1795" t="inlineStr">
+        <is>
+          <t>Laetice2020</t>
+        </is>
+      </c>
+      <c r="C1795" t="inlineStr">
+        <is>
+          <t>Laetitia</t>
+        </is>
+      </c>
+      <c r="D1795" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1795" t="n">
+        <v>75</v>
+      </c>
+      <c r="F1795" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1795" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1795" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1796">
+      <c r="A1796" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1796" t="inlineStr">
+        <is>
+          <t>Emilay</t>
+        </is>
+      </c>
+      <c r="C1796" t="inlineStr">
+        <is>
+          <t>Émilie</t>
+        </is>
+      </c>
+      <c r="D1796" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1796" t="n">
+        <v>76</v>
+      </c>
+      <c r="F1796" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1796" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1796" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1797">
+      <c r="A1797" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1797" t="inlineStr">
+        <is>
+          <t>Lyzone</t>
+        </is>
+      </c>
+      <c r="C1797" t="inlineStr">
+        <is>
+          <t>Lison</t>
+        </is>
+      </c>
+      <c r="D1797" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1797" t="n">
+        <v>77</v>
+      </c>
+      <c r="F1797" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1797" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1797" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1798">
+      <c r="A1798" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1798" t="inlineStr">
+        <is>
+          <t>Melissagzb</t>
+        </is>
+      </c>
+      <c r="C1798" t="inlineStr">
+        <is>
+          <t>Melissa</t>
+        </is>
+      </c>
+      <c r="D1798" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1798" t="n">
+        <v>78</v>
+      </c>
+      <c r="F1798" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1798" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1798" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1799">
+      <c r="A1799" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1799" t="inlineStr">
+        <is>
+          <t>Marie__92</t>
+        </is>
+      </c>
+      <c r="C1799" t="inlineStr">
+        <is>
+          <t>Marie</t>
+        </is>
+      </c>
+      <c r="D1799" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1799" t="n">
+        <v>79</v>
+      </c>
+      <c r="F1799" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1799" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1799" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1800">
+      <c r="A1800" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1800" t="inlineStr">
+        <is>
+          <t>K_Marp</t>
+        </is>
+      </c>
+      <c r="C1800" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
+      <c r="D1800" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1800" t="n">
+        <v>80</v>
+      </c>
+      <c r="F1800" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1800" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1800" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1801">
+      <c r="A1801" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1801" t="inlineStr">
+        <is>
+          <t>Cindie_JJA</t>
+        </is>
+      </c>
+      <c r="C1801" t="inlineStr">
+        <is>
+          <t>Cindie</t>
+        </is>
+      </c>
+      <c r="D1801" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1801" t="n">
+        <v>81</v>
+      </c>
+      <c r="F1801" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1801" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1801" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1802">
+      <c r="A1802" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1802" t="inlineStr">
+        <is>
+          <t>JKInternational</t>
+        </is>
+      </c>
+      <c r="C1802" t="inlineStr">
+        <is>
+          <t>Joachim</t>
+        </is>
+      </c>
+      <c r="D1802" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1802" t="n">
+        <v>82</v>
+      </c>
+      <c r="F1802" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1802" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1802" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1803">
+      <c r="A1803" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1803" t="inlineStr">
+        <is>
+          <t>GOAT#UE4U8KA6</t>
+        </is>
+      </c>
+      <c r="C1803" t="inlineStr">
+        <is>
+          <t>Jean Baptiste</t>
+        </is>
+      </c>
+      <c r="D1803" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1803" t="n">
+        <v>83</v>
+      </c>
+      <c r="F1803" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1803" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1803" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1804">
+      <c r="A1804" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1804" t="inlineStr">
+        <is>
+          <t>goat#AD6GS</t>
+        </is>
+      </c>
+      <c r="C1804" t="inlineStr">
+        <is>
+          <t>goat</t>
+        </is>
+      </c>
+      <c r="D1804" t="inlineStr"/>
+      <c r="E1804" t="n">
+        <v>84</v>
+      </c>
+      <c r="F1804" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1804" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1804" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1805">
+      <c r="A1805" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1805" t="inlineStr">
+        <is>
+          <t>Camillewbl</t>
+        </is>
+      </c>
+      <c r="C1805" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D1805" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1805" t="n">
+        <v>85</v>
+      </c>
+      <c r="F1805" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1805" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1805" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1806">
+      <c r="A1806" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1806" t="inlineStr">
+        <is>
+          <t>Emma_Noel</t>
+        </is>
+      </c>
+      <c r="C1806" t="inlineStr">
+        <is>
+          <t>Emma</t>
+        </is>
+      </c>
+      <c r="D1806" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1806" t="n">
+        <v>86</v>
+      </c>
+      <c r="F1806" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1806" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1806" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1807">
+      <c r="A1807" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1807" t="inlineStr">
+        <is>
+          <t>RBTL</t>
+        </is>
+      </c>
+      <c r="C1807" t="inlineStr">
+        <is>
+          <t>lea</t>
+        </is>
+      </c>
+      <c r="D1807" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1807" t="n">
+        <v>87</v>
+      </c>
+      <c r="F1807" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1807" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1807" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1808">
+      <c r="A1808" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1808" t="inlineStr">
+        <is>
+          <t>A-MOE</t>
+        </is>
+      </c>
+      <c r="C1808" t="inlineStr">
+        <is>
+          <t>Françoise</t>
+        </is>
+      </c>
+      <c r="D1808" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1808" t="n">
+        <v>88</v>
+      </c>
+      <c r="F1808" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1808" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1808" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1809">
+      <c r="A1809" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1809" t="inlineStr">
+        <is>
+          <t>Davido#4BZ54</t>
+        </is>
+      </c>
+      <c r="C1809" t="inlineStr">
+        <is>
+          <t>Davido</t>
+        </is>
+      </c>
+      <c r="D1809" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1809" t="n">
+        <v>89</v>
+      </c>
+      <c r="F1809" t="n">
+        <v>96</v>
+      </c>
+      <c r="G1809" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1809" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1810">
+      <c r="A1810" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1810" t="inlineStr">
+        <is>
+          <t>BrickXVI</t>
+        </is>
+      </c>
+      <c r="C1810" t="inlineStr">
+        <is>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="D1810" t="inlineStr"/>
+      <c r="E1810" t="n">
+        <v>90</v>
+      </c>
+      <c r="F1810" t="n">
+        <v>74</v>
+      </c>
+      <c r="G1810" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1810" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1811">
+      <c r="A1811" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1811" t="inlineStr">
+        <is>
+          <t>Taylor2901</t>
+        </is>
+      </c>
+      <c r="C1811" t="inlineStr">
+        <is>
+          <t>ousmane</t>
+        </is>
+      </c>
+      <c r="D1811" t="inlineStr"/>
+      <c r="E1811" t="n">
+        <v>91</v>
+      </c>
+      <c r="F1811" t="n">
+        <v>74</v>
+      </c>
+      <c r="G1811" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1811" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1812">
+      <c r="A1812" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1812" t="inlineStr">
+        <is>
+          <t>Ze_GOAT</t>
+        </is>
+      </c>
+      <c r="C1812" t="inlineStr">
+        <is>
+          <t>Yasser</t>
+        </is>
+      </c>
+      <c r="D1812" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1812" t="n">
+        <v>92</v>
+      </c>
+      <c r="F1812" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1812" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1812" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1813">
+      <c r="A1813" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1813" t="inlineStr">
+        <is>
+          <t>Krol#4R8XC</t>
+        </is>
+      </c>
+      <c r="C1813" t="inlineStr">
+        <is>
+          <t>Krol</t>
+        </is>
+      </c>
+      <c r="D1813" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1813" t="n">
+        <v>93</v>
+      </c>
+      <c r="F1813" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1813" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1813" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1814">
+      <c r="A1814" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1814" t="inlineStr">
+        <is>
+          <t>PacoSarra</t>
+        </is>
+      </c>
+      <c r="C1814" t="inlineStr">
+        <is>
+          <t>Ibra</t>
+        </is>
+      </c>
+      <c r="D1814" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1814" t="n">
+        <v>94</v>
+      </c>
+      <c r="F1814" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1814" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1814" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1815">
+      <c r="A1815" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1815" t="inlineStr">
+        <is>
+          <t>Droit_au_but7723</t>
+        </is>
+      </c>
+      <c r="C1815" t="inlineStr">
+        <is>
+          <t>Calixthe</t>
+        </is>
+      </c>
+      <c r="D1815" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1815" t="n">
+        <v>95</v>
+      </c>
+      <c r="F1815" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1815" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1815" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1816">
+      <c r="A1816" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1816" t="inlineStr">
+        <is>
+          <t>Ambrepic</t>
+        </is>
+      </c>
+      <c r="C1816" t="inlineStr">
+        <is>
+          <t>Ambre</t>
+        </is>
+      </c>
+      <c r="D1816" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1816" t="n">
+        <v>96</v>
+      </c>
+      <c r="F1816" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1816" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1816" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1817">
+      <c r="A1817" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1817" t="inlineStr">
+        <is>
+          <t>PavelMel</t>
+        </is>
+      </c>
+      <c r="C1817" t="inlineStr">
+        <is>
+          <t>Mélissa</t>
+        </is>
+      </c>
+      <c r="D1817" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1817" t="n">
+        <v>97</v>
+      </c>
+      <c r="F1817" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1817" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1817" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1818">
+      <c r="A1818" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1818" t="inlineStr">
+        <is>
+          <t>Mylene-Jnt</t>
+        </is>
+      </c>
+      <c r="C1818" t="inlineStr">
+        <is>
+          <t>Mylène</t>
+        </is>
+      </c>
+      <c r="D1818" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1818" t="n">
+        <v>98</v>
+      </c>
+      <c r="F1818" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1818" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1818" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1819">
+      <c r="A1819" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1819" t="inlineStr">
+        <is>
+          <t>Teddbear</t>
+        </is>
+      </c>
+      <c r="C1819" t="inlineStr">
+        <is>
+          <t>Tedy</t>
+        </is>
+      </c>
+      <c r="D1819" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1819" t="n">
+        <v>99</v>
+      </c>
+      <c r="F1819" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1819" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1819" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1820">
+      <c r="A1820" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1820" t="inlineStr">
+        <is>
+          <t>SabC1</t>
+        </is>
+      </c>
+      <c r="C1820" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="D1820" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1820" t="n">
+        <v>100</v>
+      </c>
+      <c r="F1820" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1820" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1820" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1821">
+      <c r="A1821" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1821" t="inlineStr">
+        <is>
+          <t>KIKS999</t>
+        </is>
+      </c>
+      <c r="C1821" t="inlineStr">
+        <is>
+          <t>Killian</t>
+        </is>
+      </c>
+      <c r="D1821" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1821" t="n">
+        <v>101</v>
+      </c>
+      <c r="F1821" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1821" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1821" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1822">
+      <c r="A1822" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1822" t="inlineStr">
+        <is>
+          <t>MxKnight</t>
+        </is>
+      </c>
+      <c r="C1822" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D1822" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1822" t="n">
+        <v>102</v>
+      </c>
+      <c r="F1822" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1822" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1822" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1823">
+      <c r="A1823" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1823" t="inlineStr">
+        <is>
+          <t>RomainLect</t>
+        </is>
+      </c>
+      <c r="C1823" t="inlineStr">
+        <is>
+          <t>romain</t>
+        </is>
+      </c>
+      <c r="D1823" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1823" t="n">
+        <v>103</v>
+      </c>
+      <c r="F1823" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1823" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1823" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1824">
+      <c r="A1824" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1824" t="inlineStr">
+        <is>
+          <t>SamSamH8</t>
+        </is>
+      </c>
+      <c r="C1824" t="inlineStr">
+        <is>
+          <t>Samia</t>
+        </is>
+      </c>
+      <c r="D1824" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1824" t="n">
+        <v>104</v>
+      </c>
+      <c r="F1824" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1824" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1824" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1825">
+      <c r="A1825" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1825" t="inlineStr">
+        <is>
+          <t>Daviddesco1</t>
+        </is>
+      </c>
+      <c r="C1825" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D1825" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1825" t="n">
+        <v>105</v>
+      </c>
+      <c r="F1825" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1825" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1825" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1826">
+      <c r="A1826" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1826" t="inlineStr">
+        <is>
+          <t>Sab_M45</t>
+        </is>
+      </c>
+      <c r="C1826" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="D1826" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1826" t="n">
+        <v>106</v>
+      </c>
+      <c r="F1826" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1826" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1826" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1827">
+      <c r="A1827" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1827" t="inlineStr">
+        <is>
+          <t>Valentine___</t>
+        </is>
+      </c>
+      <c r="C1827" t="inlineStr">
+        <is>
+          <t>Valentine</t>
+        </is>
+      </c>
+      <c r="D1827" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1827" t="n">
+        <v>107</v>
+      </c>
+      <c r="F1827" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1827" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1827" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1828">
+      <c r="A1828" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1828" t="inlineStr">
+        <is>
+          <t>PANENKANY</t>
+        </is>
+      </c>
+      <c r="C1828" t="inlineStr">
+        <is>
+          <t>Damien</t>
+        </is>
+      </c>
+      <c r="D1828" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1828" t="n">
+        <v>108</v>
+      </c>
+      <c r="F1828" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1828" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1828" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1829">
+      <c r="A1829" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1829" t="inlineStr">
+        <is>
+          <t>MT35T</t>
+        </is>
+      </c>
+      <c r="C1829" t="inlineStr">
+        <is>
+          <t>Mathilde</t>
+        </is>
+      </c>
+      <c r="D1829" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1829" t="n">
+        <v>109</v>
+      </c>
+      <c r="F1829" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1829" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1829" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historique_joueurs.xlsx
+++ b/historique_joueurs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1829"/>
+  <dimension ref="A1:H1938"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61150,6 +61150,3688 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1830">
+      <c r="A1830" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1830" t="inlineStr">
+        <is>
+          <t>Filipinho95</t>
+        </is>
+      </c>
+      <c r="C1830" t="inlineStr">
+        <is>
+          <t>Filipe</t>
+        </is>
+      </c>
+      <c r="D1830" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1830" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1830" t="n">
+        <v>410</v>
+      </c>
+      <c r="G1830" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1830" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1831">
+      <c r="A1831" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1831" t="inlineStr">
+        <is>
+          <t>Ninaaaa</t>
+        </is>
+      </c>
+      <c r="C1831" t="inlineStr">
+        <is>
+          <t>Nina</t>
+        </is>
+      </c>
+      <c r="D1831" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1831" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1831" t="n">
+        <v>400</v>
+      </c>
+      <c r="G1831" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1831" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1832">
+      <c r="A1832" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1832" t="inlineStr">
+        <is>
+          <t>MargauxCtln</t>
+        </is>
+      </c>
+      <c r="C1832" t="inlineStr">
+        <is>
+          <t>Margaux</t>
+        </is>
+      </c>
+      <c r="D1832" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1832" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1832" t="n">
+        <v>376</v>
+      </c>
+      <c r="G1832" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1832" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1833">
+      <c r="A1833" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1833" t="inlineStr">
+        <is>
+          <t>Mamad_Shelter</t>
+        </is>
+      </c>
+      <c r="C1833" t="inlineStr">
+        <is>
+          <t>Mamadou</t>
+        </is>
+      </c>
+      <c r="D1833" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1833" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1833" t="n">
+        <v>376</v>
+      </c>
+      <c r="G1833" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1833" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1834">
+      <c r="A1834" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1834" t="inlineStr">
+        <is>
+          <t>MagicMath</t>
+        </is>
+      </c>
+      <c r="C1834" t="inlineStr">
+        <is>
+          <t>Mathieu</t>
+        </is>
+      </c>
+      <c r="D1834" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1834" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1834" t="n">
+        <v>376</v>
+      </c>
+      <c r="G1834" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1834" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1835">
+      <c r="A1835" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1835" t="inlineStr">
+        <is>
+          <t>WalidSiuuuuu</t>
+        </is>
+      </c>
+      <c r="C1835" t="inlineStr">
+        <is>
+          <t>Walid</t>
+        </is>
+      </c>
+      <c r="D1835" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1835" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1835" t="n">
+        <v>356</v>
+      </c>
+      <c r="G1835" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1835" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1836">
+      <c r="A1836" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1836" t="inlineStr">
+        <is>
+          <t>DJOSWA</t>
+        </is>
+      </c>
+      <c r="C1836" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oswaina </t>
+        </is>
+      </c>
+      <c r="D1836" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1836" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1836" t="n">
+        <v>356</v>
+      </c>
+      <c r="G1836" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1836" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1837">
+      <c r="A1837" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1837" t="inlineStr">
+        <is>
+          <t>SID-F-ANDRE</t>
+        </is>
+      </c>
+      <c r="C1837" t="inlineStr">
+        <is>
+          <t>Denis</t>
+        </is>
+      </c>
+      <c r="D1837" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1837" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1837" t="n">
+        <v>355</v>
+      </c>
+      <c r="G1837" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1837" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1838">
+      <c r="A1838" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1838" t="inlineStr">
+        <is>
+          <t>ChrisKr1Deg1</t>
+        </is>
+      </c>
+      <c r="C1838" t="inlineStr">
+        <is>
+          <t>christophe</t>
+        </is>
+      </c>
+      <c r="D1838" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1838" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1838" t="n">
+        <v>323</v>
+      </c>
+      <c r="G1838" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1838" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1839">
+      <c r="A1839" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1839" t="inlineStr">
+        <is>
+          <t>Coucoucassecou</t>
+        </is>
+      </c>
+      <c r="C1839" t="inlineStr">
+        <is>
+          <t>Brayen</t>
+        </is>
+      </c>
+      <c r="D1839" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1839" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1839" t="n">
+        <v>322</v>
+      </c>
+      <c r="G1839" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1839" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1840">
+      <c r="A1840" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1840" t="inlineStr">
+        <is>
+          <t>Paulasipi1998</t>
+        </is>
+      </c>
+      <c r="C1840" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="D1840" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1840" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1840" t="n">
+        <v>322</v>
+      </c>
+      <c r="G1840" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1840" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1841">
+      <c r="A1841" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1841" t="inlineStr">
+        <is>
+          <t>Panaff</t>
+        </is>
+      </c>
+      <c r="C1841" t="inlineStr">
+        <is>
+          <t>Panaf</t>
+        </is>
+      </c>
+      <c r="D1841" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1841" t="n">
+        <v>12</v>
+      </c>
+      <c r="F1841" t="n">
+        <v>315</v>
+      </c>
+      <c r="G1841" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1841" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1842">
+      <c r="A1842" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1842" t="inlineStr">
+        <is>
+          <t>Stephbreton</t>
+        </is>
+      </c>
+      <c r="C1842" t="inlineStr">
+        <is>
+          <t>STEPHANE</t>
+        </is>
+      </c>
+      <c r="D1842" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1842" t="n">
+        <v>13</v>
+      </c>
+      <c r="F1842" t="n">
+        <v>307</v>
+      </c>
+      <c r="G1842" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1842" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1843">
+      <c r="A1843" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1843" t="inlineStr">
+        <is>
+          <t>Kaliced</t>
+        </is>
+      </c>
+      <c r="C1843" t="inlineStr">
+        <is>
+          <t>Kalice</t>
+        </is>
+      </c>
+      <c r="D1843" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1843" t="n">
+        <v>14</v>
+      </c>
+      <c r="F1843" t="n">
+        <v>302</v>
+      </c>
+      <c r="G1843" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1843" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1844">
+      <c r="A1844" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1844" t="inlineStr">
+        <is>
+          <t>MyriamAmr</t>
+        </is>
+      </c>
+      <c r="C1844" t="inlineStr">
+        <is>
+          <t>Myriam</t>
+        </is>
+      </c>
+      <c r="D1844" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1844" t="n">
+        <v>15</v>
+      </c>
+      <c r="F1844" t="n">
+        <v>298</v>
+      </c>
+      <c r="G1844" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1844" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1845">
+      <c r="A1845" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1845" t="inlineStr">
+        <is>
+          <t>Nonito20</t>
+        </is>
+      </c>
+      <c r="C1845" t="inlineStr">
+        <is>
+          <t>Arnaud</t>
+        </is>
+      </c>
+      <c r="D1845" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1845" t="n">
+        <v>16</v>
+      </c>
+      <c r="F1845" t="n">
+        <v>284</v>
+      </c>
+      <c r="G1845" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1845" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1846">
+      <c r="A1846" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1846" t="inlineStr">
+        <is>
+          <t>FRHTCTD10</t>
+        </is>
+      </c>
+      <c r="C1846" t="inlineStr">
+        <is>
+          <t>Candice</t>
+        </is>
+      </c>
+      <c r="D1846" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1846" t="n">
+        <v>17</v>
+      </c>
+      <c r="F1846" t="n">
+        <v>282</v>
+      </c>
+      <c r="G1846" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1846" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1847">
+      <c r="A1847" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1847" t="inlineStr">
+        <is>
+          <t>Mr-Worldwide</t>
+        </is>
+      </c>
+      <c r="C1847" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="D1847" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1847" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1847" t="n">
+        <v>280</v>
+      </c>
+      <c r="G1847" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1847" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1848">
+      <c r="A1848" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1848" t="inlineStr">
+        <is>
+          <t>Fethinho</t>
+        </is>
+      </c>
+      <c r="C1848" t="inlineStr">
+        <is>
+          <t>Fethi</t>
+        </is>
+      </c>
+      <c r="D1848" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1848" t="n">
+        <v>19</v>
+      </c>
+      <c r="F1848" t="n">
+        <v>280</v>
+      </c>
+      <c r="G1848" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1848" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1849">
+      <c r="A1849" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1849" t="inlineStr">
+        <is>
+          <t>Ouiouiausoleil</t>
+        </is>
+      </c>
+      <c r="C1849" t="inlineStr">
+        <is>
+          <t>Ouissal</t>
+        </is>
+      </c>
+      <c r="D1849" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1849" t="n">
+        <v>20</v>
+      </c>
+      <c r="F1849" t="n">
+        <v>280</v>
+      </c>
+      <c r="G1849" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1849" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1850">
+      <c r="A1850" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1850" t="inlineStr">
+        <is>
+          <t>BOUGA#2JGXP</t>
+        </is>
+      </c>
+      <c r="C1850" t="inlineStr">
+        <is>
+          <t>BOUGA</t>
+        </is>
+      </c>
+      <c r="D1850" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1850" t="n">
+        <v>21</v>
+      </c>
+      <c r="F1850" t="n">
+        <v>260</v>
+      </c>
+      <c r="G1850" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1850" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1851">
+      <c r="A1851" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1851" t="inlineStr">
+        <is>
+          <t>Anais757817</t>
+        </is>
+      </c>
+      <c r="C1851" t="inlineStr">
+        <is>
+          <t>Anaïs</t>
+        </is>
+      </c>
+      <c r="D1851" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1851" t="n">
+        <v>22</v>
+      </c>
+      <c r="F1851" t="n">
+        <v>260</v>
+      </c>
+      <c r="G1851" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1851" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1852">
+      <c r="A1852" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1852" t="inlineStr">
+        <is>
+          <t>MatuRenard</t>
+        </is>
+      </c>
+      <c r="C1852" t="inlineStr">
+        <is>
+          <t>Mathias</t>
+        </is>
+      </c>
+      <c r="D1852" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1852" t="n">
+        <v>23</v>
+      </c>
+      <c r="F1852" t="n">
+        <v>259</v>
+      </c>
+      <c r="G1852" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1852" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1853">
+      <c r="A1853" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1853" t="inlineStr">
+        <is>
+          <t>Liliuus</t>
+        </is>
+      </c>
+      <c r="C1853" t="inlineStr">
+        <is>
+          <t>Lilia</t>
+        </is>
+      </c>
+      <c r="D1853" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1853" t="n">
+        <v>24</v>
+      </c>
+      <c r="F1853" t="n">
+        <v>259</v>
+      </c>
+      <c r="G1853" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1853" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1854">
+      <c r="A1854" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1854" t="inlineStr">
+        <is>
+          <t>Ppo28</t>
+        </is>
+      </c>
+      <c r="C1854" t="inlineStr">
+        <is>
+          <t>Prescylla</t>
+        </is>
+      </c>
+      <c r="D1854" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1854" t="n">
+        <v>25</v>
+      </c>
+      <c r="F1854" t="n">
+        <v>259</v>
+      </c>
+      <c r="G1854" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1854" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1855">
+      <c r="A1855" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1855" t="inlineStr">
+        <is>
+          <t>Gronaldo_95</t>
+        </is>
+      </c>
+      <c r="C1855" t="inlineStr">
+        <is>
+          <t>Gronaldo</t>
+        </is>
+      </c>
+      <c r="D1855" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1855" t="n">
+        <v>26</v>
+      </c>
+      <c r="F1855" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1855" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1855" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1856">
+      <c r="A1856" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1856" t="inlineStr">
+        <is>
+          <t>Devilrock95</t>
+        </is>
+      </c>
+      <c r="C1856" t="inlineStr">
+        <is>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="D1856" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1856" t="n">
+        <v>27</v>
+      </c>
+      <c r="F1856" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1856" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1856" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1857">
+      <c r="A1857" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1857" t="inlineStr">
+        <is>
+          <t>Cleem22</t>
+        </is>
+      </c>
+      <c r="C1857" t="inlineStr">
+        <is>
+          <t>Clemence</t>
+        </is>
+      </c>
+      <c r="D1857" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1857" t="n">
+        <v>28</v>
+      </c>
+      <c r="F1857" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1857" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1857" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1858">
+      <c r="A1858" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1858" t="inlineStr">
+        <is>
+          <t>catherine#5FRTD</t>
+        </is>
+      </c>
+      <c r="C1858" t="inlineStr">
+        <is>
+          <t>catherine</t>
+        </is>
+      </c>
+      <c r="D1858" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1858" t="n">
+        <v>29</v>
+      </c>
+      <c r="F1858" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1858" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1858" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1859">
+      <c r="A1859" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1859" t="inlineStr">
+        <is>
+          <t>Maruyama</t>
+        </is>
+      </c>
+      <c r="C1859" t="inlineStr">
+        <is>
+          <t>Gabrielle</t>
+        </is>
+      </c>
+      <c r="D1859" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1859" t="n">
+        <v>30</v>
+      </c>
+      <c r="F1859" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1859" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1859" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1860">
+      <c r="A1860" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1860" t="inlineStr">
+        <is>
+          <t>Leandrocp</t>
+        </is>
+      </c>
+      <c r="C1860" t="inlineStr">
+        <is>
+          <t>Leandro</t>
+        </is>
+      </c>
+      <c r="D1860" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1860" t="n">
+        <v>31</v>
+      </c>
+      <c r="F1860" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1860" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1860" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1861">
+      <c r="A1861" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1861" t="inlineStr">
+        <is>
+          <t>Marion1822</t>
+        </is>
+      </c>
+      <c r="C1861" t="inlineStr">
+        <is>
+          <t>Marion</t>
+        </is>
+      </c>
+      <c r="D1861" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1861" t="n">
+        <v>32</v>
+      </c>
+      <c r="F1861" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1861" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1861" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1862">
+      <c r="A1862" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1862" t="inlineStr">
+        <is>
+          <t>chaychaychay</t>
+        </is>
+      </c>
+      <c r="C1862" t="inlineStr">
+        <is>
+          <t>Chaymaa</t>
+        </is>
+      </c>
+      <c r="D1862" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1862" t="n">
+        <v>33</v>
+      </c>
+      <c r="F1862" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1862" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1862" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1863">
+      <c r="A1863" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1863" t="inlineStr">
+        <is>
+          <t>WIL1610</t>
+        </is>
+      </c>
+      <c r="C1863" t="inlineStr">
+        <is>
+          <t>William</t>
+        </is>
+      </c>
+      <c r="D1863" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1863" t="n">
+        <v>34</v>
+      </c>
+      <c r="F1863" t="n">
+        <v>233</v>
+      </c>
+      <c r="G1863" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1863" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1864">
+      <c r="A1864" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1864" t="inlineStr">
+        <is>
+          <t>Erwan#4G91X</t>
+        </is>
+      </c>
+      <c r="C1864" t="inlineStr">
+        <is>
+          <t>Erwan</t>
+        </is>
+      </c>
+      <c r="D1864" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1864" t="n">
+        <v>35</v>
+      </c>
+      <c r="F1864" t="n">
+        <v>219</v>
+      </c>
+      <c r="G1864" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1864" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1865">
+      <c r="A1865" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1865" t="inlineStr">
+        <is>
+          <t>GLR_PRIME</t>
+        </is>
+      </c>
+      <c r="C1865" t="inlineStr">
+        <is>
+          <t>Gabriel</t>
+        </is>
+      </c>
+      <c r="D1865" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1865" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1865" t="n">
+        <v>219</v>
+      </c>
+      <c r="G1865" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1865" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1866">
+      <c r="A1866" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1866" t="inlineStr">
+        <is>
+          <t>Exia95</t>
+        </is>
+      </c>
+      <c r="C1866" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D1866" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1866" t="n">
+        <v>37</v>
+      </c>
+      <c r="F1866" t="n">
+        <v>212</v>
+      </c>
+      <c r="G1866" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1866" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1867">
+      <c r="A1867" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1867" t="inlineStr">
+        <is>
+          <t>Matt#4B4CU</t>
+        </is>
+      </c>
+      <c r="C1867" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="D1867" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1867" t="n">
+        <v>38</v>
+      </c>
+      <c r="F1867" t="n">
+        <v>211</v>
+      </c>
+      <c r="G1867" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1867" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1868">
+      <c r="A1868" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1868" t="inlineStr">
+        <is>
+          <t>dian-bgt</t>
+        </is>
+      </c>
+      <c r="C1868" t="inlineStr">
+        <is>
+          <t>Diane</t>
+        </is>
+      </c>
+      <c r="D1868" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1868" t="n">
+        <v>39</v>
+      </c>
+      <c r="F1868" t="n">
+        <v>206</v>
+      </c>
+      <c r="G1868" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1868" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1869">
+      <c r="A1869" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1869" t="inlineStr">
+        <is>
+          <t>LilianeB</t>
+        </is>
+      </c>
+      <c r="C1869" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liliane </t>
+        </is>
+      </c>
+      <c r="D1869" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1869" t="n">
+        <v>40</v>
+      </c>
+      <c r="F1869" t="n">
+        <v>206</v>
+      </c>
+      <c r="G1869" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1869" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1870">
+      <c r="A1870" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1870" t="inlineStr">
+        <is>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="C1870" t="inlineStr">
+        <is>
+          <t>Julie</t>
+        </is>
+      </c>
+      <c r="D1870" t="inlineStr"/>
+      <c r="E1870" t="n">
+        <v>41</v>
+      </c>
+      <c r="F1870" t="n">
+        <v>206</v>
+      </c>
+      <c r="G1870" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1870" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1871">
+      <c r="A1871" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1871" t="inlineStr">
+        <is>
+          <t>Romain_JO</t>
+        </is>
+      </c>
+      <c r="C1871" t="inlineStr">
+        <is>
+          <t>Romain J</t>
+        </is>
+      </c>
+      <c r="D1871" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1871" t="n">
+        <v>42</v>
+      </c>
+      <c r="F1871" t="n">
+        <v>191</v>
+      </c>
+      <c r="G1871" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1871" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1872">
+      <c r="A1872" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1872" t="inlineStr">
+        <is>
+          <t>JeremFZ</t>
+        </is>
+      </c>
+      <c r="C1872" t="inlineStr">
+        <is>
+          <t>Jérémy</t>
+        </is>
+      </c>
+      <c r="D1872" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1872" t="n">
+        <v>43</v>
+      </c>
+      <c r="F1872" t="n">
+        <v>191</v>
+      </c>
+      <c r="G1872" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1872" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1873">
+      <c r="A1873" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1873" t="inlineStr">
+        <is>
+          <t>AudreyB225</t>
+        </is>
+      </c>
+      <c r="C1873" t="inlineStr">
+        <is>
+          <t>Audrey</t>
+        </is>
+      </c>
+      <c r="D1873" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1873" t="n">
+        <v>44</v>
+      </c>
+      <c r="F1873" t="n">
+        <v>190</v>
+      </c>
+      <c r="G1873" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1873" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1874">
+      <c r="A1874" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1874" t="inlineStr">
+        <is>
+          <t>Camss</t>
+        </is>
+      </c>
+      <c r="C1874" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D1874" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1874" t="n">
+        <v>45</v>
+      </c>
+      <c r="F1874" t="n">
+        <v>190</v>
+      </c>
+      <c r="G1874" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1874" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1875">
+      <c r="A1875" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1875" t="inlineStr">
+        <is>
+          <t>BadrLeo</t>
+        </is>
+      </c>
+      <c r="C1875" t="inlineStr">
+        <is>
+          <t>Badr Leo</t>
+        </is>
+      </c>
+      <c r="D1875" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1875" t="n">
+        <v>46</v>
+      </c>
+      <c r="F1875" t="n">
+        <v>186</v>
+      </c>
+      <c r="G1875" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1875" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1876">
+      <c r="A1876" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1876" t="inlineStr">
+        <is>
+          <t>YassineZ95</t>
+        </is>
+      </c>
+      <c r="C1876" t="inlineStr">
+        <is>
+          <t>Yassine Z</t>
+        </is>
+      </c>
+      <c r="D1876" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1876" t="n">
+        <v>47</v>
+      </c>
+      <c r="F1876" t="n">
+        <v>186</v>
+      </c>
+      <c r="G1876" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1876" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1877">
+      <c r="A1877" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1877" t="inlineStr">
+        <is>
+          <t>Ilan_260_</t>
+        </is>
+      </c>
+      <c r="C1877" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ilann </t>
+        </is>
+      </c>
+      <c r="D1877" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1877" t="n">
+        <v>48</v>
+      </c>
+      <c r="F1877" t="n">
+        <v>185</v>
+      </c>
+      <c r="G1877" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1877" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1878">
+      <c r="A1878" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1878" t="inlineStr">
+        <is>
+          <t>abihuts</t>
+        </is>
+      </c>
+      <c r="C1878" t="inlineStr">
+        <is>
+          <t>Antonio Moctezuma</t>
+        </is>
+      </c>
+      <c r="D1878" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1878" t="n">
+        <v>49</v>
+      </c>
+      <c r="F1878" t="n">
+        <v>172</v>
+      </c>
+      <c r="G1878" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1878" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1879">
+      <c r="A1879" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1879" t="inlineStr">
+        <is>
+          <t>Chadia__</t>
+        </is>
+      </c>
+      <c r="C1879" t="inlineStr">
+        <is>
+          <t>Chadia</t>
+        </is>
+      </c>
+      <c r="D1879" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1879" t="n">
+        <v>50</v>
+      </c>
+      <c r="F1879" t="n">
+        <v>170</v>
+      </c>
+      <c r="G1879" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1879" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1880">
+      <c r="A1880" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1880" t="inlineStr">
+        <is>
+          <t>GOAT#UE2WM8M9</t>
+        </is>
+      </c>
+      <c r="C1880" t="inlineStr">
+        <is>
+          <t>Marilena</t>
+        </is>
+      </c>
+      <c r="D1880" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1880" t="n">
+        <v>51</v>
+      </c>
+      <c r="F1880" t="n">
+        <v>165</v>
+      </c>
+      <c r="G1880" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1880" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1881">
+      <c r="A1881" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1881" t="inlineStr">
+        <is>
+          <t>Ceciledp</t>
+        </is>
+      </c>
+      <c r="C1881" t="inlineStr">
+        <is>
+          <t>Cécile</t>
+        </is>
+      </c>
+      <c r="D1881" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1881" t="n">
+        <v>52</v>
+      </c>
+      <c r="F1881" t="n">
+        <v>145</v>
+      </c>
+      <c r="G1881" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1881" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1882">
+      <c r="A1882" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1882" t="inlineStr">
+        <is>
+          <t>Fuzo697</t>
+        </is>
+      </c>
+      <c r="C1882" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D1882" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1882" t="n">
+        <v>53</v>
+      </c>
+      <c r="F1882" t="n">
+        <v>145</v>
+      </c>
+      <c r="G1882" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1882" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1883">
+      <c r="A1883" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1883" t="inlineStr">
+        <is>
+          <t>Yebri</t>
+        </is>
+      </c>
+      <c r="C1883" t="inlineStr">
+        <is>
+          <t>Brieuc</t>
+        </is>
+      </c>
+      <c r="D1883" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1883" t="n">
+        <v>54</v>
+      </c>
+      <c r="F1883" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1883" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1883" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1884">
+      <c r="A1884" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1884" t="inlineStr">
+        <is>
+          <t>Leo_durable</t>
+        </is>
+      </c>
+      <c r="C1884" t="inlineStr">
+        <is>
+          <t>Leo</t>
+        </is>
+      </c>
+      <c r="D1884" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1884" t="n">
+        <v>55</v>
+      </c>
+      <c r="F1884" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1884" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1884" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1885">
+      <c r="A1885" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1885" t="inlineStr">
+        <is>
+          <t>EmyEnzo</t>
+        </is>
+      </c>
+      <c r="C1885" t="inlineStr">
+        <is>
+          <t>Emilie</t>
+        </is>
+      </c>
+      <c r="D1885" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1885" t="n">
+        <v>56</v>
+      </c>
+      <c r="F1885" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1885" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1885" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1886">
+      <c r="A1886" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1886" t="inlineStr">
+        <is>
+          <t>Priscilla#4LCAF</t>
+        </is>
+      </c>
+      <c r="C1886" t="inlineStr">
+        <is>
+          <t>Priscilla</t>
+        </is>
+      </c>
+      <c r="D1886" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1886" t="n">
+        <v>57</v>
+      </c>
+      <c r="F1886" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1886" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1886" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1887">
+      <c r="A1887" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1887" t="inlineStr">
+        <is>
+          <t>Pipou931</t>
+        </is>
+      </c>
+      <c r="C1887" t="inlineStr">
+        <is>
+          <t>Juliie</t>
+        </is>
+      </c>
+      <c r="D1887" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1887" t="n">
+        <v>58</v>
+      </c>
+      <c r="F1887" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1887" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1887" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1888">
+      <c r="A1888" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1888" t="inlineStr">
+        <is>
+          <t>Farah_One</t>
+        </is>
+      </c>
+      <c r="C1888" t="inlineStr">
+        <is>
+          <t>Farah</t>
+        </is>
+      </c>
+      <c r="D1888" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1888" t="n">
+        <v>59</v>
+      </c>
+      <c r="F1888" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1888" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1888" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1889">
+      <c r="A1889" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1889" t="inlineStr">
+        <is>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="C1889" t="inlineStr">
+        <is>
+          <t>François</t>
+        </is>
+      </c>
+      <c r="D1889" t="inlineStr"/>
+      <c r="E1889" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1889" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1889" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1889" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1890">
+      <c r="A1890" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1890" t="inlineStr">
+        <is>
+          <t>Seesee</t>
+        </is>
+      </c>
+      <c r="C1890" t="inlineStr">
+        <is>
+          <t>Selver</t>
+        </is>
+      </c>
+      <c r="D1890" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1890" t="n">
+        <v>61</v>
+      </c>
+      <c r="F1890" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1890" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1890" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1891">
+      <c r="A1891" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1891" t="inlineStr">
+        <is>
+          <t>lenaaik</t>
+        </is>
+      </c>
+      <c r="C1891" t="inlineStr">
+        <is>
+          <t>Lénaïk</t>
+        </is>
+      </c>
+      <c r="D1891" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1891" t="n">
+        <v>62</v>
+      </c>
+      <c r="F1891" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1891" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1891" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1892">
+      <c r="A1892" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1892" t="inlineStr">
+        <is>
+          <t>C4M</t>
+        </is>
+      </c>
+      <c r="C1892" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D1892" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1892" t="n">
+        <v>63</v>
+      </c>
+      <c r="F1892" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1892" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1892" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1893">
+      <c r="A1893" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1893" t="inlineStr">
+        <is>
+          <t>Rosa_1009</t>
+        </is>
+      </c>
+      <c r="C1893" t="inlineStr">
+        <is>
+          <t>Rosaline</t>
+        </is>
+      </c>
+      <c r="D1893" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1893" t="n">
+        <v>64</v>
+      </c>
+      <c r="F1893" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1893" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1893" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1894">
+      <c r="A1894" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1894" t="inlineStr">
+        <is>
+          <t>Elisewiss</t>
+        </is>
+      </c>
+      <c r="C1894" t="inlineStr">
+        <is>
+          <t>Elise</t>
+        </is>
+      </c>
+      <c r="D1894" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1894" t="n">
+        <v>65</v>
+      </c>
+      <c r="F1894" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1894" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1894" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1895">
+      <c r="A1895" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1895" t="inlineStr">
+        <is>
+          <t>Soraya-Y</t>
+        </is>
+      </c>
+      <c r="C1895" t="inlineStr">
+        <is>
+          <t>Soraya</t>
+        </is>
+      </c>
+      <c r="D1895" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1895" t="n">
+        <v>66</v>
+      </c>
+      <c r="F1895" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1895" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1895" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1896">
+      <c r="A1896" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1896" t="inlineStr">
+        <is>
+          <t>1993ahm</t>
+        </is>
+      </c>
+      <c r="C1896" t="inlineStr">
+        <is>
+          <t>Ahmed</t>
+        </is>
+      </c>
+      <c r="D1896" t="inlineStr"/>
+      <c r="E1896" t="n">
+        <v>67</v>
+      </c>
+      <c r="F1896" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1896" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1896" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1897">
+      <c r="A1897" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1897" t="inlineStr">
+        <is>
+          <t>Timy</t>
+        </is>
+      </c>
+      <c r="C1897" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="D1897" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1897" t="n">
+        <v>68</v>
+      </c>
+      <c r="F1897" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1897" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1897" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1898">
+      <c r="A1898" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1898" t="inlineStr">
+        <is>
+          <t>JEVAISGAGNER10</t>
+        </is>
+      </c>
+      <c r="C1898" t="inlineStr">
+        <is>
+          <t>Xavier</t>
+        </is>
+      </c>
+      <c r="D1898" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1898" t="n">
+        <v>69</v>
+      </c>
+      <c r="F1898" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1898" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1898" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1899">
+      <c r="A1899" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1899" t="inlineStr">
+        <is>
+          <t>HamzaG</t>
+        </is>
+      </c>
+      <c r="C1899" t="inlineStr">
+        <is>
+          <t>Hamza</t>
+        </is>
+      </c>
+      <c r="D1899" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1899" t="n">
+        <v>70</v>
+      </c>
+      <c r="F1899" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1899" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1899" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1900">
+      <c r="A1900" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1900" t="inlineStr">
+        <is>
+          <t>LeaBrd</t>
+        </is>
+      </c>
+      <c r="C1900" t="inlineStr">
+        <is>
+          <t>Léa</t>
+        </is>
+      </c>
+      <c r="D1900" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1900" t="n">
+        <v>71</v>
+      </c>
+      <c r="F1900" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1900" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1900" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1901">
+      <c r="A1901" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1901" t="inlineStr">
+        <is>
+          <t>davidd23</t>
+        </is>
+      </c>
+      <c r="C1901" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D1901" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1901" t="n">
+        <v>72</v>
+      </c>
+      <c r="F1901" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1901" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1901" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1902">
+      <c r="A1902" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1902" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="C1902" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="D1902" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1902" t="n">
+        <v>73</v>
+      </c>
+      <c r="F1902" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1902" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1902" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1903">
+      <c r="A1903" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1903" t="inlineStr">
+        <is>
+          <t>Kolas</t>
+        </is>
+      </c>
+      <c r="C1903" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D1903" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1903" t="n">
+        <v>74</v>
+      </c>
+      <c r="F1903" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1903" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1903" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1904">
+      <c r="A1904" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1904" t="inlineStr">
+        <is>
+          <t>Laetice2020</t>
+        </is>
+      </c>
+      <c r="C1904" t="inlineStr">
+        <is>
+          <t>Laetitia</t>
+        </is>
+      </c>
+      <c r="D1904" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1904" t="n">
+        <v>75</v>
+      </c>
+      <c r="F1904" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1904" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1904" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1905">
+      <c r="A1905" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1905" t="inlineStr">
+        <is>
+          <t>Emilay</t>
+        </is>
+      </c>
+      <c r="C1905" t="inlineStr">
+        <is>
+          <t>Émilie</t>
+        </is>
+      </c>
+      <c r="D1905" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1905" t="n">
+        <v>76</v>
+      </c>
+      <c r="F1905" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1905" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1905" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1906">
+      <c r="A1906" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1906" t="inlineStr">
+        <is>
+          <t>Lyzone</t>
+        </is>
+      </c>
+      <c r="C1906" t="inlineStr">
+        <is>
+          <t>Lison</t>
+        </is>
+      </c>
+      <c r="D1906" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1906" t="n">
+        <v>77</v>
+      </c>
+      <c r="F1906" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1906" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1906" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1907">
+      <c r="A1907" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1907" t="inlineStr">
+        <is>
+          <t>Melissagzb</t>
+        </is>
+      </c>
+      <c r="C1907" t="inlineStr">
+        <is>
+          <t>Melissa</t>
+        </is>
+      </c>
+      <c r="D1907" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1907" t="n">
+        <v>78</v>
+      </c>
+      <c r="F1907" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1907" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1907" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1908">
+      <c r="A1908" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1908" t="inlineStr">
+        <is>
+          <t>Marie__92</t>
+        </is>
+      </c>
+      <c r="C1908" t="inlineStr">
+        <is>
+          <t>Marie</t>
+        </is>
+      </c>
+      <c r="D1908" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1908" t="n">
+        <v>79</v>
+      </c>
+      <c r="F1908" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1908" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1908" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1909">
+      <c r="A1909" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1909" t="inlineStr">
+        <is>
+          <t>K_Marp</t>
+        </is>
+      </c>
+      <c r="C1909" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
+      <c r="D1909" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1909" t="n">
+        <v>80</v>
+      </c>
+      <c r="F1909" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1909" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1909" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1910">
+      <c r="A1910" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1910" t="inlineStr">
+        <is>
+          <t>Cindie_JJA</t>
+        </is>
+      </c>
+      <c r="C1910" t="inlineStr">
+        <is>
+          <t>Cindie</t>
+        </is>
+      </c>
+      <c r="D1910" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1910" t="n">
+        <v>81</v>
+      </c>
+      <c r="F1910" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1910" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1910" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1911">
+      <c r="A1911" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1911" t="inlineStr">
+        <is>
+          <t>JKInternational</t>
+        </is>
+      </c>
+      <c r="C1911" t="inlineStr">
+        <is>
+          <t>Joachim</t>
+        </is>
+      </c>
+      <c r="D1911" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1911" t="n">
+        <v>82</v>
+      </c>
+      <c r="F1911" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1911" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1911" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1912">
+      <c r="A1912" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1912" t="inlineStr">
+        <is>
+          <t>GOAT#UE4U8KA6</t>
+        </is>
+      </c>
+      <c r="C1912" t="inlineStr">
+        <is>
+          <t>Jean Baptiste</t>
+        </is>
+      </c>
+      <c r="D1912" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1912" t="n">
+        <v>83</v>
+      </c>
+      <c r="F1912" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1912" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1912" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1913">
+      <c r="A1913" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1913" t="inlineStr">
+        <is>
+          <t>goat#AD6GS</t>
+        </is>
+      </c>
+      <c r="C1913" t="inlineStr">
+        <is>
+          <t>goat</t>
+        </is>
+      </c>
+      <c r="D1913" t="inlineStr"/>
+      <c r="E1913" t="n">
+        <v>84</v>
+      </c>
+      <c r="F1913" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1913" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1913" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1914">
+      <c r="A1914" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1914" t="inlineStr">
+        <is>
+          <t>Camillewbl</t>
+        </is>
+      </c>
+      <c r="C1914" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D1914" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1914" t="n">
+        <v>85</v>
+      </c>
+      <c r="F1914" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1914" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1914" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1915">
+      <c r="A1915" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1915" t="inlineStr">
+        <is>
+          <t>Emma_Noel</t>
+        </is>
+      </c>
+      <c r="C1915" t="inlineStr">
+        <is>
+          <t>Emma</t>
+        </is>
+      </c>
+      <c r="D1915" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1915" t="n">
+        <v>86</v>
+      </c>
+      <c r="F1915" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1915" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1915" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1916">
+      <c r="A1916" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1916" t="inlineStr">
+        <is>
+          <t>RBTL</t>
+        </is>
+      </c>
+      <c r="C1916" t="inlineStr">
+        <is>
+          <t>lea</t>
+        </is>
+      </c>
+      <c r="D1916" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1916" t="n">
+        <v>87</v>
+      </c>
+      <c r="F1916" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1916" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1916" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1917">
+      <c r="A1917" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1917" t="inlineStr">
+        <is>
+          <t>A-MOE</t>
+        </is>
+      </c>
+      <c r="C1917" t="inlineStr">
+        <is>
+          <t>Françoise</t>
+        </is>
+      </c>
+      <c r="D1917" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1917" t="n">
+        <v>88</v>
+      </c>
+      <c r="F1917" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1917" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1917" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1918">
+      <c r="A1918" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1918" t="inlineStr">
+        <is>
+          <t>Davido#4BZ54</t>
+        </is>
+      </c>
+      <c r="C1918" t="inlineStr">
+        <is>
+          <t>Davido</t>
+        </is>
+      </c>
+      <c r="D1918" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1918" t="n">
+        <v>89</v>
+      </c>
+      <c r="F1918" t="n">
+        <v>96</v>
+      </c>
+      <c r="G1918" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1918" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1919">
+      <c r="A1919" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1919" t="inlineStr">
+        <is>
+          <t>BrickXVI</t>
+        </is>
+      </c>
+      <c r="C1919" t="inlineStr">
+        <is>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="D1919" t="inlineStr"/>
+      <c r="E1919" t="n">
+        <v>90</v>
+      </c>
+      <c r="F1919" t="n">
+        <v>74</v>
+      </c>
+      <c r="G1919" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1919" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1920">
+      <c r="A1920" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1920" t="inlineStr">
+        <is>
+          <t>Taylor2901</t>
+        </is>
+      </c>
+      <c r="C1920" t="inlineStr">
+        <is>
+          <t>ousmane</t>
+        </is>
+      </c>
+      <c r="D1920" t="inlineStr"/>
+      <c r="E1920" t="n">
+        <v>91</v>
+      </c>
+      <c r="F1920" t="n">
+        <v>74</v>
+      </c>
+      <c r="G1920" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1920" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1921">
+      <c r="A1921" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1921" t="inlineStr">
+        <is>
+          <t>Ze_GOAT</t>
+        </is>
+      </c>
+      <c r="C1921" t="inlineStr">
+        <is>
+          <t>Yasser</t>
+        </is>
+      </c>
+      <c r="D1921" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1921" t="n">
+        <v>92</v>
+      </c>
+      <c r="F1921" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1921" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1921" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1922">
+      <c r="A1922" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1922" t="inlineStr">
+        <is>
+          <t>Krol#4R8XC</t>
+        </is>
+      </c>
+      <c r="C1922" t="inlineStr">
+        <is>
+          <t>Krol</t>
+        </is>
+      </c>
+      <c r="D1922" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1922" t="n">
+        <v>93</v>
+      </c>
+      <c r="F1922" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1922" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1922" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1923">
+      <c r="A1923" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1923" t="inlineStr">
+        <is>
+          <t>PacoSarra</t>
+        </is>
+      </c>
+      <c r="C1923" t="inlineStr">
+        <is>
+          <t>Ibra</t>
+        </is>
+      </c>
+      <c r="D1923" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1923" t="n">
+        <v>94</v>
+      </c>
+      <c r="F1923" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1923" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1923" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1924">
+      <c r="A1924" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1924" t="inlineStr">
+        <is>
+          <t>Droit_au_but7723</t>
+        </is>
+      </c>
+      <c r="C1924" t="inlineStr">
+        <is>
+          <t>Calixthe</t>
+        </is>
+      </c>
+      <c r="D1924" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1924" t="n">
+        <v>95</v>
+      </c>
+      <c r="F1924" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1924" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1924" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1925">
+      <c r="A1925" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1925" t="inlineStr">
+        <is>
+          <t>Ambrepic</t>
+        </is>
+      </c>
+      <c r="C1925" t="inlineStr">
+        <is>
+          <t>Ambre</t>
+        </is>
+      </c>
+      <c r="D1925" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1925" t="n">
+        <v>96</v>
+      </c>
+      <c r="F1925" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1925" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1925" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1926">
+      <c r="A1926" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1926" t="inlineStr">
+        <is>
+          <t>PavelMel</t>
+        </is>
+      </c>
+      <c r="C1926" t="inlineStr">
+        <is>
+          <t>Mélissa</t>
+        </is>
+      </c>
+      <c r="D1926" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1926" t="n">
+        <v>97</v>
+      </c>
+      <c r="F1926" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1926" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1926" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1927">
+      <c r="A1927" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1927" t="inlineStr">
+        <is>
+          <t>Mylene-Jnt</t>
+        </is>
+      </c>
+      <c r="C1927" t="inlineStr">
+        <is>
+          <t>Mylène</t>
+        </is>
+      </c>
+      <c r="D1927" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1927" t="n">
+        <v>98</v>
+      </c>
+      <c r="F1927" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1927" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1927" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1928">
+      <c r="A1928" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1928" t="inlineStr">
+        <is>
+          <t>Teddbear</t>
+        </is>
+      </c>
+      <c r="C1928" t="inlineStr">
+        <is>
+          <t>Tedy</t>
+        </is>
+      </c>
+      <c r="D1928" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1928" t="n">
+        <v>99</v>
+      </c>
+      <c r="F1928" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1928" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1928" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1929">
+      <c r="A1929" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1929" t="inlineStr">
+        <is>
+          <t>SabC1</t>
+        </is>
+      </c>
+      <c r="C1929" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="D1929" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1929" t="n">
+        <v>100</v>
+      </c>
+      <c r="F1929" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1929" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1929" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1930">
+      <c r="A1930" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1930" t="inlineStr">
+        <is>
+          <t>KIKS999</t>
+        </is>
+      </c>
+      <c r="C1930" t="inlineStr">
+        <is>
+          <t>Killian</t>
+        </is>
+      </c>
+      <c r="D1930" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1930" t="n">
+        <v>101</v>
+      </c>
+      <c r="F1930" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1930" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1930" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1931">
+      <c r="A1931" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1931" t="inlineStr">
+        <is>
+          <t>MxKnight</t>
+        </is>
+      </c>
+      <c r="C1931" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D1931" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1931" t="n">
+        <v>102</v>
+      </c>
+      <c r="F1931" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1931" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1931" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1932">
+      <c r="A1932" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1932" t="inlineStr">
+        <is>
+          <t>RomainLect</t>
+        </is>
+      </c>
+      <c r="C1932" t="inlineStr">
+        <is>
+          <t>romain</t>
+        </is>
+      </c>
+      <c r="D1932" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1932" t="n">
+        <v>103</v>
+      </c>
+      <c r="F1932" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1932" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1932" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1933">
+      <c r="A1933" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1933" t="inlineStr">
+        <is>
+          <t>SamSamH8</t>
+        </is>
+      </c>
+      <c r="C1933" t="inlineStr">
+        <is>
+          <t>Samia</t>
+        </is>
+      </c>
+      <c r="D1933" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1933" t="n">
+        <v>104</v>
+      </c>
+      <c r="F1933" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1933" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1933" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1934">
+      <c r="A1934" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1934" t="inlineStr">
+        <is>
+          <t>Daviddesco1</t>
+        </is>
+      </c>
+      <c r="C1934" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D1934" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1934" t="n">
+        <v>105</v>
+      </c>
+      <c r="F1934" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1934" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1934" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1935">
+      <c r="A1935" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1935" t="inlineStr">
+        <is>
+          <t>Sab_M45</t>
+        </is>
+      </c>
+      <c r="C1935" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="D1935" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1935" t="n">
+        <v>106</v>
+      </c>
+      <c r="F1935" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1935" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1935" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1936">
+      <c r="A1936" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1936" t="inlineStr">
+        <is>
+          <t>Valentine___</t>
+        </is>
+      </c>
+      <c r="C1936" t="inlineStr">
+        <is>
+          <t>Valentine</t>
+        </is>
+      </c>
+      <c r="D1936" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1936" t="n">
+        <v>107</v>
+      </c>
+      <c r="F1936" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1936" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1936" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1937">
+      <c r="A1937" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1937" t="inlineStr">
+        <is>
+          <t>PANENKANY</t>
+        </is>
+      </c>
+      <c r="C1937" t="inlineStr">
+        <is>
+          <t>Damien</t>
+        </is>
+      </c>
+      <c r="D1937" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1937" t="n">
+        <v>108</v>
+      </c>
+      <c r="F1937" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1937" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1937" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1938">
+      <c r="A1938" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1938" t="inlineStr">
+        <is>
+          <t>MT35T</t>
+        </is>
+      </c>
+      <c r="C1938" t="inlineStr">
+        <is>
+          <t>Mathilde</t>
+        </is>
+      </c>
+      <c r="D1938" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1938" t="n">
+        <v>109</v>
+      </c>
+      <c r="F1938" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1938" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1938" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historique_joueurs.xlsx
+++ b/historique_joueurs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1938"/>
+  <dimension ref="A1:H2047"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64832,6 +64832,3688 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1939">
+      <c r="A1939" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1939" t="inlineStr">
+        <is>
+          <t>Filipinho95</t>
+        </is>
+      </c>
+      <c r="C1939" t="inlineStr">
+        <is>
+          <t>Filipe</t>
+        </is>
+      </c>
+      <c r="D1939" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1939" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1939" t="n">
+        <v>410</v>
+      </c>
+      <c r="G1939" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1939" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1940">
+      <c r="A1940" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1940" t="inlineStr">
+        <is>
+          <t>Ninaaaa</t>
+        </is>
+      </c>
+      <c r="C1940" t="inlineStr">
+        <is>
+          <t>Nina</t>
+        </is>
+      </c>
+      <c r="D1940" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1940" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1940" t="n">
+        <v>400</v>
+      </c>
+      <c r="G1940" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1940" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1941">
+      <c r="A1941" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1941" t="inlineStr">
+        <is>
+          <t>MargauxCtln</t>
+        </is>
+      </c>
+      <c r="C1941" t="inlineStr">
+        <is>
+          <t>Margaux</t>
+        </is>
+      </c>
+      <c r="D1941" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1941" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1941" t="n">
+        <v>376</v>
+      </c>
+      <c r="G1941" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1941" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1942">
+      <c r="A1942" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1942" t="inlineStr">
+        <is>
+          <t>Mamad_Shelter</t>
+        </is>
+      </c>
+      <c r="C1942" t="inlineStr">
+        <is>
+          <t>Mamadou</t>
+        </is>
+      </c>
+      <c r="D1942" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1942" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1942" t="n">
+        <v>376</v>
+      </c>
+      <c r="G1942" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1942" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1943">
+      <c r="A1943" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1943" t="inlineStr">
+        <is>
+          <t>MagicMath</t>
+        </is>
+      </c>
+      <c r="C1943" t="inlineStr">
+        <is>
+          <t>Mathieu</t>
+        </is>
+      </c>
+      <c r="D1943" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1943" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1943" t="n">
+        <v>376</v>
+      </c>
+      <c r="G1943" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1943" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1944">
+      <c r="A1944" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1944" t="inlineStr">
+        <is>
+          <t>WalidSiuuuuu</t>
+        </is>
+      </c>
+      <c r="C1944" t="inlineStr">
+        <is>
+          <t>Walid</t>
+        </is>
+      </c>
+      <c r="D1944" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1944" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1944" t="n">
+        <v>356</v>
+      </c>
+      <c r="G1944" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1944" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1945">
+      <c r="A1945" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1945" t="inlineStr">
+        <is>
+          <t>DJOSWA</t>
+        </is>
+      </c>
+      <c r="C1945" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oswaina </t>
+        </is>
+      </c>
+      <c r="D1945" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1945" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1945" t="n">
+        <v>356</v>
+      </c>
+      <c r="G1945" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1945" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1946">
+      <c r="A1946" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1946" t="inlineStr">
+        <is>
+          <t>SID-F-ANDRE</t>
+        </is>
+      </c>
+      <c r="C1946" t="inlineStr">
+        <is>
+          <t>Denis</t>
+        </is>
+      </c>
+      <c r="D1946" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1946" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1946" t="n">
+        <v>355</v>
+      </c>
+      <c r="G1946" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1946" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1947">
+      <c r="A1947" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1947" t="inlineStr">
+        <is>
+          <t>ChrisKr1Deg1</t>
+        </is>
+      </c>
+      <c r="C1947" t="inlineStr">
+        <is>
+          <t>christophe</t>
+        </is>
+      </c>
+      <c r="D1947" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1947" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1947" t="n">
+        <v>323</v>
+      </c>
+      <c r="G1947" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1947" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1948">
+      <c r="A1948" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1948" t="inlineStr">
+        <is>
+          <t>Coucoucassecou</t>
+        </is>
+      </c>
+      <c r="C1948" t="inlineStr">
+        <is>
+          <t>Brayen</t>
+        </is>
+      </c>
+      <c r="D1948" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1948" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1948" t="n">
+        <v>322</v>
+      </c>
+      <c r="G1948" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1948" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1949">
+      <c r="A1949" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1949" t="inlineStr">
+        <is>
+          <t>Paulasipi1998</t>
+        </is>
+      </c>
+      <c r="C1949" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="D1949" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1949" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1949" t="n">
+        <v>322</v>
+      </c>
+      <c r="G1949" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1949" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1950">
+      <c r="A1950" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1950" t="inlineStr">
+        <is>
+          <t>Panaff</t>
+        </is>
+      </c>
+      <c r="C1950" t="inlineStr">
+        <is>
+          <t>Panaf</t>
+        </is>
+      </c>
+      <c r="D1950" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1950" t="n">
+        <v>12</v>
+      </c>
+      <c r="F1950" t="n">
+        <v>315</v>
+      </c>
+      <c r="G1950" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1950" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1951">
+      <c r="A1951" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1951" t="inlineStr">
+        <is>
+          <t>Stephbreton</t>
+        </is>
+      </c>
+      <c r="C1951" t="inlineStr">
+        <is>
+          <t>STEPHANE</t>
+        </is>
+      </c>
+      <c r="D1951" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1951" t="n">
+        <v>13</v>
+      </c>
+      <c r="F1951" t="n">
+        <v>307</v>
+      </c>
+      <c r="G1951" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1951" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1952">
+      <c r="A1952" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1952" t="inlineStr">
+        <is>
+          <t>Kaliced</t>
+        </is>
+      </c>
+      <c r="C1952" t="inlineStr">
+        <is>
+          <t>Kalice</t>
+        </is>
+      </c>
+      <c r="D1952" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1952" t="n">
+        <v>14</v>
+      </c>
+      <c r="F1952" t="n">
+        <v>302</v>
+      </c>
+      <c r="G1952" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1952" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1953">
+      <c r="A1953" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1953" t="inlineStr">
+        <is>
+          <t>MyriamAmr</t>
+        </is>
+      </c>
+      <c r="C1953" t="inlineStr">
+        <is>
+          <t>Myriam</t>
+        </is>
+      </c>
+      <c r="D1953" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1953" t="n">
+        <v>15</v>
+      </c>
+      <c r="F1953" t="n">
+        <v>298</v>
+      </c>
+      <c r="G1953" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1953" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1954">
+      <c r="A1954" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1954" t="inlineStr">
+        <is>
+          <t>Nonito20</t>
+        </is>
+      </c>
+      <c r="C1954" t="inlineStr">
+        <is>
+          <t>Arnaud</t>
+        </is>
+      </c>
+      <c r="D1954" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1954" t="n">
+        <v>16</v>
+      </c>
+      <c r="F1954" t="n">
+        <v>284</v>
+      </c>
+      <c r="G1954" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1954" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1955">
+      <c r="A1955" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1955" t="inlineStr">
+        <is>
+          <t>FRHTCTD10</t>
+        </is>
+      </c>
+      <c r="C1955" t="inlineStr">
+        <is>
+          <t>Candice</t>
+        </is>
+      </c>
+      <c r="D1955" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1955" t="n">
+        <v>17</v>
+      </c>
+      <c r="F1955" t="n">
+        <v>282</v>
+      </c>
+      <c r="G1955" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1955" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1956">
+      <c r="A1956" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1956" t="inlineStr">
+        <is>
+          <t>Mr-Worldwide</t>
+        </is>
+      </c>
+      <c r="C1956" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="D1956" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1956" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1956" t="n">
+        <v>280</v>
+      </c>
+      <c r="G1956" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1956" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1957">
+      <c r="A1957" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1957" t="inlineStr">
+        <is>
+          <t>Fethinho</t>
+        </is>
+      </c>
+      <c r="C1957" t="inlineStr">
+        <is>
+          <t>Fethi</t>
+        </is>
+      </c>
+      <c r="D1957" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1957" t="n">
+        <v>19</v>
+      </c>
+      <c r="F1957" t="n">
+        <v>280</v>
+      </c>
+      <c r="G1957" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1957" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1958">
+      <c r="A1958" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1958" t="inlineStr">
+        <is>
+          <t>Ouiouiausoleil</t>
+        </is>
+      </c>
+      <c r="C1958" t="inlineStr">
+        <is>
+          <t>Ouissal</t>
+        </is>
+      </c>
+      <c r="D1958" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1958" t="n">
+        <v>20</v>
+      </c>
+      <c r="F1958" t="n">
+        <v>280</v>
+      </c>
+      <c r="G1958" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1958" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1959">
+      <c r="A1959" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1959" t="inlineStr">
+        <is>
+          <t>BOUGA#2JGXP</t>
+        </is>
+      </c>
+      <c r="C1959" t="inlineStr">
+        <is>
+          <t>BOUGA</t>
+        </is>
+      </c>
+      <c r="D1959" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1959" t="n">
+        <v>21</v>
+      </c>
+      <c r="F1959" t="n">
+        <v>260</v>
+      </c>
+      <c r="G1959" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1959" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1960">
+      <c r="A1960" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1960" t="inlineStr">
+        <is>
+          <t>Anais757817</t>
+        </is>
+      </c>
+      <c r="C1960" t="inlineStr">
+        <is>
+          <t>Anaïs</t>
+        </is>
+      </c>
+      <c r="D1960" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1960" t="n">
+        <v>22</v>
+      </c>
+      <c r="F1960" t="n">
+        <v>260</v>
+      </c>
+      <c r="G1960" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1960" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1961">
+      <c r="A1961" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1961" t="inlineStr">
+        <is>
+          <t>MatuRenard</t>
+        </is>
+      </c>
+      <c r="C1961" t="inlineStr">
+        <is>
+          <t>Mathias</t>
+        </is>
+      </c>
+      <c r="D1961" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1961" t="n">
+        <v>23</v>
+      </c>
+      <c r="F1961" t="n">
+        <v>259</v>
+      </c>
+      <c r="G1961" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1961" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1962">
+      <c r="A1962" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1962" t="inlineStr">
+        <is>
+          <t>Liliuus</t>
+        </is>
+      </c>
+      <c r="C1962" t="inlineStr">
+        <is>
+          <t>Lilia</t>
+        </is>
+      </c>
+      <c r="D1962" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1962" t="n">
+        <v>24</v>
+      </c>
+      <c r="F1962" t="n">
+        <v>259</v>
+      </c>
+      <c r="G1962" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1962" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1963">
+      <c r="A1963" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1963" t="inlineStr">
+        <is>
+          <t>Ppo28</t>
+        </is>
+      </c>
+      <c r="C1963" t="inlineStr">
+        <is>
+          <t>Prescylla</t>
+        </is>
+      </c>
+      <c r="D1963" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1963" t="n">
+        <v>25</v>
+      </c>
+      <c r="F1963" t="n">
+        <v>259</v>
+      </c>
+      <c r="G1963" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1963" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1964">
+      <c r="A1964" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1964" t="inlineStr">
+        <is>
+          <t>Gronaldo_95</t>
+        </is>
+      </c>
+      <c r="C1964" t="inlineStr">
+        <is>
+          <t>Gronaldo</t>
+        </is>
+      </c>
+      <c r="D1964" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1964" t="n">
+        <v>26</v>
+      </c>
+      <c r="F1964" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1964" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1964" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1965">
+      <c r="A1965" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1965" t="inlineStr">
+        <is>
+          <t>Devilrock95</t>
+        </is>
+      </c>
+      <c r="C1965" t="inlineStr">
+        <is>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="D1965" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1965" t="n">
+        <v>27</v>
+      </c>
+      <c r="F1965" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1965" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1965" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1966">
+      <c r="A1966" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1966" t="inlineStr">
+        <is>
+          <t>Cleem22</t>
+        </is>
+      </c>
+      <c r="C1966" t="inlineStr">
+        <is>
+          <t>Clemence</t>
+        </is>
+      </c>
+      <c r="D1966" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1966" t="n">
+        <v>28</v>
+      </c>
+      <c r="F1966" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1966" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1966" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1967">
+      <c r="A1967" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1967" t="inlineStr">
+        <is>
+          <t>catherine#5FRTD</t>
+        </is>
+      </c>
+      <c r="C1967" t="inlineStr">
+        <is>
+          <t>catherine</t>
+        </is>
+      </c>
+      <c r="D1967" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1967" t="n">
+        <v>29</v>
+      </c>
+      <c r="F1967" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1967" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1967" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1968">
+      <c r="A1968" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1968" t="inlineStr">
+        <is>
+          <t>Maruyama</t>
+        </is>
+      </c>
+      <c r="C1968" t="inlineStr">
+        <is>
+          <t>Gabrielle</t>
+        </is>
+      </c>
+      <c r="D1968" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1968" t="n">
+        <v>30</v>
+      </c>
+      <c r="F1968" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1968" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1968" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1969">
+      <c r="A1969" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1969" t="inlineStr">
+        <is>
+          <t>Leandrocp</t>
+        </is>
+      </c>
+      <c r="C1969" t="inlineStr">
+        <is>
+          <t>Leandro</t>
+        </is>
+      </c>
+      <c r="D1969" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1969" t="n">
+        <v>31</v>
+      </c>
+      <c r="F1969" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1969" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1969" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1970">
+      <c r="A1970" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1970" t="inlineStr">
+        <is>
+          <t>Marion1822</t>
+        </is>
+      </c>
+      <c r="C1970" t="inlineStr">
+        <is>
+          <t>Marion</t>
+        </is>
+      </c>
+      <c r="D1970" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1970" t="n">
+        <v>32</v>
+      </c>
+      <c r="F1970" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1970" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1970" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1971">
+      <c r="A1971" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1971" t="inlineStr">
+        <is>
+          <t>chaychaychay</t>
+        </is>
+      </c>
+      <c r="C1971" t="inlineStr">
+        <is>
+          <t>Chaymaa</t>
+        </is>
+      </c>
+      <c r="D1971" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1971" t="n">
+        <v>33</v>
+      </c>
+      <c r="F1971" t="n">
+        <v>239</v>
+      </c>
+      <c r="G1971" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1971" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1972">
+      <c r="A1972" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1972" t="inlineStr">
+        <is>
+          <t>WIL1610</t>
+        </is>
+      </c>
+      <c r="C1972" t="inlineStr">
+        <is>
+          <t>William</t>
+        </is>
+      </c>
+      <c r="D1972" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1972" t="n">
+        <v>34</v>
+      </c>
+      <c r="F1972" t="n">
+        <v>233</v>
+      </c>
+      <c r="G1972" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1972" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1973">
+      <c r="A1973" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1973" t="inlineStr">
+        <is>
+          <t>Erwan#4G91X</t>
+        </is>
+      </c>
+      <c r="C1973" t="inlineStr">
+        <is>
+          <t>Erwan</t>
+        </is>
+      </c>
+      <c r="D1973" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1973" t="n">
+        <v>35</v>
+      </c>
+      <c r="F1973" t="n">
+        <v>219</v>
+      </c>
+      <c r="G1973" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1973" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1974">
+      <c r="A1974" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1974" t="inlineStr">
+        <is>
+          <t>GLR_PRIME</t>
+        </is>
+      </c>
+      <c r="C1974" t="inlineStr">
+        <is>
+          <t>Gabriel</t>
+        </is>
+      </c>
+      <c r="D1974" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1974" t="n">
+        <v>36</v>
+      </c>
+      <c r="F1974" t="n">
+        <v>219</v>
+      </c>
+      <c r="G1974" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1974" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1975">
+      <c r="A1975" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1975" t="inlineStr">
+        <is>
+          <t>Exia95</t>
+        </is>
+      </c>
+      <c r="C1975" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D1975" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1975" t="n">
+        <v>37</v>
+      </c>
+      <c r="F1975" t="n">
+        <v>212</v>
+      </c>
+      <c r="G1975" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1975" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1976">
+      <c r="A1976" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1976" t="inlineStr">
+        <is>
+          <t>Matt#4B4CU</t>
+        </is>
+      </c>
+      <c r="C1976" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="D1976" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1976" t="n">
+        <v>38</v>
+      </c>
+      <c r="F1976" t="n">
+        <v>211</v>
+      </c>
+      <c r="G1976" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1976" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1977">
+      <c r="A1977" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1977" t="inlineStr">
+        <is>
+          <t>dian-bgt</t>
+        </is>
+      </c>
+      <c r="C1977" t="inlineStr">
+        <is>
+          <t>Diane</t>
+        </is>
+      </c>
+      <c r="D1977" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1977" t="n">
+        <v>39</v>
+      </c>
+      <c r="F1977" t="n">
+        <v>206</v>
+      </c>
+      <c r="G1977" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1977" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1978">
+      <c r="A1978" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1978" t="inlineStr">
+        <is>
+          <t>LilianeB</t>
+        </is>
+      </c>
+      <c r="C1978" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liliane </t>
+        </is>
+      </c>
+      <c r="D1978" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1978" t="n">
+        <v>40</v>
+      </c>
+      <c r="F1978" t="n">
+        <v>206</v>
+      </c>
+      <c r="G1978" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1978" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1979">
+      <c r="A1979" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1979" t="inlineStr">
+        <is>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="C1979" t="inlineStr">
+        <is>
+          <t>Julie</t>
+        </is>
+      </c>
+      <c r="D1979" t="inlineStr"/>
+      <c r="E1979" t="n">
+        <v>41</v>
+      </c>
+      <c r="F1979" t="n">
+        <v>206</v>
+      </c>
+      <c r="G1979" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1979" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1980">
+      <c r="A1980" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1980" t="inlineStr">
+        <is>
+          <t>Romain_JO</t>
+        </is>
+      </c>
+      <c r="C1980" t="inlineStr">
+        <is>
+          <t>Romain J</t>
+        </is>
+      </c>
+      <c r="D1980" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1980" t="n">
+        <v>42</v>
+      </c>
+      <c r="F1980" t="n">
+        <v>191</v>
+      </c>
+      <c r="G1980" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1980" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1981">
+      <c r="A1981" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1981" t="inlineStr">
+        <is>
+          <t>JeremFZ</t>
+        </is>
+      </c>
+      <c r="C1981" t="inlineStr">
+        <is>
+          <t>Jérémy</t>
+        </is>
+      </c>
+      <c r="D1981" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1981" t="n">
+        <v>43</v>
+      </c>
+      <c r="F1981" t="n">
+        <v>191</v>
+      </c>
+      <c r="G1981" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1981" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1982">
+      <c r="A1982" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1982" t="inlineStr">
+        <is>
+          <t>AudreyB225</t>
+        </is>
+      </c>
+      <c r="C1982" t="inlineStr">
+        <is>
+          <t>Audrey</t>
+        </is>
+      </c>
+      <c r="D1982" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1982" t="n">
+        <v>44</v>
+      </c>
+      <c r="F1982" t="n">
+        <v>190</v>
+      </c>
+      <c r="G1982" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1982" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1983">
+      <c r="A1983" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1983" t="inlineStr">
+        <is>
+          <t>Camss</t>
+        </is>
+      </c>
+      <c r="C1983" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D1983" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1983" t="n">
+        <v>45</v>
+      </c>
+      <c r="F1983" t="n">
+        <v>190</v>
+      </c>
+      <c r="G1983" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1983" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1984">
+      <c r="A1984" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1984" t="inlineStr">
+        <is>
+          <t>BadrLeo</t>
+        </is>
+      </c>
+      <c r="C1984" t="inlineStr">
+        <is>
+          <t>Badr Leo</t>
+        </is>
+      </c>
+      <c r="D1984" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1984" t="n">
+        <v>46</v>
+      </c>
+      <c r="F1984" t="n">
+        <v>186</v>
+      </c>
+      <c r="G1984" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1984" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1985">
+      <c r="A1985" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1985" t="inlineStr">
+        <is>
+          <t>YassineZ95</t>
+        </is>
+      </c>
+      <c r="C1985" t="inlineStr">
+        <is>
+          <t>Yassine Z</t>
+        </is>
+      </c>
+      <c r="D1985" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E1985" t="n">
+        <v>47</v>
+      </c>
+      <c r="F1985" t="n">
+        <v>186</v>
+      </c>
+      <c r="G1985" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1985" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1986">
+      <c r="A1986" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1986" t="inlineStr">
+        <is>
+          <t>Ilan_260_</t>
+        </is>
+      </c>
+      <c r="C1986" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ilann </t>
+        </is>
+      </c>
+      <c r="D1986" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1986" t="n">
+        <v>48</v>
+      </c>
+      <c r="F1986" t="n">
+        <v>185</v>
+      </c>
+      <c r="G1986" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1986" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1987">
+      <c r="A1987" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1987" t="inlineStr">
+        <is>
+          <t>abihuts</t>
+        </is>
+      </c>
+      <c r="C1987" t="inlineStr">
+        <is>
+          <t>Antonio Moctezuma</t>
+        </is>
+      </c>
+      <c r="D1987" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1987" t="n">
+        <v>49</v>
+      </c>
+      <c r="F1987" t="n">
+        <v>172</v>
+      </c>
+      <c r="G1987" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1987" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1988">
+      <c r="A1988" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1988" t="inlineStr">
+        <is>
+          <t>Chadia__</t>
+        </is>
+      </c>
+      <c r="C1988" t="inlineStr">
+        <is>
+          <t>Chadia</t>
+        </is>
+      </c>
+      <c r="D1988" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1988" t="n">
+        <v>50</v>
+      </c>
+      <c r="F1988" t="n">
+        <v>170</v>
+      </c>
+      <c r="G1988" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1988" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1989">
+      <c r="A1989" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1989" t="inlineStr">
+        <is>
+          <t>GOAT#UE2WM8M9</t>
+        </is>
+      </c>
+      <c r="C1989" t="inlineStr">
+        <is>
+          <t>Marilena</t>
+        </is>
+      </c>
+      <c r="D1989" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1989" t="n">
+        <v>51</v>
+      </c>
+      <c r="F1989" t="n">
+        <v>165</v>
+      </c>
+      <c r="G1989" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1989" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1990">
+      <c r="A1990" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1990" t="inlineStr">
+        <is>
+          <t>Ceciledp</t>
+        </is>
+      </c>
+      <c r="C1990" t="inlineStr">
+        <is>
+          <t>Cécile</t>
+        </is>
+      </c>
+      <c r="D1990" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1990" t="n">
+        <v>52</v>
+      </c>
+      <c r="F1990" t="n">
+        <v>145</v>
+      </c>
+      <c r="G1990" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1990" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1991">
+      <c r="A1991" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1991" t="inlineStr">
+        <is>
+          <t>Fuzo697</t>
+        </is>
+      </c>
+      <c r="C1991" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D1991" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1991" t="n">
+        <v>53</v>
+      </c>
+      <c r="F1991" t="n">
+        <v>145</v>
+      </c>
+      <c r="G1991" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1991" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1992">
+      <c r="A1992" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1992" t="inlineStr">
+        <is>
+          <t>Yebri</t>
+        </is>
+      </c>
+      <c r="C1992" t="inlineStr">
+        <is>
+          <t>Brieuc</t>
+        </is>
+      </c>
+      <c r="D1992" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1992" t="n">
+        <v>54</v>
+      </c>
+      <c r="F1992" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1992" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1992" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1993">
+      <c r="A1993" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1993" t="inlineStr">
+        <is>
+          <t>Leo_durable</t>
+        </is>
+      </c>
+      <c r="C1993" t="inlineStr">
+        <is>
+          <t>Leo</t>
+        </is>
+      </c>
+      <c r="D1993" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1993" t="n">
+        <v>55</v>
+      </c>
+      <c r="F1993" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1993" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1993" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1994">
+      <c r="A1994" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1994" t="inlineStr">
+        <is>
+          <t>EmyEnzo</t>
+        </is>
+      </c>
+      <c r="C1994" t="inlineStr">
+        <is>
+          <t>Emilie</t>
+        </is>
+      </c>
+      <c r="D1994" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1994" t="n">
+        <v>56</v>
+      </c>
+      <c r="F1994" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1994" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1994" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1995">
+      <c r="A1995" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1995" t="inlineStr">
+        <is>
+          <t>Priscilla#4LCAF</t>
+        </is>
+      </c>
+      <c r="C1995" t="inlineStr">
+        <is>
+          <t>Priscilla</t>
+        </is>
+      </c>
+      <c r="D1995" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E1995" t="n">
+        <v>57</v>
+      </c>
+      <c r="F1995" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1995" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1995" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1996">
+      <c r="A1996" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1996" t="inlineStr">
+        <is>
+          <t>Pipou931</t>
+        </is>
+      </c>
+      <c r="C1996" t="inlineStr">
+        <is>
+          <t>Juliie</t>
+        </is>
+      </c>
+      <c r="D1996" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E1996" t="n">
+        <v>58</v>
+      </c>
+      <c r="F1996" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1996" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1996" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1997">
+      <c r="A1997" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1997" t="inlineStr">
+        <is>
+          <t>Farah_One</t>
+        </is>
+      </c>
+      <c r="C1997" t="inlineStr">
+        <is>
+          <t>Farah</t>
+        </is>
+      </c>
+      <c r="D1997" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E1997" t="n">
+        <v>59</v>
+      </c>
+      <c r="F1997" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1997" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1997" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1998">
+      <c r="A1998" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1998" t="inlineStr">
+        <is>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="C1998" t="inlineStr">
+        <is>
+          <t>François</t>
+        </is>
+      </c>
+      <c r="D1998" t="inlineStr"/>
+      <c r="E1998" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1998" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1998" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1998" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1999">
+      <c r="A1999" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B1999" t="inlineStr">
+        <is>
+          <t>Seesee</t>
+        </is>
+      </c>
+      <c r="C1999" t="inlineStr">
+        <is>
+          <t>Selver</t>
+        </is>
+      </c>
+      <c r="D1999" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E1999" t="n">
+        <v>61</v>
+      </c>
+      <c r="F1999" t="n">
+        <v>143</v>
+      </c>
+      <c r="G1999" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1999" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2000">
+      <c r="A2000" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2000" t="inlineStr">
+        <is>
+          <t>lenaaik</t>
+        </is>
+      </c>
+      <c r="C2000" t="inlineStr">
+        <is>
+          <t>Lénaïk</t>
+        </is>
+      </c>
+      <c r="D2000" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2000" t="n">
+        <v>62</v>
+      </c>
+      <c r="F2000" t="n">
+        <v>143</v>
+      </c>
+      <c r="G2000" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2000" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2001">
+      <c r="A2001" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2001" t="inlineStr">
+        <is>
+          <t>C4M</t>
+        </is>
+      </c>
+      <c r="C2001" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D2001" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2001" t="n">
+        <v>63</v>
+      </c>
+      <c r="F2001" t="n">
+        <v>143</v>
+      </c>
+      <c r="G2001" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2001" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2002">
+      <c r="A2002" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2002" t="inlineStr">
+        <is>
+          <t>Rosa_1009</t>
+        </is>
+      </c>
+      <c r="C2002" t="inlineStr">
+        <is>
+          <t>Rosaline</t>
+        </is>
+      </c>
+      <c r="D2002" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2002" t="n">
+        <v>64</v>
+      </c>
+      <c r="F2002" t="n">
+        <v>143</v>
+      </c>
+      <c r="G2002" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2002" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2003">
+      <c r="A2003" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2003" t="inlineStr">
+        <is>
+          <t>Elisewiss</t>
+        </is>
+      </c>
+      <c r="C2003" t="inlineStr">
+        <is>
+          <t>Elise</t>
+        </is>
+      </c>
+      <c r="D2003" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2003" t="n">
+        <v>65</v>
+      </c>
+      <c r="F2003" t="n">
+        <v>143</v>
+      </c>
+      <c r="G2003" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2003" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2004">
+      <c r="A2004" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2004" t="inlineStr">
+        <is>
+          <t>Soraya-Y</t>
+        </is>
+      </c>
+      <c r="C2004" t="inlineStr">
+        <is>
+          <t>Soraya</t>
+        </is>
+      </c>
+      <c r="D2004" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2004" t="n">
+        <v>66</v>
+      </c>
+      <c r="F2004" t="n">
+        <v>143</v>
+      </c>
+      <c r="G2004" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2004" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2005">
+      <c r="A2005" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2005" t="inlineStr">
+        <is>
+          <t>1993ahm</t>
+        </is>
+      </c>
+      <c r="C2005" t="inlineStr">
+        <is>
+          <t>Ahmed</t>
+        </is>
+      </c>
+      <c r="D2005" t="inlineStr"/>
+      <c r="E2005" t="n">
+        <v>67</v>
+      </c>
+      <c r="F2005" t="n">
+        <v>143</v>
+      </c>
+      <c r="G2005" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2005" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2006">
+      <c r="A2006" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2006" t="inlineStr">
+        <is>
+          <t>Timy</t>
+        </is>
+      </c>
+      <c r="C2006" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="D2006" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2006" t="n">
+        <v>68</v>
+      </c>
+      <c r="F2006" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2006" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2006" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2007">
+      <c r="A2007" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2007" t="inlineStr">
+        <is>
+          <t>JEVAISGAGNER10</t>
+        </is>
+      </c>
+      <c r="C2007" t="inlineStr">
+        <is>
+          <t>Xavier</t>
+        </is>
+      </c>
+      <c r="D2007" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2007" t="n">
+        <v>69</v>
+      </c>
+      <c r="F2007" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2007" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2007" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2008">
+      <c r="A2008" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2008" t="inlineStr">
+        <is>
+          <t>HamzaG</t>
+        </is>
+      </c>
+      <c r="C2008" t="inlineStr">
+        <is>
+          <t>Hamza</t>
+        </is>
+      </c>
+      <c r="D2008" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2008" t="n">
+        <v>70</v>
+      </c>
+      <c r="F2008" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2008" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2008" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2009">
+      <c r="A2009" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2009" t="inlineStr">
+        <is>
+          <t>LeaBrd</t>
+        </is>
+      </c>
+      <c r="C2009" t="inlineStr">
+        <is>
+          <t>Léa</t>
+        </is>
+      </c>
+      <c r="D2009" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2009" t="n">
+        <v>71</v>
+      </c>
+      <c r="F2009" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2009" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2009" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2010">
+      <c r="A2010" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2010" t="inlineStr">
+        <is>
+          <t>davidd23</t>
+        </is>
+      </c>
+      <c r="C2010" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D2010" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2010" t="n">
+        <v>72</v>
+      </c>
+      <c r="F2010" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2010" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2010" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2011">
+      <c r="A2011" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2011" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="C2011" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="D2011" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2011" t="n">
+        <v>73</v>
+      </c>
+      <c r="F2011" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2011" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2011" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2012">
+      <c r="A2012" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2012" t="inlineStr">
+        <is>
+          <t>Kolas</t>
+        </is>
+      </c>
+      <c r="C2012" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D2012" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2012" t="n">
+        <v>74</v>
+      </c>
+      <c r="F2012" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2012" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2012" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2013">
+      <c r="A2013" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2013" t="inlineStr">
+        <is>
+          <t>Laetice2020</t>
+        </is>
+      </c>
+      <c r="C2013" t="inlineStr">
+        <is>
+          <t>Laetitia</t>
+        </is>
+      </c>
+      <c r="D2013" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2013" t="n">
+        <v>75</v>
+      </c>
+      <c r="F2013" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2013" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2013" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2014">
+      <c r="A2014" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2014" t="inlineStr">
+        <is>
+          <t>Emilay</t>
+        </is>
+      </c>
+      <c r="C2014" t="inlineStr">
+        <is>
+          <t>Émilie</t>
+        </is>
+      </c>
+      <c r="D2014" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2014" t="n">
+        <v>76</v>
+      </c>
+      <c r="F2014" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2014" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2014" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2015">
+      <c r="A2015" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2015" t="inlineStr">
+        <is>
+          <t>Lyzone</t>
+        </is>
+      </c>
+      <c r="C2015" t="inlineStr">
+        <is>
+          <t>Lison</t>
+        </is>
+      </c>
+      <c r="D2015" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2015" t="n">
+        <v>77</v>
+      </c>
+      <c r="F2015" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2015" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2015" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2016">
+      <c r="A2016" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2016" t="inlineStr">
+        <is>
+          <t>Melissagzb</t>
+        </is>
+      </c>
+      <c r="C2016" t="inlineStr">
+        <is>
+          <t>Melissa</t>
+        </is>
+      </c>
+      <c r="D2016" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2016" t="n">
+        <v>78</v>
+      </c>
+      <c r="F2016" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2016" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2016" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2017">
+      <c r="A2017" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2017" t="inlineStr">
+        <is>
+          <t>Marie__92</t>
+        </is>
+      </c>
+      <c r="C2017" t="inlineStr">
+        <is>
+          <t>Marie</t>
+        </is>
+      </c>
+      <c r="D2017" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2017" t="n">
+        <v>79</v>
+      </c>
+      <c r="F2017" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2017" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2017" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2018">
+      <c r="A2018" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2018" t="inlineStr">
+        <is>
+          <t>K_Marp</t>
+        </is>
+      </c>
+      <c r="C2018" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
+      <c r="D2018" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2018" t="n">
+        <v>80</v>
+      </c>
+      <c r="F2018" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2018" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2018" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2019">
+      <c r="A2019" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2019" t="inlineStr">
+        <is>
+          <t>Cindie_JJA</t>
+        </is>
+      </c>
+      <c r="C2019" t="inlineStr">
+        <is>
+          <t>Cindie</t>
+        </is>
+      </c>
+      <c r="D2019" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2019" t="n">
+        <v>81</v>
+      </c>
+      <c r="F2019" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2019" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2019" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2020">
+      <c r="A2020" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2020" t="inlineStr">
+        <is>
+          <t>JKInternational</t>
+        </is>
+      </c>
+      <c r="C2020" t="inlineStr">
+        <is>
+          <t>Joachim</t>
+        </is>
+      </c>
+      <c r="D2020" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2020" t="n">
+        <v>82</v>
+      </c>
+      <c r="F2020" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2020" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2020" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2021">
+      <c r="A2021" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2021" t="inlineStr">
+        <is>
+          <t>GOAT#UE4U8KA6</t>
+        </is>
+      </c>
+      <c r="C2021" t="inlineStr">
+        <is>
+          <t>Jean Baptiste</t>
+        </is>
+      </c>
+      <c r="D2021" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2021" t="n">
+        <v>83</v>
+      </c>
+      <c r="F2021" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2021" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2021" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2022">
+      <c r="A2022" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2022" t="inlineStr">
+        <is>
+          <t>goat#AD6GS</t>
+        </is>
+      </c>
+      <c r="C2022" t="inlineStr">
+        <is>
+          <t>goat</t>
+        </is>
+      </c>
+      <c r="D2022" t="inlineStr"/>
+      <c r="E2022" t="n">
+        <v>84</v>
+      </c>
+      <c r="F2022" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2022" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2022" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2023">
+      <c r="A2023" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2023" t="inlineStr">
+        <is>
+          <t>Camillewbl</t>
+        </is>
+      </c>
+      <c r="C2023" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D2023" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2023" t="n">
+        <v>85</v>
+      </c>
+      <c r="F2023" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2023" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2023" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2024">
+      <c r="A2024" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2024" t="inlineStr">
+        <is>
+          <t>Emma_Noel</t>
+        </is>
+      </c>
+      <c r="C2024" t="inlineStr">
+        <is>
+          <t>Emma</t>
+        </is>
+      </c>
+      <c r="D2024" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2024" t="n">
+        <v>86</v>
+      </c>
+      <c r="F2024" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2024" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2024" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2025">
+      <c r="A2025" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2025" t="inlineStr">
+        <is>
+          <t>RBTL</t>
+        </is>
+      </c>
+      <c r="C2025" t="inlineStr">
+        <is>
+          <t>lea</t>
+        </is>
+      </c>
+      <c r="D2025" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2025" t="n">
+        <v>87</v>
+      </c>
+      <c r="F2025" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2025" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2025" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2026">
+      <c r="A2026" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2026" t="inlineStr">
+        <is>
+          <t>A-MOE</t>
+        </is>
+      </c>
+      <c r="C2026" t="inlineStr">
+        <is>
+          <t>Françoise</t>
+        </is>
+      </c>
+      <c r="D2026" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2026" t="n">
+        <v>88</v>
+      </c>
+      <c r="F2026" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2026" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2026" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2027">
+      <c r="A2027" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2027" t="inlineStr">
+        <is>
+          <t>Davido#4BZ54</t>
+        </is>
+      </c>
+      <c r="C2027" t="inlineStr">
+        <is>
+          <t>Davido</t>
+        </is>
+      </c>
+      <c r="D2027" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2027" t="n">
+        <v>89</v>
+      </c>
+      <c r="F2027" t="n">
+        <v>96</v>
+      </c>
+      <c r="G2027" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2027" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2028">
+      <c r="A2028" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2028" t="inlineStr">
+        <is>
+          <t>BrickXVI</t>
+        </is>
+      </c>
+      <c r="C2028" t="inlineStr">
+        <is>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="D2028" t="inlineStr"/>
+      <c r="E2028" t="n">
+        <v>90</v>
+      </c>
+      <c r="F2028" t="n">
+        <v>74</v>
+      </c>
+      <c r="G2028" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2028" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2029">
+      <c r="A2029" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2029" t="inlineStr">
+        <is>
+          <t>Taylor2901</t>
+        </is>
+      </c>
+      <c r="C2029" t="inlineStr">
+        <is>
+          <t>ousmane</t>
+        </is>
+      </c>
+      <c r="D2029" t="inlineStr"/>
+      <c r="E2029" t="n">
+        <v>91</v>
+      </c>
+      <c r="F2029" t="n">
+        <v>74</v>
+      </c>
+      <c r="G2029" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2029" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2030">
+      <c r="A2030" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2030" t="inlineStr">
+        <is>
+          <t>Ze_GOAT</t>
+        </is>
+      </c>
+      <c r="C2030" t="inlineStr">
+        <is>
+          <t>Yasser</t>
+        </is>
+      </c>
+      <c r="D2030" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2030" t="n">
+        <v>92</v>
+      </c>
+      <c r="F2030" t="n">
+        <v>69</v>
+      </c>
+      <c r="G2030" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2030" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2031">
+      <c r="A2031" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2031" t="inlineStr">
+        <is>
+          <t>Krol#4R8XC</t>
+        </is>
+      </c>
+      <c r="C2031" t="inlineStr">
+        <is>
+          <t>Krol</t>
+        </is>
+      </c>
+      <c r="D2031" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2031" t="n">
+        <v>93</v>
+      </c>
+      <c r="F2031" t="n">
+        <v>69</v>
+      </c>
+      <c r="G2031" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2031" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2032">
+      <c r="A2032" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2032" t="inlineStr">
+        <is>
+          <t>PacoSarra</t>
+        </is>
+      </c>
+      <c r="C2032" t="inlineStr">
+        <is>
+          <t>Ibra</t>
+        </is>
+      </c>
+      <c r="D2032" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2032" t="n">
+        <v>94</v>
+      </c>
+      <c r="F2032" t="n">
+        <v>69</v>
+      </c>
+      <c r="G2032" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2032" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2033">
+      <c r="A2033" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2033" t="inlineStr">
+        <is>
+          <t>Droit_au_but7723</t>
+        </is>
+      </c>
+      <c r="C2033" t="inlineStr">
+        <is>
+          <t>Calixthe</t>
+        </is>
+      </c>
+      <c r="D2033" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2033" t="n">
+        <v>95</v>
+      </c>
+      <c r="F2033" t="n">
+        <v>69</v>
+      </c>
+      <c r="G2033" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2033" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2034">
+      <c r="A2034" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2034" t="inlineStr">
+        <is>
+          <t>Ambrepic</t>
+        </is>
+      </c>
+      <c r="C2034" t="inlineStr">
+        <is>
+          <t>Ambre</t>
+        </is>
+      </c>
+      <c r="D2034" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2034" t="n">
+        <v>96</v>
+      </c>
+      <c r="F2034" t="n">
+        <v>69</v>
+      </c>
+      <c r="G2034" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2034" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2035">
+      <c r="A2035" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2035" t="inlineStr">
+        <is>
+          <t>PavelMel</t>
+        </is>
+      </c>
+      <c r="C2035" t="inlineStr">
+        <is>
+          <t>Mélissa</t>
+        </is>
+      </c>
+      <c r="D2035" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2035" t="n">
+        <v>97</v>
+      </c>
+      <c r="F2035" t="n">
+        <v>49</v>
+      </c>
+      <c r="G2035" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2035" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2036">
+      <c r="A2036" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2036" t="inlineStr">
+        <is>
+          <t>Mylene-Jnt</t>
+        </is>
+      </c>
+      <c r="C2036" t="inlineStr">
+        <is>
+          <t>Mylène</t>
+        </is>
+      </c>
+      <c r="D2036" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2036" t="n">
+        <v>98</v>
+      </c>
+      <c r="F2036" t="n">
+        <v>49</v>
+      </c>
+      <c r="G2036" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2036" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2037">
+      <c r="A2037" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2037" t="inlineStr">
+        <is>
+          <t>Teddbear</t>
+        </is>
+      </c>
+      <c r="C2037" t="inlineStr">
+        <is>
+          <t>Tedy</t>
+        </is>
+      </c>
+      <c r="D2037" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2037" t="n">
+        <v>99</v>
+      </c>
+      <c r="F2037" t="n">
+        <v>49</v>
+      </c>
+      <c r="G2037" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2037" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2038">
+      <c r="A2038" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2038" t="inlineStr">
+        <is>
+          <t>SabC1</t>
+        </is>
+      </c>
+      <c r="C2038" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="D2038" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2038" t="n">
+        <v>100</v>
+      </c>
+      <c r="F2038" t="n">
+        <v>49</v>
+      </c>
+      <c r="G2038" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2038" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2039">
+      <c r="A2039" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2039" t="inlineStr">
+        <is>
+          <t>KIKS999</t>
+        </is>
+      </c>
+      <c r="C2039" t="inlineStr">
+        <is>
+          <t>Killian</t>
+        </is>
+      </c>
+      <c r="D2039" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2039" t="n">
+        <v>101</v>
+      </c>
+      <c r="F2039" t="n">
+        <v>49</v>
+      </c>
+      <c r="G2039" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2039" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2040">
+      <c r="A2040" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2040" t="inlineStr">
+        <is>
+          <t>MxKnight</t>
+        </is>
+      </c>
+      <c r="C2040" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D2040" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2040" t="n">
+        <v>102</v>
+      </c>
+      <c r="F2040" t="n">
+        <v>49</v>
+      </c>
+      <c r="G2040" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2040" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2041">
+      <c r="A2041" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2041" t="inlineStr">
+        <is>
+          <t>RomainLect</t>
+        </is>
+      </c>
+      <c r="C2041" t="inlineStr">
+        <is>
+          <t>romain</t>
+        </is>
+      </c>
+      <c r="D2041" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2041" t="n">
+        <v>103</v>
+      </c>
+      <c r="F2041" t="n">
+        <v>49</v>
+      </c>
+      <c r="G2041" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2041" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2042">
+      <c r="A2042" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2042" t="inlineStr">
+        <is>
+          <t>SamSamH8</t>
+        </is>
+      </c>
+      <c r="C2042" t="inlineStr">
+        <is>
+          <t>Samia</t>
+        </is>
+      </c>
+      <c r="D2042" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2042" t="n">
+        <v>104</v>
+      </c>
+      <c r="F2042" t="n">
+        <v>49</v>
+      </c>
+      <c r="G2042" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2042" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2043">
+      <c r="A2043" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2043" t="inlineStr">
+        <is>
+          <t>Daviddesco1</t>
+        </is>
+      </c>
+      <c r="C2043" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D2043" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2043" t="n">
+        <v>105</v>
+      </c>
+      <c r="F2043" t="n">
+        <v>49</v>
+      </c>
+      <c r="G2043" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2043" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2044">
+      <c r="A2044" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2044" t="inlineStr">
+        <is>
+          <t>Sab_M45</t>
+        </is>
+      </c>
+      <c r="C2044" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="D2044" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2044" t="n">
+        <v>106</v>
+      </c>
+      <c r="F2044" t="n">
+        <v>49</v>
+      </c>
+      <c r="G2044" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2044" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2045">
+      <c r="A2045" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2045" t="inlineStr">
+        <is>
+          <t>Valentine___</t>
+        </is>
+      </c>
+      <c r="C2045" t="inlineStr">
+        <is>
+          <t>Valentine</t>
+        </is>
+      </c>
+      <c r="D2045" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2045" t="n">
+        <v>107</v>
+      </c>
+      <c r="F2045" t="n">
+        <v>49</v>
+      </c>
+      <c r="G2045" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2045" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2046">
+      <c r="A2046" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2046" t="inlineStr">
+        <is>
+          <t>PANENKANY</t>
+        </is>
+      </c>
+      <c r="C2046" t="inlineStr">
+        <is>
+          <t>Damien</t>
+        </is>
+      </c>
+      <c r="D2046" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2046" t="n">
+        <v>108</v>
+      </c>
+      <c r="F2046" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2046" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2046" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2047">
+      <c r="A2047" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2047" t="inlineStr">
+        <is>
+          <t>MT35T</t>
+        </is>
+      </c>
+      <c r="C2047" t="inlineStr">
+        <is>
+          <t>Mathilde</t>
+        </is>
+      </c>
+      <c r="D2047" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2047" t="n">
+        <v>109</v>
+      </c>
+      <c r="F2047" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2047" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2047" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historique_joueurs.xlsx
+++ b/historique_joueurs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2047"/>
+  <dimension ref="A1:H2156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68514,6 +68514,3688 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2048">
+      <c r="A2048" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2048" t="inlineStr">
+        <is>
+          <t>Filipinho95</t>
+        </is>
+      </c>
+      <c r="C2048" t="inlineStr">
+        <is>
+          <t>Filipe</t>
+        </is>
+      </c>
+      <c r="D2048" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2048" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2048" t="n">
+        <v>410</v>
+      </c>
+      <c r="G2048" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2048" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2049">
+      <c r="A2049" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2049" t="inlineStr">
+        <is>
+          <t>Ninaaaa</t>
+        </is>
+      </c>
+      <c r="C2049" t="inlineStr">
+        <is>
+          <t>Nina</t>
+        </is>
+      </c>
+      <c r="D2049" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2049" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2049" t="n">
+        <v>400</v>
+      </c>
+      <c r="G2049" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2049" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2050">
+      <c r="A2050" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2050" t="inlineStr">
+        <is>
+          <t>MargauxCtln</t>
+        </is>
+      </c>
+      <c r="C2050" t="inlineStr">
+        <is>
+          <t>Margaux</t>
+        </is>
+      </c>
+      <c r="D2050" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2050" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2050" t="n">
+        <v>376</v>
+      </c>
+      <c r="G2050" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2050" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2051">
+      <c r="A2051" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2051" t="inlineStr">
+        <is>
+          <t>Mamad_Shelter</t>
+        </is>
+      </c>
+      <c r="C2051" t="inlineStr">
+        <is>
+          <t>Mamadou</t>
+        </is>
+      </c>
+      <c r="D2051" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2051" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2051" t="n">
+        <v>376</v>
+      </c>
+      <c r="G2051" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2051" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2052">
+      <c r="A2052" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2052" t="inlineStr">
+        <is>
+          <t>MagicMath</t>
+        </is>
+      </c>
+      <c r="C2052" t="inlineStr">
+        <is>
+          <t>Mathieu</t>
+        </is>
+      </c>
+      <c r="D2052" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2052" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2052" t="n">
+        <v>376</v>
+      </c>
+      <c r="G2052" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2052" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2053">
+      <c r="A2053" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2053" t="inlineStr">
+        <is>
+          <t>WalidSiuuuuu</t>
+        </is>
+      </c>
+      <c r="C2053" t="inlineStr">
+        <is>
+          <t>Walid</t>
+        </is>
+      </c>
+      <c r="D2053" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2053" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2053" t="n">
+        <v>356</v>
+      </c>
+      <c r="G2053" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2053" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2054">
+      <c r="A2054" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2054" t="inlineStr">
+        <is>
+          <t>DJOSWA</t>
+        </is>
+      </c>
+      <c r="C2054" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oswaina </t>
+        </is>
+      </c>
+      <c r="D2054" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2054" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2054" t="n">
+        <v>356</v>
+      </c>
+      <c r="G2054" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2054" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2055">
+      <c r="A2055" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2055" t="inlineStr">
+        <is>
+          <t>SID-F-ANDRE</t>
+        </is>
+      </c>
+      <c r="C2055" t="inlineStr">
+        <is>
+          <t>Denis</t>
+        </is>
+      </c>
+      <c r="D2055" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2055" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2055" t="n">
+        <v>355</v>
+      </c>
+      <c r="G2055" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2055" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2056">
+      <c r="A2056" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2056" t="inlineStr">
+        <is>
+          <t>ChrisKr1Deg1</t>
+        </is>
+      </c>
+      <c r="C2056" t="inlineStr">
+        <is>
+          <t>christophe</t>
+        </is>
+      </c>
+      <c r="D2056" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2056" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2056" t="n">
+        <v>323</v>
+      </c>
+      <c r="G2056" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2056" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2057">
+      <c r="A2057" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2057" t="inlineStr">
+        <is>
+          <t>Coucoucassecou</t>
+        </is>
+      </c>
+      <c r="C2057" t="inlineStr">
+        <is>
+          <t>Brayen</t>
+        </is>
+      </c>
+      <c r="D2057" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2057" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2057" t="n">
+        <v>322</v>
+      </c>
+      <c r="G2057" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2057" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2058">
+      <c r="A2058" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2058" t="inlineStr">
+        <is>
+          <t>Paulasipi1998</t>
+        </is>
+      </c>
+      <c r="C2058" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="D2058" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2058" t="n">
+        <v>11</v>
+      </c>
+      <c r="F2058" t="n">
+        <v>322</v>
+      </c>
+      <c r="G2058" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2058" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2059">
+      <c r="A2059" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2059" t="inlineStr">
+        <is>
+          <t>Panaff</t>
+        </is>
+      </c>
+      <c r="C2059" t="inlineStr">
+        <is>
+          <t>Panaf</t>
+        </is>
+      </c>
+      <c r="D2059" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2059" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2059" t="n">
+        <v>315</v>
+      </c>
+      <c r="G2059" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2059" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2060">
+      <c r="A2060" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2060" t="inlineStr">
+        <is>
+          <t>Stephbreton</t>
+        </is>
+      </c>
+      <c r="C2060" t="inlineStr">
+        <is>
+          <t>STEPHANE</t>
+        </is>
+      </c>
+      <c r="D2060" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2060" t="n">
+        <v>13</v>
+      </c>
+      <c r="F2060" t="n">
+        <v>307</v>
+      </c>
+      <c r="G2060" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2060" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2061">
+      <c r="A2061" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2061" t="inlineStr">
+        <is>
+          <t>Kaliced</t>
+        </is>
+      </c>
+      <c r="C2061" t="inlineStr">
+        <is>
+          <t>Kalice</t>
+        </is>
+      </c>
+      <c r="D2061" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2061" t="n">
+        <v>14</v>
+      </c>
+      <c r="F2061" t="n">
+        <v>302</v>
+      </c>
+      <c r="G2061" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2061" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2062">
+      <c r="A2062" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2062" t="inlineStr">
+        <is>
+          <t>MyriamAmr</t>
+        </is>
+      </c>
+      <c r="C2062" t="inlineStr">
+        <is>
+          <t>Myriam</t>
+        </is>
+      </c>
+      <c r="D2062" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2062" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2062" t="n">
+        <v>298</v>
+      </c>
+      <c r="G2062" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2062" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2063">
+      <c r="A2063" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2063" t="inlineStr">
+        <is>
+          <t>Nonito20</t>
+        </is>
+      </c>
+      <c r="C2063" t="inlineStr">
+        <is>
+          <t>Arnaud</t>
+        </is>
+      </c>
+      <c r="D2063" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2063" t="n">
+        <v>16</v>
+      </c>
+      <c r="F2063" t="n">
+        <v>284</v>
+      </c>
+      <c r="G2063" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2063" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2064">
+      <c r="A2064" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2064" t="inlineStr">
+        <is>
+          <t>FRHTCTD10</t>
+        </is>
+      </c>
+      <c r="C2064" t="inlineStr">
+        <is>
+          <t>Candice</t>
+        </is>
+      </c>
+      <c r="D2064" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2064" t="n">
+        <v>17</v>
+      </c>
+      <c r="F2064" t="n">
+        <v>282</v>
+      </c>
+      <c r="G2064" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2064" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2065">
+      <c r="A2065" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2065" t="inlineStr">
+        <is>
+          <t>Mr-Worldwide</t>
+        </is>
+      </c>
+      <c r="C2065" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="D2065" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2065" t="n">
+        <v>18</v>
+      </c>
+      <c r="F2065" t="n">
+        <v>280</v>
+      </c>
+      <c r="G2065" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2065" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2066">
+      <c r="A2066" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2066" t="inlineStr">
+        <is>
+          <t>Fethinho</t>
+        </is>
+      </c>
+      <c r="C2066" t="inlineStr">
+        <is>
+          <t>Fethi</t>
+        </is>
+      </c>
+      <c r="D2066" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2066" t="n">
+        <v>19</v>
+      </c>
+      <c r="F2066" t="n">
+        <v>280</v>
+      </c>
+      <c r="G2066" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2066" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2067">
+      <c r="A2067" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2067" t="inlineStr">
+        <is>
+          <t>Ouiouiausoleil</t>
+        </is>
+      </c>
+      <c r="C2067" t="inlineStr">
+        <is>
+          <t>Ouissal</t>
+        </is>
+      </c>
+      <c r="D2067" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2067" t="n">
+        <v>20</v>
+      </c>
+      <c r="F2067" t="n">
+        <v>280</v>
+      </c>
+      <c r="G2067" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2067" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2068">
+      <c r="A2068" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2068" t="inlineStr">
+        <is>
+          <t>BOUGA#2JGXP</t>
+        </is>
+      </c>
+      <c r="C2068" t="inlineStr">
+        <is>
+          <t>BOUGA</t>
+        </is>
+      </c>
+      <c r="D2068" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2068" t="n">
+        <v>21</v>
+      </c>
+      <c r="F2068" t="n">
+        <v>260</v>
+      </c>
+      <c r="G2068" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2068" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2069">
+      <c r="A2069" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2069" t="inlineStr">
+        <is>
+          <t>Anais757817</t>
+        </is>
+      </c>
+      <c r="C2069" t="inlineStr">
+        <is>
+          <t>Anaïs</t>
+        </is>
+      </c>
+      <c r="D2069" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2069" t="n">
+        <v>22</v>
+      </c>
+      <c r="F2069" t="n">
+        <v>260</v>
+      </c>
+      <c r="G2069" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2069" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2070">
+      <c r="A2070" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2070" t="inlineStr">
+        <is>
+          <t>MatuRenard</t>
+        </is>
+      </c>
+      <c r="C2070" t="inlineStr">
+        <is>
+          <t>Mathias</t>
+        </is>
+      </c>
+      <c r="D2070" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2070" t="n">
+        <v>23</v>
+      </c>
+      <c r="F2070" t="n">
+        <v>259</v>
+      </c>
+      <c r="G2070" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2070" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2071">
+      <c r="A2071" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2071" t="inlineStr">
+        <is>
+          <t>Liliuus</t>
+        </is>
+      </c>
+      <c r="C2071" t="inlineStr">
+        <is>
+          <t>Lilia</t>
+        </is>
+      </c>
+      <c r="D2071" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2071" t="n">
+        <v>24</v>
+      </c>
+      <c r="F2071" t="n">
+        <v>259</v>
+      </c>
+      <c r="G2071" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2071" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2072">
+      <c r="A2072" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2072" t="inlineStr">
+        <is>
+          <t>Ppo28</t>
+        </is>
+      </c>
+      <c r="C2072" t="inlineStr">
+        <is>
+          <t>Prescylla</t>
+        </is>
+      </c>
+      <c r="D2072" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2072" t="n">
+        <v>25</v>
+      </c>
+      <c r="F2072" t="n">
+        <v>259</v>
+      </c>
+      <c r="G2072" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2072" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2073">
+      <c r="A2073" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2073" t="inlineStr">
+        <is>
+          <t>Gronaldo_95</t>
+        </is>
+      </c>
+      <c r="C2073" t="inlineStr">
+        <is>
+          <t>Gronaldo</t>
+        </is>
+      </c>
+      <c r="D2073" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2073" t="n">
+        <v>26</v>
+      </c>
+      <c r="F2073" t="n">
+        <v>239</v>
+      </c>
+      <c r="G2073" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2073" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2074">
+      <c r="A2074" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2074" t="inlineStr">
+        <is>
+          <t>Devilrock95</t>
+        </is>
+      </c>
+      <c r="C2074" t="inlineStr">
+        <is>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="D2074" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2074" t="n">
+        <v>27</v>
+      </c>
+      <c r="F2074" t="n">
+        <v>239</v>
+      </c>
+      <c r="G2074" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2074" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2075">
+      <c r="A2075" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2075" t="inlineStr">
+        <is>
+          <t>Cleem22</t>
+        </is>
+      </c>
+      <c r="C2075" t="inlineStr">
+        <is>
+          <t>Clemence</t>
+        </is>
+      </c>
+      <c r="D2075" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2075" t="n">
+        <v>28</v>
+      </c>
+      <c r="F2075" t="n">
+        <v>239</v>
+      </c>
+      <c r="G2075" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2075" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2076">
+      <c r="A2076" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2076" t="inlineStr">
+        <is>
+          <t>catherine#5FRTD</t>
+        </is>
+      </c>
+      <c r="C2076" t="inlineStr">
+        <is>
+          <t>catherine</t>
+        </is>
+      </c>
+      <c r="D2076" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2076" t="n">
+        <v>29</v>
+      </c>
+      <c r="F2076" t="n">
+        <v>239</v>
+      </c>
+      <c r="G2076" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2076" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2077">
+      <c r="A2077" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2077" t="inlineStr">
+        <is>
+          <t>Maruyama</t>
+        </is>
+      </c>
+      <c r="C2077" t="inlineStr">
+        <is>
+          <t>Gabrielle</t>
+        </is>
+      </c>
+      <c r="D2077" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2077" t="n">
+        <v>30</v>
+      </c>
+      <c r="F2077" t="n">
+        <v>239</v>
+      </c>
+      <c r="G2077" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2077" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2078">
+      <c r="A2078" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2078" t="inlineStr">
+        <is>
+          <t>Leandrocp</t>
+        </is>
+      </c>
+      <c r="C2078" t="inlineStr">
+        <is>
+          <t>Leandro</t>
+        </is>
+      </c>
+      <c r="D2078" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2078" t="n">
+        <v>31</v>
+      </c>
+      <c r="F2078" t="n">
+        <v>239</v>
+      </c>
+      <c r="G2078" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2078" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2079">
+      <c r="A2079" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2079" t="inlineStr">
+        <is>
+          <t>Marion1822</t>
+        </is>
+      </c>
+      <c r="C2079" t="inlineStr">
+        <is>
+          <t>Marion</t>
+        </is>
+      </c>
+      <c r="D2079" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2079" t="n">
+        <v>32</v>
+      </c>
+      <c r="F2079" t="n">
+        <v>239</v>
+      </c>
+      <c r="G2079" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2079" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2080">
+      <c r="A2080" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2080" t="inlineStr">
+        <is>
+          <t>chaychaychay</t>
+        </is>
+      </c>
+      <c r="C2080" t="inlineStr">
+        <is>
+          <t>Chaymaa</t>
+        </is>
+      </c>
+      <c r="D2080" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2080" t="n">
+        <v>33</v>
+      </c>
+      <c r="F2080" t="n">
+        <v>239</v>
+      </c>
+      <c r="G2080" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2080" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2081">
+      <c r="A2081" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2081" t="inlineStr">
+        <is>
+          <t>WIL1610</t>
+        </is>
+      </c>
+      <c r="C2081" t="inlineStr">
+        <is>
+          <t>William</t>
+        </is>
+      </c>
+      <c r="D2081" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2081" t="n">
+        <v>34</v>
+      </c>
+      <c r="F2081" t="n">
+        <v>233</v>
+      </c>
+      <c r="G2081" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2081" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2082">
+      <c r="A2082" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2082" t="inlineStr">
+        <is>
+          <t>Erwan#4G91X</t>
+        </is>
+      </c>
+      <c r="C2082" t="inlineStr">
+        <is>
+          <t>Erwan</t>
+        </is>
+      </c>
+      <c r="D2082" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2082" t="n">
+        <v>35</v>
+      </c>
+      <c r="F2082" t="n">
+        <v>219</v>
+      </c>
+      <c r="G2082" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2082" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2083">
+      <c r="A2083" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2083" t="inlineStr">
+        <is>
+          <t>GLR_PRIME</t>
+        </is>
+      </c>
+      <c r="C2083" t="inlineStr">
+        <is>
+          <t>Gabriel</t>
+        </is>
+      </c>
+      <c r="D2083" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2083" t="n">
+        <v>36</v>
+      </c>
+      <c r="F2083" t="n">
+        <v>219</v>
+      </c>
+      <c r="G2083" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2083" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2084">
+      <c r="A2084" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2084" t="inlineStr">
+        <is>
+          <t>Exia95</t>
+        </is>
+      </c>
+      <c r="C2084" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D2084" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2084" t="n">
+        <v>37</v>
+      </c>
+      <c r="F2084" t="n">
+        <v>212</v>
+      </c>
+      <c r="G2084" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2084" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2085">
+      <c r="A2085" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2085" t="inlineStr">
+        <is>
+          <t>Matt#4B4CU</t>
+        </is>
+      </c>
+      <c r="C2085" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="D2085" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2085" t="n">
+        <v>38</v>
+      </c>
+      <c r="F2085" t="n">
+        <v>211</v>
+      </c>
+      <c r="G2085" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2085" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2086">
+      <c r="A2086" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2086" t="inlineStr">
+        <is>
+          <t>dian-bgt</t>
+        </is>
+      </c>
+      <c r="C2086" t="inlineStr">
+        <is>
+          <t>Diane</t>
+        </is>
+      </c>
+      <c r="D2086" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2086" t="n">
+        <v>39</v>
+      </c>
+      <c r="F2086" t="n">
+        <v>206</v>
+      </c>
+      <c r="G2086" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2086" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2087">
+      <c r="A2087" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2087" t="inlineStr">
+        <is>
+          <t>LilianeB</t>
+        </is>
+      </c>
+      <c r="C2087" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liliane </t>
+        </is>
+      </c>
+      <c r="D2087" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2087" t="n">
+        <v>40</v>
+      </c>
+      <c r="F2087" t="n">
+        <v>206</v>
+      </c>
+      <c r="G2087" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2087" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2088">
+      <c r="A2088" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2088" t="inlineStr">
+        <is>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="C2088" t="inlineStr">
+        <is>
+          <t>Julie</t>
+        </is>
+      </c>
+      <c r="D2088" t="inlineStr"/>
+      <c r="E2088" t="n">
+        <v>41</v>
+      </c>
+      <c r="F2088" t="n">
+        <v>206</v>
+      </c>
+      <c r="G2088" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2088" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2089" t="inlineStr">
+        <is>
+          <t>Romain_JO</t>
+        </is>
+      </c>
+      <c r="C2089" t="inlineStr">
+        <is>
+          <t>Romain J</t>
+        </is>
+      </c>
+      <c r="D2089" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2089" t="n">
+        <v>42</v>
+      </c>
+      <c r="F2089" t="n">
+        <v>191</v>
+      </c>
+      <c r="G2089" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2089" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2090">
+      <c r="A2090" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2090" t="inlineStr">
+        <is>
+          <t>JeremFZ</t>
+        </is>
+      </c>
+      <c r="C2090" t="inlineStr">
+        <is>
+          <t>Jérémy</t>
+        </is>
+      </c>
+      <c r="D2090" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2090" t="n">
+        <v>43</v>
+      </c>
+      <c r="F2090" t="n">
+        <v>191</v>
+      </c>
+      <c r="G2090" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2090" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2091">
+      <c r="A2091" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2091" t="inlineStr">
+        <is>
+          <t>AudreyB225</t>
+        </is>
+      </c>
+      <c r="C2091" t="inlineStr">
+        <is>
+          <t>Audrey</t>
+        </is>
+      </c>
+      <c r="D2091" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2091" t="n">
+        <v>44</v>
+      </c>
+      <c r="F2091" t="n">
+        <v>190</v>
+      </c>
+      <c r="G2091" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2091" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2092">
+      <c r="A2092" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2092" t="inlineStr">
+        <is>
+          <t>Camss</t>
+        </is>
+      </c>
+      <c r="C2092" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D2092" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2092" t="n">
+        <v>45</v>
+      </c>
+      <c r="F2092" t="n">
+        <v>190</v>
+      </c>
+      <c r="G2092" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2092" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2093">
+      <c r="A2093" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2093" t="inlineStr">
+        <is>
+          <t>BadrLeo</t>
+        </is>
+      </c>
+      <c r="C2093" t="inlineStr">
+        <is>
+          <t>Badr Leo</t>
+        </is>
+      </c>
+      <c r="D2093" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2093" t="n">
+        <v>46</v>
+      </c>
+      <c r="F2093" t="n">
+        <v>186</v>
+      </c>
+      <c r="G2093" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2093" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2094">
+      <c r="A2094" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2094" t="inlineStr">
+        <is>
+          <t>YassineZ95</t>
+        </is>
+      </c>
+      <c r="C2094" t="inlineStr">
+        <is>
+          <t>Yassine Z</t>
+        </is>
+      </c>
+      <c r="D2094" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2094" t="n">
+        <v>47</v>
+      </c>
+      <c r="F2094" t="n">
+        <v>186</v>
+      </c>
+      <c r="G2094" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2094" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2095">
+      <c r="A2095" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2095" t="inlineStr">
+        <is>
+          <t>Ilan_260_</t>
+        </is>
+      </c>
+      <c r="C2095" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ilann </t>
+        </is>
+      </c>
+      <c r="D2095" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2095" t="n">
+        <v>48</v>
+      </c>
+      <c r="F2095" t="n">
+        <v>185</v>
+      </c>
+      <c r="G2095" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2095" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2096">
+      <c r="A2096" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2096" t="inlineStr">
+        <is>
+          <t>abihuts</t>
+        </is>
+      </c>
+      <c r="C2096" t="inlineStr">
+        <is>
+          <t>Antonio Moctezuma</t>
+        </is>
+      </c>
+      <c r="D2096" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2096" t="n">
+        <v>49</v>
+      </c>
+      <c r="F2096" t="n">
+        <v>172</v>
+      </c>
+      <c r="G2096" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2096" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2097">
+      <c r="A2097" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2097" t="inlineStr">
+        <is>
+          <t>Chadia__</t>
+        </is>
+      </c>
+      <c r="C2097" t="inlineStr">
+        <is>
+          <t>Chadia</t>
+        </is>
+      </c>
+      <c r="D2097" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2097" t="n">
+        <v>50</v>
+      </c>
+      <c r="F2097" t="n">
+        <v>170</v>
+      </c>
+      <c r="G2097" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2097" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2098">
+      <c r="A2098" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2098" t="inlineStr">
+        <is>
+          <t>GOAT#UE2WM8M9</t>
+        </is>
+      </c>
+      <c r="C2098" t="inlineStr">
+        <is>
+          <t>Marilena</t>
+        </is>
+      </c>
+      <c r="D2098" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2098" t="n">
+        <v>51</v>
+      </c>
+      <c r="F2098" t="n">
+        <v>165</v>
+      </c>
+      <c r="G2098" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2098" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2099">
+      <c r="A2099" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2099" t="inlineStr">
+        <is>
+          <t>Ceciledp</t>
+        </is>
+      </c>
+      <c r="C2099" t="inlineStr">
+        <is>
+          <t>Cécile</t>
+        </is>
+      </c>
+      <c r="D2099" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2099" t="n">
+        <v>52</v>
+      </c>
+      <c r="F2099" t="n">
+        <v>145</v>
+      </c>
+      <c r="G2099" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2099" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2100">
+      <c r="A2100" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2100" t="inlineStr">
+        <is>
+          <t>Fuzo697</t>
+        </is>
+      </c>
+      <c r="C2100" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D2100" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2100" t="n">
+        <v>53</v>
+      </c>
+      <c r="F2100" t="n">
+        <v>145</v>
+      </c>
+      <c r="G2100" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2101" t="inlineStr">
+        <is>
+          <t>Yebri</t>
+        </is>
+      </c>
+      <c r="C2101" t="inlineStr">
+        <is>
+          <t>Brieuc</t>
+        </is>
+      </c>
+      <c r="D2101" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2101" t="n">
+        <v>54</v>
+      </c>
+      <c r="F2101" t="n">
+        <v>143</v>
+      </c>
+      <c r="G2101" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2101" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2102" t="inlineStr">
+        <is>
+          <t>Leo_durable</t>
+        </is>
+      </c>
+      <c r="C2102" t="inlineStr">
+        <is>
+          <t>Leo</t>
+        </is>
+      </c>
+      <c r="D2102" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2102" t="n">
+        <v>55</v>
+      </c>
+      <c r="F2102" t="n">
+        <v>143</v>
+      </c>
+      <c r="G2102" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2102" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2103" t="inlineStr">
+        <is>
+          <t>EmyEnzo</t>
+        </is>
+      </c>
+      <c r="C2103" t="inlineStr">
+        <is>
+          <t>Emilie</t>
+        </is>
+      </c>
+      <c r="D2103" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2103" t="n">
+        <v>56</v>
+      </c>
+      <c r="F2103" t="n">
+        <v>143</v>
+      </c>
+      <c r="G2103" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2103" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2104" t="inlineStr">
+        <is>
+          <t>Priscilla#4LCAF</t>
+        </is>
+      </c>
+      <c r="C2104" t="inlineStr">
+        <is>
+          <t>Priscilla</t>
+        </is>
+      </c>
+      <c r="D2104" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2104" t="n">
+        <v>57</v>
+      </c>
+      <c r="F2104" t="n">
+        <v>143</v>
+      </c>
+      <c r="G2104" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2104" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2105" t="inlineStr">
+        <is>
+          <t>Pipou931</t>
+        </is>
+      </c>
+      <c r="C2105" t="inlineStr">
+        <is>
+          <t>Juliie</t>
+        </is>
+      </c>
+      <c r="D2105" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2105" t="n">
+        <v>58</v>
+      </c>
+      <c r="F2105" t="n">
+        <v>143</v>
+      </c>
+      <c r="G2105" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2105" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2106" t="inlineStr">
+        <is>
+          <t>Farah_One</t>
+        </is>
+      </c>
+      <c r="C2106" t="inlineStr">
+        <is>
+          <t>Farah</t>
+        </is>
+      </c>
+      <c r="D2106" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2106" t="n">
+        <v>59</v>
+      </c>
+      <c r="F2106" t="n">
+        <v>143</v>
+      </c>
+      <c r="G2106" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2106" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2107" t="inlineStr">
+        <is>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="C2107" t="inlineStr">
+        <is>
+          <t>François</t>
+        </is>
+      </c>
+      <c r="D2107" t="inlineStr"/>
+      <c r="E2107" t="n">
+        <v>60</v>
+      </c>
+      <c r="F2107" t="n">
+        <v>143</v>
+      </c>
+      <c r="G2107" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2107" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2108" t="inlineStr">
+        <is>
+          <t>Seesee</t>
+        </is>
+      </c>
+      <c r="C2108" t="inlineStr">
+        <is>
+          <t>Selver</t>
+        </is>
+      </c>
+      <c r="D2108" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2108" t="n">
+        <v>61</v>
+      </c>
+      <c r="F2108" t="n">
+        <v>143</v>
+      </c>
+      <c r="G2108" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2108" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2109" t="inlineStr">
+        <is>
+          <t>lenaaik</t>
+        </is>
+      </c>
+      <c r="C2109" t="inlineStr">
+        <is>
+          <t>Lénaïk</t>
+        </is>
+      </c>
+      <c r="D2109" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2109" t="n">
+        <v>62</v>
+      </c>
+      <c r="F2109" t="n">
+        <v>143</v>
+      </c>
+      <c r="G2109" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2109" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2110" t="inlineStr">
+        <is>
+          <t>C4M</t>
+        </is>
+      </c>
+      <c r="C2110" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D2110" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2110" t="n">
+        <v>63</v>
+      </c>
+      <c r="F2110" t="n">
+        <v>143</v>
+      </c>
+      <c r="G2110" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2110" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2111" t="inlineStr">
+        <is>
+          <t>Rosa_1009</t>
+        </is>
+      </c>
+      <c r="C2111" t="inlineStr">
+        <is>
+          <t>Rosaline</t>
+        </is>
+      </c>
+      <c r="D2111" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2111" t="n">
+        <v>64</v>
+      </c>
+      <c r="F2111" t="n">
+        <v>143</v>
+      </c>
+      <c r="G2111" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2111" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2112" t="inlineStr">
+        <is>
+          <t>Elisewiss</t>
+        </is>
+      </c>
+      <c r="C2112" t="inlineStr">
+        <is>
+          <t>Elise</t>
+        </is>
+      </c>
+      <c r="D2112" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2112" t="n">
+        <v>65</v>
+      </c>
+      <c r="F2112" t="n">
+        <v>143</v>
+      </c>
+      <c r="G2112" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2112" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2113" t="inlineStr">
+        <is>
+          <t>Soraya-Y</t>
+        </is>
+      </c>
+      <c r="C2113" t="inlineStr">
+        <is>
+          <t>Soraya</t>
+        </is>
+      </c>
+      <c r="D2113" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2113" t="n">
+        <v>66</v>
+      </c>
+      <c r="F2113" t="n">
+        <v>143</v>
+      </c>
+      <c r="G2113" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2113" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2114" t="inlineStr">
+        <is>
+          <t>1993ahm</t>
+        </is>
+      </c>
+      <c r="C2114" t="inlineStr">
+        <is>
+          <t>Ahmed</t>
+        </is>
+      </c>
+      <c r="D2114" t="inlineStr"/>
+      <c r="E2114" t="n">
+        <v>67</v>
+      </c>
+      <c r="F2114" t="n">
+        <v>143</v>
+      </c>
+      <c r="G2114" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2114" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2115" t="inlineStr">
+        <is>
+          <t>Timy</t>
+        </is>
+      </c>
+      <c r="C2115" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="D2115" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2115" t="n">
+        <v>68</v>
+      </c>
+      <c r="F2115" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2115" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2116" t="inlineStr">
+        <is>
+          <t>JEVAISGAGNER10</t>
+        </is>
+      </c>
+      <c r="C2116" t="inlineStr">
+        <is>
+          <t>Xavier</t>
+        </is>
+      </c>
+      <c r="D2116" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2116" t="n">
+        <v>69</v>
+      </c>
+      <c r="F2116" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2116" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2117" t="inlineStr">
+        <is>
+          <t>HamzaG</t>
+        </is>
+      </c>
+      <c r="C2117" t="inlineStr">
+        <is>
+          <t>Hamza</t>
+        </is>
+      </c>
+      <c r="D2117" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2117" t="n">
+        <v>70</v>
+      </c>
+      <c r="F2117" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2117" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2118" t="inlineStr">
+        <is>
+          <t>LeaBrd</t>
+        </is>
+      </c>
+      <c r="C2118" t="inlineStr">
+        <is>
+          <t>Léa</t>
+        </is>
+      </c>
+      <c r="D2118" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2118" t="n">
+        <v>71</v>
+      </c>
+      <c r="F2118" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2118" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2119" t="inlineStr">
+        <is>
+          <t>davidd23</t>
+        </is>
+      </c>
+      <c r="C2119" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D2119" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2119" t="n">
+        <v>72</v>
+      </c>
+      <c r="F2119" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2119" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2120" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="C2120" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="D2120" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2120" t="n">
+        <v>73</v>
+      </c>
+      <c r="F2120" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2120" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2121" t="inlineStr">
+        <is>
+          <t>Kolas</t>
+        </is>
+      </c>
+      <c r="C2121" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D2121" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2121" t="n">
+        <v>74</v>
+      </c>
+      <c r="F2121" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2121" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2122" t="inlineStr">
+        <is>
+          <t>Laetice2020</t>
+        </is>
+      </c>
+      <c r="C2122" t="inlineStr">
+        <is>
+          <t>Laetitia</t>
+        </is>
+      </c>
+      <c r="D2122" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2122" t="n">
+        <v>75</v>
+      </c>
+      <c r="F2122" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2122" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2123" t="inlineStr">
+        <is>
+          <t>Emilay</t>
+        </is>
+      </c>
+      <c r="C2123" t="inlineStr">
+        <is>
+          <t>Émilie</t>
+        </is>
+      </c>
+      <c r="D2123" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2123" t="n">
+        <v>76</v>
+      </c>
+      <c r="F2123" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2123" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="A2124" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2124" t="inlineStr">
+        <is>
+          <t>Lyzone</t>
+        </is>
+      </c>
+      <c r="C2124" t="inlineStr">
+        <is>
+          <t>Lison</t>
+        </is>
+      </c>
+      <c r="D2124" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2124" t="n">
+        <v>77</v>
+      </c>
+      <c r="F2124" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2124" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2125" t="inlineStr">
+        <is>
+          <t>Melissagzb</t>
+        </is>
+      </c>
+      <c r="C2125" t="inlineStr">
+        <is>
+          <t>Melissa</t>
+        </is>
+      </c>
+      <c r="D2125" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2125" t="n">
+        <v>78</v>
+      </c>
+      <c r="F2125" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2125" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2126" t="inlineStr">
+        <is>
+          <t>Marie__92</t>
+        </is>
+      </c>
+      <c r="C2126" t="inlineStr">
+        <is>
+          <t>Marie</t>
+        </is>
+      </c>
+      <c r="D2126" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2126" t="n">
+        <v>79</v>
+      </c>
+      <c r="F2126" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2126" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2127">
+      <c r="A2127" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2127" t="inlineStr">
+        <is>
+          <t>K_Marp</t>
+        </is>
+      </c>
+      <c r="C2127" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
+      <c r="D2127" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2127" t="n">
+        <v>80</v>
+      </c>
+      <c r="F2127" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2127" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2128">
+      <c r="A2128" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2128" t="inlineStr">
+        <is>
+          <t>Cindie_JJA</t>
+        </is>
+      </c>
+      <c r="C2128" t="inlineStr">
+        <is>
+          <t>Cindie</t>
+        </is>
+      </c>
+      <c r="D2128" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2128" t="n">
+        <v>81</v>
+      </c>
+      <c r="F2128" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2128" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2129">
+      <c r="A2129" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2129" t="inlineStr">
+        <is>
+          <t>JKInternational</t>
+        </is>
+      </c>
+      <c r="C2129" t="inlineStr">
+        <is>
+          <t>Joachim</t>
+        </is>
+      </c>
+      <c r="D2129" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2129" t="n">
+        <v>82</v>
+      </c>
+      <c r="F2129" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2129" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2130">
+      <c r="A2130" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2130" t="inlineStr">
+        <is>
+          <t>GOAT#UE4U8KA6</t>
+        </is>
+      </c>
+      <c r="C2130" t="inlineStr">
+        <is>
+          <t>Jean Baptiste</t>
+        </is>
+      </c>
+      <c r="D2130" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2130" t="n">
+        <v>83</v>
+      </c>
+      <c r="F2130" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2130" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2131">
+      <c r="A2131" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2131" t="inlineStr">
+        <is>
+          <t>goat#AD6GS</t>
+        </is>
+      </c>
+      <c r="C2131" t="inlineStr">
+        <is>
+          <t>goat</t>
+        </is>
+      </c>
+      <c r="D2131" t="inlineStr"/>
+      <c r="E2131" t="n">
+        <v>84</v>
+      </c>
+      <c r="F2131" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2131" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2132">
+      <c r="A2132" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2132" t="inlineStr">
+        <is>
+          <t>Camillewbl</t>
+        </is>
+      </c>
+      <c r="C2132" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D2132" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2132" t="n">
+        <v>85</v>
+      </c>
+      <c r="F2132" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2132" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2133">
+      <c r="A2133" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2133" t="inlineStr">
+        <is>
+          <t>Emma_Noel</t>
+        </is>
+      </c>
+      <c r="C2133" t="inlineStr">
+        <is>
+          <t>Emma</t>
+        </is>
+      </c>
+      <c r="D2133" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2133" t="n">
+        <v>86</v>
+      </c>
+      <c r="F2133" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2133" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2134">
+      <c r="A2134" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2134" t="inlineStr">
+        <is>
+          <t>RBTL</t>
+        </is>
+      </c>
+      <c r="C2134" t="inlineStr">
+        <is>
+          <t>lea</t>
+        </is>
+      </c>
+      <c r="D2134" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2134" t="n">
+        <v>87</v>
+      </c>
+      <c r="F2134" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2134" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2135">
+      <c r="A2135" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2135" t="inlineStr">
+        <is>
+          <t>A-MOE</t>
+        </is>
+      </c>
+      <c r="C2135" t="inlineStr">
+        <is>
+          <t>Françoise</t>
+        </is>
+      </c>
+      <c r="D2135" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2135" t="n">
+        <v>88</v>
+      </c>
+      <c r="F2135" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2135" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2136">
+      <c r="A2136" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2136" t="inlineStr">
+        <is>
+          <t>Davido#4BZ54</t>
+        </is>
+      </c>
+      <c r="C2136" t="inlineStr">
+        <is>
+          <t>Davido</t>
+        </is>
+      </c>
+      <c r="D2136" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2136" t="n">
+        <v>89</v>
+      </c>
+      <c r="F2136" t="n">
+        <v>96</v>
+      </c>
+      <c r="G2136" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2137">
+      <c r="A2137" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2137" t="inlineStr">
+        <is>
+          <t>BrickXVI</t>
+        </is>
+      </c>
+      <c r="C2137" t="inlineStr">
+        <is>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="D2137" t="inlineStr"/>
+      <c r="E2137" t="n">
+        <v>90</v>
+      </c>
+      <c r="F2137" t="n">
+        <v>74</v>
+      </c>
+      <c r="G2137" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2138">
+      <c r="A2138" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2138" t="inlineStr">
+        <is>
+          <t>Taylor2901</t>
+        </is>
+      </c>
+      <c r="C2138" t="inlineStr">
+        <is>
+          <t>ousmane</t>
+        </is>
+      </c>
+      <c r="D2138" t="inlineStr"/>
+      <c r="E2138" t="n">
+        <v>91</v>
+      </c>
+      <c r="F2138" t="n">
+        <v>74</v>
+      </c>
+      <c r="G2138" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2139">
+      <c r="A2139" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2139" t="inlineStr">
+        <is>
+          <t>Ze_GOAT</t>
+        </is>
+      </c>
+      <c r="C2139" t="inlineStr">
+        <is>
+          <t>Yasser</t>
+        </is>
+      </c>
+      <c r="D2139" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2139" t="n">
+        <v>92</v>
+      </c>
+      <c r="F2139" t="n">
+        <v>69</v>
+      </c>
+      <c r="G2139" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2139" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2140">
+      <c r="A2140" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2140" t="inlineStr">
+        <is>
+          <t>Krol#4R8XC</t>
+        </is>
+      </c>
+      <c r="C2140" t="inlineStr">
+        <is>
+          <t>Krol</t>
+        </is>
+      </c>
+      <c r="D2140" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2140" t="n">
+        <v>93</v>
+      </c>
+      <c r="F2140" t="n">
+        <v>69</v>
+      </c>
+      <c r="G2140" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2140" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2141">
+      <c r="A2141" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2141" t="inlineStr">
+        <is>
+          <t>PacoSarra</t>
+        </is>
+      </c>
+      <c r="C2141" t="inlineStr">
+        <is>
+          <t>Ibra</t>
+        </is>
+      </c>
+      <c r="D2141" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2141" t="n">
+        <v>94</v>
+      </c>
+      <c r="F2141" t="n">
+        <v>69</v>
+      </c>
+      <c r="G2141" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2141" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2142">
+      <c r="A2142" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2142" t="inlineStr">
+        <is>
+          <t>Droit_au_but7723</t>
+        </is>
+      </c>
+      <c r="C2142" t="inlineStr">
+        <is>
+          <t>Calixthe</t>
+        </is>
+      </c>
+      <c r="D2142" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2142" t="n">
+        <v>95</v>
+      </c>
+      <c r="F2142" t="n">
+        <v>69</v>
+      </c>
+      <c r="G2142" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2142" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2143">
+      <c r="A2143" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2143" t="inlineStr">
+        <is>
+          <t>Ambrepic</t>
+        </is>
+      </c>
+      <c r="C2143" t="inlineStr">
+        <is>
+          <t>Ambre</t>
+        </is>
+      </c>
+      <c r="D2143" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2143" t="n">
+        <v>96</v>
+      </c>
+      <c r="F2143" t="n">
+        <v>69</v>
+      </c>
+      <c r="G2143" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2143" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2144">
+      <c r="A2144" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2144" t="inlineStr">
+        <is>
+          <t>PavelMel</t>
+        </is>
+      </c>
+      <c r="C2144" t="inlineStr">
+        <is>
+          <t>Mélissa</t>
+        </is>
+      </c>
+      <c r="D2144" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2144" t="n">
+        <v>97</v>
+      </c>
+      <c r="F2144" t="n">
+        <v>49</v>
+      </c>
+      <c r="G2144" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2145">
+      <c r="A2145" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2145" t="inlineStr">
+        <is>
+          <t>Mylene-Jnt</t>
+        </is>
+      </c>
+      <c r="C2145" t="inlineStr">
+        <is>
+          <t>Mylène</t>
+        </is>
+      </c>
+      <c r="D2145" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2145" t="n">
+        <v>98</v>
+      </c>
+      <c r="F2145" t="n">
+        <v>49</v>
+      </c>
+      <c r="G2145" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2146">
+      <c r="A2146" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2146" t="inlineStr">
+        <is>
+          <t>Teddbear</t>
+        </is>
+      </c>
+      <c r="C2146" t="inlineStr">
+        <is>
+          <t>Tedy</t>
+        </is>
+      </c>
+      <c r="D2146" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2146" t="n">
+        <v>99</v>
+      </c>
+      <c r="F2146" t="n">
+        <v>49</v>
+      </c>
+      <c r="G2146" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2147">
+      <c r="A2147" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2147" t="inlineStr">
+        <is>
+          <t>SabC1</t>
+        </is>
+      </c>
+      <c r="C2147" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="D2147" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2147" t="n">
+        <v>100</v>
+      </c>
+      <c r="F2147" t="n">
+        <v>49</v>
+      </c>
+      <c r="G2147" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2148">
+      <c r="A2148" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2148" t="inlineStr">
+        <is>
+          <t>KIKS999</t>
+        </is>
+      </c>
+      <c r="C2148" t="inlineStr">
+        <is>
+          <t>Killian</t>
+        </is>
+      </c>
+      <c r="D2148" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2148" t="n">
+        <v>101</v>
+      </c>
+      <c r="F2148" t="n">
+        <v>49</v>
+      </c>
+      <c r="G2148" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2149">
+      <c r="A2149" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2149" t="inlineStr">
+        <is>
+          <t>MxKnight</t>
+        </is>
+      </c>
+      <c r="C2149" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D2149" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2149" t="n">
+        <v>102</v>
+      </c>
+      <c r="F2149" t="n">
+        <v>49</v>
+      </c>
+      <c r="G2149" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2150">
+      <c r="A2150" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2150" t="inlineStr">
+        <is>
+          <t>RomainLect</t>
+        </is>
+      </c>
+      <c r="C2150" t="inlineStr">
+        <is>
+          <t>romain</t>
+        </is>
+      </c>
+      <c r="D2150" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2150" t="n">
+        <v>103</v>
+      </c>
+      <c r="F2150" t="n">
+        <v>49</v>
+      </c>
+      <c r="G2150" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2151">
+      <c r="A2151" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2151" t="inlineStr">
+        <is>
+          <t>SamSamH8</t>
+        </is>
+      </c>
+      <c r="C2151" t="inlineStr">
+        <is>
+          <t>Samia</t>
+        </is>
+      </c>
+      <c r="D2151" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2151" t="n">
+        <v>104</v>
+      </c>
+      <c r="F2151" t="n">
+        <v>49</v>
+      </c>
+      <c r="G2151" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2152">
+      <c r="A2152" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2152" t="inlineStr">
+        <is>
+          <t>Daviddesco1</t>
+        </is>
+      </c>
+      <c r="C2152" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D2152" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2152" t="n">
+        <v>105</v>
+      </c>
+      <c r="F2152" t="n">
+        <v>49</v>
+      </c>
+      <c r="G2152" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2153">
+      <c r="A2153" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2153" t="inlineStr">
+        <is>
+          <t>Sab_M45</t>
+        </is>
+      </c>
+      <c r="C2153" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="D2153" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2153" t="n">
+        <v>106</v>
+      </c>
+      <c r="F2153" t="n">
+        <v>49</v>
+      </c>
+      <c r="G2153" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2154">
+      <c r="A2154" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2154" t="inlineStr">
+        <is>
+          <t>Valentine___</t>
+        </is>
+      </c>
+      <c r="C2154" t="inlineStr">
+        <is>
+          <t>Valentine</t>
+        </is>
+      </c>
+      <c r="D2154" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2154" t="n">
+        <v>107</v>
+      </c>
+      <c r="F2154" t="n">
+        <v>49</v>
+      </c>
+      <c r="G2154" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2155">
+      <c r="A2155" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2155" t="inlineStr">
+        <is>
+          <t>PANENKANY</t>
+        </is>
+      </c>
+      <c r="C2155" t="inlineStr">
+        <is>
+          <t>Damien</t>
+        </is>
+      </c>
+      <c r="D2155" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2155" t="n">
+        <v>108</v>
+      </c>
+      <c r="F2155" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2155" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2156">
+      <c r="A2156" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B2156" t="inlineStr">
+        <is>
+          <t>MT35T</t>
+        </is>
+      </c>
+      <c r="C2156" t="inlineStr">
+        <is>
+          <t>Mathilde</t>
+        </is>
+      </c>
+      <c r="D2156" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2156" t="n">
+        <v>109</v>
+      </c>
+      <c r="F2156" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2156" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2156" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historique_joueurs.xlsx
+++ b/historique_joueurs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2156"/>
+  <dimension ref="A1:H2265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72196,6 +72196,3688 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2157">
+      <c r="A2157" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2157" t="inlineStr">
+        <is>
+          <t>Filipinho95</t>
+        </is>
+      </c>
+      <c r="C2157" t="inlineStr">
+        <is>
+          <t>Filipe</t>
+        </is>
+      </c>
+      <c r="D2157" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2157" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2157" t="n">
+        <v>552</v>
+      </c>
+      <c r="G2157" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2157" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2158">
+      <c r="A2158" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2158" t="inlineStr">
+        <is>
+          <t>Ninaaaa</t>
+        </is>
+      </c>
+      <c r="C2158" t="inlineStr">
+        <is>
+          <t>Nina</t>
+        </is>
+      </c>
+      <c r="D2158" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2158" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2158" t="n">
+        <v>542</v>
+      </c>
+      <c r="G2158" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2158" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2159">
+      <c r="A2159" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2159" t="inlineStr">
+        <is>
+          <t>Mamad_Shelter</t>
+        </is>
+      </c>
+      <c r="C2159" t="inlineStr">
+        <is>
+          <t>Mamadou</t>
+        </is>
+      </c>
+      <c r="D2159" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2159" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2159" t="n">
+        <v>498</v>
+      </c>
+      <c r="G2159" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2159" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2160">
+      <c r="A2160" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2160" t="inlineStr">
+        <is>
+          <t>SID-F-ANDRE</t>
+        </is>
+      </c>
+      <c r="C2160" t="inlineStr">
+        <is>
+          <t>Denis</t>
+        </is>
+      </c>
+      <c r="D2160" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2160" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2160" t="n">
+        <v>497</v>
+      </c>
+      <c r="G2160" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2160" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2161">
+      <c r="A2161" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2161" t="inlineStr">
+        <is>
+          <t>Panaff</t>
+        </is>
+      </c>
+      <c r="C2161" t="inlineStr">
+        <is>
+          <t>Panaf</t>
+        </is>
+      </c>
+      <c r="D2161" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2161" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2161" t="n">
+        <v>457</v>
+      </c>
+      <c r="G2161" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2161" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2162">
+      <c r="A2162" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2162" t="inlineStr">
+        <is>
+          <t>Coucoucassecou</t>
+        </is>
+      </c>
+      <c r="C2162" t="inlineStr">
+        <is>
+          <t>Brayen</t>
+        </is>
+      </c>
+      <c r="D2162" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2162" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2162" t="n">
+        <v>444</v>
+      </c>
+      <c r="G2162" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2162" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2163">
+      <c r="A2163" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2163" t="inlineStr">
+        <is>
+          <t>MyriamAmr</t>
+        </is>
+      </c>
+      <c r="C2163" t="inlineStr">
+        <is>
+          <t>Myriam</t>
+        </is>
+      </c>
+      <c r="D2163" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2163" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2163" t="n">
+        <v>440</v>
+      </c>
+      <c r="G2163" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2163" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2164">
+      <c r="A2164" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2164" t="inlineStr">
+        <is>
+          <t>Timy</t>
+        </is>
+      </c>
+      <c r="C2164" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="D2164" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2164" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2164" t="n">
+        <v>407</v>
+      </c>
+      <c r="G2164" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2164" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2165">
+      <c r="A2165" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2165" t="inlineStr">
+        <is>
+          <t>HamzaG</t>
+        </is>
+      </c>
+      <c r="C2165" t="inlineStr">
+        <is>
+          <t>Hamza</t>
+        </is>
+      </c>
+      <c r="D2165" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2165" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2165" t="n">
+        <v>407</v>
+      </c>
+      <c r="G2165" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2165" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2166">
+      <c r="A2166" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2166" t="inlineStr">
+        <is>
+          <t>Nonito20</t>
+        </is>
+      </c>
+      <c r="C2166" t="inlineStr">
+        <is>
+          <t>Arnaud</t>
+        </is>
+      </c>
+      <c r="D2166" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2166" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2166" t="n">
+        <v>406</v>
+      </c>
+      <c r="G2166" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2166" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2167">
+      <c r="A2167" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2167" t="inlineStr">
+        <is>
+          <t>BOUGA#2JGXP</t>
+        </is>
+      </c>
+      <c r="C2167" t="inlineStr">
+        <is>
+          <t>BOUGA</t>
+        </is>
+      </c>
+      <c r="D2167" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2167" t="n">
+        <v>11</v>
+      </c>
+      <c r="F2167" t="n">
+        <v>402</v>
+      </c>
+      <c r="G2167" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2167" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2168">
+      <c r="A2168" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2168" t="inlineStr">
+        <is>
+          <t>Anais757817</t>
+        </is>
+      </c>
+      <c r="C2168" t="inlineStr">
+        <is>
+          <t>Anaïs</t>
+        </is>
+      </c>
+      <c r="D2168" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2168" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2168" t="n">
+        <v>402</v>
+      </c>
+      <c r="G2168" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2168" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2169">
+      <c r="A2169" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2169" t="inlineStr">
+        <is>
+          <t>Gronaldo_95</t>
+        </is>
+      </c>
+      <c r="C2169" t="inlineStr">
+        <is>
+          <t>Gronaldo</t>
+        </is>
+      </c>
+      <c r="D2169" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2169" t="n">
+        <v>13</v>
+      </c>
+      <c r="F2169" t="n">
+        <v>381</v>
+      </c>
+      <c r="G2169" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2169" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2170">
+      <c r="A2170" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2170" t="inlineStr">
+        <is>
+          <t>catherine#5FRTD</t>
+        </is>
+      </c>
+      <c r="C2170" t="inlineStr">
+        <is>
+          <t>catherine</t>
+        </is>
+      </c>
+      <c r="D2170" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2170" t="n">
+        <v>14</v>
+      </c>
+      <c r="F2170" t="n">
+        <v>381</v>
+      </c>
+      <c r="G2170" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2170" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2171">
+      <c r="A2171" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2171" t="inlineStr">
+        <is>
+          <t>Leandrocp</t>
+        </is>
+      </c>
+      <c r="C2171" t="inlineStr">
+        <is>
+          <t>Leandro</t>
+        </is>
+      </c>
+      <c r="D2171" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2171" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2171" t="n">
+        <v>381</v>
+      </c>
+      <c r="G2171" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2171" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2172">
+      <c r="A2172" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2172" t="inlineStr">
+        <is>
+          <t>Marion1822</t>
+        </is>
+      </c>
+      <c r="C2172" t="inlineStr">
+        <is>
+          <t>Marion</t>
+        </is>
+      </c>
+      <c r="D2172" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2172" t="n">
+        <v>16</v>
+      </c>
+      <c r="F2172" t="n">
+        <v>381</v>
+      </c>
+      <c r="G2172" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2172" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2173">
+      <c r="A2173" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2173" t="inlineStr">
+        <is>
+          <t>chaychaychay</t>
+        </is>
+      </c>
+      <c r="C2173" t="inlineStr">
+        <is>
+          <t>Chaymaa</t>
+        </is>
+      </c>
+      <c r="D2173" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2173" t="n">
+        <v>17</v>
+      </c>
+      <c r="F2173" t="n">
+        <v>381</v>
+      </c>
+      <c r="G2173" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2173" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2174">
+      <c r="A2174" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2174" t="inlineStr">
+        <is>
+          <t>MargauxCtln</t>
+        </is>
+      </c>
+      <c r="C2174" t="inlineStr">
+        <is>
+          <t>Margaux</t>
+        </is>
+      </c>
+      <c r="D2174" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2174" t="n">
+        <v>18</v>
+      </c>
+      <c r="F2174" t="n">
+        <v>376</v>
+      </c>
+      <c r="G2174" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2174" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2175">
+      <c r="A2175" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2175" t="inlineStr">
+        <is>
+          <t>MagicMath</t>
+        </is>
+      </c>
+      <c r="C2175" t="inlineStr">
+        <is>
+          <t>Mathieu</t>
+        </is>
+      </c>
+      <c r="D2175" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2175" t="n">
+        <v>19</v>
+      </c>
+      <c r="F2175" t="n">
+        <v>376</v>
+      </c>
+      <c r="G2175" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2175" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2176">
+      <c r="A2176" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2176" t="inlineStr">
+        <is>
+          <t>Maruyama</t>
+        </is>
+      </c>
+      <c r="C2176" t="inlineStr">
+        <is>
+          <t>Gabrielle</t>
+        </is>
+      </c>
+      <c r="D2176" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2176" t="n">
+        <v>20</v>
+      </c>
+      <c r="F2176" t="n">
+        <v>361</v>
+      </c>
+      <c r="G2176" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2176" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2177">
+      <c r="A2177" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2177" t="inlineStr">
+        <is>
+          <t>WalidSiuuuuu</t>
+        </is>
+      </c>
+      <c r="C2177" t="inlineStr">
+        <is>
+          <t>Walid</t>
+        </is>
+      </c>
+      <c r="D2177" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2177" t="n">
+        <v>21</v>
+      </c>
+      <c r="F2177" t="n">
+        <v>356</v>
+      </c>
+      <c r="G2177" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2177" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2178">
+      <c r="A2178" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2178" t="inlineStr">
+        <is>
+          <t>DJOSWA</t>
+        </is>
+      </c>
+      <c r="C2178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oswaina </t>
+        </is>
+      </c>
+      <c r="D2178" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2178" t="n">
+        <v>22</v>
+      </c>
+      <c r="F2178" t="n">
+        <v>356</v>
+      </c>
+      <c r="G2178" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2178" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2179">
+      <c r="A2179" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2179" t="inlineStr">
+        <is>
+          <t>AudreyB225</t>
+        </is>
+      </c>
+      <c r="C2179" t="inlineStr">
+        <is>
+          <t>Audrey</t>
+        </is>
+      </c>
+      <c r="D2179" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2179" t="n">
+        <v>23</v>
+      </c>
+      <c r="F2179" t="n">
+        <v>332</v>
+      </c>
+      <c r="G2179" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2179" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2180">
+      <c r="A2180" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2180" t="inlineStr">
+        <is>
+          <t>ChrisKr1Deg1</t>
+        </is>
+      </c>
+      <c r="C2180" t="inlineStr">
+        <is>
+          <t>christophe</t>
+        </is>
+      </c>
+      <c r="D2180" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2180" t="n">
+        <v>24</v>
+      </c>
+      <c r="F2180" t="n">
+        <v>323</v>
+      </c>
+      <c r="G2180" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2180" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2181">
+      <c r="A2181" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2181" t="inlineStr">
+        <is>
+          <t>Paulasipi1998</t>
+        </is>
+      </c>
+      <c r="C2181" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="D2181" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2181" t="n">
+        <v>25</v>
+      </c>
+      <c r="F2181" t="n">
+        <v>322</v>
+      </c>
+      <c r="G2181" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2181" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2182">
+      <c r="A2182" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2182" t="inlineStr">
+        <is>
+          <t>BadrLeo</t>
+        </is>
+      </c>
+      <c r="C2182" t="inlineStr">
+        <is>
+          <t>Badr Leo</t>
+        </is>
+      </c>
+      <c r="D2182" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2182" t="n">
+        <v>26</v>
+      </c>
+      <c r="F2182" t="n">
+        <v>308</v>
+      </c>
+      <c r="G2182" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2182" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2183">
+      <c r="A2183" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2183" t="inlineStr">
+        <is>
+          <t>Ilan_260_</t>
+        </is>
+      </c>
+      <c r="C2183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ilann </t>
+        </is>
+      </c>
+      <c r="D2183" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2183" t="n">
+        <v>27</v>
+      </c>
+      <c r="F2183" t="n">
+        <v>307</v>
+      </c>
+      <c r="G2183" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2183" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2184">
+      <c r="A2184" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2184" t="inlineStr">
+        <is>
+          <t>Stephbreton</t>
+        </is>
+      </c>
+      <c r="C2184" t="inlineStr">
+        <is>
+          <t>STEPHANE</t>
+        </is>
+      </c>
+      <c r="D2184" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2184" t="n">
+        <v>28</v>
+      </c>
+      <c r="F2184" t="n">
+        <v>307</v>
+      </c>
+      <c r="G2184" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2184" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2185">
+      <c r="A2185" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2185" t="inlineStr">
+        <is>
+          <t>Kaliced</t>
+        </is>
+      </c>
+      <c r="C2185" t="inlineStr">
+        <is>
+          <t>Kalice</t>
+        </is>
+      </c>
+      <c r="D2185" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2185" t="n">
+        <v>29</v>
+      </c>
+      <c r="F2185" t="n">
+        <v>302</v>
+      </c>
+      <c r="G2185" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2185" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2186">
+      <c r="A2186" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2186" t="inlineStr">
+        <is>
+          <t>Leo_durable</t>
+        </is>
+      </c>
+      <c r="C2186" t="inlineStr">
+        <is>
+          <t>Leo</t>
+        </is>
+      </c>
+      <c r="D2186" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2186" t="n">
+        <v>30</v>
+      </c>
+      <c r="F2186" t="n">
+        <v>285</v>
+      </c>
+      <c r="G2186" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2186" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2187">
+      <c r="A2187" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2187" t="inlineStr">
+        <is>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="C2187" t="inlineStr">
+        <is>
+          <t>François</t>
+        </is>
+      </c>
+      <c r="D2187" t="inlineStr"/>
+      <c r="E2187" t="n">
+        <v>31</v>
+      </c>
+      <c r="F2187" t="n">
+        <v>285</v>
+      </c>
+      <c r="G2187" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2187" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2188">
+      <c r="A2188" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2188" t="inlineStr">
+        <is>
+          <t>FRHTCTD10</t>
+        </is>
+      </c>
+      <c r="C2188" t="inlineStr">
+        <is>
+          <t>Candice</t>
+        </is>
+      </c>
+      <c r="D2188" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2188" t="n">
+        <v>32</v>
+      </c>
+      <c r="F2188" t="n">
+        <v>282</v>
+      </c>
+      <c r="G2188" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2188" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2189">
+      <c r="A2189" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2189" t="inlineStr">
+        <is>
+          <t>Mr-Worldwide</t>
+        </is>
+      </c>
+      <c r="C2189" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="D2189" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2189" t="n">
+        <v>33</v>
+      </c>
+      <c r="F2189" t="n">
+        <v>280</v>
+      </c>
+      <c r="G2189" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2189" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2190">
+      <c r="A2190" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2190" t="inlineStr">
+        <is>
+          <t>Fethinho</t>
+        </is>
+      </c>
+      <c r="C2190" t="inlineStr">
+        <is>
+          <t>Fethi</t>
+        </is>
+      </c>
+      <c r="D2190" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2190" t="n">
+        <v>34</v>
+      </c>
+      <c r="F2190" t="n">
+        <v>280</v>
+      </c>
+      <c r="G2190" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2190" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2191">
+      <c r="A2191" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2191" t="inlineStr">
+        <is>
+          <t>Ouiouiausoleil</t>
+        </is>
+      </c>
+      <c r="C2191" t="inlineStr">
+        <is>
+          <t>Ouissal</t>
+        </is>
+      </c>
+      <c r="D2191" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2191" t="n">
+        <v>35</v>
+      </c>
+      <c r="F2191" t="n">
+        <v>280</v>
+      </c>
+      <c r="G2191" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2191" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2192">
+      <c r="A2192" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2192" t="inlineStr">
+        <is>
+          <t>Yebri</t>
+        </is>
+      </c>
+      <c r="C2192" t="inlineStr">
+        <is>
+          <t>Brieuc</t>
+        </is>
+      </c>
+      <c r="D2192" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2192" t="n">
+        <v>36</v>
+      </c>
+      <c r="F2192" t="n">
+        <v>265</v>
+      </c>
+      <c r="G2192" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2192" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2193">
+      <c r="A2193" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2193" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="C2193" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="D2193" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2193" t="n">
+        <v>37</v>
+      </c>
+      <c r="F2193" t="n">
+        <v>265</v>
+      </c>
+      <c r="G2193" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2193" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2194">
+      <c r="A2194" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2194" t="inlineStr">
+        <is>
+          <t>Kolas</t>
+        </is>
+      </c>
+      <c r="C2194" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D2194" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2194" t="n">
+        <v>38</v>
+      </c>
+      <c r="F2194" t="n">
+        <v>265</v>
+      </c>
+      <c r="G2194" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2194" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2195">
+      <c r="A2195" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2195" t="inlineStr">
+        <is>
+          <t>JKInternational</t>
+        </is>
+      </c>
+      <c r="C2195" t="inlineStr">
+        <is>
+          <t>Joachim</t>
+        </is>
+      </c>
+      <c r="D2195" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2195" t="n">
+        <v>39</v>
+      </c>
+      <c r="F2195" t="n">
+        <v>265</v>
+      </c>
+      <c r="G2195" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2195" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2196">
+      <c r="A2196" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2196" t="inlineStr">
+        <is>
+          <t>GOAT#UE4U8KA6</t>
+        </is>
+      </c>
+      <c r="C2196" t="inlineStr">
+        <is>
+          <t>Jean Baptiste</t>
+        </is>
+      </c>
+      <c r="D2196" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2196" t="n">
+        <v>40</v>
+      </c>
+      <c r="F2196" t="n">
+        <v>265</v>
+      </c>
+      <c r="G2196" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2196" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2197">
+      <c r="A2197" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2197" t="inlineStr">
+        <is>
+          <t>Soraya-Y</t>
+        </is>
+      </c>
+      <c r="C2197" t="inlineStr">
+        <is>
+          <t>Soraya</t>
+        </is>
+      </c>
+      <c r="D2197" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2197" t="n">
+        <v>41</v>
+      </c>
+      <c r="F2197" t="n">
+        <v>265</v>
+      </c>
+      <c r="G2197" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2197" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2198">
+      <c r="A2198" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2198" t="inlineStr">
+        <is>
+          <t>1993ahm</t>
+        </is>
+      </c>
+      <c r="C2198" t="inlineStr">
+        <is>
+          <t>Ahmed</t>
+        </is>
+      </c>
+      <c r="D2198" t="inlineStr"/>
+      <c r="E2198" t="n">
+        <v>42</v>
+      </c>
+      <c r="F2198" t="n">
+        <v>265</v>
+      </c>
+      <c r="G2198" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2198" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2199">
+      <c r="A2199" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2199" t="inlineStr">
+        <is>
+          <t>MatuRenard</t>
+        </is>
+      </c>
+      <c r="C2199" t="inlineStr">
+        <is>
+          <t>Mathias</t>
+        </is>
+      </c>
+      <c r="D2199" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2199" t="n">
+        <v>43</v>
+      </c>
+      <c r="F2199" t="n">
+        <v>259</v>
+      </c>
+      <c r="G2199" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2199" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2200">
+      <c r="A2200" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2200" t="inlineStr">
+        <is>
+          <t>Liliuus</t>
+        </is>
+      </c>
+      <c r="C2200" t="inlineStr">
+        <is>
+          <t>Lilia</t>
+        </is>
+      </c>
+      <c r="D2200" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2200" t="n">
+        <v>44</v>
+      </c>
+      <c r="F2200" t="n">
+        <v>259</v>
+      </c>
+      <c r="G2200" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2200" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2201">
+      <c r="A2201" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2201" t="inlineStr">
+        <is>
+          <t>Ppo28</t>
+        </is>
+      </c>
+      <c r="C2201" t="inlineStr">
+        <is>
+          <t>Prescylla</t>
+        </is>
+      </c>
+      <c r="D2201" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2201" t="n">
+        <v>45</v>
+      </c>
+      <c r="F2201" t="n">
+        <v>259</v>
+      </c>
+      <c r="G2201" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2201" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2202">
+      <c r="A2202" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2202" t="inlineStr">
+        <is>
+          <t>Devilrock95</t>
+        </is>
+      </c>
+      <c r="C2202" t="inlineStr">
+        <is>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="D2202" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2202" t="n">
+        <v>46</v>
+      </c>
+      <c r="F2202" t="n">
+        <v>239</v>
+      </c>
+      <c r="G2202" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2202" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2203">
+      <c r="A2203" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2203" t="inlineStr">
+        <is>
+          <t>Cleem22</t>
+        </is>
+      </c>
+      <c r="C2203" t="inlineStr">
+        <is>
+          <t>Clemence</t>
+        </is>
+      </c>
+      <c r="D2203" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2203" t="n">
+        <v>47</v>
+      </c>
+      <c r="F2203" t="n">
+        <v>239</v>
+      </c>
+      <c r="G2203" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2203" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2204">
+      <c r="A2204" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2204" t="inlineStr">
+        <is>
+          <t>WIL1610</t>
+        </is>
+      </c>
+      <c r="C2204" t="inlineStr">
+        <is>
+          <t>William</t>
+        </is>
+      </c>
+      <c r="D2204" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2204" t="n">
+        <v>48</v>
+      </c>
+      <c r="F2204" t="n">
+        <v>233</v>
+      </c>
+      <c r="G2204" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2204" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2205">
+      <c r="A2205" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2205" t="inlineStr">
+        <is>
+          <t>Erwan#4G91X</t>
+        </is>
+      </c>
+      <c r="C2205" t="inlineStr">
+        <is>
+          <t>Erwan</t>
+        </is>
+      </c>
+      <c r="D2205" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2205" t="n">
+        <v>49</v>
+      </c>
+      <c r="F2205" t="n">
+        <v>219</v>
+      </c>
+      <c r="G2205" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2205" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2206">
+      <c r="A2206" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2206" t="inlineStr">
+        <is>
+          <t>GLR_PRIME</t>
+        </is>
+      </c>
+      <c r="C2206" t="inlineStr">
+        <is>
+          <t>Gabriel</t>
+        </is>
+      </c>
+      <c r="D2206" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2206" t="n">
+        <v>50</v>
+      </c>
+      <c r="F2206" t="n">
+        <v>219</v>
+      </c>
+      <c r="G2206" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2206" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2207">
+      <c r="A2207" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2207" t="inlineStr">
+        <is>
+          <t>Davido#4BZ54</t>
+        </is>
+      </c>
+      <c r="C2207" t="inlineStr">
+        <is>
+          <t>Davido</t>
+        </is>
+      </c>
+      <c r="D2207" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2207" t="n">
+        <v>51</v>
+      </c>
+      <c r="F2207" t="n">
+        <v>218</v>
+      </c>
+      <c r="G2207" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2207" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2208">
+      <c r="A2208" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2208" t="inlineStr">
+        <is>
+          <t>Exia95</t>
+        </is>
+      </c>
+      <c r="C2208" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D2208" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2208" t="n">
+        <v>52</v>
+      </c>
+      <c r="F2208" t="n">
+        <v>212</v>
+      </c>
+      <c r="G2208" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2208" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2209">
+      <c r="A2209" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2209" t="inlineStr">
+        <is>
+          <t>Krol#4R8XC</t>
+        </is>
+      </c>
+      <c r="C2209" t="inlineStr">
+        <is>
+          <t>Krol</t>
+        </is>
+      </c>
+      <c r="D2209" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2209" t="n">
+        <v>53</v>
+      </c>
+      <c r="F2209" t="n">
+        <v>211</v>
+      </c>
+      <c r="G2209" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2209" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2210">
+      <c r="A2210" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2210" t="inlineStr">
+        <is>
+          <t>Matt#4B4CU</t>
+        </is>
+      </c>
+      <c r="C2210" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="D2210" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2210" t="n">
+        <v>54</v>
+      </c>
+      <c r="F2210" t="n">
+        <v>211</v>
+      </c>
+      <c r="G2210" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2210" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2211">
+      <c r="A2211" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2211" t="inlineStr">
+        <is>
+          <t>dian-bgt</t>
+        </is>
+      </c>
+      <c r="C2211" t="inlineStr">
+        <is>
+          <t>Diane</t>
+        </is>
+      </c>
+      <c r="D2211" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2211" t="n">
+        <v>55</v>
+      </c>
+      <c r="F2211" t="n">
+        <v>206</v>
+      </c>
+      <c r="G2211" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2211" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2212">
+      <c r="A2212" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2212" t="inlineStr">
+        <is>
+          <t>LilianeB</t>
+        </is>
+      </c>
+      <c r="C2212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liliane </t>
+        </is>
+      </c>
+      <c r="D2212" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2212" t="n">
+        <v>56</v>
+      </c>
+      <c r="F2212" t="n">
+        <v>206</v>
+      </c>
+      <c r="G2212" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2212" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2213">
+      <c r="A2213" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2213" t="inlineStr">
+        <is>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="C2213" t="inlineStr">
+        <is>
+          <t>Julie</t>
+        </is>
+      </c>
+      <c r="D2213" t="inlineStr"/>
+      <c r="E2213" t="n">
+        <v>57</v>
+      </c>
+      <c r="F2213" t="n">
+        <v>206</v>
+      </c>
+      <c r="G2213" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2213" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2214">
+      <c r="A2214" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2214" t="inlineStr">
+        <is>
+          <t>Ambrepic</t>
+        </is>
+      </c>
+      <c r="C2214" t="inlineStr">
+        <is>
+          <t>Ambre</t>
+        </is>
+      </c>
+      <c r="D2214" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2214" t="n">
+        <v>58</v>
+      </c>
+      <c r="F2214" t="n">
+        <v>191</v>
+      </c>
+      <c r="G2214" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2214" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2215">
+      <c r="A2215" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2215" t="inlineStr">
+        <is>
+          <t>Romain_JO</t>
+        </is>
+      </c>
+      <c r="C2215" t="inlineStr">
+        <is>
+          <t>Romain J</t>
+        </is>
+      </c>
+      <c r="D2215" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2215" t="n">
+        <v>59</v>
+      </c>
+      <c r="F2215" t="n">
+        <v>191</v>
+      </c>
+      <c r="G2215" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2215" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2216">
+      <c r="A2216" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2216" t="inlineStr">
+        <is>
+          <t>JeremFZ</t>
+        </is>
+      </c>
+      <c r="C2216" t="inlineStr">
+        <is>
+          <t>Jérémy</t>
+        </is>
+      </c>
+      <c r="D2216" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2216" t="n">
+        <v>60</v>
+      </c>
+      <c r="F2216" t="n">
+        <v>191</v>
+      </c>
+      <c r="G2216" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2216" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2217">
+      <c r="A2217" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2217" t="inlineStr">
+        <is>
+          <t>Camss</t>
+        </is>
+      </c>
+      <c r="C2217" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D2217" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2217" t="n">
+        <v>61</v>
+      </c>
+      <c r="F2217" t="n">
+        <v>190</v>
+      </c>
+      <c r="G2217" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2217" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2218">
+      <c r="A2218" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2218" t="inlineStr">
+        <is>
+          <t>YassineZ95</t>
+        </is>
+      </c>
+      <c r="C2218" t="inlineStr">
+        <is>
+          <t>Yassine Z</t>
+        </is>
+      </c>
+      <c r="D2218" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2218" t="n">
+        <v>62</v>
+      </c>
+      <c r="F2218" t="n">
+        <v>186</v>
+      </c>
+      <c r="G2218" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2218" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2219">
+      <c r="A2219" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2219" t="inlineStr">
+        <is>
+          <t>abihuts</t>
+        </is>
+      </c>
+      <c r="C2219" t="inlineStr">
+        <is>
+          <t>Antonio Moctezuma</t>
+        </is>
+      </c>
+      <c r="D2219" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2219" t="n">
+        <v>63</v>
+      </c>
+      <c r="F2219" t="n">
+        <v>172</v>
+      </c>
+      <c r="G2219" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2219" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2220">
+      <c r="A2220" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2220" t="inlineStr">
+        <is>
+          <t>Mylene-Jnt</t>
+        </is>
+      </c>
+      <c r="C2220" t="inlineStr">
+        <is>
+          <t>Mylène</t>
+        </is>
+      </c>
+      <c r="D2220" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2220" t="n">
+        <v>64</v>
+      </c>
+      <c r="F2220" t="n">
+        <v>171</v>
+      </c>
+      <c r="G2220" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2220" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2221">
+      <c r="A2221" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2221" t="inlineStr">
+        <is>
+          <t>Daviddesco1</t>
+        </is>
+      </c>
+      <c r="C2221" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D2221" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2221" t="n">
+        <v>65</v>
+      </c>
+      <c r="F2221" t="n">
+        <v>171</v>
+      </c>
+      <c r="G2221" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2221" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2222">
+      <c r="A2222" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2222" t="inlineStr">
+        <is>
+          <t>Chadia__</t>
+        </is>
+      </c>
+      <c r="C2222" t="inlineStr">
+        <is>
+          <t>Chadia</t>
+        </is>
+      </c>
+      <c r="D2222" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2222" t="n">
+        <v>66</v>
+      </c>
+      <c r="F2222" t="n">
+        <v>170</v>
+      </c>
+      <c r="G2222" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2222" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2223">
+      <c r="A2223" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2223" t="inlineStr">
+        <is>
+          <t>GOAT#UE2WM8M9</t>
+        </is>
+      </c>
+      <c r="C2223" t="inlineStr">
+        <is>
+          <t>Marilena</t>
+        </is>
+      </c>
+      <c r="D2223" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2223" t="n">
+        <v>67</v>
+      </c>
+      <c r="F2223" t="n">
+        <v>165</v>
+      </c>
+      <c r="G2223" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2223" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2224">
+      <c r="A2224" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2224" t="inlineStr">
+        <is>
+          <t>Ceciledp</t>
+        </is>
+      </c>
+      <c r="C2224" t="inlineStr">
+        <is>
+          <t>Cécile</t>
+        </is>
+      </c>
+      <c r="D2224" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2224" t="n">
+        <v>68</v>
+      </c>
+      <c r="F2224" t="n">
+        <v>145</v>
+      </c>
+      <c r="G2224" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2224" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2225">
+      <c r="A2225" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2225" t="inlineStr">
+        <is>
+          <t>Fuzo697</t>
+        </is>
+      </c>
+      <c r="C2225" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D2225" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2225" t="n">
+        <v>69</v>
+      </c>
+      <c r="F2225" t="n">
+        <v>145</v>
+      </c>
+      <c r="G2225" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2225" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2226">
+      <c r="A2226" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2226" t="inlineStr">
+        <is>
+          <t>EmyEnzo</t>
+        </is>
+      </c>
+      <c r="C2226" t="inlineStr">
+        <is>
+          <t>Emilie</t>
+        </is>
+      </c>
+      <c r="D2226" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2226" t="n">
+        <v>70</v>
+      </c>
+      <c r="F2226" t="n">
+        <v>143</v>
+      </c>
+      <c r="G2226" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2226" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2227">
+      <c r="A2227" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2227" t="inlineStr">
+        <is>
+          <t>Priscilla#4LCAF</t>
+        </is>
+      </c>
+      <c r="C2227" t="inlineStr">
+        <is>
+          <t>Priscilla</t>
+        </is>
+      </c>
+      <c r="D2227" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2227" t="n">
+        <v>71</v>
+      </c>
+      <c r="F2227" t="n">
+        <v>143</v>
+      </c>
+      <c r="G2227" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2227" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2228">
+      <c r="A2228" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2228" t="inlineStr">
+        <is>
+          <t>Pipou931</t>
+        </is>
+      </c>
+      <c r="C2228" t="inlineStr">
+        <is>
+          <t>Juliie</t>
+        </is>
+      </c>
+      <c r="D2228" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2228" t="n">
+        <v>72</v>
+      </c>
+      <c r="F2228" t="n">
+        <v>143</v>
+      </c>
+      <c r="G2228" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2228" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2229">
+      <c r="A2229" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2229" t="inlineStr">
+        <is>
+          <t>Farah_One</t>
+        </is>
+      </c>
+      <c r="C2229" t="inlineStr">
+        <is>
+          <t>Farah</t>
+        </is>
+      </c>
+      <c r="D2229" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2229" t="n">
+        <v>73</v>
+      </c>
+      <c r="F2229" t="n">
+        <v>143</v>
+      </c>
+      <c r="G2229" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2229" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2230">
+      <c r="A2230" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2230" t="inlineStr">
+        <is>
+          <t>Seesee</t>
+        </is>
+      </c>
+      <c r="C2230" t="inlineStr">
+        <is>
+          <t>Selver</t>
+        </is>
+      </c>
+      <c r="D2230" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2230" t="n">
+        <v>74</v>
+      </c>
+      <c r="F2230" t="n">
+        <v>143</v>
+      </c>
+      <c r="G2230" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2230" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2231">
+      <c r="A2231" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2231" t="inlineStr">
+        <is>
+          <t>lenaaik</t>
+        </is>
+      </c>
+      <c r="C2231" t="inlineStr">
+        <is>
+          <t>Lénaïk</t>
+        </is>
+      </c>
+      <c r="D2231" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2231" t="n">
+        <v>75</v>
+      </c>
+      <c r="F2231" t="n">
+        <v>143</v>
+      </c>
+      <c r="G2231" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2231" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2232">
+      <c r="A2232" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2232" t="inlineStr">
+        <is>
+          <t>C4M</t>
+        </is>
+      </c>
+      <c r="C2232" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D2232" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2232" t="n">
+        <v>76</v>
+      </c>
+      <c r="F2232" t="n">
+        <v>143</v>
+      </c>
+      <c r="G2232" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2232" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2233">
+      <c r="A2233" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2233" t="inlineStr">
+        <is>
+          <t>Rosa_1009</t>
+        </is>
+      </c>
+      <c r="C2233" t="inlineStr">
+        <is>
+          <t>Rosaline</t>
+        </is>
+      </c>
+      <c r="D2233" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2233" t="n">
+        <v>77</v>
+      </c>
+      <c r="F2233" t="n">
+        <v>143</v>
+      </c>
+      <c r="G2233" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2233" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2234">
+      <c r="A2234" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2234" t="inlineStr">
+        <is>
+          <t>Elisewiss</t>
+        </is>
+      </c>
+      <c r="C2234" t="inlineStr">
+        <is>
+          <t>Elise</t>
+        </is>
+      </c>
+      <c r="D2234" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2234" t="n">
+        <v>78</v>
+      </c>
+      <c r="F2234" t="n">
+        <v>143</v>
+      </c>
+      <c r="G2234" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2234" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2235">
+      <c r="A2235" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2235" t="inlineStr">
+        <is>
+          <t>JEVAISGAGNER10</t>
+        </is>
+      </c>
+      <c r="C2235" t="inlineStr">
+        <is>
+          <t>Xavier</t>
+        </is>
+      </c>
+      <c r="D2235" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2235" t="n">
+        <v>79</v>
+      </c>
+      <c r="F2235" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2235" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2235" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2236">
+      <c r="A2236" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2236" t="inlineStr">
+        <is>
+          <t>LeaBrd</t>
+        </is>
+      </c>
+      <c r="C2236" t="inlineStr">
+        <is>
+          <t>Léa</t>
+        </is>
+      </c>
+      <c r="D2236" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2236" t="n">
+        <v>80</v>
+      </c>
+      <c r="F2236" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2236" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2236" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2237">
+      <c r="A2237" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2237" t="inlineStr">
+        <is>
+          <t>davidd23</t>
+        </is>
+      </c>
+      <c r="C2237" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D2237" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2237" t="n">
+        <v>81</v>
+      </c>
+      <c r="F2237" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2237" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2237" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2238">
+      <c r="A2238" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2238" t="inlineStr">
+        <is>
+          <t>Laetice2020</t>
+        </is>
+      </c>
+      <c r="C2238" t="inlineStr">
+        <is>
+          <t>Laetitia</t>
+        </is>
+      </c>
+      <c r="D2238" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2238" t="n">
+        <v>82</v>
+      </c>
+      <c r="F2238" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2238" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2238" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2239">
+      <c r="A2239" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2239" t="inlineStr">
+        <is>
+          <t>Emilay</t>
+        </is>
+      </c>
+      <c r="C2239" t="inlineStr">
+        <is>
+          <t>Émilie</t>
+        </is>
+      </c>
+      <c r="D2239" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2239" t="n">
+        <v>83</v>
+      </c>
+      <c r="F2239" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2239" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2239" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2240">
+      <c r="A2240" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2240" t="inlineStr">
+        <is>
+          <t>Lyzone</t>
+        </is>
+      </c>
+      <c r="C2240" t="inlineStr">
+        <is>
+          <t>Lison</t>
+        </is>
+      </c>
+      <c r="D2240" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2240" t="n">
+        <v>84</v>
+      </c>
+      <c r="F2240" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2240" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2240" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2241">
+      <c r="A2241" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2241" t="inlineStr">
+        <is>
+          <t>Melissagzb</t>
+        </is>
+      </c>
+      <c r="C2241" t="inlineStr">
+        <is>
+          <t>Melissa</t>
+        </is>
+      </c>
+      <c r="D2241" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2241" t="n">
+        <v>85</v>
+      </c>
+      <c r="F2241" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2241" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2241" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2242">
+      <c r="A2242" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2242" t="inlineStr">
+        <is>
+          <t>Marie__92</t>
+        </is>
+      </c>
+      <c r="C2242" t="inlineStr">
+        <is>
+          <t>Marie</t>
+        </is>
+      </c>
+      <c r="D2242" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2242" t="n">
+        <v>86</v>
+      </c>
+      <c r="F2242" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2242" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2242" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2243">
+      <c r="A2243" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2243" t="inlineStr">
+        <is>
+          <t>K_Marp</t>
+        </is>
+      </c>
+      <c r="C2243" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
+      <c r="D2243" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2243" t="n">
+        <v>87</v>
+      </c>
+      <c r="F2243" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2243" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2243" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2244">
+      <c r="A2244" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2244" t="inlineStr">
+        <is>
+          <t>Cindie_JJA</t>
+        </is>
+      </c>
+      <c r="C2244" t="inlineStr">
+        <is>
+          <t>Cindie</t>
+        </is>
+      </c>
+      <c r="D2244" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2244" t="n">
+        <v>88</v>
+      </c>
+      <c r="F2244" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2244" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2244" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2245">
+      <c r="A2245" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2245" t="inlineStr">
+        <is>
+          <t>goat#AD6GS</t>
+        </is>
+      </c>
+      <c r="C2245" t="inlineStr">
+        <is>
+          <t>goat</t>
+        </is>
+      </c>
+      <c r="D2245" t="inlineStr"/>
+      <c r="E2245" t="n">
+        <v>89</v>
+      </c>
+      <c r="F2245" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2245" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2245" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2246">
+      <c r="A2246" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2246" t="inlineStr">
+        <is>
+          <t>Camillewbl</t>
+        </is>
+      </c>
+      <c r="C2246" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D2246" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2246" t="n">
+        <v>90</v>
+      </c>
+      <c r="F2246" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2246" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2246" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2247">
+      <c r="A2247" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2247" t="inlineStr">
+        <is>
+          <t>Emma_Noel</t>
+        </is>
+      </c>
+      <c r="C2247" t="inlineStr">
+        <is>
+          <t>Emma</t>
+        </is>
+      </c>
+      <c r="D2247" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2247" t="n">
+        <v>91</v>
+      </c>
+      <c r="F2247" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2247" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2247" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2248">
+      <c r="A2248" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2248" t="inlineStr">
+        <is>
+          <t>RBTL</t>
+        </is>
+      </c>
+      <c r="C2248" t="inlineStr">
+        <is>
+          <t>lea</t>
+        </is>
+      </c>
+      <c r="D2248" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2248" t="n">
+        <v>92</v>
+      </c>
+      <c r="F2248" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2248" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2248" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2249">
+      <c r="A2249" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2249" t="inlineStr">
+        <is>
+          <t>A-MOE</t>
+        </is>
+      </c>
+      <c r="C2249" t="inlineStr">
+        <is>
+          <t>Françoise</t>
+        </is>
+      </c>
+      <c r="D2249" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2249" t="n">
+        <v>93</v>
+      </c>
+      <c r="F2249" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2249" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2249" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2250">
+      <c r="A2250" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2250" t="inlineStr">
+        <is>
+          <t>PANENKANY</t>
+        </is>
+      </c>
+      <c r="C2250" t="inlineStr">
+        <is>
+          <t>Damien</t>
+        </is>
+      </c>
+      <c r="D2250" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2250" t="n">
+        <v>94</v>
+      </c>
+      <c r="F2250" t="n">
+        <v>122</v>
+      </c>
+      <c r="G2250" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2250" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2251">
+      <c r="A2251" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2251" t="inlineStr">
+        <is>
+          <t>BrickXVI</t>
+        </is>
+      </c>
+      <c r="C2251" t="inlineStr">
+        <is>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="D2251" t="inlineStr"/>
+      <c r="E2251" t="n">
+        <v>95</v>
+      </c>
+      <c r="F2251" t="n">
+        <v>74</v>
+      </c>
+      <c r="G2251" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2251" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2252">
+      <c r="A2252" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2252" t="inlineStr">
+        <is>
+          <t>Taylor2901</t>
+        </is>
+      </c>
+      <c r="C2252" t="inlineStr">
+        <is>
+          <t>ousmane</t>
+        </is>
+      </c>
+      <c r="D2252" t="inlineStr"/>
+      <c r="E2252" t="n">
+        <v>96</v>
+      </c>
+      <c r="F2252" t="n">
+        <v>74</v>
+      </c>
+      <c r="G2252" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2252" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2253">
+      <c r="A2253" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2253" t="inlineStr">
+        <is>
+          <t>Ze_GOAT</t>
+        </is>
+      </c>
+      <c r="C2253" t="inlineStr">
+        <is>
+          <t>Yasser</t>
+        </is>
+      </c>
+      <c r="D2253" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2253" t="n">
+        <v>97</v>
+      </c>
+      <c r="F2253" t="n">
+        <v>69</v>
+      </c>
+      <c r="G2253" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2253" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2254">
+      <c r="A2254" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2254" t="inlineStr">
+        <is>
+          <t>PacoSarra</t>
+        </is>
+      </c>
+      <c r="C2254" t="inlineStr">
+        <is>
+          <t>Ibra</t>
+        </is>
+      </c>
+      <c r="D2254" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2254" t="n">
+        <v>98</v>
+      </c>
+      <c r="F2254" t="n">
+        <v>69</v>
+      </c>
+      <c r="G2254" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2254" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2255">
+      <c r="A2255" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2255" t="inlineStr">
+        <is>
+          <t>Droit_au_but7723</t>
+        </is>
+      </c>
+      <c r="C2255" t="inlineStr">
+        <is>
+          <t>Calixthe</t>
+        </is>
+      </c>
+      <c r="D2255" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2255" t="n">
+        <v>99</v>
+      </c>
+      <c r="F2255" t="n">
+        <v>69</v>
+      </c>
+      <c r="G2255" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2255" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2256">
+      <c r="A2256" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2256" t="inlineStr">
+        <is>
+          <t>PavelMel</t>
+        </is>
+      </c>
+      <c r="C2256" t="inlineStr">
+        <is>
+          <t>Mélissa</t>
+        </is>
+      </c>
+      <c r="D2256" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2256" t="n">
+        <v>100</v>
+      </c>
+      <c r="F2256" t="n">
+        <v>49</v>
+      </c>
+      <c r="G2256" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2256" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2257">
+      <c r="A2257" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2257" t="inlineStr">
+        <is>
+          <t>Teddbear</t>
+        </is>
+      </c>
+      <c r="C2257" t="inlineStr">
+        <is>
+          <t>Tedy</t>
+        </is>
+      </c>
+      <c r="D2257" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2257" t="n">
+        <v>101</v>
+      </c>
+      <c r="F2257" t="n">
+        <v>49</v>
+      </c>
+      <c r="G2257" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2257" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2258">
+      <c r="A2258" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2258" t="inlineStr">
+        <is>
+          <t>SabC1</t>
+        </is>
+      </c>
+      <c r="C2258" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="D2258" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2258" t="n">
+        <v>102</v>
+      </c>
+      <c r="F2258" t="n">
+        <v>49</v>
+      </c>
+      <c r="G2258" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2258" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2259">
+      <c r="A2259" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2259" t="inlineStr">
+        <is>
+          <t>KIKS999</t>
+        </is>
+      </c>
+      <c r="C2259" t="inlineStr">
+        <is>
+          <t>Killian</t>
+        </is>
+      </c>
+      <c r="D2259" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2259" t="n">
+        <v>103</v>
+      </c>
+      <c r="F2259" t="n">
+        <v>49</v>
+      </c>
+      <c r="G2259" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2259" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2260">
+      <c r="A2260" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2260" t="inlineStr">
+        <is>
+          <t>MxKnight</t>
+        </is>
+      </c>
+      <c r="C2260" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D2260" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2260" t="n">
+        <v>104</v>
+      </c>
+      <c r="F2260" t="n">
+        <v>49</v>
+      </c>
+      <c r="G2260" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2260" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2261">
+      <c r="A2261" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2261" t="inlineStr">
+        <is>
+          <t>RomainLect</t>
+        </is>
+      </c>
+      <c r="C2261" t="inlineStr">
+        <is>
+          <t>romain</t>
+        </is>
+      </c>
+      <c r="D2261" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2261" t="n">
+        <v>105</v>
+      </c>
+      <c r="F2261" t="n">
+        <v>49</v>
+      </c>
+      <c r="G2261" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2261" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2262">
+      <c r="A2262" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2262" t="inlineStr">
+        <is>
+          <t>SamSamH8</t>
+        </is>
+      </c>
+      <c r="C2262" t="inlineStr">
+        <is>
+          <t>Samia</t>
+        </is>
+      </c>
+      <c r="D2262" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2262" t="n">
+        <v>106</v>
+      </c>
+      <c r="F2262" t="n">
+        <v>49</v>
+      </c>
+      <c r="G2262" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2262" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2263">
+      <c r="A2263" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2263" t="inlineStr">
+        <is>
+          <t>Sab_M45</t>
+        </is>
+      </c>
+      <c r="C2263" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="D2263" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2263" t="n">
+        <v>107</v>
+      </c>
+      <c r="F2263" t="n">
+        <v>49</v>
+      </c>
+      <c r="G2263" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2263" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2264">
+      <c r="A2264" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2264" t="inlineStr">
+        <is>
+          <t>Valentine___</t>
+        </is>
+      </c>
+      <c r="C2264" t="inlineStr">
+        <is>
+          <t>Valentine</t>
+        </is>
+      </c>
+      <c r="D2264" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2264" t="n">
+        <v>108</v>
+      </c>
+      <c r="F2264" t="n">
+        <v>49</v>
+      </c>
+      <c r="G2264" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2264" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2265">
+      <c r="A2265" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2265" t="inlineStr">
+        <is>
+          <t>MT35T</t>
+        </is>
+      </c>
+      <c r="C2265" t="inlineStr">
+        <is>
+          <t>Mathilde</t>
+        </is>
+      </c>
+      <c r="D2265" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2265" t="n">
+        <v>109</v>
+      </c>
+      <c r="F2265" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2265" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2265" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historique_joueurs.xlsx
+++ b/historique_joueurs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2265"/>
+  <dimension ref="A1:H2374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75878,6 +75878,3684 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2266">
+      <c r="A2266" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2266" t="inlineStr">
+        <is>
+          <t>Filipinho95</t>
+        </is>
+      </c>
+      <c r="C2266" t="inlineStr">
+        <is>
+          <t>Filipe</t>
+        </is>
+      </c>
+      <c r="D2266" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2266" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2266" t="n">
+        <v>596</v>
+      </c>
+      <c r="G2266" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2266" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2267">
+      <c r="A2267" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2267" t="inlineStr">
+        <is>
+          <t>Ninaaaa</t>
+        </is>
+      </c>
+      <c r="C2267" t="inlineStr">
+        <is>
+          <t>Nina</t>
+        </is>
+      </c>
+      <c r="D2267" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2267" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2267" t="n">
+        <v>586</v>
+      </c>
+      <c r="G2267" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2267" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2268">
+      <c r="A2268" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2268" t="inlineStr">
+        <is>
+          <t>Mamad_Shelter</t>
+        </is>
+      </c>
+      <c r="C2268" t="inlineStr">
+        <is>
+          <t>Mamadou</t>
+        </is>
+      </c>
+      <c r="D2268" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2268" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2268" t="n">
+        <v>542</v>
+      </c>
+      <c r="G2268" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2268" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2269">
+      <c r="A2269" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2269" t="inlineStr">
+        <is>
+          <t>SID-F-ANDRE</t>
+        </is>
+      </c>
+      <c r="C2269" t="inlineStr">
+        <is>
+          <t>Denis</t>
+        </is>
+      </c>
+      <c r="D2269" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2269" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2269" t="n">
+        <v>541</v>
+      </c>
+      <c r="G2269" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2269" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2270">
+      <c r="A2270" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2270" t="inlineStr">
+        <is>
+          <t>Panaff</t>
+        </is>
+      </c>
+      <c r="C2270" t="inlineStr">
+        <is>
+          <t>Panaf</t>
+        </is>
+      </c>
+      <c r="D2270" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2270" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2270" t="n">
+        <v>501</v>
+      </c>
+      <c r="G2270" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2270" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2271">
+      <c r="A2271" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2271" t="inlineStr">
+        <is>
+          <t>BOUGA#2JGXP</t>
+        </is>
+      </c>
+      <c r="C2271" t="inlineStr">
+        <is>
+          <t>BOUGA</t>
+        </is>
+      </c>
+      <c r="D2271" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2271" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2271" t="n">
+        <v>496</v>
+      </c>
+      <c r="G2271" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2271" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2272">
+      <c r="A2272" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2272" t="inlineStr">
+        <is>
+          <t>Coucoucassecou</t>
+        </is>
+      </c>
+      <c r="C2272" t="inlineStr">
+        <is>
+          <t>Brayen</t>
+        </is>
+      </c>
+      <c r="D2272" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2272" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2272" t="n">
+        <v>488</v>
+      </c>
+      <c r="G2272" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2272" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2273">
+      <c r="A2273" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2273" t="inlineStr">
+        <is>
+          <t>GOAT#UE4U8KA6</t>
+        </is>
+      </c>
+      <c r="C2273" t="inlineStr">
+        <is>
+          <t>Jean Baptiste</t>
+        </is>
+      </c>
+      <c r="D2273" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2273" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2273" t="n">
+        <v>485</v>
+      </c>
+      <c r="G2273" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2273" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2274">
+      <c r="A2274" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2274" t="inlineStr">
+        <is>
+          <t>Stephbreton</t>
+        </is>
+      </c>
+      <c r="C2274" t="inlineStr">
+        <is>
+          <t>STEPHANE</t>
+        </is>
+      </c>
+      <c r="D2274" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2274" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2274" t="n">
+        <v>483</v>
+      </c>
+      <c r="G2274" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2274" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2275">
+      <c r="A2275" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2275" t="inlineStr">
+        <is>
+          <t>HamzaG</t>
+        </is>
+      </c>
+      <c r="C2275" t="inlineStr">
+        <is>
+          <t>Hamza</t>
+        </is>
+      </c>
+      <c r="D2275" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2275" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2275" t="n">
+        <v>451</v>
+      </c>
+      <c r="G2275" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2275" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2276">
+      <c r="A2276" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2276" t="inlineStr">
+        <is>
+          <t>Nonito20</t>
+        </is>
+      </c>
+      <c r="C2276" t="inlineStr">
+        <is>
+          <t>Arnaud</t>
+        </is>
+      </c>
+      <c r="D2276" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2276" t="n">
+        <v>11</v>
+      </c>
+      <c r="F2276" t="n">
+        <v>450</v>
+      </c>
+      <c r="G2276" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2276" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2277">
+      <c r="A2277" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2277" t="inlineStr">
+        <is>
+          <t>Anais757817</t>
+        </is>
+      </c>
+      <c r="C2277" t="inlineStr">
+        <is>
+          <t>Anaïs</t>
+        </is>
+      </c>
+      <c r="D2277" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2277" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2277" t="n">
+        <v>446</v>
+      </c>
+      <c r="G2277" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2277" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2278">
+      <c r="A2278" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2278" t="inlineStr">
+        <is>
+          <t>MyriamAmr</t>
+        </is>
+      </c>
+      <c r="C2278" t="inlineStr">
+        <is>
+          <t>Myriam</t>
+        </is>
+      </c>
+      <c r="D2278" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2278" t="n">
+        <v>13</v>
+      </c>
+      <c r="F2278" t="n">
+        <v>440</v>
+      </c>
+      <c r="G2278" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2278" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2279">
+      <c r="A2279" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2279" t="inlineStr">
+        <is>
+          <t>Gronaldo_95</t>
+        </is>
+      </c>
+      <c r="C2279" t="inlineStr">
+        <is>
+          <t>Gronaldo</t>
+        </is>
+      </c>
+      <c r="D2279" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2279" t="n">
+        <v>14</v>
+      </c>
+      <c r="F2279" t="n">
+        <v>425</v>
+      </c>
+      <c r="G2279" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2279" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2280">
+      <c r="A2280" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2280" t="inlineStr">
+        <is>
+          <t>catherine#5FRTD</t>
+        </is>
+      </c>
+      <c r="C2280" t="inlineStr">
+        <is>
+          <t>catherine</t>
+        </is>
+      </c>
+      <c r="D2280" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2280" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2280" t="n">
+        <v>425</v>
+      </c>
+      <c r="G2280" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2280" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2281">
+      <c r="A2281" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2281" t="inlineStr">
+        <is>
+          <t>Leandrocp</t>
+        </is>
+      </c>
+      <c r="C2281" t="inlineStr">
+        <is>
+          <t>Leandro</t>
+        </is>
+      </c>
+      <c r="D2281" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2281" t="n">
+        <v>16</v>
+      </c>
+      <c r="F2281" t="n">
+        <v>425</v>
+      </c>
+      <c r="G2281" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2281" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2282">
+      <c r="A2282" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2282" t="inlineStr">
+        <is>
+          <t>Marion1822</t>
+        </is>
+      </c>
+      <c r="C2282" t="inlineStr">
+        <is>
+          <t>Marion</t>
+        </is>
+      </c>
+      <c r="D2282" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2282" t="n">
+        <v>17</v>
+      </c>
+      <c r="F2282" t="n">
+        <v>425</v>
+      </c>
+      <c r="G2282" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2282" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2283">
+      <c r="A2283" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2283" t="inlineStr">
+        <is>
+          <t>chaychaychay</t>
+        </is>
+      </c>
+      <c r="C2283" t="inlineStr">
+        <is>
+          <t>Chaymaa</t>
+        </is>
+      </c>
+      <c r="D2283" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2283" t="n">
+        <v>18</v>
+      </c>
+      <c r="F2283" t="n">
+        <v>425</v>
+      </c>
+      <c r="G2283" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2283" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2284">
+      <c r="A2284" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2284" t="inlineStr">
+        <is>
+          <t>MargauxCtln</t>
+        </is>
+      </c>
+      <c r="C2284" t="inlineStr">
+        <is>
+          <t>Margaux</t>
+        </is>
+      </c>
+      <c r="D2284" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2284" t="n">
+        <v>19</v>
+      </c>
+      <c r="F2284" t="n">
+        <v>420</v>
+      </c>
+      <c r="G2284" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2284" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2285">
+      <c r="A2285" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2285" t="inlineStr">
+        <is>
+          <t>MagicMath</t>
+        </is>
+      </c>
+      <c r="C2285" t="inlineStr">
+        <is>
+          <t>Mathieu</t>
+        </is>
+      </c>
+      <c r="D2285" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2285" t="n">
+        <v>20</v>
+      </c>
+      <c r="F2285" t="n">
+        <v>420</v>
+      </c>
+      <c r="G2285" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2285" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2286">
+      <c r="A2286" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2286" t="inlineStr">
+        <is>
+          <t>Ambrepic</t>
+        </is>
+      </c>
+      <c r="C2286" t="inlineStr">
+        <is>
+          <t>Ambre</t>
+        </is>
+      </c>
+      <c r="D2286" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2286" t="n">
+        <v>21</v>
+      </c>
+      <c r="F2286" t="n">
+        <v>411</v>
+      </c>
+      <c r="G2286" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2286" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2287">
+      <c r="A2287" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2287" t="inlineStr">
+        <is>
+          <t>Timy</t>
+        </is>
+      </c>
+      <c r="C2287" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="D2287" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2287" t="n">
+        <v>22</v>
+      </c>
+      <c r="F2287" t="n">
+        <v>407</v>
+      </c>
+      <c r="G2287" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2287" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2288">
+      <c r="A2288" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2288" t="inlineStr">
+        <is>
+          <t>Ilan_260_</t>
+        </is>
+      </c>
+      <c r="C2288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ilann </t>
+        </is>
+      </c>
+      <c r="D2288" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2288" t="n">
+        <v>23</v>
+      </c>
+      <c r="F2288" t="n">
+        <v>401</v>
+      </c>
+      <c r="G2288" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2288" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2289">
+      <c r="A2289" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2289" t="inlineStr">
+        <is>
+          <t>WalidSiuuuuu</t>
+        </is>
+      </c>
+      <c r="C2289" t="inlineStr">
+        <is>
+          <t>Walid</t>
+        </is>
+      </c>
+      <c r="D2289" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2289" t="n">
+        <v>24</v>
+      </c>
+      <c r="F2289" t="n">
+        <v>400</v>
+      </c>
+      <c r="G2289" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2289" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2290">
+      <c r="A2290" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2290" t="inlineStr">
+        <is>
+          <t>AudreyB225</t>
+        </is>
+      </c>
+      <c r="C2290" t="inlineStr">
+        <is>
+          <t>Audrey</t>
+        </is>
+      </c>
+      <c r="D2290" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2290" t="n">
+        <v>25</v>
+      </c>
+      <c r="F2290" t="n">
+        <v>376</v>
+      </c>
+      <c r="G2290" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2290" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2291">
+      <c r="A2291" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2291" t="inlineStr">
+        <is>
+          <t>ChrisKr1Deg1</t>
+        </is>
+      </c>
+      <c r="C2291" t="inlineStr">
+        <is>
+          <t>christophe</t>
+        </is>
+      </c>
+      <c r="D2291" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2291" t="n">
+        <v>26</v>
+      </c>
+      <c r="F2291" t="n">
+        <v>367</v>
+      </c>
+      <c r="G2291" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2291" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2292">
+      <c r="A2292" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2292" t="inlineStr">
+        <is>
+          <t>Paulasipi1998</t>
+        </is>
+      </c>
+      <c r="C2292" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="D2292" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2292" t="n">
+        <v>27</v>
+      </c>
+      <c r="F2292" t="n">
+        <v>366</v>
+      </c>
+      <c r="G2292" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2292" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2293">
+      <c r="A2293" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2293" t="inlineStr">
+        <is>
+          <t>Maruyama</t>
+        </is>
+      </c>
+      <c r="C2293" t="inlineStr">
+        <is>
+          <t>Gabrielle</t>
+        </is>
+      </c>
+      <c r="D2293" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2293" t="n">
+        <v>28</v>
+      </c>
+      <c r="F2293" t="n">
+        <v>361</v>
+      </c>
+      <c r="G2293" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2293" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2294">
+      <c r="A2294" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2294" t="inlineStr">
+        <is>
+          <t>DJOSWA</t>
+        </is>
+      </c>
+      <c r="C2294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oswaina </t>
+        </is>
+      </c>
+      <c r="D2294" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2294" t="n">
+        <v>29</v>
+      </c>
+      <c r="F2294" t="n">
+        <v>356</v>
+      </c>
+      <c r="G2294" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2294" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2295">
+      <c r="A2295" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2295" t="inlineStr">
+        <is>
+          <t>Kaliced</t>
+        </is>
+      </c>
+      <c r="C2295" t="inlineStr">
+        <is>
+          <t>Kalice</t>
+        </is>
+      </c>
+      <c r="D2295" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2295" t="n">
+        <v>30</v>
+      </c>
+      <c r="F2295" t="n">
+        <v>346</v>
+      </c>
+      <c r="G2295" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2295" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2296">
+      <c r="A2296" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2296" t="inlineStr">
+        <is>
+          <t>Emilay</t>
+        </is>
+      </c>
+      <c r="C2296" t="inlineStr">
+        <is>
+          <t>Émilie</t>
+        </is>
+      </c>
+      <c r="D2296" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2296" t="n">
+        <v>31</v>
+      </c>
+      <c r="F2296" t="n">
+        <v>343</v>
+      </c>
+      <c r="G2296" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2296" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2297">
+      <c r="A2297" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2297" t="inlineStr">
+        <is>
+          <t>Leo_durable</t>
+        </is>
+      </c>
+      <c r="C2297" t="inlineStr">
+        <is>
+          <t>Leo</t>
+        </is>
+      </c>
+      <c r="D2297" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2297" t="n">
+        <v>32</v>
+      </c>
+      <c r="F2297" t="n">
+        <v>329</v>
+      </c>
+      <c r="G2297" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2297" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2298">
+      <c r="A2298" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2298" t="inlineStr">
+        <is>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="C2298" t="inlineStr">
+        <is>
+          <t>François</t>
+        </is>
+      </c>
+      <c r="D2298" t="inlineStr"/>
+      <c r="E2298" t="n">
+        <v>33</v>
+      </c>
+      <c r="F2298" t="n">
+        <v>329</v>
+      </c>
+      <c r="G2298" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2298" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2299">
+      <c r="A2299" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2299" t="inlineStr">
+        <is>
+          <t>FRHTCTD10</t>
+        </is>
+      </c>
+      <c r="C2299" t="inlineStr">
+        <is>
+          <t>Candice</t>
+        </is>
+      </c>
+      <c r="D2299" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2299" t="n">
+        <v>34</v>
+      </c>
+      <c r="F2299" t="n">
+        <v>326</v>
+      </c>
+      <c r="G2299" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2299" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2300">
+      <c r="A2300" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2300" t="inlineStr">
+        <is>
+          <t>Mr-Worldwide</t>
+        </is>
+      </c>
+      <c r="C2300" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="D2300" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2300" t="n">
+        <v>35</v>
+      </c>
+      <c r="F2300" t="n">
+        <v>324</v>
+      </c>
+      <c r="G2300" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2300" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2301">
+      <c r="A2301" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2301" t="inlineStr">
+        <is>
+          <t>Fethinho</t>
+        </is>
+      </c>
+      <c r="C2301" t="inlineStr">
+        <is>
+          <t>Fethi</t>
+        </is>
+      </c>
+      <c r="D2301" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2301" t="n">
+        <v>36</v>
+      </c>
+      <c r="F2301" t="n">
+        <v>324</v>
+      </c>
+      <c r="G2301" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2301" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2302">
+      <c r="A2302" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2302" t="inlineStr">
+        <is>
+          <t>Ouiouiausoleil</t>
+        </is>
+      </c>
+      <c r="C2302" t="inlineStr">
+        <is>
+          <t>Ouissal</t>
+        </is>
+      </c>
+      <c r="D2302" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2302" t="n">
+        <v>37</v>
+      </c>
+      <c r="F2302" t="n">
+        <v>324</v>
+      </c>
+      <c r="G2302" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2302" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2303">
+      <c r="A2303" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2303" t="inlineStr">
+        <is>
+          <t>EmyEnzo</t>
+        </is>
+      </c>
+      <c r="C2303" t="inlineStr">
+        <is>
+          <t>Emilie</t>
+        </is>
+      </c>
+      <c r="D2303" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2303" t="n">
+        <v>38</v>
+      </c>
+      <c r="F2303" t="n">
+        <v>313</v>
+      </c>
+      <c r="G2303" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2303" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2304">
+      <c r="A2304" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2304" t="inlineStr">
+        <is>
+          <t>Yebri</t>
+        </is>
+      </c>
+      <c r="C2304" t="inlineStr">
+        <is>
+          <t>Brieuc</t>
+        </is>
+      </c>
+      <c r="D2304" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2304" t="n">
+        <v>39</v>
+      </c>
+      <c r="F2304" t="n">
+        <v>309</v>
+      </c>
+      <c r="G2304" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2304" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2305">
+      <c r="A2305" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2305" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="C2305" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="D2305" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2305" t="n">
+        <v>40</v>
+      </c>
+      <c r="F2305" t="n">
+        <v>309</v>
+      </c>
+      <c r="G2305" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2305" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2306">
+      <c r="A2306" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2306" t="inlineStr">
+        <is>
+          <t>Kolas</t>
+        </is>
+      </c>
+      <c r="C2306" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D2306" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2306" t="n">
+        <v>41</v>
+      </c>
+      <c r="F2306" t="n">
+        <v>309</v>
+      </c>
+      <c r="G2306" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2306" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2307">
+      <c r="A2307" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2307" t="inlineStr">
+        <is>
+          <t>JKInternational</t>
+        </is>
+      </c>
+      <c r="C2307" t="inlineStr">
+        <is>
+          <t>Joachim</t>
+        </is>
+      </c>
+      <c r="D2307" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2307" t="n">
+        <v>42</v>
+      </c>
+      <c r="F2307" t="n">
+        <v>309</v>
+      </c>
+      <c r="G2307" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2307" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2308">
+      <c r="A2308" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2308" t="inlineStr">
+        <is>
+          <t>1993ahm</t>
+        </is>
+      </c>
+      <c r="C2308" t="inlineStr">
+        <is>
+          <t>Ahmed</t>
+        </is>
+      </c>
+      <c r="D2308" t="inlineStr"/>
+      <c r="E2308" t="n">
+        <v>43</v>
+      </c>
+      <c r="F2308" t="n">
+        <v>309</v>
+      </c>
+      <c r="G2308" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2308" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2309">
+      <c r="A2309" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2309" t="inlineStr">
+        <is>
+          <t>BadrLeo</t>
+        </is>
+      </c>
+      <c r="C2309" t="inlineStr">
+        <is>
+          <t>Badr Leo</t>
+        </is>
+      </c>
+      <c r="D2309" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2309" t="n">
+        <v>44</v>
+      </c>
+      <c r="F2309" t="n">
+        <v>308</v>
+      </c>
+      <c r="G2309" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2309" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2310">
+      <c r="A2310" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2310" t="inlineStr">
+        <is>
+          <t>MatuRenard</t>
+        </is>
+      </c>
+      <c r="C2310" t="inlineStr">
+        <is>
+          <t>Mathias</t>
+        </is>
+      </c>
+      <c r="D2310" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2310" t="n">
+        <v>45</v>
+      </c>
+      <c r="F2310" t="n">
+        <v>303</v>
+      </c>
+      <c r="G2310" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2310" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2311">
+      <c r="A2311" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2311" t="inlineStr">
+        <is>
+          <t>Liliuus</t>
+        </is>
+      </c>
+      <c r="C2311" t="inlineStr">
+        <is>
+          <t>Lilia</t>
+        </is>
+      </c>
+      <c r="D2311" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2311" t="n">
+        <v>46</v>
+      </c>
+      <c r="F2311" t="n">
+        <v>303</v>
+      </c>
+      <c r="G2311" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2311" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2312">
+      <c r="A2312" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2312" t="inlineStr">
+        <is>
+          <t>Ppo28</t>
+        </is>
+      </c>
+      <c r="C2312" t="inlineStr">
+        <is>
+          <t>Prescylla</t>
+        </is>
+      </c>
+      <c r="D2312" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2312" t="n">
+        <v>47</v>
+      </c>
+      <c r="F2312" t="n">
+        <v>303</v>
+      </c>
+      <c r="G2312" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2312" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2313">
+      <c r="A2313" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2313" t="inlineStr">
+        <is>
+          <t>goat#AD6GS</t>
+        </is>
+      </c>
+      <c r="C2313" t="inlineStr">
+        <is>
+          <t>goat</t>
+        </is>
+      </c>
+      <c r="D2313" t="inlineStr"/>
+      <c r="E2313" t="n">
+        <v>48</v>
+      </c>
+      <c r="F2313" t="n">
+        <v>293</v>
+      </c>
+      <c r="G2313" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2313" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2314">
+      <c r="A2314" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2314" t="inlineStr">
+        <is>
+          <t>Devilrock95</t>
+        </is>
+      </c>
+      <c r="C2314" t="inlineStr">
+        <is>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="D2314" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2314" t="n">
+        <v>49</v>
+      </c>
+      <c r="F2314" t="n">
+        <v>283</v>
+      </c>
+      <c r="G2314" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2314" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2315">
+      <c r="A2315" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2315" t="inlineStr">
+        <is>
+          <t>Cleem22</t>
+        </is>
+      </c>
+      <c r="C2315" t="inlineStr">
+        <is>
+          <t>Clemence</t>
+        </is>
+      </c>
+      <c r="D2315" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2315" t="n">
+        <v>50</v>
+      </c>
+      <c r="F2315" t="n">
+        <v>283</v>
+      </c>
+      <c r="G2315" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2315" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2316">
+      <c r="A2316" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2316" t="inlineStr">
+        <is>
+          <t>YassineZ95</t>
+        </is>
+      </c>
+      <c r="C2316" t="inlineStr">
+        <is>
+          <t>Yassine Z</t>
+        </is>
+      </c>
+      <c r="D2316" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2316" t="n">
+        <v>51</v>
+      </c>
+      <c r="F2316" t="n">
+        <v>280</v>
+      </c>
+      <c r="G2316" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2316" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2317">
+      <c r="A2317" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2317" t="inlineStr">
+        <is>
+          <t>WIL1610</t>
+        </is>
+      </c>
+      <c r="C2317" t="inlineStr">
+        <is>
+          <t>William</t>
+        </is>
+      </c>
+      <c r="D2317" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2317" t="n">
+        <v>52</v>
+      </c>
+      <c r="F2317" t="n">
+        <v>277</v>
+      </c>
+      <c r="G2317" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2317" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2318">
+      <c r="A2318" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2318" t="inlineStr">
+        <is>
+          <t>Soraya-Y</t>
+        </is>
+      </c>
+      <c r="C2318" t="inlineStr">
+        <is>
+          <t>Soraya</t>
+        </is>
+      </c>
+      <c r="D2318" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2318" t="n">
+        <v>53</v>
+      </c>
+      <c r="F2318" t="n">
+        <v>265</v>
+      </c>
+      <c r="G2318" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2318" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2319">
+      <c r="A2319" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2319" t="inlineStr">
+        <is>
+          <t>Erwan#4G91X</t>
+        </is>
+      </c>
+      <c r="C2319" t="inlineStr">
+        <is>
+          <t>Erwan</t>
+        </is>
+      </c>
+      <c r="D2319" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2319" t="n">
+        <v>54</v>
+      </c>
+      <c r="F2319" t="n">
+        <v>263</v>
+      </c>
+      <c r="G2319" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2319" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2320">
+      <c r="A2320" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2320" t="inlineStr">
+        <is>
+          <t>Davido#4BZ54</t>
+        </is>
+      </c>
+      <c r="C2320" t="inlineStr">
+        <is>
+          <t>Davido</t>
+        </is>
+      </c>
+      <c r="D2320" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2320" t="n">
+        <v>55</v>
+      </c>
+      <c r="F2320" t="n">
+        <v>262</v>
+      </c>
+      <c r="G2320" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2320" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2321">
+      <c r="A2321" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2321" t="inlineStr">
+        <is>
+          <t>Exia95</t>
+        </is>
+      </c>
+      <c r="C2321" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D2321" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2321" t="n">
+        <v>56</v>
+      </c>
+      <c r="F2321" t="n">
+        <v>256</v>
+      </c>
+      <c r="G2321" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2321" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2322">
+      <c r="A2322" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2322" t="inlineStr">
+        <is>
+          <t>Krol#4R8XC</t>
+        </is>
+      </c>
+      <c r="C2322" t="inlineStr">
+        <is>
+          <t>Krol</t>
+        </is>
+      </c>
+      <c r="D2322" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2322" t="n">
+        <v>57</v>
+      </c>
+      <c r="F2322" t="n">
+        <v>255</v>
+      </c>
+      <c r="G2322" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2322" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2323">
+      <c r="A2323" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2323" t="inlineStr">
+        <is>
+          <t>dian-bgt</t>
+        </is>
+      </c>
+      <c r="C2323" t="inlineStr">
+        <is>
+          <t>Diane</t>
+        </is>
+      </c>
+      <c r="D2323" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2323" t="n">
+        <v>58</v>
+      </c>
+      <c r="F2323" t="n">
+        <v>250</v>
+      </c>
+      <c r="G2323" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2323" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2324">
+      <c r="A2324" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2324" t="inlineStr">
+        <is>
+          <t>LilianeB</t>
+        </is>
+      </c>
+      <c r="C2324" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liliane </t>
+        </is>
+      </c>
+      <c r="D2324" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2324" t="n">
+        <v>59</v>
+      </c>
+      <c r="F2324" t="n">
+        <v>250</v>
+      </c>
+      <c r="G2324" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2324" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2325">
+      <c r="A2325" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2325" t="inlineStr">
+        <is>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="C2325" t="inlineStr">
+        <is>
+          <t>Julie</t>
+        </is>
+      </c>
+      <c r="D2325" t="inlineStr"/>
+      <c r="E2325" t="n">
+        <v>60</v>
+      </c>
+      <c r="F2325" t="n">
+        <v>250</v>
+      </c>
+      <c r="G2325" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2325" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2326">
+      <c r="A2326" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2326" t="inlineStr">
+        <is>
+          <t>davidd23</t>
+        </is>
+      </c>
+      <c r="C2326" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D2326" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2326" t="n">
+        <v>61</v>
+      </c>
+      <c r="F2326" t="n">
+        <v>249</v>
+      </c>
+      <c r="G2326" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2326" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2327">
+      <c r="A2327" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2327" t="inlineStr">
+        <is>
+          <t>Romain_JO</t>
+        </is>
+      </c>
+      <c r="C2327" t="inlineStr">
+        <is>
+          <t>Romain J</t>
+        </is>
+      </c>
+      <c r="D2327" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2327" t="n">
+        <v>62</v>
+      </c>
+      <c r="F2327" t="n">
+        <v>235</v>
+      </c>
+      <c r="G2327" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2327" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2328">
+      <c r="A2328" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2328" t="inlineStr">
+        <is>
+          <t>JeremFZ</t>
+        </is>
+      </c>
+      <c r="C2328" t="inlineStr">
+        <is>
+          <t>Jérémy</t>
+        </is>
+      </c>
+      <c r="D2328" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2328" t="n">
+        <v>63</v>
+      </c>
+      <c r="F2328" t="n">
+        <v>235</v>
+      </c>
+      <c r="G2328" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2328" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2329">
+      <c r="A2329" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2329" t="inlineStr">
+        <is>
+          <t>Teddbear</t>
+        </is>
+      </c>
+      <c r="C2329" t="inlineStr">
+        <is>
+          <t>Tedy</t>
+        </is>
+      </c>
+      <c r="D2329" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2329" t="n">
+        <v>64</v>
+      </c>
+      <c r="F2329" t="n">
+        <v>225</v>
+      </c>
+      <c r="G2329" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2329" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2330">
+      <c r="A2330" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2330" t="inlineStr">
+        <is>
+          <t>GLR_PRIME</t>
+        </is>
+      </c>
+      <c r="C2330" t="inlineStr">
+        <is>
+          <t>Gabriel</t>
+        </is>
+      </c>
+      <c r="D2330" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2330" t="n">
+        <v>65</v>
+      </c>
+      <c r="F2330" t="n">
+        <v>219</v>
+      </c>
+      <c r="G2330" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2330" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2331">
+      <c r="A2331" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2331" t="inlineStr">
+        <is>
+          <t>Emma_Noel</t>
+        </is>
+      </c>
+      <c r="C2331" t="inlineStr">
+        <is>
+          <t>Emma</t>
+        </is>
+      </c>
+      <c r="D2331" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2331" t="n">
+        <v>66</v>
+      </c>
+      <c r="F2331" t="n">
+        <v>217</v>
+      </c>
+      <c r="G2331" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2331" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2332">
+      <c r="A2332" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2332" t="inlineStr">
+        <is>
+          <t>abihuts</t>
+        </is>
+      </c>
+      <c r="C2332" t="inlineStr">
+        <is>
+          <t>Antonio Moctezuma</t>
+        </is>
+      </c>
+      <c r="D2332" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2332" t="n">
+        <v>67</v>
+      </c>
+      <c r="F2332" t="n">
+        <v>216</v>
+      </c>
+      <c r="G2332" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2332" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2333">
+      <c r="A2333" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2333" t="inlineStr">
+        <is>
+          <t>Daviddesco1</t>
+        </is>
+      </c>
+      <c r="C2333" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D2333" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2333" t="n">
+        <v>68</v>
+      </c>
+      <c r="F2333" t="n">
+        <v>215</v>
+      </c>
+      <c r="G2333" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2333" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2334">
+      <c r="A2334" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2334" t="inlineStr">
+        <is>
+          <t>Chadia__</t>
+        </is>
+      </c>
+      <c r="C2334" t="inlineStr">
+        <is>
+          <t>Chadia</t>
+        </is>
+      </c>
+      <c r="D2334" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2334" t="n">
+        <v>69</v>
+      </c>
+      <c r="F2334" t="n">
+        <v>214</v>
+      </c>
+      <c r="G2334" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2334" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2335">
+      <c r="A2335" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2335" t="inlineStr">
+        <is>
+          <t>Matt#4B4CU</t>
+        </is>
+      </c>
+      <c r="C2335" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="D2335" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2335" t="n">
+        <v>70</v>
+      </c>
+      <c r="F2335" t="n">
+        <v>211</v>
+      </c>
+      <c r="G2335" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2335" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2336">
+      <c r="A2336" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2336" t="inlineStr">
+        <is>
+          <t>GOAT#UE2WM8M9</t>
+        </is>
+      </c>
+      <c r="C2336" t="inlineStr">
+        <is>
+          <t>Marilena</t>
+        </is>
+      </c>
+      <c r="D2336" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2336" t="n">
+        <v>71</v>
+      </c>
+      <c r="F2336" t="n">
+        <v>209</v>
+      </c>
+      <c r="G2336" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2336" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2337">
+      <c r="A2337" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2337" t="inlineStr">
+        <is>
+          <t>Camss</t>
+        </is>
+      </c>
+      <c r="C2337" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D2337" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2337" t="n">
+        <v>72</v>
+      </c>
+      <c r="F2337" t="n">
+        <v>190</v>
+      </c>
+      <c r="G2337" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2337" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2338">
+      <c r="A2338" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2338" t="inlineStr">
+        <is>
+          <t>Fuzo697</t>
+        </is>
+      </c>
+      <c r="C2338" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D2338" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2338" t="n">
+        <v>73</v>
+      </c>
+      <c r="F2338" t="n">
+        <v>189</v>
+      </c>
+      <c r="G2338" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2338" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2339">
+      <c r="A2339" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2339" t="inlineStr">
+        <is>
+          <t>Priscilla#4LCAF</t>
+        </is>
+      </c>
+      <c r="C2339" t="inlineStr">
+        <is>
+          <t>Priscilla</t>
+        </is>
+      </c>
+      <c r="D2339" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2339" t="n">
+        <v>74</v>
+      </c>
+      <c r="F2339" t="n">
+        <v>187</v>
+      </c>
+      <c r="G2339" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2339" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2340">
+      <c r="A2340" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2340" t="inlineStr">
+        <is>
+          <t>Pipou931</t>
+        </is>
+      </c>
+      <c r="C2340" t="inlineStr">
+        <is>
+          <t>Juliie</t>
+        </is>
+      </c>
+      <c r="D2340" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2340" t="n">
+        <v>75</v>
+      </c>
+      <c r="F2340" t="n">
+        <v>187</v>
+      </c>
+      <c r="G2340" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2340" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2341">
+      <c r="A2341" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2341" t="inlineStr">
+        <is>
+          <t>Seesee</t>
+        </is>
+      </c>
+      <c r="C2341" t="inlineStr">
+        <is>
+          <t>Selver</t>
+        </is>
+      </c>
+      <c r="D2341" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2341" t="n">
+        <v>76</v>
+      </c>
+      <c r="F2341" t="n">
+        <v>187</v>
+      </c>
+      <c r="G2341" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2341" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2342">
+      <c r="A2342" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2342" t="inlineStr">
+        <is>
+          <t>lenaaik</t>
+        </is>
+      </c>
+      <c r="C2342" t="inlineStr">
+        <is>
+          <t>Lénaïk</t>
+        </is>
+      </c>
+      <c r="D2342" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2342" t="n">
+        <v>77</v>
+      </c>
+      <c r="F2342" t="n">
+        <v>187</v>
+      </c>
+      <c r="G2342" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2342" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2343">
+      <c r="A2343" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2343" t="inlineStr">
+        <is>
+          <t>C4M</t>
+        </is>
+      </c>
+      <c r="C2343" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D2343" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2343" t="n">
+        <v>78</v>
+      </c>
+      <c r="F2343" t="n">
+        <v>187</v>
+      </c>
+      <c r="G2343" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2343" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2344">
+      <c r="A2344" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2344" t="inlineStr">
+        <is>
+          <t>Rosa_1009</t>
+        </is>
+      </c>
+      <c r="C2344" t="inlineStr">
+        <is>
+          <t>Rosaline</t>
+        </is>
+      </c>
+      <c r="D2344" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2344" t="n">
+        <v>79</v>
+      </c>
+      <c r="F2344" t="n">
+        <v>187</v>
+      </c>
+      <c r="G2344" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2344" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2345">
+      <c r="A2345" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2345" t="inlineStr">
+        <is>
+          <t>Elisewiss</t>
+        </is>
+      </c>
+      <c r="C2345" t="inlineStr">
+        <is>
+          <t>Elise</t>
+        </is>
+      </c>
+      <c r="D2345" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2345" t="n">
+        <v>80</v>
+      </c>
+      <c r="F2345" t="n">
+        <v>187</v>
+      </c>
+      <c r="G2345" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2345" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2346">
+      <c r="A2346" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2346" t="inlineStr">
+        <is>
+          <t>SabC1</t>
+        </is>
+      </c>
+      <c r="C2346" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="D2346" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2346" t="n">
+        <v>81</v>
+      </c>
+      <c r="F2346" t="n">
+        <v>175</v>
+      </c>
+      <c r="G2346" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2346" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2347">
+      <c r="A2347" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2347" t="inlineStr">
+        <is>
+          <t>Mylene-Jnt</t>
+        </is>
+      </c>
+      <c r="C2347" t="inlineStr">
+        <is>
+          <t>Mylène</t>
+        </is>
+      </c>
+      <c r="D2347" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2347" t="n">
+        <v>82</v>
+      </c>
+      <c r="F2347" t="n">
+        <v>171</v>
+      </c>
+      <c r="G2347" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2347" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2348">
+      <c r="A2348" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2348" t="inlineStr">
+        <is>
+          <t>JEVAISGAGNER10</t>
+        </is>
+      </c>
+      <c r="C2348" t="inlineStr">
+        <is>
+          <t>Xavier</t>
+        </is>
+      </c>
+      <c r="D2348" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2348" t="n">
+        <v>83</v>
+      </c>
+      <c r="F2348" t="n">
+        <v>167</v>
+      </c>
+      <c r="G2348" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2348" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2349">
+      <c r="A2349" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2349" t="inlineStr">
+        <is>
+          <t>LeaBrd</t>
+        </is>
+      </c>
+      <c r="C2349" t="inlineStr">
+        <is>
+          <t>Léa</t>
+        </is>
+      </c>
+      <c r="D2349" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2349" t="n">
+        <v>84</v>
+      </c>
+      <c r="F2349" t="n">
+        <v>167</v>
+      </c>
+      <c r="G2349" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2349" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2350">
+      <c r="A2350" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2350" t="inlineStr">
+        <is>
+          <t>Lyzone</t>
+        </is>
+      </c>
+      <c r="C2350" t="inlineStr">
+        <is>
+          <t>Lison</t>
+        </is>
+      </c>
+      <c r="D2350" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2350" t="n">
+        <v>85</v>
+      </c>
+      <c r="F2350" t="n">
+        <v>167</v>
+      </c>
+      <c r="G2350" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2350" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2351">
+      <c r="A2351" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2351" t="inlineStr">
+        <is>
+          <t>Melissagzb</t>
+        </is>
+      </c>
+      <c r="C2351" t="inlineStr">
+        <is>
+          <t>Melissa</t>
+        </is>
+      </c>
+      <c r="D2351" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2351" t="n">
+        <v>86</v>
+      </c>
+      <c r="F2351" t="n">
+        <v>167</v>
+      </c>
+      <c r="G2351" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2351" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2352">
+      <c r="A2352" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2352" t="inlineStr">
+        <is>
+          <t>Marie__92</t>
+        </is>
+      </c>
+      <c r="C2352" t="inlineStr">
+        <is>
+          <t>Marie</t>
+        </is>
+      </c>
+      <c r="D2352" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2352" t="n">
+        <v>87</v>
+      </c>
+      <c r="F2352" t="n">
+        <v>167</v>
+      </c>
+      <c r="G2352" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2352" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2353">
+      <c r="A2353" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2353" t="inlineStr">
+        <is>
+          <t>K_Marp</t>
+        </is>
+      </c>
+      <c r="C2353" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
+      <c r="D2353" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2353" t="n">
+        <v>88</v>
+      </c>
+      <c r="F2353" t="n">
+        <v>167</v>
+      </c>
+      <c r="G2353" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2353" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2354">
+      <c r="A2354" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2354" t="inlineStr">
+        <is>
+          <t>Camillewbl</t>
+        </is>
+      </c>
+      <c r="C2354" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D2354" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2354" t="n">
+        <v>89</v>
+      </c>
+      <c r="F2354" t="n">
+        <v>167</v>
+      </c>
+      <c r="G2354" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2354" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2355">
+      <c r="A2355" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2355" t="inlineStr">
+        <is>
+          <t>A-MOE</t>
+        </is>
+      </c>
+      <c r="C2355" t="inlineStr">
+        <is>
+          <t>Françoise</t>
+        </is>
+      </c>
+      <c r="D2355" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2355" t="n">
+        <v>90</v>
+      </c>
+      <c r="F2355" t="n">
+        <v>167</v>
+      </c>
+      <c r="G2355" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2355" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2356">
+      <c r="A2356" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2356" t="inlineStr">
+        <is>
+          <t>PANENKANY</t>
+        </is>
+      </c>
+      <c r="C2356" t="inlineStr">
+        <is>
+          <t>Damien</t>
+        </is>
+      </c>
+      <c r="D2356" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2356" t="n">
+        <v>91</v>
+      </c>
+      <c r="F2356" t="n">
+        <v>166</v>
+      </c>
+      <c r="G2356" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2356" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2357">
+      <c r="A2357" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2357" t="inlineStr">
+        <is>
+          <t>Ze_GOAT</t>
+        </is>
+      </c>
+      <c r="C2357" t="inlineStr">
+        <is>
+          <t>Yasser</t>
+        </is>
+      </c>
+      <c r="D2357" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2357" t="n">
+        <v>92</v>
+      </c>
+      <c r="F2357" t="n">
+        <v>163</v>
+      </c>
+      <c r="G2357" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2357" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2358">
+      <c r="A2358" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2358" t="inlineStr">
+        <is>
+          <t>Droit_au_but7723</t>
+        </is>
+      </c>
+      <c r="C2358" t="inlineStr">
+        <is>
+          <t>Calixthe</t>
+        </is>
+      </c>
+      <c r="D2358" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2358" t="n">
+        <v>93</v>
+      </c>
+      <c r="F2358" t="n">
+        <v>163</v>
+      </c>
+      <c r="G2358" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2358" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2359">
+      <c r="A2359" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2359" t="inlineStr">
+        <is>
+          <t>Ceciledp</t>
+        </is>
+      </c>
+      <c r="C2359" t="inlineStr">
+        <is>
+          <t>Cécile</t>
+        </is>
+      </c>
+      <c r="D2359" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2359" t="n">
+        <v>94</v>
+      </c>
+      <c r="F2359" t="n">
+        <v>145</v>
+      </c>
+      <c r="G2359" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2359" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2360">
+      <c r="A2360" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2360" t="inlineStr">
+        <is>
+          <t>Fa_One</t>
+        </is>
+      </c>
+      <c r="C2360" t="inlineStr">
+        <is>
+          <t>Farah</t>
+        </is>
+      </c>
+      <c r="D2360" t="inlineStr"/>
+      <c r="E2360" t="n">
+        <v>95</v>
+      </c>
+      <c r="F2360" t="n">
+        <v>143</v>
+      </c>
+      <c r="G2360" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2360" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2361">
+      <c r="A2361" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2361" t="inlineStr">
+        <is>
+          <t>KIKS999</t>
+        </is>
+      </c>
+      <c r="C2361" t="inlineStr">
+        <is>
+          <t>Killian</t>
+        </is>
+      </c>
+      <c r="D2361" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2361" t="n">
+        <v>96</v>
+      </c>
+      <c r="F2361" t="n">
+        <v>143</v>
+      </c>
+      <c r="G2361" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2361" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2362">
+      <c r="A2362" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2362" t="inlineStr">
+        <is>
+          <t>Valentine___</t>
+        </is>
+      </c>
+      <c r="C2362" t="inlineStr">
+        <is>
+          <t>Valentine</t>
+        </is>
+      </c>
+      <c r="D2362" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2362" t="n">
+        <v>97</v>
+      </c>
+      <c r="F2362" t="n">
+        <v>143</v>
+      </c>
+      <c r="G2362" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2362" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2363">
+      <c r="A2363" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2363" t="inlineStr">
+        <is>
+          <t>Laetice2020</t>
+        </is>
+      </c>
+      <c r="C2363" t="inlineStr">
+        <is>
+          <t>Laetitia</t>
+        </is>
+      </c>
+      <c r="D2363" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2363" t="n">
+        <v>98</v>
+      </c>
+      <c r="F2363" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2363" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2363" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2364">
+      <c r="A2364" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2364" t="inlineStr">
+        <is>
+          <t>Cindie_JJA</t>
+        </is>
+      </c>
+      <c r="C2364" t="inlineStr">
+        <is>
+          <t>Cindie</t>
+        </is>
+      </c>
+      <c r="D2364" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2364" t="n">
+        <v>99</v>
+      </c>
+      <c r="F2364" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2364" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2364" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2365">
+      <c r="A2365" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2365" t="inlineStr">
+        <is>
+          <t>RBTL</t>
+        </is>
+      </c>
+      <c r="C2365" t="inlineStr">
+        <is>
+          <t>lea</t>
+        </is>
+      </c>
+      <c r="D2365" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2365" t="n">
+        <v>100</v>
+      </c>
+      <c r="F2365" t="n">
+        <v>123</v>
+      </c>
+      <c r="G2365" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2365" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2366">
+      <c r="A2366" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2366" t="inlineStr">
+        <is>
+          <t>BrickXVI</t>
+        </is>
+      </c>
+      <c r="C2366" t="inlineStr">
+        <is>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="D2366" t="inlineStr"/>
+      <c r="E2366" t="n">
+        <v>101</v>
+      </c>
+      <c r="F2366" t="n">
+        <v>118</v>
+      </c>
+      <c r="G2366" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2366" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2367">
+      <c r="A2367" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2367" t="inlineStr">
+        <is>
+          <t>Taylor2901</t>
+        </is>
+      </c>
+      <c r="C2367" t="inlineStr">
+        <is>
+          <t>ousmane</t>
+        </is>
+      </c>
+      <c r="D2367" t="inlineStr"/>
+      <c r="E2367" t="n">
+        <v>102</v>
+      </c>
+      <c r="F2367" t="n">
+        <v>118</v>
+      </c>
+      <c r="G2367" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2367" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2368">
+      <c r="A2368" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2368" t="inlineStr">
+        <is>
+          <t>PacoSarra</t>
+        </is>
+      </c>
+      <c r="C2368" t="inlineStr">
+        <is>
+          <t>Ibra</t>
+        </is>
+      </c>
+      <c r="D2368" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2368" t="n">
+        <v>103</v>
+      </c>
+      <c r="F2368" t="n">
+        <v>113</v>
+      </c>
+      <c r="G2368" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2368" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2369">
+      <c r="A2369" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2369" t="inlineStr">
+        <is>
+          <t>PavelMel</t>
+        </is>
+      </c>
+      <c r="C2369" t="inlineStr">
+        <is>
+          <t>Mélissa</t>
+        </is>
+      </c>
+      <c r="D2369" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2369" t="n">
+        <v>104</v>
+      </c>
+      <c r="F2369" t="n">
+        <v>93</v>
+      </c>
+      <c r="G2369" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2369" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2370">
+      <c r="A2370" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2370" t="inlineStr">
+        <is>
+          <t>MxKnight</t>
+        </is>
+      </c>
+      <c r="C2370" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D2370" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2370" t="n">
+        <v>105</v>
+      </c>
+      <c r="F2370" t="n">
+        <v>93</v>
+      </c>
+      <c r="G2370" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2370" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2371">
+      <c r="A2371" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2371" t="inlineStr">
+        <is>
+          <t>RomainLect</t>
+        </is>
+      </c>
+      <c r="C2371" t="inlineStr">
+        <is>
+          <t>romain</t>
+        </is>
+      </c>
+      <c r="D2371" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2371" t="n">
+        <v>106</v>
+      </c>
+      <c r="F2371" t="n">
+        <v>93</v>
+      </c>
+      <c r="G2371" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2371" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2372">
+      <c r="A2372" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2372" t="inlineStr">
+        <is>
+          <t>SamSamH8</t>
+        </is>
+      </c>
+      <c r="C2372" t="inlineStr">
+        <is>
+          <t>Samia</t>
+        </is>
+      </c>
+      <c r="D2372" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2372" t="n">
+        <v>107</v>
+      </c>
+      <c r="F2372" t="n">
+        <v>93</v>
+      </c>
+      <c r="G2372" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2372" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2373">
+      <c r="A2373" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2373" t="inlineStr">
+        <is>
+          <t>Sab_M45</t>
+        </is>
+      </c>
+      <c r="C2373" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="D2373" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2373" t="n">
+        <v>108</v>
+      </c>
+      <c r="F2373" t="n">
+        <v>93</v>
+      </c>
+      <c r="G2373" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2373" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2374">
+      <c r="A2374" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2374" t="inlineStr">
+        <is>
+          <t>MT35T</t>
+        </is>
+      </c>
+      <c r="C2374" t="inlineStr">
+        <is>
+          <t>Mathilde</t>
+        </is>
+      </c>
+      <c r="D2374" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2374" t="n">
+        <v>109</v>
+      </c>
+      <c r="F2374" t="n">
+        <v>44</v>
+      </c>
+      <c r="G2374" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2374" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historique_joueurs.xlsx
+++ b/historique_joueurs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2374"/>
+  <dimension ref="A1:H2483"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79556,6 +79556,3684 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2375">
+      <c r="A2375" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2375" t="inlineStr">
+        <is>
+          <t>Filipinho95</t>
+        </is>
+      </c>
+      <c r="C2375" t="inlineStr">
+        <is>
+          <t>Filipe</t>
+        </is>
+      </c>
+      <c r="D2375" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2375" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2375" t="n">
+        <v>611</v>
+      </c>
+      <c r="G2375" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2375" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2376">
+      <c r="A2376" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2376" t="inlineStr">
+        <is>
+          <t>Ninaaaa</t>
+        </is>
+      </c>
+      <c r="C2376" t="inlineStr">
+        <is>
+          <t>Nina</t>
+        </is>
+      </c>
+      <c r="D2376" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2376" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2376" t="n">
+        <v>601</v>
+      </c>
+      <c r="G2376" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2376" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2377">
+      <c r="A2377" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2377" t="inlineStr">
+        <is>
+          <t>Mamad_Shelter</t>
+        </is>
+      </c>
+      <c r="C2377" t="inlineStr">
+        <is>
+          <t>Mamadou</t>
+        </is>
+      </c>
+      <c r="D2377" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2377" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2377" t="n">
+        <v>557</v>
+      </c>
+      <c r="G2377" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2377" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2378">
+      <c r="A2378" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2378" t="inlineStr">
+        <is>
+          <t>SID-F-ANDRE</t>
+        </is>
+      </c>
+      <c r="C2378" t="inlineStr">
+        <is>
+          <t>Denis</t>
+        </is>
+      </c>
+      <c r="D2378" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2378" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2378" t="n">
+        <v>556</v>
+      </c>
+      <c r="G2378" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2378" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2379">
+      <c r="A2379" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2379" t="inlineStr">
+        <is>
+          <t>Panaff</t>
+        </is>
+      </c>
+      <c r="C2379" t="inlineStr">
+        <is>
+          <t>Panaf</t>
+        </is>
+      </c>
+      <c r="D2379" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2379" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2379" t="n">
+        <v>516</v>
+      </c>
+      <c r="G2379" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2379" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2380">
+      <c r="A2380" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2380" t="inlineStr">
+        <is>
+          <t>BOUGA#2JGXP</t>
+        </is>
+      </c>
+      <c r="C2380" t="inlineStr">
+        <is>
+          <t>BOUGA</t>
+        </is>
+      </c>
+      <c r="D2380" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2380" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2380" t="n">
+        <v>511</v>
+      </c>
+      <c r="G2380" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2380" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2381">
+      <c r="A2381" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2381" t="inlineStr">
+        <is>
+          <t>Coucoucassecou</t>
+        </is>
+      </c>
+      <c r="C2381" t="inlineStr">
+        <is>
+          <t>Brayen</t>
+        </is>
+      </c>
+      <c r="D2381" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2381" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2381" t="n">
+        <v>503</v>
+      </c>
+      <c r="G2381" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2381" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2382">
+      <c r="A2382" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2382" t="inlineStr">
+        <is>
+          <t>GOAT#UE4U8KA6</t>
+        </is>
+      </c>
+      <c r="C2382" t="inlineStr">
+        <is>
+          <t>Jean Baptiste</t>
+        </is>
+      </c>
+      <c r="D2382" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2382" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2382" t="n">
+        <v>500</v>
+      </c>
+      <c r="G2382" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2382" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2383">
+      <c r="A2383" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2383" t="inlineStr">
+        <is>
+          <t>Stephbreton</t>
+        </is>
+      </c>
+      <c r="C2383" t="inlineStr">
+        <is>
+          <t>STEPHANE</t>
+        </is>
+      </c>
+      <c r="D2383" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2383" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2383" t="n">
+        <v>498</v>
+      </c>
+      <c r="G2383" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2383" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2384">
+      <c r="A2384" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2384" t="inlineStr">
+        <is>
+          <t>HamzaG</t>
+        </is>
+      </c>
+      <c r="C2384" t="inlineStr">
+        <is>
+          <t>Hamza</t>
+        </is>
+      </c>
+      <c r="D2384" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2384" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2384" t="n">
+        <v>466</v>
+      </c>
+      <c r="G2384" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2384" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2385">
+      <c r="A2385" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2385" t="inlineStr">
+        <is>
+          <t>Anais757817</t>
+        </is>
+      </c>
+      <c r="C2385" t="inlineStr">
+        <is>
+          <t>Anaïs</t>
+        </is>
+      </c>
+      <c r="D2385" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2385" t="n">
+        <v>11</v>
+      </c>
+      <c r="F2385" t="n">
+        <v>461</v>
+      </c>
+      <c r="G2385" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2385" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2386">
+      <c r="A2386" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2386" t="inlineStr">
+        <is>
+          <t>catherine#5FRTD</t>
+        </is>
+      </c>
+      <c r="C2386" t="inlineStr">
+        <is>
+          <t>catherine</t>
+        </is>
+      </c>
+      <c r="D2386" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2386" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2386" t="n">
+        <v>455</v>
+      </c>
+      <c r="G2386" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2386" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2387">
+      <c r="A2387" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2387" t="inlineStr">
+        <is>
+          <t>Nonito20</t>
+        </is>
+      </c>
+      <c r="C2387" t="inlineStr">
+        <is>
+          <t>Arnaud</t>
+        </is>
+      </c>
+      <c r="D2387" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2387" t="n">
+        <v>13</v>
+      </c>
+      <c r="F2387" t="n">
+        <v>450</v>
+      </c>
+      <c r="G2387" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2387" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2388">
+      <c r="A2388" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2388" t="inlineStr">
+        <is>
+          <t>Gronaldo_95</t>
+        </is>
+      </c>
+      <c r="C2388" t="inlineStr">
+        <is>
+          <t>Gronaldo</t>
+        </is>
+      </c>
+      <c r="D2388" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2388" t="n">
+        <v>14</v>
+      </c>
+      <c r="F2388" t="n">
+        <v>440</v>
+      </c>
+      <c r="G2388" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2388" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2389">
+      <c r="A2389" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2389" t="inlineStr">
+        <is>
+          <t>Leandrocp</t>
+        </is>
+      </c>
+      <c r="C2389" t="inlineStr">
+        <is>
+          <t>Leandro</t>
+        </is>
+      </c>
+      <c r="D2389" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2389" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2389" t="n">
+        <v>440</v>
+      </c>
+      <c r="G2389" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2389" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2390">
+      <c r="A2390" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2390" t="inlineStr">
+        <is>
+          <t>chaychaychay</t>
+        </is>
+      </c>
+      <c r="C2390" t="inlineStr">
+        <is>
+          <t>Chaymaa</t>
+        </is>
+      </c>
+      <c r="D2390" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2390" t="n">
+        <v>16</v>
+      </c>
+      <c r="F2390" t="n">
+        <v>440</v>
+      </c>
+      <c r="G2390" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2390" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2391">
+      <c r="A2391" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2391" t="inlineStr">
+        <is>
+          <t>MyriamAmr</t>
+        </is>
+      </c>
+      <c r="C2391" t="inlineStr">
+        <is>
+          <t>Myriam</t>
+        </is>
+      </c>
+      <c r="D2391" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2391" t="n">
+        <v>17</v>
+      </c>
+      <c r="F2391" t="n">
+        <v>440</v>
+      </c>
+      <c r="G2391" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2391" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2392">
+      <c r="A2392" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2392" t="inlineStr">
+        <is>
+          <t>MargauxCtln</t>
+        </is>
+      </c>
+      <c r="C2392" t="inlineStr">
+        <is>
+          <t>Margaux</t>
+        </is>
+      </c>
+      <c r="D2392" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2392" t="n">
+        <v>18</v>
+      </c>
+      <c r="F2392" t="n">
+        <v>435</v>
+      </c>
+      <c r="G2392" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2392" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2393">
+      <c r="A2393" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2393" t="inlineStr">
+        <is>
+          <t>MagicMath</t>
+        </is>
+      </c>
+      <c r="C2393" t="inlineStr">
+        <is>
+          <t>Mathieu</t>
+        </is>
+      </c>
+      <c r="D2393" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2393" t="n">
+        <v>19</v>
+      </c>
+      <c r="F2393" t="n">
+        <v>435</v>
+      </c>
+      <c r="G2393" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2393" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2394">
+      <c r="A2394" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2394" t="inlineStr">
+        <is>
+          <t>Ambrepic</t>
+        </is>
+      </c>
+      <c r="C2394" t="inlineStr">
+        <is>
+          <t>Ambre</t>
+        </is>
+      </c>
+      <c r="D2394" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2394" t="n">
+        <v>20</v>
+      </c>
+      <c r="F2394" t="n">
+        <v>426</v>
+      </c>
+      <c r="G2394" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2394" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2395">
+      <c r="A2395" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2395" t="inlineStr">
+        <is>
+          <t>Marion1822</t>
+        </is>
+      </c>
+      <c r="C2395" t="inlineStr">
+        <is>
+          <t>Marion</t>
+        </is>
+      </c>
+      <c r="D2395" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2395" t="n">
+        <v>21</v>
+      </c>
+      <c r="F2395" t="n">
+        <v>425</v>
+      </c>
+      <c r="G2395" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2395" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2396">
+      <c r="A2396" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2396" t="inlineStr">
+        <is>
+          <t>Timy</t>
+        </is>
+      </c>
+      <c r="C2396" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="D2396" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2396" t="n">
+        <v>22</v>
+      </c>
+      <c r="F2396" t="n">
+        <v>422</v>
+      </c>
+      <c r="G2396" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2396" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2397">
+      <c r="A2397" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2397" t="inlineStr">
+        <is>
+          <t>Ilan_260_</t>
+        </is>
+      </c>
+      <c r="C2397" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ilann </t>
+        </is>
+      </c>
+      <c r="D2397" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2397" t="n">
+        <v>23</v>
+      </c>
+      <c r="F2397" t="n">
+        <v>416</v>
+      </c>
+      <c r="G2397" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2397" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2398">
+      <c r="A2398" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2398" t="inlineStr">
+        <is>
+          <t>WalidSiuuuuu</t>
+        </is>
+      </c>
+      <c r="C2398" t="inlineStr">
+        <is>
+          <t>Walid</t>
+        </is>
+      </c>
+      <c r="D2398" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2398" t="n">
+        <v>24</v>
+      </c>
+      <c r="F2398" t="n">
+        <v>400</v>
+      </c>
+      <c r="G2398" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2398" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2399">
+      <c r="A2399" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2399" t="inlineStr">
+        <is>
+          <t>AudreyB225</t>
+        </is>
+      </c>
+      <c r="C2399" t="inlineStr">
+        <is>
+          <t>Audrey</t>
+        </is>
+      </c>
+      <c r="D2399" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2399" t="n">
+        <v>25</v>
+      </c>
+      <c r="F2399" t="n">
+        <v>391</v>
+      </c>
+      <c r="G2399" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2399" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2400">
+      <c r="A2400" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2400" t="inlineStr">
+        <is>
+          <t>ChrisKr1Deg1</t>
+        </is>
+      </c>
+      <c r="C2400" t="inlineStr">
+        <is>
+          <t>christophe</t>
+        </is>
+      </c>
+      <c r="D2400" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2400" t="n">
+        <v>26</v>
+      </c>
+      <c r="F2400" t="n">
+        <v>382</v>
+      </c>
+      <c r="G2400" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2400" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2401">
+      <c r="A2401" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2401" t="inlineStr">
+        <is>
+          <t>Paulasipi1998</t>
+        </is>
+      </c>
+      <c r="C2401" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="D2401" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2401" t="n">
+        <v>27</v>
+      </c>
+      <c r="F2401" t="n">
+        <v>381</v>
+      </c>
+      <c r="G2401" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2401" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2402">
+      <c r="A2402" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2402" t="inlineStr">
+        <is>
+          <t>Kaliced</t>
+        </is>
+      </c>
+      <c r="C2402" t="inlineStr">
+        <is>
+          <t>Kalice</t>
+        </is>
+      </c>
+      <c r="D2402" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2402" t="n">
+        <v>28</v>
+      </c>
+      <c r="F2402" t="n">
+        <v>376</v>
+      </c>
+      <c r="G2402" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2402" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2403">
+      <c r="A2403" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2403" t="inlineStr">
+        <is>
+          <t>Maruyama</t>
+        </is>
+      </c>
+      <c r="C2403" t="inlineStr">
+        <is>
+          <t>Gabrielle</t>
+        </is>
+      </c>
+      <c r="D2403" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2403" t="n">
+        <v>29</v>
+      </c>
+      <c r="F2403" t="n">
+        <v>376</v>
+      </c>
+      <c r="G2403" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2403" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2404">
+      <c r="A2404" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2404" t="inlineStr">
+        <is>
+          <t>DJOSWA</t>
+        </is>
+      </c>
+      <c r="C2404" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oswaina </t>
+        </is>
+      </c>
+      <c r="D2404" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2404" t="n">
+        <v>30</v>
+      </c>
+      <c r="F2404" t="n">
+        <v>371</v>
+      </c>
+      <c r="G2404" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2404" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2405">
+      <c r="A2405" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2405" t="inlineStr">
+        <is>
+          <t>Emilay</t>
+        </is>
+      </c>
+      <c r="C2405" t="inlineStr">
+        <is>
+          <t>Émilie</t>
+        </is>
+      </c>
+      <c r="D2405" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2405" t="n">
+        <v>31</v>
+      </c>
+      <c r="F2405" t="n">
+        <v>358</v>
+      </c>
+      <c r="G2405" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2405" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2406">
+      <c r="A2406" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2406" t="inlineStr">
+        <is>
+          <t>Leo_durable</t>
+        </is>
+      </c>
+      <c r="C2406" t="inlineStr">
+        <is>
+          <t>Leo</t>
+        </is>
+      </c>
+      <c r="D2406" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2406" t="n">
+        <v>32</v>
+      </c>
+      <c r="F2406" t="n">
+        <v>344</v>
+      </c>
+      <c r="G2406" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2406" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2407">
+      <c r="A2407" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2407" t="inlineStr">
+        <is>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="C2407" t="inlineStr">
+        <is>
+          <t>François</t>
+        </is>
+      </c>
+      <c r="D2407" t="inlineStr"/>
+      <c r="E2407" t="n">
+        <v>33</v>
+      </c>
+      <c r="F2407" t="n">
+        <v>344</v>
+      </c>
+      <c r="G2407" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2407" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2408">
+      <c r="A2408" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2408" t="inlineStr">
+        <is>
+          <t>FRHTCTD10</t>
+        </is>
+      </c>
+      <c r="C2408" t="inlineStr">
+        <is>
+          <t>Candice</t>
+        </is>
+      </c>
+      <c r="D2408" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2408" t="n">
+        <v>34</v>
+      </c>
+      <c r="F2408" t="n">
+        <v>341</v>
+      </c>
+      <c r="G2408" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2408" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2409">
+      <c r="A2409" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2409" t="inlineStr">
+        <is>
+          <t>Mr-Worldwide</t>
+        </is>
+      </c>
+      <c r="C2409" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="D2409" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2409" t="n">
+        <v>35</v>
+      </c>
+      <c r="F2409" t="n">
+        <v>339</v>
+      </c>
+      <c r="G2409" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2409" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2410">
+      <c r="A2410" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2410" t="inlineStr">
+        <is>
+          <t>Fethinho</t>
+        </is>
+      </c>
+      <c r="C2410" t="inlineStr">
+        <is>
+          <t>Fethi</t>
+        </is>
+      </c>
+      <c r="D2410" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2410" t="n">
+        <v>36</v>
+      </c>
+      <c r="F2410" t="n">
+        <v>339</v>
+      </c>
+      <c r="G2410" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2410" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2411">
+      <c r="A2411" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2411" t="inlineStr">
+        <is>
+          <t>Ouiouiausoleil</t>
+        </is>
+      </c>
+      <c r="C2411" t="inlineStr">
+        <is>
+          <t>Ouissal</t>
+        </is>
+      </c>
+      <c r="D2411" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2411" t="n">
+        <v>37</v>
+      </c>
+      <c r="F2411" t="n">
+        <v>339</v>
+      </c>
+      <c r="G2411" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2411" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2412">
+      <c r="A2412" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2412" t="inlineStr">
+        <is>
+          <t>EmyEnzo</t>
+        </is>
+      </c>
+      <c r="C2412" t="inlineStr">
+        <is>
+          <t>Emilie</t>
+        </is>
+      </c>
+      <c r="D2412" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2412" t="n">
+        <v>38</v>
+      </c>
+      <c r="F2412" t="n">
+        <v>328</v>
+      </c>
+      <c r="G2412" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2412" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2413">
+      <c r="A2413" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2413" t="inlineStr">
+        <is>
+          <t>Yebri</t>
+        </is>
+      </c>
+      <c r="C2413" t="inlineStr">
+        <is>
+          <t>Brieuc</t>
+        </is>
+      </c>
+      <c r="D2413" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2413" t="n">
+        <v>39</v>
+      </c>
+      <c r="F2413" t="n">
+        <v>324</v>
+      </c>
+      <c r="G2413" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2413" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2414">
+      <c r="A2414" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2414" t="inlineStr">
+        <is>
+          <t>Kolas</t>
+        </is>
+      </c>
+      <c r="C2414" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D2414" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2414" t="n">
+        <v>40</v>
+      </c>
+      <c r="F2414" t="n">
+        <v>324</v>
+      </c>
+      <c r="G2414" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2414" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2415">
+      <c r="A2415" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2415" t="inlineStr">
+        <is>
+          <t>JKInternational</t>
+        </is>
+      </c>
+      <c r="C2415" t="inlineStr">
+        <is>
+          <t>Joachim</t>
+        </is>
+      </c>
+      <c r="D2415" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2415" t="n">
+        <v>41</v>
+      </c>
+      <c r="F2415" t="n">
+        <v>324</v>
+      </c>
+      <c r="G2415" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2415" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2416">
+      <c r="A2416" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2416" t="inlineStr">
+        <is>
+          <t>BadrLeo</t>
+        </is>
+      </c>
+      <c r="C2416" t="inlineStr">
+        <is>
+          <t>Badr Leo</t>
+        </is>
+      </c>
+      <c r="D2416" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2416" t="n">
+        <v>42</v>
+      </c>
+      <c r="F2416" t="n">
+        <v>323</v>
+      </c>
+      <c r="G2416" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2416" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2417">
+      <c r="A2417" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2417" t="inlineStr">
+        <is>
+          <t>MatuRenard</t>
+        </is>
+      </c>
+      <c r="C2417" t="inlineStr">
+        <is>
+          <t>Mathias</t>
+        </is>
+      </c>
+      <c r="D2417" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2417" t="n">
+        <v>43</v>
+      </c>
+      <c r="F2417" t="n">
+        <v>318</v>
+      </c>
+      <c r="G2417" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2417" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2418">
+      <c r="A2418" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2418" t="inlineStr">
+        <is>
+          <t>Liliuus</t>
+        </is>
+      </c>
+      <c r="C2418" t="inlineStr">
+        <is>
+          <t>Lilia</t>
+        </is>
+      </c>
+      <c r="D2418" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2418" t="n">
+        <v>44</v>
+      </c>
+      <c r="F2418" t="n">
+        <v>318</v>
+      </c>
+      <c r="G2418" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2418" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2419">
+      <c r="A2419" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2419" t="inlineStr">
+        <is>
+          <t>Ppo28</t>
+        </is>
+      </c>
+      <c r="C2419" t="inlineStr">
+        <is>
+          <t>Prescylla</t>
+        </is>
+      </c>
+      <c r="D2419" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2419" t="n">
+        <v>45</v>
+      </c>
+      <c r="F2419" t="n">
+        <v>318</v>
+      </c>
+      <c r="G2419" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2419" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2420">
+      <c r="A2420" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2420" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="C2420" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="D2420" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2420" t="n">
+        <v>46</v>
+      </c>
+      <c r="F2420" t="n">
+        <v>309</v>
+      </c>
+      <c r="G2420" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2420" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2421">
+      <c r="A2421" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2421" t="inlineStr">
+        <is>
+          <t>1993ahm</t>
+        </is>
+      </c>
+      <c r="C2421" t="inlineStr">
+        <is>
+          <t>Ahmed</t>
+        </is>
+      </c>
+      <c r="D2421" t="inlineStr"/>
+      <c r="E2421" t="n">
+        <v>47</v>
+      </c>
+      <c r="F2421" t="n">
+        <v>309</v>
+      </c>
+      <c r="G2421" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2421" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2422">
+      <c r="A2422" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2422" t="inlineStr">
+        <is>
+          <t>goat#AD6GS</t>
+        </is>
+      </c>
+      <c r="C2422" t="inlineStr">
+        <is>
+          <t>goat</t>
+        </is>
+      </c>
+      <c r="D2422" t="inlineStr"/>
+      <c r="E2422" t="n">
+        <v>48</v>
+      </c>
+      <c r="F2422" t="n">
+        <v>308</v>
+      </c>
+      <c r="G2422" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2422" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2423">
+      <c r="A2423" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2423" t="inlineStr">
+        <is>
+          <t>Devilrock95</t>
+        </is>
+      </c>
+      <c r="C2423" t="inlineStr">
+        <is>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="D2423" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2423" t="n">
+        <v>49</v>
+      </c>
+      <c r="F2423" t="n">
+        <v>298</v>
+      </c>
+      <c r="G2423" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2423" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2424">
+      <c r="A2424" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2424" t="inlineStr">
+        <is>
+          <t>Cleem22</t>
+        </is>
+      </c>
+      <c r="C2424" t="inlineStr">
+        <is>
+          <t>Clemence</t>
+        </is>
+      </c>
+      <c r="D2424" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2424" t="n">
+        <v>50</v>
+      </c>
+      <c r="F2424" t="n">
+        <v>298</v>
+      </c>
+      <c r="G2424" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2424" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2425">
+      <c r="A2425" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2425" t="inlineStr">
+        <is>
+          <t>YassineZ95</t>
+        </is>
+      </c>
+      <c r="C2425" t="inlineStr">
+        <is>
+          <t>Yassine Z</t>
+        </is>
+      </c>
+      <c r="D2425" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2425" t="n">
+        <v>51</v>
+      </c>
+      <c r="F2425" t="n">
+        <v>295</v>
+      </c>
+      <c r="G2425" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2425" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2426">
+      <c r="A2426" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2426" t="inlineStr">
+        <is>
+          <t>WIL1610</t>
+        </is>
+      </c>
+      <c r="C2426" t="inlineStr">
+        <is>
+          <t>William</t>
+        </is>
+      </c>
+      <c r="D2426" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2426" t="n">
+        <v>52</v>
+      </c>
+      <c r="F2426" t="n">
+        <v>292</v>
+      </c>
+      <c r="G2426" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2426" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2427">
+      <c r="A2427" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2427" t="inlineStr">
+        <is>
+          <t>Soraya-Y</t>
+        </is>
+      </c>
+      <c r="C2427" t="inlineStr">
+        <is>
+          <t>Soraya</t>
+        </is>
+      </c>
+      <c r="D2427" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2427" t="n">
+        <v>53</v>
+      </c>
+      <c r="F2427" t="n">
+        <v>280</v>
+      </c>
+      <c r="G2427" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2427" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2428">
+      <c r="A2428" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2428" t="inlineStr">
+        <is>
+          <t>Erwan#4G91X</t>
+        </is>
+      </c>
+      <c r="C2428" t="inlineStr">
+        <is>
+          <t>Erwan</t>
+        </is>
+      </c>
+      <c r="D2428" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2428" t="n">
+        <v>54</v>
+      </c>
+      <c r="F2428" t="n">
+        <v>278</v>
+      </c>
+      <c r="G2428" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2428" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2429">
+      <c r="A2429" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2429" t="inlineStr">
+        <is>
+          <t>Davido#4BZ54</t>
+        </is>
+      </c>
+      <c r="C2429" t="inlineStr">
+        <is>
+          <t>Davido</t>
+        </is>
+      </c>
+      <c r="D2429" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2429" t="n">
+        <v>55</v>
+      </c>
+      <c r="F2429" t="n">
+        <v>277</v>
+      </c>
+      <c r="G2429" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2429" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2430">
+      <c r="A2430" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2430" t="inlineStr">
+        <is>
+          <t>Exia95</t>
+        </is>
+      </c>
+      <c r="C2430" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D2430" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2430" t="n">
+        <v>56</v>
+      </c>
+      <c r="F2430" t="n">
+        <v>271</v>
+      </c>
+      <c r="G2430" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2430" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2431">
+      <c r="A2431" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2431" t="inlineStr">
+        <is>
+          <t>Krol#4R8XC</t>
+        </is>
+      </c>
+      <c r="C2431" t="inlineStr">
+        <is>
+          <t>Krol</t>
+        </is>
+      </c>
+      <c r="D2431" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2431" t="n">
+        <v>57</v>
+      </c>
+      <c r="F2431" t="n">
+        <v>270</v>
+      </c>
+      <c r="G2431" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2431" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2432">
+      <c r="A2432" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2432" t="inlineStr">
+        <is>
+          <t>dian-bgt</t>
+        </is>
+      </c>
+      <c r="C2432" t="inlineStr">
+        <is>
+          <t>Diane</t>
+        </is>
+      </c>
+      <c r="D2432" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2432" t="n">
+        <v>58</v>
+      </c>
+      <c r="F2432" t="n">
+        <v>265</v>
+      </c>
+      <c r="G2432" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2432" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2433">
+      <c r="A2433" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2433" t="inlineStr">
+        <is>
+          <t>LilianeB</t>
+        </is>
+      </c>
+      <c r="C2433" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liliane </t>
+        </is>
+      </c>
+      <c r="D2433" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2433" t="n">
+        <v>59</v>
+      </c>
+      <c r="F2433" t="n">
+        <v>265</v>
+      </c>
+      <c r="G2433" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2433" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2434">
+      <c r="A2434" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2434" t="inlineStr">
+        <is>
+          <t>Romain_JO</t>
+        </is>
+      </c>
+      <c r="C2434" t="inlineStr">
+        <is>
+          <t>Romain J</t>
+        </is>
+      </c>
+      <c r="D2434" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2434" t="n">
+        <v>60</v>
+      </c>
+      <c r="F2434" t="n">
+        <v>250</v>
+      </c>
+      <c r="G2434" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2434" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2435">
+      <c r="A2435" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2435" t="inlineStr">
+        <is>
+          <t>JeremFZ</t>
+        </is>
+      </c>
+      <c r="C2435" t="inlineStr">
+        <is>
+          <t>Jérémy</t>
+        </is>
+      </c>
+      <c r="D2435" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2435" t="n">
+        <v>61</v>
+      </c>
+      <c r="F2435" t="n">
+        <v>250</v>
+      </c>
+      <c r="G2435" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2435" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2436">
+      <c r="A2436" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2436" t="inlineStr">
+        <is>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="C2436" t="inlineStr">
+        <is>
+          <t>Julie</t>
+        </is>
+      </c>
+      <c r="D2436" t="inlineStr"/>
+      <c r="E2436" t="n">
+        <v>62</v>
+      </c>
+      <c r="F2436" t="n">
+        <v>250</v>
+      </c>
+      <c r="G2436" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2436" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2437">
+      <c r="A2437" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2437" t="inlineStr">
+        <is>
+          <t>davidd23</t>
+        </is>
+      </c>
+      <c r="C2437" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D2437" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2437" t="n">
+        <v>63</v>
+      </c>
+      <c r="F2437" t="n">
+        <v>249</v>
+      </c>
+      <c r="G2437" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2437" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2438">
+      <c r="A2438" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2438" t="inlineStr">
+        <is>
+          <t>Teddbear</t>
+        </is>
+      </c>
+      <c r="C2438" t="inlineStr">
+        <is>
+          <t>Tedy</t>
+        </is>
+      </c>
+      <c r="D2438" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2438" t="n">
+        <v>64</v>
+      </c>
+      <c r="F2438" t="n">
+        <v>240</v>
+      </c>
+      <c r="G2438" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2438" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2439">
+      <c r="A2439" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2439" t="inlineStr">
+        <is>
+          <t>GLR_PRIME</t>
+        </is>
+      </c>
+      <c r="C2439" t="inlineStr">
+        <is>
+          <t>Gabriel</t>
+        </is>
+      </c>
+      <c r="D2439" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2439" t="n">
+        <v>65</v>
+      </c>
+      <c r="F2439" t="n">
+        <v>234</v>
+      </c>
+      <c r="G2439" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2439" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2440">
+      <c r="A2440" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2440" t="inlineStr">
+        <is>
+          <t>Emma_Noel</t>
+        </is>
+      </c>
+      <c r="C2440" t="inlineStr">
+        <is>
+          <t>Emma</t>
+        </is>
+      </c>
+      <c r="D2440" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2440" t="n">
+        <v>66</v>
+      </c>
+      <c r="F2440" t="n">
+        <v>232</v>
+      </c>
+      <c r="G2440" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2440" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2441">
+      <c r="A2441" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2441" t="inlineStr">
+        <is>
+          <t>abihuts</t>
+        </is>
+      </c>
+      <c r="C2441" t="inlineStr">
+        <is>
+          <t>Antonio Moctezuma</t>
+        </is>
+      </c>
+      <c r="D2441" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2441" t="n">
+        <v>67</v>
+      </c>
+      <c r="F2441" t="n">
+        <v>231</v>
+      </c>
+      <c r="G2441" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2441" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2442">
+      <c r="A2442" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2442" t="inlineStr">
+        <is>
+          <t>Daviddesco1</t>
+        </is>
+      </c>
+      <c r="C2442" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D2442" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2442" t="n">
+        <v>68</v>
+      </c>
+      <c r="F2442" t="n">
+        <v>230</v>
+      </c>
+      <c r="G2442" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2442" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2443">
+      <c r="A2443" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2443" t="inlineStr">
+        <is>
+          <t>Chadia__</t>
+        </is>
+      </c>
+      <c r="C2443" t="inlineStr">
+        <is>
+          <t>Chadia</t>
+        </is>
+      </c>
+      <c r="D2443" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2443" t="n">
+        <v>69</v>
+      </c>
+      <c r="F2443" t="n">
+        <v>229</v>
+      </c>
+      <c r="G2443" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2443" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2444">
+      <c r="A2444" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2444" t="inlineStr">
+        <is>
+          <t>Matt#4B4CU</t>
+        </is>
+      </c>
+      <c r="C2444" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="D2444" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2444" t="n">
+        <v>70</v>
+      </c>
+      <c r="F2444" t="n">
+        <v>226</v>
+      </c>
+      <c r="G2444" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2444" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2445">
+      <c r="A2445" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2445" t="inlineStr">
+        <is>
+          <t>GOAT#UE2WM8M9</t>
+        </is>
+      </c>
+      <c r="C2445" t="inlineStr">
+        <is>
+          <t>Marilena</t>
+        </is>
+      </c>
+      <c r="D2445" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2445" t="n">
+        <v>71</v>
+      </c>
+      <c r="F2445" t="n">
+        <v>224</v>
+      </c>
+      <c r="G2445" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2445" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2446">
+      <c r="A2446" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2446" t="inlineStr">
+        <is>
+          <t>Camss</t>
+        </is>
+      </c>
+      <c r="C2446" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D2446" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2446" t="n">
+        <v>72</v>
+      </c>
+      <c r="F2446" t="n">
+        <v>205</v>
+      </c>
+      <c r="G2446" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2446" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2447">
+      <c r="A2447" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2447" t="inlineStr">
+        <is>
+          <t>Priscilla#4LCAF</t>
+        </is>
+      </c>
+      <c r="C2447" t="inlineStr">
+        <is>
+          <t>Priscilla</t>
+        </is>
+      </c>
+      <c r="D2447" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2447" t="n">
+        <v>73</v>
+      </c>
+      <c r="F2447" t="n">
+        <v>202</v>
+      </c>
+      <c r="G2447" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2447" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2448">
+      <c r="A2448" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2448" t="inlineStr">
+        <is>
+          <t>Pipou931</t>
+        </is>
+      </c>
+      <c r="C2448" t="inlineStr">
+        <is>
+          <t>Juliie</t>
+        </is>
+      </c>
+      <c r="D2448" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2448" t="n">
+        <v>74</v>
+      </c>
+      <c r="F2448" t="n">
+        <v>202</v>
+      </c>
+      <c r="G2448" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2448" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2449">
+      <c r="A2449" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2449" t="inlineStr">
+        <is>
+          <t>Seesee</t>
+        </is>
+      </c>
+      <c r="C2449" t="inlineStr">
+        <is>
+          <t>Selver</t>
+        </is>
+      </c>
+      <c r="D2449" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2449" t="n">
+        <v>75</v>
+      </c>
+      <c r="F2449" t="n">
+        <v>202</v>
+      </c>
+      <c r="G2449" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2449" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2450">
+      <c r="A2450" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2450" t="inlineStr">
+        <is>
+          <t>lenaaik</t>
+        </is>
+      </c>
+      <c r="C2450" t="inlineStr">
+        <is>
+          <t>Lénaïk</t>
+        </is>
+      </c>
+      <c r="D2450" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2450" t="n">
+        <v>76</v>
+      </c>
+      <c r="F2450" t="n">
+        <v>202</v>
+      </c>
+      <c r="G2450" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2450" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2451">
+      <c r="A2451" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2451" t="inlineStr">
+        <is>
+          <t>C4M</t>
+        </is>
+      </c>
+      <c r="C2451" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D2451" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2451" t="n">
+        <v>77</v>
+      </c>
+      <c r="F2451" t="n">
+        <v>202</v>
+      </c>
+      <c r="G2451" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2451" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2452">
+      <c r="A2452" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2452" t="inlineStr">
+        <is>
+          <t>Rosa_1009</t>
+        </is>
+      </c>
+      <c r="C2452" t="inlineStr">
+        <is>
+          <t>Rosaline</t>
+        </is>
+      </c>
+      <c r="D2452" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2452" t="n">
+        <v>78</v>
+      </c>
+      <c r="F2452" t="n">
+        <v>202</v>
+      </c>
+      <c r="G2452" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2452" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2453">
+      <c r="A2453" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2453" t="inlineStr">
+        <is>
+          <t>Elisewiss</t>
+        </is>
+      </c>
+      <c r="C2453" t="inlineStr">
+        <is>
+          <t>Elise</t>
+        </is>
+      </c>
+      <c r="D2453" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2453" t="n">
+        <v>79</v>
+      </c>
+      <c r="F2453" t="n">
+        <v>202</v>
+      </c>
+      <c r="G2453" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2453" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2454">
+      <c r="A2454" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2454" t="inlineStr">
+        <is>
+          <t>SabC1</t>
+        </is>
+      </c>
+      <c r="C2454" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="D2454" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2454" t="n">
+        <v>80</v>
+      </c>
+      <c r="F2454" t="n">
+        <v>190</v>
+      </c>
+      <c r="G2454" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2454" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2455">
+      <c r="A2455" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2455" t="inlineStr">
+        <is>
+          <t>Fuzo697</t>
+        </is>
+      </c>
+      <c r="C2455" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D2455" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2455" t="n">
+        <v>81</v>
+      </c>
+      <c r="F2455" t="n">
+        <v>189</v>
+      </c>
+      <c r="G2455" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2455" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2456">
+      <c r="A2456" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2456" t="inlineStr">
+        <is>
+          <t>Mylene-Jnt</t>
+        </is>
+      </c>
+      <c r="C2456" t="inlineStr">
+        <is>
+          <t>Mylène</t>
+        </is>
+      </c>
+      <c r="D2456" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2456" t="n">
+        <v>82</v>
+      </c>
+      <c r="F2456" t="n">
+        <v>186</v>
+      </c>
+      <c r="G2456" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2456" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2457">
+      <c r="A2457" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2457" t="inlineStr">
+        <is>
+          <t>JEVAISGAGNER10</t>
+        </is>
+      </c>
+      <c r="C2457" t="inlineStr">
+        <is>
+          <t>Xavier</t>
+        </is>
+      </c>
+      <c r="D2457" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2457" t="n">
+        <v>83</v>
+      </c>
+      <c r="F2457" t="n">
+        <v>182</v>
+      </c>
+      <c r="G2457" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2457" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2458">
+      <c r="A2458" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2458" t="inlineStr">
+        <is>
+          <t>LeaBrd</t>
+        </is>
+      </c>
+      <c r="C2458" t="inlineStr">
+        <is>
+          <t>Léa</t>
+        </is>
+      </c>
+      <c r="D2458" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2458" t="n">
+        <v>84</v>
+      </c>
+      <c r="F2458" t="n">
+        <v>182</v>
+      </c>
+      <c r="G2458" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2458" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2459">
+      <c r="A2459" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2459" t="inlineStr">
+        <is>
+          <t>Lyzone</t>
+        </is>
+      </c>
+      <c r="C2459" t="inlineStr">
+        <is>
+          <t>Lison</t>
+        </is>
+      </c>
+      <c r="D2459" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2459" t="n">
+        <v>85</v>
+      </c>
+      <c r="F2459" t="n">
+        <v>182</v>
+      </c>
+      <c r="G2459" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2459" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2460">
+      <c r="A2460" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2460" t="inlineStr">
+        <is>
+          <t>Melissagzb</t>
+        </is>
+      </c>
+      <c r="C2460" t="inlineStr">
+        <is>
+          <t>Melissa</t>
+        </is>
+      </c>
+      <c r="D2460" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2460" t="n">
+        <v>86</v>
+      </c>
+      <c r="F2460" t="n">
+        <v>182</v>
+      </c>
+      <c r="G2460" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2460" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2461">
+      <c r="A2461" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2461" t="inlineStr">
+        <is>
+          <t>Marie__92</t>
+        </is>
+      </c>
+      <c r="C2461" t="inlineStr">
+        <is>
+          <t>Marie</t>
+        </is>
+      </c>
+      <c r="D2461" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2461" t="n">
+        <v>87</v>
+      </c>
+      <c r="F2461" t="n">
+        <v>182</v>
+      </c>
+      <c r="G2461" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2461" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2462">
+      <c r="A2462" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2462" t="inlineStr">
+        <is>
+          <t>K_Marp</t>
+        </is>
+      </c>
+      <c r="C2462" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
+      <c r="D2462" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2462" t="n">
+        <v>88</v>
+      </c>
+      <c r="F2462" t="n">
+        <v>182</v>
+      </c>
+      <c r="G2462" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2462" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2463">
+      <c r="A2463" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2463" t="inlineStr">
+        <is>
+          <t>Camillewbl</t>
+        </is>
+      </c>
+      <c r="C2463" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D2463" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2463" t="n">
+        <v>89</v>
+      </c>
+      <c r="F2463" t="n">
+        <v>182</v>
+      </c>
+      <c r="G2463" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2463" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2464">
+      <c r="A2464" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2464" t="inlineStr">
+        <is>
+          <t>A-MOE</t>
+        </is>
+      </c>
+      <c r="C2464" t="inlineStr">
+        <is>
+          <t>Françoise</t>
+        </is>
+      </c>
+      <c r="D2464" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2464" t="n">
+        <v>90</v>
+      </c>
+      <c r="F2464" t="n">
+        <v>182</v>
+      </c>
+      <c r="G2464" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2464" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2465">
+      <c r="A2465" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2465" t="inlineStr">
+        <is>
+          <t>PANENKANY</t>
+        </is>
+      </c>
+      <c r="C2465" t="inlineStr">
+        <is>
+          <t>Damien</t>
+        </is>
+      </c>
+      <c r="D2465" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2465" t="n">
+        <v>91</v>
+      </c>
+      <c r="F2465" t="n">
+        <v>181</v>
+      </c>
+      <c r="G2465" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2465" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2466">
+      <c r="A2466" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2466" t="inlineStr">
+        <is>
+          <t>Droit_au_but7723</t>
+        </is>
+      </c>
+      <c r="C2466" t="inlineStr">
+        <is>
+          <t>Calixthe</t>
+        </is>
+      </c>
+      <c r="D2466" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2466" t="n">
+        <v>92</v>
+      </c>
+      <c r="F2466" t="n">
+        <v>178</v>
+      </c>
+      <c r="G2466" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2466" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2467">
+      <c r="A2467" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2467" t="inlineStr">
+        <is>
+          <t>Ze_GOAT</t>
+        </is>
+      </c>
+      <c r="C2467" t="inlineStr">
+        <is>
+          <t>Yasser</t>
+        </is>
+      </c>
+      <c r="D2467" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2467" t="n">
+        <v>93</v>
+      </c>
+      <c r="F2467" t="n">
+        <v>163</v>
+      </c>
+      <c r="G2467" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2467" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2468">
+      <c r="A2468" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2468" t="inlineStr">
+        <is>
+          <t>Ceciledp</t>
+        </is>
+      </c>
+      <c r="C2468" t="inlineStr">
+        <is>
+          <t>Cécile</t>
+        </is>
+      </c>
+      <c r="D2468" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2468" t="n">
+        <v>94</v>
+      </c>
+      <c r="F2468" t="n">
+        <v>160</v>
+      </c>
+      <c r="G2468" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2468" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2469">
+      <c r="A2469" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2469" t="inlineStr">
+        <is>
+          <t>Fa_One</t>
+        </is>
+      </c>
+      <c r="C2469" t="inlineStr">
+        <is>
+          <t>Farah</t>
+        </is>
+      </c>
+      <c r="D2469" t="inlineStr"/>
+      <c r="E2469" t="n">
+        <v>95</v>
+      </c>
+      <c r="F2469" t="n">
+        <v>158</v>
+      </c>
+      <c r="G2469" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2469" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2470">
+      <c r="A2470" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2470" t="inlineStr">
+        <is>
+          <t>KIKS999</t>
+        </is>
+      </c>
+      <c r="C2470" t="inlineStr">
+        <is>
+          <t>Killian</t>
+        </is>
+      </c>
+      <c r="D2470" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2470" t="n">
+        <v>96</v>
+      </c>
+      <c r="F2470" t="n">
+        <v>158</v>
+      </c>
+      <c r="G2470" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2470" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2471">
+      <c r="A2471" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2471" t="inlineStr">
+        <is>
+          <t>Valentine___</t>
+        </is>
+      </c>
+      <c r="C2471" t="inlineStr">
+        <is>
+          <t>Valentine</t>
+        </is>
+      </c>
+      <c r="D2471" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2471" t="n">
+        <v>97</v>
+      </c>
+      <c r="F2471" t="n">
+        <v>158</v>
+      </c>
+      <c r="G2471" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2471" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2472">
+      <c r="A2472" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2472" t="inlineStr">
+        <is>
+          <t>Laetice2020</t>
+        </is>
+      </c>
+      <c r="C2472" t="inlineStr">
+        <is>
+          <t>Laetitia</t>
+        </is>
+      </c>
+      <c r="D2472" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2472" t="n">
+        <v>98</v>
+      </c>
+      <c r="F2472" t="n">
+        <v>138</v>
+      </c>
+      <c r="G2472" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2472" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2473">
+      <c r="A2473" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2473" t="inlineStr">
+        <is>
+          <t>Cindie_JJA</t>
+        </is>
+      </c>
+      <c r="C2473" t="inlineStr">
+        <is>
+          <t>Cindie</t>
+        </is>
+      </c>
+      <c r="D2473" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2473" t="n">
+        <v>99</v>
+      </c>
+      <c r="F2473" t="n">
+        <v>138</v>
+      </c>
+      <c r="G2473" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2473" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2474">
+      <c r="A2474" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2474" t="inlineStr">
+        <is>
+          <t>RBTL</t>
+        </is>
+      </c>
+      <c r="C2474" t="inlineStr">
+        <is>
+          <t>lea</t>
+        </is>
+      </c>
+      <c r="D2474" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2474" t="n">
+        <v>100</v>
+      </c>
+      <c r="F2474" t="n">
+        <v>138</v>
+      </c>
+      <c r="G2474" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2474" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2475">
+      <c r="A2475" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2475" t="inlineStr">
+        <is>
+          <t>BrickXVI</t>
+        </is>
+      </c>
+      <c r="C2475" t="inlineStr">
+        <is>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="D2475" t="inlineStr"/>
+      <c r="E2475" t="n">
+        <v>101</v>
+      </c>
+      <c r="F2475" t="n">
+        <v>133</v>
+      </c>
+      <c r="G2475" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2475" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2476">
+      <c r="A2476" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2476" t="inlineStr">
+        <is>
+          <t>Taylor2901</t>
+        </is>
+      </c>
+      <c r="C2476" t="inlineStr">
+        <is>
+          <t>ousmane</t>
+        </is>
+      </c>
+      <c r="D2476" t="inlineStr"/>
+      <c r="E2476" t="n">
+        <v>102</v>
+      </c>
+      <c r="F2476" t="n">
+        <v>133</v>
+      </c>
+      <c r="G2476" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2476" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2477">
+      <c r="A2477" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2477" t="inlineStr">
+        <is>
+          <t>PacoSarra</t>
+        </is>
+      </c>
+      <c r="C2477" t="inlineStr">
+        <is>
+          <t>Ibra</t>
+        </is>
+      </c>
+      <c r="D2477" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2477" t="n">
+        <v>103</v>
+      </c>
+      <c r="F2477" t="n">
+        <v>128</v>
+      </c>
+      <c r="G2477" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2477" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2478">
+      <c r="A2478" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2478" t="inlineStr">
+        <is>
+          <t>MxKnight</t>
+        </is>
+      </c>
+      <c r="C2478" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D2478" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2478" t="n">
+        <v>104</v>
+      </c>
+      <c r="F2478" t="n">
+        <v>108</v>
+      </c>
+      <c r="G2478" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2478" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2479">
+      <c r="A2479" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2479" t="inlineStr">
+        <is>
+          <t>RomainLect</t>
+        </is>
+      </c>
+      <c r="C2479" t="inlineStr">
+        <is>
+          <t>romain</t>
+        </is>
+      </c>
+      <c r="D2479" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2479" t="n">
+        <v>105</v>
+      </c>
+      <c r="F2479" t="n">
+        <v>108</v>
+      </c>
+      <c r="G2479" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2479" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2480">
+      <c r="A2480" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2480" t="inlineStr">
+        <is>
+          <t>SamSamH8</t>
+        </is>
+      </c>
+      <c r="C2480" t="inlineStr">
+        <is>
+          <t>Samia</t>
+        </is>
+      </c>
+      <c r="D2480" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2480" t="n">
+        <v>106</v>
+      </c>
+      <c r="F2480" t="n">
+        <v>108</v>
+      </c>
+      <c r="G2480" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2480" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2481">
+      <c r="A2481" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2481" t="inlineStr">
+        <is>
+          <t>Sab_M45</t>
+        </is>
+      </c>
+      <c r="C2481" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="D2481" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2481" t="n">
+        <v>107</v>
+      </c>
+      <c r="F2481" t="n">
+        <v>108</v>
+      </c>
+      <c r="G2481" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2481" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2482">
+      <c r="A2482" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2482" t="inlineStr">
+        <is>
+          <t>PavelMel</t>
+        </is>
+      </c>
+      <c r="C2482" t="inlineStr">
+        <is>
+          <t>Mélissa</t>
+        </is>
+      </c>
+      <c r="D2482" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2482" t="n">
+        <v>108</v>
+      </c>
+      <c r="F2482" t="n">
+        <v>93</v>
+      </c>
+      <c r="G2482" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2482" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2483">
+      <c r="A2483" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B2483" t="inlineStr">
+        <is>
+          <t>MT35T</t>
+        </is>
+      </c>
+      <c r="C2483" t="inlineStr">
+        <is>
+          <t>Mathilde</t>
+        </is>
+      </c>
+      <c r="D2483" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2483" t="n">
+        <v>109</v>
+      </c>
+      <c r="F2483" t="n">
+        <v>59</v>
+      </c>
+      <c r="G2483" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2483" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historique_joueurs.xlsx
+++ b/historique_joueurs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2483"/>
+  <dimension ref="A1:H2592"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83234,6 +83234,3684 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2484">
+      <c r="A2484" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2484" t="inlineStr">
+        <is>
+          <t>Ninaaaa</t>
+        </is>
+      </c>
+      <c r="C2484" t="inlineStr">
+        <is>
+          <t>Nina</t>
+        </is>
+      </c>
+      <c r="D2484" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2484" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2484" t="n">
+        <v>903</v>
+      </c>
+      <c r="G2484" t="n">
+        <v>9</v>
+      </c>
+      <c r="H2484" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2485">
+      <c r="A2485" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2485" t="inlineStr">
+        <is>
+          <t>Mamad_Shelter</t>
+        </is>
+      </c>
+      <c r="C2485" t="inlineStr">
+        <is>
+          <t>Mamadou</t>
+        </is>
+      </c>
+      <c r="D2485" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2485" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2485" t="n">
+        <v>859</v>
+      </c>
+      <c r="G2485" t="n">
+        <v>9</v>
+      </c>
+      <c r="H2485" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2486">
+      <c r="A2486" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2486" t="inlineStr">
+        <is>
+          <t>Stephbreton</t>
+        </is>
+      </c>
+      <c r="C2486" t="inlineStr">
+        <is>
+          <t>STEPHANE</t>
+        </is>
+      </c>
+      <c r="D2486" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2486" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2486" t="n">
+        <v>741</v>
+      </c>
+      <c r="G2486" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2486" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2487">
+      <c r="A2487" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2487" t="inlineStr">
+        <is>
+          <t>Coucoucassecou</t>
+        </is>
+      </c>
+      <c r="C2487" t="inlineStr">
+        <is>
+          <t>Brayen</t>
+        </is>
+      </c>
+      <c r="D2487" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2487" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2487" t="n">
+        <v>726</v>
+      </c>
+      <c r="G2487" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2487" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2488" t="inlineStr">
+        <is>
+          <t>GOAT#UE4U8KA6</t>
+        </is>
+      </c>
+      <c r="C2488" t="inlineStr">
+        <is>
+          <t>Jean Baptiste</t>
+        </is>
+      </c>
+      <c r="D2488" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2488" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2488" t="n">
+        <v>710</v>
+      </c>
+      <c r="G2488" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2488" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2489" t="inlineStr">
+        <is>
+          <t>Nonito20</t>
+        </is>
+      </c>
+      <c r="C2489" t="inlineStr">
+        <is>
+          <t>Arnaud</t>
+        </is>
+      </c>
+      <c r="D2489" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2489" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>693</v>
+      </c>
+      <c r="G2489" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2489" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2490" t="inlineStr">
+        <is>
+          <t>BOUGA#2JGXP</t>
+        </is>
+      </c>
+      <c r="C2490" t="inlineStr">
+        <is>
+          <t>BOUGA</t>
+        </is>
+      </c>
+      <c r="D2490" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2490" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2490" t="n">
+        <v>691</v>
+      </c>
+      <c r="G2490" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2490" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2491" t="inlineStr">
+        <is>
+          <t>Filipinho95</t>
+        </is>
+      </c>
+      <c r="C2491" t="inlineStr">
+        <is>
+          <t>Filipe</t>
+        </is>
+      </c>
+      <c r="D2491" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2491" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2491" t="n">
+        <v>683</v>
+      </c>
+      <c r="G2491" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2491" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2492" t="inlineStr">
+        <is>
+          <t>Anais757817</t>
+        </is>
+      </c>
+      <c r="C2492" t="inlineStr">
+        <is>
+          <t>Anaïs</t>
+        </is>
+      </c>
+      <c r="D2492" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2492" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2492" t="n">
+        <v>668</v>
+      </c>
+      <c r="G2492" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2492" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2493" t="inlineStr">
+        <is>
+          <t>catherine#5FRTD</t>
+        </is>
+      </c>
+      <c r="C2493" t="inlineStr">
+        <is>
+          <t>catherine</t>
+        </is>
+      </c>
+      <c r="D2493" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2493" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2493" t="n">
+        <v>665</v>
+      </c>
+      <c r="G2493" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2493" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2494" t="inlineStr">
+        <is>
+          <t>SID-F-ANDRE</t>
+        </is>
+      </c>
+      <c r="C2494" t="inlineStr">
+        <is>
+          <t>Denis</t>
+        </is>
+      </c>
+      <c r="D2494" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2494" t="n">
+        <v>11</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>664</v>
+      </c>
+      <c r="G2494" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2494" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2495" t="inlineStr">
+        <is>
+          <t>MagicMath</t>
+        </is>
+      </c>
+      <c r="C2495" t="inlineStr">
+        <is>
+          <t>Mathieu</t>
+        </is>
+      </c>
+      <c r="D2495" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2495" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2495" t="n">
+        <v>645</v>
+      </c>
+      <c r="G2495" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2495" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2496" t="inlineStr">
+        <is>
+          <t>Leo_durable</t>
+        </is>
+      </c>
+      <c r="C2496" t="inlineStr">
+        <is>
+          <t>Leo</t>
+        </is>
+      </c>
+      <c r="D2496" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2496" t="n">
+        <v>13</v>
+      </c>
+      <c r="F2496" t="n">
+        <v>639</v>
+      </c>
+      <c r="G2496" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2496" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2497" t="inlineStr">
+        <is>
+          <t>Panaff</t>
+        </is>
+      </c>
+      <c r="C2497" t="inlineStr">
+        <is>
+          <t>Panaf</t>
+        </is>
+      </c>
+      <c r="D2497" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2497" t="n">
+        <v>14</v>
+      </c>
+      <c r="F2497" t="n">
+        <v>631</v>
+      </c>
+      <c r="G2497" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2497" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2498" t="inlineStr">
+        <is>
+          <t>Marion1822</t>
+        </is>
+      </c>
+      <c r="C2498" t="inlineStr">
+        <is>
+          <t>Marion</t>
+        </is>
+      </c>
+      <c r="D2498" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2498" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>612</v>
+      </c>
+      <c r="G2498" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2498" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2499" t="inlineStr">
+        <is>
+          <t>goat#AD6GS</t>
+        </is>
+      </c>
+      <c r="C2499" t="inlineStr">
+        <is>
+          <t>goat</t>
+        </is>
+      </c>
+      <c r="D2499" t="inlineStr"/>
+      <c r="E2499" t="n">
+        <v>16</v>
+      </c>
+      <c r="F2499" t="n">
+        <v>603</v>
+      </c>
+      <c r="G2499" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2499" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2500" t="inlineStr">
+        <is>
+          <t>EmyEnzo</t>
+        </is>
+      </c>
+      <c r="C2500" t="inlineStr">
+        <is>
+          <t>Emilie</t>
+        </is>
+      </c>
+      <c r="D2500" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2500" t="n">
+        <v>17</v>
+      </c>
+      <c r="F2500" t="n">
+        <v>601</v>
+      </c>
+      <c r="G2500" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2500" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2501">
+      <c r="A2501" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2501" t="inlineStr">
+        <is>
+          <t>DJOSWA</t>
+        </is>
+      </c>
+      <c r="C2501" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oswaina </t>
+        </is>
+      </c>
+      <c r="D2501" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2501" t="n">
+        <v>18</v>
+      </c>
+      <c r="F2501" t="n">
+        <v>594</v>
+      </c>
+      <c r="G2501" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2501" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2502" t="inlineStr">
+        <is>
+          <t>WalidSiuuuuu</t>
+        </is>
+      </c>
+      <c r="C2502" t="inlineStr">
+        <is>
+          <t>Walid</t>
+        </is>
+      </c>
+      <c r="D2502" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2502" t="n">
+        <v>19</v>
+      </c>
+      <c r="F2502" t="n">
+        <v>580</v>
+      </c>
+      <c r="G2502" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2502" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2503" t="inlineStr">
+        <is>
+          <t>Paulasipi1998</t>
+        </is>
+      </c>
+      <c r="C2503" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="D2503" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2503" t="n">
+        <v>20</v>
+      </c>
+      <c r="F2503" t="n">
+        <v>568</v>
+      </c>
+      <c r="G2503" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2503" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2504" t="inlineStr">
+        <is>
+          <t>MyriamAmr</t>
+        </is>
+      </c>
+      <c r="C2504" t="inlineStr">
+        <is>
+          <t>Myriam</t>
+        </is>
+      </c>
+      <c r="D2504" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2504" t="n">
+        <v>21</v>
+      </c>
+      <c r="F2504" t="n">
+        <v>555</v>
+      </c>
+      <c r="G2504" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2504" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2505" t="inlineStr">
+        <is>
+          <t>FRHTCTD10</t>
+        </is>
+      </c>
+      <c r="C2505" t="inlineStr">
+        <is>
+          <t>Candice</t>
+        </is>
+      </c>
+      <c r="D2505" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2505" t="n">
+        <v>22</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>551</v>
+      </c>
+      <c r="G2505" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2505" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2506">
+      <c r="A2506" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2506" t="inlineStr">
+        <is>
+          <t>Gronaldo_95</t>
+        </is>
+      </c>
+      <c r="C2506" t="inlineStr">
+        <is>
+          <t>Gronaldo</t>
+        </is>
+      </c>
+      <c r="D2506" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2506" t="n">
+        <v>23</v>
+      </c>
+      <c r="F2506" t="n">
+        <v>548</v>
+      </c>
+      <c r="G2506" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2506" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2507">
+      <c r="A2507" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2507" t="inlineStr">
+        <is>
+          <t>Emilay</t>
+        </is>
+      </c>
+      <c r="C2507" t="inlineStr">
+        <is>
+          <t>Émilie</t>
+        </is>
+      </c>
+      <c r="D2507" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2507" t="n">
+        <v>24</v>
+      </c>
+      <c r="F2507" t="n">
+        <v>545</v>
+      </c>
+      <c r="G2507" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2507" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2508">
+      <c r="A2508" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2508" t="inlineStr">
+        <is>
+          <t>HamzaG</t>
+        </is>
+      </c>
+      <c r="C2508" t="inlineStr">
+        <is>
+          <t>Hamza</t>
+        </is>
+      </c>
+      <c r="D2508" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2508" t="n">
+        <v>25</v>
+      </c>
+      <c r="F2508" t="n">
+        <v>538</v>
+      </c>
+      <c r="G2508" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2508" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2509">
+      <c r="A2509" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2509" t="inlineStr">
+        <is>
+          <t>Yebri</t>
+        </is>
+      </c>
+      <c r="C2509" t="inlineStr">
+        <is>
+          <t>Brieuc</t>
+        </is>
+      </c>
+      <c r="D2509" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2509" t="n">
+        <v>26</v>
+      </c>
+      <c r="F2509" t="n">
+        <v>531</v>
+      </c>
+      <c r="G2509" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2509" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2510">
+      <c r="A2510" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2510" t="inlineStr">
+        <is>
+          <t>Ilan_260_</t>
+        </is>
+      </c>
+      <c r="C2510" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ilann </t>
+        </is>
+      </c>
+      <c r="D2510" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2510" t="n">
+        <v>27</v>
+      </c>
+      <c r="F2510" t="n">
+        <v>524</v>
+      </c>
+      <c r="G2510" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2510" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2511">
+      <c r="A2511" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2511" t="inlineStr">
+        <is>
+          <t>Ouiouiausoleil</t>
+        </is>
+      </c>
+      <c r="C2511" t="inlineStr">
+        <is>
+          <t>Ouissal</t>
+        </is>
+      </c>
+      <c r="D2511" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2511" t="n">
+        <v>28</v>
+      </c>
+      <c r="F2511" t="n">
+        <v>519</v>
+      </c>
+      <c r="G2511" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2511" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2512">
+      <c r="A2512" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2512" t="inlineStr">
+        <is>
+          <t>Leandrocp</t>
+        </is>
+      </c>
+      <c r="C2512" t="inlineStr">
+        <is>
+          <t>Leandro</t>
+        </is>
+      </c>
+      <c r="D2512" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2512" t="n">
+        <v>29</v>
+      </c>
+      <c r="F2512" t="n">
+        <v>512</v>
+      </c>
+      <c r="G2512" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2512" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2513">
+      <c r="A2513" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2513" t="inlineStr">
+        <is>
+          <t>chaychaychay</t>
+        </is>
+      </c>
+      <c r="C2513" t="inlineStr">
+        <is>
+          <t>Chaymaa</t>
+        </is>
+      </c>
+      <c r="D2513" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2513" t="n">
+        <v>30</v>
+      </c>
+      <c r="F2513" t="n">
+        <v>512</v>
+      </c>
+      <c r="G2513" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2513" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2514">
+      <c r="A2514" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2514" t="inlineStr">
+        <is>
+          <t>BadrLeo</t>
+        </is>
+      </c>
+      <c r="C2514" t="inlineStr">
+        <is>
+          <t>Badr Leo</t>
+        </is>
+      </c>
+      <c r="D2514" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2514" t="n">
+        <v>31</v>
+      </c>
+      <c r="F2514" t="n">
+        <v>510</v>
+      </c>
+      <c r="G2514" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2514" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2515">
+      <c r="A2515" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2515" t="inlineStr">
+        <is>
+          <t>MargauxCtln</t>
+        </is>
+      </c>
+      <c r="C2515" t="inlineStr">
+        <is>
+          <t>Margaux</t>
+        </is>
+      </c>
+      <c r="D2515" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2515" t="n">
+        <v>32</v>
+      </c>
+      <c r="F2515" t="n">
+        <v>507</v>
+      </c>
+      <c r="G2515" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2515" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2516">
+      <c r="A2516" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2516" t="inlineStr">
+        <is>
+          <t>YassineZ95</t>
+        </is>
+      </c>
+      <c r="C2516" t="inlineStr">
+        <is>
+          <t>Yassine Z</t>
+        </is>
+      </c>
+      <c r="D2516" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2516" t="n">
+        <v>33</v>
+      </c>
+      <c r="F2516" t="n">
+        <v>505</v>
+      </c>
+      <c r="G2516" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2516" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2517">
+      <c r="A2517" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2517" t="inlineStr">
+        <is>
+          <t>Ppo28</t>
+        </is>
+      </c>
+      <c r="C2517" t="inlineStr">
+        <is>
+          <t>Prescylla</t>
+        </is>
+      </c>
+      <c r="D2517" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2517" t="n">
+        <v>34</v>
+      </c>
+      <c r="F2517" t="n">
+        <v>498</v>
+      </c>
+      <c r="G2517" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2517" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2518">
+      <c r="A2518" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2518" t="inlineStr">
+        <is>
+          <t>Ambrepic</t>
+        </is>
+      </c>
+      <c r="C2518" t="inlineStr">
+        <is>
+          <t>Ambre</t>
+        </is>
+      </c>
+      <c r="D2518" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2518" t="n">
+        <v>35</v>
+      </c>
+      <c r="F2518" t="n">
+        <v>498</v>
+      </c>
+      <c r="G2518" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2518" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2519">
+      <c r="A2519" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2519" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="C2519" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="D2519" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2519" t="n">
+        <v>36</v>
+      </c>
+      <c r="F2519" t="n">
+        <v>496</v>
+      </c>
+      <c r="G2519" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2519" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2520">
+      <c r="A2520" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2520" t="inlineStr">
+        <is>
+          <t>Timy</t>
+        </is>
+      </c>
+      <c r="C2520" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="D2520" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2520" t="n">
+        <v>37</v>
+      </c>
+      <c r="F2520" t="n">
+        <v>494</v>
+      </c>
+      <c r="G2520" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2520" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2521">
+      <c r="A2521" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2521" t="inlineStr">
+        <is>
+          <t>C4M</t>
+        </is>
+      </c>
+      <c r="C2521" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D2521" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2521" t="n">
+        <v>38</v>
+      </c>
+      <c r="F2521" t="n">
+        <v>490</v>
+      </c>
+      <c r="G2521" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2521" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2522">
+      <c r="A2522" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2522" t="inlineStr">
+        <is>
+          <t>Ze_GOAT</t>
+        </is>
+      </c>
+      <c r="C2522" t="inlineStr">
+        <is>
+          <t>Yasser</t>
+        </is>
+      </c>
+      <c r="D2522" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2522" t="n">
+        <v>39</v>
+      </c>
+      <c r="F2522" t="n">
+        <v>488</v>
+      </c>
+      <c r="G2522" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2522" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2523">
+      <c r="A2523" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2523" t="inlineStr">
+        <is>
+          <t>Maruyama</t>
+        </is>
+      </c>
+      <c r="C2523" t="inlineStr">
+        <is>
+          <t>Gabrielle</t>
+        </is>
+      </c>
+      <c r="D2523" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2523" t="n">
+        <v>40</v>
+      </c>
+      <c r="F2523" t="n">
+        <v>484</v>
+      </c>
+      <c r="G2523" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2523" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2524">
+      <c r="A2524" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2524" t="inlineStr">
+        <is>
+          <t>Valentine___</t>
+        </is>
+      </c>
+      <c r="C2524" t="inlineStr">
+        <is>
+          <t>Valentine</t>
+        </is>
+      </c>
+      <c r="D2524" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2524" t="n">
+        <v>41</v>
+      </c>
+      <c r="F2524" t="n">
+        <v>483</v>
+      </c>
+      <c r="G2524" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2524" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2525">
+      <c r="A2525" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2525" t="inlineStr">
+        <is>
+          <t>Cleem22</t>
+        </is>
+      </c>
+      <c r="C2525" t="inlineStr">
+        <is>
+          <t>Clemence</t>
+        </is>
+      </c>
+      <c r="D2525" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2525" t="n">
+        <v>42</v>
+      </c>
+      <c r="F2525" t="n">
+        <v>478</v>
+      </c>
+      <c r="G2525" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2525" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2526">
+      <c r="A2526" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2526" t="inlineStr">
+        <is>
+          <t>Marie__92</t>
+        </is>
+      </c>
+      <c r="C2526" t="inlineStr">
+        <is>
+          <t>Marie</t>
+        </is>
+      </c>
+      <c r="D2526" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2526" t="n">
+        <v>43</v>
+      </c>
+      <c r="F2526" t="n">
+        <v>477</v>
+      </c>
+      <c r="G2526" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2526" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2527">
+      <c r="A2527" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2527" t="inlineStr">
+        <is>
+          <t>Fethinho</t>
+        </is>
+      </c>
+      <c r="C2527" t="inlineStr">
+        <is>
+          <t>Fethi</t>
+        </is>
+      </c>
+      <c r="D2527" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2527" t="n">
+        <v>44</v>
+      </c>
+      <c r="F2527" t="n">
+        <v>474</v>
+      </c>
+      <c r="G2527" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2527" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2528">
+      <c r="A2528" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2528" t="inlineStr">
+        <is>
+          <t>AudreyB225</t>
+        </is>
+      </c>
+      <c r="C2528" t="inlineStr">
+        <is>
+          <t>Audrey</t>
+        </is>
+      </c>
+      <c r="D2528" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2528" t="n">
+        <v>45</v>
+      </c>
+      <c r="F2528" t="n">
+        <v>463</v>
+      </c>
+      <c r="G2528" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2528" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2529">
+      <c r="A2529" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2529" t="inlineStr">
+        <is>
+          <t>Teddbear</t>
+        </is>
+      </c>
+      <c r="C2529" t="inlineStr">
+        <is>
+          <t>Tedy</t>
+        </is>
+      </c>
+      <c r="D2529" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2529" t="n">
+        <v>46</v>
+      </c>
+      <c r="F2529" t="n">
+        <v>463</v>
+      </c>
+      <c r="G2529" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2529" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2530">
+      <c r="A2530" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2530" t="inlineStr">
+        <is>
+          <t>Romain_JO</t>
+        </is>
+      </c>
+      <c r="C2530" t="inlineStr">
+        <is>
+          <t>Romain J</t>
+        </is>
+      </c>
+      <c r="D2530" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2530" t="n">
+        <v>47</v>
+      </c>
+      <c r="F2530" t="n">
+        <v>460</v>
+      </c>
+      <c r="G2530" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2530" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2531">
+      <c r="A2531" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2531" t="inlineStr">
+        <is>
+          <t>Exia95</t>
+        </is>
+      </c>
+      <c r="C2531" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D2531" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2531" t="n">
+        <v>48</v>
+      </c>
+      <c r="F2531" t="n">
+        <v>451</v>
+      </c>
+      <c r="G2531" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2531" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2532">
+      <c r="A2532" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2532" t="inlineStr">
+        <is>
+          <t>Kaliced</t>
+        </is>
+      </c>
+      <c r="C2532" t="inlineStr">
+        <is>
+          <t>Kalice</t>
+        </is>
+      </c>
+      <c r="D2532" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2532" t="n">
+        <v>49</v>
+      </c>
+      <c r="F2532" t="n">
+        <v>448</v>
+      </c>
+      <c r="G2532" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2532" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2533">
+      <c r="A2533" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2533" t="inlineStr">
+        <is>
+          <t>Chadia__</t>
+        </is>
+      </c>
+      <c r="C2533" t="inlineStr">
+        <is>
+          <t>Chadia</t>
+        </is>
+      </c>
+      <c r="D2533" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2533" t="n">
+        <v>50</v>
+      </c>
+      <c r="F2533" t="n">
+        <v>436</v>
+      </c>
+      <c r="G2533" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2533" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2534">
+      <c r="A2534" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2534" t="inlineStr">
+        <is>
+          <t>Matt#4B4CU</t>
+        </is>
+      </c>
+      <c r="C2534" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="D2534" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2534" t="n">
+        <v>51</v>
+      </c>
+      <c r="F2534" t="n">
+        <v>436</v>
+      </c>
+      <c r="G2534" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2534" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2535">
+      <c r="A2535" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2535" t="inlineStr">
+        <is>
+          <t>Cindie_JJA</t>
+        </is>
+      </c>
+      <c r="C2535" t="inlineStr">
+        <is>
+          <t>Cindie</t>
+        </is>
+      </c>
+      <c r="D2535" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2535" t="n">
+        <v>52</v>
+      </c>
+      <c r="F2535" t="n">
+        <v>433</v>
+      </c>
+      <c r="G2535" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2535" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2536">
+      <c r="A2536" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2536" t="inlineStr">
+        <is>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="C2536" t="inlineStr">
+        <is>
+          <t>Julie</t>
+        </is>
+      </c>
+      <c r="D2536" t="inlineStr"/>
+      <c r="E2536" t="n">
+        <v>53</v>
+      </c>
+      <c r="F2536" t="n">
+        <v>430</v>
+      </c>
+      <c r="G2536" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2536" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2537">
+      <c r="A2537" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2537" t="inlineStr">
+        <is>
+          <t>Soraya-Y</t>
+        </is>
+      </c>
+      <c r="C2537" t="inlineStr">
+        <is>
+          <t>Soraya</t>
+        </is>
+      </c>
+      <c r="D2537" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2537" t="n">
+        <v>54</v>
+      </c>
+      <c r="F2537" t="n">
+        <v>418</v>
+      </c>
+      <c r="G2537" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2537" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2538">
+      <c r="A2538" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2538" t="inlineStr">
+        <is>
+          <t>Mr-Worldwide</t>
+        </is>
+      </c>
+      <c r="C2538" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="D2538" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2538" t="n">
+        <v>55</v>
+      </c>
+      <c r="F2538" t="n">
+        <v>411</v>
+      </c>
+      <c r="G2538" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2538" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2539">
+      <c r="A2539" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2539" t="inlineStr">
+        <is>
+          <t>Camillewbl</t>
+        </is>
+      </c>
+      <c r="C2539" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D2539" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2539" t="n">
+        <v>56</v>
+      </c>
+      <c r="F2539" t="n">
+        <v>405</v>
+      </c>
+      <c r="G2539" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2539" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2540">
+      <c r="A2540" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2540" t="inlineStr">
+        <is>
+          <t>PANENKANY</t>
+        </is>
+      </c>
+      <c r="C2540" t="inlineStr">
+        <is>
+          <t>Damien</t>
+        </is>
+      </c>
+      <c r="D2540" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2540" t="n">
+        <v>57</v>
+      </c>
+      <c r="F2540" t="n">
+        <v>404</v>
+      </c>
+      <c r="G2540" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2540" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2541">
+      <c r="A2541" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2541" t="inlineStr">
+        <is>
+          <t>JKInternational</t>
+        </is>
+      </c>
+      <c r="C2541" t="inlineStr">
+        <is>
+          <t>Joachim</t>
+        </is>
+      </c>
+      <c r="D2541" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2541" t="n">
+        <v>58</v>
+      </c>
+      <c r="F2541" t="n">
+        <v>396</v>
+      </c>
+      <c r="G2541" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2541" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2542">
+      <c r="A2542" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2542" t="inlineStr">
+        <is>
+          <t>Erwan#4G91X</t>
+        </is>
+      </c>
+      <c r="C2542" t="inlineStr">
+        <is>
+          <t>Erwan</t>
+        </is>
+      </c>
+      <c r="D2542" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2542" t="n">
+        <v>59</v>
+      </c>
+      <c r="F2542" t="n">
+        <v>393</v>
+      </c>
+      <c r="G2542" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2542" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2543">
+      <c r="A2543" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2543" t="inlineStr">
+        <is>
+          <t>Pipou931</t>
+        </is>
+      </c>
+      <c r="C2543" t="inlineStr">
+        <is>
+          <t>Juliie</t>
+        </is>
+      </c>
+      <c r="D2543" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2543" t="n">
+        <v>60</v>
+      </c>
+      <c r="F2543" t="n">
+        <v>389</v>
+      </c>
+      <c r="G2543" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2543" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2544">
+      <c r="A2544" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2544" t="inlineStr">
+        <is>
+          <t>Seesee</t>
+        </is>
+      </c>
+      <c r="C2544" t="inlineStr">
+        <is>
+          <t>Selver</t>
+        </is>
+      </c>
+      <c r="D2544" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2544" t="n">
+        <v>61</v>
+      </c>
+      <c r="F2544" t="n">
+        <v>382</v>
+      </c>
+      <c r="G2544" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2544" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2545">
+      <c r="A2545" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2545" t="inlineStr">
+        <is>
+          <t>lenaaik</t>
+        </is>
+      </c>
+      <c r="C2545" t="inlineStr">
+        <is>
+          <t>Lénaïk</t>
+        </is>
+      </c>
+      <c r="D2545" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2545" t="n">
+        <v>62</v>
+      </c>
+      <c r="F2545" t="n">
+        <v>382</v>
+      </c>
+      <c r="G2545" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2545" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2546">
+      <c r="A2546" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2546" t="inlineStr">
+        <is>
+          <t>Elisewiss</t>
+        </is>
+      </c>
+      <c r="C2546" t="inlineStr">
+        <is>
+          <t>Elise</t>
+        </is>
+      </c>
+      <c r="D2546" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2546" t="n">
+        <v>63</v>
+      </c>
+      <c r="F2546" t="n">
+        <v>382</v>
+      </c>
+      <c r="G2546" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2546" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2547">
+      <c r="A2547" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2547" t="inlineStr">
+        <is>
+          <t>ChrisKr1Deg1</t>
+        </is>
+      </c>
+      <c r="C2547" t="inlineStr">
+        <is>
+          <t>christophe</t>
+        </is>
+      </c>
+      <c r="D2547" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2547" t="n">
+        <v>64</v>
+      </c>
+      <c r="F2547" t="n">
+        <v>382</v>
+      </c>
+      <c r="G2547" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2547" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2548">
+      <c r="A2548" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2548" t="inlineStr">
+        <is>
+          <t>1993ahm</t>
+        </is>
+      </c>
+      <c r="C2548" t="inlineStr">
+        <is>
+          <t>Ahmed</t>
+        </is>
+      </c>
+      <c r="D2548" t="inlineStr"/>
+      <c r="E2548" t="n">
+        <v>65</v>
+      </c>
+      <c r="F2548" t="n">
+        <v>381</v>
+      </c>
+      <c r="G2548" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2548" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2549">
+      <c r="A2549" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2549" t="inlineStr">
+        <is>
+          <t>Devilrock95</t>
+        </is>
+      </c>
+      <c r="C2549" t="inlineStr">
+        <is>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="D2549" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2549" t="n">
+        <v>66</v>
+      </c>
+      <c r="F2549" t="n">
+        <v>370</v>
+      </c>
+      <c r="G2549" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2549" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2550">
+      <c r="A2550" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2550" t="inlineStr">
+        <is>
+          <t>Droit_au_but7723</t>
+        </is>
+      </c>
+      <c r="C2550" t="inlineStr">
+        <is>
+          <t>Calixthe</t>
+        </is>
+      </c>
+      <c r="D2550" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2550" t="n">
+        <v>67</v>
+      </c>
+      <c r="F2550" t="n">
+        <v>358</v>
+      </c>
+      <c r="G2550" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2550" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2551">
+      <c r="A2551" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2551" t="inlineStr">
+        <is>
+          <t>Davido#4BZ54</t>
+        </is>
+      </c>
+      <c r="C2551" t="inlineStr">
+        <is>
+          <t>Davido</t>
+        </is>
+      </c>
+      <c r="D2551" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2551" t="n">
+        <v>68</v>
+      </c>
+      <c r="F2551" t="n">
+        <v>349</v>
+      </c>
+      <c r="G2551" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2551" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2552">
+      <c r="A2552" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2552" t="inlineStr">
+        <is>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="C2552" t="inlineStr">
+        <is>
+          <t>François</t>
+        </is>
+      </c>
+      <c r="D2552" t="inlineStr"/>
+      <c r="E2552" t="n">
+        <v>69</v>
+      </c>
+      <c r="F2552" t="n">
+        <v>344</v>
+      </c>
+      <c r="G2552" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2552" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2553">
+      <c r="A2553" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2553" t="inlineStr">
+        <is>
+          <t>Camss</t>
+        </is>
+      </c>
+      <c r="C2553" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D2553" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2553" t="n">
+        <v>70</v>
+      </c>
+      <c r="F2553" t="n">
+        <v>343</v>
+      </c>
+      <c r="G2553" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2553" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2554">
+      <c r="A2554" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2554" t="inlineStr">
+        <is>
+          <t>Krol#4R8XC</t>
+        </is>
+      </c>
+      <c r="C2554" t="inlineStr">
+        <is>
+          <t>Krol</t>
+        </is>
+      </c>
+      <c r="D2554" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2554" t="n">
+        <v>71</v>
+      </c>
+      <c r="F2554" t="n">
+        <v>342</v>
+      </c>
+      <c r="G2554" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2554" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2555">
+      <c r="A2555" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2555" t="inlineStr">
+        <is>
+          <t>LilianeB</t>
+        </is>
+      </c>
+      <c r="C2555" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liliane </t>
+        </is>
+      </c>
+      <c r="D2555" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2555" t="n">
+        <v>72</v>
+      </c>
+      <c r="F2555" t="n">
+        <v>337</v>
+      </c>
+      <c r="G2555" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2555" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2556">
+      <c r="A2556" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2556" t="inlineStr">
+        <is>
+          <t>Kolas</t>
+        </is>
+      </c>
+      <c r="C2556" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D2556" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2556" t="n">
+        <v>73</v>
+      </c>
+      <c r="F2556" t="n">
+        <v>324</v>
+      </c>
+      <c r="G2556" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2556" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2557">
+      <c r="A2557" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2557" t="inlineStr">
+        <is>
+          <t>JeremFZ</t>
+        </is>
+      </c>
+      <c r="C2557" t="inlineStr">
+        <is>
+          <t>Jérémy</t>
+        </is>
+      </c>
+      <c r="D2557" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2557" t="n">
+        <v>74</v>
+      </c>
+      <c r="F2557" t="n">
+        <v>322</v>
+      </c>
+      <c r="G2557" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2557" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2558">
+      <c r="A2558" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2558" t="inlineStr">
+        <is>
+          <t>MatuRenard</t>
+        </is>
+      </c>
+      <c r="C2558" t="inlineStr">
+        <is>
+          <t>Mathias</t>
+        </is>
+      </c>
+      <c r="D2558" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2558" t="n">
+        <v>75</v>
+      </c>
+      <c r="F2558" t="n">
+        <v>318</v>
+      </c>
+      <c r="G2558" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2558" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2559">
+      <c r="A2559" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2559" t="inlineStr">
+        <is>
+          <t>Liliuus</t>
+        </is>
+      </c>
+      <c r="C2559" t="inlineStr">
+        <is>
+          <t>Lilia</t>
+        </is>
+      </c>
+      <c r="D2559" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2559" t="n">
+        <v>76</v>
+      </c>
+      <c r="F2559" t="n">
+        <v>318</v>
+      </c>
+      <c r="G2559" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2559" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2560">
+      <c r="A2560" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2560" t="inlineStr">
+        <is>
+          <t>abihuts</t>
+        </is>
+      </c>
+      <c r="C2560" t="inlineStr">
+        <is>
+          <t>Antonio Moctezuma</t>
+        </is>
+      </c>
+      <c r="D2560" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2560" t="n">
+        <v>77</v>
+      </c>
+      <c r="F2560" t="n">
+        <v>303</v>
+      </c>
+      <c r="G2560" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2560" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2561">
+      <c r="A2561" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2561" t="inlineStr">
+        <is>
+          <t>Daviddesco1</t>
+        </is>
+      </c>
+      <c r="C2561" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D2561" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2561" t="n">
+        <v>78</v>
+      </c>
+      <c r="F2561" t="n">
+        <v>302</v>
+      </c>
+      <c r="G2561" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2561" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2562">
+      <c r="A2562" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2562" t="inlineStr">
+        <is>
+          <t>GOAT#UE2WM8M9</t>
+        </is>
+      </c>
+      <c r="C2562" t="inlineStr">
+        <is>
+          <t>Marilena</t>
+        </is>
+      </c>
+      <c r="D2562" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2562" t="n">
+        <v>79</v>
+      </c>
+      <c r="F2562" t="n">
+        <v>296</v>
+      </c>
+      <c r="G2562" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2562" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2563">
+      <c r="A2563" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2563" t="inlineStr">
+        <is>
+          <t>WIL1610</t>
+        </is>
+      </c>
+      <c r="C2563" t="inlineStr">
+        <is>
+          <t>William</t>
+        </is>
+      </c>
+      <c r="D2563" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2563" t="n">
+        <v>80</v>
+      </c>
+      <c r="F2563" t="n">
+        <v>292</v>
+      </c>
+      <c r="G2563" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2563" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2564">
+      <c r="A2564" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2564" t="inlineStr">
+        <is>
+          <t>Lyzone</t>
+        </is>
+      </c>
+      <c r="C2564" t="inlineStr">
+        <is>
+          <t>Lison</t>
+        </is>
+      </c>
+      <c r="D2564" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2564" t="n">
+        <v>81</v>
+      </c>
+      <c r="F2564" t="n">
+        <v>290</v>
+      </c>
+      <c r="G2564" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2564" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2565">
+      <c r="A2565" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2565" t="inlineStr">
+        <is>
+          <t>MT35T</t>
+        </is>
+      </c>
+      <c r="C2565" t="inlineStr">
+        <is>
+          <t>Mathilde</t>
+        </is>
+      </c>
+      <c r="D2565" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2565" t="n">
+        <v>82</v>
+      </c>
+      <c r="F2565" t="n">
+        <v>282</v>
+      </c>
+      <c r="G2565" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2565" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2566">
+      <c r="A2566" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2566" t="inlineStr">
+        <is>
+          <t>Priscilla#4LCAF</t>
+        </is>
+      </c>
+      <c r="C2566" t="inlineStr">
+        <is>
+          <t>Priscilla</t>
+        </is>
+      </c>
+      <c r="D2566" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2566" t="n">
+        <v>83</v>
+      </c>
+      <c r="F2566" t="n">
+        <v>274</v>
+      </c>
+      <c r="G2566" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2566" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2567">
+      <c r="A2567" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2567" t="inlineStr">
+        <is>
+          <t>Rosa_1009</t>
+        </is>
+      </c>
+      <c r="C2567" t="inlineStr">
+        <is>
+          <t>Rosaline</t>
+        </is>
+      </c>
+      <c r="D2567" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2567" t="n">
+        <v>84</v>
+      </c>
+      <c r="F2567" t="n">
+        <v>274</v>
+      </c>
+      <c r="G2567" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2567" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2568">
+      <c r="A2568" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2568" t="inlineStr">
+        <is>
+          <t>Ceciledp</t>
+        </is>
+      </c>
+      <c r="C2568" t="inlineStr">
+        <is>
+          <t>Cécile</t>
+        </is>
+      </c>
+      <c r="D2568" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2568" t="n">
+        <v>85</v>
+      </c>
+      <c r="F2568" t="n">
+        <v>268</v>
+      </c>
+      <c r="G2568" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2568" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2569">
+      <c r="A2569" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2569" t="inlineStr">
+        <is>
+          <t>PacoSarra</t>
+        </is>
+      </c>
+      <c r="C2569" t="inlineStr">
+        <is>
+          <t>Ibra</t>
+        </is>
+      </c>
+      <c r="D2569" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2569" t="n">
+        <v>86</v>
+      </c>
+      <c r="F2569" t="n">
+        <v>266</v>
+      </c>
+      <c r="G2569" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2569" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2570">
+      <c r="A2570" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2570" t="inlineStr">
+        <is>
+          <t>dian-bgt</t>
+        </is>
+      </c>
+      <c r="C2570" t="inlineStr">
+        <is>
+          <t>Diane</t>
+        </is>
+      </c>
+      <c r="D2570" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2570" t="n">
+        <v>87</v>
+      </c>
+      <c r="F2570" t="n">
+        <v>265</v>
+      </c>
+      <c r="G2570" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2570" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2571">
+      <c r="A2571" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2571" t="inlineStr">
+        <is>
+          <t>Mylene-Jnt</t>
+        </is>
+      </c>
+      <c r="C2571" t="inlineStr">
+        <is>
+          <t>Mylène</t>
+        </is>
+      </c>
+      <c r="D2571" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2571" t="n">
+        <v>88</v>
+      </c>
+      <c r="F2571" t="n">
+        <v>258</v>
+      </c>
+      <c r="G2571" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2571" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2572">
+      <c r="A2572" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2572" t="inlineStr">
+        <is>
+          <t>JEVAISGAGNER10</t>
+        </is>
+      </c>
+      <c r="C2572" t="inlineStr">
+        <is>
+          <t>Xavier</t>
+        </is>
+      </c>
+      <c r="D2572" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2572" t="n">
+        <v>89</v>
+      </c>
+      <c r="F2572" t="n">
+        <v>254</v>
+      </c>
+      <c r="G2572" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2572" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2573">
+      <c r="A2573" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2573" t="inlineStr">
+        <is>
+          <t>Melissagzb</t>
+        </is>
+      </c>
+      <c r="C2573" t="inlineStr">
+        <is>
+          <t>Melissa</t>
+        </is>
+      </c>
+      <c r="D2573" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2573" t="n">
+        <v>90</v>
+      </c>
+      <c r="F2573" t="n">
+        <v>254</v>
+      </c>
+      <c r="G2573" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2573" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2574">
+      <c r="A2574" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2574" t="inlineStr">
+        <is>
+          <t>K_Marp</t>
+        </is>
+      </c>
+      <c r="C2574" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
+      <c r="D2574" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2574" t="n">
+        <v>91</v>
+      </c>
+      <c r="F2574" t="n">
+        <v>254</v>
+      </c>
+      <c r="G2574" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2574" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2575">
+      <c r="A2575" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2575" t="inlineStr">
+        <is>
+          <t>A-MOE</t>
+        </is>
+      </c>
+      <c r="C2575" t="inlineStr">
+        <is>
+          <t>Françoise</t>
+        </is>
+      </c>
+      <c r="D2575" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2575" t="n">
+        <v>92</v>
+      </c>
+      <c r="F2575" t="n">
+        <v>254</v>
+      </c>
+      <c r="G2575" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2575" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2576">
+      <c r="A2576" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2576" t="inlineStr">
+        <is>
+          <t>davidd23</t>
+        </is>
+      </c>
+      <c r="C2576" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D2576" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2576" t="n">
+        <v>93</v>
+      </c>
+      <c r="F2576" t="n">
+        <v>249</v>
+      </c>
+      <c r="G2576" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2576" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2577">
+      <c r="A2577" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2577" t="inlineStr">
+        <is>
+          <t>Taylor2901</t>
+        </is>
+      </c>
+      <c r="C2577" t="inlineStr">
+        <is>
+          <t>ousmane</t>
+        </is>
+      </c>
+      <c r="D2577" t="inlineStr"/>
+      <c r="E2577" t="n">
+        <v>94</v>
+      </c>
+      <c r="F2577" t="n">
+        <v>241</v>
+      </c>
+      <c r="G2577" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2577" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2578">
+      <c r="A2578" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2578" t="inlineStr">
+        <is>
+          <t>GLR_PRIME</t>
+        </is>
+      </c>
+      <c r="C2578" t="inlineStr">
+        <is>
+          <t>Gabriel</t>
+        </is>
+      </c>
+      <c r="D2578" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2578" t="n">
+        <v>95</v>
+      </c>
+      <c r="F2578" t="n">
+        <v>234</v>
+      </c>
+      <c r="G2578" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2578" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2579">
+      <c r="A2579" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2579" t="inlineStr">
+        <is>
+          <t>Emma_Noel</t>
+        </is>
+      </c>
+      <c r="C2579" t="inlineStr">
+        <is>
+          <t>Emma</t>
+        </is>
+      </c>
+      <c r="D2579" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2579" t="n">
+        <v>96</v>
+      </c>
+      <c r="F2579" t="n">
+        <v>232</v>
+      </c>
+      <c r="G2579" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2579" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2580">
+      <c r="A2580" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2580" t="inlineStr">
+        <is>
+          <t>Fa_One</t>
+        </is>
+      </c>
+      <c r="C2580" t="inlineStr">
+        <is>
+          <t>Farah</t>
+        </is>
+      </c>
+      <c r="D2580" t="inlineStr"/>
+      <c r="E2580" t="n">
+        <v>97</v>
+      </c>
+      <c r="F2580" t="n">
+        <v>230</v>
+      </c>
+      <c r="G2580" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2580" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2581">
+      <c r="A2581" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2581" t="inlineStr">
+        <is>
+          <t>SamSamH8</t>
+        </is>
+      </c>
+      <c r="C2581" t="inlineStr">
+        <is>
+          <t>Samia</t>
+        </is>
+      </c>
+      <c r="D2581" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2581" t="n">
+        <v>98</v>
+      </c>
+      <c r="F2581" t="n">
+        <v>223</v>
+      </c>
+      <c r="G2581" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2581" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2582">
+      <c r="A2582" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2582" t="inlineStr">
+        <is>
+          <t>PavelMel</t>
+        </is>
+      </c>
+      <c r="C2582" t="inlineStr">
+        <is>
+          <t>Mélissa</t>
+        </is>
+      </c>
+      <c r="D2582" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2582" t="n">
+        <v>99</v>
+      </c>
+      <c r="F2582" t="n">
+        <v>208</v>
+      </c>
+      <c r="G2582" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2582" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2583">
+      <c r="A2583" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2583" t="inlineStr">
+        <is>
+          <t>BrickXVI</t>
+        </is>
+      </c>
+      <c r="C2583" t="inlineStr">
+        <is>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="D2583" t="inlineStr"/>
+      <c r="E2583" t="n">
+        <v>100</v>
+      </c>
+      <c r="F2583" t="n">
+        <v>205</v>
+      </c>
+      <c r="G2583" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2583" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2584">
+      <c r="A2584" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2584" t="inlineStr">
+        <is>
+          <t>SabC1</t>
+        </is>
+      </c>
+      <c r="C2584" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="D2584" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2584" t="n">
+        <v>101</v>
+      </c>
+      <c r="F2584" t="n">
+        <v>190</v>
+      </c>
+      <c r="G2584" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2584" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2585">
+      <c r="A2585" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2585" t="inlineStr">
+        <is>
+          <t>Fuzo697</t>
+        </is>
+      </c>
+      <c r="C2585" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D2585" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2585" t="n">
+        <v>102</v>
+      </c>
+      <c r="F2585" t="n">
+        <v>189</v>
+      </c>
+      <c r="G2585" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2585" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2586">
+      <c r="A2586" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2586" t="inlineStr">
+        <is>
+          <t>LeaBrd</t>
+        </is>
+      </c>
+      <c r="C2586" t="inlineStr">
+        <is>
+          <t>Léa</t>
+        </is>
+      </c>
+      <c r="D2586" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2586" t="n">
+        <v>103</v>
+      </c>
+      <c r="F2586" t="n">
+        <v>182</v>
+      </c>
+      <c r="G2586" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2586" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2587">
+      <c r="A2587" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2587" t="inlineStr">
+        <is>
+          <t>MxKnight</t>
+        </is>
+      </c>
+      <c r="C2587" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D2587" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2587" t="n">
+        <v>104</v>
+      </c>
+      <c r="F2587" t="n">
+        <v>180</v>
+      </c>
+      <c r="G2587" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2587" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2588">
+      <c r="A2588" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2588" t="inlineStr">
+        <is>
+          <t>Sab_M45</t>
+        </is>
+      </c>
+      <c r="C2588" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="D2588" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2588" t="n">
+        <v>105</v>
+      </c>
+      <c r="F2588" t="n">
+        <v>180</v>
+      </c>
+      <c r="G2588" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2588" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2589">
+      <c r="A2589" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2589" t="inlineStr">
+        <is>
+          <t>KIKS999</t>
+        </is>
+      </c>
+      <c r="C2589" t="inlineStr">
+        <is>
+          <t>Killian</t>
+        </is>
+      </c>
+      <c r="D2589" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2589" t="n">
+        <v>106</v>
+      </c>
+      <c r="F2589" t="n">
+        <v>158</v>
+      </c>
+      <c r="G2589" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2589" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2590">
+      <c r="A2590" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2590" t="inlineStr">
+        <is>
+          <t>Laetice2020</t>
+        </is>
+      </c>
+      <c r="C2590" t="inlineStr">
+        <is>
+          <t>Laetitia</t>
+        </is>
+      </c>
+      <c r="D2590" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2590" t="n">
+        <v>107</v>
+      </c>
+      <c r="F2590" t="n">
+        <v>138</v>
+      </c>
+      <c r="G2590" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2590" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2591">
+      <c r="A2591" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2591" t="inlineStr">
+        <is>
+          <t>RBTL</t>
+        </is>
+      </c>
+      <c r="C2591" t="inlineStr">
+        <is>
+          <t>lea</t>
+        </is>
+      </c>
+      <c r="D2591" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2591" t="n">
+        <v>108</v>
+      </c>
+      <c r="F2591" t="n">
+        <v>138</v>
+      </c>
+      <c r="G2591" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2591" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2592">
+      <c r="A2592" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2592" t="inlineStr">
+        <is>
+          <t>RomainLect</t>
+        </is>
+      </c>
+      <c r="C2592" t="inlineStr">
+        <is>
+          <t>romain</t>
+        </is>
+      </c>
+      <c r="D2592" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2592" t="n">
+        <v>109</v>
+      </c>
+      <c r="F2592" t="n">
+        <v>108</v>
+      </c>
+      <c r="G2592" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2592" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historique_joueurs.xlsx
+++ b/historique_joueurs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2592"/>
+  <dimension ref="A1:H2701"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86912,6 +86912,3684 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2593">
+      <c r="A2593" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2593" t="inlineStr">
+        <is>
+          <t>Ninaaaa</t>
+        </is>
+      </c>
+      <c r="C2593" t="inlineStr">
+        <is>
+          <t>Nina</t>
+        </is>
+      </c>
+      <c r="D2593" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2593" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2593" t="n">
+        <v>903</v>
+      </c>
+      <c r="G2593" t="n">
+        <v>9</v>
+      </c>
+      <c r="H2593" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2594">
+      <c r="A2594" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2594" t="inlineStr">
+        <is>
+          <t>Mamad_Shelter</t>
+        </is>
+      </c>
+      <c r="C2594" t="inlineStr">
+        <is>
+          <t>Mamadou</t>
+        </is>
+      </c>
+      <c r="D2594" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2594" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2594" t="n">
+        <v>859</v>
+      </c>
+      <c r="G2594" t="n">
+        <v>9</v>
+      </c>
+      <c r="H2594" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2595">
+      <c r="A2595" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2595" t="inlineStr">
+        <is>
+          <t>Stephbreton</t>
+        </is>
+      </c>
+      <c r="C2595" t="inlineStr">
+        <is>
+          <t>STEPHANE</t>
+        </is>
+      </c>
+      <c r="D2595" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2595" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2595" t="n">
+        <v>741</v>
+      </c>
+      <c r="G2595" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2595" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2596">
+      <c r="A2596" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2596" t="inlineStr">
+        <is>
+          <t>Coucoucassecou</t>
+        </is>
+      </c>
+      <c r="C2596" t="inlineStr">
+        <is>
+          <t>Brayen</t>
+        </is>
+      </c>
+      <c r="D2596" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2596" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2596" t="n">
+        <v>726</v>
+      </c>
+      <c r="G2596" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2596" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2597">
+      <c r="A2597" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2597" t="inlineStr">
+        <is>
+          <t>GOAT#UE4U8KA6</t>
+        </is>
+      </c>
+      <c r="C2597" t="inlineStr">
+        <is>
+          <t>Jean Baptiste</t>
+        </is>
+      </c>
+      <c r="D2597" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2597" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2597" t="n">
+        <v>710</v>
+      </c>
+      <c r="G2597" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2597" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2598">
+      <c r="A2598" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2598" t="inlineStr">
+        <is>
+          <t>Nonito20</t>
+        </is>
+      </c>
+      <c r="C2598" t="inlineStr">
+        <is>
+          <t>Arnaud</t>
+        </is>
+      </c>
+      <c r="D2598" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2598" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2598" t="n">
+        <v>693</v>
+      </c>
+      <c r="G2598" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2598" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2599">
+      <c r="A2599" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2599" t="inlineStr">
+        <is>
+          <t>BOUGA#2JGXP</t>
+        </is>
+      </c>
+      <c r="C2599" t="inlineStr">
+        <is>
+          <t>BOUGA</t>
+        </is>
+      </c>
+      <c r="D2599" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2599" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2599" t="n">
+        <v>691</v>
+      </c>
+      <c r="G2599" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2599" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2600">
+      <c r="A2600" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2600" t="inlineStr">
+        <is>
+          <t>Filipinho95</t>
+        </is>
+      </c>
+      <c r="C2600" t="inlineStr">
+        <is>
+          <t>Filipe</t>
+        </is>
+      </c>
+      <c r="D2600" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2600" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2600" t="n">
+        <v>683</v>
+      </c>
+      <c r="G2600" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2600" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2601">
+      <c r="A2601" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2601" t="inlineStr">
+        <is>
+          <t>Anais757817</t>
+        </is>
+      </c>
+      <c r="C2601" t="inlineStr">
+        <is>
+          <t>Anaïs</t>
+        </is>
+      </c>
+      <c r="D2601" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2601" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2601" t="n">
+        <v>668</v>
+      </c>
+      <c r="G2601" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2601" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2602">
+      <c r="A2602" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2602" t="inlineStr">
+        <is>
+          <t>catherine#5FRTD</t>
+        </is>
+      </c>
+      <c r="C2602" t="inlineStr">
+        <is>
+          <t>catherine</t>
+        </is>
+      </c>
+      <c r="D2602" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2602" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2602" t="n">
+        <v>665</v>
+      </c>
+      <c r="G2602" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2602" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2603">
+      <c r="A2603" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2603" t="inlineStr">
+        <is>
+          <t>SID-F-ANDRE</t>
+        </is>
+      </c>
+      <c r="C2603" t="inlineStr">
+        <is>
+          <t>Denis</t>
+        </is>
+      </c>
+      <c r="D2603" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2603" t="n">
+        <v>11</v>
+      </c>
+      <c r="F2603" t="n">
+        <v>664</v>
+      </c>
+      <c r="G2603" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2603" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2604">
+      <c r="A2604" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2604" t="inlineStr">
+        <is>
+          <t>MagicMath</t>
+        </is>
+      </c>
+      <c r="C2604" t="inlineStr">
+        <is>
+          <t>Mathieu</t>
+        </is>
+      </c>
+      <c r="D2604" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2604" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2604" t="n">
+        <v>645</v>
+      </c>
+      <c r="G2604" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2604" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2605">
+      <c r="A2605" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2605" t="inlineStr">
+        <is>
+          <t>Leo_durable</t>
+        </is>
+      </c>
+      <c r="C2605" t="inlineStr">
+        <is>
+          <t>Leo</t>
+        </is>
+      </c>
+      <c r="D2605" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2605" t="n">
+        <v>13</v>
+      </c>
+      <c r="F2605" t="n">
+        <v>639</v>
+      </c>
+      <c r="G2605" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2605" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2606">
+      <c r="A2606" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2606" t="inlineStr">
+        <is>
+          <t>Panaff</t>
+        </is>
+      </c>
+      <c r="C2606" t="inlineStr">
+        <is>
+          <t>Panaf</t>
+        </is>
+      </c>
+      <c r="D2606" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2606" t="n">
+        <v>14</v>
+      </c>
+      <c r="F2606" t="n">
+        <v>631</v>
+      </c>
+      <c r="G2606" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2606" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2607">
+      <c r="A2607" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2607" t="inlineStr">
+        <is>
+          <t>Marion1822</t>
+        </is>
+      </c>
+      <c r="C2607" t="inlineStr">
+        <is>
+          <t>Marion</t>
+        </is>
+      </c>
+      <c r="D2607" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2607" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2607" t="n">
+        <v>612</v>
+      </c>
+      <c r="G2607" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2607" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2608">
+      <c r="A2608" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2608" t="inlineStr">
+        <is>
+          <t>goat#AD6GS</t>
+        </is>
+      </c>
+      <c r="C2608" t="inlineStr">
+        <is>
+          <t>goat</t>
+        </is>
+      </c>
+      <c r="D2608" t="inlineStr"/>
+      <c r="E2608" t="n">
+        <v>16</v>
+      </c>
+      <c r="F2608" t="n">
+        <v>603</v>
+      </c>
+      <c r="G2608" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2608" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2609">
+      <c r="A2609" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2609" t="inlineStr">
+        <is>
+          <t>EmyEnzo</t>
+        </is>
+      </c>
+      <c r="C2609" t="inlineStr">
+        <is>
+          <t>Emilie</t>
+        </is>
+      </c>
+      <c r="D2609" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2609" t="n">
+        <v>17</v>
+      </c>
+      <c r="F2609" t="n">
+        <v>601</v>
+      </c>
+      <c r="G2609" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2609" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2610">
+      <c r="A2610" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2610" t="inlineStr">
+        <is>
+          <t>DJOSWA</t>
+        </is>
+      </c>
+      <c r="C2610" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oswaina </t>
+        </is>
+      </c>
+      <c r="D2610" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2610" t="n">
+        <v>18</v>
+      </c>
+      <c r="F2610" t="n">
+        <v>594</v>
+      </c>
+      <c r="G2610" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2610" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2611">
+      <c r="A2611" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2611" t="inlineStr">
+        <is>
+          <t>WalidSiuuuuu</t>
+        </is>
+      </c>
+      <c r="C2611" t="inlineStr">
+        <is>
+          <t>Walid</t>
+        </is>
+      </c>
+      <c r="D2611" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2611" t="n">
+        <v>19</v>
+      </c>
+      <c r="F2611" t="n">
+        <v>580</v>
+      </c>
+      <c r="G2611" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2611" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2612">
+      <c r="A2612" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2612" t="inlineStr">
+        <is>
+          <t>Paulasipi1998</t>
+        </is>
+      </c>
+      <c r="C2612" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="D2612" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2612" t="n">
+        <v>20</v>
+      </c>
+      <c r="F2612" t="n">
+        <v>568</v>
+      </c>
+      <c r="G2612" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2612" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2613">
+      <c r="A2613" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2613" t="inlineStr">
+        <is>
+          <t>MyriamAmr</t>
+        </is>
+      </c>
+      <c r="C2613" t="inlineStr">
+        <is>
+          <t>Myriam</t>
+        </is>
+      </c>
+      <c r="D2613" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2613" t="n">
+        <v>21</v>
+      </c>
+      <c r="F2613" t="n">
+        <v>555</v>
+      </c>
+      <c r="G2613" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2613" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2614">
+      <c r="A2614" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2614" t="inlineStr">
+        <is>
+          <t>FRHTCTD10</t>
+        </is>
+      </c>
+      <c r="C2614" t="inlineStr">
+        <is>
+          <t>Candice</t>
+        </is>
+      </c>
+      <c r="D2614" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2614" t="n">
+        <v>22</v>
+      </c>
+      <c r="F2614" t="n">
+        <v>551</v>
+      </c>
+      <c r="G2614" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2614" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2615">
+      <c r="A2615" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2615" t="inlineStr">
+        <is>
+          <t>Gronaldo_95</t>
+        </is>
+      </c>
+      <c r="C2615" t="inlineStr">
+        <is>
+          <t>Gronaldo</t>
+        </is>
+      </c>
+      <c r="D2615" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2615" t="n">
+        <v>23</v>
+      </c>
+      <c r="F2615" t="n">
+        <v>548</v>
+      </c>
+      <c r="G2615" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2615" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2616">
+      <c r="A2616" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2616" t="inlineStr">
+        <is>
+          <t>Emilay</t>
+        </is>
+      </c>
+      <c r="C2616" t="inlineStr">
+        <is>
+          <t>Émilie</t>
+        </is>
+      </c>
+      <c r="D2616" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2616" t="n">
+        <v>24</v>
+      </c>
+      <c r="F2616" t="n">
+        <v>545</v>
+      </c>
+      <c r="G2616" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2616" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2617">
+      <c r="A2617" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2617" t="inlineStr">
+        <is>
+          <t>HamzaG</t>
+        </is>
+      </c>
+      <c r="C2617" t="inlineStr">
+        <is>
+          <t>Hamza</t>
+        </is>
+      </c>
+      <c r="D2617" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2617" t="n">
+        <v>25</v>
+      </c>
+      <c r="F2617" t="n">
+        <v>538</v>
+      </c>
+      <c r="G2617" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2617" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2618">
+      <c r="A2618" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2618" t="inlineStr">
+        <is>
+          <t>Yebri</t>
+        </is>
+      </c>
+      <c r="C2618" t="inlineStr">
+        <is>
+          <t>Brieuc</t>
+        </is>
+      </c>
+      <c r="D2618" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2618" t="n">
+        <v>26</v>
+      </c>
+      <c r="F2618" t="n">
+        <v>531</v>
+      </c>
+      <c r="G2618" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2618" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2619">
+      <c r="A2619" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2619" t="inlineStr">
+        <is>
+          <t>Ilan_260_</t>
+        </is>
+      </c>
+      <c r="C2619" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ilann </t>
+        </is>
+      </c>
+      <c r="D2619" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2619" t="n">
+        <v>27</v>
+      </c>
+      <c r="F2619" t="n">
+        <v>524</v>
+      </c>
+      <c r="G2619" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2619" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2620">
+      <c r="A2620" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2620" t="inlineStr">
+        <is>
+          <t>Ouiouiausoleil</t>
+        </is>
+      </c>
+      <c r="C2620" t="inlineStr">
+        <is>
+          <t>Ouissal</t>
+        </is>
+      </c>
+      <c r="D2620" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2620" t="n">
+        <v>28</v>
+      </c>
+      <c r="F2620" t="n">
+        <v>519</v>
+      </c>
+      <c r="G2620" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2620" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2621">
+      <c r="A2621" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2621" t="inlineStr">
+        <is>
+          <t>Leandrocp</t>
+        </is>
+      </c>
+      <c r="C2621" t="inlineStr">
+        <is>
+          <t>Leandro</t>
+        </is>
+      </c>
+      <c r="D2621" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2621" t="n">
+        <v>29</v>
+      </c>
+      <c r="F2621" t="n">
+        <v>512</v>
+      </c>
+      <c r="G2621" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2621" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2622">
+      <c r="A2622" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2622" t="inlineStr">
+        <is>
+          <t>chaychaychay</t>
+        </is>
+      </c>
+      <c r="C2622" t="inlineStr">
+        <is>
+          <t>Chaymaa</t>
+        </is>
+      </c>
+      <c r="D2622" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2622" t="n">
+        <v>30</v>
+      </c>
+      <c r="F2622" t="n">
+        <v>512</v>
+      </c>
+      <c r="G2622" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2622" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2623">
+      <c r="A2623" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2623" t="inlineStr">
+        <is>
+          <t>BadrLeo</t>
+        </is>
+      </c>
+      <c r="C2623" t="inlineStr">
+        <is>
+          <t>Badr Leo</t>
+        </is>
+      </c>
+      <c r="D2623" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2623" t="n">
+        <v>31</v>
+      </c>
+      <c r="F2623" t="n">
+        <v>510</v>
+      </c>
+      <c r="G2623" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2623" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2624">
+      <c r="A2624" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2624" t="inlineStr">
+        <is>
+          <t>MargauxCtln</t>
+        </is>
+      </c>
+      <c r="C2624" t="inlineStr">
+        <is>
+          <t>Margaux</t>
+        </is>
+      </c>
+      <c r="D2624" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2624" t="n">
+        <v>32</v>
+      </c>
+      <c r="F2624" t="n">
+        <v>507</v>
+      </c>
+      <c r="G2624" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2624" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2625">
+      <c r="A2625" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2625" t="inlineStr">
+        <is>
+          <t>YassineZ95</t>
+        </is>
+      </c>
+      <c r="C2625" t="inlineStr">
+        <is>
+          <t>Yassine Z</t>
+        </is>
+      </c>
+      <c r="D2625" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2625" t="n">
+        <v>33</v>
+      </c>
+      <c r="F2625" t="n">
+        <v>505</v>
+      </c>
+      <c r="G2625" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2625" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2626">
+      <c r="A2626" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2626" t="inlineStr">
+        <is>
+          <t>Ppo28</t>
+        </is>
+      </c>
+      <c r="C2626" t="inlineStr">
+        <is>
+          <t>Prescylla</t>
+        </is>
+      </c>
+      <c r="D2626" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2626" t="n">
+        <v>34</v>
+      </c>
+      <c r="F2626" t="n">
+        <v>498</v>
+      </c>
+      <c r="G2626" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2626" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2627">
+      <c r="A2627" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2627" t="inlineStr">
+        <is>
+          <t>Ambrepic</t>
+        </is>
+      </c>
+      <c r="C2627" t="inlineStr">
+        <is>
+          <t>Ambre</t>
+        </is>
+      </c>
+      <c r="D2627" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2627" t="n">
+        <v>35</v>
+      </c>
+      <c r="F2627" t="n">
+        <v>498</v>
+      </c>
+      <c r="G2627" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2627" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2628">
+      <c r="A2628" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2628" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="C2628" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="D2628" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2628" t="n">
+        <v>36</v>
+      </c>
+      <c r="F2628" t="n">
+        <v>496</v>
+      </c>
+      <c r="G2628" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2628" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2629">
+      <c r="A2629" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2629" t="inlineStr">
+        <is>
+          <t>Timy</t>
+        </is>
+      </c>
+      <c r="C2629" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="D2629" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2629" t="n">
+        <v>37</v>
+      </c>
+      <c r="F2629" t="n">
+        <v>494</v>
+      </c>
+      <c r="G2629" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2629" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2630">
+      <c r="A2630" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2630" t="inlineStr">
+        <is>
+          <t>C4M</t>
+        </is>
+      </c>
+      <c r="C2630" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D2630" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2630" t="n">
+        <v>38</v>
+      </c>
+      <c r="F2630" t="n">
+        <v>490</v>
+      </c>
+      <c r="G2630" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2630" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2631">
+      <c r="A2631" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2631" t="inlineStr">
+        <is>
+          <t>Ze_GOAT</t>
+        </is>
+      </c>
+      <c r="C2631" t="inlineStr">
+        <is>
+          <t>Yasser</t>
+        </is>
+      </c>
+      <c r="D2631" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2631" t="n">
+        <v>39</v>
+      </c>
+      <c r="F2631" t="n">
+        <v>488</v>
+      </c>
+      <c r="G2631" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2631" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2632">
+      <c r="A2632" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2632" t="inlineStr">
+        <is>
+          <t>Maruyama</t>
+        </is>
+      </c>
+      <c r="C2632" t="inlineStr">
+        <is>
+          <t>Gabrielle</t>
+        </is>
+      </c>
+      <c r="D2632" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2632" t="n">
+        <v>40</v>
+      </c>
+      <c r="F2632" t="n">
+        <v>484</v>
+      </c>
+      <c r="G2632" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2632" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2633">
+      <c r="A2633" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2633" t="inlineStr">
+        <is>
+          <t>Valentine___</t>
+        </is>
+      </c>
+      <c r="C2633" t="inlineStr">
+        <is>
+          <t>Valentine</t>
+        </is>
+      </c>
+      <c r="D2633" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2633" t="n">
+        <v>41</v>
+      </c>
+      <c r="F2633" t="n">
+        <v>483</v>
+      </c>
+      <c r="G2633" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2633" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2634">
+      <c r="A2634" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2634" t="inlineStr">
+        <is>
+          <t>Cleem22</t>
+        </is>
+      </c>
+      <c r="C2634" t="inlineStr">
+        <is>
+          <t>Clemence</t>
+        </is>
+      </c>
+      <c r="D2634" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2634" t="n">
+        <v>42</v>
+      </c>
+      <c r="F2634" t="n">
+        <v>478</v>
+      </c>
+      <c r="G2634" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2634" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2635">
+      <c r="A2635" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2635" t="inlineStr">
+        <is>
+          <t>Marie__92</t>
+        </is>
+      </c>
+      <c r="C2635" t="inlineStr">
+        <is>
+          <t>Marie</t>
+        </is>
+      </c>
+      <c r="D2635" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2635" t="n">
+        <v>43</v>
+      </c>
+      <c r="F2635" t="n">
+        <v>477</v>
+      </c>
+      <c r="G2635" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2635" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2636">
+      <c r="A2636" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2636" t="inlineStr">
+        <is>
+          <t>Fethinho</t>
+        </is>
+      </c>
+      <c r="C2636" t="inlineStr">
+        <is>
+          <t>Fethi</t>
+        </is>
+      </c>
+      <c r="D2636" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2636" t="n">
+        <v>44</v>
+      </c>
+      <c r="F2636" t="n">
+        <v>474</v>
+      </c>
+      <c r="G2636" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2636" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2637">
+      <c r="A2637" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2637" t="inlineStr">
+        <is>
+          <t>AudreyB225</t>
+        </is>
+      </c>
+      <c r="C2637" t="inlineStr">
+        <is>
+          <t>Audrey</t>
+        </is>
+      </c>
+      <c r="D2637" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2637" t="n">
+        <v>45</v>
+      </c>
+      <c r="F2637" t="n">
+        <v>463</v>
+      </c>
+      <c r="G2637" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2637" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2638">
+      <c r="A2638" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2638" t="inlineStr">
+        <is>
+          <t>Teddbear</t>
+        </is>
+      </c>
+      <c r="C2638" t="inlineStr">
+        <is>
+          <t>Tedy</t>
+        </is>
+      </c>
+      <c r="D2638" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2638" t="n">
+        <v>46</v>
+      </c>
+      <c r="F2638" t="n">
+        <v>463</v>
+      </c>
+      <c r="G2638" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2638" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2639">
+      <c r="A2639" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2639" t="inlineStr">
+        <is>
+          <t>Romain_JO</t>
+        </is>
+      </c>
+      <c r="C2639" t="inlineStr">
+        <is>
+          <t>Romain J</t>
+        </is>
+      </c>
+      <c r="D2639" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2639" t="n">
+        <v>47</v>
+      </c>
+      <c r="F2639" t="n">
+        <v>460</v>
+      </c>
+      <c r="G2639" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2639" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2640">
+      <c r="A2640" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2640" t="inlineStr">
+        <is>
+          <t>Exia95</t>
+        </is>
+      </c>
+      <c r="C2640" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D2640" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2640" t="n">
+        <v>48</v>
+      </c>
+      <c r="F2640" t="n">
+        <v>451</v>
+      </c>
+      <c r="G2640" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2640" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2641">
+      <c r="A2641" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2641" t="inlineStr">
+        <is>
+          <t>Kaliced</t>
+        </is>
+      </c>
+      <c r="C2641" t="inlineStr">
+        <is>
+          <t>Kalice</t>
+        </is>
+      </c>
+      <c r="D2641" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2641" t="n">
+        <v>49</v>
+      </c>
+      <c r="F2641" t="n">
+        <v>448</v>
+      </c>
+      <c r="G2641" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2641" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2642">
+      <c r="A2642" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2642" t="inlineStr">
+        <is>
+          <t>Chadia__</t>
+        </is>
+      </c>
+      <c r="C2642" t="inlineStr">
+        <is>
+          <t>Chadia</t>
+        </is>
+      </c>
+      <c r="D2642" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2642" t="n">
+        <v>50</v>
+      </c>
+      <c r="F2642" t="n">
+        <v>436</v>
+      </c>
+      <c r="G2642" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2642" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2643">
+      <c r="A2643" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2643" t="inlineStr">
+        <is>
+          <t>Matt#4B4CU</t>
+        </is>
+      </c>
+      <c r="C2643" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="D2643" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2643" t="n">
+        <v>51</v>
+      </c>
+      <c r="F2643" t="n">
+        <v>436</v>
+      </c>
+      <c r="G2643" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2643" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2644">
+      <c r="A2644" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2644" t="inlineStr">
+        <is>
+          <t>Cindie_JJA</t>
+        </is>
+      </c>
+      <c r="C2644" t="inlineStr">
+        <is>
+          <t>Cindie</t>
+        </is>
+      </c>
+      <c r="D2644" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2644" t="n">
+        <v>52</v>
+      </c>
+      <c r="F2644" t="n">
+        <v>433</v>
+      </c>
+      <c r="G2644" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2644" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2645">
+      <c r="A2645" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2645" t="inlineStr">
+        <is>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="C2645" t="inlineStr">
+        <is>
+          <t>Julie</t>
+        </is>
+      </c>
+      <c r="D2645" t="inlineStr"/>
+      <c r="E2645" t="n">
+        <v>53</v>
+      </c>
+      <c r="F2645" t="n">
+        <v>430</v>
+      </c>
+      <c r="G2645" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2645" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2646">
+      <c r="A2646" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2646" t="inlineStr">
+        <is>
+          <t>Soraya-Y</t>
+        </is>
+      </c>
+      <c r="C2646" t="inlineStr">
+        <is>
+          <t>Soraya</t>
+        </is>
+      </c>
+      <c r="D2646" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2646" t="n">
+        <v>54</v>
+      </c>
+      <c r="F2646" t="n">
+        <v>418</v>
+      </c>
+      <c r="G2646" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2646" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2647">
+      <c r="A2647" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2647" t="inlineStr">
+        <is>
+          <t>Mr-Worldwide</t>
+        </is>
+      </c>
+      <c r="C2647" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="D2647" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2647" t="n">
+        <v>55</v>
+      </c>
+      <c r="F2647" t="n">
+        <v>411</v>
+      </c>
+      <c r="G2647" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2647" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2648">
+      <c r="A2648" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2648" t="inlineStr">
+        <is>
+          <t>Camillewbl</t>
+        </is>
+      </c>
+      <c r="C2648" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D2648" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2648" t="n">
+        <v>56</v>
+      </c>
+      <c r="F2648" t="n">
+        <v>405</v>
+      </c>
+      <c r="G2648" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2648" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2649">
+      <c r="A2649" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2649" t="inlineStr">
+        <is>
+          <t>PANENKANY</t>
+        </is>
+      </c>
+      <c r="C2649" t="inlineStr">
+        <is>
+          <t>Damien</t>
+        </is>
+      </c>
+      <c r="D2649" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2649" t="n">
+        <v>57</v>
+      </c>
+      <c r="F2649" t="n">
+        <v>404</v>
+      </c>
+      <c r="G2649" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2649" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2650">
+      <c r="A2650" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2650" t="inlineStr">
+        <is>
+          <t>JKInternational</t>
+        </is>
+      </c>
+      <c r="C2650" t="inlineStr">
+        <is>
+          <t>Joachim</t>
+        </is>
+      </c>
+      <c r="D2650" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2650" t="n">
+        <v>58</v>
+      </c>
+      <c r="F2650" t="n">
+        <v>396</v>
+      </c>
+      <c r="G2650" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2650" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2651">
+      <c r="A2651" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2651" t="inlineStr">
+        <is>
+          <t>Erwan#4G91X</t>
+        </is>
+      </c>
+      <c r="C2651" t="inlineStr">
+        <is>
+          <t>Erwan</t>
+        </is>
+      </c>
+      <c r="D2651" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2651" t="n">
+        <v>59</v>
+      </c>
+      <c r="F2651" t="n">
+        <v>393</v>
+      </c>
+      <c r="G2651" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2651" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2652">
+      <c r="A2652" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2652" t="inlineStr">
+        <is>
+          <t>Pipou931</t>
+        </is>
+      </c>
+      <c r="C2652" t="inlineStr">
+        <is>
+          <t>Juliie</t>
+        </is>
+      </c>
+      <c r="D2652" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2652" t="n">
+        <v>60</v>
+      </c>
+      <c r="F2652" t="n">
+        <v>389</v>
+      </c>
+      <c r="G2652" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2652" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2653">
+      <c r="A2653" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2653" t="inlineStr">
+        <is>
+          <t>Seesee</t>
+        </is>
+      </c>
+      <c r="C2653" t="inlineStr">
+        <is>
+          <t>Selver</t>
+        </is>
+      </c>
+      <c r="D2653" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2653" t="n">
+        <v>61</v>
+      </c>
+      <c r="F2653" t="n">
+        <v>382</v>
+      </c>
+      <c r="G2653" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2653" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2654">
+      <c r="A2654" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2654" t="inlineStr">
+        <is>
+          <t>lenaaik</t>
+        </is>
+      </c>
+      <c r="C2654" t="inlineStr">
+        <is>
+          <t>Lénaïk</t>
+        </is>
+      </c>
+      <c r="D2654" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2654" t="n">
+        <v>62</v>
+      </c>
+      <c r="F2654" t="n">
+        <v>382</v>
+      </c>
+      <c r="G2654" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2654" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2655">
+      <c r="A2655" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2655" t="inlineStr">
+        <is>
+          <t>Elisewiss</t>
+        </is>
+      </c>
+      <c r="C2655" t="inlineStr">
+        <is>
+          <t>Elise</t>
+        </is>
+      </c>
+      <c r="D2655" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2655" t="n">
+        <v>63</v>
+      </c>
+      <c r="F2655" t="n">
+        <v>382</v>
+      </c>
+      <c r="G2655" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2655" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2656">
+      <c r="A2656" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2656" t="inlineStr">
+        <is>
+          <t>ChrisKr1Deg1</t>
+        </is>
+      </c>
+      <c r="C2656" t="inlineStr">
+        <is>
+          <t>christophe</t>
+        </is>
+      </c>
+      <c r="D2656" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2656" t="n">
+        <v>64</v>
+      </c>
+      <c r="F2656" t="n">
+        <v>382</v>
+      </c>
+      <c r="G2656" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2656" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2657">
+      <c r="A2657" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2657" t="inlineStr">
+        <is>
+          <t>1993ahm</t>
+        </is>
+      </c>
+      <c r="C2657" t="inlineStr">
+        <is>
+          <t>Ahmed</t>
+        </is>
+      </c>
+      <c r="D2657" t="inlineStr"/>
+      <c r="E2657" t="n">
+        <v>65</v>
+      </c>
+      <c r="F2657" t="n">
+        <v>381</v>
+      </c>
+      <c r="G2657" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2657" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2658">
+      <c r="A2658" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2658" t="inlineStr">
+        <is>
+          <t>Devilrock95</t>
+        </is>
+      </c>
+      <c r="C2658" t="inlineStr">
+        <is>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="D2658" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2658" t="n">
+        <v>66</v>
+      </c>
+      <c r="F2658" t="n">
+        <v>370</v>
+      </c>
+      <c r="G2658" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2658" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2659">
+      <c r="A2659" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2659" t="inlineStr">
+        <is>
+          <t>Droit_au_but7723</t>
+        </is>
+      </c>
+      <c r="C2659" t="inlineStr">
+        <is>
+          <t>Calixthe</t>
+        </is>
+      </c>
+      <c r="D2659" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2659" t="n">
+        <v>67</v>
+      </c>
+      <c r="F2659" t="n">
+        <v>358</v>
+      </c>
+      <c r="G2659" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2659" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2660">
+      <c r="A2660" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2660" t="inlineStr">
+        <is>
+          <t>Davido#4BZ54</t>
+        </is>
+      </c>
+      <c r="C2660" t="inlineStr">
+        <is>
+          <t>Davido</t>
+        </is>
+      </c>
+      <c r="D2660" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2660" t="n">
+        <v>68</v>
+      </c>
+      <c r="F2660" t="n">
+        <v>349</v>
+      </c>
+      <c r="G2660" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2660" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2661">
+      <c r="A2661" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2661" t="inlineStr">
+        <is>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="C2661" t="inlineStr">
+        <is>
+          <t>François</t>
+        </is>
+      </c>
+      <c r="D2661" t="inlineStr"/>
+      <c r="E2661" t="n">
+        <v>69</v>
+      </c>
+      <c r="F2661" t="n">
+        <v>344</v>
+      </c>
+      <c r="G2661" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2661" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2662">
+      <c r="A2662" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2662" t="inlineStr">
+        <is>
+          <t>Camss</t>
+        </is>
+      </c>
+      <c r="C2662" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D2662" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2662" t="n">
+        <v>70</v>
+      </c>
+      <c r="F2662" t="n">
+        <v>343</v>
+      </c>
+      <c r="G2662" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2662" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2663">
+      <c r="A2663" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2663" t="inlineStr">
+        <is>
+          <t>Krol#4R8XC</t>
+        </is>
+      </c>
+      <c r="C2663" t="inlineStr">
+        <is>
+          <t>Krol</t>
+        </is>
+      </c>
+      <c r="D2663" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2663" t="n">
+        <v>71</v>
+      </c>
+      <c r="F2663" t="n">
+        <v>342</v>
+      </c>
+      <c r="G2663" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2663" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2664">
+      <c r="A2664" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2664" t="inlineStr">
+        <is>
+          <t>LilianeB</t>
+        </is>
+      </c>
+      <c r="C2664" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liliane </t>
+        </is>
+      </c>
+      <c r="D2664" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2664" t="n">
+        <v>72</v>
+      </c>
+      <c r="F2664" t="n">
+        <v>337</v>
+      </c>
+      <c r="G2664" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2664" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2665">
+      <c r="A2665" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2665" t="inlineStr">
+        <is>
+          <t>Kolas</t>
+        </is>
+      </c>
+      <c r="C2665" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D2665" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2665" t="n">
+        <v>73</v>
+      </c>
+      <c r="F2665" t="n">
+        <v>324</v>
+      </c>
+      <c r="G2665" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2665" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2666">
+      <c r="A2666" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2666" t="inlineStr">
+        <is>
+          <t>JeremFZ</t>
+        </is>
+      </c>
+      <c r="C2666" t="inlineStr">
+        <is>
+          <t>Jérémy</t>
+        </is>
+      </c>
+      <c r="D2666" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2666" t="n">
+        <v>74</v>
+      </c>
+      <c r="F2666" t="n">
+        <v>322</v>
+      </c>
+      <c r="G2666" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2666" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2667">
+      <c r="A2667" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2667" t="inlineStr">
+        <is>
+          <t>MatuRenard</t>
+        </is>
+      </c>
+      <c r="C2667" t="inlineStr">
+        <is>
+          <t>Mathias</t>
+        </is>
+      </c>
+      <c r="D2667" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2667" t="n">
+        <v>75</v>
+      </c>
+      <c r="F2667" t="n">
+        <v>318</v>
+      </c>
+      <c r="G2667" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2667" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2668">
+      <c r="A2668" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2668" t="inlineStr">
+        <is>
+          <t>Liliuus</t>
+        </is>
+      </c>
+      <c r="C2668" t="inlineStr">
+        <is>
+          <t>Lilia</t>
+        </is>
+      </c>
+      <c r="D2668" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2668" t="n">
+        <v>76</v>
+      </c>
+      <c r="F2668" t="n">
+        <v>318</v>
+      </c>
+      <c r="G2668" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2668" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2669">
+      <c r="A2669" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2669" t="inlineStr">
+        <is>
+          <t>abihuts</t>
+        </is>
+      </c>
+      <c r="C2669" t="inlineStr">
+        <is>
+          <t>Antonio Moctezuma</t>
+        </is>
+      </c>
+      <c r="D2669" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2669" t="n">
+        <v>77</v>
+      </c>
+      <c r="F2669" t="n">
+        <v>303</v>
+      </c>
+      <c r="G2669" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2669" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2670">
+      <c r="A2670" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2670" t="inlineStr">
+        <is>
+          <t>Daviddesco1</t>
+        </is>
+      </c>
+      <c r="C2670" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D2670" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2670" t="n">
+        <v>78</v>
+      </c>
+      <c r="F2670" t="n">
+        <v>302</v>
+      </c>
+      <c r="G2670" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2670" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2671">
+      <c r="A2671" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2671" t="inlineStr">
+        <is>
+          <t>GOAT#UE2WM8M9</t>
+        </is>
+      </c>
+      <c r="C2671" t="inlineStr">
+        <is>
+          <t>Marilena</t>
+        </is>
+      </c>
+      <c r="D2671" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2671" t="n">
+        <v>79</v>
+      </c>
+      <c r="F2671" t="n">
+        <v>296</v>
+      </c>
+      <c r="G2671" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2671" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2672">
+      <c r="A2672" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2672" t="inlineStr">
+        <is>
+          <t>WIL1610</t>
+        </is>
+      </c>
+      <c r="C2672" t="inlineStr">
+        <is>
+          <t>William</t>
+        </is>
+      </c>
+      <c r="D2672" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2672" t="n">
+        <v>80</v>
+      </c>
+      <c r="F2672" t="n">
+        <v>292</v>
+      </c>
+      <c r="G2672" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2672" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2673">
+      <c r="A2673" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2673" t="inlineStr">
+        <is>
+          <t>Lyzone</t>
+        </is>
+      </c>
+      <c r="C2673" t="inlineStr">
+        <is>
+          <t>Lison</t>
+        </is>
+      </c>
+      <c r="D2673" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2673" t="n">
+        <v>81</v>
+      </c>
+      <c r="F2673" t="n">
+        <v>290</v>
+      </c>
+      <c r="G2673" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2673" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2674">
+      <c r="A2674" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2674" t="inlineStr">
+        <is>
+          <t>MT35T</t>
+        </is>
+      </c>
+      <c r="C2674" t="inlineStr">
+        <is>
+          <t>Mathilde</t>
+        </is>
+      </c>
+      <c r="D2674" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2674" t="n">
+        <v>82</v>
+      </c>
+      <c r="F2674" t="n">
+        <v>282</v>
+      </c>
+      <c r="G2674" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2674" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2675">
+      <c r="A2675" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2675" t="inlineStr">
+        <is>
+          <t>Priscilla#4LCAF</t>
+        </is>
+      </c>
+      <c r="C2675" t="inlineStr">
+        <is>
+          <t>Priscilla</t>
+        </is>
+      </c>
+      <c r="D2675" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2675" t="n">
+        <v>83</v>
+      </c>
+      <c r="F2675" t="n">
+        <v>274</v>
+      </c>
+      <c r="G2675" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2675" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2676">
+      <c r="A2676" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2676" t="inlineStr">
+        <is>
+          <t>Rosa_1009</t>
+        </is>
+      </c>
+      <c r="C2676" t="inlineStr">
+        <is>
+          <t>Rosaline</t>
+        </is>
+      </c>
+      <c r="D2676" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2676" t="n">
+        <v>84</v>
+      </c>
+      <c r="F2676" t="n">
+        <v>274</v>
+      </c>
+      <c r="G2676" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2676" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2677">
+      <c r="A2677" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2677" t="inlineStr">
+        <is>
+          <t>Ceciledp</t>
+        </is>
+      </c>
+      <c r="C2677" t="inlineStr">
+        <is>
+          <t>Cécile</t>
+        </is>
+      </c>
+      <c r="D2677" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2677" t="n">
+        <v>85</v>
+      </c>
+      <c r="F2677" t="n">
+        <v>268</v>
+      </c>
+      <c r="G2677" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2677" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2678">
+      <c r="A2678" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2678" t="inlineStr">
+        <is>
+          <t>PacoSarra</t>
+        </is>
+      </c>
+      <c r="C2678" t="inlineStr">
+        <is>
+          <t>Ibra</t>
+        </is>
+      </c>
+      <c r="D2678" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2678" t="n">
+        <v>86</v>
+      </c>
+      <c r="F2678" t="n">
+        <v>266</v>
+      </c>
+      <c r="G2678" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2678" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2679">
+      <c r="A2679" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2679" t="inlineStr">
+        <is>
+          <t>dian-bgt</t>
+        </is>
+      </c>
+      <c r="C2679" t="inlineStr">
+        <is>
+          <t>Diane</t>
+        </is>
+      </c>
+      <c r="D2679" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2679" t="n">
+        <v>87</v>
+      </c>
+      <c r="F2679" t="n">
+        <v>265</v>
+      </c>
+      <c r="G2679" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2679" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2680">
+      <c r="A2680" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2680" t="inlineStr">
+        <is>
+          <t>Mylene-Jnt</t>
+        </is>
+      </c>
+      <c r="C2680" t="inlineStr">
+        <is>
+          <t>Mylène</t>
+        </is>
+      </c>
+      <c r="D2680" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2680" t="n">
+        <v>88</v>
+      </c>
+      <c r="F2680" t="n">
+        <v>258</v>
+      </c>
+      <c r="G2680" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2680" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2681">
+      <c r="A2681" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2681" t="inlineStr">
+        <is>
+          <t>JEVAISGAGNER10</t>
+        </is>
+      </c>
+      <c r="C2681" t="inlineStr">
+        <is>
+          <t>Xavier</t>
+        </is>
+      </c>
+      <c r="D2681" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2681" t="n">
+        <v>89</v>
+      </c>
+      <c r="F2681" t="n">
+        <v>254</v>
+      </c>
+      <c r="G2681" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2681" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2682">
+      <c r="A2682" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2682" t="inlineStr">
+        <is>
+          <t>Melissagzb</t>
+        </is>
+      </c>
+      <c r="C2682" t="inlineStr">
+        <is>
+          <t>Melissa</t>
+        </is>
+      </c>
+      <c r="D2682" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2682" t="n">
+        <v>90</v>
+      </c>
+      <c r="F2682" t="n">
+        <v>254</v>
+      </c>
+      <c r="G2682" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2682" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2683">
+      <c r="A2683" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2683" t="inlineStr">
+        <is>
+          <t>K_Marp</t>
+        </is>
+      </c>
+      <c r="C2683" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
+      <c r="D2683" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2683" t="n">
+        <v>91</v>
+      </c>
+      <c r="F2683" t="n">
+        <v>254</v>
+      </c>
+      <c r="G2683" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2683" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2684">
+      <c r="A2684" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2684" t="inlineStr">
+        <is>
+          <t>A-MOE</t>
+        </is>
+      </c>
+      <c r="C2684" t="inlineStr">
+        <is>
+          <t>Françoise</t>
+        </is>
+      </c>
+      <c r="D2684" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2684" t="n">
+        <v>92</v>
+      </c>
+      <c r="F2684" t="n">
+        <v>254</v>
+      </c>
+      <c r="G2684" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2684" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2685">
+      <c r="A2685" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2685" t="inlineStr">
+        <is>
+          <t>davidd23</t>
+        </is>
+      </c>
+      <c r="C2685" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D2685" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2685" t="n">
+        <v>93</v>
+      </c>
+      <c r="F2685" t="n">
+        <v>249</v>
+      </c>
+      <c r="G2685" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2685" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2686">
+      <c r="A2686" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2686" t="inlineStr">
+        <is>
+          <t>Taylor2901</t>
+        </is>
+      </c>
+      <c r="C2686" t="inlineStr">
+        <is>
+          <t>ousmane</t>
+        </is>
+      </c>
+      <c r="D2686" t="inlineStr"/>
+      <c r="E2686" t="n">
+        <v>94</v>
+      </c>
+      <c r="F2686" t="n">
+        <v>241</v>
+      </c>
+      <c r="G2686" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2686" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2687">
+      <c r="A2687" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2687" t="inlineStr">
+        <is>
+          <t>GLR_PRIME</t>
+        </is>
+      </c>
+      <c r="C2687" t="inlineStr">
+        <is>
+          <t>Gabriel</t>
+        </is>
+      </c>
+      <c r="D2687" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2687" t="n">
+        <v>95</v>
+      </c>
+      <c r="F2687" t="n">
+        <v>234</v>
+      </c>
+      <c r="G2687" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2687" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2688">
+      <c r="A2688" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2688" t="inlineStr">
+        <is>
+          <t>Emma_Noel</t>
+        </is>
+      </c>
+      <c r="C2688" t="inlineStr">
+        <is>
+          <t>Emma</t>
+        </is>
+      </c>
+      <c r="D2688" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2688" t="n">
+        <v>96</v>
+      </c>
+      <c r="F2688" t="n">
+        <v>232</v>
+      </c>
+      <c r="G2688" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2688" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2689">
+      <c r="A2689" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2689" t="inlineStr">
+        <is>
+          <t>Fa_One</t>
+        </is>
+      </c>
+      <c r="C2689" t="inlineStr">
+        <is>
+          <t>Farah</t>
+        </is>
+      </c>
+      <c r="D2689" t="inlineStr"/>
+      <c r="E2689" t="n">
+        <v>97</v>
+      </c>
+      <c r="F2689" t="n">
+        <v>230</v>
+      </c>
+      <c r="G2689" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2689" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2690">
+      <c r="A2690" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2690" t="inlineStr">
+        <is>
+          <t>SamSamH8</t>
+        </is>
+      </c>
+      <c r="C2690" t="inlineStr">
+        <is>
+          <t>Samia</t>
+        </is>
+      </c>
+      <c r="D2690" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2690" t="n">
+        <v>98</v>
+      </c>
+      <c r="F2690" t="n">
+        <v>223</v>
+      </c>
+      <c r="G2690" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2690" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2691">
+      <c r="A2691" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2691" t="inlineStr">
+        <is>
+          <t>PavelMel</t>
+        </is>
+      </c>
+      <c r="C2691" t="inlineStr">
+        <is>
+          <t>Mélissa</t>
+        </is>
+      </c>
+      <c r="D2691" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2691" t="n">
+        <v>99</v>
+      </c>
+      <c r="F2691" t="n">
+        <v>208</v>
+      </c>
+      <c r="G2691" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2691" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2692">
+      <c r="A2692" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2692" t="inlineStr">
+        <is>
+          <t>BrickXVI</t>
+        </is>
+      </c>
+      <c r="C2692" t="inlineStr">
+        <is>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="D2692" t="inlineStr"/>
+      <c r="E2692" t="n">
+        <v>100</v>
+      </c>
+      <c r="F2692" t="n">
+        <v>205</v>
+      </c>
+      <c r="G2692" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2692" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2693">
+      <c r="A2693" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2693" t="inlineStr">
+        <is>
+          <t>SabC1</t>
+        </is>
+      </c>
+      <c r="C2693" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="D2693" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2693" t="n">
+        <v>101</v>
+      </c>
+      <c r="F2693" t="n">
+        <v>190</v>
+      </c>
+      <c r="G2693" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2693" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2694">
+      <c r="A2694" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2694" t="inlineStr">
+        <is>
+          <t>Fuzo697</t>
+        </is>
+      </c>
+      <c r="C2694" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D2694" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2694" t="n">
+        <v>102</v>
+      </c>
+      <c r="F2694" t="n">
+        <v>189</v>
+      </c>
+      <c r="G2694" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2694" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2695">
+      <c r="A2695" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2695" t="inlineStr">
+        <is>
+          <t>LeaBrd</t>
+        </is>
+      </c>
+      <c r="C2695" t="inlineStr">
+        <is>
+          <t>Léa</t>
+        </is>
+      </c>
+      <c r="D2695" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2695" t="n">
+        <v>103</v>
+      </c>
+      <c r="F2695" t="n">
+        <v>182</v>
+      </c>
+      <c r="G2695" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2695" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2696">
+      <c r="A2696" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2696" t="inlineStr">
+        <is>
+          <t>MxKnight</t>
+        </is>
+      </c>
+      <c r="C2696" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D2696" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2696" t="n">
+        <v>104</v>
+      </c>
+      <c r="F2696" t="n">
+        <v>180</v>
+      </c>
+      <c r="G2696" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2696" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2697">
+      <c r="A2697" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2697" t="inlineStr">
+        <is>
+          <t>Sab_M45</t>
+        </is>
+      </c>
+      <c r="C2697" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="D2697" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2697" t="n">
+        <v>105</v>
+      </c>
+      <c r="F2697" t="n">
+        <v>180</v>
+      </c>
+      <c r="G2697" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2697" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2698">
+      <c r="A2698" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2698" t="inlineStr">
+        <is>
+          <t>KIKS999</t>
+        </is>
+      </c>
+      <c r="C2698" t="inlineStr">
+        <is>
+          <t>Killian</t>
+        </is>
+      </c>
+      <c r="D2698" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2698" t="n">
+        <v>106</v>
+      </c>
+      <c r="F2698" t="n">
+        <v>158</v>
+      </c>
+      <c r="G2698" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2698" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2699">
+      <c r="A2699" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2699" t="inlineStr">
+        <is>
+          <t>Laetice2020</t>
+        </is>
+      </c>
+      <c r="C2699" t="inlineStr">
+        <is>
+          <t>Laetitia</t>
+        </is>
+      </c>
+      <c r="D2699" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2699" t="n">
+        <v>107</v>
+      </c>
+      <c r="F2699" t="n">
+        <v>138</v>
+      </c>
+      <c r="G2699" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2699" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2700">
+      <c r="A2700" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2700" t="inlineStr">
+        <is>
+          <t>RBTL</t>
+        </is>
+      </c>
+      <c r="C2700" t="inlineStr">
+        <is>
+          <t>lea</t>
+        </is>
+      </c>
+      <c r="D2700" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2700" t="n">
+        <v>108</v>
+      </c>
+      <c r="F2700" t="n">
+        <v>138</v>
+      </c>
+      <c r="G2700" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2700" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2701">
+      <c r="A2701" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2701" t="inlineStr">
+        <is>
+          <t>RomainLect</t>
+        </is>
+      </c>
+      <c r="C2701" t="inlineStr">
+        <is>
+          <t>romain</t>
+        </is>
+      </c>
+      <c r="D2701" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2701" t="n">
+        <v>109</v>
+      </c>
+      <c r="F2701" t="n">
+        <v>108</v>
+      </c>
+      <c r="G2701" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2701" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historique_joueurs.xlsx
+++ b/historique_joueurs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2701"/>
+  <dimension ref="A1:H2810"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -90590,6 +90590,3684 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2702">
+      <c r="A2702" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2702" t="inlineStr">
+        <is>
+          <t>Ninaaaa</t>
+        </is>
+      </c>
+      <c r="C2702" t="inlineStr">
+        <is>
+          <t>Nina</t>
+        </is>
+      </c>
+      <c r="D2702" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2702" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2702" t="n">
+        <v>903</v>
+      </c>
+      <c r="G2702" t="n">
+        <v>9</v>
+      </c>
+      <c r="H2702" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2703">
+      <c r="A2703" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2703" t="inlineStr">
+        <is>
+          <t>Mamad_Shelter</t>
+        </is>
+      </c>
+      <c r="C2703" t="inlineStr">
+        <is>
+          <t>Mamadou</t>
+        </is>
+      </c>
+      <c r="D2703" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2703" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2703" t="n">
+        <v>859</v>
+      </c>
+      <c r="G2703" t="n">
+        <v>9</v>
+      </c>
+      <c r="H2703" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2704">
+      <c r="A2704" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2704" t="inlineStr">
+        <is>
+          <t>Stephbreton</t>
+        </is>
+      </c>
+      <c r="C2704" t="inlineStr">
+        <is>
+          <t>STEPHANE</t>
+        </is>
+      </c>
+      <c r="D2704" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2704" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2704" t="n">
+        <v>741</v>
+      </c>
+      <c r="G2704" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2704" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2705">
+      <c r="A2705" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2705" t="inlineStr">
+        <is>
+          <t>Coucoucassecou</t>
+        </is>
+      </c>
+      <c r="C2705" t="inlineStr">
+        <is>
+          <t>Brayen</t>
+        </is>
+      </c>
+      <c r="D2705" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2705" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2705" t="n">
+        <v>726</v>
+      </c>
+      <c r="G2705" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2705" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2706">
+      <c r="A2706" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2706" t="inlineStr">
+        <is>
+          <t>GOAT#UE4U8KA6</t>
+        </is>
+      </c>
+      <c r="C2706" t="inlineStr">
+        <is>
+          <t>Jean Baptiste</t>
+        </is>
+      </c>
+      <c r="D2706" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2706" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2706" t="n">
+        <v>710</v>
+      </c>
+      <c r="G2706" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2706" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2707">
+      <c r="A2707" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2707" t="inlineStr">
+        <is>
+          <t>Nonito20</t>
+        </is>
+      </c>
+      <c r="C2707" t="inlineStr">
+        <is>
+          <t>Arnaud</t>
+        </is>
+      </c>
+      <c r="D2707" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2707" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2707" t="n">
+        <v>693</v>
+      </c>
+      <c r="G2707" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2707" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2708">
+      <c r="A2708" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2708" t="inlineStr">
+        <is>
+          <t>BOUGA#2JGXP</t>
+        </is>
+      </c>
+      <c r="C2708" t="inlineStr">
+        <is>
+          <t>BOUGA</t>
+        </is>
+      </c>
+      <c r="D2708" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2708" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2708" t="n">
+        <v>691</v>
+      </c>
+      <c r="G2708" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2708" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2709">
+      <c r="A2709" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2709" t="inlineStr">
+        <is>
+          <t>Filipinho95</t>
+        </is>
+      </c>
+      <c r="C2709" t="inlineStr">
+        <is>
+          <t>Filipe</t>
+        </is>
+      </c>
+      <c r="D2709" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2709" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2709" t="n">
+        <v>683</v>
+      </c>
+      <c r="G2709" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2709" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2710">
+      <c r="A2710" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2710" t="inlineStr">
+        <is>
+          <t>Anais757817</t>
+        </is>
+      </c>
+      <c r="C2710" t="inlineStr">
+        <is>
+          <t>Anaïs</t>
+        </is>
+      </c>
+      <c r="D2710" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2710" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2710" t="n">
+        <v>668</v>
+      </c>
+      <c r="G2710" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2710" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2711">
+      <c r="A2711" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2711" t="inlineStr">
+        <is>
+          <t>catherine#5FRTD</t>
+        </is>
+      </c>
+      <c r="C2711" t="inlineStr">
+        <is>
+          <t>catherine</t>
+        </is>
+      </c>
+      <c r="D2711" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2711" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2711" t="n">
+        <v>665</v>
+      </c>
+      <c r="G2711" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2711" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2712">
+      <c r="A2712" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2712" t="inlineStr">
+        <is>
+          <t>SID-F-ANDRE</t>
+        </is>
+      </c>
+      <c r="C2712" t="inlineStr">
+        <is>
+          <t>Denis</t>
+        </is>
+      </c>
+      <c r="D2712" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2712" t="n">
+        <v>11</v>
+      </c>
+      <c r="F2712" t="n">
+        <v>664</v>
+      </c>
+      <c r="G2712" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2712" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2713">
+      <c r="A2713" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2713" t="inlineStr">
+        <is>
+          <t>MagicMath</t>
+        </is>
+      </c>
+      <c r="C2713" t="inlineStr">
+        <is>
+          <t>Mathieu</t>
+        </is>
+      </c>
+      <c r="D2713" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2713" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2713" t="n">
+        <v>645</v>
+      </c>
+      <c r="G2713" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2713" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2714">
+      <c r="A2714" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2714" t="inlineStr">
+        <is>
+          <t>Leo_durable</t>
+        </is>
+      </c>
+      <c r="C2714" t="inlineStr">
+        <is>
+          <t>Leo</t>
+        </is>
+      </c>
+      <c r="D2714" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2714" t="n">
+        <v>13</v>
+      </c>
+      <c r="F2714" t="n">
+        <v>639</v>
+      </c>
+      <c r="G2714" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2714" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2715">
+      <c r="A2715" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2715" t="inlineStr">
+        <is>
+          <t>Panaff</t>
+        </is>
+      </c>
+      <c r="C2715" t="inlineStr">
+        <is>
+          <t>Panaf</t>
+        </is>
+      </c>
+      <c r="D2715" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2715" t="n">
+        <v>14</v>
+      </c>
+      <c r="F2715" t="n">
+        <v>631</v>
+      </c>
+      <c r="G2715" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2715" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2716">
+      <c r="A2716" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2716" t="inlineStr">
+        <is>
+          <t>Marion1822</t>
+        </is>
+      </c>
+      <c r="C2716" t="inlineStr">
+        <is>
+          <t>Marion</t>
+        </is>
+      </c>
+      <c r="D2716" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2716" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2716" t="n">
+        <v>612</v>
+      </c>
+      <c r="G2716" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2716" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2717">
+      <c r="A2717" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2717" t="inlineStr">
+        <is>
+          <t>goat#AD6GS</t>
+        </is>
+      </c>
+      <c r="C2717" t="inlineStr">
+        <is>
+          <t>goat</t>
+        </is>
+      </c>
+      <c r="D2717" t="inlineStr"/>
+      <c r="E2717" t="n">
+        <v>16</v>
+      </c>
+      <c r="F2717" t="n">
+        <v>603</v>
+      </c>
+      <c r="G2717" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2717" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2718">
+      <c r="A2718" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2718" t="inlineStr">
+        <is>
+          <t>EmyEnzo</t>
+        </is>
+      </c>
+      <c r="C2718" t="inlineStr">
+        <is>
+          <t>Emilie</t>
+        </is>
+      </c>
+      <c r="D2718" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2718" t="n">
+        <v>17</v>
+      </c>
+      <c r="F2718" t="n">
+        <v>601</v>
+      </c>
+      <c r="G2718" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2718" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2719">
+      <c r="A2719" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2719" t="inlineStr">
+        <is>
+          <t>DJOSWA</t>
+        </is>
+      </c>
+      <c r="C2719" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oswaina </t>
+        </is>
+      </c>
+      <c r="D2719" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2719" t="n">
+        <v>18</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>594</v>
+      </c>
+      <c r="G2719" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2719" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2720">
+      <c r="A2720" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2720" t="inlineStr">
+        <is>
+          <t>WalidSiuuuuu</t>
+        </is>
+      </c>
+      <c r="C2720" t="inlineStr">
+        <is>
+          <t>Walid</t>
+        </is>
+      </c>
+      <c r="D2720" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2720" t="n">
+        <v>19</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>580</v>
+      </c>
+      <c r="G2720" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2720" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2721">
+      <c r="A2721" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2721" t="inlineStr">
+        <is>
+          <t>Paulasipi1998</t>
+        </is>
+      </c>
+      <c r="C2721" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="D2721" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2721" t="n">
+        <v>20</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>568</v>
+      </c>
+      <c r="G2721" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2721" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2722">
+      <c r="A2722" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2722" t="inlineStr">
+        <is>
+          <t>MyriamAmr</t>
+        </is>
+      </c>
+      <c r="C2722" t="inlineStr">
+        <is>
+          <t>Myriam</t>
+        </is>
+      </c>
+      <c r="D2722" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2722" t="n">
+        <v>21</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>555</v>
+      </c>
+      <c r="G2722" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2722" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2723" t="inlineStr">
+        <is>
+          <t>FRHTCTD10</t>
+        </is>
+      </c>
+      <c r="C2723" t="inlineStr">
+        <is>
+          <t>Candice</t>
+        </is>
+      </c>
+      <c r="D2723" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2723" t="n">
+        <v>22</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>551</v>
+      </c>
+      <c r="G2723" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2723" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2724">
+      <c r="A2724" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2724" t="inlineStr">
+        <is>
+          <t>Gronaldo_95</t>
+        </is>
+      </c>
+      <c r="C2724" t="inlineStr">
+        <is>
+          <t>Gronaldo</t>
+        </is>
+      </c>
+      <c r="D2724" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2724" t="n">
+        <v>23</v>
+      </c>
+      <c r="F2724" t="n">
+        <v>548</v>
+      </c>
+      <c r="G2724" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2724" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2725">
+      <c r="A2725" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2725" t="inlineStr">
+        <is>
+          <t>Emilay</t>
+        </is>
+      </c>
+      <c r="C2725" t="inlineStr">
+        <is>
+          <t>Émilie</t>
+        </is>
+      </c>
+      <c r="D2725" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2725" t="n">
+        <v>24</v>
+      </c>
+      <c r="F2725" t="n">
+        <v>545</v>
+      </c>
+      <c r="G2725" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2725" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2726">
+      <c r="A2726" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2726" t="inlineStr">
+        <is>
+          <t>HamzaG</t>
+        </is>
+      </c>
+      <c r="C2726" t="inlineStr">
+        <is>
+          <t>Hamza</t>
+        </is>
+      </c>
+      <c r="D2726" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2726" t="n">
+        <v>25</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>538</v>
+      </c>
+      <c r="G2726" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2726" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2727">
+      <c r="A2727" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2727" t="inlineStr">
+        <is>
+          <t>Yebri</t>
+        </is>
+      </c>
+      <c r="C2727" t="inlineStr">
+        <is>
+          <t>Brieuc</t>
+        </is>
+      </c>
+      <c r="D2727" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2727" t="n">
+        <v>26</v>
+      </c>
+      <c r="F2727" t="n">
+        <v>531</v>
+      </c>
+      <c r="G2727" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2727" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="A2728" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2728" t="inlineStr">
+        <is>
+          <t>Ilan_260_</t>
+        </is>
+      </c>
+      <c r="C2728" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ilann </t>
+        </is>
+      </c>
+      <c r="D2728" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2728" t="n">
+        <v>27</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>524</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2728" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2729">
+      <c r="A2729" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2729" t="inlineStr">
+        <is>
+          <t>Ouiouiausoleil</t>
+        </is>
+      </c>
+      <c r="C2729" t="inlineStr">
+        <is>
+          <t>Ouissal</t>
+        </is>
+      </c>
+      <c r="D2729" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2729" t="n">
+        <v>28</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>519</v>
+      </c>
+      <c r="G2729" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2729" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2730">
+      <c r="A2730" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2730" t="inlineStr">
+        <is>
+          <t>Leandrocp</t>
+        </is>
+      </c>
+      <c r="C2730" t="inlineStr">
+        <is>
+          <t>Leandro</t>
+        </is>
+      </c>
+      <c r="D2730" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2730" t="n">
+        <v>29</v>
+      </c>
+      <c r="F2730" t="n">
+        <v>512</v>
+      </c>
+      <c r="G2730" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2730" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2731">
+      <c r="A2731" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2731" t="inlineStr">
+        <is>
+          <t>chaychaychay</t>
+        </is>
+      </c>
+      <c r="C2731" t="inlineStr">
+        <is>
+          <t>Chaymaa</t>
+        </is>
+      </c>
+      <c r="D2731" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2731" t="n">
+        <v>30</v>
+      </c>
+      <c r="F2731" t="n">
+        <v>512</v>
+      </c>
+      <c r="G2731" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2731" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2732">
+      <c r="A2732" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2732" t="inlineStr">
+        <is>
+          <t>BadrLeo</t>
+        </is>
+      </c>
+      <c r="C2732" t="inlineStr">
+        <is>
+          <t>Badr Leo</t>
+        </is>
+      </c>
+      <c r="D2732" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2732" t="n">
+        <v>31</v>
+      </c>
+      <c r="F2732" t="n">
+        <v>510</v>
+      </c>
+      <c r="G2732" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2732" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2733">
+      <c r="A2733" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2733" t="inlineStr">
+        <is>
+          <t>MargauxCtln</t>
+        </is>
+      </c>
+      <c r="C2733" t="inlineStr">
+        <is>
+          <t>Margaux</t>
+        </is>
+      </c>
+      <c r="D2733" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2733" t="n">
+        <v>32</v>
+      </c>
+      <c r="F2733" t="n">
+        <v>507</v>
+      </c>
+      <c r="G2733" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2733" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2734">
+      <c r="A2734" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2734" t="inlineStr">
+        <is>
+          <t>YassineZ95</t>
+        </is>
+      </c>
+      <c r="C2734" t="inlineStr">
+        <is>
+          <t>Yassine Z</t>
+        </is>
+      </c>
+      <c r="D2734" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2734" t="n">
+        <v>33</v>
+      </c>
+      <c r="F2734" t="n">
+        <v>505</v>
+      </c>
+      <c r="G2734" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2734" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2735">
+      <c r="A2735" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2735" t="inlineStr">
+        <is>
+          <t>Ppo28</t>
+        </is>
+      </c>
+      <c r="C2735" t="inlineStr">
+        <is>
+          <t>Prescylla</t>
+        </is>
+      </c>
+      <c r="D2735" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2735" t="n">
+        <v>34</v>
+      </c>
+      <c r="F2735" t="n">
+        <v>498</v>
+      </c>
+      <c r="G2735" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2735" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2736" t="inlineStr">
+        <is>
+          <t>Ambrepic</t>
+        </is>
+      </c>
+      <c r="C2736" t="inlineStr">
+        <is>
+          <t>Ambre</t>
+        </is>
+      </c>
+      <c r="D2736" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2736" t="n">
+        <v>35</v>
+      </c>
+      <c r="F2736" t="n">
+        <v>498</v>
+      </c>
+      <c r="G2736" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2736" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2737" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="C2737" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="D2737" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2737" t="n">
+        <v>36</v>
+      </c>
+      <c r="F2737" t="n">
+        <v>496</v>
+      </c>
+      <c r="G2737" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2737" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2738" t="inlineStr">
+        <is>
+          <t>Timy</t>
+        </is>
+      </c>
+      <c r="C2738" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="D2738" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2738" t="n">
+        <v>37</v>
+      </c>
+      <c r="F2738" t="n">
+        <v>494</v>
+      </c>
+      <c r="G2738" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2738" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2739" t="inlineStr">
+        <is>
+          <t>C4M</t>
+        </is>
+      </c>
+      <c r="C2739" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D2739" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2739" t="n">
+        <v>38</v>
+      </c>
+      <c r="F2739" t="n">
+        <v>490</v>
+      </c>
+      <c r="G2739" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2739" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2740">
+      <c r="A2740" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2740" t="inlineStr">
+        <is>
+          <t>Ze_GOAT</t>
+        </is>
+      </c>
+      <c r="C2740" t="inlineStr">
+        <is>
+          <t>Yasser</t>
+        </is>
+      </c>
+      <c r="D2740" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2740" t="n">
+        <v>39</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>488</v>
+      </c>
+      <c r="G2740" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2740" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2741">
+      <c r="A2741" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2741" t="inlineStr">
+        <is>
+          <t>Maruyama</t>
+        </is>
+      </c>
+      <c r="C2741" t="inlineStr">
+        <is>
+          <t>Gabrielle</t>
+        </is>
+      </c>
+      <c r="D2741" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2741" t="n">
+        <v>40</v>
+      </c>
+      <c r="F2741" t="n">
+        <v>484</v>
+      </c>
+      <c r="G2741" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2741" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2742">
+      <c r="A2742" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2742" t="inlineStr">
+        <is>
+          <t>Valentine___</t>
+        </is>
+      </c>
+      <c r="C2742" t="inlineStr">
+        <is>
+          <t>Valentine</t>
+        </is>
+      </c>
+      <c r="D2742" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2742" t="n">
+        <v>41</v>
+      </c>
+      <c r="F2742" t="n">
+        <v>483</v>
+      </c>
+      <c r="G2742" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2742" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2743" t="inlineStr">
+        <is>
+          <t>Cleem22</t>
+        </is>
+      </c>
+      <c r="C2743" t="inlineStr">
+        <is>
+          <t>Clemence</t>
+        </is>
+      </c>
+      <c r="D2743" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2743" t="n">
+        <v>42</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>478</v>
+      </c>
+      <c r="G2743" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2743" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2744" t="inlineStr">
+        <is>
+          <t>Marie__92</t>
+        </is>
+      </c>
+      <c r="C2744" t="inlineStr">
+        <is>
+          <t>Marie</t>
+        </is>
+      </c>
+      <c r="D2744" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2744" t="n">
+        <v>43</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>477</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2744" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2745">
+      <c r="A2745" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2745" t="inlineStr">
+        <is>
+          <t>Fethinho</t>
+        </is>
+      </c>
+      <c r="C2745" t="inlineStr">
+        <is>
+          <t>Fethi</t>
+        </is>
+      </c>
+      <c r="D2745" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2745" t="n">
+        <v>44</v>
+      </c>
+      <c r="F2745" t="n">
+        <v>474</v>
+      </c>
+      <c r="G2745" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2745" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2746" t="inlineStr">
+        <is>
+          <t>AudreyB225</t>
+        </is>
+      </c>
+      <c r="C2746" t="inlineStr">
+        <is>
+          <t>Audrey</t>
+        </is>
+      </c>
+      <c r="D2746" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2746" t="n">
+        <v>45</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>463</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2747">
+      <c r="A2747" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2747" t="inlineStr">
+        <is>
+          <t>Teddbear</t>
+        </is>
+      </c>
+      <c r="C2747" t="inlineStr">
+        <is>
+          <t>Tedy</t>
+        </is>
+      </c>
+      <c r="D2747" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2747" t="n">
+        <v>46</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>463</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2747" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2748">
+      <c r="A2748" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2748" t="inlineStr">
+        <is>
+          <t>Romain_JO</t>
+        </is>
+      </c>
+      <c r="C2748" t="inlineStr">
+        <is>
+          <t>Romain J</t>
+        </is>
+      </c>
+      <c r="D2748" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2748" t="n">
+        <v>47</v>
+      </c>
+      <c r="F2748" t="n">
+        <v>460</v>
+      </c>
+      <c r="G2748" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2748" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2749" t="inlineStr">
+        <is>
+          <t>Exia95</t>
+        </is>
+      </c>
+      <c r="C2749" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D2749" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2749" t="n">
+        <v>48</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>451</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2750">
+      <c r="A2750" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2750" t="inlineStr">
+        <is>
+          <t>Kaliced</t>
+        </is>
+      </c>
+      <c r="C2750" t="inlineStr">
+        <is>
+          <t>Kalice</t>
+        </is>
+      </c>
+      <c r="D2750" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2750" t="n">
+        <v>49</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>448</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2750" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2751">
+      <c r="A2751" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2751" t="inlineStr">
+        <is>
+          <t>Chadia__</t>
+        </is>
+      </c>
+      <c r="C2751" t="inlineStr">
+        <is>
+          <t>Chadia</t>
+        </is>
+      </c>
+      <c r="D2751" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2751" t="n">
+        <v>50</v>
+      </c>
+      <c r="F2751" t="n">
+        <v>436</v>
+      </c>
+      <c r="G2751" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2751" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2752">
+      <c r="A2752" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2752" t="inlineStr">
+        <is>
+          <t>Matt#4B4CU</t>
+        </is>
+      </c>
+      <c r="C2752" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="D2752" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2752" t="n">
+        <v>51</v>
+      </c>
+      <c r="F2752" t="n">
+        <v>436</v>
+      </c>
+      <c r="G2752" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2752" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2753">
+      <c r="A2753" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2753" t="inlineStr">
+        <is>
+          <t>Cindie_JJA</t>
+        </is>
+      </c>
+      <c r="C2753" t="inlineStr">
+        <is>
+          <t>Cindie</t>
+        </is>
+      </c>
+      <c r="D2753" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2753" t="n">
+        <v>52</v>
+      </c>
+      <c r="F2753" t="n">
+        <v>433</v>
+      </c>
+      <c r="G2753" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2753" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2754">
+      <c r="A2754" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2754" t="inlineStr">
+        <is>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="C2754" t="inlineStr">
+        <is>
+          <t>Julie</t>
+        </is>
+      </c>
+      <c r="D2754" t="inlineStr"/>
+      <c r="E2754" t="n">
+        <v>53</v>
+      </c>
+      <c r="F2754" t="n">
+        <v>430</v>
+      </c>
+      <c r="G2754" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2754" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2755">
+      <c r="A2755" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2755" t="inlineStr">
+        <is>
+          <t>Soraya-Y</t>
+        </is>
+      </c>
+      <c r="C2755" t="inlineStr">
+        <is>
+          <t>Soraya</t>
+        </is>
+      </c>
+      <c r="D2755" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2755" t="n">
+        <v>54</v>
+      </c>
+      <c r="F2755" t="n">
+        <v>418</v>
+      </c>
+      <c r="G2755" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2755" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2756">
+      <c r="A2756" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2756" t="inlineStr">
+        <is>
+          <t>Mr-Worldwide</t>
+        </is>
+      </c>
+      <c r="C2756" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="D2756" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2756" t="n">
+        <v>55</v>
+      </c>
+      <c r="F2756" t="n">
+        <v>411</v>
+      </c>
+      <c r="G2756" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2756" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2757">
+      <c r="A2757" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2757" t="inlineStr">
+        <is>
+          <t>Camillewbl</t>
+        </is>
+      </c>
+      <c r="C2757" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D2757" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2757" t="n">
+        <v>56</v>
+      </c>
+      <c r="F2757" t="n">
+        <v>405</v>
+      </c>
+      <c r="G2757" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2757" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2758">
+      <c r="A2758" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2758" t="inlineStr">
+        <is>
+          <t>PANENKANY</t>
+        </is>
+      </c>
+      <c r="C2758" t="inlineStr">
+        <is>
+          <t>Damien</t>
+        </is>
+      </c>
+      <c r="D2758" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2758" t="n">
+        <v>57</v>
+      </c>
+      <c r="F2758" t="n">
+        <v>404</v>
+      </c>
+      <c r="G2758" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2758" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2759">
+      <c r="A2759" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2759" t="inlineStr">
+        <is>
+          <t>JKInternational</t>
+        </is>
+      </c>
+      <c r="C2759" t="inlineStr">
+        <is>
+          <t>Joachim</t>
+        </is>
+      </c>
+      <c r="D2759" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2759" t="n">
+        <v>58</v>
+      </c>
+      <c r="F2759" t="n">
+        <v>396</v>
+      </c>
+      <c r="G2759" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2759" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2760">
+      <c r="A2760" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2760" t="inlineStr">
+        <is>
+          <t>Erwan#4G91X</t>
+        </is>
+      </c>
+      <c r="C2760" t="inlineStr">
+        <is>
+          <t>Erwan</t>
+        </is>
+      </c>
+      <c r="D2760" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2760" t="n">
+        <v>59</v>
+      </c>
+      <c r="F2760" t="n">
+        <v>393</v>
+      </c>
+      <c r="G2760" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2760" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2761">
+      <c r="A2761" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2761" t="inlineStr">
+        <is>
+          <t>Pipou931</t>
+        </is>
+      </c>
+      <c r="C2761" t="inlineStr">
+        <is>
+          <t>Juliie</t>
+        </is>
+      </c>
+      <c r="D2761" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2761" t="n">
+        <v>60</v>
+      </c>
+      <c r="F2761" t="n">
+        <v>389</v>
+      </c>
+      <c r="G2761" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2761" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2762">
+      <c r="A2762" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2762" t="inlineStr">
+        <is>
+          <t>Seesee</t>
+        </is>
+      </c>
+      <c r="C2762" t="inlineStr">
+        <is>
+          <t>Selver</t>
+        </is>
+      </c>
+      <c r="D2762" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2762" t="n">
+        <v>61</v>
+      </c>
+      <c r="F2762" t="n">
+        <v>382</v>
+      </c>
+      <c r="G2762" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2762" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2763">
+      <c r="A2763" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2763" t="inlineStr">
+        <is>
+          <t>lenaaik</t>
+        </is>
+      </c>
+      <c r="C2763" t="inlineStr">
+        <is>
+          <t>Lénaïk</t>
+        </is>
+      </c>
+      <c r="D2763" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2763" t="n">
+        <v>62</v>
+      </c>
+      <c r="F2763" t="n">
+        <v>382</v>
+      </c>
+      <c r="G2763" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2763" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2764">
+      <c r="A2764" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2764" t="inlineStr">
+        <is>
+          <t>Elisewiss</t>
+        </is>
+      </c>
+      <c r="C2764" t="inlineStr">
+        <is>
+          <t>Elise</t>
+        </is>
+      </c>
+      <c r="D2764" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2764" t="n">
+        <v>63</v>
+      </c>
+      <c r="F2764" t="n">
+        <v>382</v>
+      </c>
+      <c r="G2764" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2764" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2765">
+      <c r="A2765" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2765" t="inlineStr">
+        <is>
+          <t>ChrisKr1Deg1</t>
+        </is>
+      </c>
+      <c r="C2765" t="inlineStr">
+        <is>
+          <t>christophe</t>
+        </is>
+      </c>
+      <c r="D2765" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2765" t="n">
+        <v>64</v>
+      </c>
+      <c r="F2765" t="n">
+        <v>382</v>
+      </c>
+      <c r="G2765" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2765" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2766">
+      <c r="A2766" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2766" t="inlineStr">
+        <is>
+          <t>1993ahm</t>
+        </is>
+      </c>
+      <c r="C2766" t="inlineStr">
+        <is>
+          <t>Ahmed</t>
+        </is>
+      </c>
+      <c r="D2766" t="inlineStr"/>
+      <c r="E2766" t="n">
+        <v>65</v>
+      </c>
+      <c r="F2766" t="n">
+        <v>381</v>
+      </c>
+      <c r="G2766" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2766" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2767">
+      <c r="A2767" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2767" t="inlineStr">
+        <is>
+          <t>Devilrock95</t>
+        </is>
+      </c>
+      <c r="C2767" t="inlineStr">
+        <is>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="D2767" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2767" t="n">
+        <v>66</v>
+      </c>
+      <c r="F2767" t="n">
+        <v>370</v>
+      </c>
+      <c r="G2767" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2767" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2768">
+      <c r="A2768" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2768" t="inlineStr">
+        <is>
+          <t>Droit_au_but7723</t>
+        </is>
+      </c>
+      <c r="C2768" t="inlineStr">
+        <is>
+          <t>Calixthe</t>
+        </is>
+      </c>
+      <c r="D2768" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2768" t="n">
+        <v>67</v>
+      </c>
+      <c r="F2768" t="n">
+        <v>358</v>
+      </c>
+      <c r="G2768" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2768" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2769">
+      <c r="A2769" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2769" t="inlineStr">
+        <is>
+          <t>Davido#4BZ54</t>
+        </is>
+      </c>
+      <c r="C2769" t="inlineStr">
+        <is>
+          <t>Davido</t>
+        </is>
+      </c>
+      <c r="D2769" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2769" t="n">
+        <v>68</v>
+      </c>
+      <c r="F2769" t="n">
+        <v>349</v>
+      </c>
+      <c r="G2769" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2769" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2770">
+      <c r="A2770" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2770" t="inlineStr">
+        <is>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="C2770" t="inlineStr">
+        <is>
+          <t>François</t>
+        </is>
+      </c>
+      <c r="D2770" t="inlineStr"/>
+      <c r="E2770" t="n">
+        <v>69</v>
+      </c>
+      <c r="F2770" t="n">
+        <v>344</v>
+      </c>
+      <c r="G2770" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2770" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2771">
+      <c r="A2771" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2771" t="inlineStr">
+        <is>
+          <t>Camss</t>
+        </is>
+      </c>
+      <c r="C2771" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D2771" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2771" t="n">
+        <v>70</v>
+      </c>
+      <c r="F2771" t="n">
+        <v>343</v>
+      </c>
+      <c r="G2771" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2771" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2772">
+      <c r="A2772" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2772" t="inlineStr">
+        <is>
+          <t>Krol#4R8XC</t>
+        </is>
+      </c>
+      <c r="C2772" t="inlineStr">
+        <is>
+          <t>Krol</t>
+        </is>
+      </c>
+      <c r="D2772" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2772" t="n">
+        <v>71</v>
+      </c>
+      <c r="F2772" t="n">
+        <v>342</v>
+      </c>
+      <c r="G2772" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2772" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2773">
+      <c r="A2773" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2773" t="inlineStr">
+        <is>
+          <t>LilianeB</t>
+        </is>
+      </c>
+      <c r="C2773" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liliane </t>
+        </is>
+      </c>
+      <c r="D2773" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2773" t="n">
+        <v>72</v>
+      </c>
+      <c r="F2773" t="n">
+        <v>337</v>
+      </c>
+      <c r="G2773" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2773" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2774">
+      <c r="A2774" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2774" t="inlineStr">
+        <is>
+          <t>Kolas</t>
+        </is>
+      </c>
+      <c r="C2774" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D2774" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2774" t="n">
+        <v>73</v>
+      </c>
+      <c r="F2774" t="n">
+        <v>324</v>
+      </c>
+      <c r="G2774" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2774" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2775">
+      <c r="A2775" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2775" t="inlineStr">
+        <is>
+          <t>JeremFZ</t>
+        </is>
+      </c>
+      <c r="C2775" t="inlineStr">
+        <is>
+          <t>Jérémy</t>
+        </is>
+      </c>
+      <c r="D2775" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2775" t="n">
+        <v>74</v>
+      </c>
+      <c r="F2775" t="n">
+        <v>322</v>
+      </c>
+      <c r="G2775" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2775" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2776">
+      <c r="A2776" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2776" t="inlineStr">
+        <is>
+          <t>MatuRenard</t>
+        </is>
+      </c>
+      <c r="C2776" t="inlineStr">
+        <is>
+          <t>Mathias</t>
+        </is>
+      </c>
+      <c r="D2776" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2776" t="n">
+        <v>75</v>
+      </c>
+      <c r="F2776" t="n">
+        <v>318</v>
+      </c>
+      <c r="G2776" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2776" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2777">
+      <c r="A2777" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2777" t="inlineStr">
+        <is>
+          <t>Liliuus</t>
+        </is>
+      </c>
+      <c r="C2777" t="inlineStr">
+        <is>
+          <t>Lilia</t>
+        </is>
+      </c>
+      <c r="D2777" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2777" t="n">
+        <v>76</v>
+      </c>
+      <c r="F2777" t="n">
+        <v>318</v>
+      </c>
+      <c r="G2777" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2777" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2778">
+      <c r="A2778" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2778" t="inlineStr">
+        <is>
+          <t>abihuts</t>
+        </is>
+      </c>
+      <c r="C2778" t="inlineStr">
+        <is>
+          <t>Antonio Moctezuma</t>
+        </is>
+      </c>
+      <c r="D2778" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2778" t="n">
+        <v>77</v>
+      </c>
+      <c r="F2778" t="n">
+        <v>303</v>
+      </c>
+      <c r="G2778" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2778" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2779">
+      <c r="A2779" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2779" t="inlineStr">
+        <is>
+          <t>Daviddesco1</t>
+        </is>
+      </c>
+      <c r="C2779" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D2779" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2779" t="n">
+        <v>78</v>
+      </c>
+      <c r="F2779" t="n">
+        <v>302</v>
+      </c>
+      <c r="G2779" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2779" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2780">
+      <c r="A2780" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2780" t="inlineStr">
+        <is>
+          <t>GOAT#UE2WM8M9</t>
+        </is>
+      </c>
+      <c r="C2780" t="inlineStr">
+        <is>
+          <t>Marilena</t>
+        </is>
+      </c>
+      <c r="D2780" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2780" t="n">
+        <v>79</v>
+      </c>
+      <c r="F2780" t="n">
+        <v>296</v>
+      </c>
+      <c r="G2780" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2780" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2781">
+      <c r="A2781" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2781" t="inlineStr">
+        <is>
+          <t>WIL1610</t>
+        </is>
+      </c>
+      <c r="C2781" t="inlineStr">
+        <is>
+          <t>William</t>
+        </is>
+      </c>
+      <c r="D2781" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2781" t="n">
+        <v>80</v>
+      </c>
+      <c r="F2781" t="n">
+        <v>292</v>
+      </c>
+      <c r="G2781" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2781" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2782">
+      <c r="A2782" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2782" t="inlineStr">
+        <is>
+          <t>Lyzone</t>
+        </is>
+      </c>
+      <c r="C2782" t="inlineStr">
+        <is>
+          <t>Lison</t>
+        </is>
+      </c>
+      <c r="D2782" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2782" t="n">
+        <v>81</v>
+      </c>
+      <c r="F2782" t="n">
+        <v>290</v>
+      </c>
+      <c r="G2782" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2782" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2783">
+      <c r="A2783" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2783" t="inlineStr">
+        <is>
+          <t>MT35T</t>
+        </is>
+      </c>
+      <c r="C2783" t="inlineStr">
+        <is>
+          <t>Mathilde</t>
+        </is>
+      </c>
+      <c r="D2783" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2783" t="n">
+        <v>82</v>
+      </c>
+      <c r="F2783" t="n">
+        <v>282</v>
+      </c>
+      <c r="G2783" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2783" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2784">
+      <c r="A2784" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2784" t="inlineStr">
+        <is>
+          <t>Priscilla#4LCAF</t>
+        </is>
+      </c>
+      <c r="C2784" t="inlineStr">
+        <is>
+          <t>Priscilla</t>
+        </is>
+      </c>
+      <c r="D2784" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2784" t="n">
+        <v>83</v>
+      </c>
+      <c r="F2784" t="n">
+        <v>274</v>
+      </c>
+      <c r="G2784" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2784" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2785">
+      <c r="A2785" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2785" t="inlineStr">
+        <is>
+          <t>Rosa_1009</t>
+        </is>
+      </c>
+      <c r="C2785" t="inlineStr">
+        <is>
+          <t>Rosaline</t>
+        </is>
+      </c>
+      <c r="D2785" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2785" t="n">
+        <v>84</v>
+      </c>
+      <c r="F2785" t="n">
+        <v>274</v>
+      </c>
+      <c r="G2785" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2785" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2786">
+      <c r="A2786" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2786" t="inlineStr">
+        <is>
+          <t>Ceciledp</t>
+        </is>
+      </c>
+      <c r="C2786" t="inlineStr">
+        <is>
+          <t>Cécile</t>
+        </is>
+      </c>
+      <c r="D2786" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2786" t="n">
+        <v>85</v>
+      </c>
+      <c r="F2786" t="n">
+        <v>268</v>
+      </c>
+      <c r="G2786" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2786" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2787">
+      <c r="A2787" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2787" t="inlineStr">
+        <is>
+          <t>PacoSarra</t>
+        </is>
+      </c>
+      <c r="C2787" t="inlineStr">
+        <is>
+          <t>Ibra</t>
+        </is>
+      </c>
+      <c r="D2787" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2787" t="n">
+        <v>86</v>
+      </c>
+      <c r="F2787" t="n">
+        <v>266</v>
+      </c>
+      <c r="G2787" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2787" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2788">
+      <c r="A2788" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2788" t="inlineStr">
+        <is>
+          <t>dian-bgt</t>
+        </is>
+      </c>
+      <c r="C2788" t="inlineStr">
+        <is>
+          <t>Diane</t>
+        </is>
+      </c>
+      <c r="D2788" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2788" t="n">
+        <v>87</v>
+      </c>
+      <c r="F2788" t="n">
+        <v>265</v>
+      </c>
+      <c r="G2788" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2788" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2789">
+      <c r="A2789" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2789" t="inlineStr">
+        <is>
+          <t>Mylene-Jnt</t>
+        </is>
+      </c>
+      <c r="C2789" t="inlineStr">
+        <is>
+          <t>Mylène</t>
+        </is>
+      </c>
+      <c r="D2789" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2789" t="n">
+        <v>88</v>
+      </c>
+      <c r="F2789" t="n">
+        <v>258</v>
+      </c>
+      <c r="G2789" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2789" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2790">
+      <c r="A2790" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2790" t="inlineStr">
+        <is>
+          <t>JEVAISGAGNER10</t>
+        </is>
+      </c>
+      <c r="C2790" t="inlineStr">
+        <is>
+          <t>Xavier</t>
+        </is>
+      </c>
+      <c r="D2790" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2790" t="n">
+        <v>89</v>
+      </c>
+      <c r="F2790" t="n">
+        <v>254</v>
+      </c>
+      <c r="G2790" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2790" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2791">
+      <c r="A2791" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2791" t="inlineStr">
+        <is>
+          <t>Melissagzb</t>
+        </is>
+      </c>
+      <c r="C2791" t="inlineStr">
+        <is>
+          <t>Melissa</t>
+        </is>
+      </c>
+      <c r="D2791" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2791" t="n">
+        <v>90</v>
+      </c>
+      <c r="F2791" t="n">
+        <v>254</v>
+      </c>
+      <c r="G2791" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2791" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2792">
+      <c r="A2792" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2792" t="inlineStr">
+        <is>
+          <t>K_Marp</t>
+        </is>
+      </c>
+      <c r="C2792" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
+      <c r="D2792" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2792" t="n">
+        <v>91</v>
+      </c>
+      <c r="F2792" t="n">
+        <v>254</v>
+      </c>
+      <c r="G2792" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2792" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2793">
+      <c r="A2793" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2793" t="inlineStr">
+        <is>
+          <t>A-MOE</t>
+        </is>
+      </c>
+      <c r="C2793" t="inlineStr">
+        <is>
+          <t>Françoise</t>
+        </is>
+      </c>
+      <c r="D2793" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2793" t="n">
+        <v>92</v>
+      </c>
+      <c r="F2793" t="n">
+        <v>254</v>
+      </c>
+      <c r="G2793" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2793" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2794">
+      <c r="A2794" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2794" t="inlineStr">
+        <is>
+          <t>davidd23</t>
+        </is>
+      </c>
+      <c r="C2794" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D2794" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2794" t="n">
+        <v>93</v>
+      </c>
+      <c r="F2794" t="n">
+        <v>249</v>
+      </c>
+      <c r="G2794" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2794" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2795">
+      <c r="A2795" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2795" t="inlineStr">
+        <is>
+          <t>Taylor2901</t>
+        </is>
+      </c>
+      <c r="C2795" t="inlineStr">
+        <is>
+          <t>ousmane</t>
+        </is>
+      </c>
+      <c r="D2795" t="inlineStr"/>
+      <c r="E2795" t="n">
+        <v>94</v>
+      </c>
+      <c r="F2795" t="n">
+        <v>241</v>
+      </c>
+      <c r="G2795" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2795" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2796">
+      <c r="A2796" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2796" t="inlineStr">
+        <is>
+          <t>GLR_PRIME</t>
+        </is>
+      </c>
+      <c r="C2796" t="inlineStr">
+        <is>
+          <t>Gabriel</t>
+        </is>
+      </c>
+      <c r="D2796" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2796" t="n">
+        <v>95</v>
+      </c>
+      <c r="F2796" t="n">
+        <v>234</v>
+      </c>
+      <c r="G2796" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2796" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2797">
+      <c r="A2797" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2797" t="inlineStr">
+        <is>
+          <t>Emma_Noel</t>
+        </is>
+      </c>
+      <c r="C2797" t="inlineStr">
+        <is>
+          <t>Emma</t>
+        </is>
+      </c>
+      <c r="D2797" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2797" t="n">
+        <v>96</v>
+      </c>
+      <c r="F2797" t="n">
+        <v>232</v>
+      </c>
+      <c r="G2797" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2797" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2798">
+      <c r="A2798" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2798" t="inlineStr">
+        <is>
+          <t>Fa_One</t>
+        </is>
+      </c>
+      <c r="C2798" t="inlineStr">
+        <is>
+          <t>Farah</t>
+        </is>
+      </c>
+      <c r="D2798" t="inlineStr"/>
+      <c r="E2798" t="n">
+        <v>97</v>
+      </c>
+      <c r="F2798" t="n">
+        <v>230</v>
+      </c>
+      <c r="G2798" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2798" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2799">
+      <c r="A2799" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2799" t="inlineStr">
+        <is>
+          <t>SamSamH8</t>
+        </is>
+      </c>
+      <c r="C2799" t="inlineStr">
+        <is>
+          <t>Samia</t>
+        </is>
+      </c>
+      <c r="D2799" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2799" t="n">
+        <v>98</v>
+      </c>
+      <c r="F2799" t="n">
+        <v>223</v>
+      </c>
+      <c r="G2799" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2799" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2800">
+      <c r="A2800" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2800" t="inlineStr">
+        <is>
+          <t>PavelMel</t>
+        </is>
+      </c>
+      <c r="C2800" t="inlineStr">
+        <is>
+          <t>Mélissa</t>
+        </is>
+      </c>
+      <c r="D2800" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2800" t="n">
+        <v>99</v>
+      </c>
+      <c r="F2800" t="n">
+        <v>208</v>
+      </c>
+      <c r="G2800" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2800" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2801">
+      <c r="A2801" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2801" t="inlineStr">
+        <is>
+          <t>BrickXVI</t>
+        </is>
+      </c>
+      <c r="C2801" t="inlineStr">
+        <is>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="D2801" t="inlineStr"/>
+      <c r="E2801" t="n">
+        <v>100</v>
+      </c>
+      <c r="F2801" t="n">
+        <v>205</v>
+      </c>
+      <c r="G2801" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2801" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2802">
+      <c r="A2802" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2802" t="inlineStr">
+        <is>
+          <t>SabC1</t>
+        </is>
+      </c>
+      <c r="C2802" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="D2802" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2802" t="n">
+        <v>101</v>
+      </c>
+      <c r="F2802" t="n">
+        <v>190</v>
+      </c>
+      <c r="G2802" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2802" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2803">
+      <c r="A2803" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2803" t="inlineStr">
+        <is>
+          <t>Fuzo697</t>
+        </is>
+      </c>
+      <c r="C2803" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D2803" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2803" t="n">
+        <v>102</v>
+      </c>
+      <c r="F2803" t="n">
+        <v>189</v>
+      </c>
+      <c r="G2803" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2803" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2804">
+      <c r="A2804" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2804" t="inlineStr">
+        <is>
+          <t>LeaBrd</t>
+        </is>
+      </c>
+      <c r="C2804" t="inlineStr">
+        <is>
+          <t>Léa</t>
+        </is>
+      </c>
+      <c r="D2804" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2804" t="n">
+        <v>103</v>
+      </c>
+      <c r="F2804" t="n">
+        <v>182</v>
+      </c>
+      <c r="G2804" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2804" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2805">
+      <c r="A2805" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2805" t="inlineStr">
+        <is>
+          <t>MxKnight</t>
+        </is>
+      </c>
+      <c r="C2805" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D2805" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2805" t="n">
+        <v>104</v>
+      </c>
+      <c r="F2805" t="n">
+        <v>180</v>
+      </c>
+      <c r="G2805" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2805" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2806">
+      <c r="A2806" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2806" t="inlineStr">
+        <is>
+          <t>Sab_M45</t>
+        </is>
+      </c>
+      <c r="C2806" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="D2806" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2806" t="n">
+        <v>105</v>
+      </c>
+      <c r="F2806" t="n">
+        <v>180</v>
+      </c>
+      <c r="G2806" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2806" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2807">
+      <c r="A2807" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2807" t="inlineStr">
+        <is>
+          <t>KIKS999</t>
+        </is>
+      </c>
+      <c r="C2807" t="inlineStr">
+        <is>
+          <t>Killian</t>
+        </is>
+      </c>
+      <c r="D2807" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2807" t="n">
+        <v>106</v>
+      </c>
+      <c r="F2807" t="n">
+        <v>158</v>
+      </c>
+      <c r="G2807" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2807" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2808">
+      <c r="A2808" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2808" t="inlineStr">
+        <is>
+          <t>Laetice2020</t>
+        </is>
+      </c>
+      <c r="C2808" t="inlineStr">
+        <is>
+          <t>Laetitia</t>
+        </is>
+      </c>
+      <c r="D2808" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2808" t="n">
+        <v>107</v>
+      </c>
+      <c r="F2808" t="n">
+        <v>138</v>
+      </c>
+      <c r="G2808" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2808" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2809">
+      <c r="A2809" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2809" t="inlineStr">
+        <is>
+          <t>RBTL</t>
+        </is>
+      </c>
+      <c r="C2809" t="inlineStr">
+        <is>
+          <t>lea</t>
+        </is>
+      </c>
+      <c r="D2809" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2809" t="n">
+        <v>108</v>
+      </c>
+      <c r="F2809" t="n">
+        <v>138</v>
+      </c>
+      <c r="G2809" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2809" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2810">
+      <c r="A2810" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2810" t="inlineStr">
+        <is>
+          <t>RomainLect</t>
+        </is>
+      </c>
+      <c r="C2810" t="inlineStr">
+        <is>
+          <t>romain</t>
+        </is>
+      </c>
+      <c r="D2810" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2810" t="n">
+        <v>109</v>
+      </c>
+      <c r="F2810" t="n">
+        <v>108</v>
+      </c>
+      <c r="G2810" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2810" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historique_joueurs.xlsx
+++ b/historique_joueurs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2810"/>
+  <dimension ref="A1:H2919"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -94268,6 +94268,3684 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2811">
+      <c r="A2811" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2811" t="inlineStr">
+        <is>
+          <t>Ninaaaa</t>
+        </is>
+      </c>
+      <c r="C2811" t="inlineStr">
+        <is>
+          <t>Nina</t>
+        </is>
+      </c>
+      <c r="D2811" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2811" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2811" t="n">
+        <v>903</v>
+      </c>
+      <c r="G2811" t="n">
+        <v>9</v>
+      </c>
+      <c r="H2811" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2812">
+      <c r="A2812" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2812" t="inlineStr">
+        <is>
+          <t>Mamad_Shelter</t>
+        </is>
+      </c>
+      <c r="C2812" t="inlineStr">
+        <is>
+          <t>Mamadou</t>
+        </is>
+      </c>
+      <c r="D2812" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2812" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2812" t="n">
+        <v>859</v>
+      </c>
+      <c r="G2812" t="n">
+        <v>9</v>
+      </c>
+      <c r="H2812" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2813">
+      <c r="A2813" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2813" t="inlineStr">
+        <is>
+          <t>Stephbreton</t>
+        </is>
+      </c>
+      <c r="C2813" t="inlineStr">
+        <is>
+          <t>STEPHANE</t>
+        </is>
+      </c>
+      <c r="D2813" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2813" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2813" t="n">
+        <v>741</v>
+      </c>
+      <c r="G2813" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2813" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2814">
+      <c r="A2814" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2814" t="inlineStr">
+        <is>
+          <t>Coucoucassecou</t>
+        </is>
+      </c>
+      <c r="C2814" t="inlineStr">
+        <is>
+          <t>Brayen</t>
+        </is>
+      </c>
+      <c r="D2814" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2814" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2814" t="n">
+        <v>726</v>
+      </c>
+      <c r="G2814" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2814" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2815">
+      <c r="A2815" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2815" t="inlineStr">
+        <is>
+          <t>GOAT#UE4U8KA6</t>
+        </is>
+      </c>
+      <c r="C2815" t="inlineStr">
+        <is>
+          <t>Jean Baptiste</t>
+        </is>
+      </c>
+      <c r="D2815" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2815" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2815" t="n">
+        <v>710</v>
+      </c>
+      <c r="G2815" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2815" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2816">
+      <c r="A2816" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2816" t="inlineStr">
+        <is>
+          <t>Nonito20</t>
+        </is>
+      </c>
+      <c r="C2816" t="inlineStr">
+        <is>
+          <t>Arnaud</t>
+        </is>
+      </c>
+      <c r="D2816" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2816" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2816" t="n">
+        <v>693</v>
+      </c>
+      <c r="G2816" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2816" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2817">
+      <c r="A2817" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2817" t="inlineStr">
+        <is>
+          <t>BOUGA#2JGXP</t>
+        </is>
+      </c>
+      <c r="C2817" t="inlineStr">
+        <is>
+          <t>BOUGA</t>
+        </is>
+      </c>
+      <c r="D2817" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2817" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2817" t="n">
+        <v>691</v>
+      </c>
+      <c r="G2817" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2817" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2818">
+      <c r="A2818" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2818" t="inlineStr">
+        <is>
+          <t>Filipinho95</t>
+        </is>
+      </c>
+      <c r="C2818" t="inlineStr">
+        <is>
+          <t>Filipe</t>
+        </is>
+      </c>
+      <c r="D2818" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2818" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2818" t="n">
+        <v>683</v>
+      </c>
+      <c r="G2818" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2818" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2819">
+      <c r="A2819" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2819" t="inlineStr">
+        <is>
+          <t>Anais757817</t>
+        </is>
+      </c>
+      <c r="C2819" t="inlineStr">
+        <is>
+          <t>Anaïs</t>
+        </is>
+      </c>
+      <c r="D2819" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2819" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2819" t="n">
+        <v>668</v>
+      </c>
+      <c r="G2819" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2819" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2820">
+      <c r="A2820" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2820" t="inlineStr">
+        <is>
+          <t>catherine#5FRTD</t>
+        </is>
+      </c>
+      <c r="C2820" t="inlineStr">
+        <is>
+          <t>catherine</t>
+        </is>
+      </c>
+      <c r="D2820" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2820" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2820" t="n">
+        <v>665</v>
+      </c>
+      <c r="G2820" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2820" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2821">
+      <c r="A2821" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2821" t="inlineStr">
+        <is>
+          <t>SID-F-ANDRE</t>
+        </is>
+      </c>
+      <c r="C2821" t="inlineStr">
+        <is>
+          <t>Denis</t>
+        </is>
+      </c>
+      <c r="D2821" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2821" t="n">
+        <v>11</v>
+      </c>
+      <c r="F2821" t="n">
+        <v>664</v>
+      </c>
+      <c r="G2821" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2821" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2822">
+      <c r="A2822" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2822" t="inlineStr">
+        <is>
+          <t>MagicMath</t>
+        </is>
+      </c>
+      <c r="C2822" t="inlineStr">
+        <is>
+          <t>Mathieu</t>
+        </is>
+      </c>
+      <c r="D2822" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2822" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2822" t="n">
+        <v>645</v>
+      </c>
+      <c r="G2822" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2822" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2823">
+      <c r="A2823" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2823" t="inlineStr">
+        <is>
+          <t>Leo_durable</t>
+        </is>
+      </c>
+      <c r="C2823" t="inlineStr">
+        <is>
+          <t>Leo</t>
+        </is>
+      </c>
+      <c r="D2823" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2823" t="n">
+        <v>13</v>
+      </c>
+      <c r="F2823" t="n">
+        <v>639</v>
+      </c>
+      <c r="G2823" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2823" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2824">
+      <c r="A2824" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2824" t="inlineStr">
+        <is>
+          <t>Panaff</t>
+        </is>
+      </c>
+      <c r="C2824" t="inlineStr">
+        <is>
+          <t>Panaf</t>
+        </is>
+      </c>
+      <c r="D2824" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2824" t="n">
+        <v>14</v>
+      </c>
+      <c r="F2824" t="n">
+        <v>631</v>
+      </c>
+      <c r="G2824" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2824" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2825">
+      <c r="A2825" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2825" t="inlineStr">
+        <is>
+          <t>Marion1822</t>
+        </is>
+      </c>
+      <c r="C2825" t="inlineStr">
+        <is>
+          <t>Marion</t>
+        </is>
+      </c>
+      <c r="D2825" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2825" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2825" t="n">
+        <v>612</v>
+      </c>
+      <c r="G2825" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2825" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2826">
+      <c r="A2826" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2826" t="inlineStr">
+        <is>
+          <t>goat#AD6GS</t>
+        </is>
+      </c>
+      <c r="C2826" t="inlineStr">
+        <is>
+          <t>goat</t>
+        </is>
+      </c>
+      <c r="D2826" t="inlineStr"/>
+      <c r="E2826" t="n">
+        <v>16</v>
+      </c>
+      <c r="F2826" t="n">
+        <v>603</v>
+      </c>
+      <c r="G2826" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2826" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2827">
+      <c r="A2827" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2827" t="inlineStr">
+        <is>
+          <t>EmyEnzo</t>
+        </is>
+      </c>
+      <c r="C2827" t="inlineStr">
+        <is>
+          <t>Emilie</t>
+        </is>
+      </c>
+      <c r="D2827" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2827" t="n">
+        <v>17</v>
+      </c>
+      <c r="F2827" t="n">
+        <v>601</v>
+      </c>
+      <c r="G2827" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2827" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2828">
+      <c r="A2828" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2828" t="inlineStr">
+        <is>
+          <t>DJOSWA</t>
+        </is>
+      </c>
+      <c r="C2828" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oswaina </t>
+        </is>
+      </c>
+      <c r="D2828" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2828" t="n">
+        <v>18</v>
+      </c>
+      <c r="F2828" t="n">
+        <v>594</v>
+      </c>
+      <c r="G2828" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2828" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2829">
+      <c r="A2829" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2829" t="inlineStr">
+        <is>
+          <t>WalidSiuuuuu</t>
+        </is>
+      </c>
+      <c r="C2829" t="inlineStr">
+        <is>
+          <t>Walid</t>
+        </is>
+      </c>
+      <c r="D2829" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2829" t="n">
+        <v>19</v>
+      </c>
+      <c r="F2829" t="n">
+        <v>580</v>
+      </c>
+      <c r="G2829" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2829" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2830">
+      <c r="A2830" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2830" t="inlineStr">
+        <is>
+          <t>Paulasipi1998</t>
+        </is>
+      </c>
+      <c r="C2830" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="D2830" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2830" t="n">
+        <v>20</v>
+      </c>
+      <c r="F2830" t="n">
+        <v>568</v>
+      </c>
+      <c r="G2830" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2830" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2831">
+      <c r="A2831" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2831" t="inlineStr">
+        <is>
+          <t>MyriamAmr</t>
+        </is>
+      </c>
+      <c r="C2831" t="inlineStr">
+        <is>
+          <t>Myriam</t>
+        </is>
+      </c>
+      <c r="D2831" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2831" t="n">
+        <v>21</v>
+      </c>
+      <c r="F2831" t="n">
+        <v>555</v>
+      </c>
+      <c r="G2831" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2831" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2832">
+      <c r="A2832" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2832" t="inlineStr">
+        <is>
+          <t>FRHTCTD10</t>
+        </is>
+      </c>
+      <c r="C2832" t="inlineStr">
+        <is>
+          <t>Candice</t>
+        </is>
+      </c>
+      <c r="D2832" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2832" t="n">
+        <v>22</v>
+      </c>
+      <c r="F2832" t="n">
+        <v>551</v>
+      </c>
+      <c r="G2832" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2832" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2833">
+      <c r="A2833" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2833" t="inlineStr">
+        <is>
+          <t>Gronaldo_95</t>
+        </is>
+      </c>
+      <c r="C2833" t="inlineStr">
+        <is>
+          <t>Gronaldo</t>
+        </is>
+      </c>
+      <c r="D2833" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2833" t="n">
+        <v>23</v>
+      </c>
+      <c r="F2833" t="n">
+        <v>548</v>
+      </c>
+      <c r="G2833" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2833" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2834">
+      <c r="A2834" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2834" t="inlineStr">
+        <is>
+          <t>Emilay</t>
+        </is>
+      </c>
+      <c r="C2834" t="inlineStr">
+        <is>
+          <t>Émilie</t>
+        </is>
+      </c>
+      <c r="D2834" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2834" t="n">
+        <v>24</v>
+      </c>
+      <c r="F2834" t="n">
+        <v>545</v>
+      </c>
+      <c r="G2834" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2834" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2835">
+      <c r="A2835" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2835" t="inlineStr">
+        <is>
+          <t>HamzaG</t>
+        </is>
+      </c>
+      <c r="C2835" t="inlineStr">
+        <is>
+          <t>Hamza</t>
+        </is>
+      </c>
+      <c r="D2835" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2835" t="n">
+        <v>25</v>
+      </c>
+      <c r="F2835" t="n">
+        <v>538</v>
+      </c>
+      <c r="G2835" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2835" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2836">
+      <c r="A2836" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2836" t="inlineStr">
+        <is>
+          <t>Yebri</t>
+        </is>
+      </c>
+      <c r="C2836" t="inlineStr">
+        <is>
+          <t>Brieuc</t>
+        </is>
+      </c>
+      <c r="D2836" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2836" t="n">
+        <v>26</v>
+      </c>
+      <c r="F2836" t="n">
+        <v>531</v>
+      </c>
+      <c r="G2836" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2836" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2837">
+      <c r="A2837" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2837" t="inlineStr">
+        <is>
+          <t>Ilan_260_</t>
+        </is>
+      </c>
+      <c r="C2837" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ilann </t>
+        </is>
+      </c>
+      <c r="D2837" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2837" t="n">
+        <v>27</v>
+      </c>
+      <c r="F2837" t="n">
+        <v>524</v>
+      </c>
+      <c r="G2837" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2837" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2838">
+      <c r="A2838" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2838" t="inlineStr">
+        <is>
+          <t>Ouiouiausoleil</t>
+        </is>
+      </c>
+      <c r="C2838" t="inlineStr">
+        <is>
+          <t>Ouissal</t>
+        </is>
+      </c>
+      <c r="D2838" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2838" t="n">
+        <v>28</v>
+      </c>
+      <c r="F2838" t="n">
+        <v>519</v>
+      </c>
+      <c r="G2838" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2838" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2839">
+      <c r="A2839" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2839" t="inlineStr">
+        <is>
+          <t>Leandrocp</t>
+        </is>
+      </c>
+      <c r="C2839" t="inlineStr">
+        <is>
+          <t>Leandro</t>
+        </is>
+      </c>
+      <c r="D2839" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2839" t="n">
+        <v>29</v>
+      </c>
+      <c r="F2839" t="n">
+        <v>512</v>
+      </c>
+      <c r="G2839" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2839" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2840">
+      <c r="A2840" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2840" t="inlineStr">
+        <is>
+          <t>chaychaychay</t>
+        </is>
+      </c>
+      <c r="C2840" t="inlineStr">
+        <is>
+          <t>Chaymaa</t>
+        </is>
+      </c>
+      <c r="D2840" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2840" t="n">
+        <v>30</v>
+      </c>
+      <c r="F2840" t="n">
+        <v>512</v>
+      </c>
+      <c r="G2840" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2840" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2841">
+      <c r="A2841" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2841" t="inlineStr">
+        <is>
+          <t>BadrLeo</t>
+        </is>
+      </c>
+      <c r="C2841" t="inlineStr">
+        <is>
+          <t>Badr Leo</t>
+        </is>
+      </c>
+      <c r="D2841" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2841" t="n">
+        <v>31</v>
+      </c>
+      <c r="F2841" t="n">
+        <v>510</v>
+      </c>
+      <c r="G2841" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2841" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2842">
+      <c r="A2842" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2842" t="inlineStr">
+        <is>
+          <t>MargauxCtln</t>
+        </is>
+      </c>
+      <c r="C2842" t="inlineStr">
+        <is>
+          <t>Margaux</t>
+        </is>
+      </c>
+      <c r="D2842" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2842" t="n">
+        <v>32</v>
+      </c>
+      <c r="F2842" t="n">
+        <v>507</v>
+      </c>
+      <c r="G2842" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2842" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2843">
+      <c r="A2843" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2843" t="inlineStr">
+        <is>
+          <t>YassineZ95</t>
+        </is>
+      </c>
+      <c r="C2843" t="inlineStr">
+        <is>
+          <t>Yassine Z</t>
+        </is>
+      </c>
+      <c r="D2843" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2843" t="n">
+        <v>33</v>
+      </c>
+      <c r="F2843" t="n">
+        <v>505</v>
+      </c>
+      <c r="G2843" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2843" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2844">
+      <c r="A2844" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2844" t="inlineStr">
+        <is>
+          <t>Ppo28</t>
+        </is>
+      </c>
+      <c r="C2844" t="inlineStr">
+        <is>
+          <t>Prescylla</t>
+        </is>
+      </c>
+      <c r="D2844" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2844" t="n">
+        <v>34</v>
+      </c>
+      <c r="F2844" t="n">
+        <v>498</v>
+      </c>
+      <c r="G2844" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2844" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2845">
+      <c r="A2845" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2845" t="inlineStr">
+        <is>
+          <t>Ambrepic</t>
+        </is>
+      </c>
+      <c r="C2845" t="inlineStr">
+        <is>
+          <t>Ambre</t>
+        </is>
+      </c>
+      <c r="D2845" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2845" t="n">
+        <v>35</v>
+      </c>
+      <c r="F2845" t="n">
+        <v>498</v>
+      </c>
+      <c r="G2845" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2845" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2846">
+      <c r="A2846" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2846" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="C2846" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="D2846" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2846" t="n">
+        <v>36</v>
+      </c>
+      <c r="F2846" t="n">
+        <v>496</v>
+      </c>
+      <c r="G2846" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2846" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2847">
+      <c r="A2847" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2847" t="inlineStr">
+        <is>
+          <t>Timy</t>
+        </is>
+      </c>
+      <c r="C2847" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="D2847" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2847" t="n">
+        <v>37</v>
+      </c>
+      <c r="F2847" t="n">
+        <v>494</v>
+      </c>
+      <c r="G2847" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2847" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2848">
+      <c r="A2848" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2848" t="inlineStr">
+        <is>
+          <t>C4M</t>
+        </is>
+      </c>
+      <c r="C2848" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D2848" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2848" t="n">
+        <v>38</v>
+      </c>
+      <c r="F2848" t="n">
+        <v>490</v>
+      </c>
+      <c r="G2848" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2848" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2849">
+      <c r="A2849" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2849" t="inlineStr">
+        <is>
+          <t>Ze_GOAT</t>
+        </is>
+      </c>
+      <c r="C2849" t="inlineStr">
+        <is>
+          <t>Yasser</t>
+        </is>
+      </c>
+      <c r="D2849" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2849" t="n">
+        <v>39</v>
+      </c>
+      <c r="F2849" t="n">
+        <v>488</v>
+      </c>
+      <c r="G2849" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2849" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2850">
+      <c r="A2850" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2850" t="inlineStr">
+        <is>
+          <t>Maruyama</t>
+        </is>
+      </c>
+      <c r="C2850" t="inlineStr">
+        <is>
+          <t>Gabrielle</t>
+        </is>
+      </c>
+      <c r="D2850" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2850" t="n">
+        <v>40</v>
+      </c>
+      <c r="F2850" t="n">
+        <v>484</v>
+      </c>
+      <c r="G2850" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2850" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2851">
+      <c r="A2851" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2851" t="inlineStr">
+        <is>
+          <t>Valentine___</t>
+        </is>
+      </c>
+      <c r="C2851" t="inlineStr">
+        <is>
+          <t>Valentine</t>
+        </is>
+      </c>
+      <c r="D2851" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2851" t="n">
+        <v>41</v>
+      </c>
+      <c r="F2851" t="n">
+        <v>483</v>
+      </c>
+      <c r="G2851" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2851" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2852">
+      <c r="A2852" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2852" t="inlineStr">
+        <is>
+          <t>Cleem22</t>
+        </is>
+      </c>
+      <c r="C2852" t="inlineStr">
+        <is>
+          <t>Clemence</t>
+        </is>
+      </c>
+      <c r="D2852" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2852" t="n">
+        <v>42</v>
+      </c>
+      <c r="F2852" t="n">
+        <v>478</v>
+      </c>
+      <c r="G2852" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2852" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2853">
+      <c r="A2853" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2853" t="inlineStr">
+        <is>
+          <t>Marie__92</t>
+        </is>
+      </c>
+      <c r="C2853" t="inlineStr">
+        <is>
+          <t>Marie</t>
+        </is>
+      </c>
+      <c r="D2853" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2853" t="n">
+        <v>43</v>
+      </c>
+      <c r="F2853" t="n">
+        <v>477</v>
+      </c>
+      <c r="G2853" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2853" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2854">
+      <c r="A2854" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2854" t="inlineStr">
+        <is>
+          <t>Fethinho</t>
+        </is>
+      </c>
+      <c r="C2854" t="inlineStr">
+        <is>
+          <t>Fethi</t>
+        </is>
+      </c>
+      <c r="D2854" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2854" t="n">
+        <v>44</v>
+      </c>
+      <c r="F2854" t="n">
+        <v>474</v>
+      </c>
+      <c r="G2854" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2854" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2855">
+      <c r="A2855" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2855" t="inlineStr">
+        <is>
+          <t>AudreyB225</t>
+        </is>
+      </c>
+      <c r="C2855" t="inlineStr">
+        <is>
+          <t>Audrey</t>
+        </is>
+      </c>
+      <c r="D2855" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2855" t="n">
+        <v>45</v>
+      </c>
+      <c r="F2855" t="n">
+        <v>463</v>
+      </c>
+      <c r="G2855" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2855" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2856">
+      <c r="A2856" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2856" t="inlineStr">
+        <is>
+          <t>Teddbear</t>
+        </is>
+      </c>
+      <c r="C2856" t="inlineStr">
+        <is>
+          <t>Tedy</t>
+        </is>
+      </c>
+      <c r="D2856" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2856" t="n">
+        <v>46</v>
+      </c>
+      <c r="F2856" t="n">
+        <v>463</v>
+      </c>
+      <c r="G2856" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2856" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2857">
+      <c r="A2857" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2857" t="inlineStr">
+        <is>
+          <t>Romain_JO</t>
+        </is>
+      </c>
+      <c r="C2857" t="inlineStr">
+        <is>
+          <t>Romain J</t>
+        </is>
+      </c>
+      <c r="D2857" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2857" t="n">
+        <v>47</v>
+      </c>
+      <c r="F2857" t="n">
+        <v>460</v>
+      </c>
+      <c r="G2857" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2857" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2858">
+      <c r="A2858" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2858" t="inlineStr">
+        <is>
+          <t>Exia95</t>
+        </is>
+      </c>
+      <c r="C2858" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D2858" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2858" t="n">
+        <v>48</v>
+      </c>
+      <c r="F2858" t="n">
+        <v>451</v>
+      </c>
+      <c r="G2858" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2858" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2859">
+      <c r="A2859" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2859" t="inlineStr">
+        <is>
+          <t>Kaliced</t>
+        </is>
+      </c>
+      <c r="C2859" t="inlineStr">
+        <is>
+          <t>Kalice</t>
+        </is>
+      </c>
+      <c r="D2859" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2859" t="n">
+        <v>49</v>
+      </c>
+      <c r="F2859" t="n">
+        <v>448</v>
+      </c>
+      <c r="G2859" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2859" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2860">
+      <c r="A2860" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2860" t="inlineStr">
+        <is>
+          <t>Chadia__</t>
+        </is>
+      </c>
+      <c r="C2860" t="inlineStr">
+        <is>
+          <t>Chadia</t>
+        </is>
+      </c>
+      <c r="D2860" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2860" t="n">
+        <v>50</v>
+      </c>
+      <c r="F2860" t="n">
+        <v>436</v>
+      </c>
+      <c r="G2860" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2860" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2861">
+      <c r="A2861" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2861" t="inlineStr">
+        <is>
+          <t>Matt#4B4CU</t>
+        </is>
+      </c>
+      <c r="C2861" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="D2861" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2861" t="n">
+        <v>51</v>
+      </c>
+      <c r="F2861" t="n">
+        <v>436</v>
+      </c>
+      <c r="G2861" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2861" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2862">
+      <c r="A2862" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2862" t="inlineStr">
+        <is>
+          <t>Cindie_JJA</t>
+        </is>
+      </c>
+      <c r="C2862" t="inlineStr">
+        <is>
+          <t>Cindie</t>
+        </is>
+      </c>
+      <c r="D2862" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2862" t="n">
+        <v>52</v>
+      </c>
+      <c r="F2862" t="n">
+        <v>433</v>
+      </c>
+      <c r="G2862" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2862" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2863">
+      <c r="A2863" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2863" t="inlineStr">
+        <is>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="C2863" t="inlineStr">
+        <is>
+          <t>Julie</t>
+        </is>
+      </c>
+      <c r="D2863" t="inlineStr"/>
+      <c r="E2863" t="n">
+        <v>53</v>
+      </c>
+      <c r="F2863" t="n">
+        <v>430</v>
+      </c>
+      <c r="G2863" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2863" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2864">
+      <c r="A2864" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2864" t="inlineStr">
+        <is>
+          <t>Soraya-Y</t>
+        </is>
+      </c>
+      <c r="C2864" t="inlineStr">
+        <is>
+          <t>Soraya</t>
+        </is>
+      </c>
+      <c r="D2864" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2864" t="n">
+        <v>54</v>
+      </c>
+      <c r="F2864" t="n">
+        <v>418</v>
+      </c>
+      <c r="G2864" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2864" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2865">
+      <c r="A2865" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2865" t="inlineStr">
+        <is>
+          <t>Mr-Worldwide</t>
+        </is>
+      </c>
+      <c r="C2865" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="D2865" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2865" t="n">
+        <v>55</v>
+      </c>
+      <c r="F2865" t="n">
+        <v>411</v>
+      </c>
+      <c r="G2865" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2865" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2866">
+      <c r="A2866" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2866" t="inlineStr">
+        <is>
+          <t>Camillewbl</t>
+        </is>
+      </c>
+      <c r="C2866" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D2866" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2866" t="n">
+        <v>56</v>
+      </c>
+      <c r="F2866" t="n">
+        <v>405</v>
+      </c>
+      <c r="G2866" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2866" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2867">
+      <c r="A2867" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2867" t="inlineStr">
+        <is>
+          <t>PANENKANY</t>
+        </is>
+      </c>
+      <c r="C2867" t="inlineStr">
+        <is>
+          <t>Damien</t>
+        </is>
+      </c>
+      <c r="D2867" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2867" t="n">
+        <v>57</v>
+      </c>
+      <c r="F2867" t="n">
+        <v>404</v>
+      </c>
+      <c r="G2867" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2867" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2868">
+      <c r="A2868" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2868" t="inlineStr">
+        <is>
+          <t>JKInternational</t>
+        </is>
+      </c>
+      <c r="C2868" t="inlineStr">
+        <is>
+          <t>Joachim</t>
+        </is>
+      </c>
+      <c r="D2868" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2868" t="n">
+        <v>58</v>
+      </c>
+      <c r="F2868" t="n">
+        <v>396</v>
+      </c>
+      <c r="G2868" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2868" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2869">
+      <c r="A2869" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2869" t="inlineStr">
+        <is>
+          <t>Erwan#4G91X</t>
+        </is>
+      </c>
+      <c r="C2869" t="inlineStr">
+        <is>
+          <t>Erwan</t>
+        </is>
+      </c>
+      <c r="D2869" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2869" t="n">
+        <v>59</v>
+      </c>
+      <c r="F2869" t="n">
+        <v>393</v>
+      </c>
+      <c r="G2869" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2869" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2870">
+      <c r="A2870" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2870" t="inlineStr">
+        <is>
+          <t>Pipou931</t>
+        </is>
+      </c>
+      <c r="C2870" t="inlineStr">
+        <is>
+          <t>Juliie</t>
+        </is>
+      </c>
+      <c r="D2870" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2870" t="n">
+        <v>60</v>
+      </c>
+      <c r="F2870" t="n">
+        <v>389</v>
+      </c>
+      <c r="G2870" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2870" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2871">
+      <c r="A2871" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2871" t="inlineStr">
+        <is>
+          <t>Seesee</t>
+        </is>
+      </c>
+      <c r="C2871" t="inlineStr">
+        <is>
+          <t>Selver</t>
+        </is>
+      </c>
+      <c r="D2871" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2871" t="n">
+        <v>61</v>
+      </c>
+      <c r="F2871" t="n">
+        <v>382</v>
+      </c>
+      <c r="G2871" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2871" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2872">
+      <c r="A2872" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2872" t="inlineStr">
+        <is>
+          <t>lenaaik</t>
+        </is>
+      </c>
+      <c r="C2872" t="inlineStr">
+        <is>
+          <t>Lénaïk</t>
+        </is>
+      </c>
+      <c r="D2872" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2872" t="n">
+        <v>62</v>
+      </c>
+      <c r="F2872" t="n">
+        <v>382</v>
+      </c>
+      <c r="G2872" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2872" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2873">
+      <c r="A2873" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2873" t="inlineStr">
+        <is>
+          <t>Elisewiss</t>
+        </is>
+      </c>
+      <c r="C2873" t="inlineStr">
+        <is>
+          <t>Elise</t>
+        </is>
+      </c>
+      <c r="D2873" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2873" t="n">
+        <v>63</v>
+      </c>
+      <c r="F2873" t="n">
+        <v>382</v>
+      </c>
+      <c r="G2873" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2873" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2874">
+      <c r="A2874" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2874" t="inlineStr">
+        <is>
+          <t>ChrisKr1Deg1</t>
+        </is>
+      </c>
+      <c r="C2874" t="inlineStr">
+        <is>
+          <t>christophe</t>
+        </is>
+      </c>
+      <c r="D2874" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2874" t="n">
+        <v>64</v>
+      </c>
+      <c r="F2874" t="n">
+        <v>382</v>
+      </c>
+      <c r="G2874" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2874" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2875">
+      <c r="A2875" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2875" t="inlineStr">
+        <is>
+          <t>1993ahm</t>
+        </is>
+      </c>
+      <c r="C2875" t="inlineStr">
+        <is>
+          <t>Ahmed</t>
+        </is>
+      </c>
+      <c r="D2875" t="inlineStr"/>
+      <c r="E2875" t="n">
+        <v>65</v>
+      </c>
+      <c r="F2875" t="n">
+        <v>381</v>
+      </c>
+      <c r="G2875" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2875" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2876">
+      <c r="A2876" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2876" t="inlineStr">
+        <is>
+          <t>Devilrock95</t>
+        </is>
+      </c>
+      <c r="C2876" t="inlineStr">
+        <is>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="D2876" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2876" t="n">
+        <v>66</v>
+      </c>
+      <c r="F2876" t="n">
+        <v>370</v>
+      </c>
+      <c r="G2876" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2876" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2877">
+      <c r="A2877" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2877" t="inlineStr">
+        <is>
+          <t>Droit_au_but7723</t>
+        </is>
+      </c>
+      <c r="C2877" t="inlineStr">
+        <is>
+          <t>Calixthe</t>
+        </is>
+      </c>
+      <c r="D2877" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2877" t="n">
+        <v>67</v>
+      </c>
+      <c r="F2877" t="n">
+        <v>358</v>
+      </c>
+      <c r="G2877" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2877" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2878">
+      <c r="A2878" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2878" t="inlineStr">
+        <is>
+          <t>Davido#4BZ54</t>
+        </is>
+      </c>
+      <c r="C2878" t="inlineStr">
+        <is>
+          <t>Davido</t>
+        </is>
+      </c>
+      <c r="D2878" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2878" t="n">
+        <v>68</v>
+      </c>
+      <c r="F2878" t="n">
+        <v>349</v>
+      </c>
+      <c r="G2878" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2878" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2879">
+      <c r="A2879" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2879" t="inlineStr">
+        <is>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="C2879" t="inlineStr">
+        <is>
+          <t>François</t>
+        </is>
+      </c>
+      <c r="D2879" t="inlineStr"/>
+      <c r="E2879" t="n">
+        <v>69</v>
+      </c>
+      <c r="F2879" t="n">
+        <v>344</v>
+      </c>
+      <c r="G2879" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2879" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2880">
+      <c r="A2880" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2880" t="inlineStr">
+        <is>
+          <t>Camss</t>
+        </is>
+      </c>
+      <c r="C2880" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D2880" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2880" t="n">
+        <v>70</v>
+      </c>
+      <c r="F2880" t="n">
+        <v>343</v>
+      </c>
+      <c r="G2880" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2880" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2881">
+      <c r="A2881" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2881" t="inlineStr">
+        <is>
+          <t>Krol#4R8XC</t>
+        </is>
+      </c>
+      <c r="C2881" t="inlineStr">
+        <is>
+          <t>Krol</t>
+        </is>
+      </c>
+      <c r="D2881" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2881" t="n">
+        <v>71</v>
+      </c>
+      <c r="F2881" t="n">
+        <v>342</v>
+      </c>
+      <c r="G2881" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2881" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2882">
+      <c r="A2882" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2882" t="inlineStr">
+        <is>
+          <t>LilianeB</t>
+        </is>
+      </c>
+      <c r="C2882" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liliane </t>
+        </is>
+      </c>
+      <c r="D2882" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2882" t="n">
+        <v>72</v>
+      </c>
+      <c r="F2882" t="n">
+        <v>337</v>
+      </c>
+      <c r="G2882" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2882" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2883">
+      <c r="A2883" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2883" t="inlineStr">
+        <is>
+          <t>Kolas</t>
+        </is>
+      </c>
+      <c r="C2883" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D2883" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2883" t="n">
+        <v>73</v>
+      </c>
+      <c r="F2883" t="n">
+        <v>324</v>
+      </c>
+      <c r="G2883" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2883" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2884">
+      <c r="A2884" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2884" t="inlineStr">
+        <is>
+          <t>JeremFZ</t>
+        </is>
+      </c>
+      <c r="C2884" t="inlineStr">
+        <is>
+          <t>Jérémy</t>
+        </is>
+      </c>
+      <c r="D2884" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2884" t="n">
+        <v>74</v>
+      </c>
+      <c r="F2884" t="n">
+        <v>322</v>
+      </c>
+      <c r="G2884" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2884" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2885">
+      <c r="A2885" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2885" t="inlineStr">
+        <is>
+          <t>MatuRenard</t>
+        </is>
+      </c>
+      <c r="C2885" t="inlineStr">
+        <is>
+          <t>Mathias</t>
+        </is>
+      </c>
+      <c r="D2885" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2885" t="n">
+        <v>75</v>
+      </c>
+      <c r="F2885" t="n">
+        <v>318</v>
+      </c>
+      <c r="G2885" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2885" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2886">
+      <c r="A2886" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2886" t="inlineStr">
+        <is>
+          <t>Liliuus</t>
+        </is>
+      </c>
+      <c r="C2886" t="inlineStr">
+        <is>
+          <t>Lilia</t>
+        </is>
+      </c>
+      <c r="D2886" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2886" t="n">
+        <v>76</v>
+      </c>
+      <c r="F2886" t="n">
+        <v>318</v>
+      </c>
+      <c r="G2886" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2886" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2887">
+      <c r="A2887" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2887" t="inlineStr">
+        <is>
+          <t>abihuts</t>
+        </is>
+      </c>
+      <c r="C2887" t="inlineStr">
+        <is>
+          <t>Antonio Moctezuma</t>
+        </is>
+      </c>
+      <c r="D2887" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2887" t="n">
+        <v>77</v>
+      </c>
+      <c r="F2887" t="n">
+        <v>303</v>
+      </c>
+      <c r="G2887" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2887" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2888">
+      <c r="A2888" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2888" t="inlineStr">
+        <is>
+          <t>Daviddesco1</t>
+        </is>
+      </c>
+      <c r="C2888" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D2888" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2888" t="n">
+        <v>78</v>
+      </c>
+      <c r="F2888" t="n">
+        <v>302</v>
+      </c>
+      <c r="G2888" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2888" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2889">
+      <c r="A2889" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2889" t="inlineStr">
+        <is>
+          <t>GOAT#UE2WM8M9</t>
+        </is>
+      </c>
+      <c r="C2889" t="inlineStr">
+        <is>
+          <t>Marilena</t>
+        </is>
+      </c>
+      <c r="D2889" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2889" t="n">
+        <v>79</v>
+      </c>
+      <c r="F2889" t="n">
+        <v>296</v>
+      </c>
+      <c r="G2889" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2889" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2890">
+      <c r="A2890" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2890" t="inlineStr">
+        <is>
+          <t>WIL1610</t>
+        </is>
+      </c>
+      <c r="C2890" t="inlineStr">
+        <is>
+          <t>William</t>
+        </is>
+      </c>
+      <c r="D2890" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2890" t="n">
+        <v>80</v>
+      </c>
+      <c r="F2890" t="n">
+        <v>292</v>
+      </c>
+      <c r="G2890" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2890" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2891">
+      <c r="A2891" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2891" t="inlineStr">
+        <is>
+          <t>Lyzone</t>
+        </is>
+      </c>
+      <c r="C2891" t="inlineStr">
+        <is>
+          <t>Lison</t>
+        </is>
+      </c>
+      <c r="D2891" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2891" t="n">
+        <v>81</v>
+      </c>
+      <c r="F2891" t="n">
+        <v>290</v>
+      </c>
+      <c r="G2891" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2891" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2892">
+      <c r="A2892" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2892" t="inlineStr">
+        <is>
+          <t>MT35T</t>
+        </is>
+      </c>
+      <c r="C2892" t="inlineStr">
+        <is>
+          <t>Mathilde</t>
+        </is>
+      </c>
+      <c r="D2892" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2892" t="n">
+        <v>82</v>
+      </c>
+      <c r="F2892" t="n">
+        <v>282</v>
+      </c>
+      <c r="G2892" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2892" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2893">
+      <c r="A2893" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2893" t="inlineStr">
+        <is>
+          <t>Priscilla#4LCAF</t>
+        </is>
+      </c>
+      <c r="C2893" t="inlineStr">
+        <is>
+          <t>Priscilla</t>
+        </is>
+      </c>
+      <c r="D2893" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2893" t="n">
+        <v>83</v>
+      </c>
+      <c r="F2893" t="n">
+        <v>274</v>
+      </c>
+      <c r="G2893" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2893" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2894">
+      <c r="A2894" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2894" t="inlineStr">
+        <is>
+          <t>Rosa_1009</t>
+        </is>
+      </c>
+      <c r="C2894" t="inlineStr">
+        <is>
+          <t>Rosaline</t>
+        </is>
+      </c>
+      <c r="D2894" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2894" t="n">
+        <v>84</v>
+      </c>
+      <c r="F2894" t="n">
+        <v>274</v>
+      </c>
+      <c r="G2894" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2894" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2895">
+      <c r="A2895" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2895" t="inlineStr">
+        <is>
+          <t>Ceciledp</t>
+        </is>
+      </c>
+      <c r="C2895" t="inlineStr">
+        <is>
+          <t>Cécile</t>
+        </is>
+      </c>
+      <c r="D2895" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2895" t="n">
+        <v>85</v>
+      </c>
+      <c r="F2895" t="n">
+        <v>268</v>
+      </c>
+      <c r="G2895" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2895" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2896">
+      <c r="A2896" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2896" t="inlineStr">
+        <is>
+          <t>PacoSarra</t>
+        </is>
+      </c>
+      <c r="C2896" t="inlineStr">
+        <is>
+          <t>Ibra</t>
+        </is>
+      </c>
+      <c r="D2896" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2896" t="n">
+        <v>86</v>
+      </c>
+      <c r="F2896" t="n">
+        <v>266</v>
+      </c>
+      <c r="G2896" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2896" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2897">
+      <c r="A2897" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2897" t="inlineStr">
+        <is>
+          <t>dian-bgt</t>
+        </is>
+      </c>
+      <c r="C2897" t="inlineStr">
+        <is>
+          <t>Diane</t>
+        </is>
+      </c>
+      <c r="D2897" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2897" t="n">
+        <v>87</v>
+      </c>
+      <c r="F2897" t="n">
+        <v>265</v>
+      </c>
+      <c r="G2897" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2897" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2898">
+      <c r="A2898" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2898" t="inlineStr">
+        <is>
+          <t>Mylene-Jnt</t>
+        </is>
+      </c>
+      <c r="C2898" t="inlineStr">
+        <is>
+          <t>Mylène</t>
+        </is>
+      </c>
+      <c r="D2898" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2898" t="n">
+        <v>88</v>
+      </c>
+      <c r="F2898" t="n">
+        <v>258</v>
+      </c>
+      <c r="G2898" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2898" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2899">
+      <c r="A2899" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2899" t="inlineStr">
+        <is>
+          <t>JEVAISGAGNER10</t>
+        </is>
+      </c>
+      <c r="C2899" t="inlineStr">
+        <is>
+          <t>Xavier</t>
+        </is>
+      </c>
+      <c r="D2899" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2899" t="n">
+        <v>89</v>
+      </c>
+      <c r="F2899" t="n">
+        <v>254</v>
+      </c>
+      <c r="G2899" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2899" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2900">
+      <c r="A2900" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2900" t="inlineStr">
+        <is>
+          <t>Melissagzb</t>
+        </is>
+      </c>
+      <c r="C2900" t="inlineStr">
+        <is>
+          <t>Melissa</t>
+        </is>
+      </c>
+      <c r="D2900" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2900" t="n">
+        <v>90</v>
+      </c>
+      <c r="F2900" t="n">
+        <v>254</v>
+      </c>
+      <c r="G2900" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2900" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2901">
+      <c r="A2901" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2901" t="inlineStr">
+        <is>
+          <t>K_Marp</t>
+        </is>
+      </c>
+      <c r="C2901" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
+      <c r="D2901" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2901" t="n">
+        <v>91</v>
+      </c>
+      <c r="F2901" t="n">
+        <v>254</v>
+      </c>
+      <c r="G2901" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2901" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2902">
+      <c r="A2902" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2902" t="inlineStr">
+        <is>
+          <t>A-MOE</t>
+        </is>
+      </c>
+      <c r="C2902" t="inlineStr">
+        <is>
+          <t>Françoise</t>
+        </is>
+      </c>
+      <c r="D2902" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2902" t="n">
+        <v>92</v>
+      </c>
+      <c r="F2902" t="n">
+        <v>254</v>
+      </c>
+      <c r="G2902" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2902" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2903">
+      <c r="A2903" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2903" t="inlineStr">
+        <is>
+          <t>davidd23</t>
+        </is>
+      </c>
+      <c r="C2903" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D2903" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2903" t="n">
+        <v>93</v>
+      </c>
+      <c r="F2903" t="n">
+        <v>249</v>
+      </c>
+      <c r="G2903" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2903" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2904">
+      <c r="A2904" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2904" t="inlineStr">
+        <is>
+          <t>Taylor2901</t>
+        </is>
+      </c>
+      <c r="C2904" t="inlineStr">
+        <is>
+          <t>ousmane</t>
+        </is>
+      </c>
+      <c r="D2904" t="inlineStr"/>
+      <c r="E2904" t="n">
+        <v>94</v>
+      </c>
+      <c r="F2904" t="n">
+        <v>241</v>
+      </c>
+      <c r="G2904" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2904" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2905">
+      <c r="A2905" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2905" t="inlineStr">
+        <is>
+          <t>GLR_PRIME</t>
+        </is>
+      </c>
+      <c r="C2905" t="inlineStr">
+        <is>
+          <t>Gabriel</t>
+        </is>
+      </c>
+      <c r="D2905" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2905" t="n">
+        <v>95</v>
+      </c>
+      <c r="F2905" t="n">
+        <v>234</v>
+      </c>
+      <c r="G2905" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2905" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2906">
+      <c r="A2906" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2906" t="inlineStr">
+        <is>
+          <t>Emma_Noel</t>
+        </is>
+      </c>
+      <c r="C2906" t="inlineStr">
+        <is>
+          <t>Emma</t>
+        </is>
+      </c>
+      <c r="D2906" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2906" t="n">
+        <v>96</v>
+      </c>
+      <c r="F2906" t="n">
+        <v>232</v>
+      </c>
+      <c r="G2906" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2906" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2907">
+      <c r="A2907" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2907" t="inlineStr">
+        <is>
+          <t>Fa_One</t>
+        </is>
+      </c>
+      <c r="C2907" t="inlineStr">
+        <is>
+          <t>Farah</t>
+        </is>
+      </c>
+      <c r="D2907" t="inlineStr"/>
+      <c r="E2907" t="n">
+        <v>97</v>
+      </c>
+      <c r="F2907" t="n">
+        <v>230</v>
+      </c>
+      <c r="G2907" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2907" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2908">
+      <c r="A2908" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2908" t="inlineStr">
+        <is>
+          <t>SamSamH8</t>
+        </is>
+      </c>
+      <c r="C2908" t="inlineStr">
+        <is>
+          <t>Samia</t>
+        </is>
+      </c>
+      <c r="D2908" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2908" t="n">
+        <v>98</v>
+      </c>
+      <c r="F2908" t="n">
+        <v>223</v>
+      </c>
+      <c r="G2908" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2908" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2909">
+      <c r="A2909" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2909" t="inlineStr">
+        <is>
+          <t>PavelMel</t>
+        </is>
+      </c>
+      <c r="C2909" t="inlineStr">
+        <is>
+          <t>Mélissa</t>
+        </is>
+      </c>
+      <c r="D2909" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2909" t="n">
+        <v>99</v>
+      </c>
+      <c r="F2909" t="n">
+        <v>208</v>
+      </c>
+      <c r="G2909" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2909" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2910">
+      <c r="A2910" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2910" t="inlineStr">
+        <is>
+          <t>BrickXVI</t>
+        </is>
+      </c>
+      <c r="C2910" t="inlineStr">
+        <is>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="D2910" t="inlineStr"/>
+      <c r="E2910" t="n">
+        <v>100</v>
+      </c>
+      <c r="F2910" t="n">
+        <v>205</v>
+      </c>
+      <c r="G2910" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2910" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2911">
+      <c r="A2911" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2911" t="inlineStr">
+        <is>
+          <t>SabC1</t>
+        </is>
+      </c>
+      <c r="C2911" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="D2911" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2911" t="n">
+        <v>101</v>
+      </c>
+      <c r="F2911" t="n">
+        <v>190</v>
+      </c>
+      <c r="G2911" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2911" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2912">
+      <c r="A2912" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2912" t="inlineStr">
+        <is>
+          <t>Fuzo697</t>
+        </is>
+      </c>
+      <c r="C2912" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D2912" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2912" t="n">
+        <v>102</v>
+      </c>
+      <c r="F2912" t="n">
+        <v>189</v>
+      </c>
+      <c r="G2912" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2912" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2913">
+      <c r="A2913" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2913" t="inlineStr">
+        <is>
+          <t>LeaBrd</t>
+        </is>
+      </c>
+      <c r="C2913" t="inlineStr">
+        <is>
+          <t>Léa</t>
+        </is>
+      </c>
+      <c r="D2913" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2913" t="n">
+        <v>103</v>
+      </c>
+      <c r="F2913" t="n">
+        <v>182</v>
+      </c>
+      <c r="G2913" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2913" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2914">
+      <c r="A2914" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2914" t="inlineStr">
+        <is>
+          <t>MxKnight</t>
+        </is>
+      </c>
+      <c r="C2914" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D2914" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2914" t="n">
+        <v>104</v>
+      </c>
+      <c r="F2914" t="n">
+        <v>180</v>
+      </c>
+      <c r="G2914" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2914" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2915">
+      <c r="A2915" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2915" t="inlineStr">
+        <is>
+          <t>Sab_M45</t>
+        </is>
+      </c>
+      <c r="C2915" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="D2915" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2915" t="n">
+        <v>105</v>
+      </c>
+      <c r="F2915" t="n">
+        <v>180</v>
+      </c>
+      <c r="G2915" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2915" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2916">
+      <c r="A2916" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2916" t="inlineStr">
+        <is>
+          <t>KIKS999</t>
+        </is>
+      </c>
+      <c r="C2916" t="inlineStr">
+        <is>
+          <t>Killian</t>
+        </is>
+      </c>
+      <c r="D2916" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2916" t="n">
+        <v>106</v>
+      </c>
+      <c r="F2916" t="n">
+        <v>158</v>
+      </c>
+      <c r="G2916" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2916" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2917">
+      <c r="A2917" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2917" t="inlineStr">
+        <is>
+          <t>Laetice2020</t>
+        </is>
+      </c>
+      <c r="C2917" t="inlineStr">
+        <is>
+          <t>Laetitia</t>
+        </is>
+      </c>
+      <c r="D2917" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2917" t="n">
+        <v>107</v>
+      </c>
+      <c r="F2917" t="n">
+        <v>138</v>
+      </c>
+      <c r="G2917" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2917" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2918">
+      <c r="A2918" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2918" t="inlineStr">
+        <is>
+          <t>RBTL</t>
+        </is>
+      </c>
+      <c r="C2918" t="inlineStr">
+        <is>
+          <t>lea</t>
+        </is>
+      </c>
+      <c r="D2918" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2918" t="n">
+        <v>108</v>
+      </c>
+      <c r="F2918" t="n">
+        <v>138</v>
+      </c>
+      <c r="G2918" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2918" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2919">
+      <c r="A2919" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2919" t="inlineStr">
+        <is>
+          <t>RomainLect</t>
+        </is>
+      </c>
+      <c r="C2919" t="inlineStr">
+        <is>
+          <t>romain</t>
+        </is>
+      </c>
+      <c r="D2919" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2919" t="n">
+        <v>109</v>
+      </c>
+      <c r="F2919" t="n">
+        <v>108</v>
+      </c>
+      <c r="G2919" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2919" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historique_joueurs.xlsx
+++ b/historique_joueurs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2919"/>
+  <dimension ref="A1:H3028"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97946,6 +97946,3684 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2920">
+      <c r="A2920" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2920" t="inlineStr">
+        <is>
+          <t>Ninaaaa</t>
+        </is>
+      </c>
+      <c r="C2920" t="inlineStr">
+        <is>
+          <t>Nina</t>
+        </is>
+      </c>
+      <c r="D2920" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2920" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2920" t="n">
+        <v>903</v>
+      </c>
+      <c r="G2920" t="n">
+        <v>9</v>
+      </c>
+      <c r="H2920" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2921">
+      <c r="A2921" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2921" t="inlineStr">
+        <is>
+          <t>Mamad_Shelter</t>
+        </is>
+      </c>
+      <c r="C2921" t="inlineStr">
+        <is>
+          <t>Mamadou</t>
+        </is>
+      </c>
+      <c r="D2921" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2921" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2921" t="n">
+        <v>859</v>
+      </c>
+      <c r="G2921" t="n">
+        <v>9</v>
+      </c>
+      <c r="H2921" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2922">
+      <c r="A2922" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2922" t="inlineStr">
+        <is>
+          <t>Stephbreton</t>
+        </is>
+      </c>
+      <c r="C2922" t="inlineStr">
+        <is>
+          <t>STEPHANE</t>
+        </is>
+      </c>
+      <c r="D2922" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2922" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2922" t="n">
+        <v>741</v>
+      </c>
+      <c r="G2922" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2922" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2923">
+      <c r="A2923" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2923" t="inlineStr">
+        <is>
+          <t>Coucoucassecou</t>
+        </is>
+      </c>
+      <c r="C2923" t="inlineStr">
+        <is>
+          <t>Brayen</t>
+        </is>
+      </c>
+      <c r="D2923" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2923" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2923" t="n">
+        <v>726</v>
+      </c>
+      <c r="G2923" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2923" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2924">
+      <c r="A2924" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2924" t="inlineStr">
+        <is>
+          <t>GOAT#UE4U8KA6</t>
+        </is>
+      </c>
+      <c r="C2924" t="inlineStr">
+        <is>
+          <t>Jean Baptiste</t>
+        </is>
+      </c>
+      <c r="D2924" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2924" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2924" t="n">
+        <v>710</v>
+      </c>
+      <c r="G2924" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2924" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2925">
+      <c r="A2925" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2925" t="inlineStr">
+        <is>
+          <t>Nonito20</t>
+        </is>
+      </c>
+      <c r="C2925" t="inlineStr">
+        <is>
+          <t>Arnaud</t>
+        </is>
+      </c>
+      <c r="D2925" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2925" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2925" t="n">
+        <v>693</v>
+      </c>
+      <c r="G2925" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2925" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2926">
+      <c r="A2926" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2926" t="inlineStr">
+        <is>
+          <t>BOUGA#2JGXP</t>
+        </is>
+      </c>
+      <c r="C2926" t="inlineStr">
+        <is>
+          <t>BOUGA</t>
+        </is>
+      </c>
+      <c r="D2926" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2926" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2926" t="n">
+        <v>691</v>
+      </c>
+      <c r="G2926" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2926" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2927">
+      <c r="A2927" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2927" t="inlineStr">
+        <is>
+          <t>Filipinho95</t>
+        </is>
+      </c>
+      <c r="C2927" t="inlineStr">
+        <is>
+          <t>Filipe</t>
+        </is>
+      </c>
+      <c r="D2927" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2927" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2927" t="n">
+        <v>683</v>
+      </c>
+      <c r="G2927" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2927" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2928">
+      <c r="A2928" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2928" t="inlineStr">
+        <is>
+          <t>Anais757817</t>
+        </is>
+      </c>
+      <c r="C2928" t="inlineStr">
+        <is>
+          <t>Anaïs</t>
+        </is>
+      </c>
+      <c r="D2928" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2928" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2928" t="n">
+        <v>668</v>
+      </c>
+      <c r="G2928" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2928" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2929">
+      <c r="A2929" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2929" t="inlineStr">
+        <is>
+          <t>catherine#5FRTD</t>
+        </is>
+      </c>
+      <c r="C2929" t="inlineStr">
+        <is>
+          <t>catherine</t>
+        </is>
+      </c>
+      <c r="D2929" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2929" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2929" t="n">
+        <v>665</v>
+      </c>
+      <c r="G2929" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2929" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2930">
+      <c r="A2930" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2930" t="inlineStr">
+        <is>
+          <t>SID-F-ANDRE</t>
+        </is>
+      </c>
+      <c r="C2930" t="inlineStr">
+        <is>
+          <t>Denis</t>
+        </is>
+      </c>
+      <c r="D2930" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2930" t="n">
+        <v>11</v>
+      </c>
+      <c r="F2930" t="n">
+        <v>664</v>
+      </c>
+      <c r="G2930" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2930" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2931">
+      <c r="A2931" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2931" t="inlineStr">
+        <is>
+          <t>MagicMath</t>
+        </is>
+      </c>
+      <c r="C2931" t="inlineStr">
+        <is>
+          <t>Mathieu</t>
+        </is>
+      </c>
+      <c r="D2931" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2931" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2931" t="n">
+        <v>645</v>
+      </c>
+      <c r="G2931" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2931" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2932">
+      <c r="A2932" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2932" t="inlineStr">
+        <is>
+          <t>Leo_durable</t>
+        </is>
+      </c>
+      <c r="C2932" t="inlineStr">
+        <is>
+          <t>Leo</t>
+        </is>
+      </c>
+      <c r="D2932" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2932" t="n">
+        <v>13</v>
+      </c>
+      <c r="F2932" t="n">
+        <v>639</v>
+      </c>
+      <c r="G2932" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2932" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2933">
+      <c r="A2933" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2933" t="inlineStr">
+        <is>
+          <t>Panaff</t>
+        </is>
+      </c>
+      <c r="C2933" t="inlineStr">
+        <is>
+          <t>Panaf</t>
+        </is>
+      </c>
+      <c r="D2933" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2933" t="n">
+        <v>14</v>
+      </c>
+      <c r="F2933" t="n">
+        <v>631</v>
+      </c>
+      <c r="G2933" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2933" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2934">
+      <c r="A2934" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2934" t="inlineStr">
+        <is>
+          <t>Marion1822</t>
+        </is>
+      </c>
+      <c r="C2934" t="inlineStr">
+        <is>
+          <t>Marion</t>
+        </is>
+      </c>
+      <c r="D2934" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2934" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2934" t="n">
+        <v>612</v>
+      </c>
+      <c r="G2934" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2934" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2935">
+      <c r="A2935" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2935" t="inlineStr">
+        <is>
+          <t>goat#AD6GS</t>
+        </is>
+      </c>
+      <c r="C2935" t="inlineStr">
+        <is>
+          <t>goat</t>
+        </is>
+      </c>
+      <c r="D2935" t="inlineStr"/>
+      <c r="E2935" t="n">
+        <v>16</v>
+      </c>
+      <c r="F2935" t="n">
+        <v>603</v>
+      </c>
+      <c r="G2935" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2935" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2936">
+      <c r="A2936" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2936" t="inlineStr">
+        <is>
+          <t>EmyEnzo</t>
+        </is>
+      </c>
+      <c r="C2936" t="inlineStr">
+        <is>
+          <t>Emilie</t>
+        </is>
+      </c>
+      <c r="D2936" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2936" t="n">
+        <v>17</v>
+      </c>
+      <c r="F2936" t="n">
+        <v>601</v>
+      </c>
+      <c r="G2936" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2936" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2937">
+      <c r="A2937" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2937" t="inlineStr">
+        <is>
+          <t>DJOSWA</t>
+        </is>
+      </c>
+      <c r="C2937" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oswaina </t>
+        </is>
+      </c>
+      <c r="D2937" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2937" t="n">
+        <v>18</v>
+      </c>
+      <c r="F2937" t="n">
+        <v>594</v>
+      </c>
+      <c r="G2937" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2937" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2938">
+      <c r="A2938" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2938" t="inlineStr">
+        <is>
+          <t>WalidSiuuuuu</t>
+        </is>
+      </c>
+      <c r="C2938" t="inlineStr">
+        <is>
+          <t>Walid</t>
+        </is>
+      </c>
+      <c r="D2938" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2938" t="n">
+        <v>19</v>
+      </c>
+      <c r="F2938" t="n">
+        <v>580</v>
+      </c>
+      <c r="G2938" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2938" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2939">
+      <c r="A2939" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2939" t="inlineStr">
+        <is>
+          <t>Paulasipi1998</t>
+        </is>
+      </c>
+      <c r="C2939" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="D2939" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2939" t="n">
+        <v>20</v>
+      </c>
+      <c r="F2939" t="n">
+        <v>568</v>
+      </c>
+      <c r="G2939" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2939" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2940">
+      <c r="A2940" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2940" t="inlineStr">
+        <is>
+          <t>MyriamAmr</t>
+        </is>
+      </c>
+      <c r="C2940" t="inlineStr">
+        <is>
+          <t>Myriam</t>
+        </is>
+      </c>
+      <c r="D2940" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2940" t="n">
+        <v>21</v>
+      </c>
+      <c r="F2940" t="n">
+        <v>555</v>
+      </c>
+      <c r="G2940" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2940" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2941">
+      <c r="A2941" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2941" t="inlineStr">
+        <is>
+          <t>FRHTCTD10</t>
+        </is>
+      </c>
+      <c r="C2941" t="inlineStr">
+        <is>
+          <t>Candice</t>
+        </is>
+      </c>
+      <c r="D2941" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2941" t="n">
+        <v>22</v>
+      </c>
+      <c r="F2941" t="n">
+        <v>551</v>
+      </c>
+      <c r="G2941" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2941" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2942">
+      <c r="A2942" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2942" t="inlineStr">
+        <is>
+          <t>Gronaldo_95</t>
+        </is>
+      </c>
+      <c r="C2942" t="inlineStr">
+        <is>
+          <t>Gronaldo</t>
+        </is>
+      </c>
+      <c r="D2942" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2942" t="n">
+        <v>23</v>
+      </c>
+      <c r="F2942" t="n">
+        <v>548</v>
+      </c>
+      <c r="G2942" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2942" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2943">
+      <c r="A2943" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2943" t="inlineStr">
+        <is>
+          <t>Emilay</t>
+        </is>
+      </c>
+      <c r="C2943" t="inlineStr">
+        <is>
+          <t>Émilie</t>
+        </is>
+      </c>
+      <c r="D2943" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2943" t="n">
+        <v>24</v>
+      </c>
+      <c r="F2943" t="n">
+        <v>545</v>
+      </c>
+      <c r="G2943" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2943" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2944">
+      <c r="A2944" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2944" t="inlineStr">
+        <is>
+          <t>HamzaG</t>
+        </is>
+      </c>
+      <c r="C2944" t="inlineStr">
+        <is>
+          <t>Hamza</t>
+        </is>
+      </c>
+      <c r="D2944" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2944" t="n">
+        <v>25</v>
+      </c>
+      <c r="F2944" t="n">
+        <v>538</v>
+      </c>
+      <c r="G2944" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2944" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2945">
+      <c r="A2945" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2945" t="inlineStr">
+        <is>
+          <t>Yebri</t>
+        </is>
+      </c>
+      <c r="C2945" t="inlineStr">
+        <is>
+          <t>Brieuc</t>
+        </is>
+      </c>
+      <c r="D2945" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2945" t="n">
+        <v>26</v>
+      </c>
+      <c r="F2945" t="n">
+        <v>531</v>
+      </c>
+      <c r="G2945" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2945" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2946">
+      <c r="A2946" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2946" t="inlineStr">
+        <is>
+          <t>Ilan_260_</t>
+        </is>
+      </c>
+      <c r="C2946" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ilann </t>
+        </is>
+      </c>
+      <c r="D2946" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2946" t="n">
+        <v>27</v>
+      </c>
+      <c r="F2946" t="n">
+        <v>524</v>
+      </c>
+      <c r="G2946" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2946" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2947">
+      <c r="A2947" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2947" t="inlineStr">
+        <is>
+          <t>Ouiouiausoleil</t>
+        </is>
+      </c>
+      <c r="C2947" t="inlineStr">
+        <is>
+          <t>Ouissal</t>
+        </is>
+      </c>
+      <c r="D2947" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2947" t="n">
+        <v>28</v>
+      </c>
+      <c r="F2947" t="n">
+        <v>519</v>
+      </c>
+      <c r="G2947" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2947" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2948">
+      <c r="A2948" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2948" t="inlineStr">
+        <is>
+          <t>Leandrocp</t>
+        </is>
+      </c>
+      <c r="C2948" t="inlineStr">
+        <is>
+          <t>Leandro</t>
+        </is>
+      </c>
+      <c r="D2948" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2948" t="n">
+        <v>29</v>
+      </c>
+      <c r="F2948" t="n">
+        <v>512</v>
+      </c>
+      <c r="G2948" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2948" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2949">
+      <c r="A2949" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2949" t="inlineStr">
+        <is>
+          <t>chaychaychay</t>
+        </is>
+      </c>
+      <c r="C2949" t="inlineStr">
+        <is>
+          <t>Chaymaa</t>
+        </is>
+      </c>
+      <c r="D2949" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2949" t="n">
+        <v>30</v>
+      </c>
+      <c r="F2949" t="n">
+        <v>512</v>
+      </c>
+      <c r="G2949" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2949" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2950">
+      <c r="A2950" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2950" t="inlineStr">
+        <is>
+          <t>BadrLeo</t>
+        </is>
+      </c>
+      <c r="C2950" t="inlineStr">
+        <is>
+          <t>Badr Leo</t>
+        </is>
+      </c>
+      <c r="D2950" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2950" t="n">
+        <v>31</v>
+      </c>
+      <c r="F2950" t="n">
+        <v>510</v>
+      </c>
+      <c r="G2950" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2950" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2951">
+      <c r="A2951" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2951" t="inlineStr">
+        <is>
+          <t>MargauxCtln</t>
+        </is>
+      </c>
+      <c r="C2951" t="inlineStr">
+        <is>
+          <t>Margaux</t>
+        </is>
+      </c>
+      <c r="D2951" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2951" t="n">
+        <v>32</v>
+      </c>
+      <c r="F2951" t="n">
+        <v>507</v>
+      </c>
+      <c r="G2951" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2951" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2952">
+      <c r="A2952" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2952" t="inlineStr">
+        <is>
+          <t>YassineZ95</t>
+        </is>
+      </c>
+      <c r="C2952" t="inlineStr">
+        <is>
+          <t>Yassine Z</t>
+        </is>
+      </c>
+      <c r="D2952" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2952" t="n">
+        <v>33</v>
+      </c>
+      <c r="F2952" t="n">
+        <v>505</v>
+      </c>
+      <c r="G2952" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2952" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2953">
+      <c r="A2953" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2953" t="inlineStr">
+        <is>
+          <t>Ppo28</t>
+        </is>
+      </c>
+      <c r="C2953" t="inlineStr">
+        <is>
+          <t>Prescylla</t>
+        </is>
+      </c>
+      <c r="D2953" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2953" t="n">
+        <v>34</v>
+      </c>
+      <c r="F2953" t="n">
+        <v>498</v>
+      </c>
+      <c r="G2953" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2953" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2954">
+      <c r="A2954" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2954" t="inlineStr">
+        <is>
+          <t>Ambrepic</t>
+        </is>
+      </c>
+      <c r="C2954" t="inlineStr">
+        <is>
+          <t>Ambre</t>
+        </is>
+      </c>
+      <c r="D2954" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2954" t="n">
+        <v>35</v>
+      </c>
+      <c r="F2954" t="n">
+        <v>498</v>
+      </c>
+      <c r="G2954" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2954" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2955">
+      <c r="A2955" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2955" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="C2955" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="D2955" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2955" t="n">
+        <v>36</v>
+      </c>
+      <c r="F2955" t="n">
+        <v>496</v>
+      </c>
+      <c r="G2955" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2955" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2956">
+      <c r="A2956" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2956" t="inlineStr">
+        <is>
+          <t>Timy</t>
+        </is>
+      </c>
+      <c r="C2956" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="D2956" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2956" t="n">
+        <v>37</v>
+      </c>
+      <c r="F2956" t="n">
+        <v>494</v>
+      </c>
+      <c r="G2956" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2956" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2957">
+      <c r="A2957" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2957" t="inlineStr">
+        <is>
+          <t>C4M</t>
+        </is>
+      </c>
+      <c r="C2957" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D2957" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2957" t="n">
+        <v>38</v>
+      </c>
+      <c r="F2957" t="n">
+        <v>490</v>
+      </c>
+      <c r="G2957" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2957" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2958">
+      <c r="A2958" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2958" t="inlineStr">
+        <is>
+          <t>Ze_GOAT</t>
+        </is>
+      </c>
+      <c r="C2958" t="inlineStr">
+        <is>
+          <t>Yasser</t>
+        </is>
+      </c>
+      <c r="D2958" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2958" t="n">
+        <v>39</v>
+      </c>
+      <c r="F2958" t="n">
+        <v>488</v>
+      </c>
+      <c r="G2958" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2958" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2959">
+      <c r="A2959" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2959" t="inlineStr">
+        <is>
+          <t>Maruyama</t>
+        </is>
+      </c>
+      <c r="C2959" t="inlineStr">
+        <is>
+          <t>Gabrielle</t>
+        </is>
+      </c>
+      <c r="D2959" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2959" t="n">
+        <v>40</v>
+      </c>
+      <c r="F2959" t="n">
+        <v>484</v>
+      </c>
+      <c r="G2959" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2959" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2960">
+      <c r="A2960" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2960" t="inlineStr">
+        <is>
+          <t>Valentine___</t>
+        </is>
+      </c>
+      <c r="C2960" t="inlineStr">
+        <is>
+          <t>Valentine</t>
+        </is>
+      </c>
+      <c r="D2960" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2960" t="n">
+        <v>41</v>
+      </c>
+      <c r="F2960" t="n">
+        <v>483</v>
+      </c>
+      <c r="G2960" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2960" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2961">
+      <c r="A2961" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2961" t="inlineStr">
+        <is>
+          <t>Cleem22</t>
+        </is>
+      </c>
+      <c r="C2961" t="inlineStr">
+        <is>
+          <t>Clemence</t>
+        </is>
+      </c>
+      <c r="D2961" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2961" t="n">
+        <v>42</v>
+      </c>
+      <c r="F2961" t="n">
+        <v>478</v>
+      </c>
+      <c r="G2961" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2961" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2962">
+      <c r="A2962" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2962" t="inlineStr">
+        <is>
+          <t>Marie__92</t>
+        </is>
+      </c>
+      <c r="C2962" t="inlineStr">
+        <is>
+          <t>Marie</t>
+        </is>
+      </c>
+      <c r="D2962" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2962" t="n">
+        <v>43</v>
+      </c>
+      <c r="F2962" t="n">
+        <v>477</v>
+      </c>
+      <c r="G2962" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2962" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2963">
+      <c r="A2963" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2963" t="inlineStr">
+        <is>
+          <t>Fethinho</t>
+        </is>
+      </c>
+      <c r="C2963" t="inlineStr">
+        <is>
+          <t>Fethi</t>
+        </is>
+      </c>
+      <c r="D2963" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2963" t="n">
+        <v>44</v>
+      </c>
+      <c r="F2963" t="n">
+        <v>474</v>
+      </c>
+      <c r="G2963" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2963" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2964">
+      <c r="A2964" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2964" t="inlineStr">
+        <is>
+          <t>AudreyB225</t>
+        </is>
+      </c>
+      <c r="C2964" t="inlineStr">
+        <is>
+          <t>Audrey</t>
+        </is>
+      </c>
+      <c r="D2964" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2964" t="n">
+        <v>45</v>
+      </c>
+      <c r="F2964" t="n">
+        <v>463</v>
+      </c>
+      <c r="G2964" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2964" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2965">
+      <c r="A2965" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2965" t="inlineStr">
+        <is>
+          <t>Teddbear</t>
+        </is>
+      </c>
+      <c r="C2965" t="inlineStr">
+        <is>
+          <t>Tedy</t>
+        </is>
+      </c>
+      <c r="D2965" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2965" t="n">
+        <v>46</v>
+      </c>
+      <c r="F2965" t="n">
+        <v>463</v>
+      </c>
+      <c r="G2965" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2965" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2966">
+      <c r="A2966" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2966" t="inlineStr">
+        <is>
+          <t>Romain_JO</t>
+        </is>
+      </c>
+      <c r="C2966" t="inlineStr">
+        <is>
+          <t>Romain J</t>
+        </is>
+      </c>
+      <c r="D2966" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2966" t="n">
+        <v>47</v>
+      </c>
+      <c r="F2966" t="n">
+        <v>460</v>
+      </c>
+      <c r="G2966" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2966" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2967">
+      <c r="A2967" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2967" t="inlineStr">
+        <is>
+          <t>Exia95</t>
+        </is>
+      </c>
+      <c r="C2967" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D2967" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2967" t="n">
+        <v>48</v>
+      </c>
+      <c r="F2967" t="n">
+        <v>451</v>
+      </c>
+      <c r="G2967" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2967" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2968">
+      <c r="A2968" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2968" t="inlineStr">
+        <is>
+          <t>Kaliced</t>
+        </is>
+      </c>
+      <c r="C2968" t="inlineStr">
+        <is>
+          <t>Kalice</t>
+        </is>
+      </c>
+      <c r="D2968" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2968" t="n">
+        <v>49</v>
+      </c>
+      <c r="F2968" t="n">
+        <v>448</v>
+      </c>
+      <c r="G2968" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2968" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2969">
+      <c r="A2969" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2969" t="inlineStr">
+        <is>
+          <t>Chadia__</t>
+        </is>
+      </c>
+      <c r="C2969" t="inlineStr">
+        <is>
+          <t>Chadia</t>
+        </is>
+      </c>
+      <c r="D2969" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2969" t="n">
+        <v>50</v>
+      </c>
+      <c r="F2969" t="n">
+        <v>436</v>
+      </c>
+      <c r="G2969" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2969" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2970">
+      <c r="A2970" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2970" t="inlineStr">
+        <is>
+          <t>Matt#4B4CU</t>
+        </is>
+      </c>
+      <c r="C2970" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="D2970" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2970" t="n">
+        <v>51</v>
+      </c>
+      <c r="F2970" t="n">
+        <v>436</v>
+      </c>
+      <c r="G2970" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2970" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2971">
+      <c r="A2971" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2971" t="inlineStr">
+        <is>
+          <t>Cindie_JJA</t>
+        </is>
+      </c>
+      <c r="C2971" t="inlineStr">
+        <is>
+          <t>Cindie</t>
+        </is>
+      </c>
+      <c r="D2971" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2971" t="n">
+        <v>52</v>
+      </c>
+      <c r="F2971" t="n">
+        <v>433</v>
+      </c>
+      <c r="G2971" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2971" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2972">
+      <c r="A2972" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2972" t="inlineStr">
+        <is>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="C2972" t="inlineStr">
+        <is>
+          <t>Julie</t>
+        </is>
+      </c>
+      <c r="D2972" t="inlineStr"/>
+      <c r="E2972" t="n">
+        <v>53</v>
+      </c>
+      <c r="F2972" t="n">
+        <v>430</v>
+      </c>
+      <c r="G2972" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2972" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2973">
+      <c r="A2973" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2973" t="inlineStr">
+        <is>
+          <t>Soraya-Y</t>
+        </is>
+      </c>
+      <c r="C2973" t="inlineStr">
+        <is>
+          <t>Soraya</t>
+        </is>
+      </c>
+      <c r="D2973" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2973" t="n">
+        <v>54</v>
+      </c>
+      <c r="F2973" t="n">
+        <v>418</v>
+      </c>
+      <c r="G2973" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2973" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2974">
+      <c r="A2974" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2974" t="inlineStr">
+        <is>
+          <t>Mr-Worldwide</t>
+        </is>
+      </c>
+      <c r="C2974" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="D2974" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2974" t="n">
+        <v>55</v>
+      </c>
+      <c r="F2974" t="n">
+        <v>411</v>
+      </c>
+      <c r="G2974" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2974" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2975">
+      <c r="A2975" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2975" t="inlineStr">
+        <is>
+          <t>Camillewbl</t>
+        </is>
+      </c>
+      <c r="C2975" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D2975" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2975" t="n">
+        <v>56</v>
+      </c>
+      <c r="F2975" t="n">
+        <v>405</v>
+      </c>
+      <c r="G2975" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2975" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2976">
+      <c r="A2976" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2976" t="inlineStr">
+        <is>
+          <t>PANENKANY</t>
+        </is>
+      </c>
+      <c r="C2976" t="inlineStr">
+        <is>
+          <t>Damien</t>
+        </is>
+      </c>
+      <c r="D2976" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E2976" t="n">
+        <v>57</v>
+      </c>
+      <c r="F2976" t="n">
+        <v>404</v>
+      </c>
+      <c r="G2976" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2976" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2977">
+      <c r="A2977" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2977" t="inlineStr">
+        <is>
+          <t>JKInternational</t>
+        </is>
+      </c>
+      <c r="C2977" t="inlineStr">
+        <is>
+          <t>Joachim</t>
+        </is>
+      </c>
+      <c r="D2977" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2977" t="n">
+        <v>58</v>
+      </c>
+      <c r="F2977" t="n">
+        <v>396</v>
+      </c>
+      <c r="G2977" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2977" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2978">
+      <c r="A2978" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2978" t="inlineStr">
+        <is>
+          <t>Erwan#4G91X</t>
+        </is>
+      </c>
+      <c r="C2978" t="inlineStr">
+        <is>
+          <t>Erwan</t>
+        </is>
+      </c>
+      <c r="D2978" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2978" t="n">
+        <v>59</v>
+      </c>
+      <c r="F2978" t="n">
+        <v>393</v>
+      </c>
+      <c r="G2978" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2978" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2979">
+      <c r="A2979" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2979" t="inlineStr">
+        <is>
+          <t>Pipou931</t>
+        </is>
+      </c>
+      <c r="C2979" t="inlineStr">
+        <is>
+          <t>Juliie</t>
+        </is>
+      </c>
+      <c r="D2979" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2979" t="n">
+        <v>60</v>
+      </c>
+      <c r="F2979" t="n">
+        <v>389</v>
+      </c>
+      <c r="G2979" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2979" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2980">
+      <c r="A2980" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2980" t="inlineStr">
+        <is>
+          <t>Seesee</t>
+        </is>
+      </c>
+      <c r="C2980" t="inlineStr">
+        <is>
+          <t>Selver</t>
+        </is>
+      </c>
+      <c r="D2980" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2980" t="n">
+        <v>61</v>
+      </c>
+      <c r="F2980" t="n">
+        <v>382</v>
+      </c>
+      <c r="G2980" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2980" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2981">
+      <c r="A2981" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2981" t="inlineStr">
+        <is>
+          <t>lenaaik</t>
+        </is>
+      </c>
+      <c r="C2981" t="inlineStr">
+        <is>
+          <t>Lénaïk</t>
+        </is>
+      </c>
+      <c r="D2981" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2981" t="n">
+        <v>62</v>
+      </c>
+      <c r="F2981" t="n">
+        <v>382</v>
+      </c>
+      <c r="G2981" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2981" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2982">
+      <c r="A2982" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2982" t="inlineStr">
+        <is>
+          <t>Elisewiss</t>
+        </is>
+      </c>
+      <c r="C2982" t="inlineStr">
+        <is>
+          <t>Elise</t>
+        </is>
+      </c>
+      <c r="D2982" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E2982" t="n">
+        <v>63</v>
+      </c>
+      <c r="F2982" t="n">
+        <v>382</v>
+      </c>
+      <c r="G2982" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2982" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2983">
+      <c r="A2983" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2983" t="inlineStr">
+        <is>
+          <t>ChrisKr1Deg1</t>
+        </is>
+      </c>
+      <c r="C2983" t="inlineStr">
+        <is>
+          <t>christophe</t>
+        </is>
+      </c>
+      <c r="D2983" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2983" t="n">
+        <v>64</v>
+      </c>
+      <c r="F2983" t="n">
+        <v>382</v>
+      </c>
+      <c r="G2983" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2983" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2984">
+      <c r="A2984" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2984" t="inlineStr">
+        <is>
+          <t>1993ahm</t>
+        </is>
+      </c>
+      <c r="C2984" t="inlineStr">
+        <is>
+          <t>Ahmed</t>
+        </is>
+      </c>
+      <c r="D2984" t="inlineStr"/>
+      <c r="E2984" t="n">
+        <v>65</v>
+      </c>
+      <c r="F2984" t="n">
+        <v>381</v>
+      </c>
+      <c r="G2984" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2984" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2985">
+      <c r="A2985" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2985" t="inlineStr">
+        <is>
+          <t>Devilrock95</t>
+        </is>
+      </c>
+      <c r="C2985" t="inlineStr">
+        <is>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="D2985" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2985" t="n">
+        <v>66</v>
+      </c>
+      <c r="F2985" t="n">
+        <v>370</v>
+      </c>
+      <c r="G2985" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2985" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2986">
+      <c r="A2986" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2986" t="inlineStr">
+        <is>
+          <t>Droit_au_but7723</t>
+        </is>
+      </c>
+      <c r="C2986" t="inlineStr">
+        <is>
+          <t>Calixthe</t>
+        </is>
+      </c>
+      <c r="D2986" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2986" t="n">
+        <v>67</v>
+      </c>
+      <c r="F2986" t="n">
+        <v>358</v>
+      </c>
+      <c r="G2986" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2986" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2987">
+      <c r="A2987" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2987" t="inlineStr">
+        <is>
+          <t>Davido#4BZ54</t>
+        </is>
+      </c>
+      <c r="C2987" t="inlineStr">
+        <is>
+          <t>Davido</t>
+        </is>
+      </c>
+      <c r="D2987" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2987" t="n">
+        <v>68</v>
+      </c>
+      <c r="F2987" t="n">
+        <v>349</v>
+      </c>
+      <c r="G2987" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2987" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2988">
+      <c r="A2988" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2988" t="inlineStr">
+        <is>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="C2988" t="inlineStr">
+        <is>
+          <t>François</t>
+        </is>
+      </c>
+      <c r="D2988" t="inlineStr"/>
+      <c r="E2988" t="n">
+        <v>69</v>
+      </c>
+      <c r="F2988" t="n">
+        <v>344</v>
+      </c>
+      <c r="G2988" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2988" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2989">
+      <c r="A2989" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2989" t="inlineStr">
+        <is>
+          <t>Camss</t>
+        </is>
+      </c>
+      <c r="C2989" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D2989" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2989" t="n">
+        <v>70</v>
+      </c>
+      <c r="F2989" t="n">
+        <v>343</v>
+      </c>
+      <c r="G2989" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2989" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2990">
+      <c r="A2990" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2990" t="inlineStr">
+        <is>
+          <t>Krol#4R8XC</t>
+        </is>
+      </c>
+      <c r="C2990" t="inlineStr">
+        <is>
+          <t>Krol</t>
+        </is>
+      </c>
+      <c r="D2990" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2990" t="n">
+        <v>71</v>
+      </c>
+      <c r="F2990" t="n">
+        <v>342</v>
+      </c>
+      <c r="G2990" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2990" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2991">
+      <c r="A2991" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2991" t="inlineStr">
+        <is>
+          <t>LilianeB</t>
+        </is>
+      </c>
+      <c r="C2991" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liliane </t>
+        </is>
+      </c>
+      <c r="D2991" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2991" t="n">
+        <v>72</v>
+      </c>
+      <c r="F2991" t="n">
+        <v>337</v>
+      </c>
+      <c r="G2991" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2991" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2992">
+      <c r="A2992" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2992" t="inlineStr">
+        <is>
+          <t>Kolas</t>
+        </is>
+      </c>
+      <c r="C2992" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D2992" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2992" t="n">
+        <v>73</v>
+      </c>
+      <c r="F2992" t="n">
+        <v>324</v>
+      </c>
+      <c r="G2992" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2992" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2993">
+      <c r="A2993" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2993" t="inlineStr">
+        <is>
+          <t>JeremFZ</t>
+        </is>
+      </c>
+      <c r="C2993" t="inlineStr">
+        <is>
+          <t>Jérémy</t>
+        </is>
+      </c>
+      <c r="D2993" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2993" t="n">
+        <v>74</v>
+      </c>
+      <c r="F2993" t="n">
+        <v>322</v>
+      </c>
+      <c r="G2993" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2993" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2994">
+      <c r="A2994" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2994" t="inlineStr">
+        <is>
+          <t>MatuRenard</t>
+        </is>
+      </c>
+      <c r="C2994" t="inlineStr">
+        <is>
+          <t>Mathias</t>
+        </is>
+      </c>
+      <c r="D2994" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2994" t="n">
+        <v>75</v>
+      </c>
+      <c r="F2994" t="n">
+        <v>318</v>
+      </c>
+      <c r="G2994" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2994" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2995">
+      <c r="A2995" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2995" t="inlineStr">
+        <is>
+          <t>Liliuus</t>
+        </is>
+      </c>
+      <c r="C2995" t="inlineStr">
+        <is>
+          <t>Lilia</t>
+        </is>
+      </c>
+      <c r="D2995" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2995" t="n">
+        <v>76</v>
+      </c>
+      <c r="F2995" t="n">
+        <v>318</v>
+      </c>
+      <c r="G2995" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2995" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2996">
+      <c r="A2996" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2996" t="inlineStr">
+        <is>
+          <t>abihuts</t>
+        </is>
+      </c>
+      <c r="C2996" t="inlineStr">
+        <is>
+          <t>Antonio Moctezuma</t>
+        </is>
+      </c>
+      <c r="D2996" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2996" t="n">
+        <v>77</v>
+      </c>
+      <c r="F2996" t="n">
+        <v>303</v>
+      </c>
+      <c r="G2996" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2996" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2997">
+      <c r="A2997" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2997" t="inlineStr">
+        <is>
+          <t>Daviddesco1</t>
+        </is>
+      </c>
+      <c r="C2997" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D2997" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E2997" t="n">
+        <v>78</v>
+      </c>
+      <c r="F2997" t="n">
+        <v>302</v>
+      </c>
+      <c r="G2997" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2997" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2998">
+      <c r="A2998" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2998" t="inlineStr">
+        <is>
+          <t>GOAT#UE2WM8M9</t>
+        </is>
+      </c>
+      <c r="C2998" t="inlineStr">
+        <is>
+          <t>Marilena</t>
+        </is>
+      </c>
+      <c r="D2998" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E2998" t="n">
+        <v>79</v>
+      </c>
+      <c r="F2998" t="n">
+        <v>296</v>
+      </c>
+      <c r="G2998" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2998" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2999">
+      <c r="A2999" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2999" t="inlineStr">
+        <is>
+          <t>WIL1610</t>
+        </is>
+      </c>
+      <c r="C2999" t="inlineStr">
+        <is>
+          <t>William</t>
+        </is>
+      </c>
+      <c r="D2999" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E2999" t="n">
+        <v>80</v>
+      </c>
+      <c r="F2999" t="n">
+        <v>292</v>
+      </c>
+      <c r="G2999" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2999" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3000">
+      <c r="A3000" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3000" t="inlineStr">
+        <is>
+          <t>Lyzone</t>
+        </is>
+      </c>
+      <c r="C3000" t="inlineStr">
+        <is>
+          <t>Lison</t>
+        </is>
+      </c>
+      <c r="D3000" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3000" t="n">
+        <v>81</v>
+      </c>
+      <c r="F3000" t="n">
+        <v>290</v>
+      </c>
+      <c r="G3000" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3000" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3001">
+      <c r="A3001" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3001" t="inlineStr">
+        <is>
+          <t>MT35T</t>
+        </is>
+      </c>
+      <c r="C3001" t="inlineStr">
+        <is>
+          <t>Mathilde</t>
+        </is>
+      </c>
+      <c r="D3001" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E3001" t="n">
+        <v>82</v>
+      </c>
+      <c r="F3001" t="n">
+        <v>282</v>
+      </c>
+      <c r="G3001" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3001" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3002">
+      <c r="A3002" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3002" t="inlineStr">
+        <is>
+          <t>Priscilla#4LCAF</t>
+        </is>
+      </c>
+      <c r="C3002" t="inlineStr">
+        <is>
+          <t>Priscilla</t>
+        </is>
+      </c>
+      <c r="D3002" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E3002" t="n">
+        <v>83</v>
+      </c>
+      <c r="F3002" t="n">
+        <v>274</v>
+      </c>
+      <c r="G3002" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3002" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3003">
+      <c r="A3003" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3003" t="inlineStr">
+        <is>
+          <t>Rosa_1009</t>
+        </is>
+      </c>
+      <c r="C3003" t="inlineStr">
+        <is>
+          <t>Rosaline</t>
+        </is>
+      </c>
+      <c r="D3003" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3003" t="n">
+        <v>84</v>
+      </c>
+      <c r="F3003" t="n">
+        <v>274</v>
+      </c>
+      <c r="G3003" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3003" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3004">
+      <c r="A3004" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3004" t="inlineStr">
+        <is>
+          <t>Ceciledp</t>
+        </is>
+      </c>
+      <c r="C3004" t="inlineStr">
+        <is>
+          <t>Cécile</t>
+        </is>
+      </c>
+      <c r="D3004" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3004" t="n">
+        <v>85</v>
+      </c>
+      <c r="F3004" t="n">
+        <v>268</v>
+      </c>
+      <c r="G3004" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3004" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3005">
+      <c r="A3005" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3005" t="inlineStr">
+        <is>
+          <t>PacoSarra</t>
+        </is>
+      </c>
+      <c r="C3005" t="inlineStr">
+        <is>
+          <t>Ibra</t>
+        </is>
+      </c>
+      <c r="D3005" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E3005" t="n">
+        <v>86</v>
+      </c>
+      <c r="F3005" t="n">
+        <v>266</v>
+      </c>
+      <c r="G3005" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3005" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3006">
+      <c r="A3006" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3006" t="inlineStr">
+        <is>
+          <t>dian-bgt</t>
+        </is>
+      </c>
+      <c r="C3006" t="inlineStr">
+        <is>
+          <t>Diane</t>
+        </is>
+      </c>
+      <c r="D3006" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3006" t="n">
+        <v>87</v>
+      </c>
+      <c r="F3006" t="n">
+        <v>265</v>
+      </c>
+      <c r="G3006" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3006" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3007">
+      <c r="A3007" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3007" t="inlineStr">
+        <is>
+          <t>Mylene-Jnt</t>
+        </is>
+      </c>
+      <c r="C3007" t="inlineStr">
+        <is>
+          <t>Mylène</t>
+        </is>
+      </c>
+      <c r="D3007" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E3007" t="n">
+        <v>88</v>
+      </c>
+      <c r="F3007" t="n">
+        <v>258</v>
+      </c>
+      <c r="G3007" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3007" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3008">
+      <c r="A3008" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3008" t="inlineStr">
+        <is>
+          <t>JEVAISGAGNER10</t>
+        </is>
+      </c>
+      <c r="C3008" t="inlineStr">
+        <is>
+          <t>Xavier</t>
+        </is>
+      </c>
+      <c r="D3008" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E3008" t="n">
+        <v>89</v>
+      </c>
+      <c r="F3008" t="n">
+        <v>254</v>
+      </c>
+      <c r="G3008" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3008" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3009">
+      <c r="A3009" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3009" t="inlineStr">
+        <is>
+          <t>Melissagzb</t>
+        </is>
+      </c>
+      <c r="C3009" t="inlineStr">
+        <is>
+          <t>Melissa</t>
+        </is>
+      </c>
+      <c r="D3009" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E3009" t="n">
+        <v>90</v>
+      </c>
+      <c r="F3009" t="n">
+        <v>254</v>
+      </c>
+      <c r="G3009" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3009" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3010">
+      <c r="A3010" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3010" t="inlineStr">
+        <is>
+          <t>K_Marp</t>
+        </is>
+      </c>
+      <c r="C3010" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
+      <c r="D3010" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E3010" t="n">
+        <v>91</v>
+      </c>
+      <c r="F3010" t="n">
+        <v>254</v>
+      </c>
+      <c r="G3010" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3010" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3011">
+      <c r="A3011" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3011" t="inlineStr">
+        <is>
+          <t>A-MOE</t>
+        </is>
+      </c>
+      <c r="C3011" t="inlineStr">
+        <is>
+          <t>Françoise</t>
+        </is>
+      </c>
+      <c r="D3011" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3011" t="n">
+        <v>92</v>
+      </c>
+      <c r="F3011" t="n">
+        <v>254</v>
+      </c>
+      <c r="G3011" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3011" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3012">
+      <c r="A3012" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3012" t="inlineStr">
+        <is>
+          <t>davidd23</t>
+        </is>
+      </c>
+      <c r="C3012" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D3012" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3012" t="n">
+        <v>93</v>
+      </c>
+      <c r="F3012" t="n">
+        <v>249</v>
+      </c>
+      <c r="G3012" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3012" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3013">
+      <c r="A3013" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3013" t="inlineStr">
+        <is>
+          <t>Taylor2901</t>
+        </is>
+      </c>
+      <c r="C3013" t="inlineStr">
+        <is>
+          <t>ousmane</t>
+        </is>
+      </c>
+      <c r="D3013" t="inlineStr"/>
+      <c r="E3013" t="n">
+        <v>94</v>
+      </c>
+      <c r="F3013" t="n">
+        <v>241</v>
+      </c>
+      <c r="G3013" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3013" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3014">
+      <c r="A3014" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3014" t="inlineStr">
+        <is>
+          <t>GLR_PRIME</t>
+        </is>
+      </c>
+      <c r="C3014" t="inlineStr">
+        <is>
+          <t>Gabriel</t>
+        </is>
+      </c>
+      <c r="D3014" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3014" t="n">
+        <v>95</v>
+      </c>
+      <c r="F3014" t="n">
+        <v>234</v>
+      </c>
+      <c r="G3014" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3014" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3015">
+      <c r="A3015" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3015" t="inlineStr">
+        <is>
+          <t>Emma_Noel</t>
+        </is>
+      </c>
+      <c r="C3015" t="inlineStr">
+        <is>
+          <t>Emma</t>
+        </is>
+      </c>
+      <c r="D3015" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E3015" t="n">
+        <v>96</v>
+      </c>
+      <c r="F3015" t="n">
+        <v>232</v>
+      </c>
+      <c r="G3015" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3015" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3016">
+      <c r="A3016" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3016" t="inlineStr">
+        <is>
+          <t>Fa_One</t>
+        </is>
+      </c>
+      <c r="C3016" t="inlineStr">
+        <is>
+          <t>Farah</t>
+        </is>
+      </c>
+      <c r="D3016" t="inlineStr"/>
+      <c r="E3016" t="n">
+        <v>97</v>
+      </c>
+      <c r="F3016" t="n">
+        <v>230</v>
+      </c>
+      <c r="G3016" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3016" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3017">
+      <c r="A3017" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3017" t="inlineStr">
+        <is>
+          <t>SamSamH8</t>
+        </is>
+      </c>
+      <c r="C3017" t="inlineStr">
+        <is>
+          <t>Samia</t>
+        </is>
+      </c>
+      <c r="D3017" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3017" t="n">
+        <v>98</v>
+      </c>
+      <c r="F3017" t="n">
+        <v>223</v>
+      </c>
+      <c r="G3017" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3017" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3018">
+      <c r="A3018" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3018" t="inlineStr">
+        <is>
+          <t>PavelMel</t>
+        </is>
+      </c>
+      <c r="C3018" t="inlineStr">
+        <is>
+          <t>Mélissa</t>
+        </is>
+      </c>
+      <c r="D3018" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E3018" t="n">
+        <v>99</v>
+      </c>
+      <c r="F3018" t="n">
+        <v>208</v>
+      </c>
+      <c r="G3018" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3018" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3019">
+      <c r="A3019" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3019" t="inlineStr">
+        <is>
+          <t>BrickXVI</t>
+        </is>
+      </c>
+      <c r="C3019" t="inlineStr">
+        <is>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="D3019" t="inlineStr"/>
+      <c r="E3019" t="n">
+        <v>100</v>
+      </c>
+      <c r="F3019" t="n">
+        <v>205</v>
+      </c>
+      <c r="G3019" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3019" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3020">
+      <c r="A3020" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3020" t="inlineStr">
+        <is>
+          <t>SabC1</t>
+        </is>
+      </c>
+      <c r="C3020" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="D3020" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3020" t="n">
+        <v>101</v>
+      </c>
+      <c r="F3020" t="n">
+        <v>190</v>
+      </c>
+      <c r="G3020" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3020" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3021">
+      <c r="A3021" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3021" t="inlineStr">
+        <is>
+          <t>Fuzo697</t>
+        </is>
+      </c>
+      <c r="C3021" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D3021" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E3021" t="n">
+        <v>102</v>
+      </c>
+      <c r="F3021" t="n">
+        <v>189</v>
+      </c>
+      <c r="G3021" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3021" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3022">
+      <c r="A3022" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3022" t="inlineStr">
+        <is>
+          <t>LeaBrd</t>
+        </is>
+      </c>
+      <c r="C3022" t="inlineStr">
+        <is>
+          <t>Léa</t>
+        </is>
+      </c>
+      <c r="D3022" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E3022" t="n">
+        <v>103</v>
+      </c>
+      <c r="F3022" t="n">
+        <v>182</v>
+      </c>
+      <c r="G3022" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3022" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3023">
+      <c r="A3023" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3023" t="inlineStr">
+        <is>
+          <t>MxKnight</t>
+        </is>
+      </c>
+      <c r="C3023" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D3023" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E3023" t="n">
+        <v>104</v>
+      </c>
+      <c r="F3023" t="n">
+        <v>180</v>
+      </c>
+      <c r="G3023" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3023" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3024">
+      <c r="A3024" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3024" t="inlineStr">
+        <is>
+          <t>Sab_M45</t>
+        </is>
+      </c>
+      <c r="C3024" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="D3024" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3024" t="n">
+        <v>105</v>
+      </c>
+      <c r="F3024" t="n">
+        <v>180</v>
+      </c>
+      <c r="G3024" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3024" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3025">
+      <c r="A3025" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3025" t="inlineStr">
+        <is>
+          <t>KIKS999</t>
+        </is>
+      </c>
+      <c r="C3025" t="inlineStr">
+        <is>
+          <t>Killian</t>
+        </is>
+      </c>
+      <c r="D3025" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E3025" t="n">
+        <v>106</v>
+      </c>
+      <c r="F3025" t="n">
+        <v>158</v>
+      </c>
+      <c r="G3025" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3025" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3026">
+      <c r="A3026" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3026" t="inlineStr">
+        <is>
+          <t>Laetice2020</t>
+        </is>
+      </c>
+      <c r="C3026" t="inlineStr">
+        <is>
+          <t>Laetitia</t>
+        </is>
+      </c>
+      <c r="D3026" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3026" t="n">
+        <v>107</v>
+      </c>
+      <c r="F3026" t="n">
+        <v>138</v>
+      </c>
+      <c r="G3026" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3026" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3027">
+      <c r="A3027" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3027" t="inlineStr">
+        <is>
+          <t>RBTL</t>
+        </is>
+      </c>
+      <c r="C3027" t="inlineStr">
+        <is>
+          <t>lea</t>
+        </is>
+      </c>
+      <c r="D3027" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E3027" t="n">
+        <v>108</v>
+      </c>
+      <c r="F3027" t="n">
+        <v>138</v>
+      </c>
+      <c r="G3027" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3027" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3028">
+      <c r="A3028" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3028" t="inlineStr">
+        <is>
+          <t>RomainLect</t>
+        </is>
+      </c>
+      <c r="C3028" t="inlineStr">
+        <is>
+          <t>romain</t>
+        </is>
+      </c>
+      <c r="D3028" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E3028" t="n">
+        <v>109</v>
+      </c>
+      <c r="F3028" t="n">
+        <v>108</v>
+      </c>
+      <c r="G3028" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3028" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historique_joueurs.xlsx
+++ b/historique_joueurs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3028"/>
+  <dimension ref="A1:H3137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101624,6 +101624,3684 @@
         <v>0</v>
       </c>
     </row>
+    <row r="3029">
+      <c r="A3029" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3029" t="inlineStr">
+        <is>
+          <t>Nonito20</t>
+        </is>
+      </c>
+      <c r="C3029" t="inlineStr">
+        <is>
+          <t>Arnaud</t>
+        </is>
+      </c>
+      <c r="D3029" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3029" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3029" t="n">
+        <v>1025</v>
+      </c>
+      <c r="G3029" t="n">
+        <v>8</v>
+      </c>
+      <c r="H3029" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3030">
+      <c r="A3030" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3030" t="inlineStr">
+        <is>
+          <t>Ninaaaa</t>
+        </is>
+      </c>
+      <c r="C3030" t="inlineStr">
+        <is>
+          <t>Nina</t>
+        </is>
+      </c>
+      <c r="D3030" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E3030" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3030" t="n">
+        <v>903</v>
+      </c>
+      <c r="G3030" t="n">
+        <v>9</v>
+      </c>
+      <c r="H3030" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3031">
+      <c r="A3031" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3031" t="inlineStr">
+        <is>
+          <t>Mamad_Shelter</t>
+        </is>
+      </c>
+      <c r="C3031" t="inlineStr">
+        <is>
+          <t>Mamadou</t>
+        </is>
+      </c>
+      <c r="D3031" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E3031" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3031" t="n">
+        <v>859</v>
+      </c>
+      <c r="G3031" t="n">
+        <v>9</v>
+      </c>
+      <c r="H3031" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3032">
+      <c r="A3032" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3032" t="inlineStr">
+        <is>
+          <t>WalidSiuuuuu</t>
+        </is>
+      </c>
+      <c r="C3032" t="inlineStr">
+        <is>
+          <t>Walid</t>
+        </is>
+      </c>
+      <c r="D3032" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3032" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3032" t="n">
+        <v>746</v>
+      </c>
+      <c r="G3032" t="n">
+        <v>8</v>
+      </c>
+      <c r="H3032" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3033">
+      <c r="A3033" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3033" t="inlineStr">
+        <is>
+          <t>Stephbreton</t>
+        </is>
+      </c>
+      <c r="C3033" t="inlineStr">
+        <is>
+          <t>STEPHANE</t>
+        </is>
+      </c>
+      <c r="D3033" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E3033" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3033" t="n">
+        <v>741</v>
+      </c>
+      <c r="G3033" t="n">
+        <v>7</v>
+      </c>
+      <c r="H3033" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3034">
+      <c r="A3034" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3034" t="inlineStr">
+        <is>
+          <t>AudreyB225</t>
+        </is>
+      </c>
+      <c r="C3034" t="inlineStr">
+        <is>
+          <t>Audrey</t>
+        </is>
+      </c>
+      <c r="D3034" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E3034" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3034" t="n">
+        <v>733</v>
+      </c>
+      <c r="G3034" t="n">
+        <v>7</v>
+      </c>
+      <c r="H3034" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3035">
+      <c r="A3035" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3035" t="inlineStr">
+        <is>
+          <t>Coucoucassecou</t>
+        </is>
+      </c>
+      <c r="C3035" t="inlineStr">
+        <is>
+          <t>Brayen</t>
+        </is>
+      </c>
+      <c r="D3035" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E3035" t="n">
+        <v>7</v>
+      </c>
+      <c r="F3035" t="n">
+        <v>726</v>
+      </c>
+      <c r="G3035" t="n">
+        <v>8</v>
+      </c>
+      <c r="H3035" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3036">
+      <c r="A3036" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3036" t="inlineStr">
+        <is>
+          <t>GOAT#UE4U8KA6</t>
+        </is>
+      </c>
+      <c r="C3036" t="inlineStr">
+        <is>
+          <t>Jean Baptiste</t>
+        </is>
+      </c>
+      <c r="D3036" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E3036" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3036" t="n">
+        <v>710</v>
+      </c>
+      <c r="G3036" t="n">
+        <v>8</v>
+      </c>
+      <c r="H3036" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3037">
+      <c r="A3037" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3037" t="inlineStr">
+        <is>
+          <t>BOUGA#2JGXP</t>
+        </is>
+      </c>
+      <c r="C3037" t="inlineStr">
+        <is>
+          <t>BOUGA</t>
+        </is>
+      </c>
+      <c r="D3037" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E3037" t="n">
+        <v>9</v>
+      </c>
+      <c r="F3037" t="n">
+        <v>691</v>
+      </c>
+      <c r="G3037" t="n">
+        <v>8</v>
+      </c>
+      <c r="H3037" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3038">
+      <c r="A3038" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3038" t="inlineStr">
+        <is>
+          <t>Filipinho95</t>
+        </is>
+      </c>
+      <c r="C3038" t="inlineStr">
+        <is>
+          <t>Filipe</t>
+        </is>
+      </c>
+      <c r="D3038" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E3038" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3038" t="n">
+        <v>683</v>
+      </c>
+      <c r="G3038" t="n">
+        <v>8</v>
+      </c>
+      <c r="H3038" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3039">
+      <c r="A3039" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3039" t="inlineStr">
+        <is>
+          <t>Anais757817</t>
+        </is>
+      </c>
+      <c r="C3039" t="inlineStr">
+        <is>
+          <t>Anaïs</t>
+        </is>
+      </c>
+      <c r="D3039" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E3039" t="n">
+        <v>11</v>
+      </c>
+      <c r="F3039" t="n">
+        <v>668</v>
+      </c>
+      <c r="G3039" t="n">
+        <v>8</v>
+      </c>
+      <c r="H3039" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3040">
+      <c r="A3040" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3040" t="inlineStr">
+        <is>
+          <t>catherine#5FRTD</t>
+        </is>
+      </c>
+      <c r="C3040" t="inlineStr">
+        <is>
+          <t>catherine</t>
+        </is>
+      </c>
+      <c r="D3040" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3040" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3040" t="n">
+        <v>665</v>
+      </c>
+      <c r="G3040" t="n">
+        <v>8</v>
+      </c>
+      <c r="H3040" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3041">
+      <c r="A3041" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3041" t="inlineStr">
+        <is>
+          <t>SID-F-ANDRE</t>
+        </is>
+      </c>
+      <c r="C3041" t="inlineStr">
+        <is>
+          <t>Denis</t>
+        </is>
+      </c>
+      <c r="D3041" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E3041" t="n">
+        <v>13</v>
+      </c>
+      <c r="F3041" t="n">
+        <v>664</v>
+      </c>
+      <c r="G3041" t="n">
+        <v>7</v>
+      </c>
+      <c r="H3041" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3042">
+      <c r="A3042" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3042" t="inlineStr">
+        <is>
+          <t>Ze_GOAT</t>
+        </is>
+      </c>
+      <c r="C3042" t="inlineStr">
+        <is>
+          <t>Yasser</t>
+        </is>
+      </c>
+      <c r="D3042" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E3042" t="n">
+        <v>14</v>
+      </c>
+      <c r="F3042" t="n">
+        <v>654</v>
+      </c>
+      <c r="G3042" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3042" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3043">
+      <c r="A3043" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3043" t="inlineStr">
+        <is>
+          <t>MagicMath</t>
+        </is>
+      </c>
+      <c r="C3043" t="inlineStr">
+        <is>
+          <t>Mathieu</t>
+        </is>
+      </c>
+      <c r="D3043" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E3043" t="n">
+        <v>15</v>
+      </c>
+      <c r="F3043" t="n">
+        <v>645</v>
+      </c>
+      <c r="G3043" t="n">
+        <v>8</v>
+      </c>
+      <c r="H3043" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3044">
+      <c r="A3044" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3044" t="inlineStr">
+        <is>
+          <t>YassineZ95</t>
+        </is>
+      </c>
+      <c r="C3044" t="inlineStr">
+        <is>
+          <t>Yassine Z</t>
+        </is>
+      </c>
+      <c r="D3044" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E3044" t="n">
+        <v>16</v>
+      </c>
+      <c r="F3044" t="n">
+        <v>640</v>
+      </c>
+      <c r="G3044" t="n">
+        <v>7</v>
+      </c>
+      <c r="H3044" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3045">
+      <c r="A3045" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3045" t="inlineStr">
+        <is>
+          <t>Leo_durable</t>
+        </is>
+      </c>
+      <c r="C3045" t="inlineStr">
+        <is>
+          <t>Leo</t>
+        </is>
+      </c>
+      <c r="D3045" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E3045" t="n">
+        <v>17</v>
+      </c>
+      <c r="F3045" t="n">
+        <v>639</v>
+      </c>
+      <c r="G3045" t="n">
+        <v>8</v>
+      </c>
+      <c r="H3045" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3046">
+      <c r="A3046" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3046" t="inlineStr">
+        <is>
+          <t>Panaff</t>
+        </is>
+      </c>
+      <c r="C3046" t="inlineStr">
+        <is>
+          <t>Panaf</t>
+        </is>
+      </c>
+      <c r="D3046" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E3046" t="n">
+        <v>18</v>
+      </c>
+      <c r="F3046" t="n">
+        <v>631</v>
+      </c>
+      <c r="G3046" t="n">
+        <v>7</v>
+      </c>
+      <c r="H3046" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3047">
+      <c r="A3047" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3047" t="inlineStr">
+        <is>
+          <t>Marion1822</t>
+        </is>
+      </c>
+      <c r="C3047" t="inlineStr">
+        <is>
+          <t>Marion</t>
+        </is>
+      </c>
+      <c r="D3047" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E3047" t="n">
+        <v>19</v>
+      </c>
+      <c r="F3047" t="n">
+        <v>612</v>
+      </c>
+      <c r="G3047" t="n">
+        <v>7</v>
+      </c>
+      <c r="H3047" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3048">
+      <c r="A3048" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3048" t="inlineStr">
+        <is>
+          <t>goat#AD6GS</t>
+        </is>
+      </c>
+      <c r="C3048" t="inlineStr">
+        <is>
+          <t>goat</t>
+        </is>
+      </c>
+      <c r="D3048" t="inlineStr"/>
+      <c r="E3048" t="n">
+        <v>20</v>
+      </c>
+      <c r="F3048" t="n">
+        <v>603</v>
+      </c>
+      <c r="G3048" t="n">
+        <v>8</v>
+      </c>
+      <c r="H3048" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3049">
+      <c r="A3049" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3049" t="inlineStr">
+        <is>
+          <t>EmyEnzo</t>
+        </is>
+      </c>
+      <c r="C3049" t="inlineStr">
+        <is>
+          <t>Emilie</t>
+        </is>
+      </c>
+      <c r="D3049" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E3049" t="n">
+        <v>21</v>
+      </c>
+      <c r="F3049" t="n">
+        <v>601</v>
+      </c>
+      <c r="G3049" t="n">
+        <v>7</v>
+      </c>
+      <c r="H3049" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3050">
+      <c r="A3050" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3050" t="inlineStr">
+        <is>
+          <t>DJOSWA</t>
+        </is>
+      </c>
+      <c r="C3050" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oswaina </t>
+        </is>
+      </c>
+      <c r="D3050" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E3050" t="n">
+        <v>22</v>
+      </c>
+      <c r="F3050" t="n">
+        <v>594</v>
+      </c>
+      <c r="G3050" t="n">
+        <v>7</v>
+      </c>
+      <c r="H3050" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3051">
+      <c r="A3051" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3051" t="inlineStr">
+        <is>
+          <t>Paulasipi1998</t>
+        </is>
+      </c>
+      <c r="C3051" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="D3051" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3051" t="n">
+        <v>23</v>
+      </c>
+      <c r="F3051" t="n">
+        <v>568</v>
+      </c>
+      <c r="G3051" t="n">
+        <v>7</v>
+      </c>
+      <c r="H3051" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3052">
+      <c r="A3052" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3052" t="inlineStr">
+        <is>
+          <t>MyriamAmr</t>
+        </is>
+      </c>
+      <c r="C3052" t="inlineStr">
+        <is>
+          <t>Myriam</t>
+        </is>
+      </c>
+      <c r="D3052" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E3052" t="n">
+        <v>24</v>
+      </c>
+      <c r="F3052" t="n">
+        <v>555</v>
+      </c>
+      <c r="G3052" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3052" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3053">
+      <c r="A3053" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3053" t="inlineStr">
+        <is>
+          <t>FRHTCTD10</t>
+        </is>
+      </c>
+      <c r="C3053" t="inlineStr">
+        <is>
+          <t>Candice</t>
+        </is>
+      </c>
+      <c r="D3053" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E3053" t="n">
+        <v>25</v>
+      </c>
+      <c r="F3053" t="n">
+        <v>551</v>
+      </c>
+      <c r="G3053" t="n">
+        <v>7</v>
+      </c>
+      <c r="H3053" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3054">
+      <c r="A3054" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3054" t="inlineStr">
+        <is>
+          <t>Gronaldo_95</t>
+        </is>
+      </c>
+      <c r="C3054" t="inlineStr">
+        <is>
+          <t>Gronaldo</t>
+        </is>
+      </c>
+      <c r="D3054" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E3054" t="n">
+        <v>26</v>
+      </c>
+      <c r="F3054" t="n">
+        <v>548</v>
+      </c>
+      <c r="G3054" t="n">
+        <v>7</v>
+      </c>
+      <c r="H3054" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3055">
+      <c r="A3055" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3055" t="inlineStr">
+        <is>
+          <t>Emilay</t>
+        </is>
+      </c>
+      <c r="C3055" t="inlineStr">
+        <is>
+          <t>Émilie</t>
+        </is>
+      </c>
+      <c r="D3055" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E3055" t="n">
+        <v>27</v>
+      </c>
+      <c r="F3055" t="n">
+        <v>545</v>
+      </c>
+      <c r="G3055" t="n">
+        <v>7</v>
+      </c>
+      <c r="H3055" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3056">
+      <c r="A3056" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3056" t="inlineStr">
+        <is>
+          <t>HamzaG</t>
+        </is>
+      </c>
+      <c r="C3056" t="inlineStr">
+        <is>
+          <t>Hamza</t>
+        </is>
+      </c>
+      <c r="D3056" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E3056" t="n">
+        <v>28</v>
+      </c>
+      <c r="F3056" t="n">
+        <v>538</v>
+      </c>
+      <c r="G3056" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3056" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3057">
+      <c r="A3057" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3057" t="inlineStr">
+        <is>
+          <t>Yebri</t>
+        </is>
+      </c>
+      <c r="C3057" t="inlineStr">
+        <is>
+          <t>Brieuc</t>
+        </is>
+      </c>
+      <c r="D3057" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3057" t="n">
+        <v>29</v>
+      </c>
+      <c r="F3057" t="n">
+        <v>531</v>
+      </c>
+      <c r="G3057" t="n">
+        <v>7</v>
+      </c>
+      <c r="H3057" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3058">
+      <c r="A3058" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3058" t="inlineStr">
+        <is>
+          <t>Ilan_260_</t>
+        </is>
+      </c>
+      <c r="C3058" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ilann </t>
+        </is>
+      </c>
+      <c r="D3058" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3058" t="n">
+        <v>30</v>
+      </c>
+      <c r="F3058" t="n">
+        <v>524</v>
+      </c>
+      <c r="G3058" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3058" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3059">
+      <c r="A3059" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3059" t="inlineStr">
+        <is>
+          <t>Ouiouiausoleil</t>
+        </is>
+      </c>
+      <c r="C3059" t="inlineStr">
+        <is>
+          <t>Ouissal</t>
+        </is>
+      </c>
+      <c r="D3059" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3059" t="n">
+        <v>31</v>
+      </c>
+      <c r="F3059" t="n">
+        <v>519</v>
+      </c>
+      <c r="G3059" t="n">
+        <v>7</v>
+      </c>
+      <c r="H3059" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3060">
+      <c r="A3060" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3060" t="inlineStr">
+        <is>
+          <t>Leandrocp</t>
+        </is>
+      </c>
+      <c r="C3060" t="inlineStr">
+        <is>
+          <t>Leandro</t>
+        </is>
+      </c>
+      <c r="D3060" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E3060" t="n">
+        <v>32</v>
+      </c>
+      <c r="F3060" t="n">
+        <v>512</v>
+      </c>
+      <c r="G3060" t="n">
+        <v>7</v>
+      </c>
+      <c r="H3060" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3061">
+      <c r="A3061" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3061" t="inlineStr">
+        <is>
+          <t>chaychaychay</t>
+        </is>
+      </c>
+      <c r="C3061" t="inlineStr">
+        <is>
+          <t>Chaymaa</t>
+        </is>
+      </c>
+      <c r="D3061" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E3061" t="n">
+        <v>33</v>
+      </c>
+      <c r="F3061" t="n">
+        <v>512</v>
+      </c>
+      <c r="G3061" t="n">
+        <v>7</v>
+      </c>
+      <c r="H3061" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3062">
+      <c r="A3062" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3062" t="inlineStr">
+        <is>
+          <t>BadrLeo</t>
+        </is>
+      </c>
+      <c r="C3062" t="inlineStr">
+        <is>
+          <t>Badr Leo</t>
+        </is>
+      </c>
+      <c r="D3062" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E3062" t="n">
+        <v>34</v>
+      </c>
+      <c r="F3062" t="n">
+        <v>510</v>
+      </c>
+      <c r="G3062" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3062" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3063">
+      <c r="A3063" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3063" t="inlineStr">
+        <is>
+          <t>MargauxCtln</t>
+        </is>
+      </c>
+      <c r="C3063" t="inlineStr">
+        <is>
+          <t>Margaux</t>
+        </is>
+      </c>
+      <c r="D3063" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E3063" t="n">
+        <v>35</v>
+      </c>
+      <c r="F3063" t="n">
+        <v>507</v>
+      </c>
+      <c r="G3063" t="n">
+        <v>7</v>
+      </c>
+      <c r="H3063" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3064">
+      <c r="A3064" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3064" t="inlineStr">
+        <is>
+          <t>Ppo28</t>
+        </is>
+      </c>
+      <c r="C3064" t="inlineStr">
+        <is>
+          <t>Prescylla</t>
+        </is>
+      </c>
+      <c r="D3064" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E3064" t="n">
+        <v>36</v>
+      </c>
+      <c r="F3064" t="n">
+        <v>498</v>
+      </c>
+      <c r="G3064" t="n">
+        <v>7</v>
+      </c>
+      <c r="H3064" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3065">
+      <c r="A3065" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3065" t="inlineStr">
+        <is>
+          <t>Ambrepic</t>
+        </is>
+      </c>
+      <c r="C3065" t="inlineStr">
+        <is>
+          <t>Ambre</t>
+        </is>
+      </c>
+      <c r="D3065" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E3065" t="n">
+        <v>37</v>
+      </c>
+      <c r="F3065" t="n">
+        <v>498</v>
+      </c>
+      <c r="G3065" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3065" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3066">
+      <c r="A3066" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3066" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="C3066" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="D3066" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E3066" t="n">
+        <v>38</v>
+      </c>
+      <c r="F3066" t="n">
+        <v>496</v>
+      </c>
+      <c r="G3066" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3066" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3067">
+      <c r="A3067" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3067" t="inlineStr">
+        <is>
+          <t>Timy</t>
+        </is>
+      </c>
+      <c r="C3067" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="D3067" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3067" t="n">
+        <v>39</v>
+      </c>
+      <c r="F3067" t="n">
+        <v>494</v>
+      </c>
+      <c r="G3067" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3067" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3068">
+      <c r="A3068" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3068" t="inlineStr">
+        <is>
+          <t>C4M</t>
+        </is>
+      </c>
+      <c r="C3068" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D3068" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3068" t="n">
+        <v>40</v>
+      </c>
+      <c r="F3068" t="n">
+        <v>490</v>
+      </c>
+      <c r="G3068" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3068" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3069">
+      <c r="A3069" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3069" t="inlineStr">
+        <is>
+          <t>Maruyama</t>
+        </is>
+      </c>
+      <c r="C3069" t="inlineStr">
+        <is>
+          <t>Gabrielle</t>
+        </is>
+      </c>
+      <c r="D3069" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E3069" t="n">
+        <v>41</v>
+      </c>
+      <c r="F3069" t="n">
+        <v>484</v>
+      </c>
+      <c r="G3069" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3069" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3070">
+      <c r="A3070" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3070" t="inlineStr">
+        <is>
+          <t>Valentine___</t>
+        </is>
+      </c>
+      <c r="C3070" t="inlineStr">
+        <is>
+          <t>Valentine</t>
+        </is>
+      </c>
+      <c r="D3070" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E3070" t="n">
+        <v>42</v>
+      </c>
+      <c r="F3070" t="n">
+        <v>483</v>
+      </c>
+      <c r="G3070" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3070" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3071">
+      <c r="A3071" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3071" t="inlineStr">
+        <is>
+          <t>Cleem22</t>
+        </is>
+      </c>
+      <c r="C3071" t="inlineStr">
+        <is>
+          <t>Clemence</t>
+        </is>
+      </c>
+      <c r="D3071" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3071" t="n">
+        <v>43</v>
+      </c>
+      <c r="F3071" t="n">
+        <v>478</v>
+      </c>
+      <c r="G3071" t="n">
+        <v>7</v>
+      </c>
+      <c r="H3071" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3072">
+      <c r="A3072" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3072" t="inlineStr">
+        <is>
+          <t>Camss</t>
+        </is>
+      </c>
+      <c r="C3072" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D3072" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3072" t="n">
+        <v>44</v>
+      </c>
+      <c r="F3072" t="n">
+        <v>478</v>
+      </c>
+      <c r="G3072" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3072" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3073">
+      <c r="A3073" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3073" t="inlineStr">
+        <is>
+          <t>Marie__92</t>
+        </is>
+      </c>
+      <c r="C3073" t="inlineStr">
+        <is>
+          <t>Marie</t>
+        </is>
+      </c>
+      <c r="D3073" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E3073" t="n">
+        <v>45</v>
+      </c>
+      <c r="F3073" t="n">
+        <v>477</v>
+      </c>
+      <c r="G3073" t="n">
+        <v>7</v>
+      </c>
+      <c r="H3073" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3074">
+      <c r="A3074" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3074" t="inlineStr">
+        <is>
+          <t>Fethinho</t>
+        </is>
+      </c>
+      <c r="C3074" t="inlineStr">
+        <is>
+          <t>Fethi</t>
+        </is>
+      </c>
+      <c r="D3074" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E3074" t="n">
+        <v>46</v>
+      </c>
+      <c r="F3074" t="n">
+        <v>474</v>
+      </c>
+      <c r="G3074" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3074" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3075">
+      <c r="A3075" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3075" t="inlineStr">
+        <is>
+          <t>Teddbear</t>
+        </is>
+      </c>
+      <c r="C3075" t="inlineStr">
+        <is>
+          <t>Tedy</t>
+        </is>
+      </c>
+      <c r="D3075" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E3075" t="n">
+        <v>47</v>
+      </c>
+      <c r="F3075" t="n">
+        <v>463</v>
+      </c>
+      <c r="G3075" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3075" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3076">
+      <c r="A3076" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3076" t="inlineStr">
+        <is>
+          <t>Romain_JO</t>
+        </is>
+      </c>
+      <c r="C3076" t="inlineStr">
+        <is>
+          <t>Romain J</t>
+        </is>
+      </c>
+      <c r="D3076" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E3076" t="n">
+        <v>48</v>
+      </c>
+      <c r="F3076" t="n">
+        <v>460</v>
+      </c>
+      <c r="G3076" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3076" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3077">
+      <c r="A3077" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3077" t="inlineStr">
+        <is>
+          <t>Exia95</t>
+        </is>
+      </c>
+      <c r="C3077" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D3077" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E3077" t="n">
+        <v>49</v>
+      </c>
+      <c r="F3077" t="n">
+        <v>451</v>
+      </c>
+      <c r="G3077" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3077" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3078">
+      <c r="A3078" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3078" t="inlineStr">
+        <is>
+          <t>Kaliced</t>
+        </is>
+      </c>
+      <c r="C3078" t="inlineStr">
+        <is>
+          <t>Kalice</t>
+        </is>
+      </c>
+      <c r="D3078" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E3078" t="n">
+        <v>50</v>
+      </c>
+      <c r="F3078" t="n">
+        <v>448</v>
+      </c>
+      <c r="G3078" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3078" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3079">
+      <c r="A3079" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3079" t="inlineStr">
+        <is>
+          <t>Chadia__</t>
+        </is>
+      </c>
+      <c r="C3079" t="inlineStr">
+        <is>
+          <t>Chadia</t>
+        </is>
+      </c>
+      <c r="D3079" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3079" t="n">
+        <v>51</v>
+      </c>
+      <c r="F3079" t="n">
+        <v>436</v>
+      </c>
+      <c r="G3079" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3079" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3080">
+      <c r="A3080" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3080" t="inlineStr">
+        <is>
+          <t>Matt#4B4CU</t>
+        </is>
+      </c>
+      <c r="C3080" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="D3080" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E3080" t="n">
+        <v>52</v>
+      </c>
+      <c r="F3080" t="n">
+        <v>436</v>
+      </c>
+      <c r="G3080" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3080" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3081">
+      <c r="A3081" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3081" t="inlineStr">
+        <is>
+          <t>Cindie_JJA</t>
+        </is>
+      </c>
+      <c r="C3081" t="inlineStr">
+        <is>
+          <t>Cindie</t>
+        </is>
+      </c>
+      <c r="D3081" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E3081" t="n">
+        <v>53</v>
+      </c>
+      <c r="F3081" t="n">
+        <v>433</v>
+      </c>
+      <c r="G3081" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3081" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3082">
+      <c r="A3082" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3082" t="inlineStr">
+        <is>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="C3082" t="inlineStr">
+        <is>
+          <t>Julie</t>
+        </is>
+      </c>
+      <c r="D3082" t="inlineStr"/>
+      <c r="E3082" t="n">
+        <v>54</v>
+      </c>
+      <c r="F3082" t="n">
+        <v>430</v>
+      </c>
+      <c r="G3082" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3082" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3083">
+      <c r="A3083" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3083" t="inlineStr">
+        <is>
+          <t>Soraya-Y</t>
+        </is>
+      </c>
+      <c r="C3083" t="inlineStr">
+        <is>
+          <t>Soraya</t>
+        </is>
+      </c>
+      <c r="D3083" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E3083" t="n">
+        <v>55</v>
+      </c>
+      <c r="F3083" t="n">
+        <v>418</v>
+      </c>
+      <c r="G3083" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3083" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3084">
+      <c r="A3084" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3084" t="inlineStr">
+        <is>
+          <t>Mr-Worldwide</t>
+        </is>
+      </c>
+      <c r="C3084" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="D3084" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E3084" t="n">
+        <v>56</v>
+      </c>
+      <c r="F3084" t="n">
+        <v>411</v>
+      </c>
+      <c r="G3084" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3084" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3085">
+      <c r="A3085" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3085" t="inlineStr">
+        <is>
+          <t>Camillewbl</t>
+        </is>
+      </c>
+      <c r="C3085" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D3085" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E3085" t="n">
+        <v>57</v>
+      </c>
+      <c r="F3085" t="n">
+        <v>405</v>
+      </c>
+      <c r="G3085" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3085" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3086">
+      <c r="A3086" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3086" t="inlineStr">
+        <is>
+          <t>PANENKANY</t>
+        </is>
+      </c>
+      <c r="C3086" t="inlineStr">
+        <is>
+          <t>Damien</t>
+        </is>
+      </c>
+      <c r="D3086" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E3086" t="n">
+        <v>58</v>
+      </c>
+      <c r="F3086" t="n">
+        <v>404</v>
+      </c>
+      <c r="G3086" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3086" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3087">
+      <c r="A3087" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3087" t="inlineStr">
+        <is>
+          <t>JKInternational</t>
+        </is>
+      </c>
+      <c r="C3087" t="inlineStr">
+        <is>
+          <t>Joachim</t>
+        </is>
+      </c>
+      <c r="D3087" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3087" t="n">
+        <v>59</v>
+      </c>
+      <c r="F3087" t="n">
+        <v>396</v>
+      </c>
+      <c r="G3087" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3087" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3088">
+      <c r="A3088" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3088" t="inlineStr">
+        <is>
+          <t>Erwan#4G91X</t>
+        </is>
+      </c>
+      <c r="C3088" t="inlineStr">
+        <is>
+          <t>Erwan</t>
+        </is>
+      </c>
+      <c r="D3088" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E3088" t="n">
+        <v>60</v>
+      </c>
+      <c r="F3088" t="n">
+        <v>393</v>
+      </c>
+      <c r="G3088" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3088" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3089">
+      <c r="A3089" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3089" t="inlineStr">
+        <is>
+          <t>Pipou931</t>
+        </is>
+      </c>
+      <c r="C3089" t="inlineStr">
+        <is>
+          <t>Juliie</t>
+        </is>
+      </c>
+      <c r="D3089" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3089" t="n">
+        <v>61</v>
+      </c>
+      <c r="F3089" t="n">
+        <v>389</v>
+      </c>
+      <c r="G3089" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3089" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3090">
+      <c r="A3090" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3090" t="inlineStr">
+        <is>
+          <t>Seesee</t>
+        </is>
+      </c>
+      <c r="C3090" t="inlineStr">
+        <is>
+          <t>Selver</t>
+        </is>
+      </c>
+      <c r="D3090" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E3090" t="n">
+        <v>62</v>
+      </c>
+      <c r="F3090" t="n">
+        <v>382</v>
+      </c>
+      <c r="G3090" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3090" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3091">
+      <c r="A3091" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3091" t="inlineStr">
+        <is>
+          <t>lenaaik</t>
+        </is>
+      </c>
+      <c r="C3091" t="inlineStr">
+        <is>
+          <t>Lénaïk</t>
+        </is>
+      </c>
+      <c r="D3091" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3091" t="n">
+        <v>63</v>
+      </c>
+      <c r="F3091" t="n">
+        <v>382</v>
+      </c>
+      <c r="G3091" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3091" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3092">
+      <c r="A3092" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3092" t="inlineStr">
+        <is>
+          <t>Elisewiss</t>
+        </is>
+      </c>
+      <c r="C3092" t="inlineStr">
+        <is>
+          <t>Elise</t>
+        </is>
+      </c>
+      <c r="D3092" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E3092" t="n">
+        <v>64</v>
+      </c>
+      <c r="F3092" t="n">
+        <v>382</v>
+      </c>
+      <c r="G3092" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3092" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3093">
+      <c r="A3093" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3093" t="inlineStr">
+        <is>
+          <t>ChrisKr1Deg1</t>
+        </is>
+      </c>
+      <c r="C3093" t="inlineStr">
+        <is>
+          <t>christophe</t>
+        </is>
+      </c>
+      <c r="D3093" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E3093" t="n">
+        <v>65</v>
+      </c>
+      <c r="F3093" t="n">
+        <v>382</v>
+      </c>
+      <c r="G3093" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3093" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3094">
+      <c r="A3094" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3094" t="inlineStr">
+        <is>
+          <t>1993ahm</t>
+        </is>
+      </c>
+      <c r="C3094" t="inlineStr">
+        <is>
+          <t>Ahmed</t>
+        </is>
+      </c>
+      <c r="D3094" t="inlineStr"/>
+      <c r="E3094" t="n">
+        <v>66</v>
+      </c>
+      <c r="F3094" t="n">
+        <v>381</v>
+      </c>
+      <c r="G3094" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3094" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3095">
+      <c r="A3095" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3095" t="inlineStr">
+        <is>
+          <t>Devilrock95</t>
+        </is>
+      </c>
+      <c r="C3095" t="inlineStr">
+        <is>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="D3095" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E3095" t="n">
+        <v>67</v>
+      </c>
+      <c r="F3095" t="n">
+        <v>370</v>
+      </c>
+      <c r="G3095" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3095" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3096">
+      <c r="A3096" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3096" t="inlineStr">
+        <is>
+          <t>GLR_PRIME</t>
+        </is>
+      </c>
+      <c r="C3096" t="inlineStr">
+        <is>
+          <t>Gabriel</t>
+        </is>
+      </c>
+      <c r="D3096" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3096" t="n">
+        <v>68</v>
+      </c>
+      <c r="F3096" t="n">
+        <v>369</v>
+      </c>
+      <c r="G3096" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3096" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3097">
+      <c r="A3097" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3097" t="inlineStr">
+        <is>
+          <t>Droit_au_but7723</t>
+        </is>
+      </c>
+      <c r="C3097" t="inlineStr">
+        <is>
+          <t>Calixthe</t>
+        </is>
+      </c>
+      <c r="D3097" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E3097" t="n">
+        <v>69</v>
+      </c>
+      <c r="F3097" t="n">
+        <v>358</v>
+      </c>
+      <c r="G3097" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3097" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3098">
+      <c r="A3098" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3098" t="inlineStr">
+        <is>
+          <t>Davido#4BZ54</t>
+        </is>
+      </c>
+      <c r="C3098" t="inlineStr">
+        <is>
+          <t>Davido</t>
+        </is>
+      </c>
+      <c r="D3098" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3098" t="n">
+        <v>70</v>
+      </c>
+      <c r="F3098" t="n">
+        <v>349</v>
+      </c>
+      <c r="G3098" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3098" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3099">
+      <c r="A3099" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3099" t="inlineStr">
+        <is>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="C3099" t="inlineStr">
+        <is>
+          <t>François</t>
+        </is>
+      </c>
+      <c r="D3099" t="inlineStr"/>
+      <c r="E3099" t="n">
+        <v>71</v>
+      </c>
+      <c r="F3099" t="n">
+        <v>344</v>
+      </c>
+      <c r="G3099" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3099" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3100">
+      <c r="A3100" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3100" t="inlineStr">
+        <is>
+          <t>Krol#4R8XC</t>
+        </is>
+      </c>
+      <c r="C3100" t="inlineStr">
+        <is>
+          <t>Krol</t>
+        </is>
+      </c>
+      <c r="D3100" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3100" t="n">
+        <v>72</v>
+      </c>
+      <c r="F3100" t="n">
+        <v>342</v>
+      </c>
+      <c r="G3100" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3100" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3101">
+      <c r="A3101" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3101" t="inlineStr">
+        <is>
+          <t>LilianeB</t>
+        </is>
+      </c>
+      <c r="C3101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liliane </t>
+        </is>
+      </c>
+      <c r="D3101" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3101" t="n">
+        <v>73</v>
+      </c>
+      <c r="F3101" t="n">
+        <v>337</v>
+      </c>
+      <c r="G3101" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3101" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3102">
+      <c r="A3102" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3102" t="inlineStr">
+        <is>
+          <t>Kolas</t>
+        </is>
+      </c>
+      <c r="C3102" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D3102" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E3102" t="n">
+        <v>74</v>
+      </c>
+      <c r="F3102" t="n">
+        <v>324</v>
+      </c>
+      <c r="G3102" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3102" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3103">
+      <c r="A3103" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3103" t="inlineStr">
+        <is>
+          <t>JeremFZ</t>
+        </is>
+      </c>
+      <c r="C3103" t="inlineStr">
+        <is>
+          <t>Jérémy</t>
+        </is>
+      </c>
+      <c r="D3103" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3103" t="n">
+        <v>75</v>
+      </c>
+      <c r="F3103" t="n">
+        <v>322</v>
+      </c>
+      <c r="G3103" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3104">
+      <c r="A3104" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3104" t="inlineStr">
+        <is>
+          <t>MatuRenard</t>
+        </is>
+      </c>
+      <c r="C3104" t="inlineStr">
+        <is>
+          <t>Mathias</t>
+        </is>
+      </c>
+      <c r="D3104" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E3104" t="n">
+        <v>76</v>
+      </c>
+      <c r="F3104" t="n">
+        <v>318</v>
+      </c>
+      <c r="G3104" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3104" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3105">
+      <c r="A3105" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3105" t="inlineStr">
+        <is>
+          <t>Liliuus</t>
+        </is>
+      </c>
+      <c r="C3105" t="inlineStr">
+        <is>
+          <t>Lilia</t>
+        </is>
+      </c>
+      <c r="D3105" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3105" t="n">
+        <v>77</v>
+      </c>
+      <c r="F3105" t="n">
+        <v>318</v>
+      </c>
+      <c r="G3105" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3105" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3106">
+      <c r="A3106" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3106" t="inlineStr">
+        <is>
+          <t>abihuts</t>
+        </is>
+      </c>
+      <c r="C3106" t="inlineStr">
+        <is>
+          <t>Antonio Moctezuma</t>
+        </is>
+      </c>
+      <c r="D3106" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3106" t="n">
+        <v>78</v>
+      </c>
+      <c r="F3106" t="n">
+        <v>303</v>
+      </c>
+      <c r="G3106" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3107">
+      <c r="A3107" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3107" t="inlineStr">
+        <is>
+          <t>Daviddesco1</t>
+        </is>
+      </c>
+      <c r="C3107" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D3107" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3107" t="n">
+        <v>79</v>
+      </c>
+      <c r="F3107" t="n">
+        <v>302</v>
+      </c>
+      <c r="G3107" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3108">
+      <c r="A3108" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3108" t="inlineStr">
+        <is>
+          <t>GOAT#UE2WM8M9</t>
+        </is>
+      </c>
+      <c r="C3108" t="inlineStr">
+        <is>
+          <t>Marilena</t>
+        </is>
+      </c>
+      <c r="D3108" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E3108" t="n">
+        <v>80</v>
+      </c>
+      <c r="F3108" t="n">
+        <v>296</v>
+      </c>
+      <c r="G3108" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3108" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3109">
+      <c r="A3109" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3109" t="inlineStr">
+        <is>
+          <t>WIL1610</t>
+        </is>
+      </c>
+      <c r="C3109" t="inlineStr">
+        <is>
+          <t>William</t>
+        </is>
+      </c>
+      <c r="D3109" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E3109" t="n">
+        <v>81</v>
+      </c>
+      <c r="F3109" t="n">
+        <v>292</v>
+      </c>
+      <c r="G3109" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3109" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3110">
+      <c r="A3110" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3110" t="inlineStr">
+        <is>
+          <t>Lyzone</t>
+        </is>
+      </c>
+      <c r="C3110" t="inlineStr">
+        <is>
+          <t>Lison</t>
+        </is>
+      </c>
+      <c r="D3110" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3110" t="n">
+        <v>82</v>
+      </c>
+      <c r="F3110" t="n">
+        <v>290</v>
+      </c>
+      <c r="G3110" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3111">
+      <c r="A3111" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3111" t="inlineStr">
+        <is>
+          <t>MT35T</t>
+        </is>
+      </c>
+      <c r="C3111" t="inlineStr">
+        <is>
+          <t>Mathilde</t>
+        </is>
+      </c>
+      <c r="D3111" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E3111" t="n">
+        <v>83</v>
+      </c>
+      <c r="F3111" t="n">
+        <v>282</v>
+      </c>
+      <c r="G3111" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3112">
+      <c r="A3112" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3112" t="inlineStr">
+        <is>
+          <t>Priscilla#4LCAF</t>
+        </is>
+      </c>
+      <c r="C3112" t="inlineStr">
+        <is>
+          <t>Priscilla</t>
+        </is>
+      </c>
+      <c r="D3112" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E3112" t="n">
+        <v>84</v>
+      </c>
+      <c r="F3112" t="n">
+        <v>274</v>
+      </c>
+      <c r="G3112" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3112" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3113">
+      <c r="A3113" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3113" t="inlineStr">
+        <is>
+          <t>Rosa_1009</t>
+        </is>
+      </c>
+      <c r="C3113" t="inlineStr">
+        <is>
+          <t>Rosaline</t>
+        </is>
+      </c>
+      <c r="D3113" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3113" t="n">
+        <v>85</v>
+      </c>
+      <c r="F3113" t="n">
+        <v>274</v>
+      </c>
+      <c r="G3113" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3113" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3114">
+      <c r="A3114" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3114" t="inlineStr">
+        <is>
+          <t>Ceciledp</t>
+        </is>
+      </c>
+      <c r="C3114" t="inlineStr">
+        <is>
+          <t>Cécile</t>
+        </is>
+      </c>
+      <c r="D3114" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3114" t="n">
+        <v>86</v>
+      </c>
+      <c r="F3114" t="n">
+        <v>268</v>
+      </c>
+      <c r="G3114" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3115">
+      <c r="A3115" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3115" t="inlineStr">
+        <is>
+          <t>PacoSarra</t>
+        </is>
+      </c>
+      <c r="C3115" t="inlineStr">
+        <is>
+          <t>Ibra</t>
+        </is>
+      </c>
+      <c r="D3115" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E3115" t="n">
+        <v>87</v>
+      </c>
+      <c r="F3115" t="n">
+        <v>266</v>
+      </c>
+      <c r="G3115" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3115" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3116">
+      <c r="A3116" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3116" t="inlineStr">
+        <is>
+          <t>dian-bgt</t>
+        </is>
+      </c>
+      <c r="C3116" t="inlineStr">
+        <is>
+          <t>Diane</t>
+        </is>
+      </c>
+      <c r="D3116" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3116" t="n">
+        <v>88</v>
+      </c>
+      <c r="F3116" t="n">
+        <v>265</v>
+      </c>
+      <c r="G3116" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3116" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3117">
+      <c r="A3117" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3117" t="inlineStr">
+        <is>
+          <t>Mylene-Jnt</t>
+        </is>
+      </c>
+      <c r="C3117" t="inlineStr">
+        <is>
+          <t>Mylène</t>
+        </is>
+      </c>
+      <c r="D3117" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E3117" t="n">
+        <v>89</v>
+      </c>
+      <c r="F3117" t="n">
+        <v>258</v>
+      </c>
+      <c r="G3117" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3118">
+      <c r="A3118" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3118" t="inlineStr">
+        <is>
+          <t>JEVAISGAGNER10</t>
+        </is>
+      </c>
+      <c r="C3118" t="inlineStr">
+        <is>
+          <t>Xavier</t>
+        </is>
+      </c>
+      <c r="D3118" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E3118" t="n">
+        <v>90</v>
+      </c>
+      <c r="F3118" t="n">
+        <v>254</v>
+      </c>
+      <c r="G3118" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3119">
+      <c r="A3119" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3119" t="inlineStr">
+        <is>
+          <t>Melissagzb</t>
+        </is>
+      </c>
+      <c r="C3119" t="inlineStr">
+        <is>
+          <t>Melissa</t>
+        </is>
+      </c>
+      <c r="D3119" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E3119" t="n">
+        <v>91</v>
+      </c>
+      <c r="F3119" t="n">
+        <v>254</v>
+      </c>
+      <c r="G3119" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3120">
+      <c r="A3120" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3120" t="inlineStr">
+        <is>
+          <t>K_Marp</t>
+        </is>
+      </c>
+      <c r="C3120" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
+      <c r="D3120" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E3120" t="n">
+        <v>92</v>
+      </c>
+      <c r="F3120" t="n">
+        <v>254</v>
+      </c>
+      <c r="G3120" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3121">
+      <c r="A3121" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3121" t="inlineStr">
+        <is>
+          <t>A-MOE</t>
+        </is>
+      </c>
+      <c r="C3121" t="inlineStr">
+        <is>
+          <t>Françoise</t>
+        </is>
+      </c>
+      <c r="D3121" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3121" t="n">
+        <v>93</v>
+      </c>
+      <c r="F3121" t="n">
+        <v>254</v>
+      </c>
+      <c r="G3121" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3122">
+      <c r="A3122" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3122" t="inlineStr">
+        <is>
+          <t>davidd23</t>
+        </is>
+      </c>
+      <c r="C3122" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D3122" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3122" t="n">
+        <v>94</v>
+      </c>
+      <c r="F3122" t="n">
+        <v>249</v>
+      </c>
+      <c r="G3122" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3123">
+      <c r="A3123" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3123" t="inlineStr">
+        <is>
+          <t>Taylor2901</t>
+        </is>
+      </c>
+      <c r="C3123" t="inlineStr">
+        <is>
+          <t>ousmane</t>
+        </is>
+      </c>
+      <c r="D3123" t="inlineStr"/>
+      <c r="E3123" t="n">
+        <v>95</v>
+      </c>
+      <c r="F3123" t="n">
+        <v>241</v>
+      </c>
+      <c r="G3123" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3124">
+      <c r="A3124" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3124" t="inlineStr">
+        <is>
+          <t>Emma_Noel</t>
+        </is>
+      </c>
+      <c r="C3124" t="inlineStr">
+        <is>
+          <t>Emma</t>
+        </is>
+      </c>
+      <c r="D3124" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E3124" t="n">
+        <v>96</v>
+      </c>
+      <c r="F3124" t="n">
+        <v>232</v>
+      </c>
+      <c r="G3124" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3124" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3125">
+      <c r="A3125" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3125" t="inlineStr">
+        <is>
+          <t>Fa_One</t>
+        </is>
+      </c>
+      <c r="C3125" t="inlineStr">
+        <is>
+          <t>Farah</t>
+        </is>
+      </c>
+      <c r="D3125" t="inlineStr"/>
+      <c r="E3125" t="n">
+        <v>97</v>
+      </c>
+      <c r="F3125" t="n">
+        <v>230</v>
+      </c>
+      <c r="G3125" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3125" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3126">
+      <c r="A3126" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3126" t="inlineStr">
+        <is>
+          <t>SamSamH8</t>
+        </is>
+      </c>
+      <c r="C3126" t="inlineStr">
+        <is>
+          <t>Samia</t>
+        </is>
+      </c>
+      <c r="D3126" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3126" t="n">
+        <v>98</v>
+      </c>
+      <c r="F3126" t="n">
+        <v>223</v>
+      </c>
+      <c r="G3126" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3127">
+      <c r="A3127" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3127" t="inlineStr">
+        <is>
+          <t>PavelMel</t>
+        </is>
+      </c>
+      <c r="C3127" t="inlineStr">
+        <is>
+          <t>Mélissa</t>
+        </is>
+      </c>
+      <c r="D3127" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E3127" t="n">
+        <v>99</v>
+      </c>
+      <c r="F3127" t="n">
+        <v>208</v>
+      </c>
+      <c r="G3127" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3128">
+      <c r="A3128" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3128" t="inlineStr">
+        <is>
+          <t>BrickXVI</t>
+        </is>
+      </c>
+      <c r="C3128" t="inlineStr">
+        <is>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="D3128" t="inlineStr"/>
+      <c r="E3128" t="n">
+        <v>100</v>
+      </c>
+      <c r="F3128" t="n">
+        <v>205</v>
+      </c>
+      <c r="G3128" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3129">
+      <c r="A3129" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3129" t="inlineStr">
+        <is>
+          <t>SabC1</t>
+        </is>
+      </c>
+      <c r="C3129" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="D3129" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3129" t="n">
+        <v>101</v>
+      </c>
+      <c r="F3129" t="n">
+        <v>190</v>
+      </c>
+      <c r="G3129" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3130">
+      <c r="A3130" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3130" t="inlineStr">
+        <is>
+          <t>Fuzo697</t>
+        </is>
+      </c>
+      <c r="C3130" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D3130" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E3130" t="n">
+        <v>102</v>
+      </c>
+      <c r="F3130" t="n">
+        <v>189</v>
+      </c>
+      <c r="G3130" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3131">
+      <c r="A3131" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3131" t="inlineStr">
+        <is>
+          <t>LeaBrd</t>
+        </is>
+      </c>
+      <c r="C3131" t="inlineStr">
+        <is>
+          <t>Léa</t>
+        </is>
+      </c>
+      <c r="D3131" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E3131" t="n">
+        <v>103</v>
+      </c>
+      <c r="F3131" t="n">
+        <v>182</v>
+      </c>
+      <c r="G3131" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3132">
+      <c r="A3132" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3132" t="inlineStr">
+        <is>
+          <t>MxKnight</t>
+        </is>
+      </c>
+      <c r="C3132" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D3132" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
+      <c r="E3132" t="n">
+        <v>104</v>
+      </c>
+      <c r="F3132" t="n">
+        <v>180</v>
+      </c>
+      <c r="G3132" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3133">
+      <c r="A3133" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3133" t="inlineStr">
+        <is>
+          <t>Sab_M45</t>
+        </is>
+      </c>
+      <c r="C3133" t="inlineStr">
+        <is>
+          <t>Sabrina</t>
+        </is>
+      </c>
+      <c r="D3133" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3133" t="n">
+        <v>105</v>
+      </c>
+      <c r="F3133" t="n">
+        <v>180</v>
+      </c>
+      <c r="G3133" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3134">
+      <c r="A3134" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3134" t="inlineStr">
+        <is>
+          <t>KIKS999</t>
+        </is>
+      </c>
+      <c r="C3134" t="inlineStr">
+        <is>
+          <t>Killian</t>
+        </is>
+      </c>
+      <c r="D3134" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="E3134" t="n">
+        <v>106</v>
+      </c>
+      <c r="F3134" t="n">
+        <v>158</v>
+      </c>
+      <c r="G3134" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3134" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3135">
+      <c r="A3135" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3135" t="inlineStr">
+        <is>
+          <t>Laetice2020</t>
+        </is>
+      </c>
+      <c r="C3135" t="inlineStr">
+        <is>
+          <t>Laetitia</t>
+        </is>
+      </c>
+      <c r="D3135" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E3135" t="n">
+        <v>107</v>
+      </c>
+      <c r="F3135" t="n">
+        <v>138</v>
+      </c>
+      <c r="G3135" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3136">
+      <c r="A3136" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3136" t="inlineStr">
+        <is>
+          <t>RBTL</t>
+        </is>
+      </c>
+      <c r="C3136" t="inlineStr">
+        <is>
+          <t>lea</t>
+        </is>
+      </c>
+      <c r="D3136" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="E3136" t="n">
+        <v>108</v>
+      </c>
+      <c r="F3136" t="n">
+        <v>138</v>
+      </c>
+      <c r="G3136" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3137">
+      <c r="A3137" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3137" t="inlineStr">
+        <is>
+          <t>RomainLect</t>
+        </is>
+      </c>
+      <c r="C3137" t="inlineStr">
+        <is>
+          <t>romain</t>
+        </is>
+      </c>
+      <c r="D3137" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="E3137" t="n">
+        <v>109</v>
+      </c>
+      <c r="F3137" t="n">
+        <v>108</v>
+      </c>
+      <c r="G3137" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3137" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
